--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4992" uniqueCount="4346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5142" uniqueCount="4447">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -13052,6 +13052,309 @@
   </si>
   <si>
     <t>Простыня из варёного хлопка 300х300 - М - Сапфировый</t>
+  </si>
+  <si>
+    <t>4610594534063</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро макси на резинке 180х200х30 - 125 - "Миндаль" 1х1</t>
+  </si>
+  <si>
+    <t>02-03-2026</t>
+  </si>
+  <si>
+    <t>4610594534056</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь семейное - М - 142 - Биг Бен</t>
+  </si>
+  <si>
+    <t>4610594534049</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь семейное - М - 142 - Белый Бамбук</t>
+  </si>
+  <si>
+    <t>4610594534032</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное на резинке 140х200х30 - М - 120 - Литера</t>
+  </si>
+  <si>
+    <t>4610594534025</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Жатка семейное - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4610594534018</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - М - Виридан</t>
+  </si>
+  <si>
+    <t>4610594534001</t>
+  </si>
+  <si>
+    <t>Простыня Жатка на резинке 140х200х40 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4610594533998</t>
+  </si>
+  <si>
+    <t>Наволочка Жатка 70х70 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4610594533981</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Андреза"</t>
+  </si>
+  <si>
+    <t>4610594533974</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин на резинке 230х230х40 - 130 - "Дивуар" 1х1</t>
+  </si>
+  <si>
+    <t>4610594533967</t>
+  </si>
+  <si>
+    <t>Простыня полисатин на резинке 140х200х20 - "Зайга"</t>
+  </si>
+  <si>
+    <t>4610594533950</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - "Флафи" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4610594533943</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё твил-сатин 2 спальное - "Сахарная роза" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4610594533936</t>
+  </si>
+  <si>
+    <t>Простыня Жатка на резинке 120х200х30 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4610594533929</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 130 - "Лучезарный" 1х1</t>
+  </si>
+  <si>
+    <t>4610594533912</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200 х 220 - "Темный изумруд"</t>
+  </si>
+  <si>
+    <t>4610594533905</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Севим"</t>
+  </si>
+  <si>
+    <t>4610594533899</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное на резинке 120х200х30 - "Лавандис"</t>
+  </si>
+  <si>
+    <t>4610594533882</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро макси - 130 - "Олива" 1х1</t>
+  </si>
+  <si>
+    <t>4610594533875</t>
+  </si>
+  <si>
+    <t>Пододеяльник из поплина 150 х 200 - М - Ночной колпак</t>
+  </si>
+  <si>
+    <t>4610594533868</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - "Флафи"</t>
+  </si>
+  <si>
+    <t>4610594533851</t>
+  </si>
+  <si>
+    <t>Пододеяльник из поплина 150 х 200 - М - Колечки А+В</t>
+  </si>
+  <si>
+    <t>4610594533844</t>
+  </si>
+  <si>
+    <t>Простыня полисатин на резинке 80х200х20 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4610594533837</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное с Евро простыней - 135 - "Золотистая ваниль" 1х1 с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4610594533820</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Жатка семейное на резинке 160х200х30 - "Элефас"</t>
+  </si>
+  <si>
+    <t>4610594533813</t>
+  </si>
+  <si>
+    <t>Простыня из поплина 200 х 220 - М - Грей Стайл</t>
+  </si>
+  <si>
+    <t>4610594533806</t>
+  </si>
+  <si>
+    <t>Наволочка твил-сатин 40 х 60 - "Облачка"</t>
+  </si>
+  <si>
+    <t>4610594533790</t>
+  </si>
+  <si>
+    <t>Наволочка из сатина 40 х 60 - М - 120 - Баден Гольд</t>
+  </si>
+  <si>
+    <t>4610594533783</t>
+  </si>
+  <si>
+    <t>Наволочка твил-сатин 40 х 60 - "Солнечные лучи"</t>
+  </si>
+  <si>
+    <t>4610594533776</t>
+  </si>
+  <si>
+    <t>Простыня микросатин на резинке 180х200х40 - "Розанна"</t>
+  </si>
+  <si>
+    <t>4610594533769</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин на резинке 180х200х20 - "Гриновей" 1х1</t>
+  </si>
+  <si>
+    <t>4610594533752</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп Микрофибра Евро макси на резинке 180х200х30 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4610594533745</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное на резинке 140х200х30 - "Экзотический"</t>
+  </si>
+  <si>
+    <t>4610594533738</t>
+  </si>
+  <si>
+    <t>Наволочка из поплина 60 х 60 - М - Бонди</t>
+  </si>
+  <si>
+    <t>4610594533721</t>
+  </si>
+  <si>
+    <t>Пододеяльник из твил сатина 175 х 215 - М - Архитектор</t>
+  </si>
+  <si>
+    <t>4610594533714</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок на резинке 200х220х30 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4610594533707</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 145 х 215 - "Экзотический"</t>
+  </si>
+  <si>
+    <t>4610594533691</t>
+  </si>
+  <si>
+    <t>Простыня круглая Жатка на резинке 200х200х30 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4610594533684</t>
+  </si>
+  <si>
+    <t>Простыня Жатка на резинке 140х200х20 - "Лунный Одуванчик"</t>
+  </si>
+  <si>
+    <t>4610594533677</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - "Глария"</t>
+  </si>
+  <si>
+    <t>4610594533660</t>
+  </si>
+  <si>
+    <t>Наволочка из бязи 50 х 50 - М - 142 ГОСТ - Черный</t>
+  </si>
+  <si>
+    <t>4610594533653</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Олуфими"</t>
+  </si>
+  <si>
+    <t>4610594533646</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Олуфими"</t>
+  </si>
+  <si>
+    <t>4610594533639</t>
+  </si>
+  <si>
+    <t>Пододеяльник из страйп сатина 145 х 215 - М - 140 - Белый Люкс 3х3</t>
+  </si>
+  <si>
+    <t>4610594533622</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 200х220 - 130 - "Летний дождь" 1х1</t>
+  </si>
+  <si>
+    <t>4610594533615</t>
+  </si>
+  <si>
+    <t>Простыня из поплина на резинке 160 х 200 х 20 - М - Глазурь</t>
+  </si>
+  <si>
+    <t>4610594533608</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4610594533592</t>
+  </si>
+  <si>
+    <t>Пододеяльник Жатка 145х215 - "Леопардовый Сон"</t>
+  </si>
+  <si>
+    <t>4610594533585</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 200х200 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4610594533578</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Белава"</t>
   </si>
 </sst>
 </file>
@@ -32739,6 +33042,556 @@
         <v>4265</v>
       </c>
     </row>
+    <row r="2167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2167" t="s">
+        <v>4346</v>
+      </c>
+      <c r="B2167" t="s">
+        <v>4347</v>
+      </c>
+      <c r="C2167" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2168" t="s">
+        <v>4349</v>
+      </c>
+      <c r="B2168" t="s">
+        <v>4350</v>
+      </c>
+      <c r="C2168" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2169" t="s">
+        <v>4351</v>
+      </c>
+      <c r="B2169" t="s">
+        <v>4352</v>
+      </c>
+      <c r="C2169" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2170" t="s">
+        <v>4353</v>
+      </c>
+      <c r="B2170" t="s">
+        <v>4354</v>
+      </c>
+      <c r="C2170" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2171" t="s">
+        <v>4355</v>
+      </c>
+      <c r="B2171" t="s">
+        <v>4356</v>
+      </c>
+      <c r="C2171" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2172" t="s">
+        <v>4357</v>
+      </c>
+      <c r="B2172" t="s">
+        <v>4358</v>
+      </c>
+      <c r="C2172" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2173" t="s">
+        <v>4359</v>
+      </c>
+      <c r="B2173" t="s">
+        <v>4360</v>
+      </c>
+      <c r="C2173" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2174" t="s">
+        <v>4361</v>
+      </c>
+      <c r="B2174" t="s">
+        <v>4362</v>
+      </c>
+      <c r="C2174" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2175" t="s">
+        <v>4363</v>
+      </c>
+      <c r="B2175" t="s">
+        <v>4364</v>
+      </c>
+      <c r="C2175" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2176" t="s">
+        <v>4365</v>
+      </c>
+      <c r="B2176" t="s">
+        <v>4366</v>
+      </c>
+      <c r="C2176" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2177" t="s">
+        <v>4367</v>
+      </c>
+      <c r="B2177" t="s">
+        <v>4368</v>
+      </c>
+      <c r="C2177" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2178" t="s">
+        <v>4369</v>
+      </c>
+      <c r="B2178" t="s">
+        <v>4370</v>
+      </c>
+      <c r="C2178" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2179" t="s">
+        <v>4371</v>
+      </c>
+      <c r="B2179" t="s">
+        <v>4372</v>
+      </c>
+      <c r="C2179" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2180" t="s">
+        <v>4373</v>
+      </c>
+      <c r="B2180" t="s">
+        <v>4374</v>
+      </c>
+      <c r="C2180" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2181" t="s">
+        <v>4375</v>
+      </c>
+      <c r="B2181" t="s">
+        <v>4376</v>
+      </c>
+      <c r="C2181" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2182" t="s">
+        <v>4377</v>
+      </c>
+      <c r="B2182" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C2182" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2183" t="s">
+        <v>4379</v>
+      </c>
+      <c r="B2183" t="s">
+        <v>4380</v>
+      </c>
+      <c r="C2183" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2184" t="s">
+        <v>4381</v>
+      </c>
+      <c r="B2184" t="s">
+        <v>4382</v>
+      </c>
+      <c r="C2184" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2185" t="s">
+        <v>4383</v>
+      </c>
+      <c r="B2185" t="s">
+        <v>4384</v>
+      </c>
+      <c r="C2185" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2186" t="s">
+        <v>4385</v>
+      </c>
+      <c r="B2186" t="s">
+        <v>4386</v>
+      </c>
+      <c r="C2186" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2187" t="s">
+        <v>4387</v>
+      </c>
+      <c r="B2187" t="s">
+        <v>4388</v>
+      </c>
+      <c r="C2187" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2188" t="s">
+        <v>4389</v>
+      </c>
+      <c r="B2188" t="s">
+        <v>4390</v>
+      </c>
+      <c r="C2188" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2189" t="s">
+        <v>4391</v>
+      </c>
+      <c r="B2189" t="s">
+        <v>4392</v>
+      </c>
+      <c r="C2189" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2190" t="s">
+        <v>4393</v>
+      </c>
+      <c r="B2190" t="s">
+        <v>4394</v>
+      </c>
+      <c r="C2190" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2191" t="s">
+        <v>4395</v>
+      </c>
+      <c r="B2191" t="s">
+        <v>4396</v>
+      </c>
+      <c r="C2191" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2192" t="s">
+        <v>4397</v>
+      </c>
+      <c r="B2192" t="s">
+        <v>4398</v>
+      </c>
+      <c r="C2192" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2193" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B2193" t="s">
+        <v>4400</v>
+      </c>
+      <c r="C2193" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2194" t="s">
+        <v>4401</v>
+      </c>
+      <c r="B2194" t="s">
+        <v>4402</v>
+      </c>
+      <c r="C2194" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2195" t="s">
+        <v>4403</v>
+      </c>
+      <c r="B2195" t="s">
+        <v>4404</v>
+      </c>
+      <c r="C2195" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2196" t="s">
+        <v>4405</v>
+      </c>
+      <c r="B2196" t="s">
+        <v>4406</v>
+      </c>
+      <c r="C2196" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2197" t="s">
+        <v>4407</v>
+      </c>
+      <c r="B2197" t="s">
+        <v>4408</v>
+      </c>
+      <c r="C2197" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2198" t="s">
+        <v>4409</v>
+      </c>
+      <c r="B2198" t="s">
+        <v>4410</v>
+      </c>
+      <c r="C2198" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2199" t="s">
+        <v>4411</v>
+      </c>
+      <c r="B2199" t="s">
+        <v>4412</v>
+      </c>
+      <c r="C2199" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2200" t="s">
+        <v>4413</v>
+      </c>
+      <c r="B2200" t="s">
+        <v>4414</v>
+      </c>
+      <c r="C2200" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2201" t="s">
+        <v>4415</v>
+      </c>
+      <c r="B2201" t="s">
+        <v>4416</v>
+      </c>
+      <c r="C2201" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2202" t="s">
+        <v>4417</v>
+      </c>
+      <c r="B2202" t="s">
+        <v>4418</v>
+      </c>
+      <c r="C2202" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2203" t="s">
+        <v>4419</v>
+      </c>
+      <c r="B2203" t="s">
+        <v>4420</v>
+      </c>
+      <c r="C2203" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2204" t="s">
+        <v>4421</v>
+      </c>
+      <c r="B2204" t="s">
+        <v>4422</v>
+      </c>
+      <c r="C2204" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2205" t="s">
+        <v>4423</v>
+      </c>
+      <c r="B2205" t="s">
+        <v>4424</v>
+      </c>
+      <c r="C2205" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2206" t="s">
+        <v>4425</v>
+      </c>
+      <c r="B2206" t="s">
+        <v>4426</v>
+      </c>
+      <c r="C2206" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2207" t="s">
+        <v>4427</v>
+      </c>
+      <c r="B2207" t="s">
+        <v>4428</v>
+      </c>
+      <c r="C2207" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2208" t="s">
+        <v>4429</v>
+      </c>
+      <c r="B2208" t="s">
+        <v>4430</v>
+      </c>
+      <c r="C2208" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2209" t="s">
+        <v>4431</v>
+      </c>
+      <c r="B2209" t="s">
+        <v>4432</v>
+      </c>
+      <c r="C2209" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2210" t="s">
+        <v>4433</v>
+      </c>
+      <c r="B2210" t="s">
+        <v>4434</v>
+      </c>
+      <c r="C2210" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2211" t="s">
+        <v>4435</v>
+      </c>
+      <c r="B2211" t="s">
+        <v>4436</v>
+      </c>
+      <c r="C2211" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2212" t="s">
+        <v>4437</v>
+      </c>
+      <c r="B2212" t="s">
+        <v>4438</v>
+      </c>
+      <c r="C2212" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2213" t="s">
+        <v>4439</v>
+      </c>
+      <c r="B2213" t="s">
+        <v>4440</v>
+      </c>
+      <c r="C2213" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2214" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B2214" t="s">
+        <v>4442</v>
+      </c>
+      <c r="C2214" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2215" t="s">
+        <v>4443</v>
+      </c>
+      <c r="B2215" t="s">
+        <v>4444</v>
+      </c>
+      <c r="C2215" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2216" t="s">
+        <v>4445</v>
+      </c>
+      <c r="B2216" t="s">
+        <v>4446</v>
+      </c>
+      <c r="C2216" t="s">
+        <v>4348</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5142" uniqueCount="4447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5202" uniqueCount="4488">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -13355,6 +13355,129 @@
   </si>
   <si>
     <t>Пододеяльник полисатин 150х200 - "Белава"</t>
+  </si>
+  <si>
+    <t>4610594534254</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х50 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>03-03-2026</t>
+  </si>
+  <si>
+    <t>4610594534247</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Элефас"</t>
+  </si>
+  <si>
+    <t>4610594534230</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - 130 - "Летний дождь" 1х1</t>
+  </si>
+  <si>
+    <t>4610594534223</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 142 ГОСТ - Бирюза</t>
+  </si>
+  <si>
+    <t>4610594534216</t>
+  </si>
+  <si>
+    <t>Простыня полисатин на резинке 180х200х40 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4610594534209</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 180х220 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4610594534193</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - М - Меропа</t>
+  </si>
+  <si>
+    <t>4610594534186</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин семейное на резинке 160х200х30 - "Гуголету" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4610594534179</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х60 - Сердечко</t>
+  </si>
+  <si>
+    <t>4610594534162</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Папоротниковый"</t>
+  </si>
+  <si>
+    <t>4610594534155</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Песочная роза"</t>
+  </si>
+  <si>
+    <t>4610594534148</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4610594534131</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро на резинке 160х200х30 - "Флорал" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4610594534124</t>
+  </si>
+  <si>
+    <t>Наволочка ранфорс 50х50 - Белый</t>
+  </si>
+  <si>
+    <t>4610594534117</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 125 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4610594534100</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4610594534094</t>
+  </si>
+  <si>
+    <t>Простыня полисатин на резинке 120х200х40 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4610594534087</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Глубь"</t>
+  </si>
+  <si>
+    <t>4610594534070</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Казимира"</t>
+  </si>
+  <si>
+    <t>4610594534261</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное - М - 125 - Голубая бирюза</t>
   </si>
 </sst>
 </file>
@@ -33592,6 +33715,226 @@
         <v>4348</v>
       </c>
     </row>
+    <row r="2217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2217" t="s">
+        <v>4447</v>
+      </c>
+      <c r="B2217" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C2217" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2218" t="s">
+        <v>4450</v>
+      </c>
+      <c r="B2218" t="s">
+        <v>4451</v>
+      </c>
+      <c r="C2218" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2219" t="s">
+        <v>4452</v>
+      </c>
+      <c r="B2219" t="s">
+        <v>4453</v>
+      </c>
+      <c r="C2219" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2220" t="s">
+        <v>4454</v>
+      </c>
+      <c r="B2220" t="s">
+        <v>4455</v>
+      </c>
+      <c r="C2220" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2221" t="s">
+        <v>4456</v>
+      </c>
+      <c r="B2221" t="s">
+        <v>4457</v>
+      </c>
+      <c r="C2221" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2222" t="s">
+        <v>4458</v>
+      </c>
+      <c r="B2222" t="s">
+        <v>4459</v>
+      </c>
+      <c r="C2222" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2223" t="s">
+        <v>4460</v>
+      </c>
+      <c r="B2223" t="s">
+        <v>4461</v>
+      </c>
+      <c r="C2223" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2224" t="s">
+        <v>4462</v>
+      </c>
+      <c r="B2224" t="s">
+        <v>4463</v>
+      </c>
+      <c r="C2224" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2225" t="s">
+        <v>4464</v>
+      </c>
+      <c r="B2225" t="s">
+        <v>4465</v>
+      </c>
+      <c r="C2225" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2226" t="s">
+        <v>4466</v>
+      </c>
+      <c r="B2226" t="s">
+        <v>4467</v>
+      </c>
+      <c r="C2226" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2227" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B2227" t="s">
+        <v>4469</v>
+      </c>
+      <c r="C2227" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2228" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B2228" t="s">
+        <v>4471</v>
+      </c>
+      <c r="C2228" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2229" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B2229" t="s">
+        <v>4473</v>
+      </c>
+      <c r="C2229" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2230" t="s">
+        <v>4474</v>
+      </c>
+      <c r="B2230" t="s">
+        <v>4475</v>
+      </c>
+      <c r="C2230" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2231" t="s">
+        <v>4476</v>
+      </c>
+      <c r="B2231" t="s">
+        <v>4477</v>
+      </c>
+      <c r="C2231" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2232" t="s">
+        <v>4478</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>4479</v>
+      </c>
+      <c r="C2232" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2233" t="s">
+        <v>4480</v>
+      </c>
+      <c r="B2233" t="s">
+        <v>4481</v>
+      </c>
+      <c r="C2233" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2234" t="s">
+        <v>4482</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>4483</v>
+      </c>
+      <c r="C2234" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2235" t="s">
+        <v>4484</v>
+      </c>
+      <c r="B2235" t="s">
+        <v>4485</v>
+      </c>
+      <c r="C2235" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2236" t="s">
+        <v>4486</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>4487</v>
+      </c>
+      <c r="C2236" t="s">
+        <v>4449</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5202" uniqueCount="4488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5253" uniqueCount="4523">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -13478,6 +13478,111 @@
   </si>
   <si>
     <t>КПБ Постельное бельё сатин 1,5 спальное - М - 125 - Голубая бирюза</t>
+  </si>
+  <si>
+    <t>4610594534438</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Серо-зелёный</t>
+  </si>
+  <si>
+    <t>04-03-2026</t>
+  </si>
+  <si>
+    <t>4610594534421</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - 142 ГОСТ - Оранжевый</t>
+  </si>
+  <si>
+    <t>4610594534414</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё креп-жатка 2 спальное с Евро простыней - М - 80 - Теплые Пожелания с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4610594534407</t>
+  </si>
+  <si>
+    <t>Простыня поплин 150х220 - "Бриллиантовые кружева"</t>
+  </si>
+  <si>
+    <t>4610594534391</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х220 - "Мишка в лесу"</t>
+  </si>
+  <si>
+    <t>4610594534384</t>
+  </si>
+  <si>
+    <t>Простыня жатка 240х260 - "Угольная Паутинка"</t>
+  </si>
+  <si>
+    <t>4610594534377</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Макена"</t>
+  </si>
+  <si>
+    <t>4610594534360</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - "Ферниз"</t>
+  </si>
+  <si>
+    <t>4610594534353</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё твил-сатин Евро - "Фернанда"</t>
+  </si>
+  <si>
+    <t>4610594534346</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 120х200х20 - "Стильные девчонки"</t>
+  </si>
+  <si>
+    <t>4610594534339</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное на резинке 120х200х30 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4610594534322</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - "Зелёный Страйп"</t>
+  </si>
+  <si>
+    <t>4610594534315</t>
+  </si>
+  <si>
+    <t>Простыня бязь 220х240 - Белое облако</t>
+  </si>
+  <si>
+    <t>4610594534308</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 40х60 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4610594534292</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 140х200х30 - "Марисоль"</t>
+  </si>
+  <si>
+    <t>4610594534285</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное на резинке 160х200х20 - М - Белое облако</t>
+  </si>
+  <si>
+    <t>4610594534278</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - "Лилизари"</t>
   </si>
 </sst>
 </file>
@@ -33935,6 +34040,193 @@
         <v>4449</v>
       </c>
     </row>
+    <row r="2237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2237" t="s">
+        <v>4488</v>
+      </c>
+      <c r="B2237" t="s">
+        <v>4489</v>
+      </c>
+      <c r="C2237" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2238" t="s">
+        <v>4491</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>4492</v>
+      </c>
+      <c r="C2238" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2239" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B2239" t="s">
+        <v>4494</v>
+      </c>
+      <c r="C2239" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2240" t="s">
+        <v>4495</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>4496</v>
+      </c>
+      <c r="C2240" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2241" t="s">
+        <v>4497</v>
+      </c>
+      <c r="B2241" t="s">
+        <v>4498</v>
+      </c>
+      <c r="C2241" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2242" t="s">
+        <v>4499</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>4500</v>
+      </c>
+      <c r="C2242" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2243" t="s">
+        <v>4501</v>
+      </c>
+      <c r="B2243" t="s">
+        <v>4502</v>
+      </c>
+      <c r="C2243" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2244" t="s">
+        <v>4503</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>4504</v>
+      </c>
+      <c r="C2244" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2245" t="s">
+        <v>4505</v>
+      </c>
+      <c r="B2245" t="s">
+        <v>4506</v>
+      </c>
+      <c r="C2245" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2246" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>4508</v>
+      </c>
+      <c r="C2246" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2247" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B2247" t="s">
+        <v>4510</v>
+      </c>
+      <c r="C2247" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2248" t="s">
+        <v>4511</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>4512</v>
+      </c>
+      <c r="C2248" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2249" t="s">
+        <v>4513</v>
+      </c>
+      <c r="B2249" t="s">
+        <v>4514</v>
+      </c>
+      <c r="C2249" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2250" t="s">
+        <v>4515</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>4516</v>
+      </c>
+      <c r="C2250" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2251" t="s">
+        <v>4517</v>
+      </c>
+      <c r="B2251" t="s">
+        <v>4518</v>
+      </c>
+      <c r="C2251" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2252" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B2252" t="s">
+        <v>4520</v>
+      </c>
+      <c r="C2252" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2253" t="s">
+        <v>4521</v>
+      </c>
+      <c r="B2253" t="s">
+        <v>4522</v>
+      </c>
+      <c r="C2253" t="s">
+        <v>4490</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_AE8FA9646D3454CED120E60533556CAAAF8A3150" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
+    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5253" uniqueCount="4523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="4564">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -40,7 +41,7 @@
     <t>4630460960383</t>
   </si>
   <si>
-    <t>Пододеяльник из тенселя 220 х 240 - М - Королевский пурпур</t>
+    <t>Пододеяльник из тенселя 220х240 - М - Королевский пурпур</t>
   </si>
   <si>
     <t>4630460960376</t>
@@ -12691,13 +12692,13 @@
     <t>4610594532908</t>
   </si>
   <si>
-    <t>Наволочка Жатка 70х70 - "Лесная Мелодия"</t>
+    <t>Наволочка жатка 70х70 - "Лесная Мелодия"</t>
   </si>
   <si>
     <t>4610594532892</t>
   </si>
   <si>
-    <t>Наволочка Жатка 50х70 - "Лесная Мелодия"</t>
+    <t>Наволочка жатка 50х70 - "Лесная Мелодия"</t>
   </si>
   <si>
     <t>4610594532885</t>
@@ -13583,35 +13584,158 @@
   </si>
   <si>
     <t>Пододеяльник поплин 150х200 - "Лилизари"</t>
+  </si>
+  <si>
+    <t>4610594534636</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - "Ягуар"</t>
+  </si>
+  <si>
+    <t>05-03-2026</t>
+  </si>
+  <si>
+    <t>4610594534629</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4610594534612</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 175х215 - М - 80 - Витражи</t>
+  </si>
+  <si>
+    <t>4610594534605</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Гуголету"</t>
+  </si>
+  <si>
+    <t>4610594534599</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 175х215 - "Гуголету"</t>
+  </si>
+  <si>
+    <t>4610594534582</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Гуголету"</t>
+  </si>
+  <si>
+    <t>4610594534575</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4610594534568</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Малика"</t>
+  </si>
+  <si>
+    <t>4610594534551</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - "Астролябия" А+В</t>
+  </si>
+  <si>
+    <t>4610594534544</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 145х215 - "Лесная Мелодия"</t>
+  </si>
+  <si>
+    <t>4610594534537</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 - Сиреневые маки</t>
+  </si>
+  <si>
+    <t>4610594534520</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х40 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4610594534513</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 60х60 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4610594534506</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Селадон наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594534490</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 240х260 - М - 130 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4610594534483</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 140х200х30 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4610594534476</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Инспайр"</t>
+  </si>
+  <si>
+    <t>4610594534469</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - М - Розариум А+В</t>
+  </si>
+  <si>
+    <t>4610594534452</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 140х200х30 - "Белава"</t>
+  </si>
+  <si>
+    <t>4610594534445</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 150х200 - "Графитовый Зигзаг"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -13637,10 +13761,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -13664,7 +13796,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -13941,22 +14073,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P11478"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="177" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13985,7 +14117,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -13993,7 +14125,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -14001,7 +14133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -14009,7 +14141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -14017,7 +14149,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -14025,7 +14157,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -14033,7 +14165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -14041,7 +14173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -14049,7 +14181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -14057,7 +14189,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -14065,7 +14197,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -14073,7 +14205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -25857,7 +25989,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -25865,7 +25997,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -25873,7 +26005,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -25881,7 +26013,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -25889,7 +26021,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -25897,7 +26029,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -25905,7 +26037,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -25913,7 +26045,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -25921,7 +26053,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -25929,7 +26061,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -25937,7 +26069,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -25945,7 +26077,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -25953,7 +26085,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -25961,7 +26093,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -25969,7 +26101,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -34227,13 +34359,233 @@
         <v>4490</v>
       </c>
     </row>
+    <row r="2254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2254" t="s">
+        <v>4523</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>4524</v>
+      </c>
+      <c r="C2254" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2255" t="s">
+        <v>4526</v>
+      </c>
+      <c r="B2255" t="s">
+        <v>4527</v>
+      </c>
+      <c r="C2255" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2256" t="s">
+        <v>4528</v>
+      </c>
+      <c r="B2256" t="s">
+        <v>4529</v>
+      </c>
+      <c r="C2256" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2257" t="s">
+        <v>4530</v>
+      </c>
+      <c r="B2257" t="s">
+        <v>4531</v>
+      </c>
+      <c r="C2257" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2258" t="s">
+        <v>4532</v>
+      </c>
+      <c r="B2258" t="s">
+        <v>4533</v>
+      </c>
+      <c r="C2258" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2259" t="s">
+        <v>4534</v>
+      </c>
+      <c r="B2259" t="s">
+        <v>4535</v>
+      </c>
+      <c r="C2259" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2260" t="s">
+        <v>4536</v>
+      </c>
+      <c r="B2260" t="s">
+        <v>4537</v>
+      </c>
+      <c r="C2260" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2261" t="s">
+        <v>4538</v>
+      </c>
+      <c r="B2261" t="s">
+        <v>4539</v>
+      </c>
+      <c r="C2261" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2262" t="s">
+        <v>4540</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>4541</v>
+      </c>
+      <c r="C2262" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2263" t="s">
+        <v>4542</v>
+      </c>
+      <c r="B2263" t="s">
+        <v>4543</v>
+      </c>
+      <c r="C2263" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2264" t="s">
+        <v>4544</v>
+      </c>
+      <c r="B2264" t="s">
+        <v>4545</v>
+      </c>
+      <c r="C2264" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2265" t="s">
+        <v>4546</v>
+      </c>
+      <c r="B2265" t="s">
+        <v>4547</v>
+      </c>
+      <c r="C2265" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2266" t="s">
+        <v>4548</v>
+      </c>
+      <c r="B2266" t="s">
+        <v>4549</v>
+      </c>
+      <c r="C2266" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2267" t="s">
+        <v>4550</v>
+      </c>
+      <c r="B2267" t="s">
+        <v>4551</v>
+      </c>
+      <c r="C2267" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2268" t="s">
+        <v>4552</v>
+      </c>
+      <c r="B2268" t="s">
+        <v>4553</v>
+      </c>
+      <c r="C2268" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2269" t="s">
+        <v>4554</v>
+      </c>
+      <c r="B2269" t="s">
+        <v>4555</v>
+      </c>
+      <c r="C2269" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2270" t="s">
+        <v>4556</v>
+      </c>
+      <c r="B2270" t="s">
+        <v>4557</v>
+      </c>
+      <c r="C2270" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2271" t="s">
+        <v>4558</v>
+      </c>
+      <c r="B2271" t="s">
+        <v>4559</v>
+      </c>
+      <c r="C2271" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2272" t="s">
+        <v>4560</v>
+      </c>
+      <c r="B2272" t="s">
+        <v>4561</v>
+      </c>
+      <c r="C2272" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2273" t="s">
+        <v>4562</v>
+      </c>
+      <c r="B2273" t="s">
+        <v>4563</v>
+      </c>
+      <c r="C2273" t="s">
+        <v>4525</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>
-    <row r="4890" ht="26.25" customHeight="1" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="4890" spans="7:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G4890" s="7"/>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
@@ -34249,6 +34601,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_AE8FA9646D3454CED120E60533556CAAAF8A3150" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="4564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5382" uniqueCount="4611">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -13707,35 +13706,176 @@
   </si>
   <si>
     <t>Пододеяльник жатка 150х200 - "Графитовый Зигзаг"</t>
+  </si>
+  <si>
+    <t>4610594534865</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 140х200х30 - "Кианит" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>06-03-2026</t>
+  </si>
+  <si>
+    <t>4610594534858</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Бонетто"</t>
+  </si>
+  <si>
+    <t>4610594534841</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - "Бонетто"</t>
+  </si>
+  <si>
+    <t>4610594534834</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро резинка 160х200х30 - "Фиолетовый Шёпот"</t>
+  </si>
+  <si>
+    <t>4610594534827</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - 4217 Бежевый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594534810</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Горчица наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594534803</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - М - 60S 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4610594534797</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х10 - 142 ГОСТ - Серый</t>
+  </si>
+  <si>
+    <t>4610594534780</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь семейное - "Танец крыльев"</t>
+  </si>
+  <si>
+    <t>4610594534773</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - Сливочно-кремовый</t>
+  </si>
+  <si>
+    <t>4610594534766</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Ритва"</t>
+  </si>
+  <si>
+    <t>4610594534759</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 160х200х30 - Каштановый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594534742</t>
+  </si>
+  <si>
+    <t>Наволочка бязь детская 70х70 - Царевна</t>
+  </si>
+  <si>
+    <t>4610594534735</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное резинка 160х200х30 - "Камара"</t>
+  </si>
+  <si>
+    <t>4610594534728</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль Евро-макси - 110 - Белоснежный луч</t>
+  </si>
+  <si>
+    <t>4610594534711</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 140х200х30 - "Лиловый тауп"</t>
+  </si>
+  <si>
+    <t>4610594534704</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 300х300 - "Нева"</t>
+  </si>
+  <si>
+    <t>4610594534698</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 200х200х30 - "Туманная Аура"</t>
+  </si>
+  <si>
+    <t>4610594534681</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 200х200х30 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4610594534674</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное Евро простыня - Пыльная роза наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594534667</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 120 - Пантеон А+В</t>
+  </si>
+  <si>
+    <t>4610594534650</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - М - Санто Стефано</t>
+  </si>
+  <si>
+    <t>4610594534643</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 80х200х10 - "Эдже"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -13761,18 +13901,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -13796,7 +13928,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -14073,22 +14205,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:P11478"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="177" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -14117,7 +14249,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -14125,7 +14257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -14133,7 +14265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -14141,7 +14273,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -14149,7 +14281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -14157,7 +14289,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -14165,7 +14297,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -14173,7 +14305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -14181,7 +14313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -14189,7 +14321,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -14197,7 +14329,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -14205,7 +14337,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -25989,7 +26121,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -25997,7 +26129,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -26005,7 +26137,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -26013,7 +26145,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -26021,7 +26153,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -26029,7 +26161,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -26037,7 +26169,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -26045,7 +26177,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -26053,7 +26185,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -26061,7 +26193,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -26069,7 +26201,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -26077,7 +26209,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -26085,7 +26217,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -26093,7 +26225,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -26101,7 +26233,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -34579,13 +34711,266 @@
         <v>4525</v>
       </c>
     </row>
+    <row r="2274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2274" t="s">
+        <v>4564</v>
+      </c>
+      <c r="B2274" t="s">
+        <v>4565</v>
+      </c>
+      <c r="C2274" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2275" t="s">
+        <v>4567</v>
+      </c>
+      <c r="B2275" t="s">
+        <v>4568</v>
+      </c>
+      <c r="C2275" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2276" t="s">
+        <v>4569</v>
+      </c>
+      <c r="B2276" t="s">
+        <v>4570</v>
+      </c>
+      <c r="C2276" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2277" t="s">
+        <v>4571</v>
+      </c>
+      <c r="B2277" t="s">
+        <v>4572</v>
+      </c>
+      <c r="C2277" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2278" t="s">
+        <v>4573</v>
+      </c>
+      <c r="B2278" t="s">
+        <v>4574</v>
+      </c>
+      <c r="C2278" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2279" t="s">
+        <v>4575</v>
+      </c>
+      <c r="B2279" t="s">
+        <v>4576</v>
+      </c>
+      <c r="C2279" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2280" t="s">
+        <v>4577</v>
+      </c>
+      <c r="B2280" t="s">
+        <v>4578</v>
+      </c>
+      <c r="C2280" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2281" t="s">
+        <v>4579</v>
+      </c>
+      <c r="B2281" t="s">
+        <v>4580</v>
+      </c>
+      <c r="C2281" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2282" t="s">
+        <v>4581</v>
+      </c>
+      <c r="B2282" t="s">
+        <v>4582</v>
+      </c>
+      <c r="C2282" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2283" t="s">
+        <v>4583</v>
+      </c>
+      <c r="B2283" t="s">
+        <v>4584</v>
+      </c>
+      <c r="C2283" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2284" t="s">
+        <v>4585</v>
+      </c>
+      <c r="B2284" t="s">
+        <v>4586</v>
+      </c>
+      <c r="C2284" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2285" t="s">
+        <v>4587</v>
+      </c>
+      <c r="B2285" t="s">
+        <v>4588</v>
+      </c>
+      <c r="C2285" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2286" t="s">
+        <v>4589</v>
+      </c>
+      <c r="B2286" t="s">
+        <v>4590</v>
+      </c>
+      <c r="C2286" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2287" t="s">
+        <v>4591</v>
+      </c>
+      <c r="B2287" t="s">
+        <v>4592</v>
+      </c>
+      <c r="C2287" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2288" t="s">
+        <v>4593</v>
+      </c>
+      <c r="B2288" t="s">
+        <v>4594</v>
+      </c>
+      <c r="C2288" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2289" t="s">
+        <v>4595</v>
+      </c>
+      <c r="B2289" t="s">
+        <v>4596</v>
+      </c>
+      <c r="C2289" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2290" t="s">
+        <v>4597</v>
+      </c>
+      <c r="B2290" t="s">
+        <v>4598</v>
+      </c>
+      <c r="C2290" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2291" t="s">
+        <v>4599</v>
+      </c>
+      <c r="B2291" t="s">
+        <v>4600</v>
+      </c>
+      <c r="C2291" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2292" t="s">
+        <v>4601</v>
+      </c>
+      <c r="B2292" t="s">
+        <v>4602</v>
+      </c>
+      <c r="C2292" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2293" t="s">
+        <v>4603</v>
+      </c>
+      <c r="B2293" t="s">
+        <v>4604</v>
+      </c>
+      <c r="C2293" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2294" t="s">
+        <v>4605</v>
+      </c>
+      <c r="B2294" t="s">
+        <v>4606</v>
+      </c>
+      <c r="C2294" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2295" t="s">
+        <v>4607</v>
+      </c>
+      <c r="B2295" t="s">
+        <v>4608</v>
+      </c>
+      <c r="C2295" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2296" t="s">
+        <v>4609</v>
+      </c>
+      <c r="B2296" t="s">
+        <v>4610</v>
+      </c>
+      <c r="C2296" t="s">
+        <v>4566</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>
-    <row r="4890" spans="7:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4890" ht="26.25" customHeight="1" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G4890" s="7"/>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
@@ -34601,6 +34986,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5382" uniqueCount="4611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5694" uniqueCount="4820">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -13847,6 +13847,633 @@
   </si>
   <si>
     <t>Простыня полисатин резинка 80х200х10 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4610594535893</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - "Бежалис" 1х1</t>
+  </si>
+  <si>
+    <t>09-03-2026</t>
+  </si>
+  <si>
+    <t>4610594535886</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4610594535879</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро резинка 160х200х30 - "Серебряный Папоротник" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535862</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро-макси - "Шторм"</t>
+  </si>
+  <si>
+    <t>4610594535855</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное - Петроль</t>
+  </si>
+  <si>
+    <t>4610594535848</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 40х60 - "Леопардовый Сон"</t>
+  </si>
+  <si>
+    <t>4610594535831</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - Маренго</t>
+  </si>
+  <si>
+    <t>4610594535824</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 140х200х30 - 4216 Серебро наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535817</t>
+  </si>
+  <si>
+    <t>Простыня бязь 220х240 - 125 - Монохромная Полоса</t>
+  </si>
+  <si>
+    <t>4610594535800</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 125 - Монохромная Полоса</t>
+  </si>
+  <si>
+    <t>4610594535794</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль семейное - 110 - Лайнс</t>
+  </si>
+  <si>
+    <t>4610594535787</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 120х200х30 - 125 - Паслен А+В</t>
+  </si>
+  <si>
+    <t>4610594535770</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное - "Октябрьская берёза" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535763</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4610594535756</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок Евро-макси - Сапфировый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535749</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 125 - "Индиго" 1х1</t>
+  </si>
+  <si>
+    <t>4610594535732</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 90х200х30 - "Небесный глянцевая" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535725</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Бисквитный</t>
+  </si>
+  <si>
+    <t>4610594535718</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х30 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4610594535701</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - М - 135 - Грейс-Бэй 1х1</t>
+  </si>
+  <si>
+    <t>4610594535695</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - М - Гуава</t>
+  </si>
+  <si>
+    <t>4610594535688</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4610594535671</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - "Сентори"</t>
+  </si>
+  <si>
+    <t>4610594535664</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 150х200 - "Астероид"</t>
+  </si>
+  <si>
+    <t>4610594535657</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 150х200 - М - 142 - Антиквариат</t>
+  </si>
+  <si>
+    <t>4610594535640</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - Розариум А+В наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535633</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное - 125 - "Шампань" 1х1 Универсал</t>
+  </si>
+  <si>
+    <t>4610594535626</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 160х200х30 - Бертолеция</t>
+  </si>
+  <si>
+    <t>4610594535619</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Серый Райнар"</t>
+  </si>
+  <si>
+    <t>4610594535602</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 175х215 - М - Сладкий сон (А+В)</t>
+  </si>
+  <si>
+    <t>4610594535596</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 50х70 - Сладкий сон (А+В)</t>
+  </si>
+  <si>
+    <t>4610594535589</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 200х200 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4610594535572</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х40 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4610594535565</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Гелиос 1х1</t>
+  </si>
+  <si>
+    <t>4610594535558</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 60х60 - 80 - Теплые Пожелания</t>
+  </si>
+  <si>
+    <t>4610594535541</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х20 - Малахит</t>
+  </si>
+  <si>
+    <t>4610594535534</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Малахит</t>
+  </si>
+  <si>
+    <t>4610594535527</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - М - Малахит</t>
+  </si>
+  <si>
+    <t>4610594535510</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 140х200х30 - "Стальная тень" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535503</t>
+  </si>
+  <si>
+    <t>Простыня бязь 220х240 - 142 - Антиквариат</t>
+  </si>
+  <si>
+    <t>4610594535497</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - М - 142 ГОСТ - Оранжевый</t>
+  </si>
+  <si>
+    <t>4610594535480</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 160х200х20 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4610594535473</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 180х200х30 - "Легкий роман"</t>
+  </si>
+  <si>
+    <t>4610594535466</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 160х200х20 - 120 - Пантеон А+В</t>
+  </si>
+  <si>
+    <t>4610594535459</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 240х260 - М - 140 - Белый Люкс</t>
+  </si>
+  <si>
+    <t>4610594535442</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 200х200х30 - "Белый Оникс"</t>
+  </si>
+  <si>
+    <t>4610594535435</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 140 - Белый Люкс</t>
+  </si>
+  <si>
+    <t>4610594535428</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 220х240 - "Мелиссит"</t>
+  </si>
+  <si>
+    <t>4610594535411</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Белава"</t>
+  </si>
+  <si>
+    <t>4610594535404</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 210х210х30 - "Угольная Паутинка"</t>
+  </si>
+  <si>
+    <t>4610594535398</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро резинка 160х200х30 - 120 - Морион наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535381</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 240х260 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4610594535374</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х30 - "Лериса" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535367</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Лериса"</t>
+  </si>
+  <si>
+    <t>4610594535350</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - "Лериса"</t>
+  </si>
+  <si>
+    <t>4610594535343</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х40 - "Лериса"</t>
+  </si>
+  <si>
+    <t>4610594535336</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное - 140 - Голубой 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535329</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Аделаида"</t>
+  </si>
+  <si>
+    <t>4610594535312</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - "Лесная Вуаль" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535305</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное Евро простыня - Петроль наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535299</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Бахати"</t>
+  </si>
+  <si>
+    <t>4610594535282</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 80х200х10 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4610594535275</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 80х200х10 - "Димитра"</t>
+  </si>
+  <si>
+    <t>4610594535268</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 180х200х30 - Петроль наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535251</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - Берлинская лазурь наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535244</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро-макси - "Бездна" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535237</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 160х200х30 - "Розовый опал"</t>
+  </si>
+  <si>
+    <t>4610594535220</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин браш 145х215 - "Розовый опал"</t>
+  </si>
+  <si>
+    <t>4610594535213</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 50х70 - "Розовый опал"</t>
+  </si>
+  <si>
+    <t>4610594535206</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Мазарин блу</t>
+  </si>
+  <si>
+    <t>4610594535190</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро-макси - "Розовый Сад" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535183</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил Евро-макси - "Гармоника"</t>
+  </si>
+  <si>
+    <t>4610594535176</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро-макси - "Флорал"</t>
+  </si>
+  <si>
+    <t>4610594535169</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил Евро-макси - "Фернанда" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535152</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х200 - М - 135 - Грейс-Бэй 1х1</t>
+  </si>
+  <si>
+    <t>4610594535145</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро-макси - "Страстный гранат" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535138</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное Евро простыня - "Природный Абстракт" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535121</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Снежный Лепесток"</t>
+  </si>
+  <si>
+    <t>4610594535114</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - "Синтера" 1х1</t>
+  </si>
+  <si>
+    <t>4610594535107</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 145х215 - "Синтера" 1х1</t>
+  </si>
+  <si>
+    <t>4610594535091</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Астероид"</t>
+  </si>
+  <si>
+    <t>4610594535084</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 60х60 - 125 - Сладкий Мёд сиреневый</t>
+  </si>
+  <si>
+    <t>4610594535077</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Серая умбра</t>
+  </si>
+  <si>
+    <t>4610594535060</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 140х200х30 - "Цветы в Тумане"</t>
+  </si>
+  <si>
+    <t>4610594535053</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 125 - Дом Периньон</t>
+  </si>
+  <si>
+    <t>4610594535046</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Холодная элегия"</t>
+  </si>
+  <si>
+    <t>4610594535039</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - Уголёк наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535022</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х60 - "Цветы в Тумане"</t>
+  </si>
+  <si>
+    <t>4610594535015</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Вуалетка</t>
+  </si>
+  <si>
+    <t>4610594535008</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - Вуалетка</t>
+  </si>
+  <si>
+    <t>4610594534995</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 140х200х30 - "Бейж" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594534988</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Угольная Паутинка"</t>
+  </si>
+  <si>
+    <t>4610594534971</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль семейное резинка 180х200х30 - 110 - Белоснежный луч наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594534964</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - М - 120 - Переплёт</t>
+  </si>
+  <si>
+    <t>4610594534957</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Брызги прибоя</t>
+  </si>
+  <si>
+    <t>4610594534940</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Дзета Ориона</t>
+  </si>
+  <si>
+    <t>4610594534933</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Пыльная роза</t>
+  </si>
+  <si>
+    <t>4610594534926</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Серис"</t>
+  </si>
+  <si>
+    <t>4610594534919</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 120х200х20 - Гранола</t>
+  </si>
+  <si>
+    <t>4610594534902</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 40х40 - "Мишка в лесу"</t>
+  </si>
+  <si>
+    <t>4610594534896</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 40х40 - Индостан</t>
+  </si>
+  <si>
+    <t>4610594534889</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль 1,5 спальное - 110 - Посев Одуванчика А+В</t>
+  </si>
+  <si>
+    <t>4610594534872</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси - "Угольная Паутинка"</t>
+  </si>
+  <si>
+    <t>4610594535909</t>
+  </si>
+  <si>
+    <t>Полотенце махровое 100 х 150 - АЛА - Отель Фитнес Белое</t>
   </si>
 </sst>
 </file>
@@ -34964,6 +35591,1150 @@
         <v>4566</v>
       </c>
     </row>
+    <row r="2297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2297" t="s">
+        <v>4611</v>
+      </c>
+      <c r="B2297" t="s">
+        <v>4612</v>
+      </c>
+      <c r="C2297" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2298" t="s">
+        <v>4614</v>
+      </c>
+      <c r="B2298" t="s">
+        <v>4615</v>
+      </c>
+      <c r="C2298" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2299" t="s">
+        <v>4616</v>
+      </c>
+      <c r="B2299" t="s">
+        <v>4617</v>
+      </c>
+      <c r="C2299" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2300" t="s">
+        <v>4618</v>
+      </c>
+      <c r="B2300" t="s">
+        <v>4619</v>
+      </c>
+      <c r="C2300" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2301" t="s">
+        <v>4620</v>
+      </c>
+      <c r="B2301" t="s">
+        <v>4621</v>
+      </c>
+      <c r="C2301" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2302" t="s">
+        <v>4622</v>
+      </c>
+      <c r="B2302" t="s">
+        <v>4623</v>
+      </c>
+      <c r="C2302" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2303" t="s">
+        <v>4624</v>
+      </c>
+      <c r="B2303" t="s">
+        <v>4625</v>
+      </c>
+      <c r="C2303" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2304" t="s">
+        <v>4626</v>
+      </c>
+      <c r="B2304" t="s">
+        <v>4627</v>
+      </c>
+      <c r="C2304" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2305" t="s">
+        <v>4628</v>
+      </c>
+      <c r="B2305" t="s">
+        <v>4629</v>
+      </c>
+      <c r="C2305" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2306" t="s">
+        <v>4630</v>
+      </c>
+      <c r="B2306" t="s">
+        <v>4631</v>
+      </c>
+      <c r="C2306" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2307" t="s">
+        <v>4632</v>
+      </c>
+      <c r="B2307" t="s">
+        <v>4633</v>
+      </c>
+      <c r="C2307" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2308" t="s">
+        <v>4634</v>
+      </c>
+      <c r="B2308" t="s">
+        <v>4635</v>
+      </c>
+      <c r="C2308" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2309" t="s">
+        <v>4636</v>
+      </c>
+      <c r="B2309" t="s">
+        <v>4637</v>
+      </c>
+      <c r="C2309" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2310" t="s">
+        <v>4638</v>
+      </c>
+      <c r="B2310" t="s">
+        <v>4639</v>
+      </c>
+      <c r="C2310" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2311" t="s">
+        <v>4640</v>
+      </c>
+      <c r="B2311" t="s">
+        <v>4641</v>
+      </c>
+      <c r="C2311" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2312" t="s">
+        <v>4642</v>
+      </c>
+      <c r="B2312" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C2312" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2313" t="s">
+        <v>4644</v>
+      </c>
+      <c r="B2313" t="s">
+        <v>4645</v>
+      </c>
+      <c r="C2313" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2314" t="s">
+        <v>4646</v>
+      </c>
+      <c r="B2314" t="s">
+        <v>4647</v>
+      </c>
+      <c r="C2314" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2315" t="s">
+        <v>4648</v>
+      </c>
+      <c r="B2315" t="s">
+        <v>4649</v>
+      </c>
+      <c r="C2315" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2316" t="s">
+        <v>4650</v>
+      </c>
+      <c r="B2316" t="s">
+        <v>4651</v>
+      </c>
+      <c r="C2316" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2317" t="s">
+        <v>4652</v>
+      </c>
+      <c r="B2317" t="s">
+        <v>4653</v>
+      </c>
+      <c r="C2317" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2318" t="s">
+        <v>4654</v>
+      </c>
+      <c r="B2318" t="s">
+        <v>4655</v>
+      </c>
+      <c r="C2318" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2319" t="s">
+        <v>4656</v>
+      </c>
+      <c r="B2319" t="s">
+        <v>4657</v>
+      </c>
+      <c r="C2319" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2320" t="s">
+        <v>4658</v>
+      </c>
+      <c r="B2320" t="s">
+        <v>4659</v>
+      </c>
+      <c r="C2320" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2321" t="s">
+        <v>4660</v>
+      </c>
+      <c r="B2321" t="s">
+        <v>4661</v>
+      </c>
+      <c r="C2321" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2322" t="s">
+        <v>4662</v>
+      </c>
+      <c r="B2322" t="s">
+        <v>4663</v>
+      </c>
+      <c r="C2322" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2323" t="s">
+        <v>4664</v>
+      </c>
+      <c r="B2323" t="s">
+        <v>4665</v>
+      </c>
+      <c r="C2323" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2324" t="s">
+        <v>4666</v>
+      </c>
+      <c r="B2324" t="s">
+        <v>4667</v>
+      </c>
+      <c r="C2324" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2325" t="s">
+        <v>4668</v>
+      </c>
+      <c r="B2325" t="s">
+        <v>4669</v>
+      </c>
+      <c r="C2325" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2326" t="s">
+        <v>4670</v>
+      </c>
+      <c r="B2326" t="s">
+        <v>4671</v>
+      </c>
+      <c r="C2326" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2327" t="s">
+        <v>4672</v>
+      </c>
+      <c r="B2327" t="s">
+        <v>4673</v>
+      </c>
+      <c r="C2327" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2328" t="s">
+        <v>4674</v>
+      </c>
+      <c r="B2328" t="s">
+        <v>4675</v>
+      </c>
+      <c r="C2328" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2329" t="s">
+        <v>4676</v>
+      </c>
+      <c r="B2329" t="s">
+        <v>4677</v>
+      </c>
+      <c r="C2329" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2330" t="s">
+        <v>4678</v>
+      </c>
+      <c r="B2330" t="s">
+        <v>4679</v>
+      </c>
+      <c r="C2330" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2331" t="s">
+        <v>4680</v>
+      </c>
+      <c r="B2331" t="s">
+        <v>4681</v>
+      </c>
+      <c r="C2331" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2332" t="s">
+        <v>4682</v>
+      </c>
+      <c r="B2332" t="s">
+        <v>4683</v>
+      </c>
+      <c r="C2332" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2333" t="s">
+        <v>4684</v>
+      </c>
+      <c r="B2333" t="s">
+        <v>4685</v>
+      </c>
+      <c r="C2333" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2334" t="s">
+        <v>4686</v>
+      </c>
+      <c r="B2334" t="s">
+        <v>4687</v>
+      </c>
+      <c r="C2334" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2335" t="s">
+        <v>4688</v>
+      </c>
+      <c r="B2335" t="s">
+        <v>4689</v>
+      </c>
+      <c r="C2335" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2336" t="s">
+        <v>4690</v>
+      </c>
+      <c r="B2336" t="s">
+        <v>4691</v>
+      </c>
+      <c r="C2336" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2337" t="s">
+        <v>4692</v>
+      </c>
+      <c r="B2337" t="s">
+        <v>4693</v>
+      </c>
+      <c r="C2337" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2338" t="s">
+        <v>4694</v>
+      </c>
+      <c r="B2338" t="s">
+        <v>4695</v>
+      </c>
+      <c r="C2338" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2339" t="s">
+        <v>4696</v>
+      </c>
+      <c r="B2339" t="s">
+        <v>4697</v>
+      </c>
+      <c r="C2339" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2340" t="s">
+        <v>4698</v>
+      </c>
+      <c r="B2340" t="s">
+        <v>4699</v>
+      </c>
+      <c r="C2340" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2341" t="s">
+        <v>4700</v>
+      </c>
+      <c r="B2341" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C2341" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2342" t="s">
+        <v>4702</v>
+      </c>
+      <c r="B2342" t="s">
+        <v>4703</v>
+      </c>
+      <c r="C2342" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2343" t="s">
+        <v>4704</v>
+      </c>
+      <c r="B2343" t="s">
+        <v>4705</v>
+      </c>
+      <c r="C2343" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2344" t="s">
+        <v>4706</v>
+      </c>
+      <c r="B2344" t="s">
+        <v>4707</v>
+      </c>
+      <c r="C2344" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2345" t="s">
+        <v>4708</v>
+      </c>
+      <c r="B2345" t="s">
+        <v>4709</v>
+      </c>
+      <c r="C2345" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2346" t="s">
+        <v>4710</v>
+      </c>
+      <c r="B2346" t="s">
+        <v>4711</v>
+      </c>
+      <c r="C2346" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2347" t="s">
+        <v>4712</v>
+      </c>
+      <c r="B2347" t="s">
+        <v>4713</v>
+      </c>
+      <c r="C2347" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2348" t="s">
+        <v>4714</v>
+      </c>
+      <c r="B2348" t="s">
+        <v>4715</v>
+      </c>
+      <c r="C2348" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2349" t="s">
+        <v>4716</v>
+      </c>
+      <c r="B2349" t="s">
+        <v>4717</v>
+      </c>
+      <c r="C2349" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2350" t="s">
+        <v>4718</v>
+      </c>
+      <c r="B2350" t="s">
+        <v>4719</v>
+      </c>
+      <c r="C2350" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2351" t="s">
+        <v>4720</v>
+      </c>
+      <c r="B2351" t="s">
+        <v>4721</v>
+      </c>
+      <c r="C2351" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2352" t="s">
+        <v>4722</v>
+      </c>
+      <c r="B2352" t="s">
+        <v>4723</v>
+      </c>
+      <c r="C2352" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2353" t="s">
+        <v>4724</v>
+      </c>
+      <c r="B2353" t="s">
+        <v>4725</v>
+      </c>
+      <c r="C2353" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2354" t="s">
+        <v>4726</v>
+      </c>
+      <c r="B2354" t="s">
+        <v>4727</v>
+      </c>
+      <c r="C2354" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2355" t="s">
+        <v>4728</v>
+      </c>
+      <c r="B2355" t="s">
+        <v>4729</v>
+      </c>
+      <c r="C2355" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2356" t="s">
+        <v>4730</v>
+      </c>
+      <c r="B2356" t="s">
+        <v>4731</v>
+      </c>
+      <c r="C2356" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2357" t="s">
+        <v>4732</v>
+      </c>
+      <c r="B2357" t="s">
+        <v>4733</v>
+      </c>
+      <c r="C2357" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2358" t="s">
+        <v>4734</v>
+      </c>
+      <c r="B2358" t="s">
+        <v>4735</v>
+      </c>
+      <c r="C2358" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2359" t="s">
+        <v>4736</v>
+      </c>
+      <c r="B2359" t="s">
+        <v>4737</v>
+      </c>
+      <c r="C2359" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2360" t="s">
+        <v>4738</v>
+      </c>
+      <c r="B2360" t="s">
+        <v>4739</v>
+      </c>
+      <c r="C2360" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2361" t="s">
+        <v>4740</v>
+      </c>
+      <c r="B2361" t="s">
+        <v>4741</v>
+      </c>
+      <c r="C2361" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2362" t="s">
+        <v>4742</v>
+      </c>
+      <c r="B2362" t="s">
+        <v>4743</v>
+      </c>
+      <c r="C2362" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2363" t="s">
+        <v>4744</v>
+      </c>
+      <c r="B2363" t="s">
+        <v>4745</v>
+      </c>
+      <c r="C2363" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2364" t="s">
+        <v>4746</v>
+      </c>
+      <c r="B2364" t="s">
+        <v>4747</v>
+      </c>
+      <c r="C2364" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2365" t="s">
+        <v>4748</v>
+      </c>
+      <c r="B2365" t="s">
+        <v>4749</v>
+      </c>
+      <c r="C2365" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2366" t="s">
+        <v>4750</v>
+      </c>
+      <c r="B2366" t="s">
+        <v>4751</v>
+      </c>
+      <c r="C2366" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2367" t="s">
+        <v>4752</v>
+      </c>
+      <c r="B2367" t="s">
+        <v>4753</v>
+      </c>
+      <c r="C2367" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2368" t="s">
+        <v>4754</v>
+      </c>
+      <c r="B2368" t="s">
+        <v>4755</v>
+      </c>
+      <c r="C2368" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2369" t="s">
+        <v>4756</v>
+      </c>
+      <c r="B2369" t="s">
+        <v>4757</v>
+      </c>
+      <c r="C2369" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2370" t="s">
+        <v>4758</v>
+      </c>
+      <c r="B2370" t="s">
+        <v>4759</v>
+      </c>
+      <c r="C2370" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2371" t="s">
+        <v>4760</v>
+      </c>
+      <c r="B2371" t="s">
+        <v>4761</v>
+      </c>
+      <c r="C2371" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2372" t="s">
+        <v>4762</v>
+      </c>
+      <c r="B2372" t="s">
+        <v>4763</v>
+      </c>
+      <c r="C2372" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2373" t="s">
+        <v>4764</v>
+      </c>
+      <c r="B2373" t="s">
+        <v>4765</v>
+      </c>
+      <c r="C2373" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2374" t="s">
+        <v>4766</v>
+      </c>
+      <c r="B2374" t="s">
+        <v>4767</v>
+      </c>
+      <c r="C2374" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2375" t="s">
+        <v>4768</v>
+      </c>
+      <c r="B2375" t="s">
+        <v>4769</v>
+      </c>
+      <c r="C2375" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2376" t="s">
+        <v>4770</v>
+      </c>
+      <c r="B2376" t="s">
+        <v>4771</v>
+      </c>
+      <c r="C2376" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2377" t="s">
+        <v>4772</v>
+      </c>
+      <c r="B2377" t="s">
+        <v>4773</v>
+      </c>
+      <c r="C2377" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2378" t="s">
+        <v>4774</v>
+      </c>
+      <c r="B2378" t="s">
+        <v>4775</v>
+      </c>
+      <c r="C2378" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2379" t="s">
+        <v>4776</v>
+      </c>
+      <c r="B2379" t="s">
+        <v>4777</v>
+      </c>
+      <c r="C2379" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2380" t="s">
+        <v>4778</v>
+      </c>
+      <c r="B2380" t="s">
+        <v>4779</v>
+      </c>
+      <c r="C2380" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2381" t="s">
+        <v>4780</v>
+      </c>
+      <c r="B2381" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C2381" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2382" t="s">
+        <v>4782</v>
+      </c>
+      <c r="B2382" t="s">
+        <v>4783</v>
+      </c>
+      <c r="C2382" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2383" t="s">
+        <v>4784</v>
+      </c>
+      <c r="B2383" t="s">
+        <v>4785</v>
+      </c>
+      <c r="C2383" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2384" t="s">
+        <v>4786</v>
+      </c>
+      <c r="B2384" t="s">
+        <v>4787</v>
+      </c>
+      <c r="C2384" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2385" t="s">
+        <v>4788</v>
+      </c>
+      <c r="B2385" t="s">
+        <v>4789</v>
+      </c>
+      <c r="C2385" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2386" t="s">
+        <v>4790</v>
+      </c>
+      <c r="B2386" t="s">
+        <v>4791</v>
+      </c>
+      <c r="C2386" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2387" t="s">
+        <v>4792</v>
+      </c>
+      <c r="B2387" t="s">
+        <v>4793</v>
+      </c>
+      <c r="C2387" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2388" t="s">
+        <v>4794</v>
+      </c>
+      <c r="B2388" t="s">
+        <v>4795</v>
+      </c>
+      <c r="C2388" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2389" t="s">
+        <v>4796</v>
+      </c>
+      <c r="B2389" t="s">
+        <v>4797</v>
+      </c>
+      <c r="C2389" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2390" t="s">
+        <v>4798</v>
+      </c>
+      <c r="B2390" t="s">
+        <v>4799</v>
+      </c>
+      <c r="C2390" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2391" t="s">
+        <v>4800</v>
+      </c>
+      <c r="B2391" t="s">
+        <v>4801</v>
+      </c>
+      <c r="C2391" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2392" t="s">
+        <v>4802</v>
+      </c>
+      <c r="B2392" t="s">
+        <v>4803</v>
+      </c>
+      <c r="C2392" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2393" t="s">
+        <v>4804</v>
+      </c>
+      <c r="B2393" t="s">
+        <v>4805</v>
+      </c>
+      <c r="C2393" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2394" t="s">
+        <v>4806</v>
+      </c>
+      <c r="B2394" t="s">
+        <v>4807</v>
+      </c>
+      <c r="C2394" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2395" t="s">
+        <v>4808</v>
+      </c>
+      <c r="B2395" t="s">
+        <v>4809</v>
+      </c>
+      <c r="C2395" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2396" t="s">
+        <v>4810</v>
+      </c>
+      <c r="B2396" t="s">
+        <v>4811</v>
+      </c>
+      <c r="C2396" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2397" t="s">
+        <v>4812</v>
+      </c>
+      <c r="B2397" t="s">
+        <v>4813</v>
+      </c>
+      <c r="C2397" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2398" t="s">
+        <v>4814</v>
+      </c>
+      <c r="B2398" t="s">
+        <v>4815</v>
+      </c>
+      <c r="C2398" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2399" t="s">
+        <v>4816</v>
+      </c>
+      <c r="B2399" t="s">
+        <v>4817</v>
+      </c>
+      <c r="C2399" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2400" t="s">
+        <v>4818</v>
+      </c>
+      <c r="B2400" t="s">
+        <v>4819</v>
+      </c>
+      <c r="C2400" t="s">
+        <v>4613</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5694" uniqueCount="4820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5736" uniqueCount="4849">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -14474,6 +14474,93 @@
   </si>
   <si>
     <t>Полотенце махровое 100 х 150 - АЛА - Отель Фитнес Белое</t>
+  </si>
+  <si>
+    <t>4610594536043</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Анхела"</t>
+  </si>
+  <si>
+    <t>10-03-2026</t>
+  </si>
+  <si>
+    <t>4610594536036</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - 120 - Серебристый металлик наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594536029</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х10 - "История сов"</t>
+  </si>
+  <si>
+    <t>4610594536012</t>
+  </si>
+  <si>
+    <t>Простыня сатин 240х260 - 125 - Белая</t>
+  </si>
+  <si>
+    <t>4610594536005</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 140 - Белый Лучик</t>
+  </si>
+  <si>
+    <t>4610594535992</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - 140 - Белый Люкс</t>
+  </si>
+  <si>
+    <t>4610594535985</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 260х260 - "Севим"</t>
+  </si>
+  <si>
+    <t>4610594535978</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Твист"</t>
+  </si>
+  <si>
+    <t>4610594535961</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 175х215 - М - 135 - Секондо колоро 1х1</t>
+  </si>
+  <si>
+    <t>4610594535954</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 120 - Баден Гольд</t>
+  </si>
+  <si>
+    <t>4610594535947</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Серебро Облаков" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594535930</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Лилия флосс"</t>
+  </si>
+  <si>
+    <t>4610594535923</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 175х215 - "Воздушное касание"</t>
+  </si>
+  <si>
+    <t>4610594535916</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 145х215 - "Крылатые сны"</t>
   </si>
 </sst>
 </file>
@@ -36735,6 +36822,160 @@
         <v>4613</v>
       </c>
     </row>
+    <row r="2401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2401" t="s">
+        <v>4820</v>
+      </c>
+      <c r="B2401" t="s">
+        <v>4821</v>
+      </c>
+      <c r="C2401" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2402" t="s">
+        <v>4823</v>
+      </c>
+      <c r="B2402" t="s">
+        <v>4824</v>
+      </c>
+      <c r="C2402" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2403" t="s">
+        <v>4825</v>
+      </c>
+      <c r="B2403" t="s">
+        <v>4826</v>
+      </c>
+      <c r="C2403" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2404" t="s">
+        <v>4827</v>
+      </c>
+      <c r="B2404" t="s">
+        <v>4828</v>
+      </c>
+      <c r="C2404" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2405" t="s">
+        <v>4829</v>
+      </c>
+      <c r="B2405" t="s">
+        <v>4830</v>
+      </c>
+      <c r="C2405" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2406" t="s">
+        <v>4831</v>
+      </c>
+      <c r="B2406" t="s">
+        <v>4832</v>
+      </c>
+      <c r="C2406" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2407" t="s">
+        <v>4833</v>
+      </c>
+      <c r="B2407" t="s">
+        <v>4834</v>
+      </c>
+      <c r="C2407" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2408" t="s">
+        <v>4835</v>
+      </c>
+      <c r="B2408" t="s">
+        <v>4836</v>
+      </c>
+      <c r="C2408" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2409" t="s">
+        <v>4837</v>
+      </c>
+      <c r="B2409" t="s">
+        <v>4838</v>
+      </c>
+      <c r="C2409" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2410" t="s">
+        <v>4839</v>
+      </c>
+      <c r="B2410" t="s">
+        <v>4840</v>
+      </c>
+      <c r="C2410" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2411" t="s">
+        <v>4841</v>
+      </c>
+      <c r="B2411" t="s">
+        <v>4842</v>
+      </c>
+      <c r="C2411" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2412" t="s">
+        <v>4843</v>
+      </c>
+      <c r="B2412" t="s">
+        <v>4844</v>
+      </c>
+      <c r="C2412" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2413" t="s">
+        <v>4845</v>
+      </c>
+      <c r="B2413" t="s">
+        <v>4846</v>
+      </c>
+      <c r="C2413" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2414" t="s">
+        <v>4847</v>
+      </c>
+      <c r="B2414" t="s">
+        <v>4848</v>
+      </c>
+      <c r="C2414" t="s">
+        <v>4822</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5736" uniqueCount="4849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5778" uniqueCount="4878">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -14561,6 +14561,93 @@
   </si>
   <si>
     <t>Пододеяльник поплин 145х215 - "Крылатые сны"</t>
+  </si>
+  <si>
+    <t>4610594536180</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 150х200 - М - 120 - Северные Волки</t>
+  </si>
+  <si>
+    <t>11-03-2026</t>
+  </si>
+  <si>
+    <t>4610594536173</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 120 - Северные Волки</t>
+  </si>
+  <si>
+    <t>4610594536166</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4610594536159</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Эвергрин"</t>
+  </si>
+  <si>
+    <t>4610594536142</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4610594536135</t>
+  </si>
+  <si>
+    <t>Простыня круглая из тенселя на резинке 240х240х20 - М - 60S 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4610594536128</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4610594536111</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая 180х220 - Мулетон Полиэстер</t>
+  </si>
+  <si>
+    <t>4610594536104</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 200х200х30 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4610594536098</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - 142 ГОСТ - Оранжевый</t>
+  </si>
+  <si>
+    <t>4610594536081</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - 142 ГОСТ - Черный</t>
+  </si>
+  <si>
+    <t>4610594536074</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 200х200х30 - Кремовый бархат</t>
+  </si>
+  <si>
+    <t>4610594536067</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное Евро простыня - 120 - Белое</t>
+  </si>
+  <si>
+    <t>4610594536050</t>
+  </si>
+  <si>
+    <t>Простыня Жатка на резинке 160х200х20 - "Плюмас"</t>
   </si>
 </sst>
 </file>
@@ -36976,6 +37063,160 @@
         <v>4822</v>
       </c>
     </row>
+    <row r="2415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2415" t="s">
+        <v>4849</v>
+      </c>
+      <c r="B2415" t="s">
+        <v>4850</v>
+      </c>
+      <c r="C2415" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2416" t="s">
+        <v>4852</v>
+      </c>
+      <c r="B2416" t="s">
+        <v>4853</v>
+      </c>
+      <c r="C2416" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2417" t="s">
+        <v>4854</v>
+      </c>
+      <c r="B2417" t="s">
+        <v>4855</v>
+      </c>
+      <c r="C2417" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2418" t="s">
+        <v>4856</v>
+      </c>
+      <c r="B2418" t="s">
+        <v>4857</v>
+      </c>
+      <c r="C2418" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2419" t="s">
+        <v>4858</v>
+      </c>
+      <c r="B2419" t="s">
+        <v>4859</v>
+      </c>
+      <c r="C2419" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2420" t="s">
+        <v>4860</v>
+      </c>
+      <c r="B2420" t="s">
+        <v>4861</v>
+      </c>
+      <c r="C2420" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2421" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B2421" t="s">
+        <v>4863</v>
+      </c>
+      <c r="C2421" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2422" t="s">
+        <v>4864</v>
+      </c>
+      <c r="B2422" t="s">
+        <v>4865</v>
+      </c>
+      <c r="C2422" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2423" t="s">
+        <v>4866</v>
+      </c>
+      <c r="B2423" t="s">
+        <v>4867</v>
+      </c>
+      <c r="C2423" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2424" t="s">
+        <v>4868</v>
+      </c>
+      <c r="B2424" t="s">
+        <v>4869</v>
+      </c>
+      <c r="C2424" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2425" t="s">
+        <v>4870</v>
+      </c>
+      <c r="B2425" t="s">
+        <v>4871</v>
+      </c>
+      <c r="C2425" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2426" t="s">
+        <v>4872</v>
+      </c>
+      <c r="B2426" t="s">
+        <v>4873</v>
+      </c>
+      <c r="C2426" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2427" t="s">
+        <v>4874</v>
+      </c>
+      <c r="B2427" t="s">
+        <v>4875</v>
+      </c>
+      <c r="C2427" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2428" t="s">
+        <v>4876</v>
+      </c>
+      <c r="B2428" t="s">
+        <v>4877</v>
+      </c>
+      <c r="C2428" t="s">
+        <v>4851</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5778" uniqueCount="4878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5844" uniqueCount="4923">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -14648,6 +14648,141 @@
   </si>
   <si>
     <t>Простыня Жатка на резинке 160х200х20 - "Плюмас"</t>
+  </si>
+  <si>
+    <t>4610594536401</t>
+  </si>
+  <si>
+    <t>Простыня жатка 240х260 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>12-03-2026</t>
+  </si>
+  <si>
+    <t>4610594536395</t>
+  </si>
+  <si>
+    <t>Простыня жатка 240х260 - "Звёздный Вальс"</t>
+  </si>
+  <si>
+    <t>4610594536388</t>
+  </si>
+  <si>
+    <t>Простыня бязь 220х240 - 142 ГОСТ - Белый</t>
+  </si>
+  <si>
+    <t>4610594536371</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё бязь 1,5 спальное - 120 - Колыбель на зеленом</t>
+  </si>
+  <si>
+    <t>4610594536364</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4610594536357</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 300х300 - "Светлый лён"</t>
+  </si>
+  <si>
+    <t>4610594536340</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - "Ажур" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594536333</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное резинка 140х200х30 - "Инспайр"</t>
+  </si>
+  <si>
+    <t>4610594536326</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное на резинке 140х200х30 - "Серебро Лондона"</t>
+  </si>
+  <si>
+    <t>4610594536319</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 140 - Голубой 1х1</t>
+  </si>
+  <si>
+    <t>4610594536302</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4610594536296</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4610594536289</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 120 - Лиловая дымка</t>
+  </si>
+  <si>
+    <t>4610594536272</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 70х70 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>4610594536265</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х30 - "Ритва"</t>
+  </si>
+  <si>
+    <t>4610594536258</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Ритва"</t>
+  </si>
+  <si>
+    <t>4610594536241</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - "Лилия флосс"</t>
+  </si>
+  <si>
+    <t>4610594536234</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - "Бархатный Букет"</t>
+  </si>
+  <si>
+    <t>4610594536227</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 80х200х10 - 142 ГОСТ - Черный</t>
+  </si>
+  <si>
+    <t>4610594536210</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 175х215 - "Флорал"</t>
+  </si>
+  <si>
+    <t>4610594536203</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - "Флорал"</t>
+  </si>
+  <si>
+    <t>4610594536197</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х30 - "Оливейт"</t>
   </si>
 </sst>
 </file>
@@ -37217,6 +37352,248 @@
         <v>4851</v>
       </c>
     </row>
+    <row r="2429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2429" t="s">
+        <v>4878</v>
+      </c>
+      <c r="B2429" t="s">
+        <v>4879</v>
+      </c>
+      <c r="C2429" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2430" t="s">
+        <v>4881</v>
+      </c>
+      <c r="B2430" t="s">
+        <v>4882</v>
+      </c>
+      <c r="C2430" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2431" t="s">
+        <v>4883</v>
+      </c>
+      <c r="B2431" t="s">
+        <v>4884</v>
+      </c>
+      <c r="C2431" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2432" t="s">
+        <v>4885</v>
+      </c>
+      <c r="B2432" t="s">
+        <v>4886</v>
+      </c>
+      <c r="C2432" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2433" t="s">
+        <v>4887</v>
+      </c>
+      <c r="B2433" t="s">
+        <v>4888</v>
+      </c>
+      <c r="C2433" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2434" t="s">
+        <v>4889</v>
+      </c>
+      <c r="B2434" t="s">
+        <v>4890</v>
+      </c>
+      <c r="C2434" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2435" t="s">
+        <v>4891</v>
+      </c>
+      <c r="B2435" t="s">
+        <v>4892</v>
+      </c>
+      <c r="C2435" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2436" t="s">
+        <v>4893</v>
+      </c>
+      <c r="B2436" t="s">
+        <v>4894</v>
+      </c>
+      <c r="C2436" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2437" t="s">
+        <v>4895</v>
+      </c>
+      <c r="B2437" t="s">
+        <v>4896</v>
+      </c>
+      <c r="C2437" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2438" t="s">
+        <v>4897</v>
+      </c>
+      <c r="B2438" t="s">
+        <v>4898</v>
+      </c>
+      <c r="C2438" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2439" t="s">
+        <v>4899</v>
+      </c>
+      <c r="B2439" t="s">
+        <v>4900</v>
+      </c>
+      <c r="C2439" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2440" t="s">
+        <v>4901</v>
+      </c>
+      <c r="B2440" t="s">
+        <v>4902</v>
+      </c>
+      <c r="C2440" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2441" t="s">
+        <v>4903</v>
+      </c>
+      <c r="B2441" t="s">
+        <v>4904</v>
+      </c>
+      <c r="C2441" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2442" t="s">
+        <v>4905</v>
+      </c>
+      <c r="B2442" t="s">
+        <v>4906</v>
+      </c>
+      <c r="C2442" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2443" t="s">
+        <v>4907</v>
+      </c>
+      <c r="B2443" t="s">
+        <v>4908</v>
+      </c>
+      <c r="C2443" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2444" t="s">
+        <v>4909</v>
+      </c>
+      <c r="B2444" t="s">
+        <v>4910</v>
+      </c>
+      <c r="C2444" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2445" t="s">
+        <v>4911</v>
+      </c>
+      <c r="B2445" t="s">
+        <v>4912</v>
+      </c>
+      <c r="C2445" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2446" t="s">
+        <v>4913</v>
+      </c>
+      <c r="B2446" t="s">
+        <v>4914</v>
+      </c>
+      <c r="C2446" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2447" t="s">
+        <v>4915</v>
+      </c>
+      <c r="B2447" t="s">
+        <v>4916</v>
+      </c>
+      <c r="C2447" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2448" t="s">
+        <v>4917</v>
+      </c>
+      <c r="B2448" t="s">
+        <v>4918</v>
+      </c>
+      <c r="C2448" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2449" t="s">
+        <v>4919</v>
+      </c>
+      <c r="B2449" t="s">
+        <v>4920</v>
+      </c>
+      <c r="C2449" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2450" t="s">
+        <v>4921</v>
+      </c>
+      <c r="B2450" t="s">
+        <v>4922</v>
+      </c>
+      <c r="C2450" t="s">
+        <v>4880</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5844" uniqueCount="4923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5940" uniqueCount="4988">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -14783,6 +14783,201 @@
   </si>
   <si>
     <t>КПБ Постельное бельё поплин Евро резинка 160х200х30 - "Оливейт"</t>
+  </si>
+  <si>
+    <t>4610594536715</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Астероид"</t>
+  </si>
+  <si>
+    <t>13-03-2026</t>
+  </si>
+  <si>
+    <t>4610594536708</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - М - Черный блеск</t>
+  </si>
+  <si>
+    <t>4610594536692</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - М - 135 - Барбаденсис 1х1</t>
+  </si>
+  <si>
+    <t>4610594536685</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 80х200х10 - 142 ГОСТ - Кленовый</t>
+  </si>
+  <si>
+    <t>4610594536678</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 80х200х10 - 142 ГОСТ - Серый</t>
+  </si>
+  <si>
+    <t>4610594536661</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 50х70 - Фиолето</t>
+  </si>
+  <si>
+    <t>4610594536654</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 125 - Слонята на желтом</t>
+  </si>
+  <si>
+    <t>4610594536647</t>
+  </si>
+  <si>
+    <t>Простыня жаккард резинка 180х200х40 - Флорибунда</t>
+  </si>
+  <si>
+    <t>4610594536630</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 180х200х40 - Бертолеция</t>
+  </si>
+  <si>
+    <t>4610594536623</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 180х200х40 - Кайбаб</t>
+  </si>
+  <si>
+    <t>4610594536616</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Олуфими"</t>
+  </si>
+  <si>
+    <t>4610594536609</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х40 - Селадон</t>
+  </si>
+  <si>
+    <t>4610594536593</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Огнерон"</t>
+  </si>
+  <si>
+    <t>4610594536586</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Морбидецца наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594536579</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 40х60 - 323 Серый</t>
+  </si>
+  <si>
+    <t>4610594536562</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 142 ГОСТ - Изумруд</t>
+  </si>
+  <si>
+    <t>4610594536555</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 140х200х40 - Петроль</t>
+  </si>
+  <si>
+    <t>4610594536548</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - М - Петроль</t>
+  </si>
+  <si>
+    <t>4610594536531</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Петроль</t>
+  </si>
+  <si>
+    <t>4610594536524</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - "Оливейт"</t>
+  </si>
+  <si>
+    <t>4610594536517</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 120х200х20 - "Фиолетовый Шёпот"</t>
+  </si>
+  <si>
+    <t>4610594536500</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 120х200х20 - "Инспайр"</t>
+  </si>
+  <si>
+    <t>4610594536494</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси резинка 180х200х30 - "Альфредо"</t>
+  </si>
+  <si>
+    <t>4610594536487</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Тирас"</t>
+  </si>
+  <si>
+    <t>4610594536470</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - 135 - Лаймкват 1х1</t>
+  </si>
+  <si>
+    <t>4610594536463</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро-макси - "Бездна"</t>
+  </si>
+  <si>
+    <t>4610594536456</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х30 - "Гуголету"</t>
+  </si>
+  <si>
+    <t>4610594536449</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - 60S 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4610594536432</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 1,5 спальное резинка 140х200х30 - "Кремневый серый" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594536425</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 160х200х20 - "Милда" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594536418</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 220х240 - М - Прерия</t>
+  </si>
+  <si>
+    <t>4610594536722</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Лав юселф"</t>
   </si>
 </sst>
 </file>
@@ -37594,6 +37789,358 @@
         <v>4880</v>
       </c>
     </row>
+    <row r="2451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2451" t="s">
+        <v>4923</v>
+      </c>
+      <c r="B2451" t="s">
+        <v>4924</v>
+      </c>
+      <c r="C2451" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2452" t="s">
+        <v>4926</v>
+      </c>
+      <c r="B2452" t="s">
+        <v>4927</v>
+      </c>
+      <c r="C2452" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2453" t="s">
+        <v>4928</v>
+      </c>
+      <c r="B2453" t="s">
+        <v>4929</v>
+      </c>
+      <c r="C2453" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2454" t="s">
+        <v>4930</v>
+      </c>
+      <c r="B2454" t="s">
+        <v>4931</v>
+      </c>
+      <c r="C2454" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2455" t="s">
+        <v>4932</v>
+      </c>
+      <c r="B2455" t="s">
+        <v>4933</v>
+      </c>
+      <c r="C2455" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2456" t="s">
+        <v>4934</v>
+      </c>
+      <c r="B2456" t="s">
+        <v>4935</v>
+      </c>
+      <c r="C2456" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2457" t="s">
+        <v>4936</v>
+      </c>
+      <c r="B2457" t="s">
+        <v>4937</v>
+      </c>
+      <c r="C2457" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2458" t="s">
+        <v>4938</v>
+      </c>
+      <c r="B2458" t="s">
+        <v>4939</v>
+      </c>
+      <c r="C2458" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2459" t="s">
+        <v>4940</v>
+      </c>
+      <c r="B2459" t="s">
+        <v>4941</v>
+      </c>
+      <c r="C2459" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2460" t="s">
+        <v>4942</v>
+      </c>
+      <c r="B2460" t="s">
+        <v>4943</v>
+      </c>
+      <c r="C2460" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2461" t="s">
+        <v>4944</v>
+      </c>
+      <c r="B2461" t="s">
+        <v>4945</v>
+      </c>
+      <c r="C2461" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2462" t="s">
+        <v>4946</v>
+      </c>
+      <c r="B2462" t="s">
+        <v>4947</v>
+      </c>
+      <c r="C2462" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2463" t="s">
+        <v>4948</v>
+      </c>
+      <c r="B2463" t="s">
+        <v>4949</v>
+      </c>
+      <c r="C2463" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2464" t="s">
+        <v>4950</v>
+      </c>
+      <c r="B2464" t="s">
+        <v>4951</v>
+      </c>
+      <c r="C2464" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2465" t="s">
+        <v>4952</v>
+      </c>
+      <c r="B2465" t="s">
+        <v>4953</v>
+      </c>
+      <c r="C2465" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2466" t="s">
+        <v>4954</v>
+      </c>
+      <c r="B2466" t="s">
+        <v>4955</v>
+      </c>
+      <c r="C2466" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2467" t="s">
+        <v>4956</v>
+      </c>
+      <c r="B2467" t="s">
+        <v>4957</v>
+      </c>
+      <c r="C2467" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2468" t="s">
+        <v>4958</v>
+      </c>
+      <c r="B2468" t="s">
+        <v>4959</v>
+      </c>
+      <c r="C2468" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2469" t="s">
+        <v>4960</v>
+      </c>
+      <c r="B2469" t="s">
+        <v>4961</v>
+      </c>
+      <c r="C2469" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2470" t="s">
+        <v>4962</v>
+      </c>
+      <c r="B2470" t="s">
+        <v>4963</v>
+      </c>
+      <c r="C2470" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2471" t="s">
+        <v>4964</v>
+      </c>
+      <c r="B2471" t="s">
+        <v>4965</v>
+      </c>
+      <c r="C2471" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2472" t="s">
+        <v>4966</v>
+      </c>
+      <c r="B2472" t="s">
+        <v>4967</v>
+      </c>
+      <c r="C2472" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2473" t="s">
+        <v>4968</v>
+      </c>
+      <c r="B2473" t="s">
+        <v>4969</v>
+      </c>
+      <c r="C2473" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2474" t="s">
+        <v>4970</v>
+      </c>
+      <c r="B2474" t="s">
+        <v>4971</v>
+      </c>
+      <c r="C2474" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2475" t="s">
+        <v>4972</v>
+      </c>
+      <c r="B2475" t="s">
+        <v>4973</v>
+      </c>
+      <c r="C2475" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2476" t="s">
+        <v>4974</v>
+      </c>
+      <c r="B2476" t="s">
+        <v>4975</v>
+      </c>
+      <c r="C2476" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2477" t="s">
+        <v>4976</v>
+      </c>
+      <c r="B2477" t="s">
+        <v>4977</v>
+      </c>
+      <c r="C2477" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2478" t="s">
+        <v>4978</v>
+      </c>
+      <c r="B2478" t="s">
+        <v>4979</v>
+      </c>
+      <c r="C2478" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2479" t="s">
+        <v>4980</v>
+      </c>
+      <c r="B2479" t="s">
+        <v>4981</v>
+      </c>
+      <c r="C2479" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2480" t="s">
+        <v>4982</v>
+      </c>
+      <c r="B2480" t="s">
+        <v>4983</v>
+      </c>
+      <c r="C2480" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2481" t="s">
+        <v>4984</v>
+      </c>
+      <c r="B2481" t="s">
+        <v>4985</v>
+      </c>
+      <c r="C2481" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2482" t="s">
+        <v>4986</v>
+      </c>
+      <c r="B2482" t="s">
+        <v>4987</v>
+      </c>
+      <c r="C2482" t="s">
+        <v>4925</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5940" uniqueCount="4988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6150" uniqueCount="5129">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -14978,6 +14978,429 @@
   </si>
   <si>
     <t>Простыня жатка 300х300 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4610594537422</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 40х60 - "Кианит"</t>
+  </si>
+  <si>
+    <t>15-03-2026</t>
+  </si>
+  <si>
+    <t>4610594537415</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4610594537408</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - "Мяурель"</t>
+  </si>
+  <si>
+    <t>4610594537392</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4610594537385</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Лемпи"</t>
+  </si>
+  <si>
+    <t>4610594537378</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 145х215 - М - 140 - Сияющая бирюза</t>
+  </si>
+  <si>
+    <t>4610594537361</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси резинка 180х200х30 - "Белый Этюд" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594537354</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 125 - "Фиалка" 1х1</t>
+  </si>
+  <si>
+    <t>4610594537347</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х30 - 140 - Сирень 1х1</t>
+  </si>
+  <si>
+    <t>4610594537330</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - М - 140 - Сирень 1х1</t>
+  </si>
+  <si>
+    <t>4610594537323</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х40 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4610594537316</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Милда"</t>
+  </si>
+  <si>
+    <t>4610594537309</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - М - 140 - Агатовый серый 1х1</t>
+  </si>
+  <si>
+    <t>4610594537293</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Агатовый серый 1х1</t>
+  </si>
+  <si>
+    <t>4610594537286</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 1,5 спальное резинка 120х200х30 - "Шторм"</t>
+  </si>
+  <si>
+    <t>4610594537279</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра Евро резинка 160х200х30 - "Марисоль"</t>
+  </si>
+  <si>
+    <t>4610594537262</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 90х200х30 - 60S Белый</t>
+  </si>
+  <si>
+    <t>4610594537255</t>
+  </si>
+  <si>
+    <t>Простыня поплин 180х220 - Кончерто гроссо</t>
+  </si>
+  <si>
+    <t>4610594537248</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - 120 - Баден Гольд</t>
+  </si>
+  <si>
+    <t>4610594537231</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Камара"</t>
+  </si>
+  <si>
+    <t>4610594537224</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Камара"</t>
+  </si>
+  <si>
+    <t>4610594537217</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 40х60 - "Камара"</t>
+  </si>
+  <si>
+    <t>4610594537200</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль семейное резинка 180х200х30 - 110 - Каори на желтом</t>
+  </si>
+  <si>
+    <t>4610594537194</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - "Нежный Листопад" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594537187</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 175х215 - "Лериса"</t>
+  </si>
+  <si>
+    <t>4610594537170</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 112х147 - "Баюнчик"</t>
+  </si>
+  <si>
+    <t>4610594537163</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4610594537156</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 125 - Шампань 3х3</t>
+  </si>
+  <si>
+    <t>4610594537149</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс 300х300 - "Ванильный раф"</t>
+  </si>
+  <si>
+    <t>4610594537132</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х40 - "Небра"</t>
+  </si>
+  <si>
+    <t>4610594537125</t>
+  </si>
+  <si>
+    <t>Простыня сатин 220х240 - "Цветы в Тумане"</t>
+  </si>
+  <si>
+    <t>4610594537118</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Лаванда Страйп"</t>
+  </si>
+  <si>
+    <t>4610594537101</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - "Тонкий Лист" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594537095</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х50 - "Цветы в Тумане"</t>
+  </si>
+  <si>
+    <t>4610594537088</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Мятный Квадро"</t>
+  </si>
+  <si>
+    <t>4610594537071</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х50 - Бисквитный</t>
+  </si>
+  <si>
+    <t>4610594537064</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х30 - "Мирелле"</t>
+  </si>
+  <si>
+    <t>4610594537057</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 240х260 - "Гуголету"</t>
+  </si>
+  <si>
+    <t>4610594537040</t>
+  </si>
+  <si>
+    <t>Простыня круглая ранфорс резинка 220х220х20 - Белый</t>
+  </si>
+  <si>
+    <t>4610594537033</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин твил резинка 220х220х20 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4610594537026</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 80х200х20 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4610594537019</t>
+  </si>
+  <si>
+    <t>Наволочка микрофибра 50х70 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4610594537002</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - 142 - Кленовый</t>
+  </si>
+  <si>
+    <t>4610594536999</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 120х200х20 - "Залив"</t>
+  </si>
+  <si>
+    <t>4610594536982</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 140 - Лаванда 1х1</t>
+  </si>
+  <si>
+    <t>4610594536975</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное - "Замороженный Перец" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594536968</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 135 - Секондо колоро 1х1</t>
+  </si>
+  <si>
+    <t>4610594536951</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 135 - Секондо колоро 1х1</t>
+  </si>
+  <si>
+    <t>4610594536944</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра 220х240 - "Эстрелья"</t>
+  </si>
+  <si>
+    <t>4610594536937</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро резинка 160х200х30 - 125 - Голубая бирюза</t>
+  </si>
+  <si>
+    <t>4610594536920</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - Бирюзовый берег наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594536913</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро на резинке 160х200х30 - М - 125 - однотонный Бирюза с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4610594536906</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Аргентум</t>
+  </si>
+  <si>
+    <t>4610594536890</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - М - Пинклайт</t>
+  </si>
+  <si>
+    <t>4610594536883</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х40 - 80 - Витражи</t>
+  </si>
+  <si>
+    <t>4610594536876</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное - "Звёздный Вальс" Универсал</t>
+  </si>
+  <si>
+    <t>4610594536869</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Дзета Ориона</t>
+  </si>
+  <si>
+    <t>4610594536852</t>
+  </si>
+  <si>
+    <t>Простыня жатка 200х220 - "Снежный Хищник"</t>
+  </si>
+  <si>
+    <t>4610594536845</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - 115 - Забавные енотики А+В</t>
+  </si>
+  <si>
+    <t>4610594536838</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - М - 60S 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4610594536821</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4610594536814</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4610594536807</t>
+  </si>
+  <si>
+    <t>Простыня круглая микросатин резинка 230х230х20 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4610594536791</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 230х230х30 - 140 - Шоколад 1х1</t>
+  </si>
+  <si>
+    <t>4610594536784</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 230х230х30 - 140 - Космос 1х1</t>
+  </si>
+  <si>
+    <t>4610594536777</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 220х220х40 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4610594536760</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 90х200х10 - 120 - Взмах бабочки (зеленый)</t>
+  </si>
+  <si>
+    <t>4610594536753</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 125 - Дневной Аромат</t>
+  </si>
+  <si>
+    <t>4610594536746</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - М - 60S 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4610594536739</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - М - 140 - Пудра 1х1</t>
   </si>
 </sst>
 </file>
@@ -38141,6 +38564,776 @@
         <v>4925</v>
       </c>
     </row>
+    <row r="2483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2483" t="s">
+        <v>4988</v>
+      </c>
+      <c r="B2483" t="s">
+        <v>4989</v>
+      </c>
+      <c r="C2483" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2484" t="s">
+        <v>4991</v>
+      </c>
+      <c r="B2484" t="s">
+        <v>4992</v>
+      </c>
+      <c r="C2484" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2485" t="s">
+        <v>4993</v>
+      </c>
+      <c r="B2485" t="s">
+        <v>4994</v>
+      </c>
+      <c r="C2485" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2486" t="s">
+        <v>4995</v>
+      </c>
+      <c r="B2486" t="s">
+        <v>4996</v>
+      </c>
+      <c r="C2486" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2487" t="s">
+        <v>4997</v>
+      </c>
+      <c r="B2487" t="s">
+        <v>4998</v>
+      </c>
+      <c r="C2487" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2488" t="s">
+        <v>4999</v>
+      </c>
+      <c r="B2488" t="s">
+        <v>5000</v>
+      </c>
+      <c r="C2488" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2489" t="s">
+        <v>5001</v>
+      </c>
+      <c r="B2489" t="s">
+        <v>5002</v>
+      </c>
+      <c r="C2489" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2490" t="s">
+        <v>5003</v>
+      </c>
+      <c r="B2490" t="s">
+        <v>5004</v>
+      </c>
+      <c r="C2490" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2491" t="s">
+        <v>5005</v>
+      </c>
+      <c r="B2491" t="s">
+        <v>5006</v>
+      </c>
+      <c r="C2491" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2492" t="s">
+        <v>5007</v>
+      </c>
+      <c r="B2492" t="s">
+        <v>5008</v>
+      </c>
+      <c r="C2492" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2493" t="s">
+        <v>5009</v>
+      </c>
+      <c r="B2493" t="s">
+        <v>5010</v>
+      </c>
+      <c r="C2493" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2494" t="s">
+        <v>5011</v>
+      </c>
+      <c r="B2494" t="s">
+        <v>5012</v>
+      </c>
+      <c r="C2494" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2495" t="s">
+        <v>5013</v>
+      </c>
+      <c r="B2495" t="s">
+        <v>5014</v>
+      </c>
+      <c r="C2495" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2496" t="s">
+        <v>5015</v>
+      </c>
+      <c r="B2496" t="s">
+        <v>5016</v>
+      </c>
+      <c r="C2496" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2497" t="s">
+        <v>5017</v>
+      </c>
+      <c r="B2497" t="s">
+        <v>5018</v>
+      </c>
+      <c r="C2497" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2498" t="s">
+        <v>5019</v>
+      </c>
+      <c r="B2498" t="s">
+        <v>5020</v>
+      </c>
+      <c r="C2498" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2499" t="s">
+        <v>5021</v>
+      </c>
+      <c r="B2499" t="s">
+        <v>5022</v>
+      </c>
+      <c r="C2499" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2500" t="s">
+        <v>5023</v>
+      </c>
+      <c r="B2500" t="s">
+        <v>5024</v>
+      </c>
+      <c r="C2500" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2501" t="s">
+        <v>5025</v>
+      </c>
+      <c r="B2501" t="s">
+        <v>5026</v>
+      </c>
+      <c r="C2501" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2502" t="s">
+        <v>5027</v>
+      </c>
+      <c r="B2502" t="s">
+        <v>5028</v>
+      </c>
+      <c r="C2502" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2503" t="s">
+        <v>5029</v>
+      </c>
+      <c r="B2503" t="s">
+        <v>5030</v>
+      </c>
+      <c r="C2503" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2504" t="s">
+        <v>5031</v>
+      </c>
+      <c r="B2504" t="s">
+        <v>5032</v>
+      </c>
+      <c r="C2504" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2505" t="s">
+        <v>5033</v>
+      </c>
+      <c r="B2505" t="s">
+        <v>5034</v>
+      </c>
+      <c r="C2505" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2506" t="s">
+        <v>5035</v>
+      </c>
+      <c r="B2506" t="s">
+        <v>5036</v>
+      </c>
+      <c r="C2506" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2507" t="s">
+        <v>5037</v>
+      </c>
+      <c r="B2507" t="s">
+        <v>5038</v>
+      </c>
+      <c r="C2507" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2508" t="s">
+        <v>5039</v>
+      </c>
+      <c r="B2508" t="s">
+        <v>5040</v>
+      </c>
+      <c r="C2508" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2509" t="s">
+        <v>5041</v>
+      </c>
+      <c r="B2509" t="s">
+        <v>5042</v>
+      </c>
+      <c r="C2509" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2510" t="s">
+        <v>5043</v>
+      </c>
+      <c r="B2510" t="s">
+        <v>5044</v>
+      </c>
+      <c r="C2510" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2511" t="s">
+        <v>5045</v>
+      </c>
+      <c r="B2511" t="s">
+        <v>5046</v>
+      </c>
+      <c r="C2511" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2512" t="s">
+        <v>5047</v>
+      </c>
+      <c r="B2512" t="s">
+        <v>5048</v>
+      </c>
+      <c r="C2512" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2513" t="s">
+        <v>5049</v>
+      </c>
+      <c r="B2513" t="s">
+        <v>5050</v>
+      </c>
+      <c r="C2513" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2514" t="s">
+        <v>5051</v>
+      </c>
+      <c r="B2514" t="s">
+        <v>5052</v>
+      </c>
+      <c r="C2514" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2515" t="s">
+        <v>5053</v>
+      </c>
+      <c r="B2515" t="s">
+        <v>5054</v>
+      </c>
+      <c r="C2515" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2516" t="s">
+        <v>5055</v>
+      </c>
+      <c r="B2516" t="s">
+        <v>5056</v>
+      </c>
+      <c r="C2516" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2517" t="s">
+        <v>5057</v>
+      </c>
+      <c r="B2517" t="s">
+        <v>5058</v>
+      </c>
+      <c r="C2517" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2518" t="s">
+        <v>5059</v>
+      </c>
+      <c r="B2518" t="s">
+        <v>5060</v>
+      </c>
+      <c r="C2518" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2519" t="s">
+        <v>5061</v>
+      </c>
+      <c r="B2519" t="s">
+        <v>5062</v>
+      </c>
+      <c r="C2519" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2520" t="s">
+        <v>5063</v>
+      </c>
+      <c r="B2520" t="s">
+        <v>5064</v>
+      </c>
+      <c r="C2520" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2521" t="s">
+        <v>5065</v>
+      </c>
+      <c r="B2521" t="s">
+        <v>5066</v>
+      </c>
+      <c r="C2521" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2522" t="s">
+        <v>5067</v>
+      </c>
+      <c r="B2522" t="s">
+        <v>5068</v>
+      </c>
+      <c r="C2522" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2523" t="s">
+        <v>5069</v>
+      </c>
+      <c r="B2523" t="s">
+        <v>5070</v>
+      </c>
+      <c r="C2523" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2524" t="s">
+        <v>5071</v>
+      </c>
+      <c r="B2524" t="s">
+        <v>5072</v>
+      </c>
+      <c r="C2524" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2525" t="s">
+        <v>5073</v>
+      </c>
+      <c r="B2525" t="s">
+        <v>5074</v>
+      </c>
+      <c r="C2525" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2526" t="s">
+        <v>5075</v>
+      </c>
+      <c r="B2526" t="s">
+        <v>5076</v>
+      </c>
+      <c r="C2526" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2527" t="s">
+        <v>5077</v>
+      </c>
+      <c r="B2527" t="s">
+        <v>5078</v>
+      </c>
+      <c r="C2527" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2528" t="s">
+        <v>5079</v>
+      </c>
+      <c r="B2528" t="s">
+        <v>5080</v>
+      </c>
+      <c r="C2528" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2529" t="s">
+        <v>5081</v>
+      </c>
+      <c r="B2529" t="s">
+        <v>5082</v>
+      </c>
+      <c r="C2529" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2530" t="s">
+        <v>5083</v>
+      </c>
+      <c r="B2530" t="s">
+        <v>5084</v>
+      </c>
+      <c r="C2530" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2531" t="s">
+        <v>5085</v>
+      </c>
+      <c r="B2531" t="s">
+        <v>5086</v>
+      </c>
+      <c r="C2531" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2532" t="s">
+        <v>5087</v>
+      </c>
+      <c r="B2532" t="s">
+        <v>5088</v>
+      </c>
+      <c r="C2532" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2533" t="s">
+        <v>5089</v>
+      </c>
+      <c r="B2533" t="s">
+        <v>5090</v>
+      </c>
+      <c r="C2533" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2534" t="s">
+        <v>5091</v>
+      </c>
+      <c r="B2534" t="s">
+        <v>5092</v>
+      </c>
+      <c r="C2534" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2535" t="s">
+        <v>5093</v>
+      </c>
+      <c r="B2535" t="s">
+        <v>5094</v>
+      </c>
+      <c r="C2535" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2536" t="s">
+        <v>5095</v>
+      </c>
+      <c r="B2536" t="s">
+        <v>5096</v>
+      </c>
+      <c r="C2536" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2537" t="s">
+        <v>5097</v>
+      </c>
+      <c r="B2537" t="s">
+        <v>5098</v>
+      </c>
+      <c r="C2537" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2538" t="s">
+        <v>5099</v>
+      </c>
+      <c r="B2538" t="s">
+        <v>5100</v>
+      </c>
+      <c r="C2538" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2539" t="s">
+        <v>5101</v>
+      </c>
+      <c r="B2539" t="s">
+        <v>5102</v>
+      </c>
+      <c r="C2539" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2540" t="s">
+        <v>5103</v>
+      </c>
+      <c r="B2540" t="s">
+        <v>5104</v>
+      </c>
+      <c r="C2540" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2541" t="s">
+        <v>5105</v>
+      </c>
+      <c r="B2541" t="s">
+        <v>5106</v>
+      </c>
+      <c r="C2541" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2542" t="s">
+        <v>5107</v>
+      </c>
+      <c r="B2542" t="s">
+        <v>5108</v>
+      </c>
+      <c r="C2542" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2543" t="s">
+        <v>5109</v>
+      </c>
+      <c r="B2543" t="s">
+        <v>5110</v>
+      </c>
+      <c r="C2543" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2544" t="s">
+        <v>5111</v>
+      </c>
+      <c r="B2544" t="s">
+        <v>5112</v>
+      </c>
+      <c r="C2544" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2545" t="s">
+        <v>5113</v>
+      </c>
+      <c r="B2545" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C2545" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2546" t="s">
+        <v>5115</v>
+      </c>
+      <c r="B2546" t="s">
+        <v>5116</v>
+      </c>
+      <c r="C2546" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2547" t="s">
+        <v>5117</v>
+      </c>
+      <c r="B2547" t="s">
+        <v>5118</v>
+      </c>
+      <c r="C2547" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2548" t="s">
+        <v>5119</v>
+      </c>
+      <c r="B2548" t="s">
+        <v>5120</v>
+      </c>
+      <c r="C2548" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2549" t="s">
+        <v>5121</v>
+      </c>
+      <c r="B2549" t="s">
+        <v>5122</v>
+      </c>
+      <c r="C2549" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2550" t="s">
+        <v>5123</v>
+      </c>
+      <c r="B2550" t="s">
+        <v>5124</v>
+      </c>
+      <c r="C2550" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2551" t="s">
+        <v>5125</v>
+      </c>
+      <c r="B2551" t="s">
+        <v>5126</v>
+      </c>
+      <c r="C2551" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2552" t="s">
+        <v>5127</v>
+      </c>
+      <c r="B2552" t="s">
+        <v>5128</v>
+      </c>
+      <c r="C2552" t="s">
+        <v>4990</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6150" uniqueCount="5129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6219" uniqueCount="5176">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -15401,6 +15401,147 @@
   </si>
   <si>
     <t>Пододеяльник страйп-сатин 150х200 - М - 140 - Пудра 1х1</t>
+  </si>
+  <si>
+    <t>4610594537651</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 90х200х30 - "Котик в космосе"</t>
+  </si>
+  <si>
+    <t>16-03-2026</t>
+  </si>
+  <si>
+    <t>4610594537644</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное резинка 160х200х20 - "Звёздный туман" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594537637</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Экзотический"</t>
+  </si>
+  <si>
+    <t>4610594537620</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 140х200х30 - "Линнея" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594537613</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 130 - Пудровый 1х1</t>
+  </si>
+  <si>
+    <t>4610594537606</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 150х220 - 140 - Пудра 1х1</t>
+  </si>
+  <si>
+    <t>4610594537590</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - М - Вуалетка</t>
+  </si>
+  <si>
+    <t>4610594537583</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро - Грей Стайл</t>
+  </si>
+  <si>
+    <t>4610594537576</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Ритва"</t>
+  </si>
+  <si>
+    <t>4610594537569</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - Премиум ТС 320 Белый</t>
+  </si>
+  <si>
+    <t>4610594537552</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - Премиум ТС 320 Кортес</t>
+  </si>
+  <si>
+    <t>4610594537545</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - Премиум ТС 320 Кортес</t>
+  </si>
+  <si>
+    <t>4610594537538</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 150х200 - М - Премиум ТС 320 Кортес</t>
+  </si>
+  <si>
+    <t>4610594537521</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро-макси - "Оливейт"</t>
+  </si>
+  <si>
+    <t>4610594537514</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - М - 60S 4323 Бежево-розовый</t>
+  </si>
+  <si>
+    <t>4610594537507</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - М - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4610594537491</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное - "Дино-пати" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594537484</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 140х200х20 - 221 Бежевый</t>
+  </si>
+  <si>
+    <t>4610594537477</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное Евро простыня - "Фиолетовый Шёпот"</t>
+  </si>
+  <si>
+    <t>4610594537460</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4610594537453</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 90х200х10 - "Тирас"</t>
+  </si>
+  <si>
+    <t>4610594537446</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4610594537439</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 200х220 - "Лесная тень"</t>
   </si>
 </sst>
 </file>
@@ -39334,6 +39475,259 @@
         <v>4990</v>
       </c>
     </row>
+    <row r="2553" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2553" t="s">
+        <v>5129</v>
+      </c>
+      <c r="B2553" t="s">
+        <v>5130</v>
+      </c>
+      <c r="C2553" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2554" t="s">
+        <v>5132</v>
+      </c>
+      <c r="B2554" t="s">
+        <v>5133</v>
+      </c>
+      <c r="C2554" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2555" t="s">
+        <v>5134</v>
+      </c>
+      <c r="B2555" t="s">
+        <v>5135</v>
+      </c>
+      <c r="C2555" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2556" t="s">
+        <v>5136</v>
+      </c>
+      <c r="B2556" t="s">
+        <v>5137</v>
+      </c>
+      <c r="C2556" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2557" t="s">
+        <v>5138</v>
+      </c>
+      <c r="B2557" t="s">
+        <v>5139</v>
+      </c>
+      <c r="C2557" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2558" t="s">
+        <v>5140</v>
+      </c>
+      <c r="B2558" t="s">
+        <v>5141</v>
+      </c>
+      <c r="C2558" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2559" t="s">
+        <v>5142</v>
+      </c>
+      <c r="B2559" t="s">
+        <v>5143</v>
+      </c>
+      <c r="C2559" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2560" t="s">
+        <v>5144</v>
+      </c>
+      <c r="B2560" t="s">
+        <v>5145</v>
+      </c>
+      <c r="C2560" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2561" t="s">
+        <v>5146</v>
+      </c>
+      <c r="B2561" t="s">
+        <v>5147</v>
+      </c>
+      <c r="C2561" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2562" t="s">
+        <v>5148</v>
+      </c>
+      <c r="B2562" t="s">
+        <v>5149</v>
+      </c>
+      <c r="C2562" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2563" t="s">
+        <v>5150</v>
+      </c>
+      <c r="B2563" t="s">
+        <v>5151</v>
+      </c>
+      <c r="C2563" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2564" t="s">
+        <v>5152</v>
+      </c>
+      <c r="B2564" t="s">
+        <v>5153</v>
+      </c>
+      <c r="C2564" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2565" t="s">
+        <v>5154</v>
+      </c>
+      <c r="B2565" t="s">
+        <v>5155</v>
+      </c>
+      <c r="C2565" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2566" t="s">
+        <v>5156</v>
+      </c>
+      <c r="B2566" t="s">
+        <v>5157</v>
+      </c>
+      <c r="C2566" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2567" t="s">
+        <v>5158</v>
+      </c>
+      <c r="B2567" t="s">
+        <v>5159</v>
+      </c>
+      <c r="C2567" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2568" t="s">
+        <v>5160</v>
+      </c>
+      <c r="B2568" t="s">
+        <v>5161</v>
+      </c>
+      <c r="C2568" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2569" t="s">
+        <v>5162</v>
+      </c>
+      <c r="B2569" t="s">
+        <v>5163</v>
+      </c>
+      <c r="C2569" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2570" t="s">
+        <v>5164</v>
+      </c>
+      <c r="B2570" t="s">
+        <v>5165</v>
+      </c>
+      <c r="C2570" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2571" t="s">
+        <v>5166</v>
+      </c>
+      <c r="B2571" t="s">
+        <v>5167</v>
+      </c>
+      <c r="C2571" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2572" t="s">
+        <v>5168</v>
+      </c>
+      <c r="B2572" t="s">
+        <v>5169</v>
+      </c>
+      <c r="C2572" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2573" t="s">
+        <v>5170</v>
+      </c>
+      <c r="B2573" t="s">
+        <v>5171</v>
+      </c>
+      <c r="C2573" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2574" t="s">
+        <v>5172</v>
+      </c>
+      <c r="B2574" t="s">
+        <v>5173</v>
+      </c>
+      <c r="C2574" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2575" t="s">
+        <v>5174</v>
+      </c>
+      <c r="B2575" t="s">
+        <v>5175</v>
+      </c>
+      <c r="C2575" t="s">
+        <v>5131</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6219" uniqueCount="5176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6291" uniqueCount="5225">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -15542,6 +15542,153 @@
   </si>
   <si>
     <t>Простыня сатин твил 200х220 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>4610594537897</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - 120 - Урубамба</t>
+  </si>
+  <si>
+    <t>17-03-2026</t>
+  </si>
+  <si>
+    <t>4610594537880</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4610594537873</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 40х60 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4610594537866</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси - "Димитра"</t>
+  </si>
+  <si>
+    <t>4610594537859</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х50 - Молочный</t>
+  </si>
+  <si>
+    <t>4610594537842</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 200х220 - Вечерний песок</t>
+  </si>
+  <si>
+    <t>4610594537835</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4610594537828</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 180х200х30 - 120 - Белый</t>
+  </si>
+  <si>
+    <t>4610594537811</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 40х60 - "Облачка"</t>
+  </si>
+  <si>
+    <t>4610594537804</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 60х60 - Прохлада ментола</t>
+  </si>
+  <si>
+    <t>4610594537798</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 60х60 - Морской</t>
+  </si>
+  <si>
+    <t>4610594537781</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х50 - 125 - Виолет Мореля</t>
+  </si>
+  <si>
+    <t>4610594537774</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 180х220 - "Сахарная роза"</t>
+  </si>
+  <si>
+    <t>4610594537767</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 200х200х30 - 110 - Белоснежный луч</t>
+  </si>
+  <si>
+    <t>4610594537750</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 50х70 - Ежевичный смузи</t>
+  </si>
+  <si>
+    <t>4610594537743</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х200 - "Хореография"</t>
+  </si>
+  <si>
+    <t>4610594537736</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х200 - М - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4610594537729</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 60х60 - 135 - Таволга</t>
+  </si>
+  <si>
+    <t>4610594537712</t>
+  </si>
+  <si>
+    <t>Пододеяльник из страйп микрофибры 200 х 200 - М - 85 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4610594537705</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х10 - 120 - Морской Цветок</t>
+  </si>
+  <si>
+    <t>4610594537699</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - "Эвергрин"</t>
+  </si>
+  <si>
+    <t>4610594537682</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х20 - "Касилия"</t>
+  </si>
+  <si>
+    <t>4610594537675</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х10 - 142 ГОСТ - Изумруд</t>
+  </si>
+  <si>
+    <t>4610594537668</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 220х240 - М - 110 - Белоснежный луч</t>
   </si>
 </sst>
 </file>
@@ -39728,6 +39875,270 @@
         <v>5131</v>
       </c>
     </row>
+    <row r="2576" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2576" t="s">
+        <v>5176</v>
+      </c>
+      <c r="B2576" t="s">
+        <v>5177</v>
+      </c>
+      <c r="C2576" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2577" t="s">
+        <v>5179</v>
+      </c>
+      <c r="B2577" t="s">
+        <v>5180</v>
+      </c>
+      <c r="C2577" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2578" t="s">
+        <v>5181</v>
+      </c>
+      <c r="B2578" t="s">
+        <v>5182</v>
+      </c>
+      <c r="C2578" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2579" t="s">
+        <v>5183</v>
+      </c>
+      <c r="B2579" t="s">
+        <v>5184</v>
+      </c>
+      <c r="C2579" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2580" t="s">
+        <v>5185</v>
+      </c>
+      <c r="B2580" t="s">
+        <v>5186</v>
+      </c>
+      <c r="C2580" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2581" t="s">
+        <v>5187</v>
+      </c>
+      <c r="B2581" t="s">
+        <v>5188</v>
+      </c>
+      <c r="C2581" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2582" t="s">
+        <v>5189</v>
+      </c>
+      <c r="B2582" t="s">
+        <v>5190</v>
+      </c>
+      <c r="C2582" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2583" t="s">
+        <v>5191</v>
+      </c>
+      <c r="B2583" t="s">
+        <v>5192</v>
+      </c>
+      <c r="C2583" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2584" t="s">
+        <v>5193</v>
+      </c>
+      <c r="B2584" t="s">
+        <v>5194</v>
+      </c>
+      <c r="C2584" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2585" t="s">
+        <v>5195</v>
+      </c>
+      <c r="B2585" t="s">
+        <v>5196</v>
+      </c>
+      <c r="C2585" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2586" t="s">
+        <v>5197</v>
+      </c>
+      <c r="B2586" t="s">
+        <v>5198</v>
+      </c>
+      <c r="C2586" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2587" t="s">
+        <v>5199</v>
+      </c>
+      <c r="B2587" t="s">
+        <v>5200</v>
+      </c>
+      <c r="C2587" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2588" t="s">
+        <v>5201</v>
+      </c>
+      <c r="B2588" t="s">
+        <v>5202</v>
+      </c>
+      <c r="C2588" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2589" t="s">
+        <v>5203</v>
+      </c>
+      <c r="B2589" t="s">
+        <v>5204</v>
+      </c>
+      <c r="C2589" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2590" t="s">
+        <v>5205</v>
+      </c>
+      <c r="B2590" t="s">
+        <v>5206</v>
+      </c>
+      <c r="C2590" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2591" t="s">
+        <v>5207</v>
+      </c>
+      <c r="B2591" t="s">
+        <v>5208</v>
+      </c>
+      <c r="C2591" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2592" t="s">
+        <v>5209</v>
+      </c>
+      <c r="B2592" t="s">
+        <v>5210</v>
+      </c>
+      <c r="C2592" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2593" t="s">
+        <v>5211</v>
+      </c>
+      <c r="B2593" t="s">
+        <v>5212</v>
+      </c>
+      <c r="C2593" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2594" t="s">
+        <v>5213</v>
+      </c>
+      <c r="B2594" t="s">
+        <v>5214</v>
+      </c>
+      <c r="C2594" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2595" t="s">
+        <v>5215</v>
+      </c>
+      <c r="B2595" t="s">
+        <v>5216</v>
+      </c>
+      <c r="C2595" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2596" t="s">
+        <v>5217</v>
+      </c>
+      <c r="B2596" t="s">
+        <v>5218</v>
+      </c>
+      <c r="C2596" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2597" t="s">
+        <v>5219</v>
+      </c>
+      <c r="B2597" t="s">
+        <v>5220</v>
+      </c>
+      <c r="C2597" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2598" t="s">
+        <v>5221</v>
+      </c>
+      <c r="B2598" t="s">
+        <v>5222</v>
+      </c>
+      <c r="C2598" t="s">
+        <v>5178</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2599" t="s">
+        <v>5223</v>
+      </c>
+      <c r="B2599" t="s">
+        <v>5224</v>
+      </c>
+      <c r="C2599" t="s">
+        <v>5178</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6291" uniqueCount="5225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6345" uniqueCount="5262">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -15689,6 +15689,117 @@
   </si>
   <si>
     <t>Пододеяльник перкаль 220х240 - М - 110 - Белоснежный луч</t>
+  </si>
+  <si>
+    <t>4610594537903</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - Ясное небо наволочки 50х70</t>
+  </si>
+  <si>
+    <t>18-03-2026</t>
+  </si>
+  <si>
+    <t>4610594538078</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси резинка 180х200х30 - "Белый Этюд"</t>
+  </si>
+  <si>
+    <t>4610594538061</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - "Лиловый тауп" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594538054</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х30 - Прелат А+В</t>
+  </si>
+  <si>
+    <t>4610594538047</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 150х220 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4610594538030</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь семейное - 120 - Луговой Нектар А+В</t>
+  </si>
+  <si>
+    <t>4610594538023</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Темный изумруд"</t>
+  </si>
+  <si>
+    <t>4610594538016</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Темный изумруд"</t>
+  </si>
+  <si>
+    <t>4610594538009</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное резинка 160х200х20 - "Астероид" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594537996</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Белый Этюд"</t>
+  </si>
+  <si>
+    <t>4610594537989</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4610594537972</t>
+  </si>
+  <si>
+    <t>КПБ Постельное белье тенсель Евро - М - 60S 4393 Темно-серый</t>
+  </si>
+  <si>
+    <t>4610594537965</t>
+  </si>
+  <si>
+    <t>Простыня круглая микрофибра резинка 210х210х20 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4610594537958</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 70х70 - Чёрная гавань</t>
+  </si>
+  <si>
+    <t>4610594537941</t>
+  </si>
+  <si>
+    <t>Простыня бязь 100х150 - 120 - Развлечение</t>
+  </si>
+  <si>
+    <t>4610594537934</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - Горький шоколад наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594537927</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х30 - "Тирас"</t>
+  </si>
+  <si>
+    <t>4610594537910</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х30 - "Эвергрин"</t>
   </si>
 </sst>
 </file>
@@ -40139,6 +40250,204 @@
         <v>5178</v>
       </c>
     </row>
+    <row r="2600" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2600" t="s">
+        <v>5225</v>
+      </c>
+      <c r="B2600" t="s">
+        <v>5226</v>
+      </c>
+      <c r="C2600" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2601" t="s">
+        <v>5228</v>
+      </c>
+      <c r="B2601" t="s">
+        <v>5229</v>
+      </c>
+      <c r="C2601" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2602" t="s">
+        <v>5230</v>
+      </c>
+      <c r="B2602" t="s">
+        <v>5231</v>
+      </c>
+      <c r="C2602" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2603" t="s">
+        <v>5232</v>
+      </c>
+      <c r="B2603" t="s">
+        <v>5233</v>
+      </c>
+      <c r="C2603" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2604" t="s">
+        <v>5234</v>
+      </c>
+      <c r="B2604" t="s">
+        <v>5235</v>
+      </c>
+      <c r="C2604" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2605" t="s">
+        <v>5236</v>
+      </c>
+      <c r="B2605" t="s">
+        <v>5237</v>
+      </c>
+      <c r="C2605" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2606" t="s">
+        <v>5238</v>
+      </c>
+      <c r="B2606" t="s">
+        <v>5239</v>
+      </c>
+      <c r="C2606" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2607" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2607" t="s">
+        <v>5240</v>
+      </c>
+      <c r="B2607" t="s">
+        <v>5241</v>
+      </c>
+      <c r="C2607" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2608" t="s">
+        <v>5242</v>
+      </c>
+      <c r="B2608" t="s">
+        <v>5243</v>
+      </c>
+      <c r="C2608" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2609" t="s">
+        <v>5244</v>
+      </c>
+      <c r="B2609" t="s">
+        <v>5245</v>
+      </c>
+      <c r="C2609" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2610" t="s">
+        <v>5246</v>
+      </c>
+      <c r="B2610" t="s">
+        <v>5247</v>
+      </c>
+      <c r="C2610" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2611" t="s">
+        <v>5248</v>
+      </c>
+      <c r="B2611" t="s">
+        <v>5249</v>
+      </c>
+      <c r="C2611" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2612" t="s">
+        <v>5250</v>
+      </c>
+      <c r="B2612" t="s">
+        <v>5251</v>
+      </c>
+      <c r="C2612" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2613" t="s">
+        <v>5252</v>
+      </c>
+      <c r="B2613" t="s">
+        <v>5253</v>
+      </c>
+      <c r="C2613" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2614" t="s">
+        <v>5254</v>
+      </c>
+      <c r="B2614" t="s">
+        <v>5255</v>
+      </c>
+      <c r="C2614" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2615" t="s">
+        <v>5256</v>
+      </c>
+      <c r="B2615" t="s">
+        <v>5257</v>
+      </c>
+      <c r="C2615" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2616" t="s">
+        <v>5258</v>
+      </c>
+      <c r="B2616" t="s">
+        <v>5259</v>
+      </c>
+      <c r="C2616" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2617" t="s">
+        <v>5260</v>
+      </c>
+      <c r="B2617" t="s">
+        <v>5261</v>
+      </c>
+      <c r="C2617" t="s">
+        <v>5227</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6345" uniqueCount="5262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6387" uniqueCount="5291">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -15800,6 +15800,93 @@
   </si>
   <si>
     <t>Простыня полисатин резинка 140х200х30 - "Эвергрин"</t>
+  </si>
+  <si>
+    <t>4610594538214</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Кианит"</t>
+  </si>
+  <si>
+    <t>19-03-2026</t>
+  </si>
+  <si>
+    <t>4610594538207</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х40 - 135 - Блу Хейз 1х1</t>
+  </si>
+  <si>
+    <t>4610594538191</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 240х260 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4610594538184</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 60х60 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4610594538177</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - М - Индостан</t>
+  </si>
+  <si>
+    <t>4610594538160</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - М - Прерия</t>
+  </si>
+  <si>
+    <t>4610594538153</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 240х260 - "Салатовый"</t>
+  </si>
+  <si>
+    <t>4610594538146</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4610594538139</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - 140 - Агатовый серый 1х1</t>
+  </si>
+  <si>
+    <t>4610594538122</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 220х240 - М - 125 - Светло-серый 3</t>
+  </si>
+  <si>
+    <t>4610594538115</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 200х220 - Нежно-розовый</t>
+  </si>
+  <si>
+    <t>4610594538108</t>
+  </si>
+  <si>
+    <t>Пододеяльник из страйп микрофибры 200 х 220 - М - 85 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4610594538092</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 175х215 - М - 120 - Урубамба</t>
+  </si>
+  <si>
+    <t>4610594538085</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 160х200х20 - "Тирас" наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -40448,6 +40535,160 @@
         <v>5227</v>
       </c>
     </row>
+    <row r="2618" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2618" t="s">
+        <v>5262</v>
+      </c>
+      <c r="B2618" t="s">
+        <v>5263</v>
+      </c>
+      <c r="C2618" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2619" t="s">
+        <v>5265</v>
+      </c>
+      <c r="B2619" t="s">
+        <v>5266</v>
+      </c>
+      <c r="C2619" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2620" t="s">
+        <v>5267</v>
+      </c>
+      <c r="B2620" t="s">
+        <v>5268</v>
+      </c>
+      <c r="C2620" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2621" t="s">
+        <v>5269</v>
+      </c>
+      <c r="B2621" t="s">
+        <v>5270</v>
+      </c>
+      <c r="C2621" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2622" t="s">
+        <v>5271</v>
+      </c>
+      <c r="B2622" t="s">
+        <v>5272</v>
+      </c>
+      <c r="C2622" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2623" t="s">
+        <v>5273</v>
+      </c>
+      <c r="B2623" t="s">
+        <v>5274</v>
+      </c>
+      <c r="C2623" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2624" t="s">
+        <v>5275</v>
+      </c>
+      <c r="B2624" t="s">
+        <v>5276</v>
+      </c>
+      <c r="C2624" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2625" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2625" t="s">
+        <v>5277</v>
+      </c>
+      <c r="B2625" t="s">
+        <v>5278</v>
+      </c>
+      <c r="C2625" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2626" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2626" t="s">
+        <v>5279</v>
+      </c>
+      <c r="B2626" t="s">
+        <v>5280</v>
+      </c>
+      <c r="C2626" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2627" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2627" t="s">
+        <v>5281</v>
+      </c>
+      <c r="B2627" t="s">
+        <v>5282</v>
+      </c>
+      <c r="C2627" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2628" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2628" t="s">
+        <v>5283</v>
+      </c>
+      <c r="B2628" t="s">
+        <v>5284</v>
+      </c>
+      <c r="C2628" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2629" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2629" t="s">
+        <v>5285</v>
+      </c>
+      <c r="B2629" t="s">
+        <v>5286</v>
+      </c>
+      <c r="C2629" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2630" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2630" t="s">
+        <v>5287</v>
+      </c>
+      <c r="B2630" t="s">
+        <v>5288</v>
+      </c>
+      <c r="C2630" t="s">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="2631" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2631" t="s">
+        <v>5289</v>
+      </c>
+      <c r="B2631" t="s">
+        <v>5290</v>
+      </c>
+      <c r="C2631" t="s">
+        <v>5264</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6387" uniqueCount="5291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6507" uniqueCount="5372">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -15887,6 +15887,249 @@
   </si>
   <si>
     <t>КПБ Постельное бельё полисатин 2 спальное резинка 160х200х20 - "Тирас" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594538610</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - "Морозный туман"</t>
+  </si>
+  <si>
+    <t>20-03-2026</t>
+  </si>
+  <si>
+    <t>4610594538603</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 200х220 - 135 - Фирюз 1х1</t>
+  </si>
+  <si>
+    <t>4610594538597</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное резинка 160х200х30 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4610594538580</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - Гранола</t>
+  </si>
+  <si>
+    <t>4610594538573</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х30 - "Милкшейк"</t>
+  </si>
+  <si>
+    <t>4610594538566</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х40 - 60S 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4610594538559</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Ларион"</t>
+  </si>
+  <si>
+    <t>4610594538542</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4610594538535</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4610594538528</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 120х200х30 - Сливочно-кремовый</t>
+  </si>
+  <si>
+    <t>4610594538511</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Милда"</t>
+  </si>
+  <si>
+    <t>4610594538504</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Серебряный Папоротник"</t>
+  </si>
+  <si>
+    <t>4610594538498</t>
+  </si>
+  <si>
+    <t>Простыня сатин 180х220 - 135 - Кремово-белый</t>
+  </si>
+  <si>
+    <t>4610594538481</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 180х220 - "Овсяный"</t>
+  </si>
+  <si>
+    <t>4610594538474</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 200х200х30 - 110 - Полнолуние</t>
+  </si>
+  <si>
+    <t>4610594538467</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 160х200х30 - "Небосвод"</t>
+  </si>
+  <si>
+    <t>4610594538450</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - М - Пыльная роза</t>
+  </si>
+  <si>
+    <t>4610594538443</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - Белое облако</t>
+  </si>
+  <si>
+    <t>4610594538436</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Голубая дымка"</t>
+  </si>
+  <si>
+    <t>4610594538429</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Лиловый тауп"</t>
+  </si>
+  <si>
+    <t>4610594538412</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 60х60 - "Асуль"</t>
+  </si>
+  <si>
+    <t>4610594538405</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4610594538399</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 240х260 - М - Дымчатый</t>
+  </si>
+  <si>
+    <t>4610594538382</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 240х260 - М - Молочный</t>
+  </si>
+  <si>
+    <t>4610594538375</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - "Медный" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594538368</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х30 - 135 - Солнечный, полоска 1х1</t>
+  </si>
+  <si>
+    <t>4610594538351</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё бязь для детских кроваток - Нежный сон 1 гол.</t>
+  </si>
+  <si>
+    <t>4610594538344</t>
+  </si>
+  <si>
+    <t>Простыня круглая микрофибра резинка 200х200х30 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4610594538337</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Туманная Ветвь"</t>
+  </si>
+  <si>
+    <t>4610594538320</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - М - Мазарин блу</t>
+  </si>
+  <si>
+    <t>4610594538313</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 90х200х30 - "Голубая дымка"</t>
+  </si>
+  <si>
+    <t>4610594538306</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Мазарин блу</t>
+  </si>
+  <si>
+    <t>4610594538290</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - "Призрачная лагуна"</t>
+  </si>
+  <si>
+    <t>4610594538283</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 140х200х30 - "Асуль"</t>
+  </si>
+  <si>
+    <t>4610594538276</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х50 - "Коралловый Шёлк"</t>
+  </si>
+  <si>
+    <t>4610594538269</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х200 - М - Премиум ТС 320 Кортес</t>
+  </si>
+  <si>
+    <t>4610594538252</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс 240х260 - Голубой</t>
+  </si>
+  <si>
+    <t>4610594538245</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - "Чёрный Страйп"</t>
+  </si>
+  <si>
+    <t>4610594538238</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - "Пухлянки" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594538221</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 200х220 - "Холодная элегия"</t>
   </si>
 </sst>
 </file>
@@ -40689,6 +40932,446 @@
         <v>5264</v>
       </c>
     </row>
+    <row r="2632" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2632" t="s">
+        <v>5291</v>
+      </c>
+      <c r="B2632" t="s">
+        <v>5292</v>
+      </c>
+      <c r="C2632" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2633" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2633" t="s">
+        <v>5294</v>
+      </c>
+      <c r="B2633" t="s">
+        <v>5295</v>
+      </c>
+      <c r="C2633" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2634" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2634" t="s">
+        <v>5296</v>
+      </c>
+      <c r="B2634" t="s">
+        <v>5297</v>
+      </c>
+      <c r="C2634" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2635" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2635" t="s">
+        <v>5298</v>
+      </c>
+      <c r="B2635" t="s">
+        <v>5299</v>
+      </c>
+      <c r="C2635" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2636" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2636" t="s">
+        <v>5300</v>
+      </c>
+      <c r="B2636" t="s">
+        <v>5301</v>
+      </c>
+      <c r="C2636" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2637" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2637" t="s">
+        <v>5302</v>
+      </c>
+      <c r="B2637" t="s">
+        <v>5303</v>
+      </c>
+      <c r="C2637" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2638" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2638" t="s">
+        <v>5304</v>
+      </c>
+      <c r="B2638" t="s">
+        <v>5305</v>
+      </c>
+      <c r="C2638" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2639" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2639" t="s">
+        <v>5306</v>
+      </c>
+      <c r="B2639" t="s">
+        <v>5307</v>
+      </c>
+      <c r="C2639" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2640" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2640" t="s">
+        <v>5308</v>
+      </c>
+      <c r="B2640" t="s">
+        <v>5309</v>
+      </c>
+      <c r="C2640" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2641" t="s">
+        <v>5310</v>
+      </c>
+      <c r="B2641" t="s">
+        <v>5311</v>
+      </c>
+      <c r="C2641" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2642" t="s">
+        <v>5312</v>
+      </c>
+      <c r="B2642" t="s">
+        <v>5313</v>
+      </c>
+      <c r="C2642" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2643" t="s">
+        <v>5314</v>
+      </c>
+      <c r="B2643" t="s">
+        <v>5315</v>
+      </c>
+      <c r="C2643" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2644" t="s">
+        <v>5316</v>
+      </c>
+      <c r="B2644" t="s">
+        <v>5317</v>
+      </c>
+      <c r="C2644" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2645" t="s">
+        <v>5318</v>
+      </c>
+      <c r="B2645" t="s">
+        <v>5319</v>
+      </c>
+      <c r="C2645" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2646" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2646" t="s">
+        <v>5320</v>
+      </c>
+      <c r="B2646" t="s">
+        <v>5321</v>
+      </c>
+      <c r="C2646" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2647" t="s">
+        <v>5322</v>
+      </c>
+      <c r="B2647" t="s">
+        <v>5323</v>
+      </c>
+      <c r="C2647" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2648" t="s">
+        <v>5324</v>
+      </c>
+      <c r="B2648" t="s">
+        <v>5325</v>
+      </c>
+      <c r="C2648" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2649" t="s">
+        <v>5326</v>
+      </c>
+      <c r="B2649" t="s">
+        <v>5327</v>
+      </c>
+      <c r="C2649" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2650" t="s">
+        <v>5328</v>
+      </c>
+      <c r="B2650" t="s">
+        <v>5329</v>
+      </c>
+      <c r="C2650" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2651" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2651" t="s">
+        <v>5330</v>
+      </c>
+      <c r="B2651" t="s">
+        <v>5331</v>
+      </c>
+      <c r="C2651" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2652" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2652" t="s">
+        <v>5332</v>
+      </c>
+      <c r="B2652" t="s">
+        <v>5333</v>
+      </c>
+      <c r="C2652" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2653" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2653" t="s">
+        <v>5334</v>
+      </c>
+      <c r="B2653" t="s">
+        <v>5335</v>
+      </c>
+      <c r="C2653" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2654" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2654" t="s">
+        <v>5336</v>
+      </c>
+      <c r="B2654" t="s">
+        <v>5337</v>
+      </c>
+      <c r="C2654" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2655" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2655" t="s">
+        <v>5338</v>
+      </c>
+      <c r="B2655" t="s">
+        <v>5339</v>
+      </c>
+      <c r="C2655" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2656" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2656" t="s">
+        <v>5340</v>
+      </c>
+      <c r="B2656" t="s">
+        <v>5341</v>
+      </c>
+      <c r="C2656" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2657" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2657" t="s">
+        <v>5342</v>
+      </c>
+      <c r="B2657" t="s">
+        <v>5343</v>
+      </c>
+      <c r="C2657" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2658" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2658" t="s">
+        <v>5344</v>
+      </c>
+      <c r="B2658" t="s">
+        <v>5345</v>
+      </c>
+      <c r="C2658" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2659" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2659" t="s">
+        <v>5346</v>
+      </c>
+      <c r="B2659" t="s">
+        <v>5347</v>
+      </c>
+      <c r="C2659" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2660" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2660" t="s">
+        <v>5348</v>
+      </c>
+      <c r="B2660" t="s">
+        <v>5349</v>
+      </c>
+      <c r="C2660" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2661" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2661" t="s">
+        <v>5350</v>
+      </c>
+      <c r="B2661" t="s">
+        <v>5351</v>
+      </c>
+      <c r="C2661" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2662" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2662" t="s">
+        <v>5352</v>
+      </c>
+      <c r="B2662" t="s">
+        <v>5353</v>
+      </c>
+      <c r="C2662" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2663" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2663" t="s">
+        <v>5354</v>
+      </c>
+      <c r="B2663" t="s">
+        <v>5355</v>
+      </c>
+      <c r="C2663" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2664" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2664" t="s">
+        <v>5356</v>
+      </c>
+      <c r="B2664" t="s">
+        <v>5357</v>
+      </c>
+      <c r="C2664" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2665" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2665" t="s">
+        <v>5358</v>
+      </c>
+      <c r="B2665" t="s">
+        <v>5359</v>
+      </c>
+      <c r="C2665" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2666" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2666" t="s">
+        <v>5360</v>
+      </c>
+      <c r="B2666" t="s">
+        <v>5361</v>
+      </c>
+      <c r="C2666" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2667" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2667" t="s">
+        <v>5362</v>
+      </c>
+      <c r="B2667" t="s">
+        <v>5363</v>
+      </c>
+      <c r="C2667" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2668" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2668" t="s">
+        <v>5364</v>
+      </c>
+      <c r="B2668" t="s">
+        <v>5365</v>
+      </c>
+      <c r="C2668" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2669" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2669" t="s">
+        <v>5366</v>
+      </c>
+      <c r="B2669" t="s">
+        <v>5367</v>
+      </c>
+      <c r="C2669" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2670" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2670" t="s">
+        <v>5368</v>
+      </c>
+      <c r="B2670" t="s">
+        <v>5369</v>
+      </c>
+      <c r="C2670" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="2671" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2671" t="s">
+        <v>5370</v>
+      </c>
+      <c r="B2671" t="s">
+        <v>5371</v>
+      </c>
+      <c r="C2671" t="s">
+        <v>5293</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6507" uniqueCount="5372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6642" uniqueCount="5463">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -16130,6 +16130,279 @@
   </si>
   <si>
     <t>Простыня тенсель 200х220 - "Холодная элегия"</t>
+  </si>
+  <si>
+    <t>4610594539068</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное резинка 180х200х30 - "Лесная Мелодия"</t>
+  </si>
+  <si>
+    <t>22-03-2026</t>
+  </si>
+  <si>
+    <t>4610594539051</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 160х200х20 - Премиум ТС 320 Белый</t>
+  </si>
+  <si>
+    <t>4610594539044</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное резинка 160х200х30 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4610594539037</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 200х200 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4610594539020</t>
+  </si>
+  <si>
+    <t>Наволочка микрофибра 50х70 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4610594539013</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 160х200х20 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4610594539006</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Блестящий миндаль</t>
+  </si>
+  <si>
+    <t>4610594538993</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 135 - Фирюз 1х1</t>
+  </si>
+  <si>
+    <t>4610594538986</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Лаванда 1х1</t>
+  </si>
+  <si>
+    <t>4610594538979</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Росток 1х1</t>
+  </si>
+  <si>
+    <t>4610594538962</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Бирюзовый Рельеф" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594538955</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси - "Серебряный Папоротник"</t>
+  </si>
+  <si>
+    <t>4610594538948</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное Евро простыня - Меропа</t>
+  </si>
+  <si>
+    <t>4610594538931</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное Евро простыня - Морбидецца наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594538924</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - "Лунь" 1х1</t>
+  </si>
+  <si>
+    <t>4610594538917</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - "Бежалис" 1х1</t>
+  </si>
+  <si>
+    <t>4610594538900</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 130 - "Летний дождь" 1х1</t>
+  </si>
+  <si>
+    <t>4610594538894</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - "Меридиан" 1х1</t>
+  </si>
+  <si>
+    <t>4610594538887</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 60х60 - "Калинте" 1х1</t>
+  </si>
+  <si>
+    <t>4610594538870</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - "Калинте" 1х1</t>
+  </si>
+  <si>
+    <t>4610594538863</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - "Лериса" Универсал</t>
+  </si>
+  <si>
+    <t>4610594538856</t>
+  </si>
+  <si>
+    <t>Простыня тенсель на резинке 120х200х20 - "Сливочный"</t>
+  </si>
+  <si>
+    <t>4610594538849</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 200х220 - М - 638 Крем-брюле</t>
+  </si>
+  <si>
+    <t>4610594538832</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - 638 Крем-брюле</t>
+  </si>
+  <si>
+    <t>4610594538825</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 300х300 - Бисквитный</t>
+  </si>
+  <si>
+    <t>4610594538818</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Серая умбра</t>
+  </si>
+  <si>
+    <t>4610594538801</t>
+  </si>
+  <si>
+    <t>Простыня из тенселя 240 х 260 - М - 60S 4393 Темно-серый</t>
+  </si>
+  <si>
+    <t>4610594538795</t>
+  </si>
+  <si>
+    <t>Наволочка из тенселя 50 х 70 - М - 60S 4393 Темно-серый</t>
+  </si>
+  <si>
+    <t>4610594538788</t>
+  </si>
+  <si>
+    <t>Пододеяльник из тенселя 220 х 240 - М - 60S 4393 Темно-серый</t>
+  </si>
+  <si>
+    <t>4610594538771</t>
+  </si>
+  <si>
+    <t>Наволочка из тенселя 50 х 50 - М - 60S 4393 Темно-серый</t>
+  </si>
+  <si>
+    <t>4610594538764</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Гуголету"</t>
+  </si>
+  <si>
+    <t>4610594538757</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 160х200х30 - Светло-пюсовый</t>
+  </si>
+  <si>
+    <t>4610594538740</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Голубая дымка"</t>
+  </si>
+  <si>
+    <t>4610594538733</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Голубая дымка" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594538726</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х20 - "Голубая дымка"</t>
+  </si>
+  <si>
+    <t>4610594538719</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - Розовая лаванда</t>
+  </si>
+  <si>
+    <t>4610594538702</t>
+  </si>
+  <si>
+    <t>Простыня жатка 150х220 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4610594538696</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил семейное - "Фернанда"</t>
+  </si>
+  <si>
+    <t>4610594538689</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - 135 - Кремово-белый</t>
+  </si>
+  <si>
+    <t>4610594538672</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 140х200х30 - 224 Розовый</t>
+  </si>
+  <si>
+    <t>4610594538665</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 200х200х20 - "Ритва"</t>
+  </si>
+  <si>
+    <t>4610594538658</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - "Формула-1"</t>
+  </si>
+  <si>
+    <t>4610594538641</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - Дзета Ориона наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594538634</t>
+  </si>
+  <si>
+    <t>Наволочка из сатина 50 х 70 - М - Габриэль (темный)</t>
+  </si>
+  <si>
+    <t>4610594538627</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 140х200х40 - "Звёздный Вальс"</t>
   </si>
 </sst>
 </file>
@@ -41372,6 +41645,501 @@
         <v>5293</v>
       </c>
     </row>
+    <row r="2672" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2672" t="s">
+        <v>5372</v>
+      </c>
+      <c r="B2672" t="s">
+        <v>5373</v>
+      </c>
+      <c r="C2672" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2673" t="s">
+        <v>5375</v>
+      </c>
+      <c r="B2673" t="s">
+        <v>5376</v>
+      </c>
+      <c r="C2673" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2674" t="s">
+        <v>5377</v>
+      </c>
+      <c r="B2674" t="s">
+        <v>5378</v>
+      </c>
+      <c r="C2674" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2675" t="s">
+        <v>5379</v>
+      </c>
+      <c r="B2675" t="s">
+        <v>5380</v>
+      </c>
+      <c r="C2675" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2676" t="s">
+        <v>5381</v>
+      </c>
+      <c r="B2676" t="s">
+        <v>5382</v>
+      </c>
+      <c r="C2676" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2677" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2677" t="s">
+        <v>5383</v>
+      </c>
+      <c r="B2677" t="s">
+        <v>5384</v>
+      </c>
+      <c r="C2677" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2678" t="s">
+        <v>5385</v>
+      </c>
+      <c r="B2678" t="s">
+        <v>5386</v>
+      </c>
+      <c r="C2678" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2679" t="s">
+        <v>5387</v>
+      </c>
+      <c r="B2679" t="s">
+        <v>5388</v>
+      </c>
+      <c r="C2679" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2680" t="s">
+        <v>5389</v>
+      </c>
+      <c r="B2680" t="s">
+        <v>5390</v>
+      </c>
+      <c r="C2680" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2681" t="s">
+        <v>5391</v>
+      </c>
+      <c r="B2681" t="s">
+        <v>5392</v>
+      </c>
+      <c r="C2681" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2682" t="s">
+        <v>5393</v>
+      </c>
+      <c r="B2682" t="s">
+        <v>5394</v>
+      </c>
+      <c r="C2682" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2683" t="s">
+        <v>5395</v>
+      </c>
+      <c r="B2683" t="s">
+        <v>5396</v>
+      </c>
+      <c r="C2683" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2684" t="s">
+        <v>5397</v>
+      </c>
+      <c r="B2684" t="s">
+        <v>5398</v>
+      </c>
+      <c r="C2684" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2685" t="s">
+        <v>5399</v>
+      </c>
+      <c r="B2685" t="s">
+        <v>5400</v>
+      </c>
+      <c r="C2685" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2686" t="s">
+        <v>5401</v>
+      </c>
+      <c r="B2686" t="s">
+        <v>5402</v>
+      </c>
+      <c r="C2686" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2687" t="s">
+        <v>5403</v>
+      </c>
+      <c r="B2687" t="s">
+        <v>5404</v>
+      </c>
+      <c r="C2687" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2688" t="s">
+        <v>5405</v>
+      </c>
+      <c r="B2688" t="s">
+        <v>5406</v>
+      </c>
+      <c r="C2688" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2689" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2689" t="s">
+        <v>5407</v>
+      </c>
+      <c r="B2689" t="s">
+        <v>5408</v>
+      </c>
+      <c r="C2689" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2690" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2690" t="s">
+        <v>5409</v>
+      </c>
+      <c r="B2690" t="s">
+        <v>5410</v>
+      </c>
+      <c r="C2690" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2691" t="s">
+        <v>5411</v>
+      </c>
+      <c r="B2691" t="s">
+        <v>5412</v>
+      </c>
+      <c r="C2691" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2692" t="s">
+        <v>5413</v>
+      </c>
+      <c r="B2692" t="s">
+        <v>5414</v>
+      </c>
+      <c r="C2692" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2693" t="s">
+        <v>5415</v>
+      </c>
+      <c r="B2693" t="s">
+        <v>5416</v>
+      </c>
+      <c r="C2693" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2694" t="s">
+        <v>5417</v>
+      </c>
+      <c r="B2694" t="s">
+        <v>5418</v>
+      </c>
+      <c r="C2694" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2695" t="s">
+        <v>5419</v>
+      </c>
+      <c r="B2695" t="s">
+        <v>5420</v>
+      </c>
+      <c r="C2695" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2696" t="s">
+        <v>5421</v>
+      </c>
+      <c r="B2696" t="s">
+        <v>5422</v>
+      </c>
+      <c r="C2696" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2697" t="s">
+        <v>5423</v>
+      </c>
+      <c r="B2697" t="s">
+        <v>5424</v>
+      </c>
+      <c r="C2697" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2698" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B2698" t="s">
+        <v>5426</v>
+      </c>
+      <c r="C2698" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2699" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B2699" t="s">
+        <v>5428</v>
+      </c>
+      <c r="C2699" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2700" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B2700" t="s">
+        <v>5430</v>
+      </c>
+      <c r="C2700" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2701" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B2701" t="s">
+        <v>5432</v>
+      </c>
+      <c r="C2701" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2702" t="s">
+        <v>5433</v>
+      </c>
+      <c r="B2702" t="s">
+        <v>5434</v>
+      </c>
+      <c r="C2702" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2703" t="s">
+        <v>5435</v>
+      </c>
+      <c r="B2703" t="s">
+        <v>5436</v>
+      </c>
+      <c r="C2703" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2704" t="s">
+        <v>5437</v>
+      </c>
+      <c r="B2704" t="s">
+        <v>5438</v>
+      </c>
+      <c r="C2704" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2705" t="s">
+        <v>5439</v>
+      </c>
+      <c r="B2705" t="s">
+        <v>5440</v>
+      </c>
+      <c r="C2705" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2706" t="s">
+        <v>5441</v>
+      </c>
+      <c r="B2706" t="s">
+        <v>5442</v>
+      </c>
+      <c r="C2706" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2707" t="s">
+        <v>5443</v>
+      </c>
+      <c r="B2707" t="s">
+        <v>5444</v>
+      </c>
+      <c r="C2707" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2708" t="s">
+        <v>5445</v>
+      </c>
+      <c r="B2708" t="s">
+        <v>5446</v>
+      </c>
+      <c r="C2708" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2709" t="s">
+        <v>5447</v>
+      </c>
+      <c r="B2709" t="s">
+        <v>5448</v>
+      </c>
+      <c r="C2709" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2710" t="s">
+        <v>5449</v>
+      </c>
+      <c r="B2710" t="s">
+        <v>5450</v>
+      </c>
+      <c r="C2710" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2711" t="s">
+        <v>5451</v>
+      </c>
+      <c r="B2711" t="s">
+        <v>5452</v>
+      </c>
+      <c r="C2711" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2712" t="s">
+        <v>5453</v>
+      </c>
+      <c r="B2712" t="s">
+        <v>5454</v>
+      </c>
+      <c r="C2712" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2713" t="s">
+        <v>5455</v>
+      </c>
+      <c r="B2713" t="s">
+        <v>5456</v>
+      </c>
+      <c r="C2713" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2714" t="s">
+        <v>5457</v>
+      </c>
+      <c r="B2714" t="s">
+        <v>5458</v>
+      </c>
+      <c r="C2714" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2715" t="s">
+        <v>5459</v>
+      </c>
+      <c r="B2715" t="s">
+        <v>5460</v>
+      </c>
+      <c r="C2715" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2716" t="s">
+        <v>5461</v>
+      </c>
+      <c r="B2716" t="s">
+        <v>5462</v>
+      </c>
+      <c r="C2716" t="s">
+        <v>5374</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6642" uniqueCount="5463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6819" uniqueCount="5582">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -16403,6 +16403,363 @@
   </si>
   <si>
     <t>Простыня жатка резинка 140х200х40 - "Звёздный Вальс"</t>
+  </si>
+  <si>
+    <t>4610594539655</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Миндаль 1х1</t>
+  </si>
+  <si>
+    <t>24-03-2026</t>
+  </si>
+  <si>
+    <t>4610594539648</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси резинка 180х200х30 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4610594539631</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - 120 - Голубая Латка</t>
+  </si>
+  <si>
+    <t>4610594539624</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 90х200х30 - "Серебряный Лес" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594539617</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Милда"</t>
+  </si>
+  <si>
+    <t>4610594539600</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Белава"</t>
+  </si>
+  <si>
+    <t>4610594539594</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - М - 60S Белый</t>
+  </si>
+  <si>
+    <t>4610594539587</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - "Зелёный Страйп"</t>
+  </si>
+  <si>
+    <t>4610594539570</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х50 - Белый</t>
+  </si>
+  <si>
+    <t>4610594539563</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х30 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4610594539556</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 125 - Папирус темный 1х1 1</t>
+  </si>
+  <si>
+    <t>4610594539549</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 60х60 - 135 - Дарк Блу 1х1</t>
+  </si>
+  <si>
+    <t>4610594539532</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 120х200х40 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4610594539525</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 30 х 50 - Черничный смузи</t>
+  </si>
+  <si>
+    <t>4610594539518</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 145х215 - "Гармоника"</t>
+  </si>
+  <si>
+    <t>4610594539501</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - "Селинто"</t>
+  </si>
+  <si>
+    <t>4610594539495</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Цветочный Шёпот"</t>
+  </si>
+  <si>
+    <t>4610594539488</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное - "Лав юселф" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594539471</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - 140 - Лаванда 1х1</t>
+  </si>
+  <si>
+    <t>4610594539464</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 150х220 - 224 Розовый</t>
+  </si>
+  <si>
+    <t>4610594539457</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4610594539440</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Кофейный крем"</t>
+  </si>
+  <si>
+    <t>4610594539433</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 120х200х10 - "Принцесса"</t>
+  </si>
+  <si>
+    <t>4610594539426</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 70х70 - "Овсяный"</t>
+  </si>
+  <si>
+    <t>4610594539419</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное - "Угольная Паутинка" Универсал</t>
+  </si>
+  <si>
+    <t>4610594539402</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 50х70 - "Лимонный крем"</t>
+  </si>
+  <si>
+    <t>4610594539396</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин браш резинка 230х230х30 - "Лимонный крем"</t>
+  </si>
+  <si>
+    <t>4610594539389</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 220х240 - "Калинте" 1х1</t>
+  </si>
+  <si>
+    <t>4610594539372</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное - 140 - Винно-красный 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594539365</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4610594539358</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - М - Маренго</t>
+  </si>
+  <si>
+    <t>4610594539341</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - Глазурь</t>
+  </si>
+  <si>
+    <t>4610594539334</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 220х240 - М - Вайт Фейри</t>
+  </si>
+  <si>
+    <t>4610594539327</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 220х240 - М - 125 - Белое тепло</t>
+  </si>
+  <si>
+    <t>4610594539310</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное резинка 140х200х30 - "Далиян"</t>
+  </si>
+  <si>
+    <t>4610594539303</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 220х240 - "Фиорис"</t>
+  </si>
+  <si>
+    <t>4610594539297</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - М - Кончерто гроссо</t>
+  </si>
+  <si>
+    <t>4610594539280</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 220х240 - "Шторм"</t>
+  </si>
+  <si>
+    <t>4610594539273</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 70х70 - Вайт Фейри</t>
+  </si>
+  <si>
+    <t>4610594539266</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х50 - 130 - "Летний дождь" 1х1</t>
+  </si>
+  <si>
+    <t>4610594539259</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х50 - 135 - Кортадерия 1х1</t>
+  </si>
+  <si>
+    <t>4610594539242</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х30 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4610594539235</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - Кончерто гроссо наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594539228</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 50х50 - "Солнечные лучи"</t>
+  </si>
+  <si>
+    <t>4610594539211</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 50х50 - "Тянь-Шань"</t>
+  </si>
+  <si>
+    <t>4610594539204</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - "Пролив" 1х1</t>
+  </si>
+  <si>
+    <t>4610594539198</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - "Пролив" 1х1</t>
+  </si>
+  <si>
+    <t>4610594539181</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - "Пролив" 1х1</t>
+  </si>
+  <si>
+    <t>4610594539174</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 200х220х20 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4610594539167</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 125 - Аквамарин 1х1</t>
+  </si>
+  <si>
+    <t>4610594539150</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - "Далиян"</t>
+  </si>
+  <si>
+    <t>4610594539143</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 175х215 - М - 125 - Дневной Аромат</t>
+  </si>
+  <si>
+    <t>4610594539136</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - М - Данделионс А+В</t>
+  </si>
+  <si>
+    <t>4610594539129</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 220х220х30 - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4610594539112</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Звёздный Вальс"</t>
+  </si>
+  <si>
+    <t>4610594539105</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 175х215 - М - Сливочно-кремовый</t>
+  </si>
+  <si>
+    <t>4610594539099</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - 60S 4323 Бежево-розовый</t>
+  </si>
+  <si>
+    <t>4610594539082</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - М - 140 - Кремовая пудра 1х1</t>
+  </si>
+  <si>
+    <t>4610594539075</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - М - 135 - Бежевый крем 1х1</t>
   </si>
 </sst>
 </file>
@@ -42140,6 +42497,655 @@
         <v>5374</v>
       </c>
     </row>
+    <row r="2717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2717" t="s">
+        <v>5463</v>
+      </c>
+      <c r="B2717" t="s">
+        <v>5464</v>
+      </c>
+      <c r="C2717" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2718" t="s">
+        <v>5466</v>
+      </c>
+      <c r="B2718" t="s">
+        <v>5467</v>
+      </c>
+      <c r="C2718" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2719" t="s">
+        <v>5468</v>
+      </c>
+      <c r="B2719" t="s">
+        <v>5469</v>
+      </c>
+      <c r="C2719" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2720" t="s">
+        <v>5470</v>
+      </c>
+      <c r="B2720" t="s">
+        <v>5471</v>
+      </c>
+      <c r="C2720" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2721" t="s">
+        <v>5472</v>
+      </c>
+      <c r="B2721" t="s">
+        <v>5473</v>
+      </c>
+      <c r="C2721" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2722" t="s">
+        <v>5474</v>
+      </c>
+      <c r="B2722" t="s">
+        <v>5475</v>
+      </c>
+      <c r="C2722" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2723" t="s">
+        <v>5476</v>
+      </c>
+      <c r="B2723" t="s">
+        <v>5477</v>
+      </c>
+      <c r="C2723" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2724" t="s">
+        <v>5478</v>
+      </c>
+      <c r="B2724" t="s">
+        <v>5479</v>
+      </c>
+      <c r="C2724" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2725" t="s">
+        <v>5480</v>
+      </c>
+      <c r="B2725" t="s">
+        <v>5481</v>
+      </c>
+      <c r="C2725" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2726" t="s">
+        <v>5482</v>
+      </c>
+      <c r="B2726" t="s">
+        <v>5483</v>
+      </c>
+      <c r="C2726" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2727" t="s">
+        <v>5484</v>
+      </c>
+      <c r="B2727" t="s">
+        <v>5485</v>
+      </c>
+      <c r="C2727" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2728" t="s">
+        <v>5486</v>
+      </c>
+      <c r="B2728" t="s">
+        <v>5487</v>
+      </c>
+      <c r="C2728" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2729" t="s">
+        <v>5488</v>
+      </c>
+      <c r="B2729" t="s">
+        <v>5489</v>
+      </c>
+      <c r="C2729" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2730" t="s">
+        <v>5490</v>
+      </c>
+      <c r="B2730" t="s">
+        <v>5491</v>
+      </c>
+      <c r="C2730" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2731" t="s">
+        <v>5492</v>
+      </c>
+      <c r="B2731" t="s">
+        <v>5493</v>
+      </c>
+      <c r="C2731" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2732" t="s">
+        <v>5494</v>
+      </c>
+      <c r="B2732" t="s">
+        <v>5495</v>
+      </c>
+      <c r="C2732" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2733" t="s">
+        <v>5496</v>
+      </c>
+      <c r="B2733" t="s">
+        <v>5497</v>
+      </c>
+      <c r="C2733" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2734" t="s">
+        <v>5498</v>
+      </c>
+      <c r="B2734" t="s">
+        <v>5499</v>
+      </c>
+      <c r="C2734" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2735" t="s">
+        <v>5500</v>
+      </c>
+      <c r="B2735" t="s">
+        <v>5501</v>
+      </c>
+      <c r="C2735" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2736" t="s">
+        <v>5502</v>
+      </c>
+      <c r="B2736" t="s">
+        <v>5503</v>
+      </c>
+      <c r="C2736" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2737" t="s">
+        <v>5504</v>
+      </c>
+      <c r="B2737" t="s">
+        <v>5505</v>
+      </c>
+      <c r="C2737" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2738" t="s">
+        <v>5506</v>
+      </c>
+      <c r="B2738" t="s">
+        <v>5507</v>
+      </c>
+      <c r="C2738" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2739" t="s">
+        <v>5508</v>
+      </c>
+      <c r="B2739" t="s">
+        <v>5509</v>
+      </c>
+      <c r="C2739" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2740" t="s">
+        <v>5510</v>
+      </c>
+      <c r="B2740" t="s">
+        <v>5511</v>
+      </c>
+      <c r="C2740" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2741" t="s">
+        <v>5512</v>
+      </c>
+      <c r="B2741" t="s">
+        <v>5513</v>
+      </c>
+      <c r="C2741" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2742" t="s">
+        <v>5514</v>
+      </c>
+      <c r="B2742" t="s">
+        <v>5515</v>
+      </c>
+      <c r="C2742" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2743" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2743" t="s">
+        <v>5516</v>
+      </c>
+      <c r="B2743" t="s">
+        <v>5517</v>
+      </c>
+      <c r="C2743" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2744" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2744" t="s">
+        <v>5518</v>
+      </c>
+      <c r="B2744" t="s">
+        <v>5519</v>
+      </c>
+      <c r="C2744" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2745" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2745" t="s">
+        <v>5520</v>
+      </c>
+      <c r="B2745" t="s">
+        <v>5521</v>
+      </c>
+      <c r="C2745" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2746" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2746" t="s">
+        <v>5522</v>
+      </c>
+      <c r="B2746" t="s">
+        <v>5523</v>
+      </c>
+      <c r="C2746" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2747" t="s">
+        <v>5524</v>
+      </c>
+      <c r="B2747" t="s">
+        <v>5525</v>
+      </c>
+      <c r="C2747" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2748" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2748" t="s">
+        <v>5526</v>
+      </c>
+      <c r="B2748" t="s">
+        <v>5527</v>
+      </c>
+      <c r="C2748" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2749" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2749" t="s">
+        <v>5528</v>
+      </c>
+      <c r="B2749" t="s">
+        <v>5529</v>
+      </c>
+      <c r="C2749" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2750" t="s">
+        <v>5530</v>
+      </c>
+      <c r="B2750" t="s">
+        <v>5531</v>
+      </c>
+      <c r="C2750" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2751" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2751" t="s">
+        <v>5532</v>
+      </c>
+      <c r="B2751" t="s">
+        <v>5533</v>
+      </c>
+      <c r="C2751" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2752" t="s">
+        <v>5534</v>
+      </c>
+      <c r="B2752" t="s">
+        <v>5535</v>
+      </c>
+      <c r="C2752" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2753" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2753" t="s">
+        <v>5536</v>
+      </c>
+      <c r="B2753" t="s">
+        <v>5537</v>
+      </c>
+      <c r="C2753" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2754" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2754" t="s">
+        <v>5538</v>
+      </c>
+      <c r="B2754" t="s">
+        <v>5539</v>
+      </c>
+      <c r="C2754" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2755" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2755" t="s">
+        <v>5540</v>
+      </c>
+      <c r="B2755" t="s">
+        <v>5541</v>
+      </c>
+      <c r="C2755" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2756" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2756" t="s">
+        <v>5542</v>
+      </c>
+      <c r="B2756" t="s">
+        <v>5543</v>
+      </c>
+      <c r="C2756" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2757" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2757" t="s">
+        <v>5544</v>
+      </c>
+      <c r="B2757" t="s">
+        <v>5545</v>
+      </c>
+      <c r="C2757" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2758" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2758" t="s">
+        <v>5546</v>
+      </c>
+      <c r="B2758" t="s">
+        <v>5547</v>
+      </c>
+      <c r="C2758" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2759" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2759" t="s">
+        <v>5548</v>
+      </c>
+      <c r="B2759" t="s">
+        <v>5549</v>
+      </c>
+      <c r="C2759" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2760" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2760" t="s">
+        <v>5550</v>
+      </c>
+      <c r="B2760" t="s">
+        <v>5551</v>
+      </c>
+      <c r="C2760" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2761" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2761" t="s">
+        <v>5552</v>
+      </c>
+      <c r="B2761" t="s">
+        <v>5553</v>
+      </c>
+      <c r="C2761" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2762" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2762" t="s">
+        <v>5554</v>
+      </c>
+      <c r="B2762" t="s">
+        <v>5555</v>
+      </c>
+      <c r="C2762" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2763" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2763" t="s">
+        <v>5556</v>
+      </c>
+      <c r="B2763" t="s">
+        <v>5557</v>
+      </c>
+      <c r="C2763" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2764" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2764" t="s">
+        <v>5558</v>
+      </c>
+      <c r="B2764" t="s">
+        <v>5559</v>
+      </c>
+      <c r="C2764" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2765" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2765" t="s">
+        <v>5560</v>
+      </c>
+      <c r="B2765" t="s">
+        <v>5561</v>
+      </c>
+      <c r="C2765" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2766" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2766" t="s">
+        <v>5562</v>
+      </c>
+      <c r="B2766" t="s">
+        <v>5563</v>
+      </c>
+      <c r="C2766" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2767" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2767" t="s">
+        <v>5564</v>
+      </c>
+      <c r="B2767" t="s">
+        <v>5565</v>
+      </c>
+      <c r="C2767" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2768" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2768" t="s">
+        <v>5566</v>
+      </c>
+      <c r="B2768" t="s">
+        <v>5567</v>
+      </c>
+      <c r="C2768" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2769" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2769" t="s">
+        <v>5568</v>
+      </c>
+      <c r="B2769" t="s">
+        <v>5569</v>
+      </c>
+      <c r="C2769" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2770" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2770" t="s">
+        <v>5570</v>
+      </c>
+      <c r="B2770" t="s">
+        <v>5571</v>
+      </c>
+      <c r="C2770" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2771" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2771" t="s">
+        <v>5572</v>
+      </c>
+      <c r="B2771" t="s">
+        <v>5573</v>
+      </c>
+      <c r="C2771" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2772" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2772" t="s">
+        <v>5574</v>
+      </c>
+      <c r="B2772" t="s">
+        <v>5575</v>
+      </c>
+      <c r="C2772" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2773" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2773" t="s">
+        <v>5576</v>
+      </c>
+      <c r="B2773" t="s">
+        <v>5577</v>
+      </c>
+      <c r="C2773" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2774" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2774" t="s">
+        <v>5578</v>
+      </c>
+      <c r="B2774" t="s">
+        <v>5579</v>
+      </c>
+      <c r="C2774" t="s">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="2775" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2775" t="s">
+        <v>5580</v>
+      </c>
+      <c r="B2775" t="s">
+        <v>5581</v>
+      </c>
+      <c r="C2775" t="s">
+        <v>5465</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6819" uniqueCount="5582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6936" uniqueCount="5661">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -16760,6 +16760,243 @@
   </si>
   <si>
     <t>Пододеяльник страйп-сатин 150х200 - М - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4660674648159</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 240х260 - "Бездна"</t>
+  </si>
+  <si>
+    <t>26-03-2026</t>
+  </si>
+  <si>
+    <t>4660674648142</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Песочная роза" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674648135</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - М - 120 - Музыкальные Совята</t>
+  </si>
+  <si>
+    <t>4660674648128</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - М - 120 - Розовый Воздух</t>
+  </si>
+  <si>
+    <t>4660674648111</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 175х215 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4610594539990</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 50х70 - "Фиорелла"</t>
+  </si>
+  <si>
+    <t>4610594539983</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 120х200х30 - "Мелиссит"</t>
+  </si>
+  <si>
+    <t>4610594539976</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 175х215 - "Фиорелла"</t>
+  </si>
+  <si>
+    <t>4610594539969</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Зайга"</t>
+  </si>
+  <si>
+    <t>4610594539952</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 175х215 - "Агапия"</t>
+  </si>
+  <si>
+    <t>4610594539945</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное резинка 140х200х30 - "Пухлянки"</t>
+  </si>
+  <si>
+    <t>4610594539938</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил Евро - "Фернанда"</t>
+  </si>
+  <si>
+    <t>4610594539921</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - Гранола</t>
+  </si>
+  <si>
+    <t>4610594539914</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х30 - "Глария"</t>
+  </si>
+  <si>
+    <t>4610594539907</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - Премиум ТС 320 Вишенка</t>
+  </si>
+  <si>
+    <t>4610594539891</t>
+  </si>
+  <si>
+    <t>Простыня сатин 200х220 - Премиум ТС 320 Бесконечность</t>
+  </si>
+  <si>
+    <t>4610594539884</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 175х215 - М - Премиум ТС 320 Бесконечность</t>
+  </si>
+  <si>
+    <t>4610594539877</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - Розовая лаванда</t>
+  </si>
+  <si>
+    <t>4610594539860</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 260х260 - "Глубь"</t>
+  </si>
+  <si>
+    <t>4610594539853</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 260х260 - "Сахарная роза"</t>
+  </si>
+  <si>
+    <t>4610594539846</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Твист"</t>
+  </si>
+  <si>
+    <t>4610594539839</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Небра"</t>
+  </si>
+  <si>
+    <t>4610594539822</t>
+  </si>
+  <si>
+    <t>Простыня страйп-поплин 200 х 220 - М - Гестхаус Белый 3х3</t>
+  </si>
+  <si>
+    <t>4610594539815</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 240х260 - 323 Серый</t>
+  </si>
+  <si>
+    <t>4610594539808</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 200х220х20 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4610594539792</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра 1,5 спальное резинка 120х200х30 - "Альбелла" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594539785</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное - "Коньячный" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594539778</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 260х260 - Чериньола</t>
+  </si>
+  <si>
+    <t>4610594539761</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 90х200х30 - 41-020 Серебряный наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594539754</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 120х200х30 - "Дино-пати" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594539747</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - 125 - Тёплый песок</t>
+  </si>
+  <si>
+    <t>4610594539730</t>
+  </si>
+  <si>
+    <t>Простыня бязь 80х120 - 142 ГОСТ - Темно-синяя</t>
+  </si>
+  <si>
+    <t>4610594539723</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 300х300 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4610594539716</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Олуфими"</t>
+  </si>
+  <si>
+    <t>4610594539709</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4610594539693</t>
+  </si>
+  <si>
+    <t>Простыня круглая микросатин резинка 200х200х20 - "Смоки"</t>
+  </si>
+  <si>
+    <t>4610594539686</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 140х200х30 - Бертолеция наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4610594539679</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - "Сирента"</t>
+  </si>
+  <si>
+    <t>4610594539662</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Морозный туман"</t>
   </si>
 </sst>
 </file>
@@ -43146,6 +43383,435 @@
         <v>5465</v>
       </c>
     </row>
+    <row r="2776" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2776" t="s">
+        <v>5582</v>
+      </c>
+      <c r="B2776" t="s">
+        <v>5583</v>
+      </c>
+      <c r="C2776" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2777" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2777" t="s">
+        <v>5585</v>
+      </c>
+      <c r="B2777" t="s">
+        <v>5586</v>
+      </c>
+      <c r="C2777" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2778" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2778" t="s">
+        <v>5587</v>
+      </c>
+      <c r="B2778" t="s">
+        <v>5588</v>
+      </c>
+      <c r="C2778" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2779" t="s">
+        <v>5589</v>
+      </c>
+      <c r="B2779" t="s">
+        <v>5590</v>
+      </c>
+      <c r="C2779" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2780" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2780" t="s">
+        <v>5591</v>
+      </c>
+      <c r="B2780" t="s">
+        <v>5592</v>
+      </c>
+      <c r="C2780" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2781" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2781" t="s">
+        <v>5593</v>
+      </c>
+      <c r="B2781" t="s">
+        <v>5594</v>
+      </c>
+      <c r="C2781" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2782" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2782" t="s">
+        <v>5595</v>
+      </c>
+      <c r="B2782" t="s">
+        <v>5596</v>
+      </c>
+      <c r="C2782" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2783" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2783" t="s">
+        <v>5597</v>
+      </c>
+      <c r="B2783" t="s">
+        <v>5598</v>
+      </c>
+      <c r="C2783" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2784" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2784" t="s">
+        <v>5599</v>
+      </c>
+      <c r="B2784" t="s">
+        <v>5600</v>
+      </c>
+      <c r="C2784" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2785" t="s">
+        <v>5601</v>
+      </c>
+      <c r="B2785" t="s">
+        <v>5602</v>
+      </c>
+      <c r="C2785" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2786" t="s">
+        <v>5603</v>
+      </c>
+      <c r="B2786" t="s">
+        <v>5604</v>
+      </c>
+      <c r="C2786" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2787" t="s">
+        <v>5605</v>
+      </c>
+      <c r="B2787" t="s">
+        <v>5606</v>
+      </c>
+      <c r="C2787" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2788" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2788" t="s">
+        <v>5607</v>
+      </c>
+      <c r="B2788" t="s">
+        <v>5608</v>
+      </c>
+      <c r="C2788" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2789" t="s">
+        <v>5609</v>
+      </c>
+      <c r="B2789" t="s">
+        <v>5610</v>
+      </c>
+      <c r="C2789" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2790" t="s">
+        <v>5611</v>
+      </c>
+      <c r="B2790" t="s">
+        <v>5612</v>
+      </c>
+      <c r="C2790" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2791" t="s">
+        <v>5613</v>
+      </c>
+      <c r="B2791" t="s">
+        <v>5614</v>
+      </c>
+      <c r="C2791" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2792" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2792" t="s">
+        <v>5615</v>
+      </c>
+      <c r="B2792" t="s">
+        <v>5616</v>
+      </c>
+      <c r="C2792" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2793" t="s">
+        <v>5617</v>
+      </c>
+      <c r="B2793" t="s">
+        <v>5618</v>
+      </c>
+      <c r="C2793" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2794" t="s">
+        <v>5619</v>
+      </c>
+      <c r="B2794" t="s">
+        <v>5620</v>
+      </c>
+      <c r="C2794" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2795" t="s">
+        <v>5621</v>
+      </c>
+      <c r="B2795" t="s">
+        <v>5622</v>
+      </c>
+      <c r="C2795" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2796" t="s">
+        <v>5623</v>
+      </c>
+      <c r="B2796" t="s">
+        <v>5624</v>
+      </c>
+      <c r="C2796" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2797" t="s">
+        <v>5625</v>
+      </c>
+      <c r="B2797" t="s">
+        <v>5626</v>
+      </c>
+      <c r="C2797" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2798" t="s">
+        <v>5627</v>
+      </c>
+      <c r="B2798" t="s">
+        <v>5628</v>
+      </c>
+      <c r="C2798" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2799" t="s">
+        <v>5629</v>
+      </c>
+      <c r="B2799" t="s">
+        <v>5630</v>
+      </c>
+      <c r="C2799" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2800" t="s">
+        <v>5631</v>
+      </c>
+      <c r="B2800" t="s">
+        <v>5632</v>
+      </c>
+      <c r="C2800" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2801" t="s">
+        <v>5633</v>
+      </c>
+      <c r="B2801" t="s">
+        <v>5634</v>
+      </c>
+      <c r="C2801" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2802" t="s">
+        <v>5635</v>
+      </c>
+      <c r="B2802" t="s">
+        <v>5636</v>
+      </c>
+      <c r="C2802" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2803" t="s">
+        <v>5637</v>
+      </c>
+      <c r="B2803" t="s">
+        <v>5638</v>
+      </c>
+      <c r="C2803" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2804" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2804" t="s">
+        <v>5639</v>
+      </c>
+      <c r="B2804" t="s">
+        <v>5640</v>
+      </c>
+      <c r="C2804" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2805" t="s">
+        <v>5641</v>
+      </c>
+      <c r="B2805" t="s">
+        <v>5642</v>
+      </c>
+      <c r="C2805" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2806" t="s">
+        <v>5643</v>
+      </c>
+      <c r="B2806" t="s">
+        <v>5644</v>
+      </c>
+      <c r="C2806" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2807" t="s">
+        <v>5645</v>
+      </c>
+      <c r="B2807" t="s">
+        <v>5646</v>
+      </c>
+      <c r="C2807" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2808" t="s">
+        <v>5647</v>
+      </c>
+      <c r="B2808" t="s">
+        <v>5648</v>
+      </c>
+      <c r="C2808" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2809" t="s">
+        <v>5649</v>
+      </c>
+      <c r="B2809" t="s">
+        <v>5650</v>
+      </c>
+      <c r="C2809" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2810" t="s">
+        <v>5651</v>
+      </c>
+      <c r="B2810" t="s">
+        <v>5652</v>
+      </c>
+      <c r="C2810" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2811" t="s">
+        <v>5653</v>
+      </c>
+      <c r="B2811" t="s">
+        <v>5654</v>
+      </c>
+      <c r="C2811" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2812" t="s">
+        <v>5655</v>
+      </c>
+      <c r="B2812" t="s">
+        <v>5656</v>
+      </c>
+      <c r="C2812" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2813" t="s">
+        <v>5657</v>
+      </c>
+      <c r="B2813" t="s">
+        <v>5658</v>
+      </c>
+      <c r="C2813" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2814" t="s">
+        <v>5659</v>
+      </c>
+      <c r="B2814" t="s">
+        <v>5660</v>
+      </c>
+      <c r="C2814" t="s">
+        <v>5584</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6936" uniqueCount="5661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7038" uniqueCount="5730">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -16997,6 +16997,213 @@
   </si>
   <si>
     <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Морозный туман"</t>
+  </si>
+  <si>
+    <t>4660674648494</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Эдже"</t>
+  </si>
+  <si>
+    <t>27-03-2026</t>
+  </si>
+  <si>
+    <t>4660674648487</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 40х60 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4660674648470</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 220х240 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4660674648463</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Снежный Лепесток"</t>
+  </si>
+  <si>
+    <t>4660674648456</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - "Цветочный Шёпот"</t>
+  </si>
+  <si>
+    <t>4660674648449</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное - "Туманная Ветвь"</t>
+  </si>
+  <si>
+    <t>4660674648432</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро - 140 - Винно-красный 1х1</t>
+  </si>
+  <si>
+    <t>4660674648425</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - 120 - Спящий Мишка на бежевом</t>
+  </si>
+  <si>
+    <t>4660674648418</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х200 - М - 135 - Цитрус 3х3</t>
+  </si>
+  <si>
+    <t>4660674648401</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 200х220 - Кремовый бархат</t>
+  </si>
+  <si>
+    <t>4660674648395</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 220х240 - 80 - Югацу</t>
+  </si>
+  <si>
+    <t>4660674648388</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 60S 4234 Морская нимфа</t>
+  </si>
+  <si>
+    <t>4660674648371</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 240х260 - "Мелек"</t>
+  </si>
+  <si>
+    <t>4660674648364</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - "Бриллиантовые кружева"</t>
+  </si>
+  <si>
+    <t>4660674648357</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 90х200х20 - "Эстрелья"</t>
+  </si>
+  <si>
+    <t>4660674648340</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 135 - Амур де Молен 1х1</t>
+  </si>
+  <si>
+    <t>4660674648333</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Р - 60S Белый</t>
+  </si>
+  <si>
+    <t>4660674648326</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - Пинклайт</t>
+  </si>
+  <si>
+    <t>4660674648319</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - Премиум ТС 320 Белый</t>
+  </si>
+  <si>
+    <t>4660674648302</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х200х40 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4660674648296</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 135 - Марриотт Белый 3х3</t>
+  </si>
+  <si>
+    <t>4660674648289</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс 300х300 - "Кремневый серый"</t>
+  </si>
+  <si>
+    <t>4660674648272</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - Черный матовый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674648265</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - М - Изумруд Эсмеральды</t>
+  </si>
+  <si>
+    <t>4660674648258</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - М - Аргентум</t>
+  </si>
+  <si>
+    <t>4660674648241</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - "Ледяной Рассвет"</t>
+  </si>
+  <si>
+    <t>4660674648234</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - "Ритва"</t>
+  </si>
+  <si>
+    <t>4660674648227</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4660674648210</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 120х200х20 - Аква Циан</t>
+  </si>
+  <si>
+    <t>4660674648203</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Пинклайт</t>
+  </si>
+  <si>
+    <t>4660674648197</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 ГОСТ - Кленовый</t>
+  </si>
+  <si>
+    <t>4660674648180</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Дино-пати"</t>
+  </si>
+  <si>
+    <t>4660674648173</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х40 - 135 - Мокрый асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4660674648166</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 160х200х30 - Графит (меланж)</t>
   </si>
 </sst>
 </file>
@@ -43812,6 +44019,380 @@
         <v>5584</v>
       </c>
     </row>
+    <row r="2815" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2815" t="s">
+        <v>5661</v>
+      </c>
+      <c r="B2815" t="s">
+        <v>5662</v>
+      </c>
+      <c r="C2815" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2816" t="s">
+        <v>5664</v>
+      </c>
+      <c r="B2816" t="s">
+        <v>5665</v>
+      </c>
+      <c r="C2816" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2817" t="s">
+        <v>5666</v>
+      </c>
+      <c r="B2817" t="s">
+        <v>5667</v>
+      </c>
+      <c r="C2817" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2818" t="s">
+        <v>5668</v>
+      </c>
+      <c r="B2818" t="s">
+        <v>5669</v>
+      </c>
+      <c r="C2818" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2819" t="s">
+        <v>5670</v>
+      </c>
+      <c r="B2819" t="s">
+        <v>5671</v>
+      </c>
+      <c r="C2819" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2820" t="s">
+        <v>5672</v>
+      </c>
+      <c r="B2820" t="s">
+        <v>5673</v>
+      </c>
+      <c r="C2820" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2821" t="s">
+        <v>5674</v>
+      </c>
+      <c r="B2821" t="s">
+        <v>5675</v>
+      </c>
+      <c r="C2821" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2822" t="s">
+        <v>5676</v>
+      </c>
+      <c r="B2822" t="s">
+        <v>5677</v>
+      </c>
+      <c r="C2822" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2823" t="s">
+        <v>5678</v>
+      </c>
+      <c r="B2823" t="s">
+        <v>5679</v>
+      </c>
+      <c r="C2823" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2824" t="s">
+        <v>5680</v>
+      </c>
+      <c r="B2824" t="s">
+        <v>5681</v>
+      </c>
+      <c r="C2824" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2825" t="s">
+        <v>5682</v>
+      </c>
+      <c r="B2825" t="s">
+        <v>5683</v>
+      </c>
+      <c r="C2825" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2826" t="s">
+        <v>5684</v>
+      </c>
+      <c r="B2826" t="s">
+        <v>5685</v>
+      </c>
+      <c r="C2826" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2827" t="s">
+        <v>5686</v>
+      </c>
+      <c r="B2827" t="s">
+        <v>5687</v>
+      </c>
+      <c r="C2827" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2828" t="s">
+        <v>5688</v>
+      </c>
+      <c r="B2828" t="s">
+        <v>5689</v>
+      </c>
+      <c r="C2828" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2829" t="s">
+        <v>5690</v>
+      </c>
+      <c r="B2829" t="s">
+        <v>5691</v>
+      </c>
+      <c r="C2829" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2830" t="s">
+        <v>5692</v>
+      </c>
+      <c r="B2830" t="s">
+        <v>5693</v>
+      </c>
+      <c r="C2830" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2831" t="s">
+        <v>5694</v>
+      </c>
+      <c r="B2831" t="s">
+        <v>5695</v>
+      </c>
+      <c r="C2831" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2832" t="s">
+        <v>5696</v>
+      </c>
+      <c r="B2832" t="s">
+        <v>5697</v>
+      </c>
+      <c r="C2832" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2833" t="s">
+        <v>5698</v>
+      </c>
+      <c r="B2833" t="s">
+        <v>5699</v>
+      </c>
+      <c r="C2833" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2834" t="s">
+        <v>5700</v>
+      </c>
+      <c r="B2834" t="s">
+        <v>5701</v>
+      </c>
+      <c r="C2834" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2835" t="s">
+        <v>5702</v>
+      </c>
+      <c r="B2835" t="s">
+        <v>5703</v>
+      </c>
+      <c r="C2835" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2836" t="s">
+        <v>5704</v>
+      </c>
+      <c r="B2836" t="s">
+        <v>5705</v>
+      </c>
+      <c r="C2836" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2837" t="s">
+        <v>5706</v>
+      </c>
+      <c r="B2837" t="s">
+        <v>5707</v>
+      </c>
+      <c r="C2837" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2838" t="s">
+        <v>5708</v>
+      </c>
+      <c r="B2838" t="s">
+        <v>5709</v>
+      </c>
+      <c r="C2838" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2839" t="s">
+        <v>5710</v>
+      </c>
+      <c r="B2839" t="s">
+        <v>5711</v>
+      </c>
+      <c r="C2839" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2840" t="s">
+        <v>5712</v>
+      </c>
+      <c r="B2840" t="s">
+        <v>5713</v>
+      </c>
+      <c r="C2840" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2841" t="s">
+        <v>5714</v>
+      </c>
+      <c r="B2841" t="s">
+        <v>5715</v>
+      </c>
+      <c r="C2841" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2842" t="s">
+        <v>5716</v>
+      </c>
+      <c r="B2842" t="s">
+        <v>5717</v>
+      </c>
+      <c r="C2842" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2843" t="s">
+        <v>5718</v>
+      </c>
+      <c r="B2843" t="s">
+        <v>5719</v>
+      </c>
+      <c r="C2843" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2844" t="s">
+        <v>5720</v>
+      </c>
+      <c r="B2844" t="s">
+        <v>5721</v>
+      </c>
+      <c r="C2844" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2845" t="s">
+        <v>5722</v>
+      </c>
+      <c r="B2845" t="s">
+        <v>5723</v>
+      </c>
+      <c r="C2845" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2846" t="s">
+        <v>5724</v>
+      </c>
+      <c r="B2846" t="s">
+        <v>5725</v>
+      </c>
+      <c r="C2846" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2847" t="s">
+        <v>5726</v>
+      </c>
+      <c r="B2847" t="s">
+        <v>5727</v>
+      </c>
+      <c r="C2847" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2848" t="s">
+        <v>5728</v>
+      </c>
+      <c r="B2848" t="s">
+        <v>5729</v>
+      </c>
+      <c r="C2848" t="s">
+        <v>5663</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7038" uniqueCount="5730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7221" uniqueCount="5853">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -17204,6 +17204,375 @@
   </si>
   <si>
     <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 160х200х30 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4660674649101</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное резинка 140х200х30 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>30-03-2026</t>
+  </si>
+  <si>
+    <t>4660674649095</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 50х70 - "Дино-пати"</t>
+  </si>
+  <si>
+    <t>4660674649088</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 200х220 - 130 - Полуночный ультрамарин 1х1</t>
+  </si>
+  <si>
+    <t>4660674649071</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - "Чёрный Страйп"</t>
+  </si>
+  <si>
+    <t>4660674649064</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 60х60 - "Флорал"</t>
+  </si>
+  <si>
+    <t>4660674649057</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х200 - "Флорал"</t>
+  </si>
+  <si>
+    <t>4660674649040</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х30 - 130 - Белая 1х1</t>
+  </si>
+  <si>
+    <t>4660674649033</t>
+  </si>
+  <si>
+    <t>Простыня из сатина 220 х 240 - М - 140 - Белый Люкс</t>
+  </si>
+  <si>
+    <t>4660674649026</t>
+  </si>
+  <si>
+    <t>Простыня сатин 220х240 - Премиум ТС 320 Белый</t>
+  </si>
+  <si>
+    <t>4660674649019</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё поплин 1,5 спальное - "Стильные девчонки"</t>
+  </si>
+  <si>
+    <t>4660674649002</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - 71 Персик</t>
+  </si>
+  <si>
+    <t>4660674648999</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 112 х 147 - М - 120 - Бомонд</t>
+  </si>
+  <si>
+    <t>4660674648982</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х30 - 135 - Марриотт Белый 3х3</t>
+  </si>
+  <si>
+    <t>4660674648975</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 125 - Шашки Шампань 0,5х0,5</t>
+  </si>
+  <si>
+    <t>4660674648968</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4660674648951</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - 125 - Шашки Шампань 0,5х0,5</t>
+  </si>
+  <si>
+    <t>4660674648944</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 260х260 - "Туманная Аура"</t>
+  </si>
+  <si>
+    <t>4660674648937</t>
+  </si>
+  <si>
+    <t>Простыня сатин 280х280 - 120 - Серебристый металлик</t>
+  </si>
+  <si>
+    <t>4660674648920</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая 180х220 - Мулетон Хлопок</t>
+  </si>
+  <si>
+    <t>4660674648913</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - Розариум А+В</t>
+  </si>
+  <si>
+    <t>4660674648906</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 180х220 - Пастельно-розовый</t>
+  </si>
+  <si>
+    <t>4660674648890</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4660674648883</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 130 - "Серый туман" 1х1</t>
+  </si>
+  <si>
+    <t>4660674648876</t>
+  </si>
+  <si>
+    <t>Наволочка ранфорс 40х60 - "Ванильный раф"</t>
+  </si>
+  <si>
+    <t>4660674648869</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 135 - Амур де Молен 1х1</t>
+  </si>
+  <si>
+    <t>4660674648852</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - Серая умбра</t>
+  </si>
+  <si>
+    <t>4660674648845</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Ларион"</t>
+  </si>
+  <si>
+    <t>4660674648838</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 160х200х20 - Бонди</t>
+  </si>
+  <si>
+    <t>4660674648821</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное - 140 - Космос 1х1</t>
+  </si>
+  <si>
+    <t>4660674648814</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - М - 125 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4660674648807</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро - "Лериса"</t>
+  </si>
+  <si>
+    <t>4660674648791</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Макена"</t>
+  </si>
+  <si>
+    <t>4660674648784</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - "Карибская волна"</t>
+  </si>
+  <si>
+    <t>4660674648777</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - "Далиян"</t>
+  </si>
+  <si>
+    <t>4660674648760</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - 60S 4216 Серебро</t>
+  </si>
+  <si>
+    <t>4660674648753</t>
+  </si>
+  <si>
+    <t>Простыня сатин 240х260 - 140 - Сияющая бирюза</t>
+  </si>
+  <si>
+    <t>4660674648746</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 240х260 - М - 140 - Сияющая бирюза</t>
+  </si>
+  <si>
+    <t>4660674648739</t>
+  </si>
+  <si>
+    <t>Наволочка микросатин 50х70 - "Бежевый шлейф"</t>
+  </si>
+  <si>
+    <t>4660674648722</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4660674648715</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 70х70 - "Андреза"</t>
+  </si>
+  <si>
+    <t>4660674648708</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное резинка 140х200х30 - 135 - Бежевый крем 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674648692</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 1,5 спальное резинка 120х200х30 - "Шторм" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674648685</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 150х200 - "Нефритовый"</t>
+  </si>
+  <si>
+    <t>4660674648678</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 240х260 - "Розанна"</t>
+  </si>
+  <si>
+    <t>4660674648661</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - 129 Темно-зеленый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674648654</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин King Size резинка 200х200х30 - "Шторм"</t>
+  </si>
+  <si>
+    <t>4660674648647</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 60х60 - 135 - Цитрус 3х3</t>
+  </si>
+  <si>
+    <t>4660674648630</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 90х200х30 - "Мирелле"</t>
+  </si>
+  <si>
+    <t>4660674648623</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Сахарная роза"</t>
+  </si>
+  <si>
+    <t>4660674648616</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс 180х220 - "Лазурный бриз"</t>
+  </si>
+  <si>
+    <t>4660674648609</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Голубой 1х1</t>
+  </si>
+  <si>
+    <t>4660674648593</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Димитра"</t>
+  </si>
+  <si>
+    <t>4660674648586</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 140х200х20 - Премиум ТС 320 "Лиминал"</t>
+  </si>
+  <si>
+    <t>4660674648579</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 145х215 - "Флорал"</t>
+  </si>
+  <si>
+    <t>4660674648562</t>
+  </si>
+  <si>
+    <t>Простыня поплин 220х240 - Кружева на голубом</t>
+  </si>
+  <si>
+    <t>4660674648555</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 120х200х30 - 125 - Рея наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674648548</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Далиян"</t>
+  </si>
+  <si>
+    <t>4660674648531</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - "Далиян"</t>
+  </si>
+  <si>
+    <t>4660674648524</t>
+  </si>
+  <si>
+    <t>Пододеяльник ранфорс 200х220 - "Ванильный раф"</t>
+  </si>
+  <si>
+    <t>4660674648517</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Макена" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674648500</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Звёздный Вальс" наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -44393,6 +44762,677 @@
         <v>5663</v>
       </c>
     </row>
+    <row r="2849" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2849" t="s">
+        <v>5730</v>
+      </c>
+      <c r="B2849" t="s">
+        <v>5731</v>
+      </c>
+      <c r="C2849" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2850" t="s">
+        <v>5733</v>
+      </c>
+      <c r="B2850" t="s">
+        <v>5734</v>
+      </c>
+      <c r="C2850" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2851" t="s">
+        <v>5735</v>
+      </c>
+      <c r="B2851" t="s">
+        <v>5736</v>
+      </c>
+      <c r="C2851" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2852" t="s">
+        <v>5737</v>
+      </c>
+      <c r="B2852" t="s">
+        <v>5738</v>
+      </c>
+      <c r="C2852" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2853" t="s">
+        <v>5739</v>
+      </c>
+      <c r="B2853" t="s">
+        <v>5740</v>
+      </c>
+      <c r="C2853" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2854" t="s">
+        <v>5741</v>
+      </c>
+      <c r="B2854" t="s">
+        <v>5742</v>
+      </c>
+      <c r="C2854" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2855" t="s">
+        <v>5743</v>
+      </c>
+      <c r="B2855" t="s">
+        <v>5744</v>
+      </c>
+      <c r="C2855" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2856" t="s">
+        <v>5745</v>
+      </c>
+      <c r="B2856" t="s">
+        <v>5746</v>
+      </c>
+      <c r="C2856" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2857" t="s">
+        <v>5747</v>
+      </c>
+      <c r="B2857" t="s">
+        <v>5748</v>
+      </c>
+      <c r="C2857" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2858" t="s">
+        <v>5749</v>
+      </c>
+      <c r="B2858" t="s">
+        <v>5750</v>
+      </c>
+      <c r="C2858" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2859" t="s">
+        <v>5751</v>
+      </c>
+      <c r="B2859" t="s">
+        <v>5752</v>
+      </c>
+      <c r="C2859" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2860" t="s">
+        <v>5753</v>
+      </c>
+      <c r="B2860" t="s">
+        <v>5754</v>
+      </c>
+      <c r="C2860" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2861" t="s">
+        <v>5755</v>
+      </c>
+      <c r="B2861" t="s">
+        <v>5756</v>
+      </c>
+      <c r="C2861" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2862" t="s">
+        <v>5757</v>
+      </c>
+      <c r="B2862" t="s">
+        <v>5758</v>
+      </c>
+      <c r="C2862" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2863" t="s">
+        <v>5759</v>
+      </c>
+      <c r="B2863" t="s">
+        <v>5760</v>
+      </c>
+      <c r="C2863" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2864" t="s">
+        <v>5761</v>
+      </c>
+      <c r="B2864" t="s">
+        <v>5762</v>
+      </c>
+      <c r="C2864" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2865" t="s">
+        <v>5763</v>
+      </c>
+      <c r="B2865" t="s">
+        <v>5764</v>
+      </c>
+      <c r="C2865" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2866" t="s">
+        <v>5765</v>
+      </c>
+      <c r="B2866" t="s">
+        <v>5766</v>
+      </c>
+      <c r="C2866" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2867" t="s">
+        <v>5767</v>
+      </c>
+      <c r="B2867" t="s">
+        <v>5768</v>
+      </c>
+      <c r="C2867" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2868" t="s">
+        <v>5769</v>
+      </c>
+      <c r="B2868" t="s">
+        <v>5770</v>
+      </c>
+      <c r="C2868" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2869" t="s">
+        <v>5771</v>
+      </c>
+      <c r="B2869" t="s">
+        <v>5772</v>
+      </c>
+      <c r="C2869" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2870" t="s">
+        <v>5773</v>
+      </c>
+      <c r="B2870" t="s">
+        <v>5774</v>
+      </c>
+      <c r="C2870" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2871" t="s">
+        <v>5775</v>
+      </c>
+      <c r="B2871" t="s">
+        <v>5776</v>
+      </c>
+      <c r="C2871" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2872" t="s">
+        <v>5777</v>
+      </c>
+      <c r="B2872" t="s">
+        <v>5778</v>
+      </c>
+      <c r="C2872" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2873" t="s">
+        <v>5779</v>
+      </c>
+      <c r="B2873" t="s">
+        <v>5780</v>
+      </c>
+      <c r="C2873" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2874" t="s">
+        <v>5781</v>
+      </c>
+      <c r="B2874" t="s">
+        <v>5782</v>
+      </c>
+      <c r="C2874" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2875" t="s">
+        <v>5783</v>
+      </c>
+      <c r="B2875" t="s">
+        <v>5784</v>
+      </c>
+      <c r="C2875" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2876" t="s">
+        <v>5785</v>
+      </c>
+      <c r="B2876" t="s">
+        <v>5786</v>
+      </c>
+      <c r="C2876" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2877" t="s">
+        <v>5787</v>
+      </c>
+      <c r="B2877" t="s">
+        <v>5788</v>
+      </c>
+      <c r="C2877" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2878" t="s">
+        <v>5789</v>
+      </c>
+      <c r="B2878" t="s">
+        <v>5790</v>
+      </c>
+      <c r="C2878" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2879" t="s">
+        <v>5791</v>
+      </c>
+      <c r="B2879" t="s">
+        <v>5792</v>
+      </c>
+      <c r="C2879" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2880" t="s">
+        <v>5793</v>
+      </c>
+      <c r="B2880" t="s">
+        <v>5794</v>
+      </c>
+      <c r="C2880" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2881" t="s">
+        <v>5795</v>
+      </c>
+      <c r="B2881" t="s">
+        <v>5796</v>
+      </c>
+      <c r="C2881" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2882" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2882" t="s">
+        <v>5797</v>
+      </c>
+      <c r="B2882" t="s">
+        <v>5798</v>
+      </c>
+      <c r="C2882" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2883" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2883" t="s">
+        <v>5799</v>
+      </c>
+      <c r="B2883" t="s">
+        <v>5800</v>
+      </c>
+      <c r="C2883" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2884" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2884" t="s">
+        <v>5801</v>
+      </c>
+      <c r="B2884" t="s">
+        <v>5802</v>
+      </c>
+      <c r="C2884" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2885" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2885" t="s">
+        <v>5803</v>
+      </c>
+      <c r="B2885" t="s">
+        <v>5804</v>
+      </c>
+      <c r="C2885" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2886" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2886" t="s">
+        <v>5805</v>
+      </c>
+      <c r="B2886" t="s">
+        <v>5806</v>
+      </c>
+      <c r="C2886" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2887" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2887" t="s">
+        <v>5807</v>
+      </c>
+      <c r="B2887" t="s">
+        <v>5808</v>
+      </c>
+      <c r="C2887" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2888" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2888" t="s">
+        <v>5809</v>
+      </c>
+      <c r="B2888" t="s">
+        <v>5810</v>
+      </c>
+      <c r="C2888" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2889" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2889" t="s">
+        <v>5811</v>
+      </c>
+      <c r="B2889" t="s">
+        <v>5812</v>
+      </c>
+      <c r="C2889" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2890" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2890" t="s">
+        <v>5813</v>
+      </c>
+      <c r="B2890" t="s">
+        <v>5814</v>
+      </c>
+      <c r="C2890" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2891" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2891" t="s">
+        <v>5815</v>
+      </c>
+      <c r="B2891" t="s">
+        <v>5816</v>
+      </c>
+      <c r="C2891" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2892" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2892" t="s">
+        <v>5817</v>
+      </c>
+      <c r="B2892" t="s">
+        <v>5818</v>
+      </c>
+      <c r="C2892" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2893" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2893" t="s">
+        <v>5819</v>
+      </c>
+      <c r="B2893" t="s">
+        <v>5820</v>
+      </c>
+      <c r="C2893" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2894" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2894" t="s">
+        <v>5821</v>
+      </c>
+      <c r="B2894" t="s">
+        <v>5822</v>
+      </c>
+      <c r="C2894" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2895" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2895" t="s">
+        <v>5823</v>
+      </c>
+      <c r="B2895" t="s">
+        <v>5824</v>
+      </c>
+      <c r="C2895" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2896" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2896" t="s">
+        <v>5825</v>
+      </c>
+      <c r="B2896" t="s">
+        <v>5826</v>
+      </c>
+      <c r="C2896" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2897" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2897" t="s">
+        <v>5827</v>
+      </c>
+      <c r="B2897" t="s">
+        <v>5828</v>
+      </c>
+      <c r="C2897" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2898" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2898" t="s">
+        <v>5829</v>
+      </c>
+      <c r="B2898" t="s">
+        <v>5830</v>
+      </c>
+      <c r="C2898" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2899" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2899" t="s">
+        <v>5831</v>
+      </c>
+      <c r="B2899" t="s">
+        <v>5832</v>
+      </c>
+      <c r="C2899" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2900" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2900" t="s">
+        <v>5833</v>
+      </c>
+      <c r="B2900" t="s">
+        <v>5834</v>
+      </c>
+      <c r="C2900" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2901" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2901" t="s">
+        <v>5835</v>
+      </c>
+      <c r="B2901" t="s">
+        <v>5836</v>
+      </c>
+      <c r="C2901" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2902" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2902" t="s">
+        <v>5837</v>
+      </c>
+      <c r="B2902" t="s">
+        <v>5838</v>
+      </c>
+      <c r="C2902" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2903" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2903" t="s">
+        <v>5839</v>
+      </c>
+      <c r="B2903" t="s">
+        <v>5840</v>
+      </c>
+      <c r="C2903" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2904" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2904" t="s">
+        <v>5841</v>
+      </c>
+      <c r="B2904" t="s">
+        <v>5842</v>
+      </c>
+      <c r="C2904" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2905" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2905" t="s">
+        <v>5843</v>
+      </c>
+      <c r="B2905" t="s">
+        <v>5844</v>
+      </c>
+      <c r="C2905" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2906" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2906" t="s">
+        <v>5845</v>
+      </c>
+      <c r="B2906" t="s">
+        <v>5846</v>
+      </c>
+      <c r="C2906" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2907" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2907" t="s">
+        <v>5847</v>
+      </c>
+      <c r="B2907" t="s">
+        <v>5848</v>
+      </c>
+      <c r="C2907" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2908" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2908" t="s">
+        <v>5849</v>
+      </c>
+      <c r="B2908" t="s">
+        <v>5850</v>
+      </c>
+      <c r="C2908" t="s">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="2909" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2909" t="s">
+        <v>5851</v>
+      </c>
+      <c r="B2909" t="s">
+        <v>5852</v>
+      </c>
+      <c r="C2909" t="s">
+        <v>5732</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7221" uniqueCount="5853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7254" uniqueCount="5876">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -17573,6 +17573,75 @@
   </si>
   <si>
     <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Звёздный Вальс" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674649217</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 50х70 - Кремовый бархат</t>
+  </si>
+  <si>
+    <t>31-03-2026</t>
+  </si>
+  <si>
+    <t>4660674649200</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 140х200х30 - "Карибская волна"</t>
+  </si>
+  <si>
+    <t>4660674649194</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 150х200 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4660674649187</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 260х260 - "Гуголету"</t>
+  </si>
+  <si>
+    <t>4660674649170</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 140х200х30 - Белый</t>
+  </si>
+  <si>
+    <t>4660674649163</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель King Size семейное резинка 200х200х30 - 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4660674649156</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 180х200х30 - Прохлада ментола наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674649149</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Дюна"</t>
+  </si>
+  <si>
+    <t>4660674649132</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х45 - 130 - "Лучезарный" 1х1</t>
+  </si>
+  <si>
+    <t>4660674649125</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4660674649118</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х200 - М - 140 - Миндаль 1х1</t>
   </si>
 </sst>
 </file>
@@ -45433,6 +45502,127 @@
         <v>5732</v>
       </c>
     </row>
+    <row r="2910" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2910" t="s">
+        <v>5853</v>
+      </c>
+      <c r="B2910" t="s">
+        <v>5854</v>
+      </c>
+      <c r="C2910" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2911" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2911" t="s">
+        <v>5856</v>
+      </c>
+      <c r="B2911" t="s">
+        <v>5857</v>
+      </c>
+      <c r="C2911" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2912" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2912" t="s">
+        <v>5858</v>
+      </c>
+      <c r="B2912" t="s">
+        <v>5859</v>
+      </c>
+      <c r="C2912" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2913" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2913" t="s">
+        <v>5860</v>
+      </c>
+      <c r="B2913" t="s">
+        <v>5861</v>
+      </c>
+      <c r="C2913" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2914" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2914" t="s">
+        <v>5862</v>
+      </c>
+      <c r="B2914" t="s">
+        <v>5863</v>
+      </c>
+      <c r="C2914" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2915" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2915" t="s">
+        <v>5864</v>
+      </c>
+      <c r="B2915" t="s">
+        <v>5865</v>
+      </c>
+      <c r="C2915" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2916" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2916" t="s">
+        <v>5866</v>
+      </c>
+      <c r="B2916" t="s">
+        <v>5867</v>
+      </c>
+      <c r="C2916" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2917" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2917" t="s">
+        <v>5868</v>
+      </c>
+      <c r="B2917" t="s">
+        <v>5869</v>
+      </c>
+      <c r="C2917" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2918" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2918" t="s">
+        <v>5870</v>
+      </c>
+      <c r="B2918" t="s">
+        <v>5871</v>
+      </c>
+      <c r="C2918" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2919" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2919" t="s">
+        <v>5872</v>
+      </c>
+      <c r="B2919" t="s">
+        <v>5873</v>
+      </c>
+      <c r="C2919" t="s">
+        <v>5855</v>
+      </c>
+    </row>
+    <row r="2920" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2920" t="s">
+        <v>5874</v>
+      </c>
+      <c r="B2920" t="s">
+        <v>5875</v>
+      </c>
+      <c r="C2920" t="s">
+        <v>5855</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5645C886-4F33-4A1A-87EE-E442D3B6E071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
+    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7254" uniqueCount="5876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7353" uniqueCount="5943">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -17642,35 +17643,236 @@
   </si>
   <si>
     <t>Пододеяльник страйп-сатин 200х200 - М - 140 - Миндаль 1х1</t>
+  </si>
+  <si>
+    <t>4660674649545</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>02-04-2026</t>
+  </si>
+  <si>
+    <t>4660674649538</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - М - 60S 4235 Темно-синий</t>
+  </si>
+  <si>
+    <t>4660674649521</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное - "Инспайр"</t>
+  </si>
+  <si>
+    <t>4660674649514</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 125 - Черный 1х1</t>
+  </si>
+  <si>
+    <t>4660674649507</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное - "Звёздный Вальс"</t>
+  </si>
+  <si>
+    <t>4660674649491</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное - "Вилайн" 1х1</t>
+  </si>
+  <si>
+    <t>4660674649484</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Лесная Вуаль"</t>
+  </si>
+  <si>
+    <t>4660674649477</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Лесная Вуаль"</t>
+  </si>
+  <si>
+    <t>4660674649460</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х20 - 130 - Лучезарный 1х1</t>
+  </si>
+  <si>
+    <t>4660674649453</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 220х240 - "Шторм"</t>
+  </si>
+  <si>
+    <t>4660674649446</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 140х200х30 - 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4660674649439</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 220х220х30 - 60S 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4660674649422</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль Евро-макси - 110 - Посев Одуванчика А+В наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4660674649415</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Фирюз 1х1</t>
+  </si>
+  <si>
+    <t>4660674649408</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 125 - Белое тепло</t>
+  </si>
+  <si>
+    <t>4660674649392</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 80х200х20 - 142 ГОСТ - Черный</t>
+  </si>
+  <si>
+    <t>4660674649385</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4660674649378</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х220х30 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4660674649361</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4660674649354</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - "Зелёный Страйп"</t>
+  </si>
+  <si>
+    <t>4660674649347</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 220х240 - "Элиот" 1х1</t>
+  </si>
+  <si>
+    <t>4660674649330</t>
+  </si>
+  <si>
+    <t>Простыня круглая микрофибра резинка 200х200х20 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4660674649323</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра 280х280 - "Марисоль"</t>
+  </si>
+  <si>
+    <t>4660674649316</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Брызги прибоя</t>
+  </si>
+  <si>
+    <t>4660674649309</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Ледяная Мята"</t>
+  </si>
+  <si>
+    <t>4660674649293</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Солнечный 1х1</t>
+  </si>
+  <si>
+    <t>4660674649286</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - "Румянец"</t>
+  </si>
+  <si>
+    <t>4660674649279</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Бархатный Букет" Универсал</t>
+  </si>
+  <si>
+    <t>4660674649262</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - 120 - Будни осьминожки</t>
+  </si>
+  <si>
+    <t>4660674649255</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра 180х220 - "Марисоль"</t>
+  </si>
+  <si>
+    <t>4660674649248</t>
+  </si>
+  <si>
+    <t>Простыня сатин 240х260 - 125 - Тапиока</t>
+  </si>
+  <si>
+    <t>4660674649231</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - 60S 4373 Пудровый</t>
+  </si>
+  <si>
+    <t>4660674649224</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 125 - Предгорье</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -17696,10 +17898,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -17723,7 +17933,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -18000,22 +18210,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P11478"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="177" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18044,7 +18254,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -18052,7 +18262,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -18060,7 +18270,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -18068,7 +18278,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -18076,7 +18286,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -18084,7 +18294,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -18092,7 +18302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -18100,7 +18310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -18108,7 +18318,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -18116,7 +18326,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -18124,7 +18334,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -18132,7 +18342,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -29916,7 +30126,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -29924,7 +30134,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -29932,7 +30142,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -29940,7 +30150,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -29948,7 +30158,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -29956,7 +30166,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -29964,7 +30174,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -29972,7 +30182,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -29980,7 +30190,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -29988,7 +30198,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -29996,7 +30206,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -30004,7 +30214,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -30012,7 +30222,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -30020,7 +30230,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -30028,7 +30238,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -45623,13 +45833,376 @@
         <v>5855</v>
       </c>
     </row>
+    <row r="2921" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2921" t="s">
+        <v>5876</v>
+      </c>
+      <c r="B2921" t="s">
+        <v>5877</v>
+      </c>
+      <c r="C2921" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2922" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2922" t="s">
+        <v>5879</v>
+      </c>
+      <c r="B2922" t="s">
+        <v>5880</v>
+      </c>
+      <c r="C2922" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2923" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2923" t="s">
+        <v>5881</v>
+      </c>
+      <c r="B2923" t="s">
+        <v>5882</v>
+      </c>
+      <c r="C2923" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2924" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2924" t="s">
+        <v>5883</v>
+      </c>
+      <c r="B2924" t="s">
+        <v>5884</v>
+      </c>
+      <c r="C2924" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2925" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2925" t="s">
+        <v>5885</v>
+      </c>
+      <c r="B2925" t="s">
+        <v>5886</v>
+      </c>
+      <c r="C2925" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2926" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2926" t="s">
+        <v>5887</v>
+      </c>
+      <c r="B2926" t="s">
+        <v>5888</v>
+      </c>
+      <c r="C2926" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2927" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2927" t="s">
+        <v>5889</v>
+      </c>
+      <c r="B2927" t="s">
+        <v>5890</v>
+      </c>
+      <c r="C2927" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2928" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2928" t="s">
+        <v>5891</v>
+      </c>
+      <c r="B2928" t="s">
+        <v>5892</v>
+      </c>
+      <c r="C2928" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2929" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2929" t="s">
+        <v>5893</v>
+      </c>
+      <c r="B2929" t="s">
+        <v>5894</v>
+      </c>
+      <c r="C2929" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2930" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2930" t="s">
+        <v>5895</v>
+      </c>
+      <c r="B2930" t="s">
+        <v>5896</v>
+      </c>
+      <c r="C2930" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2931" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2931" t="s">
+        <v>5897</v>
+      </c>
+      <c r="B2931" t="s">
+        <v>5898</v>
+      </c>
+      <c r="C2931" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2932" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2932" t="s">
+        <v>5899</v>
+      </c>
+      <c r="B2932" t="s">
+        <v>5900</v>
+      </c>
+      <c r="C2932" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2933" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2933" t="s">
+        <v>5901</v>
+      </c>
+      <c r="B2933" t="s">
+        <v>5902</v>
+      </c>
+      <c r="C2933" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2934" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2934" t="s">
+        <v>5903</v>
+      </c>
+      <c r="B2934" t="s">
+        <v>5904</v>
+      </c>
+      <c r="C2934" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2935" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2935" t="s">
+        <v>5905</v>
+      </c>
+      <c r="B2935" t="s">
+        <v>5906</v>
+      </c>
+      <c r="C2935" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2936" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2936" t="s">
+        <v>5907</v>
+      </c>
+      <c r="B2936" t="s">
+        <v>5908</v>
+      </c>
+      <c r="C2936" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2937" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2937" t="s">
+        <v>5909</v>
+      </c>
+      <c r="B2937" t="s">
+        <v>5910</v>
+      </c>
+      <c r="C2937" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2938" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2938" t="s">
+        <v>5911</v>
+      </c>
+      <c r="B2938" t="s">
+        <v>5912</v>
+      </c>
+      <c r="C2938" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2939" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2939" t="s">
+        <v>5913</v>
+      </c>
+      <c r="B2939" t="s">
+        <v>5914</v>
+      </c>
+      <c r="C2939" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2940" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2940" t="s">
+        <v>5915</v>
+      </c>
+      <c r="B2940" t="s">
+        <v>5916</v>
+      </c>
+      <c r="C2940" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2941" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2941" t="s">
+        <v>5917</v>
+      </c>
+      <c r="B2941" t="s">
+        <v>5918</v>
+      </c>
+      <c r="C2941" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2942" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2942" t="s">
+        <v>5919</v>
+      </c>
+      <c r="B2942" t="s">
+        <v>5920</v>
+      </c>
+      <c r="C2942" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2943" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2943" t="s">
+        <v>5921</v>
+      </c>
+      <c r="B2943" t="s">
+        <v>5922</v>
+      </c>
+      <c r="C2943" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2944" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2944" t="s">
+        <v>5923</v>
+      </c>
+      <c r="B2944" t="s">
+        <v>5924</v>
+      </c>
+      <c r="C2944" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2945" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2945" t="s">
+        <v>5925</v>
+      </c>
+      <c r="B2945" t="s">
+        <v>5926</v>
+      </c>
+      <c r="C2945" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2946" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2946" t="s">
+        <v>5927</v>
+      </c>
+      <c r="B2946" t="s">
+        <v>5928</v>
+      </c>
+      <c r="C2946" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2947" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2947" t="s">
+        <v>5929</v>
+      </c>
+      <c r="B2947" t="s">
+        <v>5930</v>
+      </c>
+      <c r="C2947" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2948" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2948" t="s">
+        <v>5931</v>
+      </c>
+      <c r="B2948" t="s">
+        <v>5932</v>
+      </c>
+      <c r="C2948" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2949" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2949" t="s">
+        <v>5933</v>
+      </c>
+      <c r="B2949" t="s">
+        <v>5934</v>
+      </c>
+      <c r="C2949" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2950" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2950" t="s">
+        <v>5935</v>
+      </c>
+      <c r="B2950" t="s">
+        <v>5936</v>
+      </c>
+      <c r="C2950" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2951" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2951" t="s">
+        <v>5937</v>
+      </c>
+      <c r="B2951" t="s">
+        <v>5938</v>
+      </c>
+      <c r="C2951" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2952" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2952" t="s">
+        <v>5939</v>
+      </c>
+      <c r="B2952" t="s">
+        <v>5940</v>
+      </c>
+      <c r="C2952" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2953" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2953" t="s">
+        <v>5941</v>
+      </c>
+      <c r="B2953" t="s">
+        <v>5942</v>
+      </c>
+      <c r="C2953" t="s">
+        <v>5878</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>
-    <row r="4890" ht="26.25" customHeight="1" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="4890" spans="7:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G4890" s="7"/>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
@@ -45645,6 +46218,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5645C886-4F33-4A1A-87EE-E442D3B6E071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7353" uniqueCount="5943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7401" uniqueCount="5975">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -17844,35 +17843,131 @@
   </si>
   <si>
     <t>Наволочка бязь 70х70 - 125 - Предгорье</t>
+  </si>
+  <si>
+    <t>4660674649699</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 200х220 - "Смоки"</t>
+  </si>
+  <si>
+    <t>4660674649682</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Трендис"</t>
+  </si>
+  <si>
+    <t>4660674649675</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Изумруд Эсмеральды</t>
+  </si>
+  <si>
+    <t>4660674649668</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Изумруд Эсмеральды</t>
+  </si>
+  <si>
+    <t>4660674649651</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 260х260 - "Легкий роман"</t>
+  </si>
+  <si>
+    <t>4660674649644</t>
+  </si>
+  <si>
+    <t>Простыня детская из бязи 150 х 220 - М - 125 - В ассортименте</t>
+  </si>
+  <si>
+    <t>4660674649637</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Лаймкват 1х1</t>
+  </si>
+  <si>
+    <t>4660674649620</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 80х200х20 - 142 ГОСТ - Серый</t>
+  </si>
+  <si>
+    <t>4660674649613</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 200х220х40 - "Шторм"</t>
+  </si>
+  <si>
+    <t>4660674649606</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Сиренево-розовый"</t>
+  </si>
+  <si>
+    <t>4660674649590</t>
+  </si>
+  <si>
+    <t>Простыня из бязи на резинке 90 х 200 х 30 - М - 142 - Монстера на коричневом</t>
+  </si>
+  <si>
+    <t>4660674649583</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - М - 60S 4251 Хвойный</t>
+  </si>
+  <si>
+    <t>4660674649576</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 175х215 - М - Пинкроуз</t>
+  </si>
+  <si>
+    <t>4660674649569</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 90х200х30 - "Бирюзовый Рельеф"</t>
+  </si>
+  <si>
+    <t>4660674649552</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4660674649705</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Нежно-розовый</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -17898,18 +17993,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -17933,7 +18020,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -18210,22 +18297,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:P11478"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="177" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18254,7 +18341,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -18262,7 +18349,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -18270,7 +18357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -18278,7 +18365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -18286,7 +18373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -18294,7 +18381,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -18302,7 +18389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -18310,7 +18397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -18318,7 +18405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -18326,7 +18413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -18334,7 +18421,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -18342,7 +18429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -30126,7 +30213,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -30134,7 +30221,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -30142,7 +30229,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -30150,7 +30237,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -30158,7 +30245,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -30166,7 +30253,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -30174,7 +30261,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -30182,7 +30269,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -30190,7 +30277,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -30198,7 +30285,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -30206,7 +30293,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -30214,7 +30301,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -30222,7 +30309,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -30230,7 +30317,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -30238,7 +30325,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -46196,13 +46283,189 @@
         <v>5878</v>
       </c>
     </row>
+    <row r="2954" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2954" t="s">
+        <v>5943</v>
+      </c>
+      <c r="B2954" t="s">
+        <v>5944</v>
+      </c>
+      <c r="C2954" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2955" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2955" t="s">
+        <v>5945</v>
+      </c>
+      <c r="B2955" t="s">
+        <v>5946</v>
+      </c>
+      <c r="C2955" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2956" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2956" t="s">
+        <v>5947</v>
+      </c>
+      <c r="B2956" t="s">
+        <v>5948</v>
+      </c>
+      <c r="C2956" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2957" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2957" t="s">
+        <v>5949</v>
+      </c>
+      <c r="B2957" t="s">
+        <v>5950</v>
+      </c>
+      <c r="C2957" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2958" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2958" t="s">
+        <v>5951</v>
+      </c>
+      <c r="B2958" t="s">
+        <v>5952</v>
+      </c>
+      <c r="C2958" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2959" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2959" t="s">
+        <v>5953</v>
+      </c>
+      <c r="B2959" t="s">
+        <v>5954</v>
+      </c>
+      <c r="C2959" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2960" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2960" t="s">
+        <v>5955</v>
+      </c>
+      <c r="B2960" t="s">
+        <v>5956</v>
+      </c>
+      <c r="C2960" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2961" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2961" t="s">
+        <v>5957</v>
+      </c>
+      <c r="B2961" t="s">
+        <v>5958</v>
+      </c>
+      <c r="C2961" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2962" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2962" t="s">
+        <v>5959</v>
+      </c>
+      <c r="B2962" t="s">
+        <v>5960</v>
+      </c>
+      <c r="C2962" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2963" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2963" t="s">
+        <v>5961</v>
+      </c>
+      <c r="B2963" t="s">
+        <v>5962</v>
+      </c>
+      <c r="C2963" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2964" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2964" t="s">
+        <v>5963</v>
+      </c>
+      <c r="B2964" t="s">
+        <v>5964</v>
+      </c>
+      <c r="C2964" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2965" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2965" t="s">
+        <v>5965</v>
+      </c>
+      <c r="B2965" t="s">
+        <v>5966</v>
+      </c>
+      <c r="C2965" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2966" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2966" t="s">
+        <v>5967</v>
+      </c>
+      <c r="B2966" t="s">
+        <v>5968</v>
+      </c>
+      <c r="C2966" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2967" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2967" t="s">
+        <v>5969</v>
+      </c>
+      <c r="B2967" t="s">
+        <v>5970</v>
+      </c>
+      <c r="C2967" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2968" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2968" t="s">
+        <v>5971</v>
+      </c>
+      <c r="B2968" t="s">
+        <v>5972</v>
+      </c>
+      <c r="C2968" t="s">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="2969" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2969" t="s">
+        <v>5973</v>
+      </c>
+      <c r="B2969" t="s">
+        <v>5974</v>
+      </c>
+      <c r="C2969" t="s">
+        <v>5878</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>
-    <row r="4890" spans="7:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4890" ht="26.25" customHeight="1" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G4890" s="7"/>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
@@ -46218,6 +46481,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919661E0-02A4-4D5C-BDAF-E01257779D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Краткий отчет'!$A$4:$C$2979</definedName>
+    <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7431" uniqueCount="5996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7698" uniqueCount="6175">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -8957,87 +8956,87 @@
     <t>Простыня круглая ранфорс на резинке 210х210х20 - "Лазурный бриз"</t>
   </si>
   <si>
+    <t>4660674645462</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Жатка 2 спальное - "Лесная Мелодия" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4660674645455</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль 1,5 спальное на резинке 120х200х30 - М - 110 - Посев Одуванчика А+В с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4660674645448</t>
+  </si>
+  <si>
+    <t>Пододеяльник из перкаля 175 х 215 - М - 110 - Белоснежный луч</t>
+  </si>
+  <si>
+    <t>4660674645431</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро макси - М - 135 - Кувертюр 1х1 с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4660674645424</t>
+  </si>
+  <si>
+    <t>КПБ Постельное белье тенсель семейное на резинке 180х200х30 - "Песочная роза"</t>
+  </si>
+  <si>
+    <t>4660674645417</t>
+  </si>
+  <si>
+    <t>Простыня из креп-жатки 220 х 240 - М - 80 - Теплые Пожелания</t>
+  </si>
+  <si>
+    <t>4660674645400</t>
+  </si>
+  <si>
+    <t>КПБ Постельное белье микросатин 2 спальное с Евро простыней - "Смоки" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4660674645394</t>
+  </si>
+  <si>
+    <t>КПБ Постельное белье микросатин 2 спальное с Евро простыней - "Шторм" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4660674645387</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Микрофибра 1,5 спальное на резинке 120х200х30 - "Эстрелья"</t>
+  </si>
+  <si>
+    <t>4660674645370</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Микрофибра 1,5 спальное на резинке 120х200х30 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4660674645363</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль Евро на резинке 160х200х30 - М - 110 - Лайнс с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4660674645356</t>
+  </si>
+  <si>
+    <t>Простыня из страйп-сатина на резинке 200 х 220 х 30 - М - 135 - Барбаденсис 1х1</t>
+  </si>
+  <si>
+    <t>4660674645349</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150 х 200 - "Кленовая зелень"</t>
+  </si>
+  <si>
     <t>08-02-2026</t>
   </si>
   <si>
-    <t>4660674645462</t>
-  </si>
-  <si>
-    <t>КПБ Постельное бельё Жатка 2 спальное - "Лесная Мелодия" с наволочками 50х70</t>
-  </si>
-  <si>
-    <t>4660674645455</t>
-  </si>
-  <si>
-    <t>КПБ Постельное бельё перкаль 1,5 спальное на резинке 120х200х30 - М - 110 - Посев Одуванчика А+В с наволочками 50х70</t>
-  </si>
-  <si>
-    <t>4660674645448</t>
-  </si>
-  <si>
-    <t>Пододеяльник из перкаля 175 х 215 - М - 110 - Белоснежный луч</t>
-  </si>
-  <si>
-    <t>4660674645431</t>
-  </si>
-  <si>
-    <t>КПБ Постельное бельё страйп-сатин Евро макси - М - 135 - Кувертюр 1х1 с наволочками 50х70</t>
-  </si>
-  <si>
-    <t>4660674645424</t>
-  </si>
-  <si>
-    <t>КПБ Постельное белье тенсель семейное на резинке 180х200х30 - "Песочная роза"</t>
-  </si>
-  <si>
-    <t>4660674645417</t>
-  </si>
-  <si>
-    <t>Простыня из креп-жатки 220 х 240 - М - 80 - Теплые Пожелания</t>
-  </si>
-  <si>
-    <t>4660674645400</t>
-  </si>
-  <si>
-    <t>КПБ Постельное белье микросатин 2 спальное с Евро простыней - "Смоки" с наволочками 50х70</t>
-  </si>
-  <si>
-    <t>4660674645394</t>
-  </si>
-  <si>
-    <t>КПБ Постельное белье микросатин 2 спальное с Евро простыней - "Шторм" с наволочками 50х70</t>
-  </si>
-  <si>
-    <t>4660674645387</t>
-  </si>
-  <si>
-    <t>КПБ Постельное бельё Микрофибра 1,5 спальное на резинке 120х200х30 - "Эстрелья"</t>
-  </si>
-  <si>
-    <t>4660674645370</t>
-  </si>
-  <si>
-    <t>КПБ Постельное бельё Микрофибра 1,5 спальное на резинке 120х200х30 - "Петкана"</t>
-  </si>
-  <si>
-    <t>4660674645363</t>
-  </si>
-  <si>
-    <t>КПБ Постельное бельё перкаль Евро на резинке 160х200х30 - М - 110 - Лайнс с наволочками 50х70</t>
-  </si>
-  <si>
-    <t>4660674645356</t>
-  </si>
-  <si>
-    <t>Простыня из страйп-сатина на резинке 200 х 220 х 30 - М - 135 - Барбаденсис 1х1</t>
-  </si>
-  <si>
-    <t>4660674645349</t>
-  </si>
-  <si>
-    <t>Пододеяльник полисатин 150 х 200 - "Кленовая зелень"</t>
-  </si>
-  <si>
     <t>4660674645332</t>
   </si>
   <si>
@@ -12608,15 +12607,15 @@
     <t>Наволочка поплин 50х70 - "Далиян"</t>
   </si>
   <si>
+    <t>4610594533141</t>
+  </si>
+  <si>
+    <t>Простыня Микрофибра на резинке 160х200х20 - "Петкана"</t>
+  </si>
+  <si>
     <t>27-02-2026</t>
   </si>
   <si>
-    <t>4610594533141</t>
-  </si>
-  <si>
-    <t>Простыня Микрофибра на резинке 160х200х20 - "Петкана"</t>
-  </si>
-  <si>
     <t>4610594533134</t>
   </si>
   <si>
@@ -18006,35 +18005,572 @@
   </si>
   <si>
     <t>Пододеяльник страйп-сатин 150х200 - М - 135 - Фирюз 1х1</t>
+  </si>
+  <si>
+    <t>4681001600947</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 120х200х30 - 110 - Полнолуние</t>
+  </si>
+  <si>
+    <t>05-04-2026</t>
+  </si>
+  <si>
+    <t>4681001600930</t>
+  </si>
+  <si>
+    <t>Простыня жатка 180х220 - "Макена"</t>
+  </si>
+  <si>
+    <t>4681001600923</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин семейное - "Шторм" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600916</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро-макси резинка 180х200х30 - "Шторм"</t>
+  </si>
+  <si>
+    <t>4681001600909</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 125 - Черный 1х1</t>
+  </si>
+  <si>
+    <t>4681001600893</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 220х240 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>4681001600886</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Бахати"</t>
+  </si>
+  <si>
+    <t>4681001600879</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 60х60 - "Кофейный крем"</t>
+  </si>
+  <si>
+    <t>4681001600862</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - М - Блестящий миндаль</t>
+  </si>
+  <si>
+    <t>4681001600855</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное Евро простыня - 142 - Стилизация</t>
+  </si>
+  <si>
+    <t>4681001600848</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - 60S Белый</t>
+  </si>
+  <si>
+    <t>4681001600831</t>
+  </si>
+  <si>
+    <t>Простыня бязь 240х260 - "Вэспер"</t>
+  </si>
+  <si>
+    <t>4681001600824</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - Мечта наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600817</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - "Цветочный Шёпот" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600800</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро - "Вэспер" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600794</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Инспайр"</t>
+  </si>
+  <si>
+    <t>4681001600787</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х200 - "Инспайр"</t>
+  </si>
+  <si>
+    <t>4681001600770</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Винно-красный 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600763</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль 2 спальное резинка 160х200х20 - 110 - Белоснежный луч</t>
+  </si>
+  <si>
+    <t>4681001600756</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Графитовый Зигзаг"</t>
+  </si>
+  <si>
+    <t>4681001600749</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 220х220х30 - 135 - Форастеро 1х1</t>
+  </si>
+  <si>
+    <t>4681001600732</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 220х220х30 - 135 - Марриотт Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001600725</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Звёздный Вальс"</t>
+  </si>
+  <si>
+    <t>4681001600718</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Сирента"</t>
+  </si>
+  <si>
+    <t>4681001600701</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - "Сирента" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600695</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 200х200х30 - "Бежевый шлейф"</t>
+  </si>
+  <si>
+    <t>4681001600688</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - 120 - Хадусамат наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600671</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 220х220х30 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001600664</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Призрачная лагуна" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600657</t>
+  </si>
+  <si>
+    <t>Простыня жатка 150х220 - "Замороженный Перец"</t>
+  </si>
+  <si>
+    <t>4681001600640</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 40х40 - "Анселмо"</t>
+  </si>
+  <si>
+    <t>4681001600633</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - 125 - "Бразилин" 1х1</t>
+  </si>
+  <si>
+    <t>4681001600626</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 145х215 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4681001600619</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 70х70 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4681001600602</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Кленовая зелень" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600596</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Эвергрин"</t>
+  </si>
+  <si>
+    <t>4681001600589</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 160х200х30 - Премиум ТС 320 Кортес наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600572</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное резинка 140х200х30 - 140 - Сирень 1х1</t>
+  </si>
+  <si>
+    <t>4681001600565</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - М - Магма А+В</t>
+  </si>
+  <si>
+    <t>4681001600558</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 180х220 - Серо-зелёный</t>
+  </si>
+  <si>
+    <t>4681001600541</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Цветочный Шарм"</t>
+  </si>
+  <si>
+    <t>4681001600534</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х200 - М - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001600527</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001600510</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х200х30 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001600503</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 140х200х30 - "Самолётики" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600497</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Нежный Листопад"</t>
+  </si>
+  <si>
+    <t>4681001600480</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 220х240 - "Графитовый Зигзаг"</t>
+  </si>
+  <si>
+    <t>4681001600473</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х20 - "Песчаный ветер"</t>
+  </si>
+  <si>
+    <t>4681001600466</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х20 - "Челестэ"</t>
+  </si>
+  <si>
+    <t>4681001600459</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Латунь"</t>
+  </si>
+  <si>
+    <t>4681001600442</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Латунь"</t>
+  </si>
+  <si>
+    <t>4681001600435</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х200 - "Угольная Паутинка"</t>
+  </si>
+  <si>
+    <t>4681001600428</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Сумерин"</t>
+  </si>
+  <si>
+    <t>4681001600411</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х30 - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001600404</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - М - Полуночный постинг А+В</t>
+  </si>
+  <si>
+    <t>4681001600398</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - М - Кружева на сером</t>
+  </si>
+  <si>
+    <t>4681001600381</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х45 - 140 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001600374</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - 80 - Черный кот</t>
+  </si>
+  <si>
+    <t>4681001600367</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Жатка семейное на резинке 180х200х30 - "Плюмас"</t>
+  </si>
+  <si>
+    <t>4681001600350</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 220х240 - М - Глазурь</t>
+  </si>
+  <si>
+    <t>4681001600343</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 180х200х30 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001600336</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 ГОСТ - Перья</t>
+  </si>
+  <si>
+    <t>4681001600329</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 ГОСТ - Космические Звёзды</t>
+  </si>
+  <si>
+    <t>4681001600312</t>
+  </si>
+  <si>
+    <t>Простыня бязь 220х240 - 120 - Северные Волки</t>
+  </si>
+  <si>
+    <t>4681001600305</t>
+  </si>
+  <si>
+    <t>Простыня из сатина 150 х 220 - М - 120 - В ассортименте</t>
+  </si>
+  <si>
+    <t>4681001600299</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - 80 - Теплые Пожелания</t>
+  </si>
+  <si>
+    <t>4681001600282</t>
+  </si>
+  <si>
+    <t>Простыня жаккард 200х220 - Палладион</t>
+  </si>
+  <si>
+    <t>4681001600275</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 200х200х30 - "Белава"</t>
+  </si>
+  <si>
+    <t>4681001600268</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 180х220 - "Облачка"</t>
+  </si>
+  <si>
+    <t>4681001600251</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 175х215 - "Селинто"</t>
+  </si>
+  <si>
+    <t>4681001600244</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 220х240 - 125 - "Фая" 1х1</t>
+  </si>
+  <si>
+    <t>4681001600237</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - "Вакита"</t>
+  </si>
+  <si>
+    <t>4681001600220</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001600213</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - М - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001600206</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Снежный Хищник"</t>
+  </si>
+  <si>
+    <t>4681001600190</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - М - Уголёк</t>
+  </si>
+  <si>
+    <t>4681001600183</t>
+  </si>
+  <si>
+    <t>Простыня жатка 260х260 - "Макена"</t>
+  </si>
+  <si>
+    <t>4681001600176</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Грей блес</t>
+  </si>
+  <si>
+    <t>4681001600169</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 60х60 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4681001600152</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Олуфими"</t>
+  </si>
+  <si>
+    <t>4681001600145</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4681001600138</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - "Цветочный Шёпот"</t>
+  </si>
+  <si>
+    <t>4681001600121</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Серый Райнар"</t>
+  </si>
+  <si>
+    <t>4681001600114</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 150х200 - "Розанна"</t>
+  </si>
+  <si>
+    <t>4681001600107</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Насыщенный розовый</t>
+  </si>
+  <si>
+    <t>4681001600091</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Мускусная дыня 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001600084</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Блестящий миндаль</t>
+  </si>
+  <si>
+    <t>4681001600077</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - 130 - Hotel Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001600060</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 130 - Hotel Белый 3х3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -18060,18 +18596,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -18095,7 +18623,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -18383,22 +18911,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:P11478"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="177" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18427,7 +18955,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -18435,7 +18963,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -18443,7 +18971,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -18451,7 +18979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -18459,7 +18987,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -18467,7 +18995,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -18475,7 +19003,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -18483,7 +19011,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -18491,7 +19019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -18499,7 +19027,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -18507,7 +19035,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -18515,7 +19043,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -30299,7 +30827,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -30307,7 +30835,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -30315,7 +30843,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -30323,111 +30851,111 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
+        <v>2979</v>
+      </c>
+      <c r="B1492" t="s">
         <v>2980</v>
       </c>
-      <c r="B1492" t="s">
+    </row>
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1493" t="s">
         <v>2981</v>
       </c>
-    </row>
-    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1493" t="s">
+      <c r="B1493" t="s">
         <v>2982</v>
       </c>
-      <c r="B1493" t="s">
+    </row>
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1494" t="s">
         <v>2983</v>
       </c>
-    </row>
-    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1494" t="s">
+      <c r="B1494" t="s">
         <v>2984</v>
       </c>
-      <c r="B1494" t="s">
+    </row>
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1495" t="s">
         <v>2985</v>
       </c>
-    </row>
-    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1495" t="s">
+      <c r="B1495" t="s">
         <v>2986</v>
       </c>
-      <c r="B1495" t="s">
+    </row>
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1496" t="s">
         <v>2987</v>
       </c>
-    </row>
-    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1496" t="s">
+      <c r="B1496" t="s">
         <v>2988</v>
       </c>
-      <c r="B1496" t="s">
+    </row>
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1497" t="s">
         <v>2989</v>
       </c>
-    </row>
-    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1497" t="s">
+      <c r="B1497" t="s">
         <v>2990</v>
       </c>
-      <c r="B1497" t="s">
+    </row>
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1498" t="s">
         <v>2991</v>
       </c>
-    </row>
-    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1498" t="s">
+      <c r="B1498" t="s">
         <v>2992</v>
       </c>
-      <c r="B1498" t="s">
+    </row>
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1499" t="s">
         <v>2993</v>
       </c>
-    </row>
-    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1499" t="s">
+      <c r="B1499" t="s">
         <v>2994</v>
       </c>
-      <c r="B1499" t="s">
+    </row>
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1500" t="s">
         <v>2995</v>
       </c>
-    </row>
-    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1500" t="s">
+      <c r="B1500" t="s">
         <v>2996</v>
       </c>
-      <c r="B1500" t="s">
+    </row>
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1501" t="s">
         <v>2997</v>
       </c>
-    </row>
-    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1501" t="s">
+      <c r="B1501" t="s">
         <v>2998</v>
       </c>
-      <c r="B1501" t="s">
+    </row>
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1502" t="s">
         <v>2999</v>
       </c>
-    </row>
-    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1502" t="s">
+      <c r="B1502" t="s">
         <v>3000</v>
       </c>
-      <c r="B1502" t="s">
+    </row>
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1503" t="s">
         <v>3001</v>
       </c>
-    </row>
-    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1503" t="s">
+      <c r="B1503" t="s">
         <v>3002</v>
-      </c>
-      <c r="B1503" t="s">
-        <v>3003</v>
       </c>
     </row>
     <row r="1504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1504" t="s">
+        <v>3003</v>
+      </c>
+      <c r="B1504" t="s">
         <v>3004</v>
       </c>
-      <c r="B1504" t="s">
+      <c r="C1504" t="s">
         <v>3005</v>
-      </c>
-      <c r="C1504" t="s">
-        <v>2979</v>
       </c>
     </row>
     <row r="1505" spans="1:3" x14ac:dyDescent="0.25">
@@ -30438,7 +30966,7 @@
         <v>3007</v>
       </c>
       <c r="C1505" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1506" spans="1:3" x14ac:dyDescent="0.25">
@@ -30449,7 +30977,7 @@
         <v>3009</v>
       </c>
       <c r="C1506" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.25">
@@ -30460,7 +30988,7 @@
         <v>3011</v>
       </c>
       <c r="C1507" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1508" spans="1:3" x14ac:dyDescent="0.25">
@@ -30471,7 +30999,7 @@
         <v>3013</v>
       </c>
       <c r="C1508" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.25">
@@ -30482,7 +31010,7 @@
         <v>3015</v>
       </c>
       <c r="C1509" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1510" spans="1:3" x14ac:dyDescent="0.25">
@@ -30493,7 +31021,7 @@
         <v>3017</v>
       </c>
       <c r="C1510" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1511" spans="1:3" x14ac:dyDescent="0.25">
@@ -30504,7 +31032,7 @@
         <v>3019</v>
       </c>
       <c r="C1511" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1512" spans="1:3" x14ac:dyDescent="0.25">
@@ -30515,7 +31043,7 @@
         <v>3021</v>
       </c>
       <c r="C1512" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1513" spans="1:3" x14ac:dyDescent="0.25">
@@ -30526,7 +31054,7 @@
         <v>3023</v>
       </c>
       <c r="C1513" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1514" spans="1:3" x14ac:dyDescent="0.25">
@@ -30537,7 +31065,7 @@
         <v>3025</v>
       </c>
       <c r="C1514" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1515" spans="1:3" x14ac:dyDescent="0.25">
@@ -30548,7 +31076,7 @@
         <v>3027</v>
       </c>
       <c r="C1515" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1516" spans="1:3" x14ac:dyDescent="0.25">
@@ -30559,7 +31087,7 @@
         <v>3029</v>
       </c>
       <c r="C1516" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1517" spans="1:3" x14ac:dyDescent="0.25">
@@ -30570,7 +31098,7 @@
         <v>3031</v>
       </c>
       <c r="C1517" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.25">
@@ -30581,7 +31109,7 @@
         <v>3033</v>
       </c>
       <c r="C1518" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1519" spans="1:3" x14ac:dyDescent="0.25">
@@ -30592,7 +31120,7 @@
         <v>3035</v>
       </c>
       <c r="C1519" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.25">
@@ -30603,7 +31131,7 @@
         <v>3037</v>
       </c>
       <c r="C1520" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1521" spans="1:3" x14ac:dyDescent="0.25">
@@ -30614,7 +31142,7 @@
         <v>3039</v>
       </c>
       <c r="C1521" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1522" spans="1:3" x14ac:dyDescent="0.25">
@@ -30625,7 +31153,7 @@
         <v>3041</v>
       </c>
       <c r="C1522" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1523" spans="1:3" x14ac:dyDescent="0.25">
@@ -30636,7 +31164,7 @@
         <v>3043</v>
       </c>
       <c r="C1523" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1524" spans="1:3" x14ac:dyDescent="0.25">
@@ -30647,7 +31175,7 @@
         <v>3045</v>
       </c>
       <c r="C1524" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1525" spans="1:3" x14ac:dyDescent="0.25">
@@ -30658,7 +31186,7 @@
         <v>3047</v>
       </c>
       <c r="C1525" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1526" spans="1:3" x14ac:dyDescent="0.25">
@@ -30669,7 +31197,7 @@
         <v>3049</v>
       </c>
       <c r="C1526" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1527" spans="1:3" x14ac:dyDescent="0.25">
@@ -30680,7 +31208,7 @@
         <v>3051</v>
       </c>
       <c r="C1527" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1528" spans="1:3" x14ac:dyDescent="0.25">
@@ -30691,7 +31219,7 @@
         <v>3053</v>
       </c>
       <c r="C1528" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.25">
@@ -30702,7 +31230,7 @@
         <v>3055</v>
       </c>
       <c r="C1529" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1530" spans="1:3" x14ac:dyDescent="0.25">
@@ -30713,7 +31241,7 @@
         <v>3057</v>
       </c>
       <c r="C1530" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.25">
@@ -30724,7 +31252,7 @@
         <v>3059</v>
       </c>
       <c r="C1531" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1532" spans="1:3" x14ac:dyDescent="0.25">
@@ -30735,7 +31263,7 @@
         <v>3061</v>
       </c>
       <c r="C1532" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1533" spans="1:3" x14ac:dyDescent="0.25">
@@ -30746,7 +31274,7 @@
         <v>3063</v>
       </c>
       <c r="C1533" t="s">
-        <v>2979</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1534" spans="1:3" x14ac:dyDescent="0.25">
@@ -36900,13 +37428,13 @@
     </row>
     <row r="2093" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2093" t="s">
+        <v>4196</v>
+      </c>
+      <c r="B2093" t="s">
         <v>4197</v>
       </c>
-      <c r="B2093" t="s">
+      <c r="C2093" t="s">
         <v>4198</v>
-      </c>
-      <c r="C2093" t="s">
-        <v>4196</v>
       </c>
     </row>
     <row r="2094" spans="1:3" x14ac:dyDescent="0.25">
@@ -36917,7 +37445,7 @@
         <v>4200</v>
       </c>
       <c r="C2094" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2095" spans="1:3" x14ac:dyDescent="0.25">
@@ -36928,7 +37456,7 @@
         <v>4202</v>
       </c>
       <c r="C2095" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2096" spans="1:3" x14ac:dyDescent="0.25">
@@ -36939,7 +37467,7 @@
         <v>4204</v>
       </c>
       <c r="C2096" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2097" spans="1:3" x14ac:dyDescent="0.25">
@@ -36950,7 +37478,7 @@
         <v>4206</v>
       </c>
       <c r="C2097" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2098" spans="1:3" x14ac:dyDescent="0.25">
@@ -36961,7 +37489,7 @@
         <v>4208</v>
       </c>
       <c r="C2098" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2099" spans="1:3" x14ac:dyDescent="0.25">
@@ -36972,7 +37500,7 @@
         <v>4210</v>
       </c>
       <c r="C2099" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2100" spans="1:3" x14ac:dyDescent="0.25">
@@ -36983,7 +37511,7 @@
         <v>4212</v>
       </c>
       <c r="C2100" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2101" spans="1:3" x14ac:dyDescent="0.25">
@@ -36994,7 +37522,7 @@
         <v>4214</v>
       </c>
       <c r="C2101" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2102" spans="1:3" x14ac:dyDescent="0.25">
@@ -37005,7 +37533,7 @@
         <v>4216</v>
       </c>
       <c r="C2102" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2103" spans="1:3" x14ac:dyDescent="0.25">
@@ -37016,7 +37544,7 @@
         <v>4218</v>
       </c>
       <c r="C2103" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2104" spans="1:3" x14ac:dyDescent="0.25">
@@ -37027,7 +37555,7 @@
         <v>4220</v>
       </c>
       <c r="C2104" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="2105" spans="1:3" x14ac:dyDescent="0.25">
@@ -46655,13 +47183,992 @@
         <v>5935</v>
       </c>
     </row>
+    <row r="2980" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2980" t="s">
+        <v>5996</v>
+      </c>
+      <c r="B2980" t="s">
+        <v>5997</v>
+      </c>
+      <c r="C2980" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2981" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2981" t="s">
+        <v>5999</v>
+      </c>
+      <c r="B2981" t="s">
+        <v>6000</v>
+      </c>
+      <c r="C2981" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2982" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2982" t="s">
+        <v>6001</v>
+      </c>
+      <c r="B2982" t="s">
+        <v>6002</v>
+      </c>
+      <c r="C2982" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2983" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2983" t="s">
+        <v>6003</v>
+      </c>
+      <c r="B2983" t="s">
+        <v>6004</v>
+      </c>
+      <c r="C2983" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2984" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2984" t="s">
+        <v>6005</v>
+      </c>
+      <c r="B2984" t="s">
+        <v>6006</v>
+      </c>
+      <c r="C2984" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2985" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2985" t="s">
+        <v>6007</v>
+      </c>
+      <c r="B2985" t="s">
+        <v>6008</v>
+      </c>
+      <c r="C2985" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2986" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2986" t="s">
+        <v>6009</v>
+      </c>
+      <c r="B2986" t="s">
+        <v>6010</v>
+      </c>
+      <c r="C2986" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2987" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2987" t="s">
+        <v>6011</v>
+      </c>
+      <c r="B2987" t="s">
+        <v>6012</v>
+      </c>
+      <c r="C2987" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2988" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2988" t="s">
+        <v>6013</v>
+      </c>
+      <c r="B2988" t="s">
+        <v>6014</v>
+      </c>
+      <c r="C2988" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2989" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2989" t="s">
+        <v>6015</v>
+      </c>
+      <c r="B2989" t="s">
+        <v>6016</v>
+      </c>
+      <c r="C2989" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2990" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2990" t="s">
+        <v>6017</v>
+      </c>
+      <c r="B2990" t="s">
+        <v>6018</v>
+      </c>
+      <c r="C2990" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2991" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2991" t="s">
+        <v>6019</v>
+      </c>
+      <c r="B2991" t="s">
+        <v>6020</v>
+      </c>
+      <c r="C2991" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2992" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2992" t="s">
+        <v>6021</v>
+      </c>
+      <c r="B2992" t="s">
+        <v>6022</v>
+      </c>
+      <c r="C2992" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2993" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2993" t="s">
+        <v>6023</v>
+      </c>
+      <c r="B2993" t="s">
+        <v>6024</v>
+      </c>
+      <c r="C2993" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2994" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2994" t="s">
+        <v>6025</v>
+      </c>
+      <c r="B2994" t="s">
+        <v>6026</v>
+      </c>
+      <c r="C2994" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2995" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2995" t="s">
+        <v>6027</v>
+      </c>
+      <c r="B2995" t="s">
+        <v>6028</v>
+      </c>
+      <c r="C2995" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2996" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2996" t="s">
+        <v>6029</v>
+      </c>
+      <c r="B2996" t="s">
+        <v>6030</v>
+      </c>
+      <c r="C2996" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2997" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2997" t="s">
+        <v>6031</v>
+      </c>
+      <c r="B2997" t="s">
+        <v>6032</v>
+      </c>
+      <c r="C2997" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2998" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2998" t="s">
+        <v>6033</v>
+      </c>
+      <c r="B2998" t="s">
+        <v>6034</v>
+      </c>
+      <c r="C2998" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="2999" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2999" t="s">
+        <v>6035</v>
+      </c>
+      <c r="B2999" t="s">
+        <v>6036</v>
+      </c>
+      <c r="C2999" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3000" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3000" t="s">
+        <v>6037</v>
+      </c>
+      <c r="B3000" t="s">
+        <v>6038</v>
+      </c>
+      <c r="C3000" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3001" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3001" t="s">
+        <v>6039</v>
+      </c>
+      <c r="B3001" t="s">
+        <v>6040</v>
+      </c>
+      <c r="C3001" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3002" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3002" t="s">
+        <v>6041</v>
+      </c>
+      <c r="B3002" t="s">
+        <v>6042</v>
+      </c>
+      <c r="C3002" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3003" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3003" t="s">
+        <v>6043</v>
+      </c>
+      <c r="B3003" t="s">
+        <v>6044</v>
+      </c>
+      <c r="C3003" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3004" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3004" t="s">
+        <v>6045</v>
+      </c>
+      <c r="B3004" t="s">
+        <v>6046</v>
+      </c>
+      <c r="C3004" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3005" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3005" t="s">
+        <v>6047</v>
+      </c>
+      <c r="B3005" t="s">
+        <v>6048</v>
+      </c>
+      <c r="C3005" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3006" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3006" t="s">
+        <v>6049</v>
+      </c>
+      <c r="B3006" t="s">
+        <v>6050</v>
+      </c>
+      <c r="C3006" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3007" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3007" t="s">
+        <v>6051</v>
+      </c>
+      <c r="B3007" t="s">
+        <v>6052</v>
+      </c>
+      <c r="C3007" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3008" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3008" t="s">
+        <v>6053</v>
+      </c>
+      <c r="B3008" t="s">
+        <v>6054</v>
+      </c>
+      <c r="C3008" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3009" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3009" t="s">
+        <v>6055</v>
+      </c>
+      <c r="B3009" t="s">
+        <v>6056</v>
+      </c>
+      <c r="C3009" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3010" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3010" t="s">
+        <v>6057</v>
+      </c>
+      <c r="B3010" t="s">
+        <v>6058</v>
+      </c>
+      <c r="C3010" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3011" t="s">
+        <v>6059</v>
+      </c>
+      <c r="B3011" t="s">
+        <v>6060</v>
+      </c>
+      <c r="C3011" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3012" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3012" t="s">
+        <v>6061</v>
+      </c>
+      <c r="B3012" t="s">
+        <v>6062</v>
+      </c>
+      <c r="C3012" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3013" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3013" t="s">
+        <v>6063</v>
+      </c>
+      <c r="B3013" t="s">
+        <v>6064</v>
+      </c>
+      <c r="C3013" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3014" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3014" t="s">
+        <v>6065</v>
+      </c>
+      <c r="B3014" t="s">
+        <v>6066</v>
+      </c>
+      <c r="C3014" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3015" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3015" t="s">
+        <v>6067</v>
+      </c>
+      <c r="B3015" t="s">
+        <v>6068</v>
+      </c>
+      <c r="C3015" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3016" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3016" t="s">
+        <v>6069</v>
+      </c>
+      <c r="B3016" t="s">
+        <v>6070</v>
+      </c>
+      <c r="C3016" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3017" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3017" t="s">
+        <v>6071</v>
+      </c>
+      <c r="B3017" t="s">
+        <v>6072</v>
+      </c>
+      <c r="C3017" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3018" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3018" t="s">
+        <v>6073</v>
+      </c>
+      <c r="B3018" t="s">
+        <v>6074</v>
+      </c>
+      <c r="C3018" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3019" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3019" t="s">
+        <v>6075</v>
+      </c>
+      <c r="B3019" t="s">
+        <v>6076</v>
+      </c>
+      <c r="C3019" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3020" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3020" t="s">
+        <v>6077</v>
+      </c>
+      <c r="B3020" t="s">
+        <v>6078</v>
+      </c>
+      <c r="C3020" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3021" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3021" t="s">
+        <v>6079</v>
+      </c>
+      <c r="B3021" t="s">
+        <v>6080</v>
+      </c>
+      <c r="C3021" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3022" t="s">
+        <v>6081</v>
+      </c>
+      <c r="B3022" t="s">
+        <v>6082</v>
+      </c>
+      <c r="C3022" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3023" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3023" t="s">
+        <v>6083</v>
+      </c>
+      <c r="B3023" t="s">
+        <v>6084</v>
+      </c>
+      <c r="C3023" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3024" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3024" t="s">
+        <v>6085</v>
+      </c>
+      <c r="B3024" t="s">
+        <v>6086</v>
+      </c>
+      <c r="C3024" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3025" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3025" t="s">
+        <v>6087</v>
+      </c>
+      <c r="B3025" t="s">
+        <v>6088</v>
+      </c>
+      <c r="C3025" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3026" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3026" t="s">
+        <v>6089</v>
+      </c>
+      <c r="B3026" t="s">
+        <v>6090</v>
+      </c>
+      <c r="C3026" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3027" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3027" t="s">
+        <v>6091</v>
+      </c>
+      <c r="B3027" t="s">
+        <v>6092</v>
+      </c>
+      <c r="C3027" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3028" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3028" t="s">
+        <v>6093</v>
+      </c>
+      <c r="B3028" t="s">
+        <v>6094</v>
+      </c>
+      <c r="C3028" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3029" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3029" t="s">
+        <v>6095</v>
+      </c>
+      <c r="B3029" t="s">
+        <v>6096</v>
+      </c>
+      <c r="C3029" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3030" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3030" t="s">
+        <v>6097</v>
+      </c>
+      <c r="B3030" t="s">
+        <v>6098</v>
+      </c>
+      <c r="C3030" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3031" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3031" t="s">
+        <v>6099</v>
+      </c>
+      <c r="B3031" t="s">
+        <v>6100</v>
+      </c>
+      <c r="C3031" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3032" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3032" t="s">
+        <v>6101</v>
+      </c>
+      <c r="B3032" t="s">
+        <v>6102</v>
+      </c>
+      <c r="C3032" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3033" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3033" t="s">
+        <v>6103</v>
+      </c>
+      <c r="B3033" t="s">
+        <v>6104</v>
+      </c>
+      <c r="C3033" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3034" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3034" t="s">
+        <v>6105</v>
+      </c>
+      <c r="B3034" t="s">
+        <v>6106</v>
+      </c>
+      <c r="C3034" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3035" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3035" t="s">
+        <v>6107</v>
+      </c>
+      <c r="B3035" t="s">
+        <v>6108</v>
+      </c>
+      <c r="C3035" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3036" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3036" t="s">
+        <v>6109</v>
+      </c>
+      <c r="B3036" t="s">
+        <v>6110</v>
+      </c>
+      <c r="C3036" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3037" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3037" t="s">
+        <v>6111</v>
+      </c>
+      <c r="B3037" t="s">
+        <v>6112</v>
+      </c>
+      <c r="C3037" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3038" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3038" t="s">
+        <v>6113</v>
+      </c>
+      <c r="B3038" t="s">
+        <v>6114</v>
+      </c>
+      <c r="C3038" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3039" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3039" t="s">
+        <v>6115</v>
+      </c>
+      <c r="B3039" t="s">
+        <v>6116</v>
+      </c>
+      <c r="C3039" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3040" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3040" t="s">
+        <v>6117</v>
+      </c>
+      <c r="B3040" t="s">
+        <v>6118</v>
+      </c>
+      <c r="C3040" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3041" t="s">
+        <v>6119</v>
+      </c>
+      <c r="B3041" t="s">
+        <v>6120</v>
+      </c>
+      <c r="C3041" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3042" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3042" t="s">
+        <v>6121</v>
+      </c>
+      <c r="B3042" t="s">
+        <v>6122</v>
+      </c>
+      <c r="C3042" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3043" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3043" t="s">
+        <v>6123</v>
+      </c>
+      <c r="B3043" t="s">
+        <v>6124</v>
+      </c>
+      <c r="C3043" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3044" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3044" t="s">
+        <v>6125</v>
+      </c>
+      <c r="B3044" t="s">
+        <v>6126</v>
+      </c>
+      <c r="C3044" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3045" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3045" t="s">
+        <v>6127</v>
+      </c>
+      <c r="B3045" t="s">
+        <v>6128</v>
+      </c>
+      <c r="C3045" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3046" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3046" t="s">
+        <v>6129</v>
+      </c>
+      <c r="B3046" t="s">
+        <v>6130</v>
+      </c>
+      <c r="C3046" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3047" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3047" t="s">
+        <v>6131</v>
+      </c>
+      <c r="B3047" t="s">
+        <v>6132</v>
+      </c>
+      <c r="C3047" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3048" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3048" t="s">
+        <v>6133</v>
+      </c>
+      <c r="B3048" t="s">
+        <v>6134</v>
+      </c>
+      <c r="C3048" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3049" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3049" t="s">
+        <v>6135</v>
+      </c>
+      <c r="B3049" t="s">
+        <v>6136</v>
+      </c>
+      <c r="C3049" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3050" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3050" t="s">
+        <v>6137</v>
+      </c>
+      <c r="B3050" t="s">
+        <v>6138</v>
+      </c>
+      <c r="C3050" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3051" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3051" t="s">
+        <v>6139</v>
+      </c>
+      <c r="B3051" t="s">
+        <v>6140</v>
+      </c>
+      <c r="C3051" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3052" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3052" t="s">
+        <v>6141</v>
+      </c>
+      <c r="B3052" t="s">
+        <v>6142</v>
+      </c>
+      <c r="C3052" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3053" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3053" t="s">
+        <v>6143</v>
+      </c>
+      <c r="B3053" t="s">
+        <v>6144</v>
+      </c>
+      <c r="C3053" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3054" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3054" t="s">
+        <v>6145</v>
+      </c>
+      <c r="B3054" t="s">
+        <v>6146</v>
+      </c>
+      <c r="C3054" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3055" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3055" t="s">
+        <v>6147</v>
+      </c>
+      <c r="B3055" t="s">
+        <v>6148</v>
+      </c>
+      <c r="C3055" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3056" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3056" t="s">
+        <v>6149</v>
+      </c>
+      <c r="B3056" t="s">
+        <v>6150</v>
+      </c>
+      <c r="C3056" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3057" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3057" t="s">
+        <v>6151</v>
+      </c>
+      <c r="B3057" t="s">
+        <v>6152</v>
+      </c>
+      <c r="C3057" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3058" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3058" t="s">
+        <v>6153</v>
+      </c>
+      <c r="B3058" t="s">
+        <v>6154</v>
+      </c>
+      <c r="C3058" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3059" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3059" t="s">
+        <v>6155</v>
+      </c>
+      <c r="B3059" t="s">
+        <v>6156</v>
+      </c>
+      <c r="C3059" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3060" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3060" t="s">
+        <v>6157</v>
+      </c>
+      <c r="B3060" t="s">
+        <v>6158</v>
+      </c>
+      <c r="C3060" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3061" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3061" t="s">
+        <v>6159</v>
+      </c>
+      <c r="B3061" t="s">
+        <v>6160</v>
+      </c>
+      <c r="C3061" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3062" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3062" t="s">
+        <v>6161</v>
+      </c>
+      <c r="B3062" t="s">
+        <v>6162</v>
+      </c>
+      <c r="C3062" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3063" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3063" t="s">
+        <v>6163</v>
+      </c>
+      <c r="B3063" t="s">
+        <v>6164</v>
+      </c>
+      <c r="C3063" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3064" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3064" t="s">
+        <v>6165</v>
+      </c>
+      <c r="B3064" t="s">
+        <v>6166</v>
+      </c>
+      <c r="C3064" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3065" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3065" t="s">
+        <v>6167</v>
+      </c>
+      <c r="B3065" t="s">
+        <v>6168</v>
+      </c>
+      <c r="C3065" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3066" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3066" t="s">
+        <v>6169</v>
+      </c>
+      <c r="B3066" t="s">
+        <v>6170</v>
+      </c>
+      <c r="C3066" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3067" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3067" t="s">
+        <v>6171</v>
+      </c>
+      <c r="B3067" t="s">
+        <v>6172</v>
+      </c>
+      <c r="C3067" t="s">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="3068" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3068" t="s">
+        <v>6173</v>
+      </c>
+      <c r="B3068" t="s">
+        <v>6174</v>
+      </c>
+      <c r="C3068" t="s">
+        <v>5998</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>
-    <row r="4890" spans="7:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4890" ht="26.25" customHeight="1" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G4890" s="7"/>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
@@ -46676,10 +48183,8 @@
       <c r="B11478" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:B2979">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B2979"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="3450" yWindow="3660" windowWidth="21600" windowHeight="11385"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7698" uniqueCount="6175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7794" uniqueCount="6240">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -18542,6 +18542,201 @@
   </si>
   <si>
     <t>Наволочка страйп-сатин 50х70 - 130 - Hotel Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001601265</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 90х200х30 - "Кетеван" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>06-04-2026</t>
+  </si>
+  <si>
+    <t>4681001601258</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 135 - Кувертюр 1х1</t>
+  </si>
+  <si>
+    <t>4681001601241</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001601234</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Тенерифе 1х1</t>
+  </si>
+  <si>
+    <t>4681001601227</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001601210</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Макена"</t>
+  </si>
+  <si>
+    <t>4681001601203</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - "Элиот" 1х1</t>
+  </si>
+  <si>
+    <t>4681001601197</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001601180</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 130 - Сланцево-серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001601173</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - М - Аргентум</t>
+  </si>
+  <si>
+    <t>4681001601166</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Дасти Роуз"</t>
+  </si>
+  <si>
+    <t>4681001601159</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Черный блеск наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601142</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин семейное - "Далиян"</t>
+  </si>
+  <si>
+    <t>4681001601135</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил семейное - "Хризоколла"</t>
+  </si>
+  <si>
+    <t>4681001601128</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - "Крылатые сны"</t>
+  </si>
+  <si>
+    <t>4681001601111</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - "Крылатые сны" Универсал</t>
+  </si>
+  <si>
+    <t>4681001601104</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4681001601098</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - М - "История сов"</t>
+  </si>
+  <si>
+    <t>4681001601081</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Морбидецца</t>
+  </si>
+  <si>
+    <t>4681001601074</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - М - Морбидецца</t>
+  </si>
+  <si>
+    <t>4681001601067</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 200х220 - 110 - Озеро Цветов</t>
+  </si>
+  <si>
+    <t>4681001601050</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 140 - Лагуна 1х1</t>
+  </si>
+  <si>
+    <t>4681001601043</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё поплин 1,5 спальное - 115 - Крольчата А+В</t>
+  </si>
+  <si>
+    <t>4681001601036</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 60х60 - 120 - Хадусамат</t>
+  </si>
+  <si>
+    <t>4681001601029</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 60х60 - 125 - Дом Периньон</t>
+  </si>
+  <si>
+    <t>4681001601012</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра Евро-макси резинка 180х200х30 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001601005</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное - "Лесная Мелодия"</t>
+  </si>
+  <si>
+    <t>4681001600992</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001600985</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Петроль</t>
+  </si>
+  <si>
+    <t>4681001600978</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 40х40 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001600961</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х30 - 125 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001600954</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - М - Грей блес</t>
   </si>
 </sst>
 </file>
@@ -18625,18 +18820,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -18912,11 +19096,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:P11478"/>
+  <dimension ref="A1:P11478"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
-    <col min="2" max="2" width="177" customWidth="1"/>
+    <col min="2" max="2" width="124.5703125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -48162,29 +48346,377 @@
         <v>5998</v>
       </c>
     </row>
+    <row r="3069" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3069" t="s">
+        <v>6175</v>
+      </c>
+      <c r="B3069" t="s">
+        <v>6176</v>
+      </c>
+      <c r="C3069" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3070" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3070" t="s">
+        <v>6178</v>
+      </c>
+      <c r="B3070" t="s">
+        <v>6179</v>
+      </c>
+      <c r="C3070" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3071" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3071" t="s">
+        <v>6180</v>
+      </c>
+      <c r="B3071" t="s">
+        <v>6181</v>
+      </c>
+      <c r="C3071" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3072" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3072" t="s">
+        <v>6182</v>
+      </c>
+      <c r="B3072" t="s">
+        <v>6183</v>
+      </c>
+      <c r="C3072" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3073" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3073" t="s">
+        <v>6184</v>
+      </c>
+      <c r="B3073" t="s">
+        <v>6185</v>
+      </c>
+      <c r="C3073" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3074" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3074" t="s">
+        <v>6186</v>
+      </c>
+      <c r="B3074" t="s">
+        <v>6187</v>
+      </c>
+      <c r="C3074" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3075" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3075" t="s">
+        <v>6188</v>
+      </c>
+      <c r="B3075" t="s">
+        <v>6189</v>
+      </c>
+      <c r="C3075" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3076" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3076" t="s">
+        <v>6190</v>
+      </c>
+      <c r="B3076" t="s">
+        <v>6191</v>
+      </c>
+      <c r="C3076" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3077" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3077" t="s">
+        <v>6192</v>
+      </c>
+      <c r="B3077" t="s">
+        <v>6193</v>
+      </c>
+      <c r="C3077" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3078" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3078" t="s">
+        <v>6194</v>
+      </c>
+      <c r="B3078" t="s">
+        <v>6195</v>
+      </c>
+      <c r="C3078" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3079" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3079" t="s">
+        <v>6196</v>
+      </c>
+      <c r="B3079" t="s">
+        <v>6197</v>
+      </c>
+      <c r="C3079" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3080" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3080" t="s">
+        <v>6198</v>
+      </c>
+      <c r="B3080" t="s">
+        <v>6199</v>
+      </c>
+      <c r="C3080" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3081" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3081" t="s">
+        <v>6200</v>
+      </c>
+      <c r="B3081" t="s">
+        <v>6201</v>
+      </c>
+      <c r="C3081" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3082" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3082" t="s">
+        <v>6202</v>
+      </c>
+      <c r="B3082" t="s">
+        <v>6203</v>
+      </c>
+      <c r="C3082" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3083" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3083" t="s">
+        <v>6204</v>
+      </c>
+      <c r="B3083" t="s">
+        <v>6205</v>
+      </c>
+      <c r="C3083" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3084" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3084" t="s">
+        <v>6206</v>
+      </c>
+      <c r="B3084" t="s">
+        <v>6207</v>
+      </c>
+      <c r="C3084" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3085" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3085" t="s">
+        <v>6208</v>
+      </c>
+      <c r="B3085" t="s">
+        <v>6209</v>
+      </c>
+      <c r="C3085" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3086" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3086" t="s">
+        <v>6210</v>
+      </c>
+      <c r="B3086" t="s">
+        <v>6211</v>
+      </c>
+      <c r="C3086" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3087" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3087" t="s">
+        <v>6212</v>
+      </c>
+      <c r="B3087" t="s">
+        <v>6213</v>
+      </c>
+      <c r="C3087" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3088" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3088" t="s">
+        <v>6214</v>
+      </c>
+      <c r="B3088" t="s">
+        <v>6215</v>
+      </c>
+      <c r="C3088" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3089" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3089" t="s">
+        <v>6216</v>
+      </c>
+      <c r="B3089" t="s">
+        <v>6217</v>
+      </c>
+      <c r="C3089" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3090" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3090" t="s">
+        <v>6218</v>
+      </c>
+      <c r="B3090" t="s">
+        <v>6219</v>
+      </c>
+      <c r="C3090" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3091" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3091" t="s">
+        <v>6220</v>
+      </c>
+      <c r="B3091" t="s">
+        <v>6221</v>
+      </c>
+      <c r="C3091" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3092" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3092" t="s">
+        <v>6222</v>
+      </c>
+      <c r="B3092" t="s">
+        <v>6223</v>
+      </c>
+      <c r="C3092" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3093" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3093" t="s">
+        <v>6224</v>
+      </c>
+      <c r="B3093" t="s">
+        <v>6225</v>
+      </c>
+      <c r="C3093" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3094" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3094" t="s">
+        <v>6226</v>
+      </c>
+      <c r="B3094" t="s">
+        <v>6227</v>
+      </c>
+      <c r="C3094" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3095" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3095" t="s">
+        <v>6228</v>
+      </c>
+      <c r="B3095" t="s">
+        <v>6229</v>
+      </c>
+      <c r="C3095" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3096" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3096" t="s">
+        <v>6230</v>
+      </c>
+      <c r="B3096" t="s">
+        <v>6231</v>
+      </c>
+      <c r="C3096" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3097" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3097" t="s">
+        <v>6232</v>
+      </c>
+      <c r="B3097" t="s">
+        <v>6233</v>
+      </c>
+      <c r="C3097" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3098" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3098" t="s">
+        <v>6234</v>
+      </c>
+      <c r="B3098" t="s">
+        <v>6235</v>
+      </c>
+      <c r="C3098" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3099" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3099" t="s">
+        <v>6236</v>
+      </c>
+      <c r="B3099" t="s">
+        <v>6237</v>
+      </c>
+      <c r="C3099" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="3100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3100" t="s">
+        <v>6238</v>
+      </c>
+      <c r="B3100" t="s">
+        <v>6239</v>
+      </c>
+      <c r="C3100" t="s">
+        <v>6177</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>
-    <row r="4890" ht="26.25" customHeight="1" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="4890" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G4890" s="7"/>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>
-    <row r="7776" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10818" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10818" s="7"/>
     </row>
-    <row r="10905" ht="128.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11478" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11478" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:B2979"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7794" uniqueCount="6240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7878" uniqueCount="6297">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -18737,6 +18737,177 @@
   </si>
   <si>
     <t>Пододеяльник тенсель 220х240 - М - Грей блес</t>
+  </si>
+  <si>
+    <t>4681001601548</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 200х200 - "Смоки"</t>
+  </si>
+  <si>
+    <t>07-04-2026</t>
+  </si>
+  <si>
+    <t>4681001601531</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс Евро-макси резинка 180х200х30 - "Кремневый серый" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601524</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс Евро-макси резинка 180х200х30 - "Лазурный бриз" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601517</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - 140 - Тенерифе 1х1</t>
+  </si>
+  <si>
+    <t>4681001601500</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 240х260 - М - Премиум ТС 320 Вишенка</t>
+  </si>
+  <si>
+    <t>4681001601494</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное Евро простыня - Дымчатый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601487</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х200 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001601470</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра 1,5 спальное - "Марисоль"</t>
+  </si>
+  <si>
+    <t>4681001601463</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001601456</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая 150 х 220 - М - Мулетон Полиэстер</t>
+  </si>
+  <si>
+    <t>4681001601449</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х40 - "Корги-пати"</t>
+  </si>
+  <si>
+    <t>4681001601432</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное Евро простыня - "Линнея" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601425</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 220х240 - М - 130 - Сланцево-серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001601418</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4681001601401</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 180х200х40 - "Белый Оникс"</t>
+  </si>
+  <si>
+    <t>4681001601395</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 70х70 - "Белый Оникс"</t>
+  </si>
+  <si>
+    <t>4681001601388</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин браш 175х215 - "Белый Оникс"</t>
+  </si>
+  <si>
+    <t>4681001601371</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 50х70 - "Белый Оникс"</t>
+  </si>
+  <si>
+    <t>4681001601364</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - "История сов"</t>
+  </si>
+  <si>
+    <t>4681001601357</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - "Твист"</t>
+  </si>
+  <si>
+    <t>4681001601340</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - "Милкшейк"</t>
+  </si>
+  <si>
+    <t>4681001601333</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное Евро простыня - 140 - Сияющая бирюза</t>
+  </si>
+  <si>
+    <t>4681001601326</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 142 ГОСТ - Оранжевый</t>
+  </si>
+  <si>
+    <t>4681001601319</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 230х230х20 - "Нуга"</t>
+  </si>
+  <si>
+    <t>4681001601302</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 230х230х20 - "Лунь" 1х1</t>
+  </si>
+  <si>
+    <t>4681001601296</t>
+  </si>
+  <si>
+    <t>Простыня жаккард 220х240 - Солнечное кружево</t>
+  </si>
+  <si>
+    <t>4681001601289</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 200х200 - М - Солнечное кружево</t>
+  </si>
+  <si>
+    <t>4681001601272</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 50х70 - Солнечное кружево</t>
   </si>
 </sst>
 </file>
@@ -48698,6 +48869,314 @@
         <v>6177</v>
       </c>
     </row>
+    <row r="3101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3101" t="s">
+        <v>6240</v>
+      </c>
+      <c r="B3101" t="s">
+        <v>6241</v>
+      </c>
+      <c r="C3101" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3102" t="s">
+        <v>6243</v>
+      </c>
+      <c r="B3102" t="s">
+        <v>6244</v>
+      </c>
+      <c r="C3102" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3103" t="s">
+        <v>6245</v>
+      </c>
+      <c r="B3103" t="s">
+        <v>6246</v>
+      </c>
+      <c r="C3103" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3104" t="s">
+        <v>6247</v>
+      </c>
+      <c r="B3104" t="s">
+        <v>6248</v>
+      </c>
+      <c r="C3104" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3105" t="s">
+        <v>6249</v>
+      </c>
+      <c r="B3105" t="s">
+        <v>6250</v>
+      </c>
+      <c r="C3105" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3106" t="s">
+        <v>6251</v>
+      </c>
+      <c r="B3106" t="s">
+        <v>6252</v>
+      </c>
+      <c r="C3106" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3107" t="s">
+        <v>6253</v>
+      </c>
+      <c r="B3107" t="s">
+        <v>6254</v>
+      </c>
+      <c r="C3107" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3108" t="s">
+        <v>6255</v>
+      </c>
+      <c r="B3108" t="s">
+        <v>6256</v>
+      </c>
+      <c r="C3108" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3109" t="s">
+        <v>6257</v>
+      </c>
+      <c r="B3109" t="s">
+        <v>6258</v>
+      </c>
+      <c r="C3109" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3110" t="s">
+        <v>6259</v>
+      </c>
+      <c r="B3110" t="s">
+        <v>6260</v>
+      </c>
+      <c r="C3110" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3111" t="s">
+        <v>6261</v>
+      </c>
+      <c r="B3111" t="s">
+        <v>6262</v>
+      </c>
+      <c r="C3111" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3112" t="s">
+        <v>6263</v>
+      </c>
+      <c r="B3112" t="s">
+        <v>6264</v>
+      </c>
+      <c r="C3112" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3113" t="s">
+        <v>6265</v>
+      </c>
+      <c r="B3113" t="s">
+        <v>6266</v>
+      </c>
+      <c r="C3113" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3114" t="s">
+        <v>6267</v>
+      </c>
+      <c r="B3114" t="s">
+        <v>6268</v>
+      </c>
+      <c r="C3114" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3115" t="s">
+        <v>6269</v>
+      </c>
+      <c r="B3115" t="s">
+        <v>6270</v>
+      </c>
+      <c r="C3115" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3116" t="s">
+        <v>6271</v>
+      </c>
+      <c r="B3116" t="s">
+        <v>6272</v>
+      </c>
+      <c r="C3116" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3117" t="s">
+        <v>6273</v>
+      </c>
+      <c r="B3117" t="s">
+        <v>6274</v>
+      </c>
+      <c r="C3117" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3118" t="s">
+        <v>6275</v>
+      </c>
+      <c r="B3118" t="s">
+        <v>6276</v>
+      </c>
+      <c r="C3118" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3119" t="s">
+        <v>6277</v>
+      </c>
+      <c r="B3119" t="s">
+        <v>6278</v>
+      </c>
+      <c r="C3119" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3120" t="s">
+        <v>6279</v>
+      </c>
+      <c r="B3120" t="s">
+        <v>6280</v>
+      </c>
+      <c r="C3120" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3121" t="s">
+        <v>6281</v>
+      </c>
+      <c r="B3121" t="s">
+        <v>6282</v>
+      </c>
+      <c r="C3121" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3122" t="s">
+        <v>6283</v>
+      </c>
+      <c r="B3122" t="s">
+        <v>6284</v>
+      </c>
+      <c r="C3122" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3123" t="s">
+        <v>6285</v>
+      </c>
+      <c r="B3123" t="s">
+        <v>6286</v>
+      </c>
+      <c r="C3123" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3124" t="s">
+        <v>6287</v>
+      </c>
+      <c r="B3124" t="s">
+        <v>6288</v>
+      </c>
+      <c r="C3124" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3125" t="s">
+        <v>6289</v>
+      </c>
+      <c r="B3125" t="s">
+        <v>6290</v>
+      </c>
+      <c r="C3125" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3126" t="s">
+        <v>6291</v>
+      </c>
+      <c r="B3126" t="s">
+        <v>6292</v>
+      </c>
+      <c r="C3126" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3127" t="s">
+        <v>6293</v>
+      </c>
+      <c r="B3127" t="s">
+        <v>6294</v>
+      </c>
+      <c r="C3127" t="s">
+        <v>6242</v>
+      </c>
+    </row>
+    <row r="3128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3128" t="s">
+        <v>6295</v>
+      </c>
+      <c r="B3128" t="s">
+        <v>6296</v>
+      </c>
+      <c r="C3128" t="s">
+        <v>6242</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7878" uniqueCount="6297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7989" uniqueCount="6372">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -18908,6 +18908,231 @@
   </si>
   <si>
     <t>Наволочка жаккард 50х70 - Солнечное кружево</t>
+  </si>
+  <si>
+    <t>4681001601913</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 120х200х30 - "Кетеван" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>08-04-2026</t>
+  </si>
+  <si>
+    <t>4681001601906</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Сердечный Вихрь"</t>
+  </si>
+  <si>
+    <t>4681001601890</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4681001601883</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 1,5 спальное резинка 120х200х30 - "Ванильный раф" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601876</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Вечерний песок</t>
+  </si>
+  <si>
+    <t>4681001601869</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х50 - 140 - Тенерифе 1х1</t>
+  </si>
+  <si>
+    <t>4681001601852</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - 80 - Витражи</t>
+  </si>
+  <si>
+    <t>4681001601845</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 2 спальное резинка 160х200х30 - "Страстный гранат" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601838</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - М - Льняной</t>
+  </si>
+  <si>
+    <t>4681001601821</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - М - Маренго</t>
+  </si>
+  <si>
+    <t>4681001601814</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4681001601807</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 140х200х30 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001601791</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Льняной</t>
+  </si>
+  <si>
+    <t>4681001601784</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4681001601777</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 240х260 - "Асуль"</t>
+  </si>
+  <si>
+    <t>4681001601760</t>
+  </si>
+  <si>
+    <t>Простыня из тенселя 180 х 220 - М - Речной жемчуг 1х1</t>
+  </si>
+  <si>
+    <t>4681001601753</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - "Песочная роза"</t>
+  </si>
+  <si>
+    <t>4681001601746</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 300х300 - Бертолеция</t>
+  </si>
+  <si>
+    <t>4681001601739</t>
+  </si>
+  <si>
+    <t>Наволочка микрофибра 60х60 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4681001601722</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х20 - 125 - "Капучино" 1х1</t>
+  </si>
+  <si>
+    <t>4681001601715</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Казимира"</t>
+  </si>
+  <si>
+    <t>4681001601708</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 2 спальное - "Нева" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601692</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 180х200х40 - "Бирюзовый Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001601685</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 180х200х40 - "Белый Этюд"</t>
+  </si>
+  <si>
+    <t>4681001601678</t>
+  </si>
+  <si>
+    <t>Простыня жатка 220х240 - "Графитовый Зигзаг"</t>
+  </si>
+  <si>
+    <t>4681001601661</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - Черный блеск наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601654</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 180х200х40 - "Розанна"</t>
+  </si>
+  <si>
+    <t>4681001601647</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4681001601630</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное резинка 160х200х20 - "Оллорины"</t>
+  </si>
+  <si>
+    <t>4681001601623</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 90х200х30 - "Лесная Мелодия"</t>
+  </si>
+  <si>
+    <t>4681001601616</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 2 спальное резинка 160х200х20 - "Нева" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601609</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - М - ГОСТ 142 - Хитрые Зайчата на желтом</t>
+  </si>
+  <si>
+    <t>4681001601593</t>
+  </si>
+  <si>
+    <t>Наволочка из тенселя 70 х 70 - М - 60S Сливочный</t>
+  </si>
+  <si>
+    <t>4681001601586</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 175х215 - "Золти"</t>
+  </si>
+  <si>
+    <t>4681001601579</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Олуфими"</t>
+  </si>
+  <si>
+    <t>4681001601562</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 80х200х30 - "Серебро Облаков"</t>
+  </si>
+  <si>
+    <t>4681001601555</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 175х215 - М - 135 - Пармелия 1х1</t>
   </si>
 </sst>
 </file>
@@ -49177,6 +49402,413 @@
         <v>6242</v>
       </c>
     </row>
+    <row r="3129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3129" t="s">
+        <v>6297</v>
+      </c>
+      <c r="B3129" t="s">
+        <v>6298</v>
+      </c>
+      <c r="C3129" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3130" t="s">
+        <v>6300</v>
+      </c>
+      <c r="B3130" t="s">
+        <v>6301</v>
+      </c>
+      <c r="C3130" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3131" t="s">
+        <v>6302</v>
+      </c>
+      <c r="B3131" t="s">
+        <v>6303</v>
+      </c>
+      <c r="C3131" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3132" t="s">
+        <v>6304</v>
+      </c>
+      <c r="B3132" t="s">
+        <v>6305</v>
+      </c>
+      <c r="C3132" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3133" t="s">
+        <v>6306</v>
+      </c>
+      <c r="B3133" t="s">
+        <v>6307</v>
+      </c>
+      <c r="C3133" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3134" t="s">
+        <v>6308</v>
+      </c>
+      <c r="B3134" t="s">
+        <v>6309</v>
+      </c>
+      <c r="C3134" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3135" t="s">
+        <v>6310</v>
+      </c>
+      <c r="B3135" t="s">
+        <v>6311</v>
+      </c>
+      <c r="C3135" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3136" t="s">
+        <v>6312</v>
+      </c>
+      <c r="B3136" t="s">
+        <v>6313</v>
+      </c>
+      <c r="C3136" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3137" t="s">
+        <v>6314</v>
+      </c>
+      <c r="B3137" t="s">
+        <v>6315</v>
+      </c>
+      <c r="C3137" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3138" t="s">
+        <v>6316</v>
+      </c>
+      <c r="B3138" t="s">
+        <v>6317</v>
+      </c>
+      <c r="C3138" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3139" t="s">
+        <v>6318</v>
+      </c>
+      <c r="B3139" t="s">
+        <v>6319</v>
+      </c>
+      <c r="C3139" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3140" t="s">
+        <v>6320</v>
+      </c>
+      <c r="B3140" t="s">
+        <v>6321</v>
+      </c>
+      <c r="C3140" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3141" t="s">
+        <v>6322</v>
+      </c>
+      <c r="B3141" t="s">
+        <v>6323</v>
+      </c>
+      <c r="C3141" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3142" t="s">
+        <v>6324</v>
+      </c>
+      <c r="B3142" t="s">
+        <v>6325</v>
+      </c>
+      <c r="C3142" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3143" t="s">
+        <v>6326</v>
+      </c>
+      <c r="B3143" t="s">
+        <v>6327</v>
+      </c>
+      <c r="C3143" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3144" t="s">
+        <v>6328</v>
+      </c>
+      <c r="B3144" t="s">
+        <v>6329</v>
+      </c>
+      <c r="C3144" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3145" t="s">
+        <v>6330</v>
+      </c>
+      <c r="B3145" t="s">
+        <v>6331</v>
+      </c>
+      <c r="C3145" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3146" t="s">
+        <v>6332</v>
+      </c>
+      <c r="B3146" t="s">
+        <v>6333</v>
+      </c>
+      <c r="C3146" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3147" t="s">
+        <v>6334</v>
+      </c>
+      <c r="B3147" t="s">
+        <v>6335</v>
+      </c>
+      <c r="C3147" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3148" t="s">
+        <v>6336</v>
+      </c>
+      <c r="B3148" t="s">
+        <v>6337</v>
+      </c>
+      <c r="C3148" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3149" t="s">
+        <v>6338</v>
+      </c>
+      <c r="B3149" t="s">
+        <v>6339</v>
+      </c>
+      <c r="C3149" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3150" t="s">
+        <v>6340</v>
+      </c>
+      <c r="B3150" t="s">
+        <v>6341</v>
+      </c>
+      <c r="C3150" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3151" t="s">
+        <v>6342</v>
+      </c>
+      <c r="B3151" t="s">
+        <v>6343</v>
+      </c>
+      <c r="C3151" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3152" t="s">
+        <v>6344</v>
+      </c>
+      <c r="B3152" t="s">
+        <v>6345</v>
+      </c>
+      <c r="C3152" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3153" t="s">
+        <v>6346</v>
+      </c>
+      <c r="B3153" t="s">
+        <v>6347</v>
+      </c>
+      <c r="C3153" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3154" t="s">
+        <v>6348</v>
+      </c>
+      <c r="B3154" t="s">
+        <v>6349</v>
+      </c>
+      <c r="C3154" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3155" t="s">
+        <v>6350</v>
+      </c>
+      <c r="B3155" t="s">
+        <v>6351</v>
+      </c>
+      <c r="C3155" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3156" t="s">
+        <v>6352</v>
+      </c>
+      <c r="B3156" t="s">
+        <v>6353</v>
+      </c>
+      <c r="C3156" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3157" t="s">
+        <v>6354</v>
+      </c>
+      <c r="B3157" t="s">
+        <v>6355</v>
+      </c>
+      <c r="C3157" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3158" t="s">
+        <v>6356</v>
+      </c>
+      <c r="B3158" t="s">
+        <v>6357</v>
+      </c>
+      <c r="C3158" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3159" t="s">
+        <v>6358</v>
+      </c>
+      <c r="B3159" t="s">
+        <v>6359</v>
+      </c>
+      <c r="C3159" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3160" t="s">
+        <v>6360</v>
+      </c>
+      <c r="B3160" t="s">
+        <v>6361</v>
+      </c>
+      <c r="C3160" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3161" t="s">
+        <v>6362</v>
+      </c>
+      <c r="B3161" t="s">
+        <v>6363</v>
+      </c>
+      <c r="C3161" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3162" t="s">
+        <v>6364</v>
+      </c>
+      <c r="B3162" t="s">
+        <v>6365</v>
+      </c>
+      <c r="C3162" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3163" t="s">
+        <v>6366</v>
+      </c>
+      <c r="B3163" t="s">
+        <v>6367</v>
+      </c>
+      <c r="C3163" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3164" t="s">
+        <v>6368</v>
+      </c>
+      <c r="B3164" t="s">
+        <v>6369</v>
+      </c>
+      <c r="C3164" t="s">
+        <v>6299</v>
+      </c>
+    </row>
+    <row r="3165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3165" t="s">
+        <v>6370</v>
+      </c>
+      <c r="B3165" t="s">
+        <v>6371</v>
+      </c>
+      <c r="C3165" t="s">
+        <v>6299</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7989" uniqueCount="6372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8133" uniqueCount="6469">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -19133,6 +19133,297 @@
   </si>
   <si>
     <t>Пододеяльник страйп-сатин 175х215 - М - 135 - Пармелия 1х1</t>
+  </si>
+  <si>
+    <t>4681001602347</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 70х70 - "Гуголету"</t>
+  </si>
+  <si>
+    <t>09-04-2026</t>
+  </si>
+  <si>
+    <t>4681001602330</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - М - Розариум А+В</t>
+  </si>
+  <si>
+    <t>4681001602323</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 150х200 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4681001602316</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное на резинке 120х200х30 - "Сливочный"</t>
+  </si>
+  <si>
+    <t>4681001602309</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - Нежно-розовый</t>
+  </si>
+  <si>
+    <t>4681001602293</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 280х280 - "Сахарная роза"</t>
+  </si>
+  <si>
+    <t>4681001602286</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 70х70 - 110 - Полнолуние</t>
+  </si>
+  <si>
+    <t>4681001602279</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё поплин 1,5 спальное - "Стильные девчонки" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602262</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 90х200х30 - 145 - Серая 1х1</t>
+  </si>
+  <si>
+    <t>4681001602255</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х20 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001602248</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 220х220х30 - 140 - Асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4681001602231</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - 125 - Куманика</t>
+  </si>
+  <si>
+    <t>4681001602224</t>
+  </si>
+  <si>
+    <t>Простыня сатин 150х220 - "Небесный глянцевая"</t>
+  </si>
+  <si>
+    <t>4681001602217</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Веселые Корги"</t>
+  </si>
+  <si>
+    <t>4681001602200</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Гималайские маки</t>
+  </si>
+  <si>
+    <t>4681001602194</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - "Манцель" 3х3</t>
+  </si>
+  <si>
+    <t>4681001602187</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 240х260 - 110 - Белоснежный луч</t>
+  </si>
+  <si>
+    <t>4681001602170</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное Евро простыня - "Лесная Мелодия" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602163</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 240х260 - Белый</t>
+  </si>
+  <si>
+    <t>4681001602156</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс 240х260 - Белый</t>
+  </si>
+  <si>
+    <t>4681001602149</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 240х260 - М - 120 - Снежинка</t>
+  </si>
+  <si>
+    <t>4681001602132</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 40х40 - Лайлак</t>
+  </si>
+  <si>
+    <t>4681001602125</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х40 - "Розовый Сад"</t>
+  </si>
+  <si>
+    <t>4681001602118</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное - "Самолётики" Универсал</t>
+  </si>
+  <si>
+    <t>4681001602101</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х30 - "Ягуар"</t>
+  </si>
+  <si>
+    <t>4681001602095</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро-макси - "Залив"</t>
+  </si>
+  <si>
+    <t>4681001602088</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Лесная Мелодия"</t>
+  </si>
+  <si>
+    <t>4681001602071</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Сиренево-розовый"</t>
+  </si>
+  <si>
+    <t>4681001602064</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4681001602057</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Мелиссит"</t>
+  </si>
+  <si>
+    <t>4681001602040</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Белава"</t>
+  </si>
+  <si>
+    <t>4681001602033</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4681001602026</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 1,5 спальное резинка 120х200х30 - "Страстный гранат" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602019</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 260х260 - "Шторм"</t>
+  </si>
+  <si>
+    <t>4681001602002</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>4681001601999</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 200х200х30 - "Имани"</t>
+  </si>
+  <si>
+    <t>4681001601982</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 200х200х20 - "Легкий роман"</t>
+  </si>
+  <si>
+    <t>4681001601975</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 70х70 - Кремовый бархат</t>
+  </si>
+  <si>
+    <t>4681001601968</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс резинка 200х220х30 - "Ванильный раф"</t>
+  </si>
+  <si>
+    <t>4681001601951</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное Евро простыня - 142 - Белое</t>
+  </si>
+  <si>
+    <t>4681001601944</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 90х200х30 - Дзета Ориона</t>
+  </si>
+  <si>
+    <t>4681001601937</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - 130 - "Дивуар" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001601920</t>
+  </si>
+  <si>
+    <t>Простыня из тенселя 300 х 300 - М - 60S 4393 Темно-серый</t>
+  </si>
+  <si>
+    <t>4681001602392</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 120х200х30 - 130 - "Дивуар" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602385</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - М - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001602378</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001602361</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001602354</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 135 - Углерод 1х1</t>
   </si>
 </sst>
 </file>
@@ -49809,6 +50100,534 @@
         <v>6299</v>
       </c>
     </row>
+    <row r="3166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3166" t="s">
+        <v>6372</v>
+      </c>
+      <c r="B3166" t="s">
+        <v>6373</v>
+      </c>
+      <c r="C3166" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3167" t="s">
+        <v>6375</v>
+      </c>
+      <c r="B3167" t="s">
+        <v>6376</v>
+      </c>
+      <c r="C3167" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3168" t="s">
+        <v>6377</v>
+      </c>
+      <c r="B3168" t="s">
+        <v>6378</v>
+      </c>
+      <c r="C3168" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3169" t="s">
+        <v>6379</v>
+      </c>
+      <c r="B3169" t="s">
+        <v>6380</v>
+      </c>
+      <c r="C3169" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3170" t="s">
+        <v>6381</v>
+      </c>
+      <c r="B3170" t="s">
+        <v>6382</v>
+      </c>
+      <c r="C3170" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3171" t="s">
+        <v>6383</v>
+      </c>
+      <c r="B3171" t="s">
+        <v>6384</v>
+      </c>
+      <c r="C3171" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3172" t="s">
+        <v>6385</v>
+      </c>
+      <c r="B3172" t="s">
+        <v>6386</v>
+      </c>
+      <c r="C3172" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3173" t="s">
+        <v>6387</v>
+      </c>
+      <c r="B3173" t="s">
+        <v>6388</v>
+      </c>
+      <c r="C3173" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3174" t="s">
+        <v>6389</v>
+      </c>
+      <c r="B3174" t="s">
+        <v>6390</v>
+      </c>
+      <c r="C3174" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3175" t="s">
+        <v>6391</v>
+      </c>
+      <c r="B3175" t="s">
+        <v>6392</v>
+      </c>
+      <c r="C3175" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3176" t="s">
+        <v>6393</v>
+      </c>
+      <c r="B3176" t="s">
+        <v>6394</v>
+      </c>
+      <c r="C3176" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3177" t="s">
+        <v>6395</v>
+      </c>
+      <c r="B3177" t="s">
+        <v>6396</v>
+      </c>
+      <c r="C3177" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3178" t="s">
+        <v>6397</v>
+      </c>
+      <c r="B3178" t="s">
+        <v>6398</v>
+      </c>
+      <c r="C3178" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3179" t="s">
+        <v>6399</v>
+      </c>
+      <c r="B3179" t="s">
+        <v>6400</v>
+      </c>
+      <c r="C3179" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3180" t="s">
+        <v>6401</v>
+      </c>
+      <c r="B3180" t="s">
+        <v>6402</v>
+      </c>
+      <c r="C3180" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3181" t="s">
+        <v>6403</v>
+      </c>
+      <c r="B3181" t="s">
+        <v>6404</v>
+      </c>
+      <c r="C3181" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3182" t="s">
+        <v>6405</v>
+      </c>
+      <c r="B3182" t="s">
+        <v>6406</v>
+      </c>
+      <c r="C3182" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3183" t="s">
+        <v>6407</v>
+      </c>
+      <c r="B3183" t="s">
+        <v>6408</v>
+      </c>
+      <c r="C3183" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3184" t="s">
+        <v>6409</v>
+      </c>
+      <c r="B3184" t="s">
+        <v>6410</v>
+      </c>
+      <c r="C3184" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3185" t="s">
+        <v>6411</v>
+      </c>
+      <c r="B3185" t="s">
+        <v>6412</v>
+      </c>
+      <c r="C3185" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3186" t="s">
+        <v>6413</v>
+      </c>
+      <c r="B3186" t="s">
+        <v>6414</v>
+      </c>
+      <c r="C3186" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3187" t="s">
+        <v>6415</v>
+      </c>
+      <c r="B3187" t="s">
+        <v>6416</v>
+      </c>
+      <c r="C3187" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3188" t="s">
+        <v>6417</v>
+      </c>
+      <c r="B3188" t="s">
+        <v>6418</v>
+      </c>
+      <c r="C3188" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3189" t="s">
+        <v>6419</v>
+      </c>
+      <c r="B3189" t="s">
+        <v>6420</v>
+      </c>
+      <c r="C3189" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3190" t="s">
+        <v>6421</v>
+      </c>
+      <c r="B3190" t="s">
+        <v>6422</v>
+      </c>
+      <c r="C3190" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3191" t="s">
+        <v>6423</v>
+      </c>
+      <c r="B3191" t="s">
+        <v>6424</v>
+      </c>
+      <c r="C3191" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3192" t="s">
+        <v>6425</v>
+      </c>
+      <c r="B3192" t="s">
+        <v>6426</v>
+      </c>
+      <c r="C3192" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3193" t="s">
+        <v>6427</v>
+      </c>
+      <c r="B3193" t="s">
+        <v>6428</v>
+      </c>
+      <c r="C3193" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3194" t="s">
+        <v>6429</v>
+      </c>
+      <c r="B3194" t="s">
+        <v>6430</v>
+      </c>
+      <c r="C3194" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3195" t="s">
+        <v>6431</v>
+      </c>
+      <c r="B3195" t="s">
+        <v>6432</v>
+      </c>
+      <c r="C3195" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3196" t="s">
+        <v>6433</v>
+      </c>
+      <c r="B3196" t="s">
+        <v>6434</v>
+      </c>
+      <c r="C3196" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3197" t="s">
+        <v>6435</v>
+      </c>
+      <c r="B3197" t="s">
+        <v>6436</v>
+      </c>
+      <c r="C3197" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3198" t="s">
+        <v>6437</v>
+      </c>
+      <c r="B3198" t="s">
+        <v>6438</v>
+      </c>
+      <c r="C3198" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3199" t="s">
+        <v>6439</v>
+      </c>
+      <c r="B3199" t="s">
+        <v>6440</v>
+      </c>
+      <c r="C3199" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3200" t="s">
+        <v>6441</v>
+      </c>
+      <c r="B3200" t="s">
+        <v>6442</v>
+      </c>
+      <c r="C3200" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3201" t="s">
+        <v>6443</v>
+      </c>
+      <c r="B3201" t="s">
+        <v>6444</v>
+      </c>
+      <c r="C3201" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3202" t="s">
+        <v>6445</v>
+      </c>
+      <c r="B3202" t="s">
+        <v>6446</v>
+      </c>
+      <c r="C3202" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3203" t="s">
+        <v>6447</v>
+      </c>
+      <c r="B3203" t="s">
+        <v>6448</v>
+      </c>
+      <c r="C3203" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3204" t="s">
+        <v>6449</v>
+      </c>
+      <c r="B3204" t="s">
+        <v>6450</v>
+      </c>
+      <c r="C3204" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3205" t="s">
+        <v>6451</v>
+      </c>
+      <c r="B3205" t="s">
+        <v>6452</v>
+      </c>
+      <c r="C3205" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3206" t="s">
+        <v>6453</v>
+      </c>
+      <c r="B3206" t="s">
+        <v>6454</v>
+      </c>
+      <c r="C3206" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3207" t="s">
+        <v>6455</v>
+      </c>
+      <c r="B3207" t="s">
+        <v>6456</v>
+      </c>
+      <c r="C3207" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3208" t="s">
+        <v>6457</v>
+      </c>
+      <c r="B3208" t="s">
+        <v>6458</v>
+      </c>
+      <c r="C3208" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3209" t="s">
+        <v>6459</v>
+      </c>
+      <c r="B3209" t="s">
+        <v>6460</v>
+      </c>
+      <c r="C3209" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3210" t="s">
+        <v>6461</v>
+      </c>
+      <c r="B3210" t="s">
+        <v>6462</v>
+      </c>
+      <c r="C3210" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3211" t="s">
+        <v>6463</v>
+      </c>
+      <c r="B3211" t="s">
+        <v>6464</v>
+      </c>
+      <c r="C3211" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3212" t="s">
+        <v>6465</v>
+      </c>
+      <c r="B3212" t="s">
+        <v>6466</v>
+      </c>
+      <c r="C3212" t="s">
+        <v>6374</v>
+      </c>
+    </row>
+    <row r="3213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3213" t="s">
+        <v>6467</v>
+      </c>
+      <c r="B3213" t="s">
+        <v>6468</v>
+      </c>
+      <c r="C3213" t="s">
+        <v>6374</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8133" uniqueCount="6469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8232" uniqueCount="6536">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -19424,6 +19424,207 @@
   </si>
   <si>
     <t>Наволочка страйп-сатин 70х70 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001602729</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х30 - Гестхаус Белый 3х3 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>10-04-2026</t>
+  </si>
+  <si>
+    <t>4681001602712</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х30 - Ясное небо наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602705</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 120х200х30 - 140 - Асфальт 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602699</t>
+  </si>
+  <si>
+    <t>Простыня бязь 220х240 - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001602682</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 240х260 - "Папоротниковый"</t>
+  </si>
+  <si>
+    <t>4681001602675</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 142 ГОСТ - Зеленый</t>
+  </si>
+  <si>
+    <t>4681001602668</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин King Size семейное резинка 200х200х30 - Премиум ТС 320 Вишенка</t>
+  </si>
+  <si>
+    <t>4681001602651</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - "Сумбари" 1х1</t>
+  </si>
+  <si>
+    <t>4681001602644</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - М - 140 - Золото заката 1х1</t>
+  </si>
+  <si>
+    <t>4681001602637</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Аделаида"</t>
+  </si>
+  <si>
+    <t>4681001602620</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 175х215 - "Угольная Паутинка"</t>
+  </si>
+  <si>
+    <t>4681001602613</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Угольная Паутинка"</t>
+  </si>
+  <si>
+    <t>4681001602606</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Угольная Паутинка"</t>
+  </si>
+  <si>
+    <t>4681001602590</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 260х260 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001602583</t>
+  </si>
+  <si>
+    <t>Наволочка микросатин 50х70 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4681001602576</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное Евро простыня - Черный блеск наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602569</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Светлая орхидея</t>
+  </si>
+  <si>
+    <t>4681001602552</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Светлая орхидея</t>
+  </si>
+  <si>
+    <t>4681001602545</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 140х200х30 - "Октябрьская берёза"</t>
+  </si>
+  <si>
+    <t>4681001602538</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное - "Цветы в Тумане"</t>
+  </si>
+  <si>
+    <t>4681001602521</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Трендис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602514</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 160х200х30 - 120 - Урубамба</t>
+  </si>
+  <si>
+    <t>4681001602507</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Фазенда Лиара наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602491</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Лемпи" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602484</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро-макси резинка 180х200х30 - "Бездна"</t>
+  </si>
+  <si>
+    <t>4681001602477</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 240х260 - "Кофейный крем"</t>
+  </si>
+  <si>
+    <t>4681001602460</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х20 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001602453</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 70х70 - Серо-зелёный</t>
+  </si>
+  <si>
+    <t>4681001602446</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра 2 спальное Евро простыня - "Альбелла" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602439</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 180х200х30 - "Марципан"</t>
+  </si>
+  <si>
+    <t>4681001602422</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное резинка 140х200х30 - Весенняя акварель 2 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602415</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 125 - Дневной Аромат</t>
+  </si>
+  <si>
+    <t>4681001602408</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 60S 4217 Бежевый</t>
   </si>
 </sst>
 </file>
@@ -50628,6 +50829,369 @@
         <v>6374</v>
       </c>
     </row>
+    <row r="3214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3214" t="s">
+        <v>6469</v>
+      </c>
+      <c r="B3214" t="s">
+        <v>6470</v>
+      </c>
+      <c r="C3214" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3215" t="s">
+        <v>6472</v>
+      </c>
+      <c r="B3215" t="s">
+        <v>6473</v>
+      </c>
+      <c r="C3215" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3216" t="s">
+        <v>6474</v>
+      </c>
+      <c r="B3216" t="s">
+        <v>6475</v>
+      </c>
+      <c r="C3216" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3217" t="s">
+        <v>6476</v>
+      </c>
+      <c r="B3217" t="s">
+        <v>6477</v>
+      </c>
+      <c r="C3217" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3218" t="s">
+        <v>6478</v>
+      </c>
+      <c r="B3218" t="s">
+        <v>6479</v>
+      </c>
+      <c r="C3218" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3219" t="s">
+        <v>6480</v>
+      </c>
+      <c r="B3219" t="s">
+        <v>6481</v>
+      </c>
+      <c r="C3219" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3220" t="s">
+        <v>6482</v>
+      </c>
+      <c r="B3220" t="s">
+        <v>6483</v>
+      </c>
+      <c r="C3220" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3221" t="s">
+        <v>6484</v>
+      </c>
+      <c r="B3221" t="s">
+        <v>6485</v>
+      </c>
+      <c r="C3221" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3222" t="s">
+        <v>6486</v>
+      </c>
+      <c r="B3222" t="s">
+        <v>6487</v>
+      </c>
+      <c r="C3222" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3223" t="s">
+        <v>6488</v>
+      </c>
+      <c r="B3223" t="s">
+        <v>6489</v>
+      </c>
+      <c r="C3223" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3224" t="s">
+        <v>6490</v>
+      </c>
+      <c r="B3224" t="s">
+        <v>6491</v>
+      </c>
+      <c r="C3224" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3225" t="s">
+        <v>6492</v>
+      </c>
+      <c r="B3225" t="s">
+        <v>6493</v>
+      </c>
+      <c r="C3225" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3226" t="s">
+        <v>6494</v>
+      </c>
+      <c r="B3226" t="s">
+        <v>6495</v>
+      </c>
+      <c r="C3226" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3227" t="s">
+        <v>6496</v>
+      </c>
+      <c r="B3227" t="s">
+        <v>6497</v>
+      </c>
+      <c r="C3227" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3228" t="s">
+        <v>6498</v>
+      </c>
+      <c r="B3228" t="s">
+        <v>6499</v>
+      </c>
+      <c r="C3228" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3229" t="s">
+        <v>6500</v>
+      </c>
+      <c r="B3229" t="s">
+        <v>6501</v>
+      </c>
+      <c r="C3229" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3230" t="s">
+        <v>6502</v>
+      </c>
+      <c r="B3230" t="s">
+        <v>6503</v>
+      </c>
+      <c r="C3230" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3231" t="s">
+        <v>6504</v>
+      </c>
+      <c r="B3231" t="s">
+        <v>6505</v>
+      </c>
+      <c r="C3231" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3232" t="s">
+        <v>6506</v>
+      </c>
+      <c r="B3232" t="s">
+        <v>6507</v>
+      </c>
+      <c r="C3232" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3233" t="s">
+        <v>6508</v>
+      </c>
+      <c r="B3233" t="s">
+        <v>6509</v>
+      </c>
+      <c r="C3233" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3234" t="s">
+        <v>6510</v>
+      </c>
+      <c r="B3234" t="s">
+        <v>6511</v>
+      </c>
+      <c r="C3234" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3235" t="s">
+        <v>6512</v>
+      </c>
+      <c r="B3235" t="s">
+        <v>6513</v>
+      </c>
+      <c r="C3235" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3236" t="s">
+        <v>6514</v>
+      </c>
+      <c r="B3236" t="s">
+        <v>6515</v>
+      </c>
+      <c r="C3236" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3237" t="s">
+        <v>6516</v>
+      </c>
+      <c r="B3237" t="s">
+        <v>6517</v>
+      </c>
+      <c r="C3237" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3238" t="s">
+        <v>6518</v>
+      </c>
+      <c r="B3238" t="s">
+        <v>6519</v>
+      </c>
+      <c r="C3238" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3239" t="s">
+        <v>6520</v>
+      </c>
+      <c r="B3239" t="s">
+        <v>6521</v>
+      </c>
+      <c r="C3239" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3240" t="s">
+        <v>6522</v>
+      </c>
+      <c r="B3240" t="s">
+        <v>6523</v>
+      </c>
+      <c r="C3240" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3241" t="s">
+        <v>6524</v>
+      </c>
+      <c r="B3241" t="s">
+        <v>6525</v>
+      </c>
+      <c r="C3241" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3242" t="s">
+        <v>6526</v>
+      </c>
+      <c r="B3242" t="s">
+        <v>6527</v>
+      </c>
+      <c r="C3242" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3243" t="s">
+        <v>6528</v>
+      </c>
+      <c r="B3243" t="s">
+        <v>6529</v>
+      </c>
+      <c r="C3243" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3244" t="s">
+        <v>6530</v>
+      </c>
+      <c r="B3244" t="s">
+        <v>6531</v>
+      </c>
+      <c r="C3244" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3245" t="s">
+        <v>6532</v>
+      </c>
+      <c r="B3245" t="s">
+        <v>6533</v>
+      </c>
+      <c r="C3245" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="3246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3246" t="s">
+        <v>6534</v>
+      </c>
+      <c r="B3246" t="s">
+        <v>6535</v>
+      </c>
+      <c r="C3246" t="s">
+        <v>6471</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8232" uniqueCount="6536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8565" uniqueCount="6759">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -19625,6 +19625,675 @@
   </si>
   <si>
     <t>Наволочка тенсель 50х70 - 60S 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4681001603832</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Каштановый</t>
+  </si>
+  <si>
+    <t>12-04-2026</t>
+  </si>
+  <si>
+    <t>4681001603825</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - "Кофейный крем" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603818</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - М - Малахит</t>
+  </si>
+  <si>
+    <t>4681001603801</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х45 - 130 - Сланцево-серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001603795</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 220х240 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001603788</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 50х70 - "Салатовый"</t>
+  </si>
+  <si>
+    <t>4681001603771</t>
+  </si>
+  <si>
+    <t>Простыня бязь 260х260 - "Кетеван"</t>
+  </si>
+  <si>
+    <t>4681001603764</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х230х30 - 130 - Сланцево-серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001603757</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 210х210х20 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4681001603740</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное на резинке 160х200х20 - М - 120 - Чёрный мрамор</t>
+  </si>
+  <si>
+    <t>4681001603733</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро-макси - "Смоки" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603726</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 120х200х20 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4681001603719</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 60х60 - 125 - Дневной Аромат</t>
+  </si>
+  <si>
+    <t>4681001603702</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 180х220 - Белый</t>
+  </si>
+  <si>
+    <t>4681001603696</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил резинка 80х200х20 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>4681001603689</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Бенигно"</t>
+  </si>
+  <si>
+    <t>4681001603672</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил резинка 200х220х30 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001603665</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001603658</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 70х70 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001603641</t>
+  </si>
+  <si>
+    <t>Наволочка сатин-твил 50х70 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001603634</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 130 - "Изумрудный малахит" 1х1</t>
+  </si>
+  <si>
+    <t>4681001603627</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 60S 129 Темно-зеленый</t>
+  </si>
+  <si>
+    <t>4681001603610</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 60S 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4681001603603</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 60х60 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001603597</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001603580</t>
+  </si>
+  <si>
+    <t>Простыня жатка 240х260 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001603573</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х30 - 125 - "Персик" 1х1</t>
+  </si>
+  <si>
+    <t>4681001603566</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - Маренго наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603559</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Лилизари"</t>
+  </si>
+  <si>
+    <t>4681001603542</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4681001603535</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 300х300 - "Холодная элегия"</t>
+  </si>
+  <si>
+    <t>4681001603528</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро-макси - Аква Циан наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603511</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро-макси - Сливочно-кремовый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603504</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - "Ягуар"</t>
+  </si>
+  <si>
+    <t>4681001603498</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - М - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001603481</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001603474</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 80х200х30 - Премиум ТС 320 Вишенка</t>
+  </si>
+  <si>
+    <t>4681001603467</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 145х215 - М - Премиум ТС 320 Вишенка</t>
+  </si>
+  <si>
+    <t>4681001603450</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - ГОСТ - "Францеска"</t>
+  </si>
+  <si>
+    <t>4681001603443</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - ГОСТ - "Францеска"</t>
+  </si>
+  <si>
+    <t>4681001603436</t>
+  </si>
+  <si>
+    <t>Наволочка микрофибра 50х70 - "Имани"</t>
+  </si>
+  <si>
+    <t>4681001603429</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 140х200х30 - Светлая орхидея наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603412</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х40 - 135 - Лаймкват 1х1</t>
+  </si>
+  <si>
+    <t>4681001603405</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - Берлинская лазурь</t>
+  </si>
+  <si>
+    <t>4681001603399</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 125 - Василек 1х1</t>
+  </si>
+  <si>
+    <t>4681001603382</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Чернила 1х1</t>
+  </si>
+  <si>
+    <t>4681001603375</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Дарк Блу 1х1</t>
+  </si>
+  <si>
+    <t>4681001603368</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 130 - Полуночный ультрамарин 1х1</t>
+  </si>
+  <si>
+    <t>4681001603351</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Темно-синий 0,5х0,5</t>
+  </si>
+  <si>
+    <t>4681001603344</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - М - 60S Белый</t>
+  </si>
+  <si>
+    <t>4681001603337</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 175х215 - "Бонетто"</t>
+  </si>
+  <si>
+    <t>4681001603320</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая 200х220 - Мулетон Полиэстер</t>
+  </si>
+  <si>
+    <t>4681001603313</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Макена"</t>
+  </si>
+  <si>
+    <t>4681001603306</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х30 - 140 - Золото заката 1х1</t>
+  </si>
+  <si>
+    <t>4681001603290</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 90х200х30 - "Медный" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603283</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное Евро простыня - "Замороженный Перец"</t>
+  </si>
+  <si>
+    <t>4681001603276</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 1,5 спальное резинка 120х200х30 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4681001603269</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 180х200х40 - Какао с молоком</t>
+  </si>
+  <si>
+    <t>4681001603252</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 2 спальное - Архитектор</t>
+  </si>
+  <si>
+    <t>4681001603245</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 135 - Кортадерия 1х1</t>
+  </si>
+  <si>
+    <t>4681001603238</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - М - 80 - Витражи</t>
+  </si>
+  <si>
+    <t>4681001603221</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное резинка 180х200х30 - "Звёздный Вальс" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603214</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 142 - Сиреневые маки</t>
+  </si>
+  <si>
+    <t>4681001603207</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 80х200х20 - 142 ГОСТ - Темно-синяя</t>
+  </si>
+  <si>
+    <t>4681001603191</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное резинка 160х200х20 - "Снежный Хищник" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603184</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Черный янтарь 3х3 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603177</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х50 - "Танец крыльев"</t>
+  </si>
+  <si>
+    <t>4681001603160</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х200 - "Вилайн" 1х1</t>
+  </si>
+  <si>
+    <t>4681001603153</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - "Мяурель"</t>
+  </si>
+  <si>
+    <t>4681001603146</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 140х200х30 - 4217 Бежевый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603139</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Маренго</t>
+  </si>
+  <si>
+    <t>4681001603122</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Лаванда Страйп"</t>
+  </si>
+  <si>
+    <t>4681001603115</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - ГОСТ 142 - Лунные Овечки на голубом</t>
+  </si>
+  <si>
+    <t>4681001603108</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - ГОСТ 142 - Зверята на розовом</t>
+  </si>
+  <si>
+    <t>4681001603092</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - ГОСТ 142 - Сладкий Мёд зелёный</t>
+  </si>
+  <si>
+    <t>4681001603085</t>
+  </si>
+  <si>
+    <t>Простыня жатка 220х240 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001603078</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Трендис"</t>
+  </si>
+  <si>
+    <t>4681001603061</t>
+  </si>
+  <si>
+    <t>Простыня круглая микросатин резинка 230х230х30 - "Смоки"</t>
+  </si>
+  <si>
+    <t>4681001603054</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - "Сумбари" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603047</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х30 - 140 - Космос 1х1</t>
+  </si>
+  <si>
+    <t>4681001603030</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 150х220 - "Солнечные лучи"</t>
+  </si>
+  <si>
+    <t>4681001603023</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель King Size семейное резинка 200х200х30 - "Цветочный Шёпот"</t>
+  </si>
+  <si>
+    <t>4681001603016</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х20 - Изумруд Эсмеральды</t>
+  </si>
+  <si>
+    <t>4681001603009</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х40 - "Эшлин" 1х1</t>
+  </si>
+  <si>
+    <t>4681001602996</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - Дзета Ориона</t>
+  </si>
+  <si>
+    <t>4681001602989</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - 5431</t>
+  </si>
+  <si>
+    <t>4681001602972</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 150х220 - "Призрачная лагуна"</t>
+  </si>
+  <si>
+    <t>4681001602965</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 220х240 - 80 - Витражи</t>
+  </si>
+  <si>
+    <t>4681001602958</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х20 - 135 - "Золотистая ваниль" 1х1</t>
+  </si>
+  <si>
+    <t>4681001602941</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё поплин 1,5 спальное - "Формула-1" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602934</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 160х200х30 - 140 - Сирень 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602927</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х20 - "Мелиссит"</t>
+  </si>
+  <si>
+    <t>4681001602910</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Серис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602903</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Пинклайт наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602897</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - Светлая орхидея</t>
+  </si>
+  <si>
+    <t>4681001602880</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - "Дювеля" 1х1</t>
+  </si>
+  <si>
+    <t>4681001602873</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 300х300 - "Лимонный крем"</t>
+  </si>
+  <si>
+    <t>4681001602866</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 300х300 - "Бежевый Коралл"</t>
+  </si>
+  <si>
+    <t>4681001602859</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 300х300 - "Овсяный"</t>
+  </si>
+  <si>
+    <t>4681001602842</t>
+  </si>
+  <si>
+    <t>Простыня бязь 200х220 - 142 - Антиквариат</t>
+  </si>
+  <si>
+    <t>4681001602835</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 135 - Эмерэльд 1х1</t>
+  </si>
+  <si>
+    <t>4681001602828</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - 140 - Сирень 1х1</t>
+  </si>
+  <si>
+    <t>4681001602811</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х30 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001602804</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х30 - "Бежалис" 1х1</t>
+  </si>
+  <si>
+    <t>4681001602798</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - Гестхаус Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001602781</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил Евро резинка 160х200х30 - "Самолётики" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001602774</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 ГОСТ - Калейдоскоп Бабочек</t>
+  </si>
+  <si>
+    <t>4681001602767</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Эмерэльд 1х1</t>
+  </si>
+  <si>
+    <t>4681001602750</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 140х200х20 - 142 - Белый Бамбук</t>
+  </si>
+  <si>
+    <t>4681001602743</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 145х215 - "Леопардовый Сон"</t>
+  </si>
+  <si>
+    <t>4681001602736</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х220х30 - "Эбру"</t>
   </si>
 </sst>
 </file>
@@ -51192,6 +51861,1227 @@
         <v>6471</v>
       </c>
     </row>
+    <row r="3247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3247" t="s">
+        <v>6536</v>
+      </c>
+      <c r="B3247" t="s">
+        <v>6537</v>
+      </c>
+      <c r="C3247" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3248" t="s">
+        <v>6539</v>
+      </c>
+      <c r="B3248" t="s">
+        <v>6540</v>
+      </c>
+      <c r="C3248" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3249" t="s">
+        <v>6541</v>
+      </c>
+      <c r="B3249" t="s">
+        <v>6542</v>
+      </c>
+      <c r="C3249" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3250" t="s">
+        <v>6543</v>
+      </c>
+      <c r="B3250" t="s">
+        <v>6544</v>
+      </c>
+      <c r="C3250" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3251" t="s">
+        <v>6545</v>
+      </c>
+      <c r="B3251" t="s">
+        <v>6546</v>
+      </c>
+      <c r="C3251" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3252" t="s">
+        <v>6547</v>
+      </c>
+      <c r="B3252" t="s">
+        <v>6548</v>
+      </c>
+      <c r="C3252" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3253" t="s">
+        <v>6549</v>
+      </c>
+      <c r="B3253" t="s">
+        <v>6550</v>
+      </c>
+      <c r="C3253" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3254" t="s">
+        <v>6551</v>
+      </c>
+      <c r="B3254" t="s">
+        <v>6552</v>
+      </c>
+      <c r="C3254" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3255" t="s">
+        <v>6553</v>
+      </c>
+      <c r="B3255" t="s">
+        <v>6554</v>
+      </c>
+      <c r="C3255" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3256" t="s">
+        <v>6555</v>
+      </c>
+      <c r="B3256" t="s">
+        <v>6556</v>
+      </c>
+      <c r="C3256" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3257" t="s">
+        <v>6557</v>
+      </c>
+      <c r="B3257" t="s">
+        <v>6558</v>
+      </c>
+      <c r="C3257" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3258" t="s">
+        <v>6559</v>
+      </c>
+      <c r="B3258" t="s">
+        <v>6560</v>
+      </c>
+      <c r="C3258" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3259" t="s">
+        <v>6561</v>
+      </c>
+      <c r="B3259" t="s">
+        <v>6562</v>
+      </c>
+      <c r="C3259" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3260" t="s">
+        <v>6563</v>
+      </c>
+      <c r="B3260" t="s">
+        <v>6564</v>
+      </c>
+      <c r="C3260" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3261" t="s">
+        <v>6565</v>
+      </c>
+      <c r="B3261" t="s">
+        <v>6566</v>
+      </c>
+      <c r="C3261" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3262" t="s">
+        <v>6567</v>
+      </c>
+      <c r="B3262" t="s">
+        <v>6568</v>
+      </c>
+      <c r="C3262" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3263" t="s">
+        <v>6569</v>
+      </c>
+      <c r="B3263" t="s">
+        <v>6570</v>
+      </c>
+      <c r="C3263" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3264" t="s">
+        <v>6571</v>
+      </c>
+      <c r="B3264" t="s">
+        <v>6572</v>
+      </c>
+      <c r="C3264" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3265" t="s">
+        <v>6573</v>
+      </c>
+      <c r="B3265" t="s">
+        <v>6574</v>
+      </c>
+      <c r="C3265" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3266" t="s">
+        <v>6575</v>
+      </c>
+      <c r="B3266" t="s">
+        <v>6576</v>
+      </c>
+      <c r="C3266" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3267" t="s">
+        <v>6577</v>
+      </c>
+      <c r="B3267" t="s">
+        <v>6578</v>
+      </c>
+      <c r="C3267" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3268" t="s">
+        <v>6579</v>
+      </c>
+      <c r="B3268" t="s">
+        <v>6580</v>
+      </c>
+      <c r="C3268" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3269" t="s">
+        <v>6581</v>
+      </c>
+      <c r="B3269" t="s">
+        <v>6582</v>
+      </c>
+      <c r="C3269" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3270" t="s">
+        <v>6583</v>
+      </c>
+      <c r="B3270" t="s">
+        <v>6584</v>
+      </c>
+      <c r="C3270" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3271" t="s">
+        <v>6585</v>
+      </c>
+      <c r="B3271" t="s">
+        <v>6586</v>
+      </c>
+      <c r="C3271" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3272" t="s">
+        <v>6587</v>
+      </c>
+      <c r="B3272" t="s">
+        <v>6588</v>
+      </c>
+      <c r="C3272" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3273" t="s">
+        <v>6589</v>
+      </c>
+      <c r="B3273" t="s">
+        <v>6590</v>
+      </c>
+      <c r="C3273" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3274" t="s">
+        <v>6591</v>
+      </c>
+      <c r="B3274" t="s">
+        <v>6592</v>
+      </c>
+      <c r="C3274" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3275" t="s">
+        <v>6593</v>
+      </c>
+      <c r="B3275" t="s">
+        <v>6594</v>
+      </c>
+      <c r="C3275" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3276" t="s">
+        <v>6595</v>
+      </c>
+      <c r="B3276" t="s">
+        <v>6596</v>
+      </c>
+      <c r="C3276" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3277" t="s">
+        <v>6597</v>
+      </c>
+      <c r="B3277" t="s">
+        <v>6598</v>
+      </c>
+      <c r="C3277" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3278" t="s">
+        <v>6599</v>
+      </c>
+      <c r="B3278" t="s">
+        <v>6600</v>
+      </c>
+      <c r="C3278" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3279" t="s">
+        <v>6601</v>
+      </c>
+      <c r="B3279" t="s">
+        <v>6602</v>
+      </c>
+      <c r="C3279" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3280" t="s">
+        <v>6603</v>
+      </c>
+      <c r="B3280" t="s">
+        <v>6604</v>
+      </c>
+      <c r="C3280" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3281" t="s">
+        <v>6605</v>
+      </c>
+      <c r="B3281" t="s">
+        <v>6606</v>
+      </c>
+      <c r="C3281" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3282" t="s">
+        <v>6607</v>
+      </c>
+      <c r="B3282" t="s">
+        <v>6608</v>
+      </c>
+      <c r="C3282" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3283" t="s">
+        <v>6609</v>
+      </c>
+      <c r="B3283" t="s">
+        <v>6610</v>
+      </c>
+      <c r="C3283" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3284" t="s">
+        <v>6611</v>
+      </c>
+      <c r="B3284" t="s">
+        <v>6612</v>
+      </c>
+      <c r="C3284" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3285" t="s">
+        <v>6613</v>
+      </c>
+      <c r="B3285" t="s">
+        <v>6614</v>
+      </c>
+      <c r="C3285" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3286" t="s">
+        <v>6615</v>
+      </c>
+      <c r="B3286" t="s">
+        <v>6616</v>
+      </c>
+      <c r="C3286" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3287" t="s">
+        <v>6617</v>
+      </c>
+      <c r="B3287" t="s">
+        <v>6618</v>
+      </c>
+      <c r="C3287" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3288" t="s">
+        <v>6619</v>
+      </c>
+      <c r="B3288" t="s">
+        <v>6620</v>
+      </c>
+      <c r="C3288" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3289" t="s">
+        <v>6621</v>
+      </c>
+      <c r="B3289" t="s">
+        <v>6622</v>
+      </c>
+      <c r="C3289" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3290" t="s">
+        <v>6623</v>
+      </c>
+      <c r="B3290" t="s">
+        <v>6624</v>
+      </c>
+      <c r="C3290" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3291" t="s">
+        <v>6625</v>
+      </c>
+      <c r="B3291" t="s">
+        <v>6626</v>
+      </c>
+      <c r="C3291" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3292" t="s">
+        <v>6627</v>
+      </c>
+      <c r="B3292" t="s">
+        <v>6628</v>
+      </c>
+      <c r="C3292" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3293" t="s">
+        <v>6629</v>
+      </c>
+      <c r="B3293" t="s">
+        <v>6630</v>
+      </c>
+      <c r="C3293" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3294" t="s">
+        <v>6631</v>
+      </c>
+      <c r="B3294" t="s">
+        <v>6632</v>
+      </c>
+      <c r="C3294" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3295" t="s">
+        <v>6633</v>
+      </c>
+      <c r="B3295" t="s">
+        <v>6634</v>
+      </c>
+      <c r="C3295" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3296" t="s">
+        <v>6635</v>
+      </c>
+      <c r="B3296" t="s">
+        <v>6636</v>
+      </c>
+      <c r="C3296" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3297" t="s">
+        <v>6637</v>
+      </c>
+      <c r="B3297" t="s">
+        <v>6638</v>
+      </c>
+      <c r="C3297" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3298" t="s">
+        <v>6639</v>
+      </c>
+      <c r="B3298" t="s">
+        <v>6640</v>
+      </c>
+      <c r="C3298" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3299" t="s">
+        <v>6641</v>
+      </c>
+      <c r="B3299" t="s">
+        <v>6642</v>
+      </c>
+      <c r="C3299" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3300" t="s">
+        <v>6643</v>
+      </c>
+      <c r="B3300" t="s">
+        <v>6644</v>
+      </c>
+      <c r="C3300" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3301" t="s">
+        <v>6645</v>
+      </c>
+      <c r="B3301" t="s">
+        <v>6646</v>
+      </c>
+      <c r="C3301" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3302" t="s">
+        <v>6647</v>
+      </c>
+      <c r="B3302" t="s">
+        <v>6648</v>
+      </c>
+      <c r="C3302" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3303" t="s">
+        <v>6649</v>
+      </c>
+      <c r="B3303" t="s">
+        <v>6650</v>
+      </c>
+      <c r="C3303" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3304" t="s">
+        <v>6651</v>
+      </c>
+      <c r="B3304" t="s">
+        <v>6652</v>
+      </c>
+      <c r="C3304" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3305" t="s">
+        <v>6653</v>
+      </c>
+      <c r="B3305" t="s">
+        <v>6654</v>
+      </c>
+      <c r="C3305" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3306" t="s">
+        <v>6655</v>
+      </c>
+      <c r="B3306" t="s">
+        <v>6656</v>
+      </c>
+      <c r="C3306" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3307" t="s">
+        <v>6657</v>
+      </c>
+      <c r="B3307" t="s">
+        <v>6658</v>
+      </c>
+      <c r="C3307" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3308" t="s">
+        <v>6659</v>
+      </c>
+      <c r="B3308" t="s">
+        <v>6660</v>
+      </c>
+      <c r="C3308" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3309" t="s">
+        <v>6661</v>
+      </c>
+      <c r="B3309" t="s">
+        <v>6662</v>
+      </c>
+      <c r="C3309" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3310" t="s">
+        <v>6663</v>
+      </c>
+      <c r="B3310" t="s">
+        <v>6664</v>
+      </c>
+      <c r="C3310" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3311" t="s">
+        <v>6665</v>
+      </c>
+      <c r="B3311" t="s">
+        <v>6666</v>
+      </c>
+      <c r="C3311" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3312" t="s">
+        <v>6667</v>
+      </c>
+      <c r="B3312" t="s">
+        <v>6668</v>
+      </c>
+      <c r="C3312" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3313" t="s">
+        <v>6669</v>
+      </c>
+      <c r="B3313" t="s">
+        <v>6670</v>
+      </c>
+      <c r="C3313" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3314" t="s">
+        <v>6671</v>
+      </c>
+      <c r="B3314" t="s">
+        <v>6672</v>
+      </c>
+      <c r="C3314" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3315" t="s">
+        <v>6673</v>
+      </c>
+      <c r="B3315" t="s">
+        <v>6674</v>
+      </c>
+      <c r="C3315" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3316" t="s">
+        <v>6675</v>
+      </c>
+      <c r="B3316" t="s">
+        <v>6676</v>
+      </c>
+      <c r="C3316" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3317" t="s">
+        <v>6677</v>
+      </c>
+      <c r="B3317" t="s">
+        <v>6678</v>
+      </c>
+      <c r="C3317" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3318" t="s">
+        <v>6679</v>
+      </c>
+      <c r="B3318" t="s">
+        <v>6680</v>
+      </c>
+      <c r="C3318" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3319" t="s">
+        <v>6681</v>
+      </c>
+      <c r="B3319" t="s">
+        <v>6682</v>
+      </c>
+      <c r="C3319" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3320" t="s">
+        <v>6683</v>
+      </c>
+      <c r="B3320" t="s">
+        <v>6684</v>
+      </c>
+      <c r="C3320" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3321" t="s">
+        <v>6685</v>
+      </c>
+      <c r="B3321" t="s">
+        <v>6686</v>
+      </c>
+      <c r="C3321" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3322" t="s">
+        <v>6687</v>
+      </c>
+      <c r="B3322" t="s">
+        <v>6688</v>
+      </c>
+      <c r="C3322" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3323" t="s">
+        <v>6689</v>
+      </c>
+      <c r="B3323" t="s">
+        <v>6690</v>
+      </c>
+      <c r="C3323" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3324" t="s">
+        <v>6691</v>
+      </c>
+      <c r="B3324" t="s">
+        <v>6692</v>
+      </c>
+      <c r="C3324" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3325" t="s">
+        <v>6693</v>
+      </c>
+      <c r="B3325" t="s">
+        <v>6694</v>
+      </c>
+      <c r="C3325" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3326" t="s">
+        <v>6695</v>
+      </c>
+      <c r="B3326" t="s">
+        <v>6696</v>
+      </c>
+      <c r="C3326" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3327" t="s">
+        <v>6697</v>
+      </c>
+      <c r="B3327" t="s">
+        <v>6698</v>
+      </c>
+      <c r="C3327" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3328" t="s">
+        <v>6699</v>
+      </c>
+      <c r="B3328" t="s">
+        <v>6700</v>
+      </c>
+      <c r="C3328" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3329" t="s">
+        <v>6701</v>
+      </c>
+      <c r="B3329" t="s">
+        <v>6702</v>
+      </c>
+      <c r="C3329" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3330" t="s">
+        <v>6703</v>
+      </c>
+      <c r="B3330" t="s">
+        <v>6704</v>
+      </c>
+      <c r="C3330" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3331" t="s">
+        <v>6705</v>
+      </c>
+      <c r="B3331" t="s">
+        <v>6706</v>
+      </c>
+      <c r="C3331" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3332" t="s">
+        <v>6707</v>
+      </c>
+      <c r="B3332" t="s">
+        <v>6708</v>
+      </c>
+      <c r="C3332" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3333" t="s">
+        <v>6709</v>
+      </c>
+      <c r="B3333" t="s">
+        <v>6710</v>
+      </c>
+      <c r="C3333" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3334" t="s">
+        <v>6711</v>
+      </c>
+      <c r="B3334" t="s">
+        <v>6712</v>
+      </c>
+      <c r="C3334" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3335" t="s">
+        <v>6713</v>
+      </c>
+      <c r="B3335" t="s">
+        <v>6714</v>
+      </c>
+      <c r="C3335" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3336" t="s">
+        <v>6715</v>
+      </c>
+      <c r="B3336" t="s">
+        <v>6716</v>
+      </c>
+      <c r="C3336" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3337" t="s">
+        <v>6717</v>
+      </c>
+      <c r="B3337" t="s">
+        <v>6718</v>
+      </c>
+      <c r="C3337" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3338" t="s">
+        <v>6719</v>
+      </c>
+      <c r="B3338" t="s">
+        <v>6720</v>
+      </c>
+      <c r="C3338" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3339" t="s">
+        <v>6721</v>
+      </c>
+      <c r="B3339" t="s">
+        <v>6722</v>
+      </c>
+      <c r="C3339" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3340" t="s">
+        <v>6723</v>
+      </c>
+      <c r="B3340" t="s">
+        <v>6724</v>
+      </c>
+      <c r="C3340" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3341" t="s">
+        <v>6725</v>
+      </c>
+      <c r="B3341" t="s">
+        <v>6726</v>
+      </c>
+      <c r="C3341" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3342" t="s">
+        <v>6727</v>
+      </c>
+      <c r="B3342" t="s">
+        <v>6728</v>
+      </c>
+      <c r="C3342" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3343" t="s">
+        <v>6729</v>
+      </c>
+      <c r="B3343" t="s">
+        <v>6730</v>
+      </c>
+      <c r="C3343" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3344" t="s">
+        <v>6731</v>
+      </c>
+      <c r="B3344" t="s">
+        <v>6732</v>
+      </c>
+      <c r="C3344" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3345" t="s">
+        <v>6733</v>
+      </c>
+      <c r="B3345" t="s">
+        <v>6734</v>
+      </c>
+      <c r="C3345" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3346" t="s">
+        <v>6735</v>
+      </c>
+      <c r="B3346" t="s">
+        <v>6736</v>
+      </c>
+      <c r="C3346" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3347" t="s">
+        <v>6737</v>
+      </c>
+      <c r="B3347" t="s">
+        <v>6738</v>
+      </c>
+      <c r="C3347" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3348" t="s">
+        <v>6739</v>
+      </c>
+      <c r="B3348" t="s">
+        <v>6740</v>
+      </c>
+      <c r="C3348" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3349" t="s">
+        <v>6741</v>
+      </c>
+      <c r="B3349" t="s">
+        <v>6742</v>
+      </c>
+      <c r="C3349" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3350" t="s">
+        <v>6743</v>
+      </c>
+      <c r="B3350" t="s">
+        <v>6744</v>
+      </c>
+      <c r="C3350" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3351" t="s">
+        <v>6745</v>
+      </c>
+      <c r="B3351" t="s">
+        <v>6746</v>
+      </c>
+      <c r="C3351" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3352" t="s">
+        <v>6747</v>
+      </c>
+      <c r="B3352" t="s">
+        <v>6748</v>
+      </c>
+      <c r="C3352" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3353" t="s">
+        <v>6749</v>
+      </c>
+      <c r="B3353" t="s">
+        <v>6750</v>
+      </c>
+      <c r="C3353" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3354" t="s">
+        <v>6751</v>
+      </c>
+      <c r="B3354" t="s">
+        <v>6752</v>
+      </c>
+      <c r="C3354" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3355" t="s">
+        <v>6753</v>
+      </c>
+      <c r="B3355" t="s">
+        <v>6754</v>
+      </c>
+      <c r="C3355" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3356" t="s">
+        <v>6755</v>
+      </c>
+      <c r="B3356" t="s">
+        <v>6756</v>
+      </c>
+      <c r="C3356" t="s">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="3357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3357" t="s">
+        <v>6757</v>
+      </c>
+      <c r="B3357" t="s">
+        <v>6758</v>
+      </c>
+      <c r="C3357" t="s">
+        <v>6538</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8565" uniqueCount="6759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8664" uniqueCount="6826">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -20294,6 +20294,207 @@
   </si>
   <si>
     <t>Простыня полисатин резинка 200х220х30 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001604167</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Фиолетовый Шёпот"</t>
+  </si>
+  <si>
+    <t>13-04-2026</t>
+  </si>
+  <si>
+    <t>4681001604150</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин-жаккард 1,5 спальное резинка 120х200х30 - "Рендалис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604143</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4681001604136</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 140х200х30 - "Думнат" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604129</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 150х200 - М - Белый</t>
+  </si>
+  <si>
+    <t>4681001604112</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Бахати"</t>
+  </si>
+  <si>
+    <t>4681001604105</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х20 - 142 ГОСТ - Черный</t>
+  </si>
+  <si>
+    <t>4681001604099</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин King Size резинка 200х200х30 - "Бездна" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604082</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая резинка 140 х 200 х 10 - Мулетон Хлопок</t>
+  </si>
+  <si>
+    <t>4681001604075</t>
+  </si>
+  <si>
+    <t>Наволочка ранфорс 50х70 - "Лиловая нежность"</t>
+  </si>
+  <si>
+    <t>4681001604068</t>
+  </si>
+  <si>
+    <t>Простыня бязь 280х280 - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001604051</t>
+  </si>
+  <si>
+    <t>Простыня бязь 280х280 - "Джуман"</t>
+  </si>
+  <si>
+    <t>4681001604044</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 200х220 - 140 - Золото заката 1х1</t>
+  </si>
+  <si>
+    <t>4681001604037</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 - Монстера на коричневом</t>
+  </si>
+  <si>
+    <t>4681001604020</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Миндаль Страйп"</t>
+  </si>
+  <si>
+    <t>4681001604013</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 200х200х40 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4681001604006</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 220х240 - "Ягуар"</t>
+  </si>
+  <si>
+    <t>4681001603993</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 220х240 - М - 142 - Рецепт любви</t>
+  </si>
+  <si>
+    <t>4681001603986</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 220х240 - "Лавандис"</t>
+  </si>
+  <si>
+    <t>4681001603979</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 230х230х30 - 60S Белый</t>
+  </si>
+  <si>
+    <t>4681001603962</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 230х230х30 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001603955</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 230х230х30 - 60S 4294 Перламутровый</t>
+  </si>
+  <si>
+    <t>4681001603948</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное резинка 140х200х30 - "Сирента" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603931</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х30 - "Астероид"</t>
+  </si>
+  <si>
+    <t>4681001603924</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 125 - "Ваниль" 1х1</t>
+  </si>
+  <si>
+    <t>4681001603917</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное - Бертолеция наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001603900</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Ритва"</t>
+  </si>
+  <si>
+    <t>4681001603894</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - "Селинто"</t>
+  </si>
+  <si>
+    <t>4681001603887</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 50х70 - Лайлак</t>
+  </si>
+  <si>
+    <t>4681001603870</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин браш резинка 200х200х20 - "Лимонный крем"</t>
+  </si>
+  <si>
+    <t>4681001603863</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин браш резинка 200х200х20 - "Белый Оникс"</t>
+  </si>
+  <si>
+    <t>4681001603856</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 200х200х20 - 60S Белый</t>
+  </si>
+  <si>
+    <t>4681001603849</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин резинка 200х200х20 - Премиум ТС 320 Белый</t>
   </si>
 </sst>
 </file>
@@ -53082,6 +53283,369 @@
         <v>6538</v>
       </c>
     </row>
+    <row r="3358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3358" t="s">
+        <v>6759</v>
+      </c>
+      <c r="B3358" t="s">
+        <v>6760</v>
+      </c>
+      <c r="C3358" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3359" t="s">
+        <v>6762</v>
+      </c>
+      <c r="B3359" t="s">
+        <v>6763</v>
+      </c>
+      <c r="C3359" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3360" t="s">
+        <v>6764</v>
+      </c>
+      <c r="B3360" t="s">
+        <v>6765</v>
+      </c>
+      <c r="C3360" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3361" t="s">
+        <v>6766</v>
+      </c>
+      <c r="B3361" t="s">
+        <v>6767</v>
+      </c>
+      <c r="C3361" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3362" t="s">
+        <v>6768</v>
+      </c>
+      <c r="B3362" t="s">
+        <v>6769</v>
+      </c>
+      <c r="C3362" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3363" t="s">
+        <v>6770</v>
+      </c>
+      <c r="B3363" t="s">
+        <v>6771</v>
+      </c>
+      <c r="C3363" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3364" t="s">
+        <v>6772</v>
+      </c>
+      <c r="B3364" t="s">
+        <v>6773</v>
+      </c>
+      <c r="C3364" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3365" t="s">
+        <v>6774</v>
+      </c>
+      <c r="B3365" t="s">
+        <v>6775</v>
+      </c>
+      <c r="C3365" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3366" t="s">
+        <v>6776</v>
+      </c>
+      <c r="B3366" t="s">
+        <v>6777</v>
+      </c>
+      <c r="C3366" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3367" t="s">
+        <v>6778</v>
+      </c>
+      <c r="B3367" t="s">
+        <v>6779</v>
+      </c>
+      <c r="C3367" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3368" t="s">
+        <v>6780</v>
+      </c>
+      <c r="B3368" t="s">
+        <v>6781</v>
+      </c>
+      <c r="C3368" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3369" t="s">
+        <v>6782</v>
+      </c>
+      <c r="B3369" t="s">
+        <v>6783</v>
+      </c>
+      <c r="C3369" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3370" t="s">
+        <v>6784</v>
+      </c>
+      <c r="B3370" t="s">
+        <v>6785</v>
+      </c>
+      <c r="C3370" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3371" t="s">
+        <v>6786</v>
+      </c>
+      <c r="B3371" t="s">
+        <v>6787</v>
+      </c>
+      <c r="C3371" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3372" t="s">
+        <v>6788</v>
+      </c>
+      <c r="B3372" t="s">
+        <v>6789</v>
+      </c>
+      <c r="C3372" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3373" t="s">
+        <v>6790</v>
+      </c>
+      <c r="B3373" t="s">
+        <v>6791</v>
+      </c>
+      <c r="C3373" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3374" t="s">
+        <v>6792</v>
+      </c>
+      <c r="B3374" t="s">
+        <v>6793</v>
+      </c>
+      <c r="C3374" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3375" t="s">
+        <v>6794</v>
+      </c>
+      <c r="B3375" t="s">
+        <v>6795</v>
+      </c>
+      <c r="C3375" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3376" t="s">
+        <v>6796</v>
+      </c>
+      <c r="B3376" t="s">
+        <v>6797</v>
+      </c>
+      <c r="C3376" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3377" t="s">
+        <v>6798</v>
+      </c>
+      <c r="B3377" t="s">
+        <v>6799</v>
+      </c>
+      <c r="C3377" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3378" t="s">
+        <v>6800</v>
+      </c>
+      <c r="B3378" t="s">
+        <v>6801</v>
+      </c>
+      <c r="C3378" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3379" t="s">
+        <v>6802</v>
+      </c>
+      <c r="B3379" t="s">
+        <v>6803</v>
+      </c>
+      <c r="C3379" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3380" t="s">
+        <v>6804</v>
+      </c>
+      <c r="B3380" t="s">
+        <v>6805</v>
+      </c>
+      <c r="C3380" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3381" t="s">
+        <v>6806</v>
+      </c>
+      <c r="B3381" t="s">
+        <v>6807</v>
+      </c>
+      <c r="C3381" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3382" t="s">
+        <v>6808</v>
+      </c>
+      <c r="B3382" t="s">
+        <v>6809</v>
+      </c>
+      <c r="C3382" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3383" t="s">
+        <v>6810</v>
+      </c>
+      <c r="B3383" t="s">
+        <v>6811</v>
+      </c>
+      <c r="C3383" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3384" t="s">
+        <v>6812</v>
+      </c>
+      <c r="B3384" t="s">
+        <v>6813</v>
+      </c>
+      <c r="C3384" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3385" t="s">
+        <v>6814</v>
+      </c>
+      <c r="B3385" t="s">
+        <v>6815</v>
+      </c>
+      <c r="C3385" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3386" t="s">
+        <v>6816</v>
+      </c>
+      <c r="B3386" t="s">
+        <v>6817</v>
+      </c>
+      <c r="C3386" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3387" t="s">
+        <v>6818</v>
+      </c>
+      <c r="B3387" t="s">
+        <v>6819</v>
+      </c>
+      <c r="C3387" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3388" t="s">
+        <v>6820</v>
+      </c>
+      <c r="B3388" t="s">
+        <v>6821</v>
+      </c>
+      <c r="C3388" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3389" t="s">
+        <v>6822</v>
+      </c>
+      <c r="B3389" t="s">
+        <v>6823</v>
+      </c>
+      <c r="C3389" t="s">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="3390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3390" t="s">
+        <v>6824</v>
+      </c>
+      <c r="B3390" t="s">
+        <v>6825</v>
+      </c>
+      <c r="C3390" t="s">
+        <v>6761</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8664" uniqueCount="6826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8754" uniqueCount="6887">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -20495,6 +20495,189 @@
   </si>
   <si>
     <t>Простыня круглая сатин резинка 200х200х20 - Премиум ТС 320 Белый</t>
+  </si>
+  <si>
+    <t>4681001604464</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - "Нежный Листопад"</t>
+  </si>
+  <si>
+    <t>14-04-2026</t>
+  </si>
+  <si>
+    <t>4681001604457</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 240х260 - М - Снежное королевство</t>
+  </si>
+  <si>
+    <t>4681001604440</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 300х300 - Петроль</t>
+  </si>
+  <si>
+    <t>4681001604433</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 210х210х30 - "Астероид"</t>
+  </si>
+  <si>
+    <t>4681001604426</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - М - Чериньола</t>
+  </si>
+  <si>
+    <t>4681001604419</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - "Флафи"</t>
+  </si>
+  <si>
+    <t>4681001604402</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001604396</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 140х200х30 - "Графитовый Зигзаг"</t>
+  </si>
+  <si>
+    <t>4681001604389</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 220х240 - "Лесная Мелодия"</t>
+  </si>
+  <si>
+    <t>4681001604372</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - ГОСТ 142 - Зверята на желтом</t>
+  </si>
+  <si>
+    <t>4681001604365</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин резинка 220х220х20 - 140 - Белый Люкс</t>
+  </si>
+  <si>
+    <t>4681001604358</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 140х200х30 - 142 - Таунхаус наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604341</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 90х200х30 - "Лазурный Мегаполис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604334</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - 60S 4292 Кремовый</t>
+  </si>
+  <si>
+    <t>4681001604327</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное - "Графитовый Зигзаг" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604310</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 160х200х20 - "Вакита"</t>
+  </si>
+  <si>
+    <t>4681001604303</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - "Крылатые сны"</t>
+  </si>
+  <si>
+    <t>4681001604297</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - 90 - Гепарды</t>
+  </si>
+  <si>
+    <t>4681001604280</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х30 - 100 - Кружащие перья</t>
+  </si>
+  <si>
+    <t>4681001604273</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро резинка 160х200х30 - "Бежевый шлейф"</t>
+  </si>
+  <si>
+    <t>4681001604266</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - "Бахати" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604259</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - "Белава" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604242</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х20 - "Ритва"</t>
+  </si>
+  <si>
+    <t>4681001604235</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 200х220 - "Асуль"</t>
+  </si>
+  <si>
+    <t>4681001604228</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4681001604211</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - М - Меропа</t>
+  </si>
+  <si>
+    <t>4681001604204</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Меропа</t>
+  </si>
+  <si>
+    <t>4681001604198</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 90х200х30 - "Линнея" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604181</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4681001604174</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Белый Страйп"</t>
   </si>
 </sst>
 </file>
@@ -53646,6 +53829,336 @@
         <v>6761</v>
       </c>
     </row>
+    <row r="3391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3391" t="s">
+        <v>6826</v>
+      </c>
+      <c r="B3391" t="s">
+        <v>6827</v>
+      </c>
+      <c r="C3391" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3392" t="s">
+        <v>6829</v>
+      </c>
+      <c r="B3392" t="s">
+        <v>6830</v>
+      </c>
+      <c r="C3392" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3393" t="s">
+        <v>6831</v>
+      </c>
+      <c r="B3393" t="s">
+        <v>6832</v>
+      </c>
+      <c r="C3393" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3394" t="s">
+        <v>6833</v>
+      </c>
+      <c r="B3394" t="s">
+        <v>6834</v>
+      </c>
+      <c r="C3394" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3395" t="s">
+        <v>6835</v>
+      </c>
+      <c r="B3395" t="s">
+        <v>6836</v>
+      </c>
+      <c r="C3395" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3396" t="s">
+        <v>6837</v>
+      </c>
+      <c r="B3396" t="s">
+        <v>6838</v>
+      </c>
+      <c r="C3396" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3397" t="s">
+        <v>6839</v>
+      </c>
+      <c r="B3397" t="s">
+        <v>6840</v>
+      </c>
+      <c r="C3397" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3398" t="s">
+        <v>6841</v>
+      </c>
+      <c r="B3398" t="s">
+        <v>6842</v>
+      </c>
+      <c r="C3398" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3399" t="s">
+        <v>6843</v>
+      </c>
+      <c r="B3399" t="s">
+        <v>6844</v>
+      </c>
+      <c r="C3399" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3400" t="s">
+        <v>6845</v>
+      </c>
+      <c r="B3400" t="s">
+        <v>6846</v>
+      </c>
+      <c r="C3400" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3401" t="s">
+        <v>6847</v>
+      </c>
+      <c r="B3401" t="s">
+        <v>6848</v>
+      </c>
+      <c r="C3401" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3402" t="s">
+        <v>6849</v>
+      </c>
+      <c r="B3402" t="s">
+        <v>6850</v>
+      </c>
+      <c r="C3402" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3403" t="s">
+        <v>6851</v>
+      </c>
+      <c r="B3403" t="s">
+        <v>6852</v>
+      </c>
+      <c r="C3403" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3404" t="s">
+        <v>6853</v>
+      </c>
+      <c r="B3404" t="s">
+        <v>6854</v>
+      </c>
+      <c r="C3404" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3405" t="s">
+        <v>6855</v>
+      </c>
+      <c r="B3405" t="s">
+        <v>6856</v>
+      </c>
+      <c r="C3405" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3406" t="s">
+        <v>6857</v>
+      </c>
+      <c r="B3406" t="s">
+        <v>6858</v>
+      </c>
+      <c r="C3406" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3407" t="s">
+        <v>6859</v>
+      </c>
+      <c r="B3407" t="s">
+        <v>6860</v>
+      </c>
+      <c r="C3407" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3408" t="s">
+        <v>6861</v>
+      </c>
+      <c r="B3408" t="s">
+        <v>6862</v>
+      </c>
+      <c r="C3408" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3409" t="s">
+        <v>6863</v>
+      </c>
+      <c r="B3409" t="s">
+        <v>6864</v>
+      </c>
+      <c r="C3409" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3410" t="s">
+        <v>6865</v>
+      </c>
+      <c r="B3410" t="s">
+        <v>6866</v>
+      </c>
+      <c r="C3410" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3411" t="s">
+        <v>6867</v>
+      </c>
+      <c r="B3411" t="s">
+        <v>6868</v>
+      </c>
+      <c r="C3411" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3412" t="s">
+        <v>6869</v>
+      </c>
+      <c r="B3412" t="s">
+        <v>6870</v>
+      </c>
+      <c r="C3412" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3413" t="s">
+        <v>6871</v>
+      </c>
+      <c r="B3413" t="s">
+        <v>6872</v>
+      </c>
+      <c r="C3413" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3414" t="s">
+        <v>6873</v>
+      </c>
+      <c r="B3414" t="s">
+        <v>6874</v>
+      </c>
+      <c r="C3414" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3415" t="s">
+        <v>6875</v>
+      </c>
+      <c r="B3415" t="s">
+        <v>6876</v>
+      </c>
+      <c r="C3415" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3416" t="s">
+        <v>6877</v>
+      </c>
+      <c r="B3416" t="s">
+        <v>6878</v>
+      </c>
+      <c r="C3416" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3417" t="s">
+        <v>6879</v>
+      </c>
+      <c r="B3417" t="s">
+        <v>6880</v>
+      </c>
+      <c r="C3417" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3418" t="s">
+        <v>6881</v>
+      </c>
+      <c r="B3418" t="s">
+        <v>6882</v>
+      </c>
+      <c r="C3418" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3419" t="s">
+        <v>6883</v>
+      </c>
+      <c r="B3419" t="s">
+        <v>6884</v>
+      </c>
+      <c r="C3419" t="s">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="3420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3420" t="s">
+        <v>6885</v>
+      </c>
+      <c r="B3420" t="s">
+        <v>6886</v>
+      </c>
+      <c r="C3420" t="s">
+        <v>6828</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8754" uniqueCount="6887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8832" uniqueCount="6940">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -20678,6 +20678,165 @@
   </si>
   <si>
     <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001604723</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - 129 Темно-зеленый</t>
+  </si>
+  <si>
+    <t>15-04-2026</t>
+  </si>
+  <si>
+    <t>4681001604716</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001604709</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 140х200х30 - "Ритва"</t>
+  </si>
+  <si>
+    <t>4681001604693</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х40 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001604686</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное резинка 160х200х20 - 142 - Белый Бамбук</t>
+  </si>
+  <si>
+    <t>4681001604679</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 200х220 - "Бриолен" 1х1</t>
+  </si>
+  <si>
+    <t>4681001604662</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 90х200х30 - "Овсяный"</t>
+  </si>
+  <si>
+    <t>4681001604655</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 90х200х20 - "Блю Айс"</t>
+  </si>
+  <si>
+    <t>4681001604648</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси - "Тирас"</t>
+  </si>
+  <si>
+    <t>4681001604631</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Прохлада ментола</t>
+  </si>
+  <si>
+    <t>4681001604624</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х40 - "Белава"</t>
+  </si>
+  <si>
+    <t>4681001604617</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 140х200х30 - 142 - Биг Бен наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604600</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - Фазенда Лиара наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604594</t>
+  </si>
+  <si>
+    <t>Простыня круглая из тенселя на резинке 210 х 210 х 40 - М - Горчица</t>
+  </si>
+  <si>
+    <t>4681001604587</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 140 - Шоколад 1х1</t>
+  </si>
+  <si>
+    <t>4681001604570</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро-макси - "Танец крыльев"</t>
+  </si>
+  <si>
+    <t>4681001604563</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро-макси - 125 - Паслен А+В</t>
+  </si>
+  <si>
+    <t>4681001604556</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х30 - "Бахати"</t>
+  </si>
+  <si>
+    <t>4681001604549</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин-жаккард Евро - Снежное королевство</t>
+  </si>
+  <si>
+    <t>4681001604532</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 200х220 - Снежное королевство</t>
+  </si>
+  <si>
+    <t>4681001604525</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 200х200 - Вайт Фейри</t>
+  </si>
+  <si>
+    <t>4681001604518</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 210х210х30 - 135 - Марриотт Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001604501</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Городской стиль</t>
+  </si>
+  <si>
+    <t>4681001604495</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 70х70 - 226 Синий</t>
+  </si>
+  <si>
+    <t>4681001604488</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - "Мелвис" 1х1</t>
+  </si>
+  <si>
+    <t>4681001604471</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Природный Абстракт"</t>
   </si>
 </sst>
 </file>
@@ -54159,6 +54318,292 @@
         <v>6828</v>
       </c>
     </row>
+    <row r="3421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3421" t="s">
+        <v>6887</v>
+      </c>
+      <c r="B3421" t="s">
+        <v>6888</v>
+      </c>
+      <c r="C3421" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3422" t="s">
+        <v>6890</v>
+      </c>
+      <c r="B3422" t="s">
+        <v>6891</v>
+      </c>
+      <c r="C3422" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3423" t="s">
+        <v>6892</v>
+      </c>
+      <c r="B3423" t="s">
+        <v>6893</v>
+      </c>
+      <c r="C3423" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3424" t="s">
+        <v>6894</v>
+      </c>
+      <c r="B3424" t="s">
+        <v>6895</v>
+      </c>
+      <c r="C3424" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3425" t="s">
+        <v>6896</v>
+      </c>
+      <c r="B3425" t="s">
+        <v>6897</v>
+      </c>
+      <c r="C3425" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3426" t="s">
+        <v>6898</v>
+      </c>
+      <c r="B3426" t="s">
+        <v>6899</v>
+      </c>
+      <c r="C3426" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3427" t="s">
+        <v>6900</v>
+      </c>
+      <c r="B3427" t="s">
+        <v>6901</v>
+      </c>
+      <c r="C3427" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3428" t="s">
+        <v>6902</v>
+      </c>
+      <c r="B3428" t="s">
+        <v>6903</v>
+      </c>
+      <c r="C3428" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3429" t="s">
+        <v>6904</v>
+      </c>
+      <c r="B3429" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C3429" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3430" t="s">
+        <v>6906</v>
+      </c>
+      <c r="B3430" t="s">
+        <v>6907</v>
+      </c>
+      <c r="C3430" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3431" t="s">
+        <v>6908</v>
+      </c>
+      <c r="B3431" t="s">
+        <v>6909</v>
+      </c>
+      <c r="C3431" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3432" t="s">
+        <v>6910</v>
+      </c>
+      <c r="B3432" t="s">
+        <v>6911</v>
+      </c>
+      <c r="C3432" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3433" t="s">
+        <v>6912</v>
+      </c>
+      <c r="B3433" t="s">
+        <v>6913</v>
+      </c>
+      <c r="C3433" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3434" t="s">
+        <v>6914</v>
+      </c>
+      <c r="B3434" t="s">
+        <v>6915</v>
+      </c>
+      <c r="C3434" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3435" t="s">
+        <v>6916</v>
+      </c>
+      <c r="B3435" t="s">
+        <v>6917</v>
+      </c>
+      <c r="C3435" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3436" t="s">
+        <v>6918</v>
+      </c>
+      <c r="B3436" t="s">
+        <v>6919</v>
+      </c>
+      <c r="C3436" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3437" t="s">
+        <v>6920</v>
+      </c>
+      <c r="B3437" t="s">
+        <v>6921</v>
+      </c>
+      <c r="C3437" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3438" t="s">
+        <v>6922</v>
+      </c>
+      <c r="B3438" t="s">
+        <v>6923</v>
+      </c>
+      <c r="C3438" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3439" t="s">
+        <v>6924</v>
+      </c>
+      <c r="B3439" t="s">
+        <v>6925</v>
+      </c>
+      <c r="C3439" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3440" t="s">
+        <v>6926</v>
+      </c>
+      <c r="B3440" t="s">
+        <v>6927</v>
+      </c>
+      <c r="C3440" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3441" t="s">
+        <v>6928</v>
+      </c>
+      <c r="B3441" t="s">
+        <v>6929</v>
+      </c>
+      <c r="C3441" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3442" t="s">
+        <v>6930</v>
+      </c>
+      <c r="B3442" t="s">
+        <v>6931</v>
+      </c>
+      <c r="C3442" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3443" t="s">
+        <v>6932</v>
+      </c>
+      <c r="B3443" t="s">
+        <v>6933</v>
+      </c>
+      <c r="C3443" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3444" t="s">
+        <v>6934</v>
+      </c>
+      <c r="B3444" t="s">
+        <v>6935</v>
+      </c>
+      <c r="C3444" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3445" t="s">
+        <v>6936</v>
+      </c>
+      <c r="B3445" t="s">
+        <v>6937</v>
+      </c>
+      <c r="C3445" t="s">
+        <v>6889</v>
+      </c>
+    </row>
+    <row r="3446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3446" t="s">
+        <v>6938</v>
+      </c>
+      <c r="B3446" t="s">
+        <v>6939</v>
+      </c>
+      <c r="C3446" t="s">
+        <v>6889</v>
+      </c>
+    </row>
     <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3449" s="6"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8832" uniqueCount="6940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8892" uniqueCount="6981">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -20837,6 +20837,129 @@
   </si>
   <si>
     <t>Простыня жатка 280х280 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001604921</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 200х200 - "Криола"</t>
+  </si>
+  <si>
+    <t>16-04-2026</t>
+  </si>
+  <si>
+    <t>4681001604914</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 300х300 - 125 - Терракота</t>
+  </si>
+  <si>
+    <t>4681001604907</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс 240х260 - "Ванильный раф"</t>
+  </si>
+  <si>
+    <t>4681001604891</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное - "Вилайн" 1х1 Универсал</t>
+  </si>
+  <si>
+    <t>4681001604884</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - Магма А+В</t>
+  </si>
+  <si>
+    <t>4681001604877</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 210х210х40 - Селадон</t>
+  </si>
+  <si>
+    <t>4681001604860</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 200х220 - "Залив"</t>
+  </si>
+  <si>
+    <t>4681001604853</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х220 - "Церматт"</t>
+  </si>
+  <si>
+    <t>4681001604846</t>
+  </si>
+  <si>
+    <t>Простыня жатка 200х220 - "Звёздный Вальс"</t>
+  </si>
+  <si>
+    <t>4681001604839</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 50х50 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001604822</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин Евро-макси - "Пудинг"</t>
+  </si>
+  <si>
+    <t>4681001604815</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 125 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001604808</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 70х70 - Ванильный</t>
+  </si>
+  <si>
+    <t>4681001604792</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Белава"</t>
+  </si>
+  <si>
+    <t>4681001604785</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 135 - Цитрус 3х3</t>
+  </si>
+  <si>
+    <t>4681001604778</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 135 - НамДокМай 1х1</t>
+  </si>
+  <si>
+    <t>4681001604761</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 140 - Золото заката 1х1</t>
+  </si>
+  <si>
+    <t>4681001604754</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 120х200х30 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001604747</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х200 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001604730</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - 142 - Оранжевый</t>
   </si>
 </sst>
 </file>
@@ -54604,8 +54727,225 @@
         <v>6889</v>
       </c>
     </row>
-    <row r="3449" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3449" s="6"/>
+    <row r="3447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3447" t="s">
+        <v>6940</v>
+      </c>
+      <c r="B3447" t="s">
+        <v>6941</v>
+      </c>
+      <c r="C3447" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3448" t="s">
+        <v>6943</v>
+      </c>
+      <c r="B3448" t="s">
+        <v>6944</v>
+      </c>
+      <c r="C3448" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3449" s="6" t="s">
+        <v>6945</v>
+      </c>
+      <c r="B3449" t="s">
+        <v>6946</v>
+      </c>
+      <c r="C3449" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3450" t="s">
+        <v>6947</v>
+      </c>
+      <c r="B3450" t="s">
+        <v>6948</v>
+      </c>
+      <c r="C3450" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3451" t="s">
+        <v>6949</v>
+      </c>
+      <c r="B3451" t="s">
+        <v>6950</v>
+      </c>
+      <c r="C3451" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3452" t="s">
+        <v>6951</v>
+      </c>
+      <c r="B3452" t="s">
+        <v>6952</v>
+      </c>
+      <c r="C3452" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3453" t="s">
+        <v>6953</v>
+      </c>
+      <c r="B3453" t="s">
+        <v>6954</v>
+      </c>
+      <c r="C3453" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3454" t="s">
+        <v>6955</v>
+      </c>
+      <c r="B3454" t="s">
+        <v>6956</v>
+      </c>
+      <c r="C3454" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3455" t="s">
+        <v>6957</v>
+      </c>
+      <c r="B3455" t="s">
+        <v>6958</v>
+      </c>
+      <c r="C3455" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3456" t="s">
+        <v>6959</v>
+      </c>
+      <c r="B3456" t="s">
+        <v>6960</v>
+      </c>
+      <c r="C3456" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3457" t="s">
+        <v>6961</v>
+      </c>
+      <c r="B3457" t="s">
+        <v>6962</v>
+      </c>
+      <c r="C3457" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3458" t="s">
+        <v>6963</v>
+      </c>
+      <c r="B3458" t="s">
+        <v>6964</v>
+      </c>
+      <c r="C3458" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3459" t="s">
+        <v>6965</v>
+      </c>
+      <c r="B3459" t="s">
+        <v>6966</v>
+      </c>
+      <c r="C3459" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3460" t="s">
+        <v>6967</v>
+      </c>
+      <c r="B3460" t="s">
+        <v>6968</v>
+      </c>
+      <c r="C3460" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3461" t="s">
+        <v>6969</v>
+      </c>
+      <c r="B3461" t="s">
+        <v>6970</v>
+      </c>
+      <c r="C3461" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3462" t="s">
+        <v>6971</v>
+      </c>
+      <c r="B3462" t="s">
+        <v>6972</v>
+      </c>
+      <c r="C3462" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3463" t="s">
+        <v>6973</v>
+      </c>
+      <c r="B3463" t="s">
+        <v>6974</v>
+      </c>
+      <c r="C3463" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3464" t="s">
+        <v>6975</v>
+      </c>
+      <c r="B3464" t="s">
+        <v>6976</v>
+      </c>
+      <c r="C3464" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3465" t="s">
+        <v>6977</v>
+      </c>
+      <c r="B3465" t="s">
+        <v>6978</v>
+      </c>
+      <c r="C3465" t="s">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="3466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3466" t="s">
+        <v>6979</v>
+      </c>
+      <c r="B3466" t="s">
+        <v>6980</v>
+      </c>
+      <c r="C3466" t="s">
+        <v>6942</v>
+      </c>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8892" uniqueCount="6981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8925" uniqueCount="7004">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -20960,6 +20960,75 @@
   </si>
   <si>
     <t>Пододеяльник бязь 145х215 - 142 - Оранжевый</t>
+  </si>
+  <si>
+    <t>4681001605034</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х220х30 - "Серебро Облаков"</t>
+  </si>
+  <si>
+    <t>17-04-2026</t>
+  </si>
+  <si>
+    <t>4681001605027</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х40 - 60S 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4681001605010</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - "Корги-пати"</t>
+  </si>
+  <si>
+    <t>4681001605003</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 200х200х30 - 135 - Марриотт Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001604990</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 1,5 спальное резинка 140х200х30 - Белый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604983</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х30 - Белоснежное наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001604976</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 160х200х30 - 130 - Антрацитовый</t>
+  </si>
+  <si>
+    <t>4681001604969</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 160х200х30 - 120 - Иолит</t>
+  </si>
+  <si>
+    <t>4681001604952</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х30 - "Инспайр"</t>
+  </si>
+  <si>
+    <t>4681001604945</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - "Ледяная Мята"</t>
+  </si>
+  <si>
+    <t>4681001604938</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Зайга"</t>
   </si>
 </sst>
 </file>
@@ -54947,6 +55016,127 @@
         <v>6942</v>
       </c>
     </row>
+    <row r="3467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3467" t="s">
+        <v>6981</v>
+      </c>
+      <c r="B3467" t="s">
+        <v>6982</v>
+      </c>
+      <c r="C3467" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3468" t="s">
+        <v>6984</v>
+      </c>
+      <c r="B3468" t="s">
+        <v>6985</v>
+      </c>
+      <c r="C3468" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3469" t="s">
+        <v>6986</v>
+      </c>
+      <c r="B3469" t="s">
+        <v>6987</v>
+      </c>
+      <c r="C3469" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3470" t="s">
+        <v>6988</v>
+      </c>
+      <c r="B3470" t="s">
+        <v>6989</v>
+      </c>
+      <c r="C3470" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3471" t="s">
+        <v>6990</v>
+      </c>
+      <c r="B3471" t="s">
+        <v>6991</v>
+      </c>
+      <c r="C3471" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3472" t="s">
+        <v>6992</v>
+      </c>
+      <c r="B3472" t="s">
+        <v>6993</v>
+      </c>
+      <c r="C3472" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3473" t="s">
+        <v>6994</v>
+      </c>
+      <c r="B3473" t="s">
+        <v>6995</v>
+      </c>
+      <c r="C3473" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3474" t="s">
+        <v>6996</v>
+      </c>
+      <c r="B3474" t="s">
+        <v>6997</v>
+      </c>
+      <c r="C3474" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3475" t="s">
+        <v>6998</v>
+      </c>
+      <c r="B3475" t="s">
+        <v>6999</v>
+      </c>
+      <c r="C3475" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3476" t="s">
+        <v>7000</v>
+      </c>
+      <c r="B3476" t="s">
+        <v>7001</v>
+      </c>
+      <c r="C3476" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3477" t="s">
+        <v>7002</v>
+      </c>
+      <c r="B3477" t="s">
+        <v>7003</v>
+      </c>
+      <c r="C3477" t="s">
+        <v>6983</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2899A2-C4A6-4729-9F65-82C3ADC858CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="3660" windowWidth="21600" windowHeight="11385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
+    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8925" uniqueCount="7004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9006" uniqueCount="7058">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -21029,35 +21030,197 @@
   </si>
   <si>
     <t>Пододеяльник полисатин 200х220 - "Зайга"</t>
+  </si>
+  <si>
+    <t>4681001605294</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4681001605287</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 175х215 - 140 - Голубой 1х1</t>
+  </si>
+  <si>
+    <t>4681001605270</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - Небесный Пиксель А+В наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605263</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - Магма А+В наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605256</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Замороженный Перец" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605249</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 140х200х30 - "Севим" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605232</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - "Табия"</t>
+  </si>
+  <si>
+    <t>4681001605225</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х50 - "Севим"</t>
+  </si>
+  <si>
+    <t>4681001605218</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 2 спальное резинка 160х200х30 - "Ванильный раф"</t>
+  </si>
+  <si>
+    <t>4681001605201</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - Нирвана наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605195</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 150х200 - "Звёздный Вальс"</t>
+  </si>
+  <si>
+    <t>4681001605188</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 140 - Винно-красный 1х1</t>
+  </si>
+  <si>
+    <t>4681001605171</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - "Экзотический"</t>
+  </si>
+  <si>
+    <t>4681001605164</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 180х200х40 - 120 - Трюфель</t>
+  </si>
+  <si>
+    <t>4681001605157</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс резинка 180х200х40 - "Фантасмагория"</t>
+  </si>
+  <si>
+    <t>4681001605140</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 142 - Флокс</t>
+  </si>
+  <si>
+    <t>4681001605133</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное Евро простыня - "Цветы в Тумане"</t>
+  </si>
+  <si>
+    <t>4681001605126</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Данделионс А+В</t>
+  </si>
+  <si>
+    <t>4681001605119</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 129 Темно-зеленый</t>
+  </si>
+  <si>
+    <t>4681001605102</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - Танец под водой</t>
+  </si>
+  <si>
+    <t>4681001605096</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Тонкий Лист"</t>
+  </si>
+  <si>
+    <t>4681001605089</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х30 - "Манцель" 3х3</t>
+  </si>
+  <si>
+    <t>4681001605072</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 140х200х30 - Меропа наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605065</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро - "Нефритовый" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605058</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 4373 Пудровый</t>
+  </si>
+  <si>
+    <t>4681001605041</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 180х200х30 - "Флорес" 1х1</t>
+  </si>
+  <si>
+    <t>4681001605300</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - 120 - Белый</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -21083,10 +21246,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -21110,7 +21281,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -21387,22 +21558,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -21431,7 +21602,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -21439,7 +21610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -21447,7 +21618,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -21455,7 +21626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -21463,7 +21634,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -21471,7 +21642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -21479,7 +21650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -21487,7 +21658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -21495,7 +21666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -21503,7 +21674,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -21511,7 +21682,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -21519,7 +21690,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -33303,7 +33474,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -33311,7 +33482,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -33319,7 +33490,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -33327,7 +33498,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -33335,7 +33506,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -33343,7 +33514,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -33351,7 +33522,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -33359,7 +33530,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -33367,7 +33538,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -33375,7 +33546,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -33383,7 +33554,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -33391,7 +33562,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -33399,7 +33570,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -33407,7 +33578,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -33415,7 +33586,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -55134,6 +55305,303 @@
         <v>7003</v>
       </c>
       <c r="C3477" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3478" t="s">
+        <v>7004</v>
+      </c>
+      <c r="B3478" t="s">
+        <v>7005</v>
+      </c>
+      <c r="C3478" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3479" t="s">
+        <v>7006</v>
+      </c>
+      <c r="B3479" t="s">
+        <v>7007</v>
+      </c>
+      <c r="C3479" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3480" t="s">
+        <v>7008</v>
+      </c>
+      <c r="B3480" t="s">
+        <v>7009</v>
+      </c>
+      <c r="C3480" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3481" t="s">
+        <v>7010</v>
+      </c>
+      <c r="B3481" t="s">
+        <v>7011</v>
+      </c>
+      <c r="C3481" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3482" t="s">
+        <v>7012</v>
+      </c>
+      <c r="B3482" t="s">
+        <v>7013</v>
+      </c>
+      <c r="C3482" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3483" t="s">
+        <v>7014</v>
+      </c>
+      <c r="B3483" t="s">
+        <v>7015</v>
+      </c>
+      <c r="C3483" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3484" t="s">
+        <v>7016</v>
+      </c>
+      <c r="B3484" t="s">
+        <v>7017</v>
+      </c>
+      <c r="C3484" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3485" t="s">
+        <v>7018</v>
+      </c>
+      <c r="B3485" t="s">
+        <v>7019</v>
+      </c>
+      <c r="C3485" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3486" t="s">
+        <v>7020</v>
+      </c>
+      <c r="B3486" t="s">
+        <v>7021</v>
+      </c>
+      <c r="C3486" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3487" t="s">
+        <v>7022</v>
+      </c>
+      <c r="B3487" t="s">
+        <v>7023</v>
+      </c>
+      <c r="C3487" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3488" t="s">
+        <v>7024</v>
+      </c>
+      <c r="B3488" t="s">
+        <v>7025</v>
+      </c>
+      <c r="C3488" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3489" t="s">
+        <v>7026</v>
+      </c>
+      <c r="B3489" t="s">
+        <v>7027</v>
+      </c>
+      <c r="C3489" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3490" t="s">
+        <v>7028</v>
+      </c>
+      <c r="B3490" t="s">
+        <v>7029</v>
+      </c>
+      <c r="C3490" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3491" t="s">
+        <v>7030</v>
+      </c>
+      <c r="B3491" t="s">
+        <v>7031</v>
+      </c>
+      <c r="C3491" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3492" t="s">
+        <v>7032</v>
+      </c>
+      <c r="B3492" t="s">
+        <v>7033</v>
+      </c>
+      <c r="C3492" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3493" t="s">
+        <v>7034</v>
+      </c>
+      <c r="B3493" t="s">
+        <v>7035</v>
+      </c>
+      <c r="C3493" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3494" t="s">
+        <v>7036</v>
+      </c>
+      <c r="B3494" t="s">
+        <v>7037</v>
+      </c>
+      <c r="C3494" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3495" t="s">
+        <v>7038</v>
+      </c>
+      <c r="B3495" t="s">
+        <v>7039</v>
+      </c>
+      <c r="C3495" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3496" t="s">
+        <v>7040</v>
+      </c>
+      <c r="B3496" t="s">
+        <v>7041</v>
+      </c>
+      <c r="C3496" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3497" t="s">
+        <v>7042</v>
+      </c>
+      <c r="B3497" t="s">
+        <v>7043</v>
+      </c>
+      <c r="C3497" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3498" t="s">
+        <v>7044</v>
+      </c>
+      <c r="B3498" t="s">
+        <v>7045</v>
+      </c>
+      <c r="C3498" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3499" t="s">
+        <v>7046</v>
+      </c>
+      <c r="B3499" t="s">
+        <v>7047</v>
+      </c>
+      <c r="C3499" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3500" t="s">
+        <v>7048</v>
+      </c>
+      <c r="B3500" t="s">
+        <v>7049</v>
+      </c>
+      <c r="C3500" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3501" t="s">
+        <v>7050</v>
+      </c>
+      <c r="B3501" t="s">
+        <v>7051</v>
+      </c>
+      <c r="C3501" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3502" t="s">
+        <v>7052</v>
+      </c>
+      <c r="B3502" t="s">
+        <v>7053</v>
+      </c>
+      <c r="C3502" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3503" t="s">
+        <v>7054</v>
+      </c>
+      <c r="B3503" t="s">
+        <v>7055</v>
+      </c>
+      <c r="C3503" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="3504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3504" t="s">
+        <v>7056</v>
+      </c>
+      <c r="B3504" t="s">
+        <v>7057</v>
+      </c>
+      <c r="C3504" t="s">
         <v>6983</v>
       </c>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2899A2-C4A6-4729-9F65-82C3ADC858CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9006" uniqueCount="7058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9309" uniqueCount="7261">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -21192,35 +21191,644 @@
   </si>
   <si>
     <t>Простыня бязь 150х220 - 120 - Белый</t>
+  </si>
+  <si>
+    <t>4681001606314</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Твист"</t>
+  </si>
+  <si>
+    <t>19-04-2026</t>
+  </si>
+  <si>
+    <t>4681001606307</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 60х60 - "Твист"</t>
+  </si>
+  <si>
+    <t>4681001606291</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 150х200 - 142 - Белый</t>
+  </si>
+  <si>
+    <t>4681001606284</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 120 - Голубая Латка</t>
+  </si>
+  <si>
+    <t>4681001606277</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - Арабески (беж)</t>
+  </si>
+  <si>
+    <t>4681001606260</t>
+  </si>
+  <si>
+    <t>Простыня сатин 150х220 - "Песчаная вуаль"</t>
+  </si>
+  <si>
+    <t>4681001606253</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х30 - Небесный Пиксель А+В наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606246</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 220х240 - "Фиорелла"</t>
+  </si>
+  <si>
+    <t>4681001606239</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро-макси - "Интерстеллар"</t>
+  </si>
+  <si>
+    <t>4681001606222</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 180х200х30 - Гималайские маки</t>
+  </si>
+  <si>
+    <t>4681001606215</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин браш 175х215 - "Серпентин"</t>
+  </si>
+  <si>
+    <t>4681001606208</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001606192</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Меропа наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606185</t>
+  </si>
+  <si>
+    <t>Простыня бязь 300х300 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001606178</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль 1,5 спальное резинка 140х200х30 - 110 - Изысканность наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606161</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль 2 спальное резинка 160х200х20 - 110 - Каори на желтом наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606154</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 130 - "Изумрудный малахит" 1х1</t>
+  </si>
+  <si>
+    <t>4681001606147</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - Грей блес</t>
+  </si>
+  <si>
+    <t>4681001606130</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное - 130 - Пудровый 1х1</t>
+  </si>
+  <si>
+    <t>4681001606123</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - Данделионс А+В</t>
+  </si>
+  <si>
+    <t>4681001606116</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное резинка 140х200х30 - Прелат А+В</t>
+  </si>
+  <si>
+    <t>4681001606109</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 200х220 - Какао с молоком</t>
+  </si>
+  <si>
+    <t>4681001606093</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Какао с молоком</t>
+  </si>
+  <si>
+    <t>4681001606086</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 200х200х40 - 125 - Марсала</t>
+  </si>
+  <si>
+    <t>4681001606079</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 145х215 - Премиум ТС 320 Бесконечность</t>
+  </si>
+  <si>
+    <t>4681001606062</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - Премиум ТС 320 Бесконечность</t>
+  </si>
+  <si>
+    <t>4681001606055</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 80х200х30 - Премиум ТС 320 Бесконечность</t>
+  </si>
+  <si>
+    <t>4681001606048</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное резинка 160х200х30 - Зеленый чай</t>
+  </si>
+  <si>
+    <t>4681001606031</t>
+  </si>
+  <si>
+    <t>Простыня круглая микросатин резинка 220х220х20 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4681001606024</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное резинка 160х200х30 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001606017</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Нева"</t>
+  </si>
+  <si>
+    <t>4681001606000</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил резинка 140х200х20 - "Нева"</t>
+  </si>
+  <si>
+    <t>4681001605997</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Зайга"</t>
+  </si>
+  <si>
+    <t>4681001605980</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 200х220 - "Небосвод"</t>
+  </si>
+  <si>
+    <t>4681001605973</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Белый</t>
+  </si>
+  <si>
+    <t>4681001605966</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Песчаный ветер"</t>
+  </si>
+  <si>
+    <t>4681001605959</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Инспайр" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605942</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - 140 - Асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4681001605935</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 180х220 - 110 - Каори на зеленом</t>
+  </si>
+  <si>
+    <t>4681001605928</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 140х200х30 - 110 - Каори на зеленом</t>
+  </si>
+  <si>
+    <t>4681001605911</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 50х70 - 110 - Каори на зеленом</t>
+  </si>
+  <si>
+    <t>4681001605904</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 40х60 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001605898</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Горький шоколад</t>
+  </si>
+  <si>
+    <t>4681001605881</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное - 135 - Фирюз 1х1</t>
+  </si>
+  <si>
+    <t>4681001605874</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - 140 - Росток 1х1</t>
+  </si>
+  <si>
+    <t>4681001605867</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 180х200х30 - 140 - Космос 1х1</t>
+  </si>
+  <si>
+    <t>4681001605850</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил Евро - "Ардуино"</t>
+  </si>
+  <si>
+    <t>4681001605843</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Графитовый Зигзаг"</t>
+  </si>
+  <si>
+    <t>4681001605836</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Графитовый Зигзаг"</t>
+  </si>
+  <si>
+    <t>4681001605829</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 150х200 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4681001605812</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - 129 Темно-зеленый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605805</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 180х200х30 - "Морозный туман" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605799</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро - 140 - Черный янтарь 3х3</t>
+  </si>
+  <si>
+    <t>4681001605782</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 70х70 - Палладион</t>
+  </si>
+  <si>
+    <t>4681001605775</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - Белый</t>
+  </si>
+  <si>
+    <t>4681001605768</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Бахати"</t>
+  </si>
+  <si>
+    <t>4681001605751</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 120х200х20 - "Аркашон"</t>
+  </si>
+  <si>
+    <t>4681001605744</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - 80 - Витражи наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605737</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 90х200х30 - 120 - Диши Корал наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605720</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 200х200х20 - "Вилайн" 1х1</t>
+  </si>
+  <si>
+    <t>4681001605713</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 60х60 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001605706</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 145х215 - 115 - Забавные енотики А+В</t>
+  </si>
+  <si>
+    <t>4681001605690</t>
+  </si>
+  <si>
+    <t>Простыня поплин 150х220 - 115 - Забавные енотики А+В</t>
+  </si>
+  <si>
+    <t>4681001605683</t>
+  </si>
+  <si>
+    <t>Простыня бязь 220х240 - 142 - Сиреневые маки</t>
+  </si>
+  <si>
+    <t>4681001605676</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 2 спальное Евро простыня - "Фельсина"</t>
+  </si>
+  <si>
+    <t>4681001605669</t>
+  </si>
+  <si>
+    <t>Простыня жаккард 220х240 - "Элеонора"</t>
+  </si>
+  <si>
+    <t>4681001605652</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 150х200 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001605645</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х220х40 - "Твист"</t>
+  </si>
+  <si>
+    <t>4681001605638</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель King Size резинка 200х200х30 - Черный блеск наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605621</t>
+  </si>
+  <si>
+    <t>Наволочка микросатин 70х70 - "Небосвод"</t>
+  </si>
+  <si>
+    <t>4681001605614</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х20 - 142 - Антиквариат</t>
+  </si>
+  <si>
+    <t>4681001605607</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - Мечта</t>
+  </si>
+  <si>
+    <t>4681001605591</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 140х200х30 - 142 - Антиквариат наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605584</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра 2 спальное резинка 160х200х20 - "Петкана" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001605577</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 150х220 - 110 - Каори на зеленом</t>
+  </si>
+  <si>
+    <t>4681001605560</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001605553</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 150х200 - Вайт Фейри</t>
+  </si>
+  <si>
+    <t>4681001605546</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - Черный блеск</t>
+  </si>
+  <si>
+    <t>4681001605539</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 140х200х30 - "Стальная тень" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001605522</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 140х200х20 - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001605515</t>
+  </si>
+  <si>
+    <t>Простыня круглая микрофибра резинка 200х200х30 - "Марисоль"</t>
+  </si>
+  <si>
+    <t>4681001605508</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра 1,5 спальное резинка 140х200х30 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001605492</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро-макси - 125 - Тапиока</t>
+  </si>
+  <si>
+    <t>4681001605485</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 145х215 - 125 - Виолет Мореля</t>
+  </si>
+  <si>
+    <t>4681001605478</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 175х215 - 120 - Северные Волки</t>
+  </si>
+  <si>
+    <t>4681001605461</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х50 - 142 - Желтый</t>
+  </si>
+  <si>
+    <t>4681001605454</t>
+  </si>
+  <si>
+    <t>Простыня из бязи 150 х 220 - М - 125 - В ассортименте</t>
+  </si>
+  <si>
+    <t>4681001605447</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 280х280 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001605430</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 175х215 - "Анселмо"</t>
+  </si>
+  <si>
+    <t>4681001605423</t>
+  </si>
+  <si>
+    <t>Наволочка из бязи 50 х 70 - М - 100 - Отбеленная</t>
+  </si>
+  <si>
+    <t>4681001605416</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 220х240 - 120 - Отбеленный</t>
+  </si>
+  <si>
+    <t>4681001605409</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Тонкий Лист"</t>
+  </si>
+  <si>
+    <t>4681001605393</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 4307 Сливочный Страйп 1х1</t>
+  </si>
+  <si>
+    <t>4681001605386</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - R16-70 A</t>
+  </si>
+  <si>
+    <t>4681001605379</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Дзета Ориона</t>
+  </si>
+  <si>
+    <t>4681001605362</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - Морбидецца</t>
+  </si>
+  <si>
+    <t>4681001605355</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 90х200х40 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001605348</t>
+  </si>
+  <si>
+    <t>Простыня жатка 240х260 - "Бирюзовый Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001605331</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Лесная Вуаль"</t>
+  </si>
+  <si>
+    <t>4681001605324</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - 142 - Зверята на желтом</t>
+  </si>
+  <si>
+    <t>4681001605317</t>
+  </si>
+  <si>
+    <t>Простыня бязь 80х120 - 142 - Зверята на желтом</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -21246,18 +21854,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -21281,7 +21881,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -21558,22 +22158,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -21602,7 +22202,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -21610,7 +22210,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -21618,7 +22218,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -21626,7 +22226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -21634,7 +22234,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -21642,7 +22242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -21650,7 +22250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -21658,7 +22258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -21666,7 +22266,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -21674,7 +22274,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -21682,7 +22282,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -21690,7 +22290,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -33474,7 +34074,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -33482,7 +34082,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -33490,7 +34090,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -33498,7 +34098,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -33506,7 +34106,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -33514,7 +34114,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -33522,7 +34122,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -33530,7 +34130,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -33538,7 +34138,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -33546,7 +34146,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -33554,7 +34154,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -33562,7 +34162,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -33570,7 +34170,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -33578,7 +34178,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -33586,7 +34186,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -55603,6 +56203,1117 @@
       </c>
       <c r="C3504" t="s">
         <v>6983</v>
+      </c>
+    </row>
+    <row r="3505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3505" t="s">
+        <v>7058</v>
+      </c>
+      <c r="B3505" t="s">
+        <v>7059</v>
+      </c>
+      <c r="C3505" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3506" t="s">
+        <v>7061</v>
+      </c>
+      <c r="B3506" t="s">
+        <v>7062</v>
+      </c>
+      <c r="C3506" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3507" t="s">
+        <v>7063</v>
+      </c>
+      <c r="B3507" t="s">
+        <v>7064</v>
+      </c>
+      <c r="C3507" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3508" t="s">
+        <v>7065</v>
+      </c>
+      <c r="B3508" t="s">
+        <v>7066</v>
+      </c>
+      <c r="C3508" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3509" t="s">
+        <v>7067</v>
+      </c>
+      <c r="B3509" t="s">
+        <v>7068</v>
+      </c>
+      <c r="C3509" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3510" t="s">
+        <v>7069</v>
+      </c>
+      <c r="B3510" t="s">
+        <v>7070</v>
+      </c>
+      <c r="C3510" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3511" t="s">
+        <v>7071</v>
+      </c>
+      <c r="B3511" t="s">
+        <v>7072</v>
+      </c>
+      <c r="C3511" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3512" t="s">
+        <v>7073</v>
+      </c>
+      <c r="B3512" t="s">
+        <v>7074</v>
+      </c>
+      <c r="C3512" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3513" t="s">
+        <v>7075</v>
+      </c>
+      <c r="B3513" t="s">
+        <v>7076</v>
+      </c>
+      <c r="C3513" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3514" t="s">
+        <v>7077</v>
+      </c>
+      <c r="B3514" t="s">
+        <v>7078</v>
+      </c>
+      <c r="C3514" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3515" t="s">
+        <v>7079</v>
+      </c>
+      <c r="B3515" t="s">
+        <v>7080</v>
+      </c>
+      <c r="C3515" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3516" t="s">
+        <v>7081</v>
+      </c>
+      <c r="B3516" t="s">
+        <v>7082</v>
+      </c>
+      <c r="C3516" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3517" t="s">
+        <v>7083</v>
+      </c>
+      <c r="B3517" t="s">
+        <v>7084</v>
+      </c>
+      <c r="C3517" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3518" t="s">
+        <v>7085</v>
+      </c>
+      <c r="B3518" t="s">
+        <v>7086</v>
+      </c>
+      <c r="C3518" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3519" t="s">
+        <v>7087</v>
+      </c>
+      <c r="B3519" t="s">
+        <v>7088</v>
+      </c>
+      <c r="C3519" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3520" t="s">
+        <v>7089</v>
+      </c>
+      <c r="B3520" t="s">
+        <v>7090</v>
+      </c>
+      <c r="C3520" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3521" t="s">
+        <v>7091</v>
+      </c>
+      <c r="B3521" t="s">
+        <v>7092</v>
+      </c>
+      <c r="C3521" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3522" t="s">
+        <v>7093</v>
+      </c>
+      <c r="B3522" t="s">
+        <v>7094</v>
+      </c>
+      <c r="C3522" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3523" t="s">
+        <v>7095</v>
+      </c>
+      <c r="B3523" t="s">
+        <v>7096</v>
+      </c>
+      <c r="C3523" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3524" t="s">
+        <v>7097</v>
+      </c>
+      <c r="B3524" t="s">
+        <v>7098</v>
+      </c>
+      <c r="C3524" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3525" t="s">
+        <v>7099</v>
+      </c>
+      <c r="B3525" t="s">
+        <v>7100</v>
+      </c>
+      <c r="C3525" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3526" t="s">
+        <v>7101</v>
+      </c>
+      <c r="B3526" t="s">
+        <v>7102</v>
+      </c>
+      <c r="C3526" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3527" t="s">
+        <v>7103</v>
+      </c>
+      <c r="B3527" t="s">
+        <v>7104</v>
+      </c>
+      <c r="C3527" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3528" t="s">
+        <v>7105</v>
+      </c>
+      <c r="B3528" t="s">
+        <v>7106</v>
+      </c>
+      <c r="C3528" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3529" t="s">
+        <v>7107</v>
+      </c>
+      <c r="B3529" t="s">
+        <v>7108</v>
+      </c>
+      <c r="C3529" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3530" t="s">
+        <v>7109</v>
+      </c>
+      <c r="B3530" t="s">
+        <v>7110</v>
+      </c>
+      <c r="C3530" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3531" t="s">
+        <v>7111</v>
+      </c>
+      <c r="B3531" t="s">
+        <v>7112</v>
+      </c>
+      <c r="C3531" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3532" t="s">
+        <v>7113</v>
+      </c>
+      <c r="B3532" t="s">
+        <v>7114</v>
+      </c>
+      <c r="C3532" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3533" t="s">
+        <v>7115</v>
+      </c>
+      <c r="B3533" t="s">
+        <v>7116</v>
+      </c>
+      <c r="C3533" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3534" t="s">
+        <v>7117</v>
+      </c>
+      <c r="B3534" t="s">
+        <v>7118</v>
+      </c>
+      <c r="C3534" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3535" t="s">
+        <v>7119</v>
+      </c>
+      <c r="B3535" t="s">
+        <v>7120</v>
+      </c>
+      <c r="C3535" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3536" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3536" t="s">
+        <v>7121</v>
+      </c>
+      <c r="B3536" t="s">
+        <v>7122</v>
+      </c>
+      <c r="C3536" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3537" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3537" t="s">
+        <v>7123</v>
+      </c>
+      <c r="B3537" t="s">
+        <v>7124</v>
+      </c>
+      <c r="C3537" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3538" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3538" t="s">
+        <v>7125</v>
+      </c>
+      <c r="B3538" t="s">
+        <v>7126</v>
+      </c>
+      <c r="C3538" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3539" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3539" t="s">
+        <v>7127</v>
+      </c>
+      <c r="B3539" t="s">
+        <v>7128</v>
+      </c>
+      <c r="C3539" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3540" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3540" t="s">
+        <v>7129</v>
+      </c>
+      <c r="B3540" t="s">
+        <v>7130</v>
+      </c>
+      <c r="C3540" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3541" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3541" t="s">
+        <v>7131</v>
+      </c>
+      <c r="B3541" t="s">
+        <v>7132</v>
+      </c>
+      <c r="C3541" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3542" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3542" t="s">
+        <v>7133</v>
+      </c>
+      <c r="B3542" t="s">
+        <v>7134</v>
+      </c>
+      <c r="C3542" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3543" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3543" t="s">
+        <v>7135</v>
+      </c>
+      <c r="B3543" t="s">
+        <v>7136</v>
+      </c>
+      <c r="C3543" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3544" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3544" t="s">
+        <v>7137</v>
+      </c>
+      <c r="B3544" t="s">
+        <v>7138</v>
+      </c>
+      <c r="C3544" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3545" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3545" t="s">
+        <v>7139</v>
+      </c>
+      <c r="B3545" t="s">
+        <v>7140</v>
+      </c>
+      <c r="C3545" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3546" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3546" t="s">
+        <v>7141</v>
+      </c>
+      <c r="B3546" t="s">
+        <v>7142</v>
+      </c>
+      <c r="C3546" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3547" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3547" t="s">
+        <v>7143</v>
+      </c>
+      <c r="B3547" t="s">
+        <v>7144</v>
+      </c>
+      <c r="C3547" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3548" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3548" t="s">
+        <v>7145</v>
+      </c>
+      <c r="B3548" t="s">
+        <v>7146</v>
+      </c>
+      <c r="C3548" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3549" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3549" t="s">
+        <v>7147</v>
+      </c>
+      <c r="B3549" t="s">
+        <v>7148</v>
+      </c>
+      <c r="C3549" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3550" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3550" t="s">
+        <v>7149</v>
+      </c>
+      <c r="B3550" t="s">
+        <v>7150</v>
+      </c>
+      <c r="C3550" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3551" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3551" t="s">
+        <v>7151</v>
+      </c>
+      <c r="B3551" t="s">
+        <v>7152</v>
+      </c>
+      <c r="C3551" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3552" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3552" t="s">
+        <v>7153</v>
+      </c>
+      <c r="B3552" t="s">
+        <v>7154</v>
+      </c>
+      <c r="C3552" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3553" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3553" t="s">
+        <v>7155</v>
+      </c>
+      <c r="B3553" t="s">
+        <v>7156</v>
+      </c>
+      <c r="C3553" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3554" t="s">
+        <v>7157</v>
+      </c>
+      <c r="B3554" t="s">
+        <v>7158</v>
+      </c>
+      <c r="C3554" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3555" t="s">
+        <v>7159</v>
+      </c>
+      <c r="B3555" t="s">
+        <v>7160</v>
+      </c>
+      <c r="C3555" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3556" t="s">
+        <v>7161</v>
+      </c>
+      <c r="B3556" t="s">
+        <v>7162</v>
+      </c>
+      <c r="C3556" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3557" t="s">
+        <v>7163</v>
+      </c>
+      <c r="B3557" t="s">
+        <v>7164</v>
+      </c>
+      <c r="C3557" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3558" t="s">
+        <v>7165</v>
+      </c>
+      <c r="B3558" t="s">
+        <v>7166</v>
+      </c>
+      <c r="C3558" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3559" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3559" t="s">
+        <v>7167</v>
+      </c>
+      <c r="B3559" t="s">
+        <v>7168</v>
+      </c>
+      <c r="C3559" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3560" t="s">
+        <v>7169</v>
+      </c>
+      <c r="B3560" t="s">
+        <v>7170</v>
+      </c>
+      <c r="C3560" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3561" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3561" t="s">
+        <v>7171</v>
+      </c>
+      <c r="B3561" t="s">
+        <v>7172</v>
+      </c>
+      <c r="C3561" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3562" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3562" t="s">
+        <v>7173</v>
+      </c>
+      <c r="B3562" t="s">
+        <v>7174</v>
+      </c>
+      <c r="C3562" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3563" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3563" t="s">
+        <v>7175</v>
+      </c>
+      <c r="B3563" t="s">
+        <v>7176</v>
+      </c>
+      <c r="C3563" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3564" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3564" t="s">
+        <v>7177</v>
+      </c>
+      <c r="B3564" t="s">
+        <v>7178</v>
+      </c>
+      <c r="C3564" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3565" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3565" t="s">
+        <v>7179</v>
+      </c>
+      <c r="B3565" t="s">
+        <v>7180</v>
+      </c>
+      <c r="C3565" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3566" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3566" t="s">
+        <v>7181</v>
+      </c>
+      <c r="B3566" t="s">
+        <v>7182</v>
+      </c>
+      <c r="C3566" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3567" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3567" t="s">
+        <v>7183</v>
+      </c>
+      <c r="B3567" t="s">
+        <v>7184</v>
+      </c>
+      <c r="C3567" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3568" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3568" t="s">
+        <v>7185</v>
+      </c>
+      <c r="B3568" t="s">
+        <v>7186</v>
+      </c>
+      <c r="C3568" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3569" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3569" t="s">
+        <v>7187</v>
+      </c>
+      <c r="B3569" t="s">
+        <v>7188</v>
+      </c>
+      <c r="C3569" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3570" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3570" t="s">
+        <v>7189</v>
+      </c>
+      <c r="B3570" t="s">
+        <v>7190</v>
+      </c>
+      <c r="C3570" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3571" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3571" t="s">
+        <v>7191</v>
+      </c>
+      <c r="B3571" t="s">
+        <v>7192</v>
+      </c>
+      <c r="C3571" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3572" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3572" t="s">
+        <v>7193</v>
+      </c>
+      <c r="B3572" t="s">
+        <v>7194</v>
+      </c>
+      <c r="C3572" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3573" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3573" t="s">
+        <v>7195</v>
+      </c>
+      <c r="B3573" t="s">
+        <v>7196</v>
+      </c>
+      <c r="C3573" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3574" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3574" t="s">
+        <v>7197</v>
+      </c>
+      <c r="B3574" t="s">
+        <v>7198</v>
+      </c>
+      <c r="C3574" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3575" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3575" t="s">
+        <v>7199</v>
+      </c>
+      <c r="B3575" t="s">
+        <v>7200</v>
+      </c>
+      <c r="C3575" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3576" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3576" t="s">
+        <v>7201</v>
+      </c>
+      <c r="B3576" t="s">
+        <v>7202</v>
+      </c>
+      <c r="C3576" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3577" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3577" t="s">
+        <v>7203</v>
+      </c>
+      <c r="B3577" t="s">
+        <v>7204</v>
+      </c>
+      <c r="C3577" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3578" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3578" t="s">
+        <v>7205</v>
+      </c>
+      <c r="B3578" t="s">
+        <v>7206</v>
+      </c>
+      <c r="C3578" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3579" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3579" t="s">
+        <v>7207</v>
+      </c>
+      <c r="B3579" t="s">
+        <v>7208</v>
+      </c>
+      <c r="C3579" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3580" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3580" t="s">
+        <v>7209</v>
+      </c>
+      <c r="B3580" t="s">
+        <v>7210</v>
+      </c>
+      <c r="C3580" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3581" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3581" t="s">
+        <v>7211</v>
+      </c>
+      <c r="B3581" t="s">
+        <v>7212</v>
+      </c>
+      <c r="C3581" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3582" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3582" t="s">
+        <v>7213</v>
+      </c>
+      <c r="B3582" t="s">
+        <v>7214</v>
+      </c>
+      <c r="C3582" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3583" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3583" t="s">
+        <v>7215</v>
+      </c>
+      <c r="B3583" t="s">
+        <v>7216</v>
+      </c>
+      <c r="C3583" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3584" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3584" t="s">
+        <v>7217</v>
+      </c>
+      <c r="B3584" t="s">
+        <v>7218</v>
+      </c>
+      <c r="C3584" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3585" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3585" t="s">
+        <v>7219</v>
+      </c>
+      <c r="B3585" t="s">
+        <v>7220</v>
+      </c>
+      <c r="C3585" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3586" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3586" t="s">
+        <v>7221</v>
+      </c>
+      <c r="B3586" t="s">
+        <v>7222</v>
+      </c>
+      <c r="C3586" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3587" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3587" t="s">
+        <v>7223</v>
+      </c>
+      <c r="B3587" t="s">
+        <v>7224</v>
+      </c>
+      <c r="C3587" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3588" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3588" t="s">
+        <v>7225</v>
+      </c>
+      <c r="B3588" t="s">
+        <v>7226</v>
+      </c>
+      <c r="C3588" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3589" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3589" t="s">
+        <v>7227</v>
+      </c>
+      <c r="B3589" t="s">
+        <v>7228</v>
+      </c>
+      <c r="C3589" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3590" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3590" t="s">
+        <v>7229</v>
+      </c>
+      <c r="B3590" t="s">
+        <v>7230</v>
+      </c>
+      <c r="C3590" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3591" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3591" t="s">
+        <v>7231</v>
+      </c>
+      <c r="B3591" t="s">
+        <v>7232</v>
+      </c>
+      <c r="C3591" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3592" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3592" t="s">
+        <v>7233</v>
+      </c>
+      <c r="B3592" t="s">
+        <v>7234</v>
+      </c>
+      <c r="C3592" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3593" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3593" t="s">
+        <v>7235</v>
+      </c>
+      <c r="B3593" t="s">
+        <v>7236</v>
+      </c>
+      <c r="C3593" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3594" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3594" t="s">
+        <v>7237</v>
+      </c>
+      <c r="B3594" t="s">
+        <v>7238</v>
+      </c>
+      <c r="C3594" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3595" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3595" t="s">
+        <v>7239</v>
+      </c>
+      <c r="B3595" t="s">
+        <v>7240</v>
+      </c>
+      <c r="C3595" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3596" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3596" t="s">
+        <v>7241</v>
+      </c>
+      <c r="B3596" t="s">
+        <v>7242</v>
+      </c>
+      <c r="C3596" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3597" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3597" t="s">
+        <v>7243</v>
+      </c>
+      <c r="B3597" t="s">
+        <v>7244</v>
+      </c>
+      <c r="C3597" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3598" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3598" t="s">
+        <v>7245</v>
+      </c>
+      <c r="B3598" t="s">
+        <v>7246</v>
+      </c>
+      <c r="C3598" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3599" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3599" t="s">
+        <v>7247</v>
+      </c>
+      <c r="B3599" t="s">
+        <v>7248</v>
+      </c>
+      <c r="C3599" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3600" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3600" t="s">
+        <v>7249</v>
+      </c>
+      <c r="B3600" t="s">
+        <v>7250</v>
+      </c>
+      <c r="C3600" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3601" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3601" t="s">
+        <v>7251</v>
+      </c>
+      <c r="B3601" t="s">
+        <v>7252</v>
+      </c>
+      <c r="C3601" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3602" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3602" t="s">
+        <v>7253</v>
+      </c>
+      <c r="B3602" t="s">
+        <v>7254</v>
+      </c>
+      <c r="C3602" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3603" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3603" t="s">
+        <v>7255</v>
+      </c>
+      <c r="B3603" t="s">
+        <v>7256</v>
+      </c>
+      <c r="C3603" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3604" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3604" t="s">
+        <v>7257</v>
+      </c>
+      <c r="B3604" t="s">
+        <v>7258</v>
+      </c>
+      <c r="C3604" t="s">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="3605" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3605" t="s">
+        <v>7259</v>
+      </c>
+      <c r="B3605" t="s">
+        <v>7260</v>
+      </c>
+      <c r="C3605" t="s">
+        <v>7060</v>
       </c>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9309" uniqueCount="7261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9414" uniqueCount="7332">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -21800,6 +21800,219 @@
   </si>
   <si>
     <t>Простыня бязь 80х120 - 142 - Зверята на желтом</t>
+  </si>
+  <si>
+    <t>4681001606666</t>
+  </si>
+  <si>
+    <t>Простыня сатин 240х260 - "Персиль"</t>
+  </si>
+  <si>
+    <t>20-04-2026</t>
+  </si>
+  <si>
+    <t>4681001606659</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - Мечта</t>
+  </si>
+  <si>
+    <t>4681001606642</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь семейное резинка 160х200х30 - "Кетеван" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606635</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 240х260 - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001606628</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин King Size семейное резинка 200х200х30 - "Шторм" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606611</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 80х200х10 - 142 - Кленовый</t>
+  </si>
+  <si>
+    <t>4681001606604</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс резинка 90х200х20 - Голубой</t>
+  </si>
+  <si>
+    <t>4681001606598</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс резинка 90х200х20 - "Фантасмагория"</t>
+  </si>
+  <si>
+    <t>4681001606581</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - Апачи</t>
+  </si>
+  <si>
+    <t>4681001606574</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001606567</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 120 - Диши Корал</t>
+  </si>
+  <si>
+    <t>4681001606550</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 160х200х20 - "Глисса" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606543</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - "Миндаль Страйп"</t>
+  </si>
+  <si>
+    <t>4681001606536</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х220х30 - "Миндаль Страйп"</t>
+  </si>
+  <si>
+    <t>4681001606529</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Миндаль Страйп"</t>
+  </si>
+  <si>
+    <t>4681001606512</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Мортис"</t>
+  </si>
+  <si>
+    <t>4681001606505</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 200х220 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001606499</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро - "Ягуар"</t>
+  </si>
+  <si>
+    <t>4681001606482</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х40 - "Грэлис" 1х1</t>
+  </si>
+  <si>
+    <t>4681001606475</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - "Фрезия" 1х1</t>
+  </si>
+  <si>
+    <t>4681001606468</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х40 - "Фрезия" 1х1</t>
+  </si>
+  <si>
+    <t>4681001606451</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 90х200х30 - 135 - Безлунная ночь 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606444</t>
+  </si>
+  <si>
+    <t>Простыня жаккард 200х220 - Вайт Фейри</t>
+  </si>
+  <si>
+    <t>4681001606437</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 175х215 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001606420</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - Гималайские маки</t>
+  </si>
+  <si>
+    <t>4681001606413</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - Белый</t>
+  </si>
+  <si>
+    <t>4681001606406</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 142 - Оранжевый</t>
+  </si>
+  <si>
+    <t>4681001606390</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001606383</t>
+  </si>
+  <si>
+    <t>Простыня бязь 220х240 - 142 - Каори на зеленом</t>
+  </si>
+  <si>
+    <t>4681001606376</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - "Ягуар" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606369</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - Серая умбра наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606352</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - 4234 Морская нимфа</t>
+  </si>
+  <si>
+    <t>4681001606345</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - 4216 Серебро</t>
+  </si>
+  <si>
+    <t>4681001606338</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х40 - "Зайга"</t>
+  </si>
+  <si>
+    <t>4681001606321</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Ажур" наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -57316,6 +57529,391 @@
         <v>7060</v>
       </c>
     </row>
+    <row r="3606" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3606" t="s">
+        <v>7261</v>
+      </c>
+      <c r="B3606" t="s">
+        <v>7262</v>
+      </c>
+      <c r="C3606" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3607" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3607" t="s">
+        <v>7264</v>
+      </c>
+      <c r="B3607" t="s">
+        <v>7265</v>
+      </c>
+      <c r="C3607" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3608" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3608" t="s">
+        <v>7266</v>
+      </c>
+      <c r="B3608" t="s">
+        <v>7267</v>
+      </c>
+      <c r="C3608" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3609" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3609" t="s">
+        <v>7268</v>
+      </c>
+      <c r="B3609" t="s">
+        <v>7269</v>
+      </c>
+      <c r="C3609" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3610" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3610" t="s">
+        <v>7270</v>
+      </c>
+      <c r="B3610" t="s">
+        <v>7271</v>
+      </c>
+      <c r="C3610" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3611" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3611" t="s">
+        <v>7272</v>
+      </c>
+      <c r="B3611" t="s">
+        <v>7273</v>
+      </c>
+      <c r="C3611" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3612" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3612" t="s">
+        <v>7274</v>
+      </c>
+      <c r="B3612" t="s">
+        <v>7275</v>
+      </c>
+      <c r="C3612" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3613" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3613" t="s">
+        <v>7276</v>
+      </c>
+      <c r="B3613" t="s">
+        <v>7277</v>
+      </c>
+      <c r="C3613" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3614" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3614" t="s">
+        <v>7278</v>
+      </c>
+      <c r="B3614" t="s">
+        <v>7279</v>
+      </c>
+      <c r="C3614" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3615" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3615" t="s">
+        <v>7280</v>
+      </c>
+      <c r="B3615" t="s">
+        <v>7281</v>
+      </c>
+      <c r="C3615" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3616" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3616" t="s">
+        <v>7282</v>
+      </c>
+      <c r="B3616" t="s">
+        <v>7283</v>
+      </c>
+      <c r="C3616" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3617" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3617" t="s">
+        <v>7284</v>
+      </c>
+      <c r="B3617" t="s">
+        <v>7285</v>
+      </c>
+      <c r="C3617" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3618" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3618" t="s">
+        <v>7286</v>
+      </c>
+      <c r="B3618" t="s">
+        <v>7287</v>
+      </c>
+      <c r="C3618" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3619" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3619" t="s">
+        <v>7288</v>
+      </c>
+      <c r="B3619" t="s">
+        <v>7289</v>
+      </c>
+      <c r="C3619" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3620" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3620" t="s">
+        <v>7290</v>
+      </c>
+      <c r="B3620" t="s">
+        <v>7291</v>
+      </c>
+      <c r="C3620" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3621" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3621" t="s">
+        <v>7292</v>
+      </c>
+      <c r="B3621" t="s">
+        <v>7293</v>
+      </c>
+      <c r="C3621" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3622" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3622" t="s">
+        <v>7294</v>
+      </c>
+      <c r="B3622" t="s">
+        <v>7295</v>
+      </c>
+      <c r="C3622" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3623" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3623" t="s">
+        <v>7296</v>
+      </c>
+      <c r="B3623" t="s">
+        <v>7297</v>
+      </c>
+      <c r="C3623" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3624" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3624" t="s">
+        <v>7298</v>
+      </c>
+      <c r="B3624" t="s">
+        <v>7299</v>
+      </c>
+      <c r="C3624" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3625" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3625" t="s">
+        <v>7300</v>
+      </c>
+      <c r="B3625" t="s">
+        <v>7301</v>
+      </c>
+      <c r="C3625" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3626" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3626" t="s">
+        <v>7302</v>
+      </c>
+      <c r="B3626" t="s">
+        <v>7303</v>
+      </c>
+      <c r="C3626" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3627" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3627" t="s">
+        <v>7304</v>
+      </c>
+      <c r="B3627" t="s">
+        <v>7305</v>
+      </c>
+      <c r="C3627" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3628" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3628" t="s">
+        <v>7306</v>
+      </c>
+      <c r="B3628" t="s">
+        <v>7307</v>
+      </c>
+      <c r="C3628" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3629" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3629" t="s">
+        <v>7308</v>
+      </c>
+      <c r="B3629" t="s">
+        <v>7309</v>
+      </c>
+      <c r="C3629" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3630" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3630" t="s">
+        <v>7310</v>
+      </c>
+      <c r="B3630" t="s">
+        <v>7311</v>
+      </c>
+      <c r="C3630" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3631" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3631" t="s">
+        <v>7312</v>
+      </c>
+      <c r="B3631" t="s">
+        <v>7313</v>
+      </c>
+      <c r="C3631" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3632" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3632" t="s">
+        <v>7314</v>
+      </c>
+      <c r="B3632" t="s">
+        <v>7315</v>
+      </c>
+      <c r="C3632" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3633" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3633" t="s">
+        <v>7316</v>
+      </c>
+      <c r="B3633" t="s">
+        <v>7317</v>
+      </c>
+      <c r="C3633" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3634" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3634" t="s">
+        <v>7318</v>
+      </c>
+      <c r="B3634" t="s">
+        <v>7319</v>
+      </c>
+      <c r="C3634" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3635" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3635" t="s">
+        <v>7320</v>
+      </c>
+      <c r="B3635" t="s">
+        <v>7321</v>
+      </c>
+      <c r="C3635" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3636" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3636" t="s">
+        <v>7322</v>
+      </c>
+      <c r="B3636" t="s">
+        <v>7323</v>
+      </c>
+      <c r="C3636" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3637" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3637" t="s">
+        <v>7324</v>
+      </c>
+      <c r="B3637" t="s">
+        <v>7325</v>
+      </c>
+      <c r="C3637" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3638" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3638" t="s">
+        <v>7326</v>
+      </c>
+      <c r="B3638" t="s">
+        <v>7327</v>
+      </c>
+      <c r="C3638" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3639" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3639" t="s">
+        <v>7328</v>
+      </c>
+      <c r="B3639" t="s">
+        <v>7329</v>
+      </c>
+      <c r="C3639" t="s">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="3640" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3640" t="s">
+        <v>7330</v>
+      </c>
+      <c r="B3640" t="s">
+        <v>7331</v>
+      </c>
+      <c r="C3640" t="s">
+        <v>7263</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,23 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E6C67C-5D79-4776-A6CA-64B853151FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
+    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9414" uniqueCount="7332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9519" uniqueCount="7403">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -22013,35 +22025,248 @@
   </si>
   <si>
     <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Ажур" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607014</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х30 - 140 - Лагуна 1х1</t>
+  </si>
+  <si>
+    <t>21-04-2026</t>
+  </si>
+  <si>
+    <t>4681001607007</t>
+  </si>
+  <si>
+    <t>Простыня жатка 240х260 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001606994</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное - "Бирюзовый Рельеф" Универсал</t>
+  </si>
+  <si>
+    <t>4681001606987</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - "Крылатые сны"</t>
+  </si>
+  <si>
+    <t>4681001606970</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Жатка семейное - "Письменный Бриз"</t>
+  </si>
+  <si>
+    <t>4681001606963</t>
+  </si>
+  <si>
+    <t>Простыня круглая ранфорс резинка 200х200х30 - Белый</t>
+  </si>
+  <si>
+    <t>4681001606956</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Мелчиоре"</t>
+  </si>
+  <si>
+    <t>4681001606949</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Мелчиоре"</t>
+  </si>
+  <si>
+    <t>4681001606932</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4681001606925</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 50х50 - Пинкроуз</t>
+  </si>
+  <si>
+    <t>4681001606918</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель King Size резинка 200х200х30 - "Золотой блеск"</t>
+  </si>
+  <si>
+    <t>4681001606901</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель King Size резинка 200х200х30 - 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4681001606895</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Аметистовый Шёлк"</t>
+  </si>
+  <si>
+    <t>4681001606888</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - Бирюзовый берег наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606871</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 260х260 - "Милда"</t>
+  </si>
+  <si>
+    <t>4681001606864</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х30 - "Латунь"</t>
+  </si>
+  <si>
+    <t>4681001606857</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Сливочный"</t>
+  </si>
+  <si>
+    <t>4681001606840</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 145х215 - "Оливейт"</t>
+  </si>
+  <si>
+    <t>4681001606833</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - "Нежный Листопад" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606826</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро - 140 - Тенерифе 1х1</t>
+  </si>
+  <si>
+    <t>4681001606819</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро - 135 - Фирюз 1х1</t>
+  </si>
+  <si>
+    <t>4681001606802</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро - Белоснежное</t>
+  </si>
+  <si>
+    <t>4681001606796</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро - 135 - Лаймкват 1х1</t>
+  </si>
+  <si>
+    <t>4681001606789</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро - 125 - "Шампань" 1х1</t>
+  </si>
+  <si>
+    <t>4681001606772</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро - 135 - Марриотт Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001606765</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное резинка 160х200х30 - "Вишня" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001606758</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 300х300 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001606741</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил резинка 120х200х30 - "Сахарная роза"</t>
+  </si>
+  <si>
+    <t>4681001606734</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Кросетта"</t>
+  </si>
+  <si>
+    <t>4681001606727</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Эдвидж"</t>
+  </si>
+  <si>
+    <t>4681001606710</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Кириако"</t>
+  </si>
+  <si>
+    <t>4681001606703</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 60х60 - "Прага"</t>
+  </si>
+  <si>
+    <t>4681001606697</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Мелчиоре"</t>
+  </si>
+  <si>
+    <t>4681001606680</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Граса"</t>
+  </si>
+  <si>
+    <t>4681001606673</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Коррадо"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -22067,10 +22292,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -22094,7 +22327,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -22371,22 +22604,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -22415,7 +22649,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -22423,7 +22657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -22431,7 +22665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -22439,7 +22673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -22447,7 +22681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -22455,7 +22689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -22463,7 +22697,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -22471,7 +22705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -22479,7 +22713,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -22487,7 +22721,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -22495,7 +22729,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -22503,7 +22737,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -34287,7 +34521,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -34295,7 +34529,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -34303,7 +34537,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -34311,7 +34545,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -34319,7 +34553,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -34327,7 +34561,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -34335,7 +34569,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -34343,7 +34577,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -34351,7 +34585,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -34359,7 +34593,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -34367,7 +34601,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -34375,7 +34609,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -34383,7 +34617,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -34391,7 +34625,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -34399,7 +34633,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -57912,6 +58146,391 @@
       </c>
       <c r="C3640" t="s">
         <v>7263</v>
+      </c>
+    </row>
+    <row r="3641" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3641" t="s">
+        <v>7332</v>
+      </c>
+      <c r="B3641" t="s">
+        <v>7333</v>
+      </c>
+      <c r="C3641" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3642" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3642" t="s">
+        <v>7335</v>
+      </c>
+      <c r="B3642" t="s">
+        <v>7336</v>
+      </c>
+      <c r="C3642" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3643" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3643" t="s">
+        <v>7337</v>
+      </c>
+      <c r="B3643" t="s">
+        <v>7338</v>
+      </c>
+      <c r="C3643" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3644" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3644" t="s">
+        <v>7339</v>
+      </c>
+      <c r="B3644" t="s">
+        <v>7340</v>
+      </c>
+      <c r="C3644" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3645" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3645" t="s">
+        <v>7341</v>
+      </c>
+      <c r="B3645" t="s">
+        <v>7342</v>
+      </c>
+      <c r="C3645" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3646" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3646" t="s">
+        <v>7343</v>
+      </c>
+      <c r="B3646" t="s">
+        <v>7344</v>
+      </c>
+      <c r="C3646" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3647" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3647" t="s">
+        <v>7345</v>
+      </c>
+      <c r="B3647" t="s">
+        <v>7346</v>
+      </c>
+      <c r="C3647" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3648" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3648" t="s">
+        <v>7347</v>
+      </c>
+      <c r="B3648" t="s">
+        <v>7348</v>
+      </c>
+      <c r="C3648" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3649" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3649" t="s">
+        <v>7349</v>
+      </c>
+      <c r="B3649" t="s">
+        <v>7350</v>
+      </c>
+      <c r="C3649" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3650" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3650" t="s">
+        <v>7351</v>
+      </c>
+      <c r="B3650" t="s">
+        <v>7352</v>
+      </c>
+      <c r="C3650" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3651" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3651" t="s">
+        <v>7353</v>
+      </c>
+      <c r="B3651" t="s">
+        <v>7354</v>
+      </c>
+      <c r="C3651" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3652" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3652" t="s">
+        <v>7355</v>
+      </c>
+      <c r="B3652" t="s">
+        <v>7356</v>
+      </c>
+      <c r="C3652" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3653" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3653" t="s">
+        <v>7357</v>
+      </c>
+      <c r="B3653" t="s">
+        <v>7358</v>
+      </c>
+      <c r="C3653" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3654" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3654" t="s">
+        <v>7359</v>
+      </c>
+      <c r="B3654" t="s">
+        <v>7360</v>
+      </c>
+      <c r="C3654" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3655" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3655" t="s">
+        <v>7361</v>
+      </c>
+      <c r="B3655" t="s">
+        <v>7362</v>
+      </c>
+      <c r="C3655" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3656" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3656" t="s">
+        <v>7363</v>
+      </c>
+      <c r="B3656" t="s">
+        <v>7364</v>
+      </c>
+      <c r="C3656" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3657" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3657" t="s">
+        <v>7365</v>
+      </c>
+      <c r="B3657" t="s">
+        <v>7366</v>
+      </c>
+      <c r="C3657" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3658" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3658" t="s">
+        <v>7367</v>
+      </c>
+      <c r="B3658" t="s">
+        <v>7368</v>
+      </c>
+      <c r="C3658" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3659" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3659" t="s">
+        <v>7369</v>
+      </c>
+      <c r="B3659" t="s">
+        <v>7370</v>
+      </c>
+      <c r="C3659" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3660" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3660" t="s">
+        <v>7371</v>
+      </c>
+      <c r="B3660" t="s">
+        <v>7372</v>
+      </c>
+      <c r="C3660" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3661" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3661" t="s">
+        <v>7373</v>
+      </c>
+      <c r="B3661" t="s">
+        <v>7374</v>
+      </c>
+      <c r="C3661" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3662" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3662" t="s">
+        <v>7375</v>
+      </c>
+      <c r="B3662" t="s">
+        <v>7376</v>
+      </c>
+      <c r="C3662" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3663" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3663" t="s">
+        <v>7377</v>
+      </c>
+      <c r="B3663" t="s">
+        <v>7378</v>
+      </c>
+      <c r="C3663" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3664" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3664" t="s">
+        <v>7379</v>
+      </c>
+      <c r="B3664" t="s">
+        <v>7380</v>
+      </c>
+      <c r="C3664" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3665" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3665" t="s">
+        <v>7381</v>
+      </c>
+      <c r="B3665" t="s">
+        <v>7382</v>
+      </c>
+      <c r="C3665" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3666" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3666" t="s">
+        <v>7383</v>
+      </c>
+      <c r="B3666" t="s">
+        <v>7384</v>
+      </c>
+      <c r="C3666" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3667" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3667" t="s">
+        <v>7385</v>
+      </c>
+      <c r="B3667" t="s">
+        <v>7386</v>
+      </c>
+      <c r="C3667" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3668" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3668" t="s">
+        <v>7387</v>
+      </c>
+      <c r="B3668" t="s">
+        <v>7388</v>
+      </c>
+      <c r="C3668" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3669" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3669" t="s">
+        <v>7389</v>
+      </c>
+      <c r="B3669" t="s">
+        <v>7390</v>
+      </c>
+      <c r="C3669" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3670" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3670" t="s">
+        <v>7391</v>
+      </c>
+      <c r="B3670" t="s">
+        <v>7392</v>
+      </c>
+      <c r="C3670" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3671" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3671" t="s">
+        <v>7393</v>
+      </c>
+      <c r="B3671" t="s">
+        <v>7394</v>
+      </c>
+      <c r="C3671" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3672" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3672" t="s">
+        <v>7395</v>
+      </c>
+      <c r="B3672" t="s">
+        <v>7396</v>
+      </c>
+      <c r="C3672" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3673" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3673" t="s">
+        <v>7397</v>
+      </c>
+      <c r="B3673" t="s">
+        <v>7398</v>
+      </c>
+      <c r="C3673" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3674" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3674" t="s">
+        <v>7399</v>
+      </c>
+      <c r="B3674" t="s">
+        <v>7400</v>
+      </c>
+      <c r="C3674" t="s">
+        <v>7334</v>
+      </c>
+    </row>
+    <row r="3675" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3675" t="s">
+        <v>7401</v>
+      </c>
+      <c r="B3675" t="s">
+        <v>7402</v>
+      </c>
+      <c r="C3675" t="s">
+        <v>7334</v>
       </c>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,35 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E6C67C-5D79-4776-A6CA-64B853151FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9519" uniqueCount="7403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9621" uniqueCount="7472">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -22238,35 +22226,242 @@
   </si>
   <si>
     <t>Наволочка сатин твил 60х60 - "Коррадо"</t>
+  </si>
+  <si>
+    <t>4681001607359</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 140х200х30 - 142 - Рецепт любви наволочки 50х70</t>
+  </si>
+  <si>
+    <t>22-04-2026</t>
+  </si>
+  <si>
+    <t>4681001607342</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х220 - "Октябрьская берёза"</t>
+  </si>
+  <si>
+    <t>4681001607335</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - Серая умбра</t>
+  </si>
+  <si>
+    <t>4681001607328</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - Серая умбра</t>
+  </si>
+  <si>
+    <t>4681001607311</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 4216 Серебро</t>
+  </si>
+  <si>
+    <t>4681001607304</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - 4216 Серебро</t>
+  </si>
+  <si>
+    <t>4681001607298</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Серая умбра</t>
+  </si>
+  <si>
+    <t>4681001607281</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 60х60 - 142 - Рецепт любви</t>
+  </si>
+  <si>
+    <t>4681001607274</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Сливочно-кремовый</t>
+  </si>
+  <si>
+    <t>4681001607267</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 220х240 - Аква Циан</t>
+  </si>
+  <si>
+    <t>4681001607250</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Санто Стефано</t>
+  </si>
+  <si>
+    <t>4681001607243</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Гуава</t>
+  </si>
+  <si>
+    <t>4681001607236</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Аква Циан</t>
+  </si>
+  <si>
+    <t>4681001607229</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 220х240 - Сливочно-кремовый</t>
+  </si>
+  <si>
+    <t>4681001607212</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 220х240 - Санто Стефано</t>
+  </si>
+  <si>
+    <t>4681001607205</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 140х200х30 - "Этрета" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607199</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 150х220 - 135 - Секондо колоро 1х1</t>
+  </si>
+  <si>
+    <t>4681001607182</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро-макси резинка 180х200х30 - "Кетеван"</t>
+  </si>
+  <si>
+    <t>4681001607175</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Эфирио"</t>
+  </si>
+  <si>
+    <t>4681001607168</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - "Манцель" 3х3 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607151</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х50 - "Солнечные лучи"</t>
+  </si>
+  <si>
+    <t>4681001607144</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 70х70 - "Нева"</t>
+  </si>
+  <si>
+    <t>4681001607137</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х40 - "Элефас"</t>
+  </si>
+  <si>
+    <t>4681001607120</t>
+  </si>
+  <si>
+    <t>Простыня поплин 200х220 - "Бриллиантовые кружева"</t>
+  </si>
+  <si>
+    <t>4681001607113</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х20 - АРТ - DE LUXE - Парижанка</t>
+  </si>
+  <si>
+    <t>4681001607106</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 70х70 - Сиена</t>
+  </si>
+  <si>
+    <t>4681001607090</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "ЭкоФлора"</t>
+  </si>
+  <si>
+    <t>4681001607083</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Лилия флосс"</t>
+  </si>
+  <si>
+    <t>4681001607076</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - Прохлада ментола</t>
+  </si>
+  <si>
+    <t>4681001607069</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 150х200 - 142 - Фикус</t>
+  </si>
+  <si>
+    <t>4681001607052</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 142 - Космические Звёзды</t>
+  </si>
+  <si>
+    <t>4681001607045</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 175х215 - 135 - НамДокМай 1х1</t>
+  </si>
+  <si>
+    <t>4681001607038</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 135 - НамДокМай 1х1</t>
+  </si>
+  <si>
+    <t>4681001607021</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая 80х180 - Мулетон Хлопок</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -22292,18 +22487,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -22327,7 +22514,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -22604,23 +22791,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -22649,7 +22836,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -22657,7 +22844,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -22665,7 +22852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -22673,7 +22860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -22681,7 +22868,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -22689,7 +22876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -22697,7 +22884,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -22705,7 +22892,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -22713,7 +22900,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -22721,7 +22908,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -22729,7 +22916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -22737,7 +22924,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -34521,7 +34708,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -34529,7 +34716,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -34537,7 +34724,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -34545,7 +34732,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -34553,7 +34740,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -34561,7 +34748,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -34569,7 +34756,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -34577,7 +34764,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -34585,7 +34772,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -34593,7 +34780,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -34601,7 +34788,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -34609,7 +34796,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -34617,7 +34804,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -34625,7 +34812,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -34633,7 +34820,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -58531,6 +58718,380 @@
       </c>
       <c r="C3675" t="s">
         <v>7334</v>
+      </c>
+    </row>
+    <row r="3676" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3676" t="s">
+        <v>7403</v>
+      </c>
+      <c r="B3676" t="s">
+        <v>7404</v>
+      </c>
+      <c r="C3676" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3677" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3677" t="s">
+        <v>7406</v>
+      </c>
+      <c r="B3677" t="s">
+        <v>7407</v>
+      </c>
+      <c r="C3677" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3678" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3678" t="s">
+        <v>7408</v>
+      </c>
+      <c r="B3678" t="s">
+        <v>7409</v>
+      </c>
+      <c r="C3678" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3679" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3679" t="s">
+        <v>7410</v>
+      </c>
+      <c r="B3679" t="s">
+        <v>7411</v>
+      </c>
+      <c r="C3679" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3680" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3680" t="s">
+        <v>7412</v>
+      </c>
+      <c r="B3680" t="s">
+        <v>7413</v>
+      </c>
+      <c r="C3680" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3681" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3681" t="s">
+        <v>7414</v>
+      </c>
+      <c r="B3681" t="s">
+        <v>7415</v>
+      </c>
+      <c r="C3681" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3682" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3682" t="s">
+        <v>7416</v>
+      </c>
+      <c r="B3682" t="s">
+        <v>7417</v>
+      </c>
+      <c r="C3682" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3683" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3683" t="s">
+        <v>7418</v>
+      </c>
+      <c r="B3683" t="s">
+        <v>7419</v>
+      </c>
+      <c r="C3683" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3684" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3684" t="s">
+        <v>7420</v>
+      </c>
+      <c r="B3684" t="s">
+        <v>7421</v>
+      </c>
+      <c r="C3684" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3685" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3685" t="s">
+        <v>7422</v>
+      </c>
+      <c r="B3685" t="s">
+        <v>7423</v>
+      </c>
+      <c r="C3685" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3686" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3686" t="s">
+        <v>7424</v>
+      </c>
+      <c r="B3686" t="s">
+        <v>7425</v>
+      </c>
+      <c r="C3686" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3687" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3687" t="s">
+        <v>7426</v>
+      </c>
+      <c r="B3687" t="s">
+        <v>7427</v>
+      </c>
+      <c r="C3687" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3688" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3688" t="s">
+        <v>7428</v>
+      </c>
+      <c r="B3688" t="s">
+        <v>7429</v>
+      </c>
+      <c r="C3688" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3689" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3689" t="s">
+        <v>7430</v>
+      </c>
+      <c r="B3689" t="s">
+        <v>7431</v>
+      </c>
+      <c r="C3689" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3690" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3690" t="s">
+        <v>7432</v>
+      </c>
+      <c r="B3690" t="s">
+        <v>7433</v>
+      </c>
+      <c r="C3690" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3691" t="s">
+        <v>7434</v>
+      </c>
+      <c r="B3691" t="s">
+        <v>7435</v>
+      </c>
+      <c r="C3691" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3692" t="s">
+        <v>7436</v>
+      </c>
+      <c r="B3692" t="s">
+        <v>7437</v>
+      </c>
+      <c r="C3692" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3693" t="s">
+        <v>7438</v>
+      </c>
+      <c r="B3693" t="s">
+        <v>7439</v>
+      </c>
+      <c r="C3693" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3694" t="s">
+        <v>7440</v>
+      </c>
+      <c r="B3694" t="s">
+        <v>7441</v>
+      </c>
+      <c r="C3694" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3695" t="s">
+        <v>7442</v>
+      </c>
+      <c r="B3695" t="s">
+        <v>7443</v>
+      </c>
+      <c r="C3695" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3696" t="s">
+        <v>7444</v>
+      </c>
+      <c r="B3696" t="s">
+        <v>7445</v>
+      </c>
+      <c r="C3696" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3697" t="s">
+        <v>7446</v>
+      </c>
+      <c r="B3697" t="s">
+        <v>7447</v>
+      </c>
+      <c r="C3697" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3698" t="s">
+        <v>7448</v>
+      </c>
+      <c r="B3698" t="s">
+        <v>7449</v>
+      </c>
+      <c r="C3698" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3699" t="s">
+        <v>7450</v>
+      </c>
+      <c r="B3699" t="s">
+        <v>7451</v>
+      </c>
+      <c r="C3699" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3700" t="s">
+        <v>7452</v>
+      </c>
+      <c r="B3700" t="s">
+        <v>7453</v>
+      </c>
+      <c r="C3700" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3701" t="s">
+        <v>7454</v>
+      </c>
+      <c r="B3701" t="s">
+        <v>7455</v>
+      </c>
+      <c r="C3701" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3702" t="s">
+        <v>7456</v>
+      </c>
+      <c r="B3702" t="s">
+        <v>7457</v>
+      </c>
+      <c r="C3702" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3703" t="s">
+        <v>7458</v>
+      </c>
+      <c r="B3703" t="s">
+        <v>7459</v>
+      </c>
+      <c r="C3703" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3704" t="s">
+        <v>7460</v>
+      </c>
+      <c r="B3704" t="s">
+        <v>7461</v>
+      </c>
+      <c r="C3704" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3705" t="s">
+        <v>7462</v>
+      </c>
+      <c r="B3705" t="s">
+        <v>7463</v>
+      </c>
+      <c r="C3705" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3706" t="s">
+        <v>7464</v>
+      </c>
+      <c r="B3706" t="s">
+        <v>7465</v>
+      </c>
+      <c r="C3706" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3707" t="s">
+        <v>7466</v>
+      </c>
+      <c r="B3707" t="s">
+        <v>7467</v>
+      </c>
+      <c r="C3707" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3708" t="s">
+        <v>7468</v>
+      </c>
+      <c r="B3708" t="s">
+        <v>7469</v>
+      </c>
+      <c r="C3708" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="3709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3709" t="s">
+        <v>7470</v>
+      </c>
+      <c r="B3709" t="s">
+        <v>7471</v>
+      </c>
+      <c r="C3709" t="s">
+        <v>7405</v>
       </c>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9621" uniqueCount="7472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9693" uniqueCount="7521">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -22433,6 +22433,153 @@
   </si>
   <si>
     <t>Простыня непромокаемая 80х180 - Мулетон Хлопок</t>
+  </si>
+  <si>
+    <t>4681001607595</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро резинка 160х200х30 - 130 - "Лучезарный" 1х1</t>
+  </si>
+  <si>
+    <t>23-04-2026</t>
+  </si>
+  <si>
+    <t>4681001607588</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное Евро простыня - "Снежный Хищник" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607571</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001607564</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - "Бархатный Букет" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607557</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - 130 - Hotel Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001607540</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 220х240 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001607533</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х50 - "Нефритовый"</t>
+  </si>
+  <si>
+    <t>4681001607526</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - "Сентори"</t>
+  </si>
+  <si>
+    <t>4681001607519</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - Халкидики</t>
+  </si>
+  <si>
+    <t>4681001607502</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Халкидики</t>
+  </si>
+  <si>
+    <t>4681001607496</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 300х300 - Халкидики</t>
+  </si>
+  <si>
+    <t>4681001607489</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х220х40 - "Серис"</t>
+  </si>
+  <si>
+    <t>4681001607472</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 120х200х40 - "Астероид"</t>
+  </si>
+  <si>
+    <t>4681001607465</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси резинка 180х200х30 - "Ночная Симфония" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607458</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 200х200х20 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4681001607441</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 145х215 - "Залив"</t>
+  </si>
+  <si>
+    <t>4681001607434</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х40 - 120 - Северные Волки</t>
+  </si>
+  <si>
+    <t>4681001607427</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 140х200х20 - 120 - Северные Волки</t>
+  </si>
+  <si>
+    <t>4681001607410</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное - "Вилайн" 1х1</t>
+  </si>
+  <si>
+    <t>4681001607403</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 145х215 - "Мелчиоре"</t>
+  </si>
+  <si>
+    <t>4681001607397</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное - "Минори"</t>
+  </si>
+  <si>
+    <t>4681001607380</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - 4292 Кремовый</t>
+  </si>
+  <si>
+    <t>4681001607373</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001607366</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - "Пейл Силвер"</t>
   </si>
 </sst>
 </file>
@@ -59094,6 +59241,270 @@
         <v>7405</v>
       </c>
     </row>
+    <row r="3710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3710" t="s">
+        <v>7472</v>
+      </c>
+      <c r="B3710" t="s">
+        <v>7473</v>
+      </c>
+      <c r="C3710" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3711" t="s">
+        <v>7475</v>
+      </c>
+      <c r="B3711" t="s">
+        <v>7476</v>
+      </c>
+      <c r="C3711" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3712" t="s">
+        <v>7477</v>
+      </c>
+      <c r="B3712" t="s">
+        <v>7478</v>
+      </c>
+      <c r="C3712" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3713" t="s">
+        <v>7479</v>
+      </c>
+      <c r="B3713" t="s">
+        <v>7480</v>
+      </c>
+      <c r="C3713" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3714" t="s">
+        <v>7481</v>
+      </c>
+      <c r="B3714" t="s">
+        <v>7482</v>
+      </c>
+      <c r="C3714" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3715" t="s">
+        <v>7483</v>
+      </c>
+      <c r="B3715" t="s">
+        <v>7484</v>
+      </c>
+      <c r="C3715" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3716" t="s">
+        <v>7485</v>
+      </c>
+      <c r="B3716" t="s">
+        <v>7486</v>
+      </c>
+      <c r="C3716" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3717" t="s">
+        <v>7487</v>
+      </c>
+      <c r="B3717" t="s">
+        <v>7488</v>
+      </c>
+      <c r="C3717" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3718" t="s">
+        <v>7489</v>
+      </c>
+      <c r="B3718" t="s">
+        <v>7490</v>
+      </c>
+      <c r="C3718" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3719" t="s">
+        <v>7491</v>
+      </c>
+      <c r="B3719" t="s">
+        <v>7492</v>
+      </c>
+      <c r="C3719" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3720" t="s">
+        <v>7493</v>
+      </c>
+      <c r="B3720" t="s">
+        <v>7494</v>
+      </c>
+      <c r="C3720" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3721" t="s">
+        <v>7495</v>
+      </c>
+      <c r="B3721" t="s">
+        <v>7496</v>
+      </c>
+      <c r="C3721" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3722" t="s">
+        <v>7497</v>
+      </c>
+      <c r="B3722" t="s">
+        <v>7498</v>
+      </c>
+      <c r="C3722" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3723" t="s">
+        <v>7499</v>
+      </c>
+      <c r="B3723" t="s">
+        <v>7500</v>
+      </c>
+      <c r="C3723" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3724" t="s">
+        <v>7501</v>
+      </c>
+      <c r="B3724" t="s">
+        <v>7502</v>
+      </c>
+      <c r="C3724" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3725" t="s">
+        <v>7503</v>
+      </c>
+      <c r="B3725" t="s">
+        <v>7504</v>
+      </c>
+      <c r="C3725" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3726" t="s">
+        <v>7505</v>
+      </c>
+      <c r="B3726" t="s">
+        <v>7506</v>
+      </c>
+      <c r="C3726" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3727" t="s">
+        <v>7507</v>
+      </c>
+      <c r="B3727" t="s">
+        <v>7508</v>
+      </c>
+      <c r="C3727" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3728" t="s">
+        <v>7509</v>
+      </c>
+      <c r="B3728" t="s">
+        <v>7510</v>
+      </c>
+      <c r="C3728" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3729" t="s">
+        <v>7511</v>
+      </c>
+      <c r="B3729" t="s">
+        <v>7512</v>
+      </c>
+      <c r="C3729" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3730" t="s">
+        <v>7513</v>
+      </c>
+      <c r="B3730" t="s">
+        <v>7514</v>
+      </c>
+      <c r="C3730" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3731" t="s">
+        <v>7515</v>
+      </c>
+      <c r="B3731" t="s">
+        <v>7516</v>
+      </c>
+      <c r="C3731" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3732" t="s">
+        <v>7517</v>
+      </c>
+      <c r="B3732" t="s">
+        <v>7518</v>
+      </c>
+      <c r="C3732" t="s">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="3733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3733" t="s">
+        <v>7519</v>
+      </c>
+      <c r="B3733" t="s">
+        <v>7520</v>
+      </c>
+      <c r="C3733" t="s">
+        <v>7474</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9693" uniqueCount="7521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9738" uniqueCount="7552">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -22580,6 +22580,99 @@
   </si>
   <si>
     <t>Простыня тенсель резинка 180х200х30 - "Пейл Силвер"</t>
+  </si>
+  <si>
+    <t>4681001607731</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро резинка 160х200х30 - "Гармония линий"</t>
+  </si>
+  <si>
+    <t>24-04-2026</t>
+  </si>
+  <si>
+    <t>4681001607724</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро резинка 160х200х30 - "Бирюзовый Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001607717</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро резинка 160х200х30 - "Мятный Квадро"</t>
+  </si>
+  <si>
+    <t>4681001607700</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х40 - 142 - Сиреневые маки</t>
+  </si>
+  <si>
+    <t>4681001607694</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Инспайр"</t>
+  </si>
+  <si>
+    <t>4681001607687</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное резинка 160х200х20 - 80 - Теплые Пожелания наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607670</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - 125 - "Шампань" 1х1</t>
+  </si>
+  <si>
+    <t>4681001607663</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Фернанда"</t>
+  </si>
+  <si>
+    <t>4681001607656</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х250х30 - 130 - "Серый туман" 1х1</t>
+  </si>
+  <si>
+    <t>4681001607649</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Бахати"</t>
+  </si>
+  <si>
+    <t>4681001607632</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 200х220х30 - "Агапия"</t>
+  </si>
+  <si>
+    <t>4681001607625</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 140х200х30 - 130 - Белый</t>
+  </si>
+  <si>
+    <t>4681001607618</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 280х280 - "Небосвод"</t>
+  </si>
+  <si>
+    <t>4681001607601</t>
+  </si>
+  <si>
+    <t>Простыня сатин 300х300 - 125 - Капучино</t>
+  </si>
+  <si>
+    <t>4681001607748</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 150х200 - "Пухлянки"</t>
   </si>
 </sst>
 </file>
@@ -59505,6 +59598,171 @@
         <v>7474</v>
       </c>
     </row>
+    <row r="3734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3734" t="s">
+        <v>7521</v>
+      </c>
+      <c r="B3734" t="s">
+        <v>7522</v>
+      </c>
+      <c r="C3734" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3735" t="s">
+        <v>7524</v>
+      </c>
+      <c r="B3735" t="s">
+        <v>7525</v>
+      </c>
+      <c r="C3735" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3736" t="s">
+        <v>7526</v>
+      </c>
+      <c r="B3736" t="s">
+        <v>7527</v>
+      </c>
+      <c r="C3736" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3737" t="s">
+        <v>7528</v>
+      </c>
+      <c r="B3737" t="s">
+        <v>7529</v>
+      </c>
+      <c r="C3737" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3738" t="s">
+        <v>7530</v>
+      </c>
+      <c r="B3738" t="s">
+        <v>7531</v>
+      </c>
+      <c r="C3738" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3739" t="s">
+        <v>7532</v>
+      </c>
+      <c r="B3739" t="s">
+        <v>7533</v>
+      </c>
+      <c r="C3739" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3740" t="s">
+        <v>7534</v>
+      </c>
+      <c r="B3740" t="s">
+        <v>7535</v>
+      </c>
+      <c r="C3740" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3741" t="s">
+        <v>7536</v>
+      </c>
+      <c r="B3741" t="s">
+        <v>7537</v>
+      </c>
+      <c r="C3741" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3742" t="s">
+        <v>7538</v>
+      </c>
+      <c r="B3742" t="s">
+        <v>7539</v>
+      </c>
+      <c r="C3742" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3743" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3743" t="s">
+        <v>7540</v>
+      </c>
+      <c r="B3743" t="s">
+        <v>7541</v>
+      </c>
+      <c r="C3743" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3744" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3744" t="s">
+        <v>7542</v>
+      </c>
+      <c r="B3744" t="s">
+        <v>7543</v>
+      </c>
+      <c r="C3744" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3745" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3745" t="s">
+        <v>7544</v>
+      </c>
+      <c r="B3745" t="s">
+        <v>7545</v>
+      </c>
+      <c r="C3745" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3746" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3746" t="s">
+        <v>7546</v>
+      </c>
+      <c r="B3746" t="s">
+        <v>7547</v>
+      </c>
+      <c r="C3746" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3747" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3747" t="s">
+        <v>7548</v>
+      </c>
+      <c r="B3747" t="s">
+        <v>7549</v>
+      </c>
+      <c r="C3747" t="s">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="3748" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3748" t="s">
+        <v>7550</v>
+      </c>
+      <c r="B3748" t="s">
+        <v>7551</v>
+      </c>
+      <c r="C3748" t="s">
+        <v>7523</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9738" uniqueCount="7552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9885" uniqueCount="7651">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -22673,6 +22673,303 @@
   </si>
   <si>
     <t>Пододеяльник бязь 150х200 - "Пухлянки"</t>
+  </si>
+  <si>
+    <t>4681001608233</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Дюна"</t>
+  </si>
+  <si>
+    <t>25-04-2026</t>
+  </si>
+  <si>
+    <t>4681001608226</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 210х210х20 - "Лемпи"</t>
+  </si>
+  <si>
+    <t>4681001608219</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 140х200х30 - 142 - Простор поля</t>
+  </si>
+  <si>
+    <t>4681001608202</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - Примавера А+В</t>
+  </si>
+  <si>
+    <t>4681001608196</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 90х200х30 - Малахит наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608189</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Песчаный ветер"</t>
+  </si>
+  <si>
+    <t>4681001608172</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное резинка 160х200х30 - Бертолеция наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608165</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин семейное резинка 180х200х30 - "Бездна" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608158</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х30 - Маренго</t>
+  </si>
+  <si>
+    <t>4681001608141</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х30 - "Голубая дымка"</t>
+  </si>
+  <si>
+    <t>4681001608134</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 80х200х30 - 140 - Агатовый серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001608127</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 140х200х30 - "Джуман"</t>
+  </si>
+  <si>
+    <t>4681001608110</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 140х200х30 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001608103</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 140х200х40 - "Ларион"</t>
+  </si>
+  <si>
+    <t>4681001608097</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 220х240 - "Криола"</t>
+  </si>
+  <si>
+    <t>4681001608080</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001608073</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 220х240 - "Белый Этюд"</t>
+  </si>
+  <si>
+    <t>4681001608066</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное резинка 160х200х30 - "Белый Этюд" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608059</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Фиорелла"</t>
+  </si>
+  <si>
+    <t>4681001608042</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х200 - 140 - Агатовый серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001608035</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х200х30 - 140 - Агатовый серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001608028</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - Прелат А+В наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608011</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль Евро резинка 160х200х30 - 110 - Полнолуние</t>
+  </si>
+  <si>
+    <t>4681001608004</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 2 спальное Евро простыня - "Дино-пати"</t>
+  </si>
+  <si>
+    <t>4681001607991</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное с Евро простыней - М - 120 - Полевые подснежники</t>
+  </si>
+  <si>
+    <t>4681001607984</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 60х60 - "Блю Айс"</t>
+  </si>
+  <si>
+    <t>4681001607977</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Мечта наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607960</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - Воздушная Мелодия А+В</t>
+  </si>
+  <si>
+    <t>4681001607953</t>
+  </si>
+  <si>
+    <t>Простыня жатка 150х220 - "Лесная Мелодия"</t>
+  </si>
+  <si>
+    <t>4681001607946</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное резинка 140х200х30 - "Глария" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607939</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - Петроль</t>
+  </si>
+  <si>
+    <t>4681001607922</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х200х30 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4681001607915</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное - "Симоне" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607908</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001607892</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 70х70 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>4681001607885</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - "Стальной"</t>
+  </si>
+  <si>
+    <t>4681001607878</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 220х220х30 - "Айвелин"</t>
+  </si>
+  <si>
+    <t>4681001607861</t>
+  </si>
+  <si>
+    <t>Простыня бязь 200х220 - Белое облако</t>
+  </si>
+  <si>
+    <t>4681001607854</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - "Мейз"</t>
+  </si>
+  <si>
+    <t>4681001607847</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - "Твист"</t>
+  </si>
+  <si>
+    <t>4681001607830</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное резинка 160х200х20 - 125 - Монохромная Полоса</t>
+  </si>
+  <si>
+    <t>4681001607823</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 50х70 - Вайт Фейри</t>
+  </si>
+  <si>
+    <t>4681001607816</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 50х70 - Снежное королевство</t>
+  </si>
+  <si>
+    <t>4681001607809</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное - "Трендис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001607793</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 70х70 - "Кверча"</t>
+  </si>
+  <si>
+    <t>4681001607786</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - "Песчаный ветер"</t>
+  </si>
+  <si>
+    <t>4681001607779</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Кверча"</t>
+  </si>
+  <si>
+    <t>4681001607762</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 150х220 - 125 - "Шоколад" 1х1 1</t>
+  </si>
+  <si>
+    <t>4681001607755</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Камара"</t>
   </si>
 </sst>
 </file>
@@ -59763,6 +60060,545 @@
         <v>7523</v>
       </c>
     </row>
+    <row r="3749" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3749" t="s">
+        <v>7552</v>
+      </c>
+      <c r="B3749" t="s">
+        <v>7553</v>
+      </c>
+      <c r="C3749" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3750" t="s">
+        <v>7555</v>
+      </c>
+      <c r="B3750" t="s">
+        <v>7556</v>
+      </c>
+      <c r="C3750" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3751" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3751" t="s">
+        <v>7557</v>
+      </c>
+      <c r="B3751" t="s">
+        <v>7558</v>
+      </c>
+      <c r="C3751" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3752" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3752" t="s">
+        <v>7559</v>
+      </c>
+      <c r="B3752" t="s">
+        <v>7560</v>
+      </c>
+      <c r="C3752" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3753" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3753" t="s">
+        <v>7561</v>
+      </c>
+      <c r="B3753" t="s">
+        <v>7562</v>
+      </c>
+      <c r="C3753" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3754" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3754" t="s">
+        <v>7563</v>
+      </c>
+      <c r="B3754" t="s">
+        <v>7564</v>
+      </c>
+      <c r="C3754" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3755" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3755" t="s">
+        <v>7565</v>
+      </c>
+      <c r="B3755" t="s">
+        <v>7566</v>
+      </c>
+      <c r="C3755" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3756" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3756" t="s">
+        <v>7567</v>
+      </c>
+      <c r="B3756" t="s">
+        <v>7568</v>
+      </c>
+      <c r="C3756" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3757" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3757" t="s">
+        <v>7569</v>
+      </c>
+      <c r="B3757" t="s">
+        <v>7570</v>
+      </c>
+      <c r="C3757" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3758" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3758" t="s">
+        <v>7571</v>
+      </c>
+      <c r="B3758" t="s">
+        <v>7572</v>
+      </c>
+      <c r="C3758" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3759" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3759" t="s">
+        <v>7573</v>
+      </c>
+      <c r="B3759" t="s">
+        <v>7574</v>
+      </c>
+      <c r="C3759" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3760" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3760" t="s">
+        <v>7575</v>
+      </c>
+      <c r="B3760" t="s">
+        <v>7576</v>
+      </c>
+      <c r="C3760" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3761" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3761" t="s">
+        <v>7577</v>
+      </c>
+      <c r="B3761" t="s">
+        <v>7578</v>
+      </c>
+      <c r="C3761" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3762" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3762" t="s">
+        <v>7579</v>
+      </c>
+      <c r="B3762" t="s">
+        <v>7580</v>
+      </c>
+      <c r="C3762" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3763" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3763" t="s">
+        <v>7581</v>
+      </c>
+      <c r="B3763" t="s">
+        <v>7582</v>
+      </c>
+      <c r="C3763" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3764" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3764" t="s">
+        <v>7583</v>
+      </c>
+      <c r="B3764" t="s">
+        <v>7584</v>
+      </c>
+      <c r="C3764" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3765" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3765" t="s">
+        <v>7585</v>
+      </c>
+      <c r="B3765" t="s">
+        <v>7586</v>
+      </c>
+      <c r="C3765" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3766" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3766" t="s">
+        <v>7587</v>
+      </c>
+      <c r="B3766" t="s">
+        <v>7588</v>
+      </c>
+      <c r="C3766" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3767" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3767" t="s">
+        <v>7589</v>
+      </c>
+      <c r="B3767" t="s">
+        <v>7590</v>
+      </c>
+      <c r="C3767" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3768" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3768" t="s">
+        <v>7591</v>
+      </c>
+      <c r="B3768" t="s">
+        <v>7592</v>
+      </c>
+      <c r="C3768" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3769" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3769" t="s">
+        <v>7593</v>
+      </c>
+      <c r="B3769" t="s">
+        <v>7594</v>
+      </c>
+      <c r="C3769" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3770" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3770" t="s">
+        <v>7595</v>
+      </c>
+      <c r="B3770" t="s">
+        <v>7596</v>
+      </c>
+      <c r="C3770" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3771" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3771" t="s">
+        <v>7597</v>
+      </c>
+      <c r="B3771" t="s">
+        <v>7598</v>
+      </c>
+      <c r="C3771" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3772" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3772" t="s">
+        <v>7599</v>
+      </c>
+      <c r="B3772" t="s">
+        <v>7600</v>
+      </c>
+      <c r="C3772" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3773" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3773" t="s">
+        <v>7601</v>
+      </c>
+      <c r="B3773" t="s">
+        <v>7602</v>
+      </c>
+      <c r="C3773" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3774" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3774" t="s">
+        <v>7603</v>
+      </c>
+      <c r="B3774" t="s">
+        <v>7604</v>
+      </c>
+      <c r="C3774" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3775" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3775" t="s">
+        <v>7605</v>
+      </c>
+      <c r="B3775" t="s">
+        <v>7606</v>
+      </c>
+      <c r="C3775" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3776" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3776" t="s">
+        <v>7607</v>
+      </c>
+      <c r="B3776" t="s">
+        <v>7608</v>
+      </c>
+      <c r="C3776" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3777" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3777" t="s">
+        <v>7609</v>
+      </c>
+      <c r="B3777" t="s">
+        <v>7610</v>
+      </c>
+      <c r="C3777" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3778" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3778" t="s">
+        <v>7611</v>
+      </c>
+      <c r="B3778" t="s">
+        <v>7612</v>
+      </c>
+      <c r="C3778" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3779" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3779" t="s">
+        <v>7613</v>
+      </c>
+      <c r="B3779" t="s">
+        <v>7614</v>
+      </c>
+      <c r="C3779" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3780" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3780" t="s">
+        <v>7615</v>
+      </c>
+      <c r="B3780" t="s">
+        <v>7616</v>
+      </c>
+      <c r="C3780" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3781" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3781" t="s">
+        <v>7617</v>
+      </c>
+      <c r="B3781" t="s">
+        <v>7618</v>
+      </c>
+      <c r="C3781" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3782" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3782" t="s">
+        <v>7619</v>
+      </c>
+      <c r="B3782" t="s">
+        <v>7620</v>
+      </c>
+      <c r="C3782" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3783" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3783" t="s">
+        <v>7621</v>
+      </c>
+      <c r="B3783" t="s">
+        <v>7622</v>
+      </c>
+      <c r="C3783" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3784" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3784" t="s">
+        <v>7623</v>
+      </c>
+      <c r="B3784" t="s">
+        <v>7624</v>
+      </c>
+      <c r="C3784" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3785" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3785" t="s">
+        <v>7625</v>
+      </c>
+      <c r="B3785" t="s">
+        <v>7626</v>
+      </c>
+      <c r="C3785" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3786" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3786" t="s">
+        <v>7627</v>
+      </c>
+      <c r="B3786" t="s">
+        <v>7628</v>
+      </c>
+      <c r="C3786" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3787" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3787" t="s">
+        <v>7629</v>
+      </c>
+      <c r="B3787" t="s">
+        <v>7630</v>
+      </c>
+      <c r="C3787" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3788" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3788" t="s">
+        <v>7631</v>
+      </c>
+      <c r="B3788" t="s">
+        <v>7632</v>
+      </c>
+      <c r="C3788" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3789" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3789" t="s">
+        <v>7633</v>
+      </c>
+      <c r="B3789" t="s">
+        <v>7634</v>
+      </c>
+      <c r="C3789" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3790" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3790" t="s">
+        <v>7635</v>
+      </c>
+      <c r="B3790" t="s">
+        <v>7636</v>
+      </c>
+      <c r="C3790" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3791" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3791" t="s">
+        <v>7637</v>
+      </c>
+      <c r="B3791" t="s">
+        <v>7638</v>
+      </c>
+      <c r="C3791" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3792" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3792" t="s">
+        <v>7639</v>
+      </c>
+      <c r="B3792" t="s">
+        <v>7640</v>
+      </c>
+      <c r="C3792" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3793" t="s">
+        <v>7641</v>
+      </c>
+      <c r="B3793" t="s">
+        <v>7642</v>
+      </c>
+      <c r="C3793" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3794" t="s">
+        <v>7643</v>
+      </c>
+      <c r="B3794" t="s">
+        <v>7644</v>
+      </c>
+      <c r="C3794" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3795" t="s">
+        <v>7645</v>
+      </c>
+      <c r="B3795" t="s">
+        <v>7646</v>
+      </c>
+      <c r="C3795" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3796" t="s">
+        <v>7647</v>
+      </c>
+      <c r="B3796" t="s">
+        <v>7648</v>
+      </c>
+      <c r="C3796" t="s">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="3797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3797" t="s">
+        <v>7649</v>
+      </c>
+      <c r="B3797" t="s">
+        <v>7650</v>
+      </c>
+      <c r="C3797" t="s">
+        <v>7554</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9885" uniqueCount="7651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10014" uniqueCount="7738">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -22970,6 +22970,267 @@
   </si>
   <si>
     <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001608660</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - Блу Скай наволочки 50х70</t>
+  </si>
+  <si>
+    <t>26-04-2026</t>
+  </si>
+  <si>
+    <t>4681001608653</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Бахати" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608646</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4681001608639</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Сумерин"</t>
+  </si>
+  <si>
+    <t>4681001608622</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Сумерин"</t>
+  </si>
+  <si>
+    <t>4681001608615</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - 4292 Кремовый</t>
+  </si>
+  <si>
+    <t>4681001608608</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х50 - Бертолеция</t>
+  </si>
+  <si>
+    <t>4681001608592</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001608585</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 90х200х20 - 120 - Чёрный мрамор</t>
+  </si>
+  <si>
+    <t>4681001608578</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 175х215 - "Млада"</t>
+  </si>
+  <si>
+    <t>4681001608561</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - Гималайские маки</t>
+  </si>
+  <si>
+    <t>4681001608554</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 210х210х30 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4681001608547</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х200 - 125 - "Сапфир" 1х1</t>
+  </si>
+  <si>
+    <t>4681001608530</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 125 - "Сапфир" 1х1</t>
+  </si>
+  <si>
+    <t>4681001608523</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 125 - "Сапфир" 1х1</t>
+  </si>
+  <si>
+    <t>4681001608516</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - Бирюзовый берег</t>
+  </si>
+  <si>
+    <t>4681001608509</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - Бирюзовый берег</t>
+  </si>
+  <si>
+    <t>4681001608493</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Грей блес</t>
+  </si>
+  <si>
+    <t>4681001608486</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Карибская волна"</t>
+  </si>
+  <si>
+    <t>4681001608479</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин резинка 200х200х30 - 120 - Морион</t>
+  </si>
+  <si>
+    <t>4681001608462</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Думнат"</t>
+  </si>
+  <si>
+    <t>4681001608455</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 240х260 - "Латунь"</t>
+  </si>
+  <si>
+    <t>4681001608448</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 120х200х10 - "Морские приключения"</t>
+  </si>
+  <si>
+    <t>4681001608431</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - 4235 Темно-синий</t>
+  </si>
+  <si>
+    <t>4681001608424</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001608417</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро резинка 160х200х30 - 140 - Кремовая пудра 1х1</t>
+  </si>
+  <si>
+    <t>4681001608400</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 90х200х30 - "Лаззаро" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608394</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 90х200х30 - "Гармония линий" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608387</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 140х200х30 - "Звёздный туман" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608370</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 200х220 - Черничный смузи</t>
+  </si>
+  <si>
+    <t>4681001608363</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - 120 - Зефир</t>
+  </si>
+  <si>
+    <t>4681001608356</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 220х240 - Премиум ТС 320 "Лиминал"</t>
+  </si>
+  <si>
+    <t>4681001608349</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Белый Люкс 1х1</t>
+  </si>
+  <si>
+    <t>4681001608332</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х50 - 140 - Белый Люкс 3х3</t>
+  </si>
+  <si>
+    <t>4681001608325</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - "Мирелле"</t>
+  </si>
+  <si>
+    <t>4681001608318</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х30 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001608301</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 150х200 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001608295</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001608288</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Гуголету"</t>
+  </si>
+  <si>
+    <t>4681001608271</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 70х70 - "Бенигно"</t>
+  </si>
+  <si>
+    <t>4681001608264</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 240х260 - "Агапия"</t>
+  </si>
+  <si>
+    <t>4681001608257</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х60 - "Агапия"</t>
+  </si>
+  <si>
+    <t>4681001608240</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 260х260 - "Залив"</t>
   </si>
 </sst>
 </file>
@@ -60599,6 +60860,479 @@
         <v>7554</v>
       </c>
     </row>
+    <row r="3798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3798" t="s">
+        <v>7651</v>
+      </c>
+      <c r="B3798" t="s">
+        <v>7652</v>
+      </c>
+      <c r="C3798" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3799" t="s">
+        <v>7654</v>
+      </c>
+      <c r="B3799" t="s">
+        <v>7655</v>
+      </c>
+      <c r="C3799" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3800" t="s">
+        <v>7656</v>
+      </c>
+      <c r="B3800" t="s">
+        <v>7657</v>
+      </c>
+      <c r="C3800" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3801" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3801" t="s">
+        <v>7658</v>
+      </c>
+      <c r="B3801" t="s">
+        <v>7659</v>
+      </c>
+      <c r="C3801" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3802" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3802" t="s">
+        <v>7660</v>
+      </c>
+      <c r="B3802" t="s">
+        <v>7661</v>
+      </c>
+      <c r="C3802" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3803" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3803" t="s">
+        <v>7662</v>
+      </c>
+      <c r="B3803" t="s">
+        <v>7663</v>
+      </c>
+      <c r="C3803" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3804" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3804" t="s">
+        <v>7664</v>
+      </c>
+      <c r="B3804" t="s">
+        <v>7665</v>
+      </c>
+      <c r="C3804" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3805" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3805" t="s">
+        <v>7666</v>
+      </c>
+      <c r="B3805" t="s">
+        <v>7667</v>
+      </c>
+      <c r="C3805" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3806" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3806" t="s">
+        <v>7668</v>
+      </c>
+      <c r="B3806" t="s">
+        <v>7669</v>
+      </c>
+      <c r="C3806" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3807" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3807" t="s">
+        <v>7670</v>
+      </c>
+      <c r="B3807" t="s">
+        <v>7671</v>
+      </c>
+      <c r="C3807" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3808" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3808" t="s">
+        <v>7672</v>
+      </c>
+      <c r="B3808" t="s">
+        <v>7673</v>
+      </c>
+      <c r="C3808" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3809" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3809" t="s">
+        <v>7674</v>
+      </c>
+      <c r="B3809" t="s">
+        <v>7675</v>
+      </c>
+      <c r="C3809" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3810" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3810" t="s">
+        <v>7676</v>
+      </c>
+      <c r="B3810" t="s">
+        <v>7677</v>
+      </c>
+      <c r="C3810" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3811" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3811" t="s">
+        <v>7678</v>
+      </c>
+      <c r="B3811" t="s">
+        <v>7679</v>
+      </c>
+      <c r="C3811" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3812" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3812" t="s">
+        <v>7680</v>
+      </c>
+      <c r="B3812" t="s">
+        <v>7681</v>
+      </c>
+      <c r="C3812" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3813" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3813" t="s">
+        <v>7682</v>
+      </c>
+      <c r="B3813" t="s">
+        <v>7683</v>
+      </c>
+      <c r="C3813" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3814" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3814" t="s">
+        <v>7684</v>
+      </c>
+      <c r="B3814" t="s">
+        <v>7685</v>
+      </c>
+      <c r="C3814" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3815" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3815" t="s">
+        <v>7686</v>
+      </c>
+      <c r="B3815" t="s">
+        <v>7687</v>
+      </c>
+      <c r="C3815" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3816" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3816" t="s">
+        <v>7688</v>
+      </c>
+      <c r="B3816" t="s">
+        <v>7689</v>
+      </c>
+      <c r="C3816" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3817" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3817" t="s">
+        <v>7690</v>
+      </c>
+      <c r="B3817" t="s">
+        <v>7691</v>
+      </c>
+      <c r="C3817" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3818" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3818" t="s">
+        <v>7692</v>
+      </c>
+      <c r="B3818" t="s">
+        <v>7693</v>
+      </c>
+      <c r="C3818" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3819" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3819" t="s">
+        <v>7694</v>
+      </c>
+      <c r="B3819" t="s">
+        <v>7695</v>
+      </c>
+      <c r="C3819" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3820" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3820" t="s">
+        <v>7696</v>
+      </c>
+      <c r="B3820" t="s">
+        <v>7697</v>
+      </c>
+      <c r="C3820" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3821" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3821" t="s">
+        <v>7698</v>
+      </c>
+      <c r="B3821" t="s">
+        <v>7699</v>
+      </c>
+      <c r="C3821" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3822" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3822" t="s">
+        <v>7700</v>
+      </c>
+      <c r="B3822" t="s">
+        <v>7701</v>
+      </c>
+      <c r="C3822" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3823" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3823" t="s">
+        <v>7702</v>
+      </c>
+      <c r="B3823" t="s">
+        <v>7703</v>
+      </c>
+      <c r="C3823" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3824" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3824" t="s">
+        <v>7704</v>
+      </c>
+      <c r="B3824" t="s">
+        <v>7705</v>
+      </c>
+      <c r="C3824" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3825" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3825" t="s">
+        <v>7706</v>
+      </c>
+      <c r="B3825" t="s">
+        <v>7707</v>
+      </c>
+      <c r="C3825" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3826" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3826" t="s">
+        <v>7708</v>
+      </c>
+      <c r="B3826" t="s">
+        <v>7709</v>
+      </c>
+      <c r="C3826" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3827" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3827" t="s">
+        <v>7710</v>
+      </c>
+      <c r="B3827" t="s">
+        <v>7711</v>
+      </c>
+      <c r="C3827" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3828" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3828" t="s">
+        <v>7712</v>
+      </c>
+      <c r="B3828" t="s">
+        <v>7713</v>
+      </c>
+      <c r="C3828" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3829" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3829" t="s">
+        <v>7714</v>
+      </c>
+      <c r="B3829" t="s">
+        <v>7715</v>
+      </c>
+      <c r="C3829" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3830" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3830" t="s">
+        <v>7716</v>
+      </c>
+      <c r="B3830" t="s">
+        <v>7717</v>
+      </c>
+      <c r="C3830" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3831" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3831" t="s">
+        <v>7718</v>
+      </c>
+      <c r="B3831" t="s">
+        <v>7719</v>
+      </c>
+      <c r="C3831" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3832" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3832" t="s">
+        <v>7720</v>
+      </c>
+      <c r="B3832" t="s">
+        <v>7721</v>
+      </c>
+      <c r="C3832" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3833" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3833" t="s">
+        <v>7722</v>
+      </c>
+      <c r="B3833" t="s">
+        <v>7723</v>
+      </c>
+      <c r="C3833" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3834" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3834" t="s">
+        <v>7724</v>
+      </c>
+      <c r="B3834" t="s">
+        <v>7725</v>
+      </c>
+      <c r="C3834" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3835" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3835" t="s">
+        <v>7726</v>
+      </c>
+      <c r="B3835" t="s">
+        <v>7727</v>
+      </c>
+      <c r="C3835" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3836" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3836" t="s">
+        <v>7728</v>
+      </c>
+      <c r="B3836" t="s">
+        <v>7729</v>
+      </c>
+      <c r="C3836" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3837" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3837" t="s">
+        <v>7730</v>
+      </c>
+      <c r="B3837" t="s">
+        <v>7731</v>
+      </c>
+      <c r="C3837" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3838" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3838" t="s">
+        <v>7732</v>
+      </c>
+      <c r="B3838" t="s">
+        <v>7733</v>
+      </c>
+      <c r="C3838" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3839" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3839" t="s">
+        <v>7734</v>
+      </c>
+      <c r="B3839" t="s">
+        <v>7735</v>
+      </c>
+      <c r="C3839" t="s">
+        <v>7653</v>
+      </c>
+    </row>
+    <row r="3840" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3840" t="s">
+        <v>7736</v>
+      </c>
+      <c r="B3840" t="s">
+        <v>7737</v>
+      </c>
+      <c r="C3840" t="s">
+        <v>7653</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10014" uniqueCount="7738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10113" uniqueCount="7805">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -23231,6 +23231,207 @@
   </si>
   <si>
     <t>Простыня микросатин 260х260 - "Залив"</t>
+  </si>
+  <si>
+    <t>4681001608998</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Эдже"</t>
+  </si>
+  <si>
+    <t>27-04-2026</t>
+  </si>
+  <si>
+    <t>4681001608981</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - "Теодор" Универсал</t>
+  </si>
+  <si>
+    <t>4681001608974</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Милда"</t>
+  </si>
+  <si>
+    <t>4681001608967</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное Евро простыня - Королевский пурпур наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608950</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро резинка 160х200х30 - "Камара" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608943</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х40 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4681001608936</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Лиловый тауп"</t>
+  </si>
+  <si>
+    <t>4681001608929</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Трендис"</t>
+  </si>
+  <si>
+    <t>4681001608912</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Эфирио"</t>
+  </si>
+  <si>
+    <t>4681001608905</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - Кружева на сером</t>
+  </si>
+  <si>
+    <t>4681001608899</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - Небесный Пиксель А+В</t>
+  </si>
+  <si>
+    <t>4681001608882</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Небесный Пиксель А+В</t>
+  </si>
+  <si>
+    <t>4681001608875</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 60х60 - 135 - Дионис 1х1</t>
+  </si>
+  <si>
+    <t>4681001608868</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - Небесный Пиксель А+В</t>
+  </si>
+  <si>
+    <t>4681001608851</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Оранж"</t>
+  </si>
+  <si>
+    <t>4681001608844</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси резинка 180х200х30 - "Макена"</t>
+  </si>
+  <si>
+    <t>4681001608837</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - Уголёк</t>
+  </si>
+  <si>
+    <t>4681001608820</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 220х240 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4681001608813</t>
+  </si>
+  <si>
+    <t>Простыня жатка 220х240 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4681001608806</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4681001608790</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4681001608783</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 200х220 - 125 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001608776</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Дюраль"</t>
+  </si>
+  <si>
+    <t>4681001608769</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 200х220х30 - "Хореография"</t>
+  </si>
+  <si>
+    <t>4681001608752</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 125 - "Черника" 1х1</t>
+  </si>
+  <si>
+    <t>4681001608745</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь семейное резинка 180х200х30 - "Айсу" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608738</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Линнея" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001608721</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 150х200 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001608714</t>
+  </si>
+  <si>
+    <t>Простыня жатка 240х260 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001608707</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 150х200 - "Бирюзовый Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001608691</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001608684</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Бирюзовый Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001608677</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - Крем-брюле</t>
   </si>
 </sst>
 </file>
@@ -61333,6 +61534,369 @@
         <v>7653</v>
       </c>
     </row>
+    <row r="3841" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3841" t="s">
+        <v>7738</v>
+      </c>
+      <c r="B3841" t="s">
+        <v>7739</v>
+      </c>
+      <c r="C3841" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3842" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3842" t="s">
+        <v>7741</v>
+      </c>
+      <c r="B3842" t="s">
+        <v>7742</v>
+      </c>
+      <c r="C3842" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3843" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3843" t="s">
+        <v>7743</v>
+      </c>
+      <c r="B3843" t="s">
+        <v>7744</v>
+      </c>
+      <c r="C3843" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3844" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3844" t="s">
+        <v>7745</v>
+      </c>
+      <c r="B3844" t="s">
+        <v>7746</v>
+      </c>
+      <c r="C3844" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3845" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3845" t="s">
+        <v>7747</v>
+      </c>
+      <c r="B3845" t="s">
+        <v>7748</v>
+      </c>
+      <c r="C3845" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3846" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3846" t="s">
+        <v>7749</v>
+      </c>
+      <c r="B3846" t="s">
+        <v>7750</v>
+      </c>
+      <c r="C3846" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3847" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3847" t="s">
+        <v>7751</v>
+      </c>
+      <c r="B3847" t="s">
+        <v>7752</v>
+      </c>
+      <c r="C3847" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3848" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3848" t="s">
+        <v>7753</v>
+      </c>
+      <c r="B3848" t="s">
+        <v>7754</v>
+      </c>
+      <c r="C3848" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3849" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3849" t="s">
+        <v>7755</v>
+      </c>
+      <c r="B3849" t="s">
+        <v>7756</v>
+      </c>
+      <c r="C3849" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3850" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3850" t="s">
+        <v>7757</v>
+      </c>
+      <c r="B3850" t="s">
+        <v>7758</v>
+      </c>
+      <c r="C3850" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3851" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3851" t="s">
+        <v>7759</v>
+      </c>
+      <c r="B3851" t="s">
+        <v>7760</v>
+      </c>
+      <c r="C3851" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3852" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3852" t="s">
+        <v>7761</v>
+      </c>
+      <c r="B3852" t="s">
+        <v>7762</v>
+      </c>
+      <c r="C3852" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3853" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3853" t="s">
+        <v>7763</v>
+      </c>
+      <c r="B3853" t="s">
+        <v>7764</v>
+      </c>
+      <c r="C3853" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3854" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3854" t="s">
+        <v>7765</v>
+      </c>
+      <c r="B3854" t="s">
+        <v>7766</v>
+      </c>
+      <c r="C3854" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3855" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3855" t="s">
+        <v>7767</v>
+      </c>
+      <c r="B3855" t="s">
+        <v>7768</v>
+      </c>
+      <c r="C3855" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3856" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3856" t="s">
+        <v>7769</v>
+      </c>
+      <c r="B3856" t="s">
+        <v>7770</v>
+      </c>
+      <c r="C3856" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3857" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3857" t="s">
+        <v>7771</v>
+      </c>
+      <c r="B3857" t="s">
+        <v>7772</v>
+      </c>
+      <c r="C3857" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3858" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3858" t="s">
+        <v>7773</v>
+      </c>
+      <c r="B3858" t="s">
+        <v>7774</v>
+      </c>
+      <c r="C3858" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3859" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3859" t="s">
+        <v>7775</v>
+      </c>
+      <c r="B3859" t="s">
+        <v>7776</v>
+      </c>
+      <c r="C3859" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3860" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3860" t="s">
+        <v>7777</v>
+      </c>
+      <c r="B3860" t="s">
+        <v>7778</v>
+      </c>
+      <c r="C3860" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3861" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3861" t="s">
+        <v>7779</v>
+      </c>
+      <c r="B3861" t="s">
+        <v>7780</v>
+      </c>
+      <c r="C3861" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3862" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3862" t="s">
+        <v>7781</v>
+      </c>
+      <c r="B3862" t="s">
+        <v>7782</v>
+      </c>
+      <c r="C3862" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3863" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3863" t="s">
+        <v>7783</v>
+      </c>
+      <c r="B3863" t="s">
+        <v>7784</v>
+      </c>
+      <c r="C3863" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3864" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3864" t="s">
+        <v>7785</v>
+      </c>
+      <c r="B3864" t="s">
+        <v>7786</v>
+      </c>
+      <c r="C3864" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3865" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3865" t="s">
+        <v>7787</v>
+      </c>
+      <c r="B3865" t="s">
+        <v>7788</v>
+      </c>
+      <c r="C3865" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3866" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3866" t="s">
+        <v>7789</v>
+      </c>
+      <c r="B3866" t="s">
+        <v>7790</v>
+      </c>
+      <c r="C3866" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3867" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3867" t="s">
+        <v>7791</v>
+      </c>
+      <c r="B3867" t="s">
+        <v>7792</v>
+      </c>
+      <c r="C3867" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3868" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3868" t="s">
+        <v>7793</v>
+      </c>
+      <c r="B3868" t="s">
+        <v>7794</v>
+      </c>
+      <c r="C3868" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3869" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3869" t="s">
+        <v>7795</v>
+      </c>
+      <c r="B3869" t="s">
+        <v>7796</v>
+      </c>
+      <c r="C3869" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3870" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3870" t="s">
+        <v>7797</v>
+      </c>
+      <c r="B3870" t="s">
+        <v>7798</v>
+      </c>
+      <c r="C3870" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3871" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3871" t="s">
+        <v>7799</v>
+      </c>
+      <c r="B3871" t="s">
+        <v>7800</v>
+      </c>
+      <c r="C3871" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3872" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3872" t="s">
+        <v>7801</v>
+      </c>
+      <c r="B3872" t="s">
+        <v>7802</v>
+      </c>
+      <c r="C3872" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="3873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3873" t="s">
+        <v>7803</v>
+      </c>
+      <c r="B3873" t="s">
+        <v>7804</v>
+      </c>
+      <c r="C3873" t="s">
+        <v>7740</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10113" uniqueCount="7805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10224" uniqueCount="7880">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -23432,6 +23432,231 @@
   </si>
   <si>
     <t>Наволочка поплин 70х70 - Крем-брюле</t>
+  </si>
+  <si>
+    <t>4681001609360</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 175х215 - "Джуман"</t>
+  </si>
+  <si>
+    <t>28-04-2026</t>
+  </si>
+  <si>
+    <t>4681001609353</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - 125 - Хитрые Зайчата на зеленом</t>
+  </si>
+  <si>
+    <t>4681001609346</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 125 - Хитрые Зайчата на зеленом</t>
+  </si>
+  <si>
+    <t>4681001609339</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро резинка 160х200х20 - 142 - Белый Бамбук</t>
+  </si>
+  <si>
+    <t>4681001609322</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - "Морозный туман"</t>
+  </si>
+  <si>
+    <t>4681001609315</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 220х220х40 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001609308</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 - Спящий Мишка на зеленом</t>
+  </si>
+  <si>
+    <t>4681001609292</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - Сарсуэла</t>
+  </si>
+  <si>
+    <t>4681001609285</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 140х200х30 - "Персиль" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609278</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х50 - 140 - Лаванда 1х1</t>
+  </si>
+  <si>
+    <t>4681001609261</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 140 х 200 х 30 - 120 - Чёрный мрамор</t>
+  </si>
+  <si>
+    <t>4681001609254</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х230х30 - 130 - "Лавандула" 1х1</t>
+  </si>
+  <si>
+    <t>4681001609247</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - 130 - "Лавандула" 1х1</t>
+  </si>
+  <si>
+    <t>4681001609230</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 130 - "Лавандула" 1х1</t>
+  </si>
+  <si>
+    <t>4681001609223</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро - "Кетеван" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609216</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Ачиль"</t>
+  </si>
+  <si>
+    <t>4681001609209</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Бенигно"</t>
+  </si>
+  <si>
+    <t>4681001609193</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Ачиль"</t>
+  </si>
+  <si>
+    <t>4681001609186</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Бенигно"</t>
+  </si>
+  <si>
+    <t>4681001609179</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 220х220х30 - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001609162</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - Горчица</t>
+  </si>
+  <si>
+    <t>4681001609155</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 145х215 - "Ягуар"</t>
+  </si>
+  <si>
+    <t>4681001609148</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х30 - Берлинская лазурь</t>
+  </si>
+  <si>
+    <t>4681001609131</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х30 - "Гармония линий"</t>
+  </si>
+  <si>
+    <t>4681001609124</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Гармония линий"</t>
+  </si>
+  <si>
+    <t>4681001609117</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х30 - 135 - "Золотистая ваниль" 1х1</t>
+  </si>
+  <si>
+    <t>4681001609100</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное Евро простыня - "Морозный туман"</t>
+  </si>
+  <si>
+    <t>4681001609094</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 150х200 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001609087</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 175х215 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001609070</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 150х200 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001609063</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 175х215 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001609056</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001609049</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001609032</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 240х260 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001609025</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001609018</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001609001</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х200х30 - "Эдже"</t>
   </si>
 </sst>
 </file>
@@ -61897,6 +62122,413 @@
         <v>7740</v>
       </c>
     </row>
+    <row r="3874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3874" t="s">
+        <v>7805</v>
+      </c>
+      <c r="B3874" t="s">
+        <v>7806</v>
+      </c>
+      <c r="C3874" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3875" t="s">
+        <v>7808</v>
+      </c>
+      <c r="B3875" t="s">
+        <v>7809</v>
+      </c>
+      <c r="C3875" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3876" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3876" t="s">
+        <v>7810</v>
+      </c>
+      <c r="B3876" t="s">
+        <v>7811</v>
+      </c>
+      <c r="C3876" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3877" t="s">
+        <v>7812</v>
+      </c>
+      <c r="B3877" t="s">
+        <v>7813</v>
+      </c>
+      <c r="C3877" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3878" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3878" t="s">
+        <v>7814</v>
+      </c>
+      <c r="B3878" t="s">
+        <v>7815</v>
+      </c>
+      <c r="C3878" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3879" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3879" t="s">
+        <v>7816</v>
+      </c>
+      <c r="B3879" t="s">
+        <v>7817</v>
+      </c>
+      <c r="C3879" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3880" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3880" t="s">
+        <v>7818</v>
+      </c>
+      <c r="B3880" t="s">
+        <v>7819</v>
+      </c>
+      <c r="C3880" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3881" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3881" t="s">
+        <v>7820</v>
+      </c>
+      <c r="B3881" t="s">
+        <v>7821</v>
+      </c>
+      <c r="C3881" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3882" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3882" t="s">
+        <v>7822</v>
+      </c>
+      <c r="B3882" t="s">
+        <v>7823</v>
+      </c>
+      <c r="C3882" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3883" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3883" t="s">
+        <v>7824</v>
+      </c>
+      <c r="B3883" t="s">
+        <v>7825</v>
+      </c>
+      <c r="C3883" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3884" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3884" t="s">
+        <v>7826</v>
+      </c>
+      <c r="B3884" t="s">
+        <v>7827</v>
+      </c>
+      <c r="C3884" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3885" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3885" t="s">
+        <v>7828</v>
+      </c>
+      <c r="B3885" t="s">
+        <v>7829</v>
+      </c>
+      <c r="C3885" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3886" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3886" t="s">
+        <v>7830</v>
+      </c>
+      <c r="B3886" t="s">
+        <v>7831</v>
+      </c>
+      <c r="C3886" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3887" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3887" t="s">
+        <v>7832</v>
+      </c>
+      <c r="B3887" t="s">
+        <v>7833</v>
+      </c>
+      <c r="C3887" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3888" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3888" t="s">
+        <v>7834</v>
+      </c>
+      <c r="B3888" t="s">
+        <v>7835</v>
+      </c>
+      <c r="C3888" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3889" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3889" t="s">
+        <v>7836</v>
+      </c>
+      <c r="B3889" t="s">
+        <v>7837</v>
+      </c>
+      <c r="C3889" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3890" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3890" t="s">
+        <v>7838</v>
+      </c>
+      <c r="B3890" t="s">
+        <v>7839</v>
+      </c>
+      <c r="C3890" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3891" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3891" t="s">
+        <v>7840</v>
+      </c>
+      <c r="B3891" t="s">
+        <v>7841</v>
+      </c>
+      <c r="C3891" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3892" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3892" t="s">
+        <v>7842</v>
+      </c>
+      <c r="B3892" t="s">
+        <v>7843</v>
+      </c>
+      <c r="C3892" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3893" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3893" t="s">
+        <v>7844</v>
+      </c>
+      <c r="B3893" t="s">
+        <v>7845</v>
+      </c>
+      <c r="C3893" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3894" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3894" t="s">
+        <v>7846</v>
+      </c>
+      <c r="B3894" t="s">
+        <v>7847</v>
+      </c>
+      <c r="C3894" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3895" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3895" t="s">
+        <v>7848</v>
+      </c>
+      <c r="B3895" t="s">
+        <v>7849</v>
+      </c>
+      <c r="C3895" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3896" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3896" t="s">
+        <v>7850</v>
+      </c>
+      <c r="B3896" t="s">
+        <v>7851</v>
+      </c>
+      <c r="C3896" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3897" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3897" t="s">
+        <v>7852</v>
+      </c>
+      <c r="B3897" t="s">
+        <v>7853</v>
+      </c>
+      <c r="C3897" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3898" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3898" t="s">
+        <v>7854</v>
+      </c>
+      <c r="B3898" t="s">
+        <v>7855</v>
+      </c>
+      <c r="C3898" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3899" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3899" t="s">
+        <v>7856</v>
+      </c>
+      <c r="B3899" t="s">
+        <v>7857</v>
+      </c>
+      <c r="C3899" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3900" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3900" t="s">
+        <v>7858</v>
+      </c>
+      <c r="B3900" t="s">
+        <v>7859</v>
+      </c>
+      <c r="C3900" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3901" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3901" t="s">
+        <v>7860</v>
+      </c>
+      <c r="B3901" t="s">
+        <v>7861</v>
+      </c>
+      <c r="C3901" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3902" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3902" t="s">
+        <v>7862</v>
+      </c>
+      <c r="B3902" t="s">
+        <v>7863</v>
+      </c>
+      <c r="C3902" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3903" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3903" t="s">
+        <v>7864</v>
+      </c>
+      <c r="B3903" t="s">
+        <v>7865</v>
+      </c>
+      <c r="C3903" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3904" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3904" t="s">
+        <v>7866</v>
+      </c>
+      <c r="B3904" t="s">
+        <v>7867</v>
+      </c>
+      <c r="C3904" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3905" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3905" t="s">
+        <v>7868</v>
+      </c>
+      <c r="B3905" t="s">
+        <v>7869</v>
+      </c>
+      <c r="C3905" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3906" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3906" t="s">
+        <v>7870</v>
+      </c>
+      <c r="B3906" t="s">
+        <v>7871</v>
+      </c>
+      <c r="C3906" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3907" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3907" t="s">
+        <v>7872</v>
+      </c>
+      <c r="B3907" t="s">
+        <v>7873</v>
+      </c>
+      <c r="C3907" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3908" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3908" t="s">
+        <v>7874</v>
+      </c>
+      <c r="B3908" t="s">
+        <v>7875</v>
+      </c>
+      <c r="C3908" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3909" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3909" t="s">
+        <v>7876</v>
+      </c>
+      <c r="B3909" t="s">
+        <v>7877</v>
+      </c>
+      <c r="C3909" t="s">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="3910" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3910" t="s">
+        <v>7878</v>
+      </c>
+      <c r="B3910" t="s">
+        <v>7879</v>
+      </c>
+      <c r="C3910" t="s">
+        <v>7807</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10224" uniqueCount="7880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10227" uniqueCount="7883">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -23657,6 +23657,15 @@
   </si>
   <si>
     <t>Простыня полисатин резинка 200х200х30 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4681001609377</t>
+  </si>
+  <si>
+    <t>Простыня из страйп микрофибры 220 х 240 - М - 85 - Белая, полоска 3х3</t>
+  </si>
+  <si>
+    <t>29-04-2026</t>
   </si>
 </sst>
 </file>
@@ -62529,6 +62538,17 @@
         <v>7807</v>
       </c>
     </row>
+    <row r="3911" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3911" t="s">
+        <v>7880</v>
+      </c>
+      <c r="B3911" t="s">
+        <v>7881</v>
+      </c>
+      <c r="C3911" t="s">
+        <v>7882</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B103D2-A9AD-406E-979E-E5F8F38B2FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
+    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10227" uniqueCount="7883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10338" uniqueCount="7957">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -23666,35 +23667,257 @@
   </si>
   <si>
     <t>29-04-2026</t>
+  </si>
+  <si>
+    <t>4681001609742</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 150х220 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4681001609735</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4681001609728</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 70х70 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001609711</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро резинка 160х200х30 - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001609704</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - "Мортис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609698</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин семейное резинка 160х200х30 - "Золти" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609681</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х200 - Премиум ТС 320 "Юсан"</t>
+  </si>
+  <si>
+    <t>4681001609674</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 240х260 - 224 Розовый</t>
+  </si>
+  <si>
+    <t>4681001609667</t>
+  </si>
+  <si>
+    <t>Простыня круглая микрофибра резинка 210х210х30 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001609650</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное Евро простыня - 135 - "Золотистая ваниль" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609643</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин-жаккард Евро - Треббиано</t>
+  </si>
+  <si>
+    <t>4681001609636</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - 142 - Фуксин</t>
+  </si>
+  <si>
+    <t>4681001609629</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Дюраль" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609612</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Лемпи"</t>
+  </si>
+  <si>
+    <t>4681001609605</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х50 - Кайбаб</t>
+  </si>
+  <si>
+    <t>4681001609599</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - 4393 Темно-серый</t>
+  </si>
+  <si>
+    <t>4681001609582</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - 129 Темно-зеленый</t>
+  </si>
+  <si>
+    <t>4681001609575</t>
+  </si>
+  <si>
+    <t>Простыня круглая из страйп-сатина на резинке 210 х 210 х 40 - М - 140 - Кремовая пудра 1х1</t>
+  </si>
+  <si>
+    <t>4681001609568</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин резинка 210х210х30 - 120 - Баден Гольд</t>
+  </si>
+  <si>
+    <t>4681001609551</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин твил резинка 210х210х30 - "Солнечные лучи"</t>
+  </si>
+  <si>
+    <t>4681001609544</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 210х210х30 - 125 - "Крем" 1х1</t>
+  </si>
+  <si>
+    <t>4681001609537</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х40 - "Вилайн" 1х1</t>
+  </si>
+  <si>
+    <t>4681001609520</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 200х200 - 142 - Биг Бен</t>
+  </si>
+  <si>
+    <t>4681001609513</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил семейное резинка 160х200х30 - "Граса" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609506</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил семейное резинка 160х200х30 - "Арника" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609490</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4681001609483</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 300х300 - Пастельно-розовый</t>
+  </si>
+  <si>
+    <t>4681001609476</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Matte Dark Grey</t>
+  </si>
+  <si>
+    <t>4681001609469</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 200х220 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001609452</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Прелат А+В</t>
+  </si>
+  <si>
+    <t>4681001609445</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 175х215 - Прелат А+В</t>
+  </si>
+  <si>
+    <t>4681001609438</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 200х200 - Палладион</t>
+  </si>
+  <si>
+    <t>4681001609421</t>
+  </si>
+  <si>
+    <t>Простыня поплин 100х150 - "Принцесса"</t>
+  </si>
+  <si>
+    <t>4681001609414</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - 120 - Кремовый Бутон</t>
+  </si>
+  <si>
+    <t>4681001609407</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х200 - "Синтера" 1х1</t>
+  </si>
+  <si>
+    <t>4681001609391</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х50 - 135 - Мокрый асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4681001609384</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 70х70 - Графит (меланж)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -23720,10 +23943,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -23747,7 +23978,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -24024,9 +24255,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
@@ -24034,13 +24265,13 @@
     <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -24069,7 +24300,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -24077,7 +24308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -24085,7 +24316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -24093,7 +24324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -24101,7 +24332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -24109,7 +24340,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -24117,7 +24348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -24125,7 +24356,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -24133,7 +24364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -24141,7 +24372,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -24149,7 +24380,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -24157,7 +24388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -35941,7 +36172,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -35949,7 +36180,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -35957,7 +36188,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -35965,7 +36196,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -35973,7 +36204,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -35981,7 +36212,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -35989,7 +36220,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -35997,7 +36228,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -36005,7 +36236,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -36013,7 +36244,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -36021,7 +36252,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -36029,7 +36260,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -36037,7 +36268,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -36045,7 +36276,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -36053,7 +36284,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -62546,6 +62777,413 @@
         <v>7881</v>
       </c>
       <c r="C3911" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3912" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3912" t="s">
+        <v>7883</v>
+      </c>
+      <c r="B3912" t="s">
+        <v>7884</v>
+      </c>
+      <c r="C3912" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3913" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3913" t="s">
+        <v>7885</v>
+      </c>
+      <c r="B3913" t="s">
+        <v>7886</v>
+      </c>
+      <c r="C3913" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3914" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3914" t="s">
+        <v>7887</v>
+      </c>
+      <c r="B3914" t="s">
+        <v>7888</v>
+      </c>
+      <c r="C3914" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3915" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3915" t="s">
+        <v>7889</v>
+      </c>
+      <c r="B3915" t="s">
+        <v>7890</v>
+      </c>
+      <c r="C3915" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3916" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3916" t="s">
+        <v>7891</v>
+      </c>
+      <c r="B3916" t="s">
+        <v>7892</v>
+      </c>
+      <c r="C3916" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3917" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3917" t="s">
+        <v>7893</v>
+      </c>
+      <c r="B3917" t="s">
+        <v>7894</v>
+      </c>
+      <c r="C3917" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3918" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3918" t="s">
+        <v>7895</v>
+      </c>
+      <c r="B3918" t="s">
+        <v>7896</v>
+      </c>
+      <c r="C3918" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3919" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3919" t="s">
+        <v>7897</v>
+      </c>
+      <c r="B3919" t="s">
+        <v>7898</v>
+      </c>
+      <c r="C3919" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3920" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3920" t="s">
+        <v>7899</v>
+      </c>
+      <c r="B3920" t="s">
+        <v>7900</v>
+      </c>
+      <c r="C3920" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3921" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3921" t="s">
+        <v>7901</v>
+      </c>
+      <c r="B3921" t="s">
+        <v>7902</v>
+      </c>
+      <c r="C3921" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3922" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3922" t="s">
+        <v>7903</v>
+      </c>
+      <c r="B3922" t="s">
+        <v>7904</v>
+      </c>
+      <c r="C3922" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3923" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3923" t="s">
+        <v>7905</v>
+      </c>
+      <c r="B3923" t="s">
+        <v>7906</v>
+      </c>
+      <c r="C3923" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3924" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3924" t="s">
+        <v>7907</v>
+      </c>
+      <c r="B3924" t="s">
+        <v>7908</v>
+      </c>
+      <c r="C3924" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3925" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3925" t="s">
+        <v>7909</v>
+      </c>
+      <c r="B3925" t="s">
+        <v>7910</v>
+      </c>
+      <c r="C3925" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3926" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3926" t="s">
+        <v>7911</v>
+      </c>
+      <c r="B3926" t="s">
+        <v>7912</v>
+      </c>
+      <c r="C3926" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3927" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3927" t="s">
+        <v>7913</v>
+      </c>
+      <c r="B3927" t="s">
+        <v>7914</v>
+      </c>
+      <c r="C3927" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3928" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3928" t="s">
+        <v>7915</v>
+      </c>
+      <c r="B3928" t="s">
+        <v>7916</v>
+      </c>
+      <c r="C3928" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3929" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3929" t="s">
+        <v>7917</v>
+      </c>
+      <c r="B3929" t="s">
+        <v>7918</v>
+      </c>
+      <c r="C3929" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3930" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3930" t="s">
+        <v>7919</v>
+      </c>
+      <c r="B3930" t="s">
+        <v>7920</v>
+      </c>
+      <c r="C3930" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3931" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3931" t="s">
+        <v>7921</v>
+      </c>
+      <c r="B3931" t="s">
+        <v>7922</v>
+      </c>
+      <c r="C3931" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3932" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3932" t="s">
+        <v>7923</v>
+      </c>
+      <c r="B3932" t="s">
+        <v>7924</v>
+      </c>
+      <c r="C3932" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3933" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3933" t="s">
+        <v>7925</v>
+      </c>
+      <c r="B3933" t="s">
+        <v>7926</v>
+      </c>
+      <c r="C3933" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3934" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3934" t="s">
+        <v>7927</v>
+      </c>
+      <c r="B3934" t="s">
+        <v>7928</v>
+      </c>
+      <c r="C3934" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3935" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3935" t="s">
+        <v>7929</v>
+      </c>
+      <c r="B3935" t="s">
+        <v>7930</v>
+      </c>
+      <c r="C3935" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3936" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3936" t="s">
+        <v>7931</v>
+      </c>
+      <c r="B3936" t="s">
+        <v>7932</v>
+      </c>
+      <c r="C3936" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3937" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3937" t="s">
+        <v>7933</v>
+      </c>
+      <c r="B3937" t="s">
+        <v>7934</v>
+      </c>
+      <c r="C3937" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3938" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3938" t="s">
+        <v>7935</v>
+      </c>
+      <c r="B3938" t="s">
+        <v>7936</v>
+      </c>
+      <c r="C3938" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3939" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3939" t="s">
+        <v>7937</v>
+      </c>
+      <c r="B3939" t="s">
+        <v>7938</v>
+      </c>
+      <c r="C3939" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3940" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3940" t="s">
+        <v>7939</v>
+      </c>
+      <c r="B3940" t="s">
+        <v>7940</v>
+      </c>
+      <c r="C3940" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3941" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3941" t="s">
+        <v>7941</v>
+      </c>
+      <c r="B3941" t="s">
+        <v>7942</v>
+      </c>
+      <c r="C3941" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3942" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3942" t="s">
+        <v>7943</v>
+      </c>
+      <c r="B3942" t="s">
+        <v>7944</v>
+      </c>
+      <c r="C3942" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3943" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3943" t="s">
+        <v>7945</v>
+      </c>
+      <c r="B3943" t="s">
+        <v>7946</v>
+      </c>
+      <c r="C3943" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3944" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3944" t="s">
+        <v>7947</v>
+      </c>
+      <c r="B3944" t="s">
+        <v>7948</v>
+      </c>
+      <c r="C3944" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3945" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3945" t="s">
+        <v>7949</v>
+      </c>
+      <c r="B3945" t="s">
+        <v>7950</v>
+      </c>
+      <c r="C3945" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3946" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3946" t="s">
+        <v>7951</v>
+      </c>
+      <c r="B3946" t="s">
+        <v>7952</v>
+      </c>
+      <c r="C3946" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3947" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3947" t="s">
+        <v>7953</v>
+      </c>
+      <c r="B3947" t="s">
+        <v>7954</v>
+      </c>
+      <c r="C3947" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="3948" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3948" t="s">
+        <v>7955</v>
+      </c>
+      <c r="B3948" t="s">
+        <v>7956</v>
+      </c>
+      <c r="C3948" t="s">
         <v>7882</v>
       </c>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B103D2-A9AD-406E-979E-E5F8F38B2FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10338" uniqueCount="7957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10362" uniqueCount="7974">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -23889,35 +23888,86 @@
   </si>
   <si>
     <t>Наволочка варёный хлопок 70х70 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001609827</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х30 - "Элефас"</t>
+  </si>
+  <si>
+    <t>30-04-2026</t>
+  </si>
+  <si>
+    <t>4681001609810</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - Пыльная роза</t>
+  </si>
+  <si>
+    <t>4681001609803</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Черный матовый</t>
+  </si>
+  <si>
+    <t>4681001609797</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - Уголёк</t>
+  </si>
+  <si>
+    <t>4681001609780</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 200х220 - Аргентум</t>
+  </si>
+  <si>
+    <t>4681001609773</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 60х60 - "Небесный глянцевая"</t>
+  </si>
+  <si>
+    <t>4681001609766</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Уголёк</t>
+  </si>
+  <si>
+    <t>4681001609759</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 140х200х30 - "Лунь" 1х1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -23943,18 +23993,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -23978,7 +24020,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -24255,9 +24297,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
@@ -24265,13 +24307,13 @@
     <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -24300,7 +24342,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -24308,7 +24350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -24316,7 +24358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -24324,7 +24366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -24332,7 +24374,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -24340,7 +24382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -24348,7 +24390,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -24356,7 +24398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -24364,7 +24406,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -24372,7 +24414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -24380,7 +24422,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -24388,7 +24430,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -36172,7 +36214,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -36180,7 +36222,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -36188,7 +36230,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -36196,7 +36238,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -36204,7 +36246,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -36212,7 +36254,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -36220,7 +36262,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -36228,7 +36270,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -36236,7 +36278,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -36244,7 +36286,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -36252,7 +36294,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -36260,7 +36302,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -36268,7 +36310,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -36276,7 +36318,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -36284,7 +36326,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -63185,6 +63227,94 @@
       </c>
       <c r="C3948" t="s">
         <v>7882</v>
+      </c>
+    </row>
+    <row r="3949" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3949" t="s">
+        <v>7957</v>
+      </c>
+      <c r="B3949" t="s">
+        <v>7958</v>
+      </c>
+      <c r="C3949" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3950" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3950" t="s">
+        <v>7960</v>
+      </c>
+      <c r="B3950" t="s">
+        <v>7961</v>
+      </c>
+      <c r="C3950" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3951" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3951" t="s">
+        <v>7962</v>
+      </c>
+      <c r="B3951" t="s">
+        <v>7963</v>
+      </c>
+      <c r="C3951" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3952" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3952" t="s">
+        <v>7964</v>
+      </c>
+      <c r="B3952" t="s">
+        <v>7965</v>
+      </c>
+      <c r="C3952" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3953" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3953" t="s">
+        <v>7966</v>
+      </c>
+      <c r="B3953" t="s">
+        <v>7967</v>
+      </c>
+      <c r="C3953" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3954" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3954" t="s">
+        <v>7968</v>
+      </c>
+      <c r="B3954" t="s">
+        <v>7969</v>
+      </c>
+      <c r="C3954" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3955" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3955" t="s">
+        <v>7970</v>
+      </c>
+      <c r="B3955" t="s">
+        <v>7971</v>
+      </c>
+      <c r="C3955" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3956" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3956" t="s">
+        <v>7972</v>
+      </c>
+      <c r="B3956" t="s">
+        <v>7973</v>
+      </c>
+      <c r="C3956" t="s">
+        <v>7959</v>
       </c>
     </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10362" uniqueCount="7974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10407" uniqueCount="8004">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -23939,6 +23939,96 @@
   </si>
   <si>
     <t>Простыня страйп-сатин резинка 140х200х30 - "Лунь" 1х1</t>
+  </si>
+  <si>
+    <t>4681001609957</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 2 спальное резинка 160х200х30 - "Залив" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609940</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 160х200х30 - 120 - Хадусамат</t>
+  </si>
+  <si>
+    <t>4681001609933</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х30 - 140 - Черный янтарь 3х3</t>
+  </si>
+  <si>
+    <t>4681001609926</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 120х200х30 - Сладкий сон (А+В) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609919</t>
+  </si>
+  <si>
+    <t>Наволочка ранфорс 70х70 - "Лиловая нежность"</t>
+  </si>
+  <si>
+    <t>4681001609902</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Горький шоколад наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609896</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 40х40 - Бертолеция</t>
+  </si>
+  <si>
+    <t>4681001609889</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - Белый</t>
+  </si>
+  <si>
+    <t>4681001609872</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Мирелле"</t>
+  </si>
+  <si>
+    <t>4681001609865</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 150х200 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001609858</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 180х200х40 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001609841</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001609834</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 40х60 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001609964</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - "Минори" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001609971</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х40 - 125 - Марсала</t>
   </si>
 </sst>
 </file>
@@ -63317,6 +63407,171 @@
         <v>7959</v>
       </c>
     </row>
+    <row r="3957" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3957" t="s">
+        <v>7974</v>
+      </c>
+      <c r="B3957" t="s">
+        <v>7975</v>
+      </c>
+      <c r="C3957" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3958" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3958" t="s">
+        <v>7976</v>
+      </c>
+      <c r="B3958" t="s">
+        <v>7977</v>
+      </c>
+      <c r="C3958" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3959" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3959" t="s">
+        <v>7978</v>
+      </c>
+      <c r="B3959" t="s">
+        <v>7979</v>
+      </c>
+      <c r="C3959" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3960" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3960" t="s">
+        <v>7980</v>
+      </c>
+      <c r="B3960" t="s">
+        <v>7981</v>
+      </c>
+      <c r="C3960" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3961" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3961" t="s">
+        <v>7982</v>
+      </c>
+      <c r="B3961" t="s">
+        <v>7983</v>
+      </c>
+      <c r="C3961" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3962" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3962" t="s">
+        <v>7984</v>
+      </c>
+      <c r="B3962" t="s">
+        <v>7985</v>
+      </c>
+      <c r="C3962" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3963" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3963" t="s">
+        <v>7986</v>
+      </c>
+      <c r="B3963" t="s">
+        <v>7987</v>
+      </c>
+      <c r="C3963" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3964" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3964" t="s">
+        <v>7988</v>
+      </c>
+      <c r="B3964" t="s">
+        <v>7989</v>
+      </c>
+      <c r="C3964" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3965" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3965" t="s">
+        <v>7990</v>
+      </c>
+      <c r="B3965" t="s">
+        <v>7991</v>
+      </c>
+      <c r="C3965" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3966" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3966" t="s">
+        <v>7992</v>
+      </c>
+      <c r="B3966" t="s">
+        <v>7993</v>
+      </c>
+      <c r="C3966" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3967" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3967" t="s">
+        <v>7994</v>
+      </c>
+      <c r="B3967" t="s">
+        <v>7995</v>
+      </c>
+      <c r="C3967" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3968" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3968" t="s">
+        <v>7996</v>
+      </c>
+      <c r="B3968" t="s">
+        <v>7997</v>
+      </c>
+      <c r="C3968" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3969" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3969" t="s">
+        <v>7998</v>
+      </c>
+      <c r="B3969" t="s">
+        <v>7999</v>
+      </c>
+      <c r="C3969" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3970" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3970" t="s">
+        <v>8000</v>
+      </c>
+      <c r="B3970" t="s">
+        <v>8001</v>
+      </c>
+      <c r="C3970" t="s">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="3971" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3971" t="s">
+        <v>8002</v>
+      </c>
+      <c r="B3971" t="s">
+        <v>8003</v>
+      </c>
+      <c r="C3971" t="s">
+        <v>7959</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10407" uniqueCount="8004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10614" uniqueCount="8143">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -24029,6 +24029,423 @@
   </si>
   <si>
     <t>Наволочка сатин 40х40 - 125 - Марсала</t>
+  </si>
+  <si>
+    <t>4681001610663</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 180х200х30 - 140 - Белый Люкс 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>02-05-2026</t>
+  </si>
+  <si>
+    <t>4681001610656</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - "Лесная Вуаль"</t>
+  </si>
+  <si>
+    <t>4681001610649</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 180х200х30 - "Альваро"</t>
+  </si>
+  <si>
+    <t>4681001610632</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Альваро"</t>
+  </si>
+  <si>
+    <t>4681001610625</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Альваро"</t>
+  </si>
+  <si>
+    <t>4681001610618</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х30 - 140 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001610601</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х30 - 140 - Голубой 1х1</t>
+  </si>
+  <si>
+    <t>4681001610595</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 175х215 - Молочный</t>
+  </si>
+  <si>
+    <t>4681001610588</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001610571</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 60х60 - 110 - Пепита светло-серая</t>
+  </si>
+  <si>
+    <t>4681001610564</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 60х60 - 140 - Белый Лучик</t>
+  </si>
+  <si>
+    <t>4681001610557</t>
+  </si>
+  <si>
+    <t>Простыня жатка 260х260 - "Снежный Хищник"</t>
+  </si>
+  <si>
+    <t>4681001610540</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси резинка 180х200х30 - 140 - Голубой 1х1</t>
+  </si>
+  <si>
+    <t>4681001610533</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Папоротниковый" Универсал</t>
+  </si>
+  <si>
+    <t>4681001610526</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - "Дюмар" 1х1</t>
+  </si>
+  <si>
+    <t>4681001610519</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро-макси резинка 180х200х30 - 135 - Кремово-белый</t>
+  </si>
+  <si>
+    <t>4681001610502</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 220х240 - 120 - Морион</t>
+  </si>
+  <si>
+    <t>4681001610496</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 150х220 - 140 - Мускусная дыня 1х1</t>
+  </si>
+  <si>
+    <t>4681001610489</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 300х300 - "Хризоколла"</t>
+  </si>
+  <si>
+    <t>4681001610472</t>
+  </si>
+  <si>
+    <t>Простыня бязь 180х220 - "Танец крыльев"</t>
+  </si>
+  <si>
+    <t>4681001610465</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 40х60 - "Мишка в лесу"</t>
+  </si>
+  <si>
+    <t>4681001610458</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 1,5 спальное резинка 120х200х30 - "Небосвод"</t>
+  </si>
+  <si>
+    <t>4681001610441</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 160х200х20 - Белый</t>
+  </si>
+  <si>
+    <t>4681001610434</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 180х200х30 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001610427</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001610410</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 200х200х30 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001610403</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - 4235 Темно-синий</t>
+  </si>
+  <si>
+    <t>4681001610397</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х30 - 140 - Кремовая пудра 1х1</t>
+  </si>
+  <si>
+    <t>4681001610380</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х30 - 140 - Агатовый серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001610373</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Думнат"</t>
+  </si>
+  <si>
+    <t>4681001610366</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро-макси резинка 180х200х30 - "Джуман" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610359</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Бертолеция</t>
+  </si>
+  <si>
+    <t>4681001610342</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное резинка 140х200х30 - 140 - Росток 1х1</t>
+  </si>
+  <si>
+    <t>4681001610335</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 140 - Тенерифе 1х1</t>
+  </si>
+  <si>
+    <t>4681001610328</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси резинка 180х200х30 - 80 - Теплые Пожелания наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610311</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 140х200х30 - "Осенний Сон"</t>
+  </si>
+  <si>
+    <t>4681001610304</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - "Пролив" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610298</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Нежный Листопад"</t>
+  </si>
+  <si>
+    <t>4681001610281</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 135 - Шартрез 3х3</t>
+  </si>
+  <si>
+    <t>4681001610274</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 135 - НамДокМай 1х1</t>
+  </si>
+  <si>
+    <t>4681001610267</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х30 - 135 - Кортадерия 1х1</t>
+  </si>
+  <si>
+    <t>4681001610250</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001610243</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Линнея" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610236</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001610229</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001610212</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х200 - "Цветы в Тумане"</t>
+  </si>
+  <si>
+    <t>4681001610205</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Серебряный Папоротник"</t>
+  </si>
+  <si>
+    <t>4681001610199</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - 142 - Желтый</t>
+  </si>
+  <si>
+    <t>4681001610182</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 145х215 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001610175</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 300х300 - "Трендис"</t>
+  </si>
+  <si>
+    <t>4681001610168</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Хрустальный оазис</t>
+  </si>
+  <si>
+    <t>4681001610151</t>
+  </si>
+  <si>
+    <t>Простыня жатка 260х260 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001610144</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - "Калинте" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610137</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - "Веселые Корги"</t>
+  </si>
+  <si>
+    <t>4681001610120</t>
+  </si>
+  <si>
+    <t>Простыня жатка 180х220 - 80 - Теплые Пожелания</t>
+  </si>
+  <si>
+    <t>4681001610113</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Ледяная Мята" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610106</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - 120 - Зефир наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610090</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Потягуш"</t>
+  </si>
+  <si>
+    <t>4681001610083</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное резинка 140х200х30 - "Гармония линий" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610076</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 150х220 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4681001610069</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Марципан" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610052</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 125 - "Индиго" 1х1</t>
+  </si>
+  <si>
+    <t>4681001610045</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 120х200х20 - 115 - Кисята А+В</t>
+  </si>
+  <si>
+    <t>4681001610038</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - Гималайские маки наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610021</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Лемпи" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610014</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное Евро простыня - "Лемпи" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610007</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 145х215 - 135 - Цитрус 3х3</t>
+  </si>
+  <si>
+    <t>4681001609995</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Гармоника"</t>
+  </si>
+  <si>
+    <t>4681001609988</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 220х240 - "Страстный гранат"</t>
   </si>
 </sst>
 </file>
@@ -63572,6 +63989,765 @@
         <v>7959</v>
       </c>
     </row>
+    <row r="3972" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3972" t="s">
+        <v>8004</v>
+      </c>
+      <c r="B3972" t="s">
+        <v>8005</v>
+      </c>
+      <c r="C3972" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3973" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3973" t="s">
+        <v>8007</v>
+      </c>
+      <c r="B3973" t="s">
+        <v>8008</v>
+      </c>
+      <c r="C3973" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3974" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3974" t="s">
+        <v>8009</v>
+      </c>
+      <c r="B3974" t="s">
+        <v>8010</v>
+      </c>
+      <c r="C3974" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3975" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3975" t="s">
+        <v>8011</v>
+      </c>
+      <c r="B3975" t="s">
+        <v>8012</v>
+      </c>
+      <c r="C3975" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3976" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3976" t="s">
+        <v>8013</v>
+      </c>
+      <c r="B3976" t="s">
+        <v>8014</v>
+      </c>
+      <c r="C3976" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3977" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3977" t="s">
+        <v>8015</v>
+      </c>
+      <c r="B3977" t="s">
+        <v>8016</v>
+      </c>
+      <c r="C3977" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3978" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3978" t="s">
+        <v>8017</v>
+      </c>
+      <c r="B3978" t="s">
+        <v>8018</v>
+      </c>
+      <c r="C3978" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3979" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3979" t="s">
+        <v>8019</v>
+      </c>
+      <c r="B3979" t="s">
+        <v>8020</v>
+      </c>
+      <c r="C3979" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3980" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3980" t="s">
+        <v>8021</v>
+      </c>
+      <c r="B3980" t="s">
+        <v>8022</v>
+      </c>
+      <c r="C3980" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3981" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3981" t="s">
+        <v>8023</v>
+      </c>
+      <c r="B3981" t="s">
+        <v>8024</v>
+      </c>
+      <c r="C3981" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3982" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3982" t="s">
+        <v>8025</v>
+      </c>
+      <c r="B3982" t="s">
+        <v>8026</v>
+      </c>
+      <c r="C3982" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3983" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3983" t="s">
+        <v>8027</v>
+      </c>
+      <c r="B3983" t="s">
+        <v>8028</v>
+      </c>
+      <c r="C3983" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3984" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3984" t="s">
+        <v>8029</v>
+      </c>
+      <c r="B3984" t="s">
+        <v>8030</v>
+      </c>
+      <c r="C3984" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3985" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3985" t="s">
+        <v>8031</v>
+      </c>
+      <c r="B3985" t="s">
+        <v>8032</v>
+      </c>
+      <c r="C3985" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3986" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3986" t="s">
+        <v>8033</v>
+      </c>
+      <c r="B3986" t="s">
+        <v>8034</v>
+      </c>
+      <c r="C3986" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3987" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3987" t="s">
+        <v>8035</v>
+      </c>
+      <c r="B3987" t="s">
+        <v>8036</v>
+      </c>
+      <c r="C3987" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3988" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3988" t="s">
+        <v>8037</v>
+      </c>
+      <c r="B3988" t="s">
+        <v>8038</v>
+      </c>
+      <c r="C3988" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3989" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3989" t="s">
+        <v>8039</v>
+      </c>
+      <c r="B3989" t="s">
+        <v>8040</v>
+      </c>
+      <c r="C3989" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3990" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3990" t="s">
+        <v>8041</v>
+      </c>
+      <c r="B3990" t="s">
+        <v>8042</v>
+      </c>
+      <c r="C3990" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3991" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3991" t="s">
+        <v>8043</v>
+      </c>
+      <c r="B3991" t="s">
+        <v>8044</v>
+      </c>
+      <c r="C3991" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3992" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3992" t="s">
+        <v>8045</v>
+      </c>
+      <c r="B3992" t="s">
+        <v>8046</v>
+      </c>
+      <c r="C3992" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3993" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3993" t="s">
+        <v>8047</v>
+      </c>
+      <c r="B3993" t="s">
+        <v>8048</v>
+      </c>
+      <c r="C3993" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3994" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3994" t="s">
+        <v>8049</v>
+      </c>
+      <c r="B3994" t="s">
+        <v>8050</v>
+      </c>
+      <c r="C3994" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3995" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3995" t="s">
+        <v>8051</v>
+      </c>
+      <c r="B3995" t="s">
+        <v>8052</v>
+      </c>
+      <c r="C3995" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3996" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3996" t="s">
+        <v>8053</v>
+      </c>
+      <c r="B3996" t="s">
+        <v>8054</v>
+      </c>
+      <c r="C3996" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3997" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3997" t="s">
+        <v>8055</v>
+      </c>
+      <c r="B3997" t="s">
+        <v>8056</v>
+      </c>
+      <c r="C3997" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3998" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3998" t="s">
+        <v>8057</v>
+      </c>
+      <c r="B3998" t="s">
+        <v>8058</v>
+      </c>
+      <c r="C3998" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="3999" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3999" t="s">
+        <v>8059</v>
+      </c>
+      <c r="B3999" t="s">
+        <v>8060</v>
+      </c>
+      <c r="C3999" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4000" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4000" t="s">
+        <v>8061</v>
+      </c>
+      <c r="B4000" t="s">
+        <v>8062</v>
+      </c>
+      <c r="C4000" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4001" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4001" t="s">
+        <v>8063</v>
+      </c>
+      <c r="B4001" t="s">
+        <v>8064</v>
+      </c>
+      <c r="C4001" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4002" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4002" t="s">
+        <v>8065</v>
+      </c>
+      <c r="B4002" t="s">
+        <v>8066</v>
+      </c>
+      <c r="C4002" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4003" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4003" t="s">
+        <v>8067</v>
+      </c>
+      <c r="B4003" t="s">
+        <v>8068</v>
+      </c>
+      <c r="C4003" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4004" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4004" t="s">
+        <v>8069</v>
+      </c>
+      <c r="B4004" t="s">
+        <v>8070</v>
+      </c>
+      <c r="C4004" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4005" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4005" t="s">
+        <v>8071</v>
+      </c>
+      <c r="B4005" t="s">
+        <v>8072</v>
+      </c>
+      <c r="C4005" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4006" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4006" t="s">
+        <v>8073</v>
+      </c>
+      <c r="B4006" t="s">
+        <v>8074</v>
+      </c>
+      <c r="C4006" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4007" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4007" t="s">
+        <v>8075</v>
+      </c>
+      <c r="B4007" t="s">
+        <v>8076</v>
+      </c>
+      <c r="C4007" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4008" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4008" t="s">
+        <v>8077</v>
+      </c>
+      <c r="B4008" t="s">
+        <v>8078</v>
+      </c>
+      <c r="C4008" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4009" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4009" t="s">
+        <v>8079</v>
+      </c>
+      <c r="B4009" t="s">
+        <v>8080</v>
+      </c>
+      <c r="C4009" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4010" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4010" t="s">
+        <v>8081</v>
+      </c>
+      <c r="B4010" t="s">
+        <v>8082</v>
+      </c>
+      <c r="C4010" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4011" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4011" t="s">
+        <v>8083</v>
+      </c>
+      <c r="B4011" t="s">
+        <v>8084</v>
+      </c>
+      <c r="C4011" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4012" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4012" t="s">
+        <v>8085</v>
+      </c>
+      <c r="B4012" t="s">
+        <v>8086</v>
+      </c>
+      <c r="C4012" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4013" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4013" t="s">
+        <v>8087</v>
+      </c>
+      <c r="B4013" t="s">
+        <v>8088</v>
+      </c>
+      <c r="C4013" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4014" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4014" t="s">
+        <v>8089</v>
+      </c>
+      <c r="B4014" t="s">
+        <v>8090</v>
+      </c>
+      <c r="C4014" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4015" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4015" t="s">
+        <v>8091</v>
+      </c>
+      <c r="B4015" t="s">
+        <v>8092</v>
+      </c>
+      <c r="C4015" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4016" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4016" t="s">
+        <v>8093</v>
+      </c>
+      <c r="B4016" t="s">
+        <v>8094</v>
+      </c>
+      <c r="C4016" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4017" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4017" t="s">
+        <v>8095</v>
+      </c>
+      <c r="B4017" t="s">
+        <v>8096</v>
+      </c>
+      <c r="C4017" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4018" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4018" t="s">
+        <v>8097</v>
+      </c>
+      <c r="B4018" t="s">
+        <v>8098</v>
+      </c>
+      <c r="C4018" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4019" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4019" t="s">
+        <v>8099</v>
+      </c>
+      <c r="B4019" t="s">
+        <v>8100</v>
+      </c>
+      <c r="C4019" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4020" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4020" t="s">
+        <v>8101</v>
+      </c>
+      <c r="B4020" t="s">
+        <v>8102</v>
+      </c>
+      <c r="C4020" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4021" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4021" t="s">
+        <v>8103</v>
+      </c>
+      <c r="B4021" t="s">
+        <v>8104</v>
+      </c>
+      <c r="C4021" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4022" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4022" t="s">
+        <v>8105</v>
+      </c>
+      <c r="B4022" t="s">
+        <v>8106</v>
+      </c>
+      <c r="C4022" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4023" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4023" t="s">
+        <v>8107</v>
+      </c>
+      <c r="B4023" t="s">
+        <v>8108</v>
+      </c>
+      <c r="C4023" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4024" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4024" t="s">
+        <v>8109</v>
+      </c>
+      <c r="B4024" t="s">
+        <v>8110</v>
+      </c>
+      <c r="C4024" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4025" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4025" t="s">
+        <v>8111</v>
+      </c>
+      <c r="B4025" t="s">
+        <v>8112</v>
+      </c>
+      <c r="C4025" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4026" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4026" t="s">
+        <v>8113</v>
+      </c>
+      <c r="B4026" t="s">
+        <v>8114</v>
+      </c>
+      <c r="C4026" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4027" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4027" t="s">
+        <v>8115</v>
+      </c>
+      <c r="B4027" t="s">
+        <v>8116</v>
+      </c>
+      <c r="C4027" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4028" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4028" t="s">
+        <v>8117</v>
+      </c>
+      <c r="B4028" t="s">
+        <v>8118</v>
+      </c>
+      <c r="C4028" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4029" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4029" t="s">
+        <v>8119</v>
+      </c>
+      <c r="B4029" t="s">
+        <v>8120</v>
+      </c>
+      <c r="C4029" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4030" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4030" t="s">
+        <v>8121</v>
+      </c>
+      <c r="B4030" t="s">
+        <v>8122</v>
+      </c>
+      <c r="C4030" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4031" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4031" t="s">
+        <v>8123</v>
+      </c>
+      <c r="B4031" t="s">
+        <v>8124</v>
+      </c>
+      <c r="C4031" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4032" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4032" t="s">
+        <v>8125</v>
+      </c>
+      <c r="B4032" t="s">
+        <v>8126</v>
+      </c>
+      <c r="C4032" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4033" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4033" t="s">
+        <v>8127</v>
+      </c>
+      <c r="B4033" t="s">
+        <v>8128</v>
+      </c>
+      <c r="C4033" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4034" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4034" t="s">
+        <v>8129</v>
+      </c>
+      <c r="B4034" t="s">
+        <v>8130</v>
+      </c>
+      <c r="C4034" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4035" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4035" t="s">
+        <v>8131</v>
+      </c>
+      <c r="B4035" t="s">
+        <v>8132</v>
+      </c>
+      <c r="C4035" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4036" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4036" t="s">
+        <v>8133</v>
+      </c>
+      <c r="B4036" t="s">
+        <v>8134</v>
+      </c>
+      <c r="C4036" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4037" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4037" t="s">
+        <v>8135</v>
+      </c>
+      <c r="B4037" t="s">
+        <v>8136</v>
+      </c>
+      <c r="C4037" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4038" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4038" t="s">
+        <v>8137</v>
+      </c>
+      <c r="B4038" t="s">
+        <v>8138</v>
+      </c>
+      <c r="C4038" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4039" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4039" t="s">
+        <v>8139</v>
+      </c>
+      <c r="B4039" t="s">
+        <v>8140</v>
+      </c>
+      <c r="C4039" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4040" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4040" t="s">
+        <v>8141</v>
+      </c>
+      <c r="B4040" t="s">
+        <v>8142</v>
+      </c>
+      <c r="C4040" t="s">
+        <v>8006</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10614" uniqueCount="8143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10764" uniqueCount="8244">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -24446,6 +24446,309 @@
   </si>
   <si>
     <t>Простыня микросатин 220х240 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4681001611158</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 1,5 спальное резинка 120х200х30 - "Кремневый серый" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>03-05-2026</t>
+  </si>
+  <si>
+    <t>4681001611141</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х40 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4681001611134</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин-жаккард Евро-макси - Солнечное кружево</t>
+  </si>
+  <si>
+    <t>4681001611127</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 125 - "Шампань" 1х1</t>
+  </si>
+  <si>
+    <t>4681001611110</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро-макси - 125 - Дом Периньон наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611103</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок Евро-макси - Ванильный наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611097</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин-жаккард Евро-макси - Солнечное кружево наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611080</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 125 - Шампань 3х3</t>
+  </si>
+  <si>
+    <t>4681001611073</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 125 - Шашки Шампань 0,5х0,5 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611066</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 125 - "Шампань" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611059</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х40 - Розовый Кварцит</t>
+  </si>
+  <si>
+    <t>4681001611042</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 120х200х30 - "Сумерин"</t>
+  </si>
+  <si>
+    <t>4681001611035</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х50 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001611028</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 180х220 - Дымчатый</t>
+  </si>
+  <si>
+    <t>4681001611011</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 180х220 - "Серпентин"</t>
+  </si>
+  <si>
+    <t>4681001611004</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 180х220 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>4681001610991</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 150х220 - "Зелёный Страйп"</t>
+  </si>
+  <si>
+    <t>4681001610984</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра 300х300 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001610977</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин семейное - "Цветы в Тумане"</t>
+  </si>
+  <si>
+    <t>4681001610960</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Ледяная Мята"</t>
+  </si>
+  <si>
+    <t>4681001610953</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - Гималайские маки</t>
+  </si>
+  <si>
+    <t>4681001610946</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Золти"</t>
+  </si>
+  <si>
+    <t>4681001610939</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 220х220х30 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001610922</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 220х220х30 - 4292 Кремовый</t>
+  </si>
+  <si>
+    <t>4681001610915</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 140х200х30 - 125 - "Миндаль" 1х1</t>
+  </si>
+  <si>
+    <t>4681001610908</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 150х220 - "Тирас"</t>
+  </si>
+  <si>
+    <t>4681001610892</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Симоне"</t>
+  </si>
+  <si>
+    <t>4681001610885</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Этайн"</t>
+  </si>
+  <si>
+    <t>4681001610878</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 140х200х40 - 4382 Персик</t>
+  </si>
+  <si>
+    <t>4681001610861</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Этайн"</t>
+  </si>
+  <si>
+    <t>4681001610854</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Симоне"</t>
+  </si>
+  <si>
+    <t>4681001610847</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Воздушное касание"</t>
+  </si>
+  <si>
+    <t>4681001610830</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 150х200 - "Вэспер"</t>
+  </si>
+  <si>
+    <t>4681001610823</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 90х200х10 - 120 - Аморфа</t>
+  </si>
+  <si>
+    <t>4681001610816</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Белый Этюд"</t>
+  </si>
+  <si>
+    <t>4681001610809</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х10 - 142 - Белый</t>
+  </si>
+  <si>
+    <t>4681001610793</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х10 - 120 - Бежевая Латка</t>
+  </si>
+  <si>
+    <t>4681001610786</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Бирюзовый берег</t>
+  </si>
+  <si>
+    <t>4681001610779</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х20 - "Севим"</t>
+  </si>
+  <si>
+    <t>4681001610762</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 1,5 спальное резинка 90х200х30 - "Кремневый серый"</t>
+  </si>
+  <si>
+    <t>4681001610755</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 90х200х30 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001610748</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 90х200х30 - 135 - Платина 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610731</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 1,5 спальное резинка 90х200х30 - "Кремневый серый" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001610724</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - 140 - Чернила 1х1</t>
+  </si>
+  <si>
+    <t>4681001610717</t>
+  </si>
+  <si>
+    <t>Наволочка ранфорс 70х70 - "Ванильный раф"</t>
+  </si>
+  <si>
+    <t>4681001610700</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 145х215 - "Казимира"</t>
+  </si>
+  <si>
+    <t>4681001610694</t>
+  </si>
+  <si>
+    <t>Наволочка ранфорс 50х70 - Голубой</t>
+  </si>
+  <si>
+    <t>4681001610687</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 240х260 - Зеленый чай</t>
+  </si>
+  <si>
+    <t>4681001610670</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 150х200 - 125 - Терракота</t>
+  </si>
+  <si>
+    <t>4681001611165</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - "Лигурия"</t>
   </si>
 </sst>
 </file>
@@ -64748,6 +65051,556 @@
         <v>8006</v>
       </c>
     </row>
+    <row r="4041" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4041" t="s">
+        <v>8143</v>
+      </c>
+      <c r="B4041" t="s">
+        <v>8144</v>
+      </c>
+      <c r="C4041" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4042" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4042" t="s">
+        <v>8146</v>
+      </c>
+      <c r="B4042" t="s">
+        <v>8147</v>
+      </c>
+      <c r="C4042" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4043" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4043" t="s">
+        <v>8148</v>
+      </c>
+      <c r="B4043" t="s">
+        <v>8149</v>
+      </c>
+      <c r="C4043" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4044" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4044" t="s">
+        <v>8150</v>
+      </c>
+      <c r="B4044" t="s">
+        <v>8151</v>
+      </c>
+      <c r="C4044" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4045" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4045" t="s">
+        <v>8152</v>
+      </c>
+      <c r="B4045" t="s">
+        <v>8153</v>
+      </c>
+      <c r="C4045" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4046" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4046" t="s">
+        <v>8154</v>
+      </c>
+      <c r="B4046" t="s">
+        <v>8155</v>
+      </c>
+      <c r="C4046" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4047" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4047" t="s">
+        <v>8156</v>
+      </c>
+      <c r="B4047" t="s">
+        <v>8157</v>
+      </c>
+      <c r="C4047" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4048" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4048" t="s">
+        <v>8158</v>
+      </c>
+      <c r="B4048" t="s">
+        <v>8159</v>
+      </c>
+      <c r="C4048" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4049" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4049" t="s">
+        <v>8160</v>
+      </c>
+      <c r="B4049" t="s">
+        <v>8161</v>
+      </c>
+      <c r="C4049" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4050" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4050" t="s">
+        <v>8162</v>
+      </c>
+      <c r="B4050" t="s">
+        <v>8163</v>
+      </c>
+      <c r="C4050" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4051" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4051" t="s">
+        <v>8164</v>
+      </c>
+      <c r="B4051" t="s">
+        <v>8165</v>
+      </c>
+      <c r="C4051" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4052" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4052" t="s">
+        <v>8166</v>
+      </c>
+      <c r="B4052" t="s">
+        <v>8167</v>
+      </c>
+      <c r="C4052" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4053" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4053" t="s">
+        <v>8168</v>
+      </c>
+      <c r="B4053" t="s">
+        <v>8169</v>
+      </c>
+      <c r="C4053" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4054" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4054" t="s">
+        <v>8170</v>
+      </c>
+      <c r="B4054" t="s">
+        <v>8171</v>
+      </c>
+      <c r="C4054" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4055" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4055" t="s">
+        <v>8172</v>
+      </c>
+      <c r="B4055" t="s">
+        <v>8173</v>
+      </c>
+      <c r="C4055" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4056" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4056" t="s">
+        <v>8174</v>
+      </c>
+      <c r="B4056" t="s">
+        <v>8175</v>
+      </c>
+      <c r="C4056" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4057" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4057" t="s">
+        <v>8176</v>
+      </c>
+      <c r="B4057" t="s">
+        <v>8177</v>
+      </c>
+      <c r="C4057" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4058" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4058" t="s">
+        <v>8178</v>
+      </c>
+      <c r="B4058" t="s">
+        <v>8179</v>
+      </c>
+      <c r="C4058" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4059" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4059" t="s">
+        <v>8180</v>
+      </c>
+      <c r="B4059" t="s">
+        <v>8181</v>
+      </c>
+      <c r="C4059" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4060" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4060" t="s">
+        <v>8182</v>
+      </c>
+      <c r="B4060" t="s">
+        <v>8183</v>
+      </c>
+      <c r="C4060" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4061" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4061" t="s">
+        <v>8184</v>
+      </c>
+      <c r="B4061" t="s">
+        <v>8185</v>
+      </c>
+      <c r="C4061" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4062" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4062" t="s">
+        <v>8186</v>
+      </c>
+      <c r="B4062" t="s">
+        <v>8187</v>
+      </c>
+      <c r="C4062" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4063" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4063" t="s">
+        <v>8188</v>
+      </c>
+      <c r="B4063" t="s">
+        <v>8189</v>
+      </c>
+      <c r="C4063" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4064" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4064" t="s">
+        <v>8190</v>
+      </c>
+      <c r="B4064" t="s">
+        <v>8191</v>
+      </c>
+      <c r="C4064" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4065" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4065" t="s">
+        <v>8192</v>
+      </c>
+      <c r="B4065" t="s">
+        <v>8193</v>
+      </c>
+      <c r="C4065" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4066" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4066" t="s">
+        <v>8194</v>
+      </c>
+      <c r="B4066" t="s">
+        <v>8195</v>
+      </c>
+      <c r="C4066" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4067" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4067" t="s">
+        <v>8196</v>
+      </c>
+      <c r="B4067" t="s">
+        <v>8197</v>
+      </c>
+      <c r="C4067" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4068" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4068" t="s">
+        <v>8198</v>
+      </c>
+      <c r="B4068" t="s">
+        <v>8199</v>
+      </c>
+      <c r="C4068" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4069" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4069" t="s">
+        <v>8200</v>
+      </c>
+      <c r="B4069" t="s">
+        <v>8201</v>
+      </c>
+      <c r="C4069" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4070" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4070" t="s">
+        <v>8202</v>
+      </c>
+      <c r="B4070" t="s">
+        <v>8203</v>
+      </c>
+      <c r="C4070" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4071" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4071" t="s">
+        <v>8204</v>
+      </c>
+      <c r="B4071" t="s">
+        <v>8205</v>
+      </c>
+      <c r="C4071" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4072" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4072" t="s">
+        <v>8206</v>
+      </c>
+      <c r="B4072" t="s">
+        <v>8207</v>
+      </c>
+      <c r="C4072" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4073" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4073" t="s">
+        <v>8208</v>
+      </c>
+      <c r="B4073" t="s">
+        <v>8209</v>
+      </c>
+      <c r="C4073" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4074" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4074" t="s">
+        <v>8210</v>
+      </c>
+      <c r="B4074" t="s">
+        <v>8211</v>
+      </c>
+      <c r="C4074" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4075" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4075" t="s">
+        <v>8212</v>
+      </c>
+      <c r="B4075" t="s">
+        <v>8213</v>
+      </c>
+      <c r="C4075" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4076" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4076" t="s">
+        <v>8214</v>
+      </c>
+      <c r="B4076" t="s">
+        <v>8215</v>
+      </c>
+      <c r="C4076" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4077" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4077" t="s">
+        <v>8216</v>
+      </c>
+      <c r="B4077" t="s">
+        <v>8217</v>
+      </c>
+      <c r="C4077" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4078" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4078" t="s">
+        <v>8218</v>
+      </c>
+      <c r="B4078" t="s">
+        <v>8219</v>
+      </c>
+      <c r="C4078" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4079" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4079" t="s">
+        <v>8220</v>
+      </c>
+      <c r="B4079" t="s">
+        <v>8221</v>
+      </c>
+      <c r="C4079" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4080" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4080" t="s">
+        <v>8222</v>
+      </c>
+      <c r="B4080" t="s">
+        <v>8223</v>
+      </c>
+      <c r="C4080" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4081" t="s">
+        <v>8224</v>
+      </c>
+      <c r="B4081" t="s">
+        <v>8225</v>
+      </c>
+      <c r="C4081" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4082" t="s">
+        <v>8226</v>
+      </c>
+      <c r="B4082" t="s">
+        <v>8227</v>
+      </c>
+      <c r="C4082" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4083" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4083" t="s">
+        <v>8228</v>
+      </c>
+      <c r="B4083" t="s">
+        <v>8229</v>
+      </c>
+      <c r="C4083" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4084" t="s">
+        <v>8230</v>
+      </c>
+      <c r="B4084" t="s">
+        <v>8231</v>
+      </c>
+      <c r="C4084" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4085" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4085" t="s">
+        <v>8232</v>
+      </c>
+      <c r="B4085" t="s">
+        <v>8233</v>
+      </c>
+      <c r="C4085" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4086" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4086" t="s">
+        <v>8234</v>
+      </c>
+      <c r="B4086" t="s">
+        <v>8235</v>
+      </c>
+      <c r="C4086" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4087" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4087" t="s">
+        <v>8236</v>
+      </c>
+      <c r="B4087" t="s">
+        <v>8237</v>
+      </c>
+      <c r="C4087" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4088" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4088" t="s">
+        <v>8238</v>
+      </c>
+      <c r="B4088" t="s">
+        <v>8239</v>
+      </c>
+      <c r="C4088" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4089" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4089" t="s">
+        <v>8240</v>
+      </c>
+      <c r="B4089" t="s">
+        <v>8241</v>
+      </c>
+      <c r="C4089" t="s">
+        <v>8145</v>
+      </c>
+    </row>
+    <row r="4090" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4090" t="s">
+        <v>8242</v>
+      </c>
+      <c r="B4090" t="s">
+        <v>8243</v>
+      </c>
+      <c r="C4090" t="s">
+        <v>8145</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10764" uniqueCount="8244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10857" uniqueCount="8307">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -24749,6 +24749,195 @@
   </si>
   <si>
     <t>Наволочка сатин 50х70 - "Лигурия"</t>
+  </si>
+  <si>
+    <t>4681001611462</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное резинка 160х200х30 - "Стальная тень" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>04-05-2026</t>
+  </si>
+  <si>
+    <t>4681001611455</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок Евро-макси - Бертолеция наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611448</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро-макси - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001611431</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро-макси - "Вэспер"</t>
+  </si>
+  <si>
+    <t>4681001611424</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро - 140 - Асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4681001611417</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х10 - "Банделис"</t>
+  </si>
+  <si>
+    <t>4681001611400</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра 280х280 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4681001611394</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 180х200х30 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001611387</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х220х30 - Серая умбра</t>
+  </si>
+  <si>
+    <t>4681001611370</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - 4216 Серебро наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611363</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - 142 - Спящий Мишка на бежевом</t>
+  </si>
+  <si>
+    <t>4681001611356</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х30 - 125 - "Фая" 1х1</t>
+  </si>
+  <si>
+    <t>4681001611349</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 210х210х30 - 80 - Югацу</t>
+  </si>
+  <si>
+    <t>4681001611332</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Казимира"</t>
+  </si>
+  <si>
+    <t>4681001611325</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х20 - 140 - Вулкан 1х1</t>
+  </si>
+  <si>
+    <t>4681001611318</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 140 - Вулкан 1х1</t>
+  </si>
+  <si>
+    <t>4681001611301</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Вулкан 1х1</t>
+  </si>
+  <si>
+    <t>4681001611295</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х60 - 130 - Блю Маджента</t>
+  </si>
+  <si>
+    <t>4681001611288</t>
+  </si>
+  <si>
+    <t>Простыня круглая ранфорс резинка 210х210х30 - Белый</t>
+  </si>
+  <si>
+    <t>4681001611271</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин твил резинка 210х210х20 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001611264</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х40 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001611257</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин семейное резинка 160х200х30 - "Фиорис"</t>
+  </si>
+  <si>
+    <t>4681001611240</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 60х60 - 135 - Пудра 0,5х0,5</t>
+  </si>
+  <si>
+    <t>4681001611233</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 220х220х20 - Розовая лаванда</t>
+  </si>
+  <si>
+    <t>4681001611226</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 220х220х20 - Льняной</t>
+  </si>
+  <si>
+    <t>4681001611219</t>
+  </si>
+  <si>
+    <t>Простыня сатин 180х220 - 140 - Белый Лучик</t>
+  </si>
+  <si>
+    <t>4681001611202</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х40 - "Зелёный Страйп"</t>
+  </si>
+  <si>
+    <t>4681001611196</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 140х200х30 - "Грэлис" 1х1</t>
+  </si>
+  <si>
+    <t>4681001611189</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - "Мейз" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611172</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Ванильный</t>
+  </si>
+  <si>
+    <t>4681001611479</t>
+  </si>
+  <si>
+    <t>Простыня из страйп микрофибры 150 х 220 - М - 85 - Белая, полоска 3х3</t>
   </si>
 </sst>
 </file>
@@ -65601,6 +65790,347 @@
         <v>8145</v>
       </c>
     </row>
+    <row r="4091" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4091" t="s">
+        <v>8244</v>
+      </c>
+      <c r="B4091" t="s">
+        <v>8245</v>
+      </c>
+      <c r="C4091" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4092" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4092" t="s">
+        <v>8247</v>
+      </c>
+      <c r="B4092" t="s">
+        <v>8248</v>
+      </c>
+      <c r="C4092" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4093" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4093" t="s">
+        <v>8249</v>
+      </c>
+      <c r="B4093" t="s">
+        <v>8250</v>
+      </c>
+      <c r="C4093" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4094" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4094" t="s">
+        <v>8251</v>
+      </c>
+      <c r="B4094" t="s">
+        <v>8252</v>
+      </c>
+      <c r="C4094" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4095" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4095" t="s">
+        <v>8253</v>
+      </c>
+      <c r="B4095" t="s">
+        <v>8254</v>
+      </c>
+      <c r="C4095" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4096" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4096" t="s">
+        <v>8255</v>
+      </c>
+      <c r="B4096" t="s">
+        <v>8256</v>
+      </c>
+      <c r="C4096" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4097" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4097" t="s">
+        <v>8257</v>
+      </c>
+      <c r="B4097" t="s">
+        <v>8258</v>
+      </c>
+      <c r="C4097" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4098" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4098" t="s">
+        <v>8259</v>
+      </c>
+      <c r="B4098" t="s">
+        <v>8260</v>
+      </c>
+      <c r="C4098" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4099" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4099" t="s">
+        <v>8261</v>
+      </c>
+      <c r="B4099" t="s">
+        <v>8262</v>
+      </c>
+      <c r="C4099" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4100" t="s">
+        <v>8263</v>
+      </c>
+      <c r="B4100" t="s">
+        <v>8264</v>
+      </c>
+      <c r="C4100" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4101" t="s">
+        <v>8265</v>
+      </c>
+      <c r="B4101" t="s">
+        <v>8266</v>
+      </c>
+      <c r="C4101" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4102" t="s">
+        <v>8267</v>
+      </c>
+      <c r="B4102" t="s">
+        <v>8268</v>
+      </c>
+      <c r="C4102" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4103" t="s">
+        <v>8269</v>
+      </c>
+      <c r="B4103" t="s">
+        <v>8270</v>
+      </c>
+      <c r="C4103" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4104" t="s">
+        <v>8271</v>
+      </c>
+      <c r="B4104" t="s">
+        <v>8272</v>
+      </c>
+      <c r="C4104" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4105" t="s">
+        <v>8273</v>
+      </c>
+      <c r="B4105" t="s">
+        <v>8274</v>
+      </c>
+      <c r="C4105" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4106" t="s">
+        <v>8275</v>
+      </c>
+      <c r="B4106" t="s">
+        <v>8276</v>
+      </c>
+      <c r="C4106" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4107" t="s">
+        <v>8277</v>
+      </c>
+      <c r="B4107" t="s">
+        <v>8278</v>
+      </c>
+      <c r="C4107" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4108" t="s">
+        <v>8279</v>
+      </c>
+      <c r="B4108" t="s">
+        <v>8280</v>
+      </c>
+      <c r="C4108" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4109" t="s">
+        <v>8281</v>
+      </c>
+      <c r="B4109" t="s">
+        <v>8282</v>
+      </c>
+      <c r="C4109" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4110" t="s">
+        <v>8283</v>
+      </c>
+      <c r="B4110" t="s">
+        <v>8284</v>
+      </c>
+      <c r="C4110" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4111" t="s">
+        <v>8285</v>
+      </c>
+      <c r="B4111" t="s">
+        <v>8286</v>
+      </c>
+      <c r="C4111" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4112" t="s">
+        <v>8287</v>
+      </c>
+      <c r="B4112" t="s">
+        <v>8288</v>
+      </c>
+      <c r="C4112" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4113" t="s">
+        <v>8289</v>
+      </c>
+      <c r="B4113" t="s">
+        <v>8290</v>
+      </c>
+      <c r="C4113" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4114" t="s">
+        <v>8291</v>
+      </c>
+      <c r="B4114" t="s">
+        <v>8292</v>
+      </c>
+      <c r="C4114" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4115" t="s">
+        <v>8293</v>
+      </c>
+      <c r="B4115" t="s">
+        <v>8294</v>
+      </c>
+      <c r="C4115" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4116" t="s">
+        <v>8295</v>
+      </c>
+      <c r="B4116" t="s">
+        <v>8296</v>
+      </c>
+      <c r="C4116" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4117" t="s">
+        <v>8297</v>
+      </c>
+      <c r="B4117" t="s">
+        <v>8298</v>
+      </c>
+      <c r="C4117" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4118" t="s">
+        <v>8299</v>
+      </c>
+      <c r="B4118" t="s">
+        <v>8300</v>
+      </c>
+      <c r="C4118" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4119" t="s">
+        <v>8301</v>
+      </c>
+      <c r="B4119" t="s">
+        <v>8302</v>
+      </c>
+      <c r="C4119" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4120" t="s">
+        <v>8303</v>
+      </c>
+      <c r="B4120" t="s">
+        <v>8304</v>
+      </c>
+      <c r="C4120" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="4121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4121" t="s">
+        <v>8305</v>
+      </c>
+      <c r="B4121" t="s">
+        <v>8306</v>
+      </c>
+      <c r="C4121" t="s">
+        <v>8246</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10857" uniqueCount="8307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10926" uniqueCount="8354">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -24938,6 +24938,147 @@
   </si>
   <si>
     <t>Простыня из страйп микрофибры 150 х 220 - М - 85 - Белая, полоска 3х3</t>
+  </si>
+  <si>
+    <t>4681001611707</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро на резинке 160х200х20 - М - 120 - Чёрный мрамор</t>
+  </si>
+  <si>
+    <t>05-05-2026</t>
+  </si>
+  <si>
+    <t>4681001611691</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 200х220 - 125 - Радмила</t>
+  </si>
+  <si>
+    <t>4681001611684</t>
+  </si>
+  <si>
+    <t>Пододеяльник ранфорс 240х260 - Голубой</t>
+  </si>
+  <si>
+    <t>4681001611677</t>
+  </si>
+  <si>
+    <t>Наволочка ранфорс 60х60 - Голубой</t>
+  </si>
+  <si>
+    <t>4681001611660</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая 80х180 - Мулетон Полиэстер</t>
+  </si>
+  <si>
+    <t>4681001611653</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 160х200х30 - 120 - Хадусамат наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611646</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х200х40 - "Огнерон"</t>
+  </si>
+  <si>
+    <t>4681001611639</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х30 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001611622</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х30 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001611615</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х30 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4681001611608</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001611592</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 - Фикус</t>
+  </si>
+  <si>
+    <t>4681001611585</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 140х200х30 - "Осенний Сон" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611578</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Грей блес</t>
+  </si>
+  <si>
+    <t>4681001611561</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001611554</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Асунсьон"</t>
+  </si>
+  <si>
+    <t>4681001611547</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х40 - "Асунсьон"</t>
+  </si>
+  <si>
+    <t>4681001611530</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро - "Звёздный туман" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611523</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - "Лилизари"</t>
+  </si>
+  <si>
+    <t>4681001611516</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - "Мяурель" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611509</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - "Селинто" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611493</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 160х200х20 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001611486</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Лиловый тауп"</t>
   </si>
 </sst>
 </file>
@@ -66131,6 +66272,259 @@
         <v>8246</v>
       </c>
     </row>
+    <row r="4122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4122" t="s">
+        <v>8307</v>
+      </c>
+      <c r="B4122" t="s">
+        <v>8308</v>
+      </c>
+      <c r="C4122" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4123" t="s">
+        <v>8310</v>
+      </c>
+      <c r="B4123" t="s">
+        <v>8311</v>
+      </c>
+      <c r="C4123" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4124" t="s">
+        <v>8312</v>
+      </c>
+      <c r="B4124" t="s">
+        <v>8313</v>
+      </c>
+      <c r="C4124" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4125" t="s">
+        <v>8314</v>
+      </c>
+      <c r="B4125" t="s">
+        <v>8315</v>
+      </c>
+      <c r="C4125" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4126" t="s">
+        <v>8316</v>
+      </c>
+      <c r="B4126" t="s">
+        <v>8317</v>
+      </c>
+      <c r="C4126" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4127" t="s">
+        <v>8318</v>
+      </c>
+      <c r="B4127" t="s">
+        <v>8319</v>
+      </c>
+      <c r="C4127" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4128" t="s">
+        <v>8320</v>
+      </c>
+      <c r="B4128" t="s">
+        <v>8321</v>
+      </c>
+      <c r="C4128" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4129" t="s">
+        <v>8322</v>
+      </c>
+      <c r="B4129" t="s">
+        <v>8323</v>
+      </c>
+      <c r="C4129" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4130" t="s">
+        <v>8324</v>
+      </c>
+      <c r="B4130" t="s">
+        <v>8325</v>
+      </c>
+      <c r="C4130" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4131" t="s">
+        <v>8326</v>
+      </c>
+      <c r="B4131" t="s">
+        <v>8327</v>
+      </c>
+      <c r="C4131" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4132" t="s">
+        <v>8328</v>
+      </c>
+      <c r="B4132" t="s">
+        <v>8329</v>
+      </c>
+      <c r="C4132" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4133" t="s">
+        <v>8330</v>
+      </c>
+      <c r="B4133" t="s">
+        <v>8331</v>
+      </c>
+      <c r="C4133" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4134" t="s">
+        <v>8332</v>
+      </c>
+      <c r="B4134" t="s">
+        <v>8333</v>
+      </c>
+      <c r="C4134" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4135" t="s">
+        <v>8334</v>
+      </c>
+      <c r="B4135" t="s">
+        <v>8335</v>
+      </c>
+      <c r="C4135" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4136" t="s">
+        <v>8336</v>
+      </c>
+      <c r="B4136" t="s">
+        <v>8337</v>
+      </c>
+      <c r="C4136" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4137" t="s">
+        <v>8338</v>
+      </c>
+      <c r="B4137" t="s">
+        <v>8339</v>
+      </c>
+      <c r="C4137" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4138" t="s">
+        <v>8340</v>
+      </c>
+      <c r="B4138" t="s">
+        <v>8341</v>
+      </c>
+      <c r="C4138" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4139" t="s">
+        <v>8342</v>
+      </c>
+      <c r="B4139" t="s">
+        <v>8343</v>
+      </c>
+      <c r="C4139" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4140" t="s">
+        <v>8344</v>
+      </c>
+      <c r="B4140" t="s">
+        <v>8345</v>
+      </c>
+      <c r="C4140" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4141" t="s">
+        <v>8346</v>
+      </c>
+      <c r="B4141" t="s">
+        <v>8347</v>
+      </c>
+      <c r="C4141" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4142" t="s">
+        <v>8348</v>
+      </c>
+      <c r="B4142" t="s">
+        <v>8349</v>
+      </c>
+      <c r="C4142" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4143" t="s">
+        <v>8350</v>
+      </c>
+      <c r="B4143" t="s">
+        <v>8351</v>
+      </c>
+      <c r="C4143" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="4144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4144" t="s">
+        <v>8352</v>
+      </c>
+      <c r="B4144" t="s">
+        <v>8353</v>
+      </c>
+      <c r="C4144" t="s">
+        <v>8309</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10926" uniqueCount="8354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10992" uniqueCount="8399">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -25079,6 +25079,141 @@
   </si>
   <si>
     <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Лиловый тауп"</t>
+  </si>
+  <si>
+    <t>4681001611929</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 280х280 - "Бездна"</t>
+  </si>
+  <si>
+    <t>06-05-2026</t>
+  </si>
+  <si>
+    <t>4681001611912</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 140х200х30 - 142 - Белый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611905</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Гранола</t>
+  </si>
+  <si>
+    <t>4681001611899</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 140х200х30 - Гранола</t>
+  </si>
+  <si>
+    <t>4681001611882</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 180х200х30 - 4292 Кремовый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611875</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин на резинке 200х200х20 - "Богумила"</t>
+  </si>
+  <si>
+    <t>4681001611868</t>
+  </si>
+  <si>
+    <t>Простыня Полисатин резинка 200х220х30 - "Мелек"</t>
+  </si>
+  <si>
+    <t>4681001611851</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное - "Бартош" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611844</t>
+  </si>
+  <si>
+    <t>Простыня круглая ранфорс резинка 200х200х30 - "Лазурный бриз"</t>
+  </si>
+  <si>
+    <t>4681001611837</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль Евро резинка 160х200х30 - 125 - Радмила</t>
+  </si>
+  <si>
+    <t>4681001611820</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - "Синтера" 1х1</t>
+  </si>
+  <si>
+    <t>4681001611813</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 50х50 - "Светлый лён"</t>
+  </si>
+  <si>
+    <t>4681001611806</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 160х200х30 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001611790</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х40 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001611783</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Аргентум</t>
+  </si>
+  <si>
+    <t>4681001611776</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - 4216 Серебро</t>
+  </si>
+  <si>
+    <t>4681001611769</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 130 - "Изумрудный малахит" 1х1</t>
+  </si>
+  <si>
+    <t>4681001611752</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Бирюзовый берег наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001611745</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 200х220 - Белый</t>
+  </si>
+  <si>
+    <t>4681001611738</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001611721</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - 4373 Пудровый</t>
+  </si>
+  <si>
+    <t>4681001611714</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - Бонди</t>
   </si>
 </sst>
 </file>
@@ -66525,6 +66660,248 @@
         <v>8309</v>
       </c>
     </row>
+    <row r="4145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4145" t="s">
+        <v>8354</v>
+      </c>
+      <c r="B4145" t="s">
+        <v>8355</v>
+      </c>
+      <c r="C4145" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4146" t="s">
+        <v>8357</v>
+      </c>
+      <c r="B4146" t="s">
+        <v>8358</v>
+      </c>
+      <c r="C4146" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4147" t="s">
+        <v>8359</v>
+      </c>
+      <c r="B4147" t="s">
+        <v>8360</v>
+      </c>
+      <c r="C4147" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4148" t="s">
+        <v>8361</v>
+      </c>
+      <c r="B4148" t="s">
+        <v>8362</v>
+      </c>
+      <c r="C4148" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4149" t="s">
+        <v>8363</v>
+      </c>
+      <c r="B4149" t="s">
+        <v>8364</v>
+      </c>
+      <c r="C4149" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4150" t="s">
+        <v>8365</v>
+      </c>
+      <c r="B4150" t="s">
+        <v>8366</v>
+      </c>
+      <c r="C4150" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4151" t="s">
+        <v>8367</v>
+      </c>
+      <c r="B4151" t="s">
+        <v>8368</v>
+      </c>
+      <c r="C4151" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4152" t="s">
+        <v>8369</v>
+      </c>
+      <c r="B4152" t="s">
+        <v>8370</v>
+      </c>
+      <c r="C4152" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4153" t="s">
+        <v>8371</v>
+      </c>
+      <c r="B4153" t="s">
+        <v>8372</v>
+      </c>
+      <c r="C4153" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4154" t="s">
+        <v>8373</v>
+      </c>
+      <c r="B4154" t="s">
+        <v>8374</v>
+      </c>
+      <c r="C4154" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4155" t="s">
+        <v>8375</v>
+      </c>
+      <c r="B4155" t="s">
+        <v>8376</v>
+      </c>
+      <c r="C4155" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4156" t="s">
+        <v>8377</v>
+      </c>
+      <c r="B4156" t="s">
+        <v>8378</v>
+      </c>
+      <c r="C4156" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4157" t="s">
+        <v>8379</v>
+      </c>
+      <c r="B4157" t="s">
+        <v>8380</v>
+      </c>
+      <c r="C4157" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4158" t="s">
+        <v>8381</v>
+      </c>
+      <c r="B4158" t="s">
+        <v>8382</v>
+      </c>
+      <c r="C4158" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4159" t="s">
+        <v>8383</v>
+      </c>
+      <c r="B4159" t="s">
+        <v>8384</v>
+      </c>
+      <c r="C4159" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4160" t="s">
+        <v>8385</v>
+      </c>
+      <c r="B4160" t="s">
+        <v>8386</v>
+      </c>
+      <c r="C4160" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4161" t="s">
+        <v>8387</v>
+      </c>
+      <c r="B4161" t="s">
+        <v>8388</v>
+      </c>
+      <c r="C4161" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4162" t="s">
+        <v>8389</v>
+      </c>
+      <c r="B4162" t="s">
+        <v>8390</v>
+      </c>
+      <c r="C4162" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4163" t="s">
+        <v>8391</v>
+      </c>
+      <c r="B4163" t="s">
+        <v>8392</v>
+      </c>
+      <c r="C4163" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4164" t="s">
+        <v>8393</v>
+      </c>
+      <c r="B4164" t="s">
+        <v>8394</v>
+      </c>
+      <c r="C4164" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4165" t="s">
+        <v>8395</v>
+      </c>
+      <c r="B4165" t="s">
+        <v>8396</v>
+      </c>
+      <c r="C4165" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="4166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4166" t="s">
+        <v>8397</v>
+      </c>
+      <c r="B4166" t="s">
+        <v>8398</v>
+      </c>
+      <c r="C4166" t="s">
+        <v>8356</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10992" uniqueCount="8399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11037" uniqueCount="8430">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -25214,6 +25214,99 @@
   </si>
   <si>
     <t>Наволочка поплин 50х50 - Бонди</t>
+  </si>
+  <si>
+    <t>4681001612032</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра семейное резинка 180х200х30 - "Петкана"</t>
+  </si>
+  <si>
+    <t>07-05-2026</t>
+  </si>
+  <si>
+    <t>4681001612025</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное резинка 180х200х30 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001612018</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - "Карибская волна" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612001</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 240х240х30 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001611998</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 145х215 - 135 - Дип Пёрпл 1х1</t>
+  </si>
+  <si>
+    <t>4681001611981</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - Маренго</t>
+  </si>
+  <si>
+    <t>4681001611974</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001611967</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - 140 - Белый Лучик</t>
+  </si>
+  <si>
+    <t>4681001611950</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 200х200 - 125 - Терракота</t>
+  </si>
+  <si>
+    <t>4681001611943</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001611936</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 220х240 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001612063</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х40 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001612056</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001612049</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - 142 - Оранжевый</t>
+  </si>
+  <si>
+    <t>4681001612070</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 120х200х30 - Графит (меланж)</t>
   </si>
 </sst>
 </file>
@@ -66902,6 +66995,171 @@
         <v>8356</v>
       </c>
     </row>
+    <row r="4167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4167" t="s">
+        <v>8399</v>
+      </c>
+      <c r="B4167" t="s">
+        <v>8400</v>
+      </c>
+      <c r="C4167" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4168" t="s">
+        <v>8402</v>
+      </c>
+      <c r="B4168" t="s">
+        <v>8403</v>
+      </c>
+      <c r="C4168" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4169" t="s">
+        <v>8404</v>
+      </c>
+      <c r="B4169" t="s">
+        <v>8405</v>
+      </c>
+      <c r="C4169" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4170" t="s">
+        <v>8406</v>
+      </c>
+      <c r="B4170" t="s">
+        <v>8407</v>
+      </c>
+      <c r="C4170" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4171" t="s">
+        <v>8408</v>
+      </c>
+      <c r="B4171" t="s">
+        <v>8409</v>
+      </c>
+      <c r="C4171" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4172" t="s">
+        <v>8410</v>
+      </c>
+      <c r="B4172" t="s">
+        <v>8411</v>
+      </c>
+      <c r="C4172" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4173" t="s">
+        <v>8412</v>
+      </c>
+      <c r="B4173" t="s">
+        <v>8413</v>
+      </c>
+      <c r="C4173" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4174" t="s">
+        <v>8414</v>
+      </c>
+      <c r="B4174" t="s">
+        <v>8415</v>
+      </c>
+      <c r="C4174" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4175" t="s">
+        <v>8416</v>
+      </c>
+      <c r="B4175" t="s">
+        <v>8417</v>
+      </c>
+      <c r="C4175" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4176" t="s">
+        <v>8418</v>
+      </c>
+      <c r="B4176" t="s">
+        <v>8419</v>
+      </c>
+      <c r="C4176" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4177" t="s">
+        <v>8420</v>
+      </c>
+      <c r="B4177" t="s">
+        <v>8421</v>
+      </c>
+      <c r="C4177" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4178" t="s">
+        <v>8422</v>
+      </c>
+      <c r="B4178" t="s">
+        <v>8423</v>
+      </c>
+      <c r="C4178" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4179" t="s">
+        <v>8424</v>
+      </c>
+      <c r="B4179" t="s">
+        <v>8425</v>
+      </c>
+      <c r="C4179" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4180" t="s">
+        <v>8426</v>
+      </c>
+      <c r="B4180" t="s">
+        <v>8427</v>
+      </c>
+      <c r="C4180" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="4181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4181" t="s">
+        <v>8428</v>
+      </c>
+      <c r="B4181" t="s">
+        <v>8429</v>
+      </c>
+      <c r="C4181" t="s">
+        <v>8401</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11037" uniqueCount="8430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="8445">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -25307,6 +25307,51 @@
   </si>
   <si>
     <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 120х200х30 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001612148</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Ясное небо</t>
+  </si>
+  <si>
+    <t>08-05-2026</t>
+  </si>
+  <si>
+    <t>4681001612131</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - 4294 Перламутровый</t>
+  </si>
+  <si>
+    <t>4681001612124</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - "Оранж"</t>
+  </si>
+  <si>
+    <t>4681001612117</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Цветочная Графика"</t>
+  </si>
+  <si>
+    <t>4681001612100</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - "Холодная элегия"</t>
+  </si>
+  <si>
+    <t>4681001612094</t>
+  </si>
+  <si>
+    <t>Простыня бязь 260х260 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001612087</t>
+  </si>
+  <si>
+    <t>Простыня бязь 260х260 - "Вэспер"</t>
   </si>
 </sst>
 </file>
@@ -67160,6 +67205,83 @@
         <v>8401</v>
       </c>
     </row>
+    <row r="4182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4182" t="s">
+        <v>8430</v>
+      </c>
+      <c r="B4182" t="s">
+        <v>8431</v>
+      </c>
+      <c r="C4182" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4183" t="s">
+        <v>8433</v>
+      </c>
+      <c r="B4183" t="s">
+        <v>8434</v>
+      </c>
+      <c r="C4183" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4184" t="s">
+        <v>8435</v>
+      </c>
+      <c r="B4184" t="s">
+        <v>8436</v>
+      </c>
+      <c r="C4184" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4185" t="s">
+        <v>8437</v>
+      </c>
+      <c r="B4185" t="s">
+        <v>8438</v>
+      </c>
+      <c r="C4185" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4186" t="s">
+        <v>8439</v>
+      </c>
+      <c r="B4186" t="s">
+        <v>8440</v>
+      </c>
+      <c r="C4186" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4187" t="s">
+        <v>8441</v>
+      </c>
+      <c r="B4187" t="s">
+        <v>8442</v>
+      </c>
+      <c r="C4187" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4188" t="s">
+        <v>8443</v>
+      </c>
+      <c r="B4188" t="s">
+        <v>8444</v>
+      </c>
+      <c r="C4188" t="s">
+        <v>8432</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="8445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11097" uniqueCount="8471">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -25352,6 +25352,84 @@
   </si>
   <si>
     <t>Простыня бязь 260х260 - "Вэспер"</t>
+  </si>
+  <si>
+    <t>4681001612278</t>
+  </si>
+  <si>
+    <t>Простыня полисатин на резинке 90х200х10 - "Богумила"</t>
+  </si>
+  <si>
+    <t>4681001612261</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 140х200х30 - Чёрная гавань наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612254</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 140х200х30 - 323 Серый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612247</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - "Бонетто" Универсал</t>
+  </si>
+  <si>
+    <t>4681001612230</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 200х220 - "Криола"</t>
+  </si>
+  <si>
+    <t>4681001612223</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро макси - "Корги-пати"</t>
+  </si>
+  <si>
+    <t>4681001612216</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х240х30 - 135 - Марриотт Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001612209</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное - Гималайские маки</t>
+  </si>
+  <si>
+    <t>4681001612193</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - "Бейж" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612186</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Халкидики</t>
+  </si>
+  <si>
+    <t>4681001612179</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 200х200 - "Бежевый шлейф"</t>
+  </si>
+  <si>
+    <t>4681001612162</t>
+  </si>
+  <si>
+    <t>Простыня круглая Жатка на резинке 200х200х30 - "Файза"</t>
+  </si>
+  <si>
+    <t>4681001612155</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 80х200х10 - "Ливел"</t>
   </si>
 </sst>
 </file>
@@ -67282,6 +67360,149 @@
         <v>8432</v>
       </c>
     </row>
+    <row r="4189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4189" t="s">
+        <v>8445</v>
+      </c>
+      <c r="B4189" t="s">
+        <v>8446</v>
+      </c>
+      <c r="C4189" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4190" t="s">
+        <v>8447</v>
+      </c>
+      <c r="B4190" t="s">
+        <v>8448</v>
+      </c>
+      <c r="C4190" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4191" t="s">
+        <v>8449</v>
+      </c>
+      <c r="B4191" t="s">
+        <v>8450</v>
+      </c>
+      <c r="C4191" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4192" t="s">
+        <v>8451</v>
+      </c>
+      <c r="B4192" t="s">
+        <v>8452</v>
+      </c>
+      <c r="C4192" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4193" t="s">
+        <v>8453</v>
+      </c>
+      <c r="B4193" t="s">
+        <v>8454</v>
+      </c>
+      <c r="C4193" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4194" t="s">
+        <v>8455</v>
+      </c>
+      <c r="B4194" t="s">
+        <v>8456</v>
+      </c>
+      <c r="C4194" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4195" t="s">
+        <v>8457</v>
+      </c>
+      <c r="B4195" t="s">
+        <v>8458</v>
+      </c>
+      <c r="C4195" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4196" t="s">
+        <v>8459</v>
+      </c>
+      <c r="B4196" t="s">
+        <v>8460</v>
+      </c>
+      <c r="C4196" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4197" t="s">
+        <v>8461</v>
+      </c>
+      <c r="B4197" t="s">
+        <v>8462</v>
+      </c>
+      <c r="C4197" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4198" t="s">
+        <v>8463</v>
+      </c>
+      <c r="B4198" t="s">
+        <v>8464</v>
+      </c>
+      <c r="C4198" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4199" t="s">
+        <v>8465</v>
+      </c>
+      <c r="B4199" t="s">
+        <v>8466</v>
+      </c>
+      <c r="C4199" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4200" t="s">
+        <v>8467</v>
+      </c>
+      <c r="B4200" t="s">
+        <v>8468</v>
+      </c>
+      <c r="C4200" t="s">
+        <v>8432</v>
+      </c>
+    </row>
+    <row r="4201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4201" t="s">
+        <v>8469</v>
+      </c>
+      <c r="B4201" t="s">
+        <v>8470</v>
+      </c>
+      <c r="C4201" t="s">
+        <v>8432</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11097" uniqueCount="8471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11190" uniqueCount="8534">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -25430,6 +25430,195 @@
   </si>
   <si>
     <t>Простыня бязь резинка 80х200х10 - "Ливел"</t>
+  </si>
+  <si>
+    <t>4681001612582</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х50 - 135 - Цитрус 3х3</t>
+  </si>
+  <si>
+    <t>09-05-2026</t>
+  </si>
+  <si>
+    <t>4681001612575</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 135 - Цитрус 3х3</t>
+  </si>
+  <si>
+    <t>4681001612568</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 135 - Блу Хейз 1х1</t>
+  </si>
+  <si>
+    <t>4681001612551</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - Гестхаус Белый 3х3 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612544</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Песочная роза" Универсал</t>
+  </si>
+  <si>
+    <t>4681001612537</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - 80 - Теплые Пожелания</t>
+  </si>
+  <si>
+    <t>4681001612520</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок Евро-макси резинка 180х200х30 - Бертолеция</t>
+  </si>
+  <si>
+    <t>4681001612513</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 125 - "Капучино" 1х1</t>
+  </si>
+  <si>
+    <t>4681001612506</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Мечта наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612490</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001612483</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро - 140 - Лагуна 1х1</t>
+  </si>
+  <si>
+    <t>4681001612476</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - 4373 Пудровый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612469</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 1,5 спальное резинка 120х200х30 - "Небосвод" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612452</t>
+  </si>
+  <si>
+    <t>Простыня сатин 280х280 - 120 - Баден Гольд</t>
+  </si>
+  <si>
+    <t>4681001612445</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 280х280 - "Папоротниковый"</t>
+  </si>
+  <si>
+    <t>4681001612438</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Графитовый Зигзаг" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612421</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Мазарин блу наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612414</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Черный янтарь 3х3</t>
+  </si>
+  <si>
+    <t>4681001612407</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001612391</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001612384</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х50 - Голубая сталь</t>
+  </si>
+  <si>
+    <t>4681001612377</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 240х260 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001612360</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4681001612353</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>4681001612346</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 300х300 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001612339</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное Евро простыня - 135 - Солнечный 1х1</t>
+  </si>
+  <si>
+    <t>4681001612322</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - "Крылатые сны"</t>
+  </si>
+  <si>
+    <t>4681001612315</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 140х200х30 - "Симоне" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612308</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - 125 - Дом Периньон</t>
+  </si>
+  <si>
+    <t>4681001612292</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х200 - "Паллада"</t>
+  </si>
+  <si>
+    <t>4681001612285</t>
+  </si>
+  <si>
+    <t>Простыня сатин 220х240 - 125 - Шоколадный птифур</t>
   </si>
 </sst>
 </file>
@@ -67503,6 +67692,347 @@
         <v>8432</v>
       </c>
     </row>
+    <row r="4202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4202" t="s">
+        <v>8471</v>
+      </c>
+      <c r="B4202" t="s">
+        <v>8472</v>
+      </c>
+      <c r="C4202" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4203" t="s">
+        <v>8474</v>
+      </c>
+      <c r="B4203" t="s">
+        <v>8475</v>
+      </c>
+      <c r="C4203" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4204" t="s">
+        <v>8476</v>
+      </c>
+      <c r="B4204" t="s">
+        <v>8477</v>
+      </c>
+      <c r="C4204" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4205" t="s">
+        <v>8478</v>
+      </c>
+      <c r="B4205" t="s">
+        <v>8479</v>
+      </c>
+      <c r="C4205" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4206" t="s">
+        <v>8480</v>
+      </c>
+      <c r="B4206" t="s">
+        <v>8481</v>
+      </c>
+      <c r="C4206" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4207" t="s">
+        <v>8482</v>
+      </c>
+      <c r="B4207" t="s">
+        <v>8483</v>
+      </c>
+      <c r="C4207" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4208" t="s">
+        <v>8484</v>
+      </c>
+      <c r="B4208" t="s">
+        <v>8485</v>
+      </c>
+      <c r="C4208" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4209" t="s">
+        <v>8486</v>
+      </c>
+      <c r="B4209" t="s">
+        <v>8487</v>
+      </c>
+      <c r="C4209" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4210" t="s">
+        <v>8488</v>
+      </c>
+      <c r="B4210" t="s">
+        <v>8489</v>
+      </c>
+      <c r="C4210" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4211" t="s">
+        <v>8490</v>
+      </c>
+      <c r="B4211" t="s">
+        <v>8491</v>
+      </c>
+      <c r="C4211" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4212" t="s">
+        <v>8492</v>
+      </c>
+      <c r="B4212" t="s">
+        <v>8493</v>
+      </c>
+      <c r="C4212" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4213" t="s">
+        <v>8494</v>
+      </c>
+      <c r="B4213" t="s">
+        <v>8495</v>
+      </c>
+      <c r="C4213" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4214" t="s">
+        <v>8496</v>
+      </c>
+      <c r="B4214" t="s">
+        <v>8497</v>
+      </c>
+      <c r="C4214" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4215" t="s">
+        <v>8498</v>
+      </c>
+      <c r="B4215" t="s">
+        <v>8499</v>
+      </c>
+      <c r="C4215" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4216" t="s">
+        <v>8500</v>
+      </c>
+      <c r="B4216" t="s">
+        <v>8501</v>
+      </c>
+      <c r="C4216" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4217" t="s">
+        <v>8502</v>
+      </c>
+      <c r="B4217" t="s">
+        <v>8503</v>
+      </c>
+      <c r="C4217" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4218" t="s">
+        <v>8504</v>
+      </c>
+      <c r="B4218" t="s">
+        <v>8505</v>
+      </c>
+      <c r="C4218" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4219" t="s">
+        <v>8506</v>
+      </c>
+      <c r="B4219" t="s">
+        <v>8507</v>
+      </c>
+      <c r="C4219" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4220" t="s">
+        <v>8508</v>
+      </c>
+      <c r="B4220" t="s">
+        <v>8509</v>
+      </c>
+      <c r="C4220" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4221" t="s">
+        <v>8510</v>
+      </c>
+      <c r="B4221" t="s">
+        <v>8511</v>
+      </c>
+      <c r="C4221" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4222" t="s">
+        <v>8512</v>
+      </c>
+      <c r="B4222" t="s">
+        <v>8513</v>
+      </c>
+      <c r="C4222" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4223" t="s">
+        <v>8514</v>
+      </c>
+      <c r="B4223" t="s">
+        <v>8515</v>
+      </c>
+      <c r="C4223" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4224" t="s">
+        <v>8516</v>
+      </c>
+      <c r="B4224" t="s">
+        <v>8517</v>
+      </c>
+      <c r="C4224" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4225" t="s">
+        <v>8518</v>
+      </c>
+      <c r="B4225" t="s">
+        <v>8519</v>
+      </c>
+      <c r="C4225" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4226" t="s">
+        <v>8520</v>
+      </c>
+      <c r="B4226" t="s">
+        <v>8521</v>
+      </c>
+      <c r="C4226" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4227" t="s">
+        <v>8522</v>
+      </c>
+      <c r="B4227" t="s">
+        <v>8523</v>
+      </c>
+      <c r="C4227" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4228" t="s">
+        <v>8524</v>
+      </c>
+      <c r="B4228" t="s">
+        <v>8525</v>
+      </c>
+      <c r="C4228" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4229" t="s">
+        <v>8526</v>
+      </c>
+      <c r="B4229" t="s">
+        <v>8527</v>
+      </c>
+      <c r="C4229" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4230" t="s">
+        <v>8528</v>
+      </c>
+      <c r="B4230" t="s">
+        <v>8529</v>
+      </c>
+      <c r="C4230" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4231" t="s">
+        <v>8530</v>
+      </c>
+      <c r="B4231" t="s">
+        <v>8531</v>
+      </c>
+      <c r="C4231" t="s">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="4232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4232" t="s">
+        <v>8532</v>
+      </c>
+      <c r="B4232" t="s">
+        <v>8533</v>
+      </c>
+      <c r="C4232" t="s">
+        <v>8473</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11190" uniqueCount="8534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11310" uniqueCount="8615">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -25619,6 +25619,249 @@
   </si>
   <si>
     <t>Простыня сатин 220х240 - 125 - Шоколадный птифур</t>
+  </si>
+  <si>
+    <t>4681001612988</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - Прохлада ментола</t>
+  </si>
+  <si>
+    <t>10-05-2026</t>
+  </si>
+  <si>
+    <t>4681001612971</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - "Голубая дымка"</t>
+  </si>
+  <si>
+    <t>4681001612964</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - "Цветочный Шёпот"</t>
+  </si>
+  <si>
+    <t>4681001612957</t>
+  </si>
+  <si>
+    <t>Простыня бязь 280х280 - "Вэспер"</t>
+  </si>
+  <si>
+    <t>4681001612940</t>
+  </si>
+  <si>
+    <t>Простыня круглая микросатин резинка 250х250х20 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4681001612933</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 70х70 - Мятное дыхание</t>
+  </si>
+  <si>
+    <t>4681001612926</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 60х60 - "Стальная тень" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001612919</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок Евро резинка 160х200х30 - Молочный</t>
+  </si>
+  <si>
+    <t>4681001612902</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 200х220х30 - 120 - Баден Гольд</t>
+  </si>
+  <si>
+    <t>4681001612896</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - 41-020 Серебряный</t>
+  </si>
+  <si>
+    <t>4681001612889</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 240х260 - 135 - Эмерэльд 1х1</t>
+  </si>
+  <si>
+    <t>4681001612872</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил резинка 180х200х40 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>4681001612865</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х20 - "Гриновей" 1х1</t>
+  </si>
+  <si>
+    <t>4681001612858</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х30 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4681001612841</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001612834</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001612827</t>
+  </si>
+  <si>
+    <t>Простыня жатка 180х220 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001612810</t>
+  </si>
+  <si>
+    <t>Простыня жатка 180х220 - "Гармония линий"</t>
+  </si>
+  <si>
+    <t>4681001612803</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Ледяной Мрамор"</t>
+  </si>
+  <si>
+    <t>4681001612797</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 300х300 - "Белый Оникс"</t>
+  </si>
+  <si>
+    <t>4681001612780</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001612773</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - "Дизанта" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612766</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 145х215 - Matte Dark Grey</t>
+  </si>
+  <si>
+    <t>4681001612759</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Песочная роза" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612742</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 180х200х40 - Вайлет</t>
+  </si>
+  <si>
+    <t>4681001612735</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное резинка 160х200х30 - 135 - Мокрый асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4681001612728</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - "Фрезия" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612711</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Жатка Евро на резинке 160х200х30 - "Файза"</t>
+  </si>
+  <si>
+    <t>4681001612704</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001612698</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин семейное резинка 180х200х30 - 140 - "Можиана Люкс"</t>
+  </si>
+  <si>
+    <t>4681001612681</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 145х215 - "Бонетто"</t>
+  </si>
+  <si>
+    <t>4681001612674</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - "Мелвис" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612667</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Вулкан 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612650</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х45 - 130 - Мятный фреш 1х1</t>
+  </si>
+  <si>
+    <t>4681001612643</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 90х200х30 - "Ливел"</t>
+  </si>
+  <si>
+    <t>4681001612636</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - 135 - Платина 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001612629</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 125 - Магеллан 1х1</t>
+  </si>
+  <si>
+    <t>4681001612612</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Богумила"</t>
+  </si>
+  <si>
+    <t>4681001612605</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 200х220 - "Кетеван"</t>
+  </si>
+  <si>
+    <t>4681001612599</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - "Танец крыльев"</t>
   </si>
 </sst>
 </file>
@@ -68033,6 +68276,446 @@
         <v>8473</v>
       </c>
     </row>
+    <row r="4233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4233" t="s">
+        <v>8534</v>
+      </c>
+      <c r="B4233" t="s">
+        <v>8535</v>
+      </c>
+      <c r="C4233" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4234" t="s">
+        <v>8537</v>
+      </c>
+      <c r="B4234" t="s">
+        <v>8538</v>
+      </c>
+      <c r="C4234" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4235" t="s">
+        <v>8539</v>
+      </c>
+      <c r="B4235" t="s">
+        <v>8540</v>
+      </c>
+      <c r="C4235" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4236" t="s">
+        <v>8541</v>
+      </c>
+      <c r="B4236" t="s">
+        <v>8542</v>
+      </c>
+      <c r="C4236" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4237" t="s">
+        <v>8543</v>
+      </c>
+      <c r="B4237" t="s">
+        <v>8544</v>
+      </c>
+      <c r="C4237" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4238" t="s">
+        <v>8545</v>
+      </c>
+      <c r="B4238" t="s">
+        <v>8546</v>
+      </c>
+      <c r="C4238" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4239" t="s">
+        <v>8547</v>
+      </c>
+      <c r="B4239" t="s">
+        <v>8548</v>
+      </c>
+      <c r="C4239" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4240" t="s">
+        <v>8549</v>
+      </c>
+      <c r="B4240" t="s">
+        <v>8550</v>
+      </c>
+      <c r="C4240" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4241" t="s">
+        <v>8551</v>
+      </c>
+      <c r="B4241" t="s">
+        <v>8552</v>
+      </c>
+      <c r="C4241" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4242" t="s">
+        <v>8553</v>
+      </c>
+      <c r="B4242" t="s">
+        <v>8554</v>
+      </c>
+      <c r="C4242" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4243" t="s">
+        <v>8555</v>
+      </c>
+      <c r="B4243" t="s">
+        <v>8556</v>
+      </c>
+      <c r="C4243" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4244" t="s">
+        <v>8557</v>
+      </c>
+      <c r="B4244" t="s">
+        <v>8558</v>
+      </c>
+      <c r="C4244" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4245" t="s">
+        <v>8559</v>
+      </c>
+      <c r="B4245" t="s">
+        <v>8560</v>
+      </c>
+      <c r="C4245" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4246" t="s">
+        <v>8561</v>
+      </c>
+      <c r="B4246" t="s">
+        <v>8562</v>
+      </c>
+      <c r="C4246" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4247" t="s">
+        <v>8563</v>
+      </c>
+      <c r="B4247" t="s">
+        <v>8564</v>
+      </c>
+      <c r="C4247" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4248" t="s">
+        <v>8565</v>
+      </c>
+      <c r="B4248" t="s">
+        <v>8566</v>
+      </c>
+      <c r="C4248" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4249" t="s">
+        <v>8567</v>
+      </c>
+      <c r="B4249" t="s">
+        <v>8568</v>
+      </c>
+      <c r="C4249" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4250" t="s">
+        <v>8569</v>
+      </c>
+      <c r="B4250" t="s">
+        <v>8570</v>
+      </c>
+      <c r="C4250" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4251" t="s">
+        <v>8571</v>
+      </c>
+      <c r="B4251" t="s">
+        <v>8572</v>
+      </c>
+      <c r="C4251" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4252" t="s">
+        <v>8573</v>
+      </c>
+      <c r="B4252" t="s">
+        <v>8574</v>
+      </c>
+      <c r="C4252" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4253" t="s">
+        <v>8575</v>
+      </c>
+      <c r="B4253" t="s">
+        <v>8576</v>
+      </c>
+      <c r="C4253" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4254" t="s">
+        <v>8577</v>
+      </c>
+      <c r="B4254" t="s">
+        <v>8578</v>
+      </c>
+      <c r="C4254" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4255" t="s">
+        <v>8579</v>
+      </c>
+      <c r="B4255" t="s">
+        <v>8580</v>
+      </c>
+      <c r="C4255" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4256" t="s">
+        <v>8581</v>
+      </c>
+      <c r="B4256" t="s">
+        <v>8582</v>
+      </c>
+      <c r="C4256" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4257" t="s">
+        <v>8583</v>
+      </c>
+      <c r="B4257" t="s">
+        <v>8584</v>
+      </c>
+      <c r="C4257" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4258" t="s">
+        <v>8585</v>
+      </c>
+      <c r="B4258" t="s">
+        <v>8586</v>
+      </c>
+      <c r="C4258" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4259" t="s">
+        <v>8587</v>
+      </c>
+      <c r="B4259" t="s">
+        <v>8588</v>
+      </c>
+      <c r="C4259" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4260" t="s">
+        <v>8589</v>
+      </c>
+      <c r="B4260" t="s">
+        <v>8590</v>
+      </c>
+      <c r="C4260" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4261" t="s">
+        <v>8591</v>
+      </c>
+      <c r="B4261" t="s">
+        <v>8592</v>
+      </c>
+      <c r="C4261" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4262" t="s">
+        <v>8593</v>
+      </c>
+      <c r="B4262" t="s">
+        <v>8594</v>
+      </c>
+      <c r="C4262" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4263" t="s">
+        <v>8595</v>
+      </c>
+      <c r="B4263" t="s">
+        <v>8596</v>
+      </c>
+      <c r="C4263" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4264" t="s">
+        <v>8597</v>
+      </c>
+      <c r="B4264" t="s">
+        <v>8598</v>
+      </c>
+      <c r="C4264" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4265" t="s">
+        <v>8599</v>
+      </c>
+      <c r="B4265" t="s">
+        <v>8600</v>
+      </c>
+      <c r="C4265" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4266" t="s">
+        <v>8601</v>
+      </c>
+      <c r="B4266" t="s">
+        <v>8602</v>
+      </c>
+      <c r="C4266" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4267" t="s">
+        <v>8603</v>
+      </c>
+      <c r="B4267" t="s">
+        <v>8604</v>
+      </c>
+      <c r="C4267" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4268" t="s">
+        <v>8605</v>
+      </c>
+      <c r="B4268" t="s">
+        <v>8606</v>
+      </c>
+      <c r="C4268" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4269" t="s">
+        <v>8607</v>
+      </c>
+      <c r="B4269" t="s">
+        <v>8608</v>
+      </c>
+      <c r="C4269" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4270" t="s">
+        <v>8609</v>
+      </c>
+      <c r="B4270" t="s">
+        <v>8610</v>
+      </c>
+      <c r="C4270" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4271" t="s">
+        <v>8611</v>
+      </c>
+      <c r="B4271" t="s">
+        <v>8612</v>
+      </c>
+      <c r="C4271" t="s">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="4272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4272" t="s">
+        <v>8613</v>
+      </c>
+      <c r="B4272" t="s">
+        <v>8614</v>
+      </c>
+      <c r="C4272" t="s">
+        <v>8536</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11310" uniqueCount="8615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11457" uniqueCount="8714">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -25862,6 +25862,303 @@
   </si>
   <si>
     <t>Наволочка бязь 70х70 - "Танец крыльев"</t>
+  </si>
+  <si>
+    <t>4681001613466</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 145х215 - "Фаусто"</t>
+  </si>
+  <si>
+    <t>11-05-2026</t>
+  </si>
+  <si>
+    <t>4681001613459</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 120х200х30 - 135 - Гелиос 1х1</t>
+  </si>
+  <si>
+    <t>4681001613442</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 160х200х20 - Розариум А+В</t>
+  </si>
+  <si>
+    <t>4681001613435</t>
+  </si>
+  <si>
+    <t>Простыня жатка 240х260 - "Ледяной Мрамор"</t>
+  </si>
+  <si>
+    <t>4681001613428</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х40 - 140 - Белый Лучик</t>
+  </si>
+  <si>
+    <t>4681001613411</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 70х70 - Вечерний песок</t>
+  </si>
+  <si>
+    <t>4681001613404</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 175х215 - "Сирента"</t>
+  </si>
+  <si>
+    <t>4681001613398</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 300х300 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001613381</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 145х215 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001613374</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001613367</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 70х70 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001613350</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 180х200х30 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001613343</t>
+  </si>
+  <si>
+    <t>Простыня бязь 300х300 - "Кетеван"</t>
+  </si>
+  <si>
+    <t>4681001613336</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х20 - Малахит</t>
+  </si>
+  <si>
+    <t>4681001613329</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - Изумруд Эсмеральды</t>
+  </si>
+  <si>
+    <t>4681001613312</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Фаусто"</t>
+  </si>
+  <si>
+    <t>4681001613305</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 140х200х30 - Изумруд Эсмеральды наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613299</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 120х200х30 - 140 - Миндаль 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613282</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 200х200х20 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001613275</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х30 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4681001613268</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин семейное резинка 160х200х30 - "Селинто"</t>
+  </si>
+  <si>
+    <t>4681001613251</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок King Size семейное резинка 200х200х30 - "Вельбард" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613244</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - Мечта</t>
+  </si>
+  <si>
+    <t>4681001613237</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Лаванда Страйп"</t>
+  </si>
+  <si>
+    <t>4681001613220</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 70х70 - Лайлак</t>
+  </si>
+  <si>
+    <t>4681001613213</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - Светлая орхидея</t>
+  </si>
+  <si>
+    <t>4681001613206</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - Премиум ТС 320 "Лавель"</t>
+  </si>
+  <si>
+    <t>4681001613190</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - Премиум ТС 320 "Лиминал"</t>
+  </si>
+  <si>
+    <t>4681001613183</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро резинка 160х200х30 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001613176</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001613169</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль семейное резинка 160х200х30 - 110 - Озеро Цветов</t>
+  </si>
+  <si>
+    <t>4681001613152</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - "Вэспер"</t>
+  </si>
+  <si>
+    <t>4681001613145</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - Гестхаус Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001613138</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - 120 - Кремовый Бутон наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613121</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х50 - "Нева"</t>
+  </si>
+  <si>
+    <t>4681001613114</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 150х220 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4681001613107</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 150х220 - "Сумерин"</t>
+  </si>
+  <si>
+    <t>4681001613091</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 140х200х30 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001613084</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль Евро-макси - "Асуль" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613077</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - 120 - Парковая Роза наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613060</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь семейное - 120 - Пантеон А+В</t>
+  </si>
+  <si>
+    <t>4681001613053</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил резинка 140х200х40 - "Сахарная роза"</t>
+  </si>
+  <si>
+    <t>4681001613046</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4681001613039</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - Блу Скай наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613022</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное с Евро простыней - "Потягуш"</t>
+  </si>
+  <si>
+    <t>4681001613015</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 220х240 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4681001613008</t>
+  </si>
+  <si>
+    <t>Простыня сатин 180х220 - "Хореография"</t>
+  </si>
+  <si>
+    <t>4681001612995</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Белый</t>
+  </si>
+  <si>
+    <t>4681001613473</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 2 спальное Евро простыня - "Бездна" наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -68716,6 +69013,545 @@
         <v>8536</v>
       </c>
     </row>
+    <row r="4273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4273" t="s">
+        <v>8615</v>
+      </c>
+      <c r="B4273" t="s">
+        <v>8616</v>
+      </c>
+      <c r="C4273" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4274" t="s">
+        <v>8618</v>
+      </c>
+      <c r="B4274" t="s">
+        <v>8619</v>
+      </c>
+      <c r="C4274" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4275" t="s">
+        <v>8620</v>
+      </c>
+      <c r="B4275" t="s">
+        <v>8621</v>
+      </c>
+      <c r="C4275" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4276" t="s">
+        <v>8622</v>
+      </c>
+      <c r="B4276" t="s">
+        <v>8623</v>
+      </c>
+      <c r="C4276" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4277" t="s">
+        <v>8624</v>
+      </c>
+      <c r="B4277" t="s">
+        <v>8625</v>
+      </c>
+      <c r="C4277" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4278" t="s">
+        <v>8626</v>
+      </c>
+      <c r="B4278" t="s">
+        <v>8627</v>
+      </c>
+      <c r="C4278" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4279" t="s">
+        <v>8628</v>
+      </c>
+      <c r="B4279" t="s">
+        <v>8629</v>
+      </c>
+      <c r="C4279" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4280" t="s">
+        <v>8630</v>
+      </c>
+      <c r="B4280" t="s">
+        <v>8631</v>
+      </c>
+      <c r="C4280" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4281" t="s">
+        <v>8632</v>
+      </c>
+      <c r="B4281" t="s">
+        <v>8633</v>
+      </c>
+      <c r="C4281" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4282" t="s">
+        <v>8634</v>
+      </c>
+      <c r="B4282" t="s">
+        <v>8635</v>
+      </c>
+      <c r="C4282" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4283" t="s">
+        <v>8636</v>
+      </c>
+      <c r="B4283" t="s">
+        <v>8637</v>
+      </c>
+      <c r="C4283" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4284" t="s">
+        <v>8638</v>
+      </c>
+      <c r="B4284" t="s">
+        <v>8639</v>
+      </c>
+      <c r="C4284" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4285" t="s">
+        <v>8640</v>
+      </c>
+      <c r="B4285" t="s">
+        <v>8641</v>
+      </c>
+      <c r="C4285" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4286" t="s">
+        <v>8642</v>
+      </c>
+      <c r="B4286" t="s">
+        <v>8643</v>
+      </c>
+      <c r="C4286" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4287" t="s">
+        <v>8644</v>
+      </c>
+      <c r="B4287" t="s">
+        <v>8645</v>
+      </c>
+      <c r="C4287" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4288" t="s">
+        <v>8646</v>
+      </c>
+      <c r="B4288" t="s">
+        <v>8647</v>
+      </c>
+      <c r="C4288" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4289" t="s">
+        <v>8648</v>
+      </c>
+      <c r="B4289" t="s">
+        <v>8649</v>
+      </c>
+      <c r="C4289" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4290" t="s">
+        <v>8650</v>
+      </c>
+      <c r="B4290" t="s">
+        <v>8651</v>
+      </c>
+      <c r="C4290" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4291" t="s">
+        <v>8652</v>
+      </c>
+      <c r="B4291" t="s">
+        <v>8653</v>
+      </c>
+      <c r="C4291" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4292" t="s">
+        <v>8654</v>
+      </c>
+      <c r="B4292" t="s">
+        <v>8655</v>
+      </c>
+      <c r="C4292" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4293" t="s">
+        <v>8656</v>
+      </c>
+      <c r="B4293" t="s">
+        <v>8657</v>
+      </c>
+      <c r="C4293" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4294" t="s">
+        <v>8658</v>
+      </c>
+      <c r="B4294" t="s">
+        <v>8659</v>
+      </c>
+      <c r="C4294" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4295" t="s">
+        <v>8660</v>
+      </c>
+      <c r="B4295" t="s">
+        <v>8661</v>
+      </c>
+      <c r="C4295" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4296" t="s">
+        <v>8662</v>
+      </c>
+      <c r="B4296" t="s">
+        <v>8663</v>
+      </c>
+      <c r="C4296" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4297" t="s">
+        <v>8664</v>
+      </c>
+      <c r="B4297" t="s">
+        <v>8665</v>
+      </c>
+      <c r="C4297" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4298" t="s">
+        <v>8666</v>
+      </c>
+      <c r="B4298" t="s">
+        <v>8667</v>
+      </c>
+      <c r="C4298" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4299" t="s">
+        <v>8668</v>
+      </c>
+      <c r="B4299" t="s">
+        <v>8669</v>
+      </c>
+      <c r="C4299" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4300" t="s">
+        <v>8670</v>
+      </c>
+      <c r="B4300" t="s">
+        <v>8671</v>
+      </c>
+      <c r="C4300" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4301" t="s">
+        <v>8672</v>
+      </c>
+      <c r="B4301" t="s">
+        <v>8673</v>
+      </c>
+      <c r="C4301" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4302" t="s">
+        <v>8674</v>
+      </c>
+      <c r="B4302" t="s">
+        <v>8675</v>
+      </c>
+      <c r="C4302" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4303" t="s">
+        <v>8676</v>
+      </c>
+      <c r="B4303" t="s">
+        <v>8677</v>
+      </c>
+      <c r="C4303" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4304" t="s">
+        <v>8678</v>
+      </c>
+      <c r="B4304" t="s">
+        <v>8679</v>
+      </c>
+      <c r="C4304" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4305" t="s">
+        <v>8680</v>
+      </c>
+      <c r="B4305" t="s">
+        <v>8681</v>
+      </c>
+      <c r="C4305" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4306" t="s">
+        <v>8682</v>
+      </c>
+      <c r="B4306" t="s">
+        <v>8683</v>
+      </c>
+      <c r="C4306" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4307" t="s">
+        <v>8684</v>
+      </c>
+      <c r="B4307" t="s">
+        <v>8685</v>
+      </c>
+      <c r="C4307" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4308" t="s">
+        <v>8686</v>
+      </c>
+      <c r="B4308" t="s">
+        <v>8687</v>
+      </c>
+      <c r="C4308" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4309" t="s">
+        <v>8688</v>
+      </c>
+      <c r="B4309" t="s">
+        <v>8689</v>
+      </c>
+      <c r="C4309" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4310" t="s">
+        <v>8690</v>
+      </c>
+      <c r="B4310" t="s">
+        <v>8691</v>
+      </c>
+      <c r="C4310" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4311" t="s">
+        <v>8692</v>
+      </c>
+      <c r="B4311" t="s">
+        <v>8693</v>
+      </c>
+      <c r="C4311" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4312" t="s">
+        <v>8694</v>
+      </c>
+      <c r="B4312" t="s">
+        <v>8695</v>
+      </c>
+      <c r="C4312" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4313" t="s">
+        <v>8696</v>
+      </c>
+      <c r="B4313" t="s">
+        <v>8697</v>
+      </c>
+      <c r="C4313" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4314" t="s">
+        <v>8698</v>
+      </c>
+      <c r="B4314" t="s">
+        <v>8699</v>
+      </c>
+      <c r="C4314" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4315" t="s">
+        <v>8700</v>
+      </c>
+      <c r="B4315" t="s">
+        <v>8701</v>
+      </c>
+      <c r="C4315" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4316" t="s">
+        <v>8702</v>
+      </c>
+      <c r="B4316" t="s">
+        <v>8703</v>
+      </c>
+      <c r="C4316" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4317" t="s">
+        <v>8704</v>
+      </c>
+      <c r="B4317" t="s">
+        <v>8705</v>
+      </c>
+      <c r="C4317" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4318" t="s">
+        <v>8706</v>
+      </c>
+      <c r="B4318" t="s">
+        <v>8707</v>
+      </c>
+      <c r="C4318" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4319" t="s">
+        <v>8708</v>
+      </c>
+      <c r="B4319" t="s">
+        <v>8709</v>
+      </c>
+      <c r="C4319" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4320" t="s">
+        <v>8710</v>
+      </c>
+      <c r="B4320" t="s">
+        <v>8711</v>
+      </c>
+      <c r="C4320" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row r="4321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4321" t="s">
+        <v>8712</v>
+      </c>
+      <c r="B4321" t="s">
+        <v>8713</v>
+      </c>
+      <c r="C4321" t="s">
+        <v>8617</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11457" uniqueCount="8714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11502" uniqueCount="8745">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -26159,6 +26159,99 @@
   </si>
   <si>
     <t>КПБ Постельное бельё микросатин 2 спальное Евро простыня - "Бездна" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613626</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 220х240 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>12-05-2026</t>
+  </si>
+  <si>
+    <t>4681001613619</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль 2 спальное - 110 - Изысканность</t>
+  </si>
+  <si>
+    <t>4681001613602</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Димитра"</t>
+  </si>
+  <si>
+    <t>4681001613596</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 280х280 - 135 - Безлунная ночь 1х1</t>
+  </si>
+  <si>
+    <t>4681001613589</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 280х280 - 140 - Вулкан 1х1</t>
+  </si>
+  <si>
+    <t>4681001613572</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Огнерон"</t>
+  </si>
+  <si>
+    <t>4681001613565</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 120х200х20 - "Туманная Аура"</t>
+  </si>
+  <si>
+    <t>4681001613558</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 160х200х30 - 125 - Радмила</t>
+  </si>
+  <si>
+    <t>4681001613541</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - "Твист"</t>
+  </si>
+  <si>
+    <t>4681001613534</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 260х260 - 135 - Эмерэльд 1х1</t>
+  </si>
+  <si>
+    <t>4681001613527</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 80х200х30 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001613510</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 70х70 - Сладкий сон (А+В)</t>
+  </si>
+  <si>
+    <t>4681001613503</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 200х220 - 110 - Белоснежный луч</t>
+  </si>
+  <si>
+    <t>4681001613497</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 200х220 - "Лазурная гладь"</t>
+  </si>
+  <si>
+    <t>4681001613480</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 175х215 - 135 - Дарк Блу 1х1</t>
   </si>
 </sst>
 </file>
@@ -69552,6 +69645,171 @@
         <v>8617</v>
       </c>
     </row>
+    <row r="4322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4322" t="s">
+        <v>8714</v>
+      </c>
+      <c r="B4322" t="s">
+        <v>8715</v>
+      </c>
+      <c r="C4322" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4323" t="s">
+        <v>8717</v>
+      </c>
+      <c r="B4323" t="s">
+        <v>8718</v>
+      </c>
+      <c r="C4323" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4324" t="s">
+        <v>8719</v>
+      </c>
+      <c r="B4324" t="s">
+        <v>8720</v>
+      </c>
+      <c r="C4324" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4325" t="s">
+        <v>8721</v>
+      </c>
+      <c r="B4325" t="s">
+        <v>8722</v>
+      </c>
+      <c r="C4325" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4326" t="s">
+        <v>8723</v>
+      </c>
+      <c r="B4326" t="s">
+        <v>8724</v>
+      </c>
+      <c r="C4326" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4327" t="s">
+        <v>8725</v>
+      </c>
+      <c r="B4327" t="s">
+        <v>8726</v>
+      </c>
+      <c r="C4327" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4328" t="s">
+        <v>8727</v>
+      </c>
+      <c r="B4328" t="s">
+        <v>8728</v>
+      </c>
+      <c r="C4328" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4329" t="s">
+        <v>8729</v>
+      </c>
+      <c r="B4329" t="s">
+        <v>8730</v>
+      </c>
+      <c r="C4329" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4330" t="s">
+        <v>8731</v>
+      </c>
+      <c r="B4330" t="s">
+        <v>8732</v>
+      </c>
+      <c r="C4330" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4331" t="s">
+        <v>8733</v>
+      </c>
+      <c r="B4331" t="s">
+        <v>8734</v>
+      </c>
+      <c r="C4331" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4332" t="s">
+        <v>8735</v>
+      </c>
+      <c r="B4332" t="s">
+        <v>8736</v>
+      </c>
+      <c r="C4332" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4333" t="s">
+        <v>8737</v>
+      </c>
+      <c r="B4333" t="s">
+        <v>8738</v>
+      </c>
+      <c r="C4333" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4334" t="s">
+        <v>8739</v>
+      </c>
+      <c r="B4334" t="s">
+        <v>8740</v>
+      </c>
+      <c r="C4334" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4335" t="s">
+        <v>8741</v>
+      </c>
+      <c r="B4335" t="s">
+        <v>8742</v>
+      </c>
+      <c r="C4335" t="s">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="4336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4336" t="s">
+        <v>8743</v>
+      </c>
+      <c r="B4336" t="s">
+        <v>8744</v>
+      </c>
+      <c r="C4336" t="s">
+        <v>8716</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11502" uniqueCount="8745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11568" uniqueCount="8790">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -26252,6 +26252,141 @@
   </si>
   <si>
     <t>Пододеяльник страйп-сатин 175х215 - 135 - Дарк Блу 1х1</t>
+  </si>
+  <si>
+    <t>4681001613848</t>
+  </si>
+  <si>
+    <t>Простыня жаккард резинка 140х200х30 - Флорибунда</t>
+  </si>
+  <si>
+    <t>13-05-2026</t>
+  </si>
+  <si>
+    <t>4681001613831</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - Прохлада ментола наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613824</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 125 - Голубая бирюза</t>
+  </si>
+  <si>
+    <t>4681001613817</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 40х40 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001613800</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х40 - 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4681001613794</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 180х200х20 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001613787</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 200х220 - Мазарин блу</t>
+  </si>
+  <si>
+    <t>4681001613770</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - Мазарин блу</t>
+  </si>
+  <si>
+    <t>4681001613763</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - "Манцель" 3х3</t>
+  </si>
+  <si>
+    <t>4681001613756</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 140х200х30 - "Страстный гранат"</t>
+  </si>
+  <si>
+    <t>4681001613749</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 140х200х30 - 125 - Марсала</t>
+  </si>
+  <si>
+    <t>4681001613732</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 90х200х30 - 125 - Куманика</t>
+  </si>
+  <si>
+    <t>4681001613725</t>
+  </si>
+  <si>
+    <t>Простыня сатин 200х220 - 140 - Сияющая бирюза</t>
+  </si>
+  <si>
+    <t>4681001613718</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Лаванда 1х1</t>
+  </si>
+  <si>
+    <t>4681001613701</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - "Фиалетта" 1х1</t>
+  </si>
+  <si>
+    <t>4681001613695</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 140 - Сирень 1х1</t>
+  </si>
+  <si>
+    <t>4681001613688</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001613671</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Челестэ"</t>
+  </si>
+  <si>
+    <t>4681001613664</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 90х200х40 - "Челестэ"</t>
+  </si>
+  <si>
+    <t>4681001613657</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Челестэ"</t>
+  </si>
+  <si>
+    <t>4681001613640</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4681001613633</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро резинка 160х200х30 - "Небесный глянцевая"</t>
   </si>
 </sst>
 </file>
@@ -69810,6 +69945,248 @@
         <v>8716</v>
       </c>
     </row>
+    <row r="4337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4337" t="s">
+        <v>8745</v>
+      </c>
+      <c r="B4337" t="s">
+        <v>8746</v>
+      </c>
+      <c r="C4337" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4338" t="s">
+        <v>8748</v>
+      </c>
+      <c r="B4338" t="s">
+        <v>8749</v>
+      </c>
+      <c r="C4338" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4339" t="s">
+        <v>8750</v>
+      </c>
+      <c r="B4339" t="s">
+        <v>8751</v>
+      </c>
+      <c r="C4339" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4340" t="s">
+        <v>8752</v>
+      </c>
+      <c r="B4340" t="s">
+        <v>8753</v>
+      </c>
+      <c r="C4340" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4341" t="s">
+        <v>8754</v>
+      </c>
+      <c r="B4341" t="s">
+        <v>8755</v>
+      </c>
+      <c r="C4341" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4342" t="s">
+        <v>8756</v>
+      </c>
+      <c r="B4342" t="s">
+        <v>8757</v>
+      </c>
+      <c r="C4342" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4343" t="s">
+        <v>8758</v>
+      </c>
+      <c r="B4343" t="s">
+        <v>8759</v>
+      </c>
+      <c r="C4343" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4344" t="s">
+        <v>8760</v>
+      </c>
+      <c r="B4344" t="s">
+        <v>8761</v>
+      </c>
+      <c r="C4344" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4345" t="s">
+        <v>8762</v>
+      </c>
+      <c r="B4345" t="s">
+        <v>8763</v>
+      </c>
+      <c r="C4345" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4346" t="s">
+        <v>8764</v>
+      </c>
+      <c r="B4346" t="s">
+        <v>8765</v>
+      </c>
+      <c r="C4346" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4347" t="s">
+        <v>8766</v>
+      </c>
+      <c r="B4347" t="s">
+        <v>8767</v>
+      </c>
+      <c r="C4347" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4348" t="s">
+        <v>8768</v>
+      </c>
+      <c r="B4348" t="s">
+        <v>8769</v>
+      </c>
+      <c r="C4348" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4349" t="s">
+        <v>8770</v>
+      </c>
+      <c r="B4349" t="s">
+        <v>8771</v>
+      </c>
+      <c r="C4349" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4350" t="s">
+        <v>8772</v>
+      </c>
+      <c r="B4350" t="s">
+        <v>8773</v>
+      </c>
+      <c r="C4350" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4351" t="s">
+        <v>8774</v>
+      </c>
+      <c r="B4351" t="s">
+        <v>8775</v>
+      </c>
+      <c r="C4351" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4352" t="s">
+        <v>8776</v>
+      </c>
+      <c r="B4352" t="s">
+        <v>8777</v>
+      </c>
+      <c r="C4352" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4353" t="s">
+        <v>8778</v>
+      </c>
+      <c r="B4353" t="s">
+        <v>8779</v>
+      </c>
+      <c r="C4353" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4354" t="s">
+        <v>8780</v>
+      </c>
+      <c r="B4354" t="s">
+        <v>8781</v>
+      </c>
+      <c r="C4354" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4355" t="s">
+        <v>8782</v>
+      </c>
+      <c r="B4355" t="s">
+        <v>8783</v>
+      </c>
+      <c r="C4355" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4356" t="s">
+        <v>8784</v>
+      </c>
+      <c r="B4356" t="s">
+        <v>8785</v>
+      </c>
+      <c r="C4356" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4357" t="s">
+        <v>8786</v>
+      </c>
+      <c r="B4357" t="s">
+        <v>8787</v>
+      </c>
+      <c r="C4357" t="s">
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="4358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4358" t="s">
+        <v>8788</v>
+      </c>
+      <c r="B4358" t="s">
+        <v>8789</v>
+      </c>
+      <c r="C4358" t="s">
+        <v>8747</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11568" uniqueCount="8790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11589" uniqueCount="8805">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -26387,6 +26387,51 @@
   </si>
   <si>
     <t>КПБ Постельное бельё сатин Евро резинка 160х200х30 - "Небесный глянцевая"</t>
+  </si>
+  <si>
+    <t>4681001613916</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х30 - Черный блеск</t>
+  </si>
+  <si>
+    <t>14-05-2026</t>
+  </si>
+  <si>
+    <t>4681001613909</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х30 - "Твист"</t>
+  </si>
+  <si>
+    <t>4681001613893</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 140х200х30 - "Лемпи" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613886</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - "Галант"</t>
+  </si>
+  <si>
+    <t>4681001613879</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х30 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4681001613862</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 40х60 - "Нева"</t>
+  </si>
+  <si>
+    <t>4681001613855</t>
+  </si>
+  <si>
+    <t>Простыня из страйп-сатина на резинке 80 х 200 х 40 - М - 135 - Блу Хейз 1х1</t>
   </si>
 </sst>
 </file>
@@ -70187,6 +70232,83 @@
         <v>8747</v>
       </c>
     </row>
+    <row r="4359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4359" t="s">
+        <v>8790</v>
+      </c>
+      <c r="B4359" t="s">
+        <v>8791</v>
+      </c>
+      <c r="C4359" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4360" t="s">
+        <v>8793</v>
+      </c>
+      <c r="B4360" t="s">
+        <v>8794</v>
+      </c>
+      <c r="C4360" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4361" t="s">
+        <v>8795</v>
+      </c>
+      <c r="B4361" t="s">
+        <v>8796</v>
+      </c>
+      <c r="C4361" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4362" t="s">
+        <v>8797</v>
+      </c>
+      <c r="B4362" t="s">
+        <v>8798</v>
+      </c>
+      <c r="C4362" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4363" t="s">
+        <v>8799</v>
+      </c>
+      <c r="B4363" t="s">
+        <v>8800</v>
+      </c>
+      <c r="C4363" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4364" t="s">
+        <v>8801</v>
+      </c>
+      <c r="B4364" t="s">
+        <v>8802</v>
+      </c>
+      <c r="C4364" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4365" t="s">
+        <v>8803</v>
+      </c>
+      <c r="B4365" t="s">
+        <v>8804</v>
+      </c>
+      <c r="C4365" t="s">
+        <v>8792</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11589" uniqueCount="8805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11628" uniqueCount="8831">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -26432,6 +26432,84 @@
   </si>
   <si>
     <t>Простыня из страйп-сатина на резинке 80 х 200 х 40 - М - 135 - Блу Хейз 1х1</t>
+  </si>
+  <si>
+    <t>4681001614043</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 180х200х30 - "Фиолетовый Шёпот"</t>
+  </si>
+  <si>
+    <t>4681001614036</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - "Крылатые сны"</t>
+  </si>
+  <si>
+    <t>4681001614029</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 160х200х30 - Молочный наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614012</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 80х200х10 - "Зайга"</t>
+  </si>
+  <si>
+    <t>4681001614005</t>
+  </si>
+  <si>
+    <t>Простыня сатин 220х240 - 140 - "Можиана Люкс"</t>
+  </si>
+  <si>
+    <t>4681001613992</t>
+  </si>
+  <si>
+    <t>Простыня бязь 200х220 - 142 - Рецепт любви</t>
+  </si>
+  <si>
+    <t>4681001613985</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Макена"</t>
+  </si>
+  <si>
+    <t>4681001613978</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - "Лиловый тауп"</t>
+  </si>
+  <si>
+    <t>4681001613961</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное - "Гуголету"</t>
+  </si>
+  <si>
+    <t>4681001613954</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное резинка 140х200х30 - "Джуман" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613947</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 175х215 - "Легкий роман"</t>
+  </si>
+  <si>
+    <t>4681001613930</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - Аква Циан наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001613923</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин резинка 220х220х30 - 140 - Белый Лучик</t>
   </si>
 </sst>
 </file>
@@ -70309,6 +70387,149 @@
         <v>8792</v>
       </c>
     </row>
+    <row r="4366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4366" t="s">
+        <v>8805</v>
+      </c>
+      <c r="B4366" t="s">
+        <v>8806</v>
+      </c>
+      <c r="C4366" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4367" t="s">
+        <v>8807</v>
+      </c>
+      <c r="B4367" t="s">
+        <v>8808</v>
+      </c>
+      <c r="C4367" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4368" t="s">
+        <v>8809</v>
+      </c>
+      <c r="B4368" t="s">
+        <v>8810</v>
+      </c>
+      <c r="C4368" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4369" t="s">
+        <v>8811</v>
+      </c>
+      <c r="B4369" t="s">
+        <v>8812</v>
+      </c>
+      <c r="C4369" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4370" t="s">
+        <v>8813</v>
+      </c>
+      <c r="B4370" t="s">
+        <v>8814</v>
+      </c>
+      <c r="C4370" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4371" t="s">
+        <v>8815</v>
+      </c>
+      <c r="B4371" t="s">
+        <v>8816</v>
+      </c>
+      <c r="C4371" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4372" t="s">
+        <v>8817</v>
+      </c>
+      <c r="B4372" t="s">
+        <v>8818</v>
+      </c>
+      <c r="C4372" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4373" t="s">
+        <v>8819</v>
+      </c>
+      <c r="B4373" t="s">
+        <v>8820</v>
+      </c>
+      <c r="C4373" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4374" t="s">
+        <v>8821</v>
+      </c>
+      <c r="B4374" t="s">
+        <v>8822</v>
+      </c>
+      <c r="C4374" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4375" t="s">
+        <v>8823</v>
+      </c>
+      <c r="B4375" t="s">
+        <v>8824</v>
+      </c>
+      <c r="C4375" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4376" t="s">
+        <v>8825</v>
+      </c>
+      <c r="B4376" t="s">
+        <v>8826</v>
+      </c>
+      <c r="C4376" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4377" t="s">
+        <v>8827</v>
+      </c>
+      <c r="B4377" t="s">
+        <v>8828</v>
+      </c>
+      <c r="C4377" t="s">
+        <v>8792</v>
+      </c>
+    </row>
+    <row r="4378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4378" t="s">
+        <v>8829</v>
+      </c>
+      <c r="B4378" t="s">
+        <v>8830</v>
+      </c>
+      <c r="C4378" t="s">
+        <v>8792</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11628" uniqueCount="8831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11682" uniqueCount="8868">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -26510,6 +26510,117 @@
   </si>
   <si>
     <t>Простыня круглая сатин резинка 220х220х30 - 140 - Белый Лучик</t>
+  </si>
+  <si>
+    <t>4681001614210</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 145х215 - "Эфирида"</t>
+  </si>
+  <si>
+    <t>15-05-2026</t>
+  </si>
+  <si>
+    <t>4681001614203</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное на резинке 140х200х30 - М - 80 - Югацу</t>
+  </si>
+  <si>
+    <t>4681001614197</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 90х200х30 - "Макена"</t>
+  </si>
+  <si>
+    <t>4681001614180</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - Мечта</t>
+  </si>
+  <si>
+    <t>4681001614173</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - Гранола наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614166</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - "Лазурный Мегаполис"</t>
+  </si>
+  <si>
+    <t>4681001614159</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Думнат"</t>
+  </si>
+  <si>
+    <t>4681001614142</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Думнат"</t>
+  </si>
+  <si>
+    <t>4681001614135</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 180х220 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4681001614128</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая 200х220 - Мулетон Хлопок</t>
+  </si>
+  <si>
+    <t>4681001614111</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Солнечные лучи"</t>
+  </si>
+  <si>
+    <t>4681001614104</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 200х200х20 - "Лазурная гладь"</t>
+  </si>
+  <si>
+    <t>4681001614098</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 60х60 - 140 - Лаванда 1х1</t>
+  </si>
+  <si>
+    <t>4681001614081</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001614074</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль Евро резинка 160х200х30 - "Асуль" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614067</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - Кончерто гроссо</t>
+  </si>
+  <si>
+    <t>4681001614050</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - Грей Стайл</t>
+  </si>
+  <si>
+    <t>4681001614227</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 145х215 - "Рендалис"</t>
   </si>
 </sst>
 </file>
@@ -70530,6 +70641,204 @@
         <v>8792</v>
       </c>
     </row>
+    <row r="4379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4379" t="s">
+        <v>8831</v>
+      </c>
+      <c r="B4379" t="s">
+        <v>8832</v>
+      </c>
+      <c r="C4379" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4380" t="s">
+        <v>8834</v>
+      </c>
+      <c r="B4380" t="s">
+        <v>8835</v>
+      </c>
+      <c r="C4380" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4381" t="s">
+        <v>8836</v>
+      </c>
+      <c r="B4381" t="s">
+        <v>8837</v>
+      </c>
+      <c r="C4381" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4382" t="s">
+        <v>8838</v>
+      </c>
+      <c r="B4382" t="s">
+        <v>8839</v>
+      </c>
+      <c r="C4382" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4383" t="s">
+        <v>8840</v>
+      </c>
+      <c r="B4383" t="s">
+        <v>8841</v>
+      </c>
+      <c r="C4383" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4384" t="s">
+        <v>8842</v>
+      </c>
+      <c r="B4384" t="s">
+        <v>8843</v>
+      </c>
+      <c r="C4384" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4385" t="s">
+        <v>8844</v>
+      </c>
+      <c r="B4385" t="s">
+        <v>8845</v>
+      </c>
+      <c r="C4385" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4386" t="s">
+        <v>8846</v>
+      </c>
+      <c r="B4386" t="s">
+        <v>8847</v>
+      </c>
+      <c r="C4386" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4387" t="s">
+        <v>8848</v>
+      </c>
+      <c r="B4387" t="s">
+        <v>8849</v>
+      </c>
+      <c r="C4387" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4388" t="s">
+        <v>8850</v>
+      </c>
+      <c r="B4388" t="s">
+        <v>8851</v>
+      </c>
+      <c r="C4388" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4389" t="s">
+        <v>8852</v>
+      </c>
+      <c r="B4389" t="s">
+        <v>8853</v>
+      </c>
+      <c r="C4389" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4390" t="s">
+        <v>8854</v>
+      </c>
+      <c r="B4390" t="s">
+        <v>8855</v>
+      </c>
+      <c r="C4390" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4391" t="s">
+        <v>8856</v>
+      </c>
+      <c r="B4391" t="s">
+        <v>8857</v>
+      </c>
+      <c r="C4391" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4392" t="s">
+        <v>8858</v>
+      </c>
+      <c r="B4392" t="s">
+        <v>8859</v>
+      </c>
+      <c r="C4392" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4393" t="s">
+        <v>8860</v>
+      </c>
+      <c r="B4393" t="s">
+        <v>8861</v>
+      </c>
+      <c r="C4393" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4394" t="s">
+        <v>8862</v>
+      </c>
+      <c r="B4394" t="s">
+        <v>8863</v>
+      </c>
+      <c r="C4394" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4395" t="s">
+        <v>8864</v>
+      </c>
+      <c r="B4395" t="s">
+        <v>8865</v>
+      </c>
+      <c r="C4395" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="4396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4396" t="s">
+        <v>8866</v>
+      </c>
+      <c r="B4396" t="s">
+        <v>8867</v>
+      </c>
+      <c r="C4396" t="s">
+        <v>8833</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11682" uniqueCount="8868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11868" uniqueCount="8993">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -26621,6 +26621,381 @@
   </si>
   <si>
     <t>Пододеяльник жаккард 145х215 - "Рендалис"</t>
+  </si>
+  <si>
+    <t>4681001614845</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - 142 - Белый</t>
+  </si>
+  <si>
+    <t>16-05-2026</t>
+  </si>
+  <si>
+    <t>4681001614838</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Вулкан 1х1</t>
+  </si>
+  <si>
+    <t>4681001614821</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное - "Серебряный Лес" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614814</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное - "Танец крыльев" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614807</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - 4216 Серебро наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614791</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин браш 2 спальное Евро простыня - Лайлак наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614784</t>
+  </si>
+  <si>
+    <t>Простыня Жатка 180х220 - "Файза"</t>
+  </si>
+  <si>
+    <t>4681001614777</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 130 - "Дивуар" 1х1</t>
+  </si>
+  <si>
+    <t>4681001614760</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - "Бартош"</t>
+  </si>
+  <si>
+    <t>4681001614753</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 50х70 - 110 - Полнолуние</t>
+  </si>
+  <si>
+    <t>4681001614746</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 180х200х40 - 110 - Полнолуние</t>
+  </si>
+  <si>
+    <t>4681001614739</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 200х220 - 110 - Полнолуние</t>
+  </si>
+  <si>
+    <t>4681001614722</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - Грей блес</t>
+  </si>
+  <si>
+    <t>4681001614715</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 180х220 - 110 - Озеро Цветов</t>
+  </si>
+  <si>
+    <t>4681001614708</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Богумила"</t>
+  </si>
+  <si>
+    <t>4681001614692</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 220х240 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001614685</t>
+  </si>
+  <si>
+    <t>Простыня Жатка на резинке 180х200х30 - "Файза"</t>
+  </si>
+  <si>
+    <t>4681001614678</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Меропа</t>
+  </si>
+  <si>
+    <t>4681001614661</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - Морбидецца</t>
+  </si>
+  <si>
+    <t>4681001614654</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - Зюйд Ост</t>
+  </si>
+  <si>
+    <t>4681001614647</t>
+  </si>
+  <si>
+    <t>Наволочка микрофибра 70х70 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4681001614630</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное резинка 160х200х30 - "Вельбард" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614623</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное резинка 160х200х30 - Зеленый чай наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614616</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 140х200х20 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001614609</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001614593</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х30 - "Астролябия" А+В</t>
+  </si>
+  <si>
+    <t>4681001614586</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 135 - Темно-синий 0,5х0,5</t>
+  </si>
+  <si>
+    <t>4681001614579</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х20 - 135 - Темно-синий 0,5х0,5</t>
+  </si>
+  <si>
+    <t>4681001614562</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 130 - Полуночный ультрамарин 1х1</t>
+  </si>
+  <si>
+    <t>4681001614555</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4681001614548</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х30 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4681001614531</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4681001614524</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 120х200х20 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4681001614517</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - Горчица</t>
+  </si>
+  <si>
+    <t>4681001614500</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х30 - "Лаванда Страйп"</t>
+  </si>
+  <si>
+    <t>4681001614494</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Горчица</t>
+  </si>
+  <si>
+    <t>4681001614487</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Замороженный Перец"</t>
+  </si>
+  <si>
+    <t>4681001614470</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х240х20 - 130 - Теплый металлик 1х1</t>
+  </si>
+  <si>
+    <t>4681001614463</t>
+  </si>
+  <si>
+    <t>Простыня жатка 260х260 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001614456</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное - 135 - Фирюз 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614449</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное - 135 - Белый 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614432</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное - 140 - Агатовый серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001614425</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х20 - "Стиллит"</t>
+  </si>
+  <si>
+    <t>4681001614418</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Стиллит"</t>
+  </si>
+  <si>
+    <t>4681001614401</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 200х220 - 140 - Асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4681001614395</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 230х230х30 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001614388</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Марципан"</t>
+  </si>
+  <si>
+    <t>4681001614371</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Марципан"</t>
+  </si>
+  <si>
+    <t>4681001614364</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Золти"</t>
+  </si>
+  <si>
+    <t>4681001614357</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 160х200х20 - "Триша" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614340</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - Бонди</t>
+  </si>
+  <si>
+    <t>4681001614333</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - Горчица</t>
+  </si>
+  <si>
+    <t>4681001614326</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х20 - "Аделаида"</t>
+  </si>
+  <si>
+    <t>4681001614319</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х20 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001614302</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х20 - "Ледяной Мрамор"</t>
+  </si>
+  <si>
+    <t>4681001614296</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 200х220 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001614289</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 200х200х40 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001614272</t>
+  </si>
+  <si>
+    <t>Наволочка микрофибра 40х60 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001614265</t>
+  </si>
+  <si>
+    <t>Наволочка микрофибра 70х70 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001614258</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Хельми" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614241</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 70х70 - 110 - Веяние А+В</t>
+  </si>
+  <si>
+    <t>4681001614234</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - "Туманная Ветвь" наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -70839,6 +71214,688 @@
         <v>8833</v>
       </c>
     </row>
+    <row r="4397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4397" t="s">
+        <v>8868</v>
+      </c>
+      <c r="B4397" t="s">
+        <v>8869</v>
+      </c>
+      <c r="C4397" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4398" t="s">
+        <v>8871</v>
+      </c>
+      <c r="B4398" t="s">
+        <v>8872</v>
+      </c>
+      <c r="C4398" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4399" t="s">
+        <v>8873</v>
+      </c>
+      <c r="B4399" t="s">
+        <v>8874</v>
+      </c>
+      <c r="C4399" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4400" t="s">
+        <v>8875</v>
+      </c>
+      <c r="B4400" t="s">
+        <v>8876</v>
+      </c>
+      <c r="C4400" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4401" t="s">
+        <v>8877</v>
+      </c>
+      <c r="B4401" t="s">
+        <v>8878</v>
+      </c>
+      <c r="C4401" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4402" t="s">
+        <v>8879</v>
+      </c>
+      <c r="B4402" t="s">
+        <v>8880</v>
+      </c>
+      <c r="C4402" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4403" t="s">
+        <v>8881</v>
+      </c>
+      <c r="B4403" t="s">
+        <v>8882</v>
+      </c>
+      <c r="C4403" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4404" t="s">
+        <v>8883</v>
+      </c>
+      <c r="B4404" t="s">
+        <v>8884</v>
+      </c>
+      <c r="C4404" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4405" t="s">
+        <v>8885</v>
+      </c>
+      <c r="B4405" t="s">
+        <v>8886</v>
+      </c>
+      <c r="C4405" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4406" t="s">
+        <v>8887</v>
+      </c>
+      <c r="B4406" t="s">
+        <v>8888</v>
+      </c>
+      <c r="C4406" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4407" t="s">
+        <v>8889</v>
+      </c>
+      <c r="B4407" t="s">
+        <v>8890</v>
+      </c>
+      <c r="C4407" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4408" t="s">
+        <v>8891</v>
+      </c>
+      <c r="B4408" t="s">
+        <v>8892</v>
+      </c>
+      <c r="C4408" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4409" t="s">
+        <v>8893</v>
+      </c>
+      <c r="B4409" t="s">
+        <v>8894</v>
+      </c>
+      <c r="C4409" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4410" t="s">
+        <v>8895</v>
+      </c>
+      <c r="B4410" t="s">
+        <v>8896</v>
+      </c>
+      <c r="C4410" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4411" t="s">
+        <v>8897</v>
+      </c>
+      <c r="B4411" t="s">
+        <v>8898</v>
+      </c>
+      <c r="C4411" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4412" t="s">
+        <v>8899</v>
+      </c>
+      <c r="B4412" t="s">
+        <v>8900</v>
+      </c>
+      <c r="C4412" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4413" t="s">
+        <v>8901</v>
+      </c>
+      <c r="B4413" t="s">
+        <v>8902</v>
+      </c>
+      <c r="C4413" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4414" t="s">
+        <v>8903</v>
+      </c>
+      <c r="B4414" t="s">
+        <v>8904</v>
+      </c>
+      <c r="C4414" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4415" t="s">
+        <v>8905</v>
+      </c>
+      <c r="B4415" t="s">
+        <v>8906</v>
+      </c>
+      <c r="C4415" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4416" t="s">
+        <v>8907</v>
+      </c>
+      <c r="B4416" t="s">
+        <v>8908</v>
+      </c>
+      <c r="C4416" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4417" t="s">
+        <v>8909</v>
+      </c>
+      <c r="B4417" t="s">
+        <v>8910</v>
+      </c>
+      <c r="C4417" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4418" t="s">
+        <v>8911</v>
+      </c>
+      <c r="B4418" t="s">
+        <v>8912</v>
+      </c>
+      <c r="C4418" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4419" t="s">
+        <v>8913</v>
+      </c>
+      <c r="B4419" t="s">
+        <v>8914</v>
+      </c>
+      <c r="C4419" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4420" t="s">
+        <v>8915</v>
+      </c>
+      <c r="B4420" t="s">
+        <v>8916</v>
+      </c>
+      <c r="C4420" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4421" t="s">
+        <v>8917</v>
+      </c>
+      <c r="B4421" t="s">
+        <v>8918</v>
+      </c>
+      <c r="C4421" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4422" t="s">
+        <v>8919</v>
+      </c>
+      <c r="B4422" t="s">
+        <v>8920</v>
+      </c>
+      <c r="C4422" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4423" t="s">
+        <v>8921</v>
+      </c>
+      <c r="B4423" t="s">
+        <v>8922</v>
+      </c>
+      <c r="C4423" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4424" t="s">
+        <v>8923</v>
+      </c>
+      <c r="B4424" t="s">
+        <v>8924</v>
+      </c>
+      <c r="C4424" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4425" t="s">
+        <v>8925</v>
+      </c>
+      <c r="B4425" t="s">
+        <v>8926</v>
+      </c>
+      <c r="C4425" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4426" t="s">
+        <v>8927</v>
+      </c>
+      <c r="B4426" t="s">
+        <v>8928</v>
+      </c>
+      <c r="C4426" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4427" t="s">
+        <v>8929</v>
+      </c>
+      <c r="B4427" t="s">
+        <v>8930</v>
+      </c>
+      <c r="C4427" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4428" t="s">
+        <v>8931</v>
+      </c>
+      <c r="B4428" t="s">
+        <v>8932</v>
+      </c>
+      <c r="C4428" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4429" t="s">
+        <v>8933</v>
+      </c>
+      <c r="B4429" t="s">
+        <v>8934</v>
+      </c>
+      <c r="C4429" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4430" t="s">
+        <v>8935</v>
+      </c>
+      <c r="B4430" t="s">
+        <v>8936</v>
+      </c>
+      <c r="C4430" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4431" t="s">
+        <v>8937</v>
+      </c>
+      <c r="B4431" t="s">
+        <v>8938</v>
+      </c>
+      <c r="C4431" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4432" t="s">
+        <v>8939</v>
+      </c>
+      <c r="B4432" t="s">
+        <v>8940</v>
+      </c>
+      <c r="C4432" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4433" t="s">
+        <v>8941</v>
+      </c>
+      <c r="B4433" t="s">
+        <v>8942</v>
+      </c>
+      <c r="C4433" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4434" t="s">
+        <v>8943</v>
+      </c>
+      <c r="B4434" t="s">
+        <v>8944</v>
+      </c>
+      <c r="C4434" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4435" t="s">
+        <v>8945</v>
+      </c>
+      <c r="B4435" t="s">
+        <v>8946</v>
+      </c>
+      <c r="C4435" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4436" t="s">
+        <v>8947</v>
+      </c>
+      <c r="B4436" t="s">
+        <v>8948</v>
+      </c>
+      <c r="C4436" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4437" t="s">
+        <v>8949</v>
+      </c>
+      <c r="B4437" t="s">
+        <v>8950</v>
+      </c>
+      <c r="C4437" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4438" t="s">
+        <v>8951</v>
+      </c>
+      <c r="B4438" t="s">
+        <v>8952</v>
+      </c>
+      <c r="C4438" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4439" t="s">
+        <v>8953</v>
+      </c>
+      <c r="B4439" t="s">
+        <v>8954</v>
+      </c>
+      <c r="C4439" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4440" t="s">
+        <v>8955</v>
+      </c>
+      <c r="B4440" t="s">
+        <v>8956</v>
+      </c>
+      <c r="C4440" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4441" t="s">
+        <v>8957</v>
+      </c>
+      <c r="B4441" t="s">
+        <v>8958</v>
+      </c>
+      <c r="C4441" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4442" t="s">
+        <v>8959</v>
+      </c>
+      <c r="B4442" t="s">
+        <v>8960</v>
+      </c>
+      <c r="C4442" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4443" t="s">
+        <v>8961</v>
+      </c>
+      <c r="B4443" t="s">
+        <v>8962</v>
+      </c>
+      <c r="C4443" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4444" t="s">
+        <v>8963</v>
+      </c>
+      <c r="B4444" t="s">
+        <v>8964</v>
+      </c>
+      <c r="C4444" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4445" t="s">
+        <v>8965</v>
+      </c>
+      <c r="B4445" t="s">
+        <v>8966</v>
+      </c>
+      <c r="C4445" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4446" t="s">
+        <v>8967</v>
+      </c>
+      <c r="B4446" t="s">
+        <v>8968</v>
+      </c>
+      <c r="C4446" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4447" t="s">
+        <v>8969</v>
+      </c>
+      <c r="B4447" t="s">
+        <v>8970</v>
+      </c>
+      <c r="C4447" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4448" t="s">
+        <v>8971</v>
+      </c>
+      <c r="B4448" t="s">
+        <v>8972</v>
+      </c>
+      <c r="C4448" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4449" t="s">
+        <v>8973</v>
+      </c>
+      <c r="B4449" t="s">
+        <v>8974</v>
+      </c>
+      <c r="C4449" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4450" t="s">
+        <v>8975</v>
+      </c>
+      <c r="B4450" t="s">
+        <v>8976</v>
+      </c>
+      <c r="C4450" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4451" t="s">
+        <v>8977</v>
+      </c>
+      <c r="B4451" t="s">
+        <v>8978</v>
+      </c>
+      <c r="C4451" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4452" t="s">
+        <v>8979</v>
+      </c>
+      <c r="B4452" t="s">
+        <v>8980</v>
+      </c>
+      <c r="C4452" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4453" t="s">
+        <v>8981</v>
+      </c>
+      <c r="B4453" t="s">
+        <v>8982</v>
+      </c>
+      <c r="C4453" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4454" t="s">
+        <v>8983</v>
+      </c>
+      <c r="B4454" t="s">
+        <v>8984</v>
+      </c>
+      <c r="C4454" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4455" t="s">
+        <v>8985</v>
+      </c>
+      <c r="B4455" t="s">
+        <v>8986</v>
+      </c>
+      <c r="C4455" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4456" t="s">
+        <v>8987</v>
+      </c>
+      <c r="B4456" t="s">
+        <v>8988</v>
+      </c>
+      <c r="C4456" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4457" t="s">
+        <v>8989</v>
+      </c>
+      <c r="B4457" t="s">
+        <v>8990</v>
+      </c>
+      <c r="C4457" t="s">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="4458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4458" t="s">
+        <v>8991</v>
+      </c>
+      <c r="B4458" t="s">
+        <v>8992</v>
+      </c>
+      <c r="C4458" t="s">
+        <v>8870</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11868" uniqueCount="8993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11997" uniqueCount="9080">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -26996,6 +26996,267 @@
   </si>
   <si>
     <t>КПБ Постельное бельё тенсель Евро - "Туманная Ветвь" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615262</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил резинка 120х200х30 - "Лесная тень"</t>
+  </si>
+  <si>
+    <t>17-05-2026</t>
+  </si>
+  <si>
+    <t>4681001615255</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Папоротниковый"</t>
+  </si>
+  <si>
+    <t>4681001615248</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 240х260 - Сиена</t>
+  </si>
+  <si>
+    <t>4681001615231</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 50х70 - Текстура 6 фиолетовый</t>
+  </si>
+  <si>
+    <t>4681001615224</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - 140 - Белый Люкс 3х3 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615217</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Бирюзовый берег</t>
+  </si>
+  <si>
+    <t>4681001615200</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Аметистовый Шёлк"</t>
+  </si>
+  <si>
+    <t>4681001615194</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 140х200х30 - "Розовый Сад" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615187</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001615170</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное - "Замороженный Перец" Универсал</t>
+  </si>
+  <si>
+    <t>4681001615163</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 40х60 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001615156</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 160х200х30 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001615149</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Айвелин"</t>
+  </si>
+  <si>
+    <t>4681001615132</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001615125</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - Морбидецца</t>
+  </si>
+  <si>
+    <t>4681001615118</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное с Евро простыней - "Золотой блеск"</t>
+  </si>
+  <si>
+    <t>4681001615101</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 260х260 - 130 - "Лавандула" 1х1</t>
+  </si>
+  <si>
+    <t>4681001615095</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 260х260 - Насыщенный розовый</t>
+  </si>
+  <si>
+    <t>4681001615088</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 150х220 - 129 Темно-зеленый</t>
+  </si>
+  <si>
+    <t>4681001615071</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х30 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001615064</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Горький шоколад</t>
+  </si>
+  <si>
+    <t>4681001615057</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро-макси резинка 180х200х30 - "Минори" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615040</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Зелёный Страйп"</t>
+  </si>
+  <si>
+    <t>4681001615033</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное на резинке 160х200х20 - "Богумила" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001615026</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х40 - 140 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001615019</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 175х215 - Розариум А+В</t>
+  </si>
+  <si>
+    <t>4681001615002</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное - Белый</t>
+  </si>
+  <si>
+    <t>4681001614999</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - 80 - Теплые Пожелания наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614982</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное - Белый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614975</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 80х200х10 - "Бахати"</t>
+  </si>
+  <si>
+    <t>4681001614968</t>
+  </si>
+  <si>
+    <t>Простыня круглая Жатка на резинке 200х200х30 - "Звездный Сон"</t>
+  </si>
+  <si>
+    <t>4681001614951</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х30 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001614944</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х220х20 - "Тонкий Лист"</t>
+  </si>
+  <si>
+    <t>4681001614937</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - "Тонкий Лист"</t>
+  </si>
+  <si>
+    <t>4681001614920</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 2 спальное - "Кремневый серый" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614913</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 80х200х30 - "Золти"</t>
+  </si>
+  <si>
+    <t>4681001614906</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Гармония линий" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001614890</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - Нирвана</t>
+  </si>
+  <si>
+    <t>4681001614883</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 70х70 - "Милкшейк"</t>
+  </si>
+  <si>
+    <t>4681001614876</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Зеленый чай</t>
+  </si>
+  <si>
+    <t>4681001614869</t>
+  </si>
+  <si>
+    <t>Простыня жатка 200х220 - "Серебряный Папоротник"</t>
+  </si>
+  <si>
+    <t>4681001614852</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 60х60 - 110 - Озеро Цветов</t>
+  </si>
+  <si>
+    <t>4681001615279</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х50 - "Лигурия"</t>
   </si>
 </sst>
 </file>
@@ -71896,6 +72157,479 @@
         <v>8870</v>
       </c>
     </row>
+    <row r="4459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4459" t="s">
+        <v>8993</v>
+      </c>
+      <c r="B4459" t="s">
+        <v>8994</v>
+      </c>
+      <c r="C4459" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4460" t="s">
+        <v>8996</v>
+      </c>
+      <c r="B4460" t="s">
+        <v>8997</v>
+      </c>
+      <c r="C4460" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4461" t="s">
+        <v>8998</v>
+      </c>
+      <c r="B4461" t="s">
+        <v>8999</v>
+      </c>
+      <c r="C4461" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4462" t="s">
+        <v>9000</v>
+      </c>
+      <c r="B4462" t="s">
+        <v>9001</v>
+      </c>
+      <c r="C4462" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4463" t="s">
+        <v>9002</v>
+      </c>
+      <c r="B4463" t="s">
+        <v>9003</v>
+      </c>
+      <c r="C4463" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4464" t="s">
+        <v>9004</v>
+      </c>
+      <c r="B4464" t="s">
+        <v>9005</v>
+      </c>
+      <c r="C4464" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4465" t="s">
+        <v>9006</v>
+      </c>
+      <c r="B4465" t="s">
+        <v>9007</v>
+      </c>
+      <c r="C4465" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4466" t="s">
+        <v>9008</v>
+      </c>
+      <c r="B4466" t="s">
+        <v>9009</v>
+      </c>
+      <c r="C4466" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4467" t="s">
+        <v>9010</v>
+      </c>
+      <c r="B4467" t="s">
+        <v>9011</v>
+      </c>
+      <c r="C4467" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4468" t="s">
+        <v>9012</v>
+      </c>
+      <c r="B4468" t="s">
+        <v>9013</v>
+      </c>
+      <c r="C4468" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4469" t="s">
+        <v>9014</v>
+      </c>
+      <c r="B4469" t="s">
+        <v>9015</v>
+      </c>
+      <c r="C4469" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4470" t="s">
+        <v>9016</v>
+      </c>
+      <c r="B4470" t="s">
+        <v>9017</v>
+      </c>
+      <c r="C4470" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4471" t="s">
+        <v>9018</v>
+      </c>
+      <c r="B4471" t="s">
+        <v>9019</v>
+      </c>
+      <c r="C4471" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4472" t="s">
+        <v>9020</v>
+      </c>
+      <c r="B4472" t="s">
+        <v>9021</v>
+      </c>
+      <c r="C4472" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4473" t="s">
+        <v>9022</v>
+      </c>
+      <c r="B4473" t="s">
+        <v>9023</v>
+      </c>
+      <c r="C4473" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4474" t="s">
+        <v>9024</v>
+      </c>
+      <c r="B4474" t="s">
+        <v>9025</v>
+      </c>
+      <c r="C4474" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4475" t="s">
+        <v>9026</v>
+      </c>
+      <c r="B4475" t="s">
+        <v>9027</v>
+      </c>
+      <c r="C4475" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4476" t="s">
+        <v>9028</v>
+      </c>
+      <c r="B4476" t="s">
+        <v>9029</v>
+      </c>
+      <c r="C4476" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4477" t="s">
+        <v>9030</v>
+      </c>
+      <c r="B4477" t="s">
+        <v>9031</v>
+      </c>
+      <c r="C4477" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4478" t="s">
+        <v>9032</v>
+      </c>
+      <c r="B4478" t="s">
+        <v>9033</v>
+      </c>
+      <c r="C4478" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4479" t="s">
+        <v>9034</v>
+      </c>
+      <c r="B4479" t="s">
+        <v>9035</v>
+      </c>
+      <c r="C4479" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4480" t="s">
+        <v>9036</v>
+      </c>
+      <c r="B4480" t="s">
+        <v>9037</v>
+      </c>
+      <c r="C4480" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4481" t="s">
+        <v>9038</v>
+      </c>
+      <c r="B4481" t="s">
+        <v>9039</v>
+      </c>
+      <c r="C4481" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4482" t="s">
+        <v>9040</v>
+      </c>
+      <c r="B4482" t="s">
+        <v>9041</v>
+      </c>
+      <c r="C4482" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4483" t="s">
+        <v>9042</v>
+      </c>
+      <c r="B4483" t="s">
+        <v>9043</v>
+      </c>
+      <c r="C4483" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4484" t="s">
+        <v>9044</v>
+      </c>
+      <c r="B4484" t="s">
+        <v>9045</v>
+      </c>
+      <c r="C4484" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4485" t="s">
+        <v>9046</v>
+      </c>
+      <c r="B4485" t="s">
+        <v>9047</v>
+      </c>
+      <c r="C4485" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4486" t="s">
+        <v>9048</v>
+      </c>
+      <c r="B4486" t="s">
+        <v>9049</v>
+      </c>
+      <c r="C4486" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4487" t="s">
+        <v>9050</v>
+      </c>
+      <c r="B4487" t="s">
+        <v>9051</v>
+      </c>
+      <c r="C4487" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4488" t="s">
+        <v>9052</v>
+      </c>
+      <c r="B4488" t="s">
+        <v>9053</v>
+      </c>
+      <c r="C4488" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4489" t="s">
+        <v>9054</v>
+      </c>
+      <c r="B4489" t="s">
+        <v>9055</v>
+      </c>
+      <c r="C4489" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4490" t="s">
+        <v>9056</v>
+      </c>
+      <c r="B4490" t="s">
+        <v>9057</v>
+      </c>
+      <c r="C4490" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4491" t="s">
+        <v>9058</v>
+      </c>
+      <c r="B4491" t="s">
+        <v>9059</v>
+      </c>
+      <c r="C4491" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4492" t="s">
+        <v>9060</v>
+      </c>
+      <c r="B4492" t="s">
+        <v>9061</v>
+      </c>
+      <c r="C4492" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4493" t="s">
+        <v>9062</v>
+      </c>
+      <c r="B4493" t="s">
+        <v>9063</v>
+      </c>
+      <c r="C4493" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4494" t="s">
+        <v>9064</v>
+      </c>
+      <c r="B4494" t="s">
+        <v>9065</v>
+      </c>
+      <c r="C4494" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4495" t="s">
+        <v>9066</v>
+      </c>
+      <c r="B4495" t="s">
+        <v>9067</v>
+      </c>
+      <c r="C4495" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4496" t="s">
+        <v>9068</v>
+      </c>
+      <c r="B4496" t="s">
+        <v>9069</v>
+      </c>
+      <c r="C4496" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4497" t="s">
+        <v>9070</v>
+      </c>
+      <c r="B4497" t="s">
+        <v>9071</v>
+      </c>
+      <c r="C4497" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4498" t="s">
+        <v>9072</v>
+      </c>
+      <c r="B4498" t="s">
+        <v>9073</v>
+      </c>
+      <c r="C4498" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4499" t="s">
+        <v>9074</v>
+      </c>
+      <c r="B4499" t="s">
+        <v>9075</v>
+      </c>
+      <c r="C4499" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4500" t="s">
+        <v>9076</v>
+      </c>
+      <c r="B4500" t="s">
+        <v>9077</v>
+      </c>
+      <c r="C4500" t="s">
+        <v>8995</v>
+      </c>
+    </row>
+    <row r="4501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4501" t="s">
+        <v>9078</v>
+      </c>
+      <c r="B4501" t="s">
+        <v>9079</v>
+      </c>
+      <c r="C4501" t="s">
+        <v>8995</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11997" uniqueCount="9080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12054" uniqueCount="9119">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -27257,6 +27257,123 @@
   </si>
   <si>
     <t>Наволочка сатин 50х50 - "Лигурия"</t>
+  </si>
+  <si>
+    <t>4681001615460</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё бязь для детских кроваток - 142 - Сладкий Мёд зелёный</t>
+  </si>
+  <si>
+    <t>18-05-2026</t>
+  </si>
+  <si>
+    <t>4681001615453</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Фиорелла"</t>
+  </si>
+  <si>
+    <t>4681001615446</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Фиорелла"</t>
+  </si>
+  <si>
+    <t>4681001615439</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Жатка 2 спальное на резинке 160х200х20 - "Альфредо"</t>
+  </si>
+  <si>
+    <t>4681001615422</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х20 - Грей Стайл</t>
+  </si>
+  <si>
+    <t>4681001615415</t>
+  </si>
+  <si>
+    <t>Пододеяльник ранфорс 175х215 - Белый</t>
+  </si>
+  <si>
+    <t>4681001615408</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - "Кианит" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615392</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро резинка 160х200х30 - "Белый Этюд"</t>
+  </si>
+  <si>
+    <t>4681001615385</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро резинка 160х200х30 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001615378</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 150х220 - Пинклайт</t>
+  </si>
+  <si>
+    <t>4681001615361</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - Данделионс А+В наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615354</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 120х200х30 - Архитектор наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615347</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 - Спящий Мишка на голубом</t>
+  </si>
+  <si>
+    <t>4681001615330</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное Евро простыня - "Аполлон" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615323</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 200х200х40 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001615316</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 140х200х30 - "Этайн" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615309</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Солнечные лучи"</t>
+  </si>
+  <si>
+    <t>4681001615293</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 60х60 - Сарсуэла</t>
+  </si>
+  <si>
+    <t>4681001615286</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное Евро простыня - Сарсуэла наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -72630,6 +72747,215 @@
         <v>8995</v>
       </c>
     </row>
+    <row r="4502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4502" t="s">
+        <v>9080</v>
+      </c>
+      <c r="B4502" t="s">
+        <v>9081</v>
+      </c>
+      <c r="C4502" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4503" t="s">
+        <v>9083</v>
+      </c>
+      <c r="B4503" t="s">
+        <v>9084</v>
+      </c>
+      <c r="C4503" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4504" t="s">
+        <v>9085</v>
+      </c>
+      <c r="B4504" t="s">
+        <v>9086</v>
+      </c>
+      <c r="C4504" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4505" t="s">
+        <v>9087</v>
+      </c>
+      <c r="B4505" t="s">
+        <v>9088</v>
+      </c>
+      <c r="C4505" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4506" t="s">
+        <v>9089</v>
+      </c>
+      <c r="B4506" t="s">
+        <v>9090</v>
+      </c>
+      <c r="C4506" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4507" t="s">
+        <v>9091</v>
+      </c>
+      <c r="B4507" t="s">
+        <v>9092</v>
+      </c>
+      <c r="C4507" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4508" t="s">
+        <v>9093</v>
+      </c>
+      <c r="B4508" t="s">
+        <v>9094</v>
+      </c>
+      <c r="C4508" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4509" t="s">
+        <v>9095</v>
+      </c>
+      <c r="B4509" t="s">
+        <v>9096</v>
+      </c>
+      <c r="C4509" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4510" t="s">
+        <v>9097</v>
+      </c>
+      <c r="B4510" t="s">
+        <v>9098</v>
+      </c>
+      <c r="C4510" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4511" t="s">
+        <v>9099</v>
+      </c>
+      <c r="B4511" t="s">
+        <v>9100</v>
+      </c>
+      <c r="C4511" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4512" t="s">
+        <v>9101</v>
+      </c>
+      <c r="B4512" t="s">
+        <v>9102</v>
+      </c>
+      <c r="C4512" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4513" t="s">
+        <v>9103</v>
+      </c>
+      <c r="B4513" t="s">
+        <v>9104</v>
+      </c>
+      <c r="C4513" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4514" t="s">
+        <v>9105</v>
+      </c>
+      <c r="B4514" t="s">
+        <v>9106</v>
+      </c>
+      <c r="C4514" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4515" t="s">
+        <v>9107</v>
+      </c>
+      <c r="B4515" t="s">
+        <v>9108</v>
+      </c>
+      <c r="C4515" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4516" t="s">
+        <v>9109</v>
+      </c>
+      <c r="B4516" t="s">
+        <v>9110</v>
+      </c>
+      <c r="C4516" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4517" t="s">
+        <v>9111</v>
+      </c>
+      <c r="B4517" t="s">
+        <v>9112</v>
+      </c>
+      <c r="C4517" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4518" t="s">
+        <v>9113</v>
+      </c>
+      <c r="B4518" t="s">
+        <v>9114</v>
+      </c>
+      <c r="C4518" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4519" t="s">
+        <v>9115</v>
+      </c>
+      <c r="B4519" t="s">
+        <v>9116</v>
+      </c>
+      <c r="C4519" t="s">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="4520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4520" t="s">
+        <v>9117</v>
+      </c>
+      <c r="B4520" t="s">
+        <v>9118</v>
+      </c>
+      <c r="C4520" t="s">
+        <v>9082</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12054" uniqueCount="9119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12111" uniqueCount="9158">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -27374,6 +27374,123 @@
   </si>
   <si>
     <t>КПБ Постельное бельё сатин 2 спальное Евро простыня - Сарсуэла наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615651</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 140х200х30 - "Бланманже"</t>
+  </si>
+  <si>
+    <t>19-05-2026</t>
+  </si>
+  <si>
+    <t>4681001615644</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок King Size семейное резинка 200х200х30 - "Стальная тень" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615637</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Белый Этюд"</t>
+  </si>
+  <si>
+    <t>4681001615620</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Белый Этюд"</t>
+  </si>
+  <si>
+    <t>4681001615613</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Белый Этюд" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615606</t>
+  </si>
+  <si>
+    <t>Простыня Жатка 280х280 - "Звездный Сон"</t>
+  </si>
+  <si>
+    <t>4681001615590</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 80х200х20 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001615583</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х30 - "Астероид"</t>
+  </si>
+  <si>
+    <t>4681001615576</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 140х200х30 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001615569</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Серебро Облаков"</t>
+  </si>
+  <si>
+    <t>4681001615552</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 - Каори на зеленом</t>
+  </si>
+  <si>
+    <t>4681001615545</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 120х200х30 - 140 - Лаванда 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615538</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 200х200х30 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001615521</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 175х215 - Макадамия</t>
+  </si>
+  <si>
+    <t>4681001615514</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 90х200х10 - "Траектория"</t>
+  </si>
+  <si>
+    <t>4681001615507</t>
+  </si>
+  <si>
+    <t>Простыня поплин 180х220 - "Оллорины"</t>
+  </si>
+  <si>
+    <t>4681001615491</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное резинка 160х200х20 - "Айсу" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615484</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 70х70 - "Кианит"</t>
+  </si>
+  <si>
+    <t>4681001615477</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное - 80 - Витражи наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -72956,6 +73073,215 @@
         <v>9082</v>
       </c>
     </row>
+    <row r="4521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4521" t="s">
+        <v>9119</v>
+      </c>
+      <c r="B4521" t="s">
+        <v>9120</v>
+      </c>
+      <c r="C4521" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4522" t="s">
+        <v>9122</v>
+      </c>
+      <c r="B4522" t="s">
+        <v>9123</v>
+      </c>
+      <c r="C4522" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4523" t="s">
+        <v>9124</v>
+      </c>
+      <c r="B4523" t="s">
+        <v>9125</v>
+      </c>
+      <c r="C4523" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4524" t="s">
+        <v>9126</v>
+      </c>
+      <c r="B4524" t="s">
+        <v>9127</v>
+      </c>
+      <c r="C4524" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4525" t="s">
+        <v>9128</v>
+      </c>
+      <c r="B4525" t="s">
+        <v>9129</v>
+      </c>
+      <c r="C4525" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4526" t="s">
+        <v>9130</v>
+      </c>
+      <c r="B4526" t="s">
+        <v>9131</v>
+      </c>
+      <c r="C4526" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4527" t="s">
+        <v>9132</v>
+      </c>
+      <c r="B4527" t="s">
+        <v>9133</v>
+      </c>
+      <c r="C4527" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4528" t="s">
+        <v>9134</v>
+      </c>
+      <c r="B4528" t="s">
+        <v>9135</v>
+      </c>
+      <c r="C4528" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4529" t="s">
+        <v>9136</v>
+      </c>
+      <c r="B4529" t="s">
+        <v>9137</v>
+      </c>
+      <c r="C4529" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4530" t="s">
+        <v>9138</v>
+      </c>
+      <c r="B4530" t="s">
+        <v>9139</v>
+      </c>
+      <c r="C4530" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4531" t="s">
+        <v>9140</v>
+      </c>
+      <c r="B4531" t="s">
+        <v>9141</v>
+      </c>
+      <c r="C4531" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4532" t="s">
+        <v>9142</v>
+      </c>
+      <c r="B4532" t="s">
+        <v>9143</v>
+      </c>
+      <c r="C4532" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4533" t="s">
+        <v>9144</v>
+      </c>
+      <c r="B4533" t="s">
+        <v>9145</v>
+      </c>
+      <c r="C4533" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4534" t="s">
+        <v>9146</v>
+      </c>
+      <c r="B4534" t="s">
+        <v>9147</v>
+      </c>
+      <c r="C4534" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4535" t="s">
+        <v>9148</v>
+      </c>
+      <c r="B4535" t="s">
+        <v>9149</v>
+      </c>
+      <c r="C4535" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4536" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4536" t="s">
+        <v>9150</v>
+      </c>
+      <c r="B4536" t="s">
+        <v>9151</v>
+      </c>
+      <c r="C4536" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4537" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4537" t="s">
+        <v>9152</v>
+      </c>
+      <c r="B4537" t="s">
+        <v>9153</v>
+      </c>
+      <c r="C4537" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4538" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4538" t="s">
+        <v>9154</v>
+      </c>
+      <c r="B4538" t="s">
+        <v>9155</v>
+      </c>
+      <c r="C4538" t="s">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="4539" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4539" t="s">
+        <v>9156</v>
+      </c>
+      <c r="B4539" t="s">
+        <v>9157</v>
+      </c>
+      <c r="C4539" t="s">
+        <v>9121</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12111" uniqueCount="9158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12168" uniqueCount="9197">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -27491,6 +27491,123 @@
   </si>
   <si>
     <t>КПБ Постельное бельё полисатин 2 спальное - 80 - Витражи наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615842</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 40х60 - "Эвергрин"</t>
+  </si>
+  <si>
+    <t>20-05-2026</t>
+  </si>
+  <si>
+    <t>4681001615835</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 40х60 - "Милда"</t>
+  </si>
+  <si>
+    <t>4681001615828</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 260х260 - "Айвелин"</t>
+  </si>
+  <si>
+    <t>4681001615811</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - Черничный смузи наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615804</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Призрачная лагуна"</t>
+  </si>
+  <si>
+    <t>4681001615798</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х30 - Белый</t>
+  </si>
+  <si>
+    <t>4681001615781</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - Белый</t>
+  </si>
+  <si>
+    <t>4681001615774</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 140х200х30 - "Эрос" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615767</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро резинка 160х200х30 - "Ледяной Мрамор"</t>
+  </si>
+  <si>
+    <t>4681001615750</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 180х200х30 - 130 - "Изумрудный малахит" 1х1</t>
+  </si>
+  <si>
+    <t>4681001615743</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 180х200х30 - 135 - Грейс-Бэй 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615736</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х30 - "Макена"</t>
+  </si>
+  <si>
+    <t>4681001615729</t>
+  </si>
+  <si>
+    <t>Простыня Жатка на резинке 160х200х30 - "Файза"</t>
+  </si>
+  <si>
+    <t>4681001615712</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин семейное резинка 160х200х30 - "Воздушное касание"</t>
+  </si>
+  <si>
+    <t>4681001615705</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - Черный матовый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615699</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х40 - 120 - Ахад</t>
+  </si>
+  <si>
+    <t>4681001615682</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное - "Думнат" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615675</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро на резинке 160х200х30 - "Сливочный"</t>
+  </si>
+  <si>
+    <t>4681001615668</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х40 - "Туманная Аура"</t>
   </si>
 </sst>
 </file>
@@ -73282,6 +73399,215 @@
         <v>9121</v>
       </c>
     </row>
+    <row r="4540" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4540" t="s">
+        <v>9158</v>
+      </c>
+      <c r="B4540" t="s">
+        <v>9159</v>
+      </c>
+      <c r="C4540" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4541" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4541" t="s">
+        <v>9161</v>
+      </c>
+      <c r="B4541" t="s">
+        <v>9162</v>
+      </c>
+      <c r="C4541" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4542" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4542" t="s">
+        <v>9163</v>
+      </c>
+      <c r="B4542" t="s">
+        <v>9164</v>
+      </c>
+      <c r="C4542" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4543" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4543" t="s">
+        <v>9165</v>
+      </c>
+      <c r="B4543" t="s">
+        <v>9166</v>
+      </c>
+      <c r="C4543" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4544" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4544" t="s">
+        <v>9167</v>
+      </c>
+      <c r="B4544" t="s">
+        <v>9168</v>
+      </c>
+      <c r="C4544" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4545" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4545" t="s">
+        <v>9169</v>
+      </c>
+      <c r="B4545" t="s">
+        <v>9170</v>
+      </c>
+      <c r="C4545" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4546" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4546" t="s">
+        <v>9171</v>
+      </c>
+      <c r="B4546" t="s">
+        <v>9172</v>
+      </c>
+      <c r="C4546" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4547" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4547" t="s">
+        <v>9173</v>
+      </c>
+      <c r="B4547" t="s">
+        <v>9174</v>
+      </c>
+      <c r="C4547" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4548" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4548" t="s">
+        <v>9175</v>
+      </c>
+      <c r="B4548" t="s">
+        <v>9176</v>
+      </c>
+      <c r="C4548" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4549" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4549" t="s">
+        <v>9177</v>
+      </c>
+      <c r="B4549" t="s">
+        <v>9178</v>
+      </c>
+      <c r="C4549" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4550" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4550" t="s">
+        <v>9179</v>
+      </c>
+      <c r="B4550" t="s">
+        <v>9180</v>
+      </c>
+      <c r="C4550" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4551" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4551" t="s">
+        <v>9181</v>
+      </c>
+      <c r="B4551" t="s">
+        <v>9182</v>
+      </c>
+      <c r="C4551" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4552" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4552" t="s">
+        <v>9183</v>
+      </c>
+      <c r="B4552" t="s">
+        <v>9184</v>
+      </c>
+      <c r="C4552" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4553" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4553" t="s">
+        <v>9185</v>
+      </c>
+      <c r="B4553" t="s">
+        <v>9186</v>
+      </c>
+      <c r="C4553" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4554" t="s">
+        <v>9187</v>
+      </c>
+      <c r="B4554" t="s">
+        <v>9188</v>
+      </c>
+      <c r="C4554" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4555" t="s">
+        <v>9189</v>
+      </c>
+      <c r="B4555" t="s">
+        <v>9190</v>
+      </c>
+      <c r="C4555" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4556" t="s">
+        <v>9191</v>
+      </c>
+      <c r="B4556" t="s">
+        <v>9192</v>
+      </c>
+      <c r="C4556" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4557" t="s">
+        <v>9193</v>
+      </c>
+      <c r="B4557" t="s">
+        <v>9194</v>
+      </c>
+      <c r="C4557" t="s">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="4558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4558" t="s">
+        <v>9195</v>
+      </c>
+      <c r="B4558" t="s">
+        <v>9196</v>
+      </c>
+      <c r="C4558" t="s">
+        <v>9160</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12168" uniqueCount="9197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12189" uniqueCount="9212">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -27608,6 +27608,51 @@
   </si>
   <si>
     <t>Простыня полисатин резинка 140х200х40 - "Туманная Аура"</t>
+  </si>
+  <si>
+    <t>4681001615910</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 300х300 - "Сиренево-розовый"</t>
+  </si>
+  <si>
+    <t>21-05-2026</t>
+  </si>
+  <si>
+    <t>4681001615903</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель King Size резинка 200х200х30 - 129 Темно-зеленый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001615897</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001615880</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 40х60 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001615873</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая 90х140 - Мулетон Хлопок</t>
+  </si>
+  <si>
+    <t>4681001615866</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Призрачная лагуна"</t>
+  </si>
+  <si>
+    <t>4681001615859</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 40х60 - "Угольная Паутинка"</t>
   </si>
 </sst>
 </file>
@@ -73608,6 +73653,83 @@
         <v>9160</v>
       </c>
     </row>
+    <row r="4559" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4559" t="s">
+        <v>9197</v>
+      </c>
+      <c r="B4559" t="s">
+        <v>9198</v>
+      </c>
+      <c r="C4559" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4560" t="s">
+        <v>9200</v>
+      </c>
+      <c r="B4560" t="s">
+        <v>9201</v>
+      </c>
+      <c r="C4560" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4561" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4561" t="s">
+        <v>9202</v>
+      </c>
+      <c r="B4561" t="s">
+        <v>9203</v>
+      </c>
+      <c r="C4561" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4562" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4562" t="s">
+        <v>9204</v>
+      </c>
+      <c r="B4562" t="s">
+        <v>9205</v>
+      </c>
+      <c r="C4562" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4563" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4563" t="s">
+        <v>9206</v>
+      </c>
+      <c r="B4563" t="s">
+        <v>9207</v>
+      </c>
+      <c r="C4563" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4564" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4564" t="s">
+        <v>9208</v>
+      </c>
+      <c r="B4564" t="s">
+        <v>9209</v>
+      </c>
+      <c r="C4564" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4565" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4565" t="s">
+        <v>9210</v>
+      </c>
+      <c r="B4565" t="s">
+        <v>9211</v>
+      </c>
+      <c r="C4565" t="s">
+        <v>9199</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12189" uniqueCount="9212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12213" uniqueCount="9228">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -27653,6 +27653,54 @@
   </si>
   <si>
     <t>Наволочка жатка 40х60 - "Угольная Паутинка"</t>
+  </si>
+  <si>
+    <t>4681001615996</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - "Бриллиантовые кружева"</t>
+  </si>
+  <si>
+    <t>4681001615989</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс резинка 200х200х30 - Белый</t>
+  </si>
+  <si>
+    <t>4681001615972</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - "Лиловый тауп"</t>
+  </si>
+  <si>
+    <t>4681001615965</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 150х200 - "Вайрон"</t>
+  </si>
+  <si>
+    <t>4681001615958</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 240х260 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001615941</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 210х210х20 - "Млада"</t>
+  </si>
+  <si>
+    <t>4681001615934</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 125 - Шампань 3х3</t>
+  </si>
+  <si>
+    <t>4681001615927</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - 125 - Белый 3х3</t>
   </si>
 </sst>
 </file>
@@ -73730,6 +73778,94 @@
         <v>9199</v>
       </c>
     </row>
+    <row r="4566" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4566" t="s">
+        <v>9212</v>
+      </c>
+      <c r="B4566" t="s">
+        <v>9213</v>
+      </c>
+      <c r="C4566" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4567" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4567" t="s">
+        <v>9214</v>
+      </c>
+      <c r="B4567" t="s">
+        <v>9215</v>
+      </c>
+      <c r="C4567" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4568" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4568" t="s">
+        <v>9216</v>
+      </c>
+      <c r="B4568" t="s">
+        <v>9217</v>
+      </c>
+      <c r="C4568" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4569" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4569" t="s">
+        <v>9218</v>
+      </c>
+      <c r="B4569" t="s">
+        <v>9219</v>
+      </c>
+      <c r="C4569" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4570" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4570" t="s">
+        <v>9220</v>
+      </c>
+      <c r="B4570" t="s">
+        <v>9221</v>
+      </c>
+      <c r="C4570" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4571" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4571" t="s">
+        <v>9222</v>
+      </c>
+      <c r="B4571" t="s">
+        <v>9223</v>
+      </c>
+      <c r="C4571" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4572" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4572" t="s">
+        <v>9224</v>
+      </c>
+      <c r="B4572" t="s">
+        <v>9225</v>
+      </c>
+      <c r="C4572" t="s">
+        <v>9199</v>
+      </c>
+    </row>
+    <row r="4573" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4573" t="s">
+        <v>9226</v>
+      </c>
+      <c r="B4573" t="s">
+        <v>9227</v>
+      </c>
+      <c r="C4573" t="s">
+        <v>9199</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12213" uniqueCount="9228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12264" uniqueCount="9263">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -27701,6 +27701,111 @@
   </si>
   <si>
     <t>Простыня страйп-сатин 300х300 - 125 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001616160</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное резинка 160х200х20 - "Джуман"</t>
+  </si>
+  <si>
+    <t>22-05-2026</t>
+  </si>
+  <si>
+    <t>4681001616153</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 140 - Голубой 1х1</t>
+  </si>
+  <si>
+    <t>4681001616146</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001616139</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - Гранола</t>
+  </si>
+  <si>
+    <t>4681001616122</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Изумруд Эсмеральды наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616115</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 230х230х20 - "Сиренево-розовый"</t>
+  </si>
+  <si>
+    <t>4681001616108</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 230х230х30 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001616092</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х200х30 - "Вилайн" 1х1</t>
+  </si>
+  <si>
+    <t>4681001616085</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х30 - "Асунсьон"</t>
+  </si>
+  <si>
+    <t>4681001616078</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 90х200х10 - 120 - Хагги Вагги</t>
+  </si>
+  <si>
+    <t>4681001616061</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 120 - Хагги Вагги</t>
+  </si>
+  <si>
+    <t>4681001616054</t>
+  </si>
+  <si>
+    <t>Простыня бязь 180х220 - 142 - Сиреневые маки</t>
+  </si>
+  <si>
+    <t>4681001616047</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 140 - Кремовая пудра 1х1</t>
+  </si>
+  <si>
+    <t>4681001616030</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Песчаный Вальс"</t>
+  </si>
+  <si>
+    <t>4681001616023</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 70х70 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001616016</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х200 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001616009</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное Евро простыня - 140 - Белый Люкс 3х3</t>
   </si>
 </sst>
 </file>
@@ -73866,6 +73971,193 @@
         <v>9199</v>
       </c>
     </row>
+    <row r="4574" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4574" t="s">
+        <v>9228</v>
+      </c>
+      <c r="B4574" t="s">
+        <v>9229</v>
+      </c>
+      <c r="C4574" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4575" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4575" t="s">
+        <v>9231</v>
+      </c>
+      <c r="B4575" t="s">
+        <v>9232</v>
+      </c>
+      <c r="C4575" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4576" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4576" t="s">
+        <v>9233</v>
+      </c>
+      <c r="B4576" t="s">
+        <v>9234</v>
+      </c>
+      <c r="C4576" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4577" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4577" t="s">
+        <v>9235</v>
+      </c>
+      <c r="B4577" t="s">
+        <v>9236</v>
+      </c>
+      <c r="C4577" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4578" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4578" t="s">
+        <v>9237</v>
+      </c>
+      <c r="B4578" t="s">
+        <v>9238</v>
+      </c>
+      <c r="C4578" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4579" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4579" t="s">
+        <v>9239</v>
+      </c>
+      <c r="B4579" t="s">
+        <v>9240</v>
+      </c>
+      <c r="C4579" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4580" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4580" t="s">
+        <v>9241</v>
+      </c>
+      <c r="B4580" t="s">
+        <v>9242</v>
+      </c>
+      <c r="C4580" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4581" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4581" t="s">
+        <v>9243</v>
+      </c>
+      <c r="B4581" t="s">
+        <v>9244</v>
+      </c>
+      <c r="C4581" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4582" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4582" t="s">
+        <v>9245</v>
+      </c>
+      <c r="B4582" t="s">
+        <v>9246</v>
+      </c>
+      <c r="C4582" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4583" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4583" t="s">
+        <v>9247</v>
+      </c>
+      <c r="B4583" t="s">
+        <v>9248</v>
+      </c>
+      <c r="C4583" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4584" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4584" t="s">
+        <v>9249</v>
+      </c>
+      <c r="B4584" t="s">
+        <v>9250</v>
+      </c>
+      <c r="C4584" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4585" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4585" t="s">
+        <v>9251</v>
+      </c>
+      <c r="B4585" t="s">
+        <v>9252</v>
+      </c>
+      <c r="C4585" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4586" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4586" t="s">
+        <v>9253</v>
+      </c>
+      <c r="B4586" t="s">
+        <v>9254</v>
+      </c>
+      <c r="C4586" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4587" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4587" t="s">
+        <v>9255</v>
+      </c>
+      <c r="B4587" t="s">
+        <v>9256</v>
+      </c>
+      <c r="C4587" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4588" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4588" t="s">
+        <v>9257</v>
+      </c>
+      <c r="B4588" t="s">
+        <v>9258</v>
+      </c>
+      <c r="C4588" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4589" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4589" t="s">
+        <v>9259</v>
+      </c>
+      <c r="B4589" t="s">
+        <v>9260</v>
+      </c>
+      <c r="C4589" t="s">
+        <v>9230</v>
+      </c>
+    </row>
+    <row r="4590" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4590" t="s">
+        <v>9261</v>
+      </c>
+      <c r="B4590" t="s">
+        <v>9262</v>
+      </c>
+      <c r="C4590" t="s">
+        <v>9230</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12264" uniqueCount="9263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12456" uniqueCount="9392">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -27806,6 +27806,393 @@
   </si>
   <si>
     <t>КПБ Постельное бельё страйп-сатин 2 спальное Евро простыня - 140 - Белый Люкс 3х3</t>
+  </si>
+  <si>
+    <t>4681001616801</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 200х200х30 - "Милда"</t>
+  </si>
+  <si>
+    <t>24-05-2026</t>
+  </si>
+  <si>
+    <t>4681001616795</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - 135 - Лаймкват 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616788</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х40 - "Пролив" 1х1</t>
+  </si>
+  <si>
+    <t>4681001616771</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное резинка 140х200х30 - 142 - Таунхаус</t>
+  </si>
+  <si>
+    <t>4681001616764</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х30 - 140 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001616757</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё бязь для детских кроваток - 142 - Приятели Леса на зеленом</t>
+  </si>
+  <si>
+    <t>4681001616740</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Карибская волна"</t>
+  </si>
+  <si>
+    <t>4681001616733</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х20 - Ясное небо</t>
+  </si>
+  <si>
+    <t>4681001616726</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин семейное резинка 160х200х30 - "Смоки"</t>
+  </si>
+  <si>
+    <t>4681001616719</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 140 - Черный янтарь 3х3</t>
+  </si>
+  <si>
+    <t>4681001616702</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 240х260 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001616696</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 240х260 - "Небосвод"</t>
+  </si>
+  <si>
+    <t>4681001616689</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 220х240 - "Серебряный Папоротник"</t>
+  </si>
+  <si>
+    <t>4681001616672</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин King Size резинка 200х200х30 - Премиум ТС 320 "Гиран"</t>
+  </si>
+  <si>
+    <t>4681001616665</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин King Size семейное резинка 200х200х30 - Премиум ТС 320 "Гиран"</t>
+  </si>
+  <si>
+    <t>4681001616658</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - Нежно-розовый</t>
+  </si>
+  <si>
+    <t>4681001616641</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х30 - Нежно-розовый</t>
+  </si>
+  <si>
+    <t>4681001616634</t>
+  </si>
+  <si>
+    <t>Простыня жатка 240х260 - "Лесная Мелодия"</t>
+  </si>
+  <si>
+    <t>4681001616627</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Жатка 1,5 спальное на резинке 120х200х30 - "Файза" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001616610</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 240х260 - 323 Серый</t>
+  </si>
+  <si>
+    <t>4681001616603</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 160х200х30 - "Лавандис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616597</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - Малахит</t>
+  </si>
+  <si>
+    <t>4681001616580</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 40х40 - Чёрная гавань</t>
+  </si>
+  <si>
+    <t>4681001616573</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Бонди</t>
+  </si>
+  <si>
+    <t>4681001616566</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 2 спальное резинка 140х200х30 - "Вельбард" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001616559</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Лямур"</t>
+  </si>
+  <si>
+    <t>4681001616542</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 145х215 - "Лямур"</t>
+  </si>
+  <si>
+    <t>4681001616535</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - Морбидецца</t>
+  </si>
+  <si>
+    <t>4681001616528</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Ардуино"</t>
+  </si>
+  <si>
+    <t>4681001616511</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Ардуино"</t>
+  </si>
+  <si>
+    <t>4681001616504</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 175х215 - "Мортис"</t>
+  </si>
+  <si>
+    <t>4681001616498</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 130 - Мятный фреш 1х1</t>
+  </si>
+  <si>
+    <t>4681001616481</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 120х200х30 - Белое облако наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616474</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Мортис"</t>
+  </si>
+  <si>
+    <t>4681001616467</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Думнат" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616450</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 140х200х30 - 120 - Трюфель наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616443</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Туманная Ветвь" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616436</t>
+  </si>
+  <si>
+    <t>Простыня микросатин резинка 200х220х30 - "Бежевый шлейф"</t>
+  </si>
+  <si>
+    <t>4681001616429</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Триша" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616412</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 260х260 - 140 - Вулкан 1х1</t>
+  </si>
+  <si>
+    <t>4681001616405</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х40 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001616399</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - "Элегантность"</t>
+  </si>
+  <si>
+    <t>4681001616382</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 200х220 - "Бежевый шлейф"</t>
+  </si>
+  <si>
+    <t>4681001616375</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 240х260 - "Стальная тень" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001616368</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное на резинке 140х200х30 - "Корги-пати" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001616351</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - "Холодная элегия" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616344</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - Серая умбра</t>
+  </si>
+  <si>
+    <t>4681001616337</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Чериньола</t>
+  </si>
+  <si>
+    <t>4681001616320</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Золотой блеск"</t>
+  </si>
+  <si>
+    <t>4681001616313</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 220х240 - 110 - Каори на зеленом</t>
+  </si>
+  <si>
+    <t>4681001616306</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х220 - "Альфонсо"</t>
+  </si>
+  <si>
+    <t>4681001616290</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 140х200х30 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001616283</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Тонкий Лист" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616276</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001616269</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 200х220 - 110 - Каори на желтом</t>
+  </si>
+  <si>
+    <t>4681001616252</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 140х200х30 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001616245</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х40 - "Ноксия"</t>
+  </si>
+  <si>
+    <t>4681001616238</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 300х300 - 110 - Белоснежный луч</t>
+  </si>
+  <si>
+    <t>4681001616221</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - "Сливочный"</t>
+  </si>
+  <si>
+    <t>4681001616214</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х20 - Прелат А+В</t>
+  </si>
+  <si>
+    <t>4681001616207</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 175х215 - "Серебряный Папоротник"</t>
+  </si>
+  <si>
+    <t>4681001616191</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Серис"</t>
+  </si>
+  <si>
+    <t>4681001616184</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное - Сарсуэла наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616177</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - 4235 Темно-синий</t>
   </si>
 </sst>
 </file>
@@ -74158,6 +74545,710 @@
         <v>9230</v>
       </c>
     </row>
+    <row r="4591" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4591" t="s">
+        <v>9263</v>
+      </c>
+      <c r="B4591" t="s">
+        <v>9264</v>
+      </c>
+      <c r="C4591" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4592" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4592" t="s">
+        <v>9266</v>
+      </c>
+      <c r="B4592" t="s">
+        <v>9267</v>
+      </c>
+      <c r="C4592" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4593" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4593" t="s">
+        <v>9268</v>
+      </c>
+      <c r="B4593" t="s">
+        <v>9269</v>
+      </c>
+      <c r="C4593" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4594" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4594" t="s">
+        <v>9270</v>
+      </c>
+      <c r="B4594" t="s">
+        <v>9271</v>
+      </c>
+      <c r="C4594" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4595" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4595" t="s">
+        <v>9272</v>
+      </c>
+      <c r="B4595" t="s">
+        <v>9273</v>
+      </c>
+      <c r="C4595" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4596" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4596" t="s">
+        <v>9274</v>
+      </c>
+      <c r="B4596" t="s">
+        <v>9275</v>
+      </c>
+      <c r="C4596" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4597" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4597" t="s">
+        <v>9276</v>
+      </c>
+      <c r="B4597" t="s">
+        <v>9277</v>
+      </c>
+      <c r="C4597" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4598" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4598" t="s">
+        <v>9278</v>
+      </c>
+      <c r="B4598" t="s">
+        <v>9279</v>
+      </c>
+      <c r="C4598" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4599" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4599" t="s">
+        <v>9280</v>
+      </c>
+      <c r="B4599" t="s">
+        <v>9281</v>
+      </c>
+      <c r="C4599" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4600" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4600" t="s">
+        <v>9282</v>
+      </c>
+      <c r="B4600" t="s">
+        <v>9283</v>
+      </c>
+      <c r="C4600" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4601" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4601" t="s">
+        <v>9284</v>
+      </c>
+      <c r="B4601" t="s">
+        <v>9285</v>
+      </c>
+      <c r="C4601" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4602" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4602" t="s">
+        <v>9286</v>
+      </c>
+      <c r="B4602" t="s">
+        <v>9287</v>
+      </c>
+      <c r="C4602" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4603" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4603" t="s">
+        <v>9288</v>
+      </c>
+      <c r="B4603" t="s">
+        <v>9289</v>
+      </c>
+      <c r="C4603" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4604" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4604" t="s">
+        <v>9290</v>
+      </c>
+      <c r="B4604" t="s">
+        <v>9291</v>
+      </c>
+      <c r="C4604" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4605" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4605" t="s">
+        <v>9292</v>
+      </c>
+      <c r="B4605" t="s">
+        <v>9293</v>
+      </c>
+      <c r="C4605" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4606" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4606" t="s">
+        <v>9294</v>
+      </c>
+      <c r="B4606" t="s">
+        <v>9295</v>
+      </c>
+      <c r="C4606" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4607" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4607" t="s">
+        <v>9296</v>
+      </c>
+      <c r="B4607" t="s">
+        <v>9297</v>
+      </c>
+      <c r="C4607" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4608" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4608" t="s">
+        <v>9298</v>
+      </c>
+      <c r="B4608" t="s">
+        <v>9299</v>
+      </c>
+      <c r="C4608" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4609" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4609" t="s">
+        <v>9300</v>
+      </c>
+      <c r="B4609" t="s">
+        <v>9301</v>
+      </c>
+      <c r="C4609" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4610" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4610" t="s">
+        <v>9302</v>
+      </c>
+      <c r="B4610" t="s">
+        <v>9303</v>
+      </c>
+      <c r="C4610" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4611" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4611" t="s">
+        <v>9304</v>
+      </c>
+      <c r="B4611" t="s">
+        <v>9305</v>
+      </c>
+      <c r="C4611" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4612" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4612" t="s">
+        <v>9306</v>
+      </c>
+      <c r="B4612" t="s">
+        <v>9307</v>
+      </c>
+      <c r="C4612" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4613" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4613" t="s">
+        <v>9308</v>
+      </c>
+      <c r="B4613" t="s">
+        <v>9309</v>
+      </c>
+      <c r="C4613" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4614" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4614" t="s">
+        <v>9310</v>
+      </c>
+      <c r="B4614" t="s">
+        <v>9311</v>
+      </c>
+      <c r="C4614" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4615" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4615" t="s">
+        <v>9312</v>
+      </c>
+      <c r="B4615" t="s">
+        <v>9313</v>
+      </c>
+      <c r="C4615" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4616" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4616" t="s">
+        <v>9314</v>
+      </c>
+      <c r="B4616" t="s">
+        <v>9315</v>
+      </c>
+      <c r="C4616" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4617" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4617" t="s">
+        <v>9316</v>
+      </c>
+      <c r="B4617" t="s">
+        <v>9317</v>
+      </c>
+      <c r="C4617" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4618" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4618" t="s">
+        <v>9318</v>
+      </c>
+      <c r="B4618" t="s">
+        <v>9319</v>
+      </c>
+      <c r="C4618" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4619" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4619" t="s">
+        <v>9320</v>
+      </c>
+      <c r="B4619" t="s">
+        <v>9321</v>
+      </c>
+      <c r="C4619" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4620" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4620" t="s">
+        <v>9322</v>
+      </c>
+      <c r="B4620" t="s">
+        <v>9323</v>
+      </c>
+      <c r="C4620" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4621" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4621" t="s">
+        <v>9324</v>
+      </c>
+      <c r="B4621" t="s">
+        <v>9325</v>
+      </c>
+      <c r="C4621" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4622" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4622" t="s">
+        <v>9326</v>
+      </c>
+      <c r="B4622" t="s">
+        <v>9327</v>
+      </c>
+      <c r="C4622" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4623" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4623" t="s">
+        <v>9328</v>
+      </c>
+      <c r="B4623" t="s">
+        <v>9329</v>
+      </c>
+      <c r="C4623" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4624" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4624" t="s">
+        <v>9330</v>
+      </c>
+      <c r="B4624" t="s">
+        <v>9331</v>
+      </c>
+      <c r="C4624" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4625" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4625" t="s">
+        <v>9332</v>
+      </c>
+      <c r="B4625" t="s">
+        <v>9333</v>
+      </c>
+      <c r="C4625" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4626" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4626" t="s">
+        <v>9334</v>
+      </c>
+      <c r="B4626" t="s">
+        <v>9335</v>
+      </c>
+      <c r="C4626" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4627" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4627" t="s">
+        <v>9336</v>
+      </c>
+      <c r="B4627" t="s">
+        <v>9337</v>
+      </c>
+      <c r="C4627" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4628" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4628" t="s">
+        <v>9338</v>
+      </c>
+      <c r="B4628" t="s">
+        <v>9339</v>
+      </c>
+      <c r="C4628" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4629" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4629" t="s">
+        <v>9340</v>
+      </c>
+      <c r="B4629" t="s">
+        <v>9341</v>
+      </c>
+      <c r="C4629" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4630" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4630" t="s">
+        <v>9342</v>
+      </c>
+      <c r="B4630" t="s">
+        <v>9343</v>
+      </c>
+      <c r="C4630" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4631" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4631" t="s">
+        <v>9344</v>
+      </c>
+      <c r="B4631" t="s">
+        <v>9345</v>
+      </c>
+      <c r="C4631" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4632" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4632" t="s">
+        <v>9346</v>
+      </c>
+      <c r="B4632" t="s">
+        <v>9347</v>
+      </c>
+      <c r="C4632" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4633" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4633" t="s">
+        <v>9348</v>
+      </c>
+      <c r="B4633" t="s">
+        <v>9349</v>
+      </c>
+      <c r="C4633" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4634" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4634" t="s">
+        <v>9350</v>
+      </c>
+      <c r="B4634" t="s">
+        <v>9351</v>
+      </c>
+      <c r="C4634" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4635" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4635" t="s">
+        <v>9352</v>
+      </c>
+      <c r="B4635" t="s">
+        <v>9353</v>
+      </c>
+      <c r="C4635" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4636" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4636" t="s">
+        <v>9354</v>
+      </c>
+      <c r="B4636" t="s">
+        <v>9355</v>
+      </c>
+      <c r="C4636" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4637" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4637" t="s">
+        <v>9356</v>
+      </c>
+      <c r="B4637" t="s">
+        <v>9357</v>
+      </c>
+      <c r="C4637" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4638" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4638" t="s">
+        <v>9358</v>
+      </c>
+      <c r="B4638" t="s">
+        <v>9359</v>
+      </c>
+      <c r="C4638" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4639" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4639" t="s">
+        <v>9360</v>
+      </c>
+      <c r="B4639" t="s">
+        <v>9361</v>
+      </c>
+      <c r="C4639" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4640" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4640" t="s">
+        <v>9362</v>
+      </c>
+      <c r="B4640" t="s">
+        <v>9363</v>
+      </c>
+      <c r="C4640" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4641" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4641" t="s">
+        <v>9364</v>
+      </c>
+      <c r="B4641" t="s">
+        <v>9365</v>
+      </c>
+      <c r="C4641" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4642" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4642" t="s">
+        <v>9366</v>
+      </c>
+      <c r="B4642" t="s">
+        <v>9367</v>
+      </c>
+      <c r="C4642" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4643" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4643" t="s">
+        <v>9368</v>
+      </c>
+      <c r="B4643" t="s">
+        <v>9369</v>
+      </c>
+      <c r="C4643" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4644" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4644" t="s">
+        <v>9370</v>
+      </c>
+      <c r="B4644" t="s">
+        <v>9371</v>
+      </c>
+      <c r="C4644" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4645" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4645" t="s">
+        <v>9372</v>
+      </c>
+      <c r="B4645" t="s">
+        <v>9373</v>
+      </c>
+      <c r="C4645" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4646" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4646" t="s">
+        <v>9374</v>
+      </c>
+      <c r="B4646" t="s">
+        <v>9375</v>
+      </c>
+      <c r="C4646" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4647" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4647" t="s">
+        <v>9376</v>
+      </c>
+      <c r="B4647" t="s">
+        <v>9377</v>
+      </c>
+      <c r="C4647" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4648" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4648" t="s">
+        <v>9378</v>
+      </c>
+      <c r="B4648" t="s">
+        <v>9379</v>
+      </c>
+      <c r="C4648" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4649" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4649" t="s">
+        <v>9380</v>
+      </c>
+      <c r="B4649" t="s">
+        <v>9381</v>
+      </c>
+      <c r="C4649" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4650" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4650" t="s">
+        <v>9382</v>
+      </c>
+      <c r="B4650" t="s">
+        <v>9383</v>
+      </c>
+      <c r="C4650" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4651" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4651" t="s">
+        <v>9384</v>
+      </c>
+      <c r="B4651" t="s">
+        <v>9385</v>
+      </c>
+      <c r="C4651" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4652" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4652" t="s">
+        <v>9386</v>
+      </c>
+      <c r="B4652" t="s">
+        <v>9387</v>
+      </c>
+      <c r="C4652" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4653" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4653" t="s">
+        <v>9388</v>
+      </c>
+      <c r="B4653" t="s">
+        <v>9389</v>
+      </c>
+      <c r="C4653" t="s">
+        <v>9265</v>
+      </c>
+    </row>
+    <row r="4654" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4654" t="s">
+        <v>9390</v>
+      </c>
+      <c r="B4654" t="s">
+        <v>9391</v>
+      </c>
+      <c r="C4654" t="s">
+        <v>9265</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12456" uniqueCount="9392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12531" uniqueCount="9443">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -28193,6 +28193,159 @@
   </si>
   <si>
     <t>Пододеяльник тенсель 220х240 - 4235 Темно-синий</t>
+  </si>
+  <si>
+    <t>4681001617037</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс Евро резинка 160х200х30 - "Ванильный раф"</t>
+  </si>
+  <si>
+    <t>25-05-2026</t>
+  </si>
+  <si>
+    <t>4681001617020</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 40х60 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001617013</t>
+  </si>
+  <si>
+    <t>Наволочка Жатка 40х60 - "Звездный Сон"</t>
+  </si>
+  <si>
+    <t>4681001617006</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - Блестящий миндаль наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616993</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 130 - Пудровый 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616986</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Миндаль 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616979</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 40х60 - "Розовый опал"</t>
+  </si>
+  <si>
+    <t>4681001616962</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - 110 - Сад Единорога</t>
+  </si>
+  <si>
+    <t>4681001616955</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - Ночной колпак</t>
+  </si>
+  <si>
+    <t>4681001616948</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 300х300 - 129 Темно-зеленый</t>
+  </si>
+  <si>
+    <t>4681001616931</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 300х300 - Голубой хрусталь</t>
+  </si>
+  <si>
+    <t>4681001616924</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 300х300 - 74 Оливковый</t>
+  </si>
+  <si>
+    <t>4681001616917</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001616900</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 140х200х30 - "Криола"</t>
+  </si>
+  <si>
+    <t>4681001616894</t>
+  </si>
+  <si>
+    <t>Наволочка микрофибра 40х60 - "Эстрелья"</t>
+  </si>
+  <si>
+    <t>4681001616887</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Бархатный Букет"</t>
+  </si>
+  <si>
+    <t>4681001616870</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Севим"</t>
+  </si>
+  <si>
+    <t>4681001616863</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Туманная Аура"</t>
+  </si>
+  <si>
+    <t>4681001616856</t>
+  </si>
+  <si>
+    <t>Простыня круглая сатин резинка 250х250х40 - "Агапия"</t>
+  </si>
+  <si>
+    <t>4681001616849</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель King Size резинка 200х200х30 - Белый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001616832</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - М - 120 - Чёрный мрамор Универсал</t>
+  </si>
+  <si>
+    <t>4681001616825</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Золотой блеск" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001616818</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное - "Джуман" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617051</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жаккард Евро-макси - "Золото короны"</t>
+  </si>
+  <si>
+    <t>4681001617044</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жаккард Евро-макси - "Боден" наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -75249,6 +75402,281 @@
         <v>9265</v>
       </c>
     </row>
+    <row r="4655" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4655" t="s">
+        <v>9392</v>
+      </c>
+      <c r="B4655" t="s">
+        <v>9393</v>
+      </c>
+      <c r="C4655" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4656" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4656" t="s">
+        <v>9395</v>
+      </c>
+      <c r="B4656" t="s">
+        <v>9396</v>
+      </c>
+      <c r="C4656" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4657" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4657" t="s">
+        <v>9397</v>
+      </c>
+      <c r="B4657" t="s">
+        <v>9398</v>
+      </c>
+      <c r="C4657" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4658" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4658" t="s">
+        <v>9399</v>
+      </c>
+      <c r="B4658" t="s">
+        <v>9400</v>
+      </c>
+      <c r="C4658" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4659" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4659" t="s">
+        <v>9401</v>
+      </c>
+      <c r="B4659" t="s">
+        <v>9402</v>
+      </c>
+      <c r="C4659" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4660" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4660" t="s">
+        <v>9403</v>
+      </c>
+      <c r="B4660" t="s">
+        <v>9404</v>
+      </c>
+      <c r="C4660" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4661" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4661" t="s">
+        <v>9405</v>
+      </c>
+      <c r="B4661" t="s">
+        <v>9406</v>
+      </c>
+      <c r="C4661" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4662" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4662" t="s">
+        <v>9407</v>
+      </c>
+      <c r="B4662" t="s">
+        <v>9408</v>
+      </c>
+      <c r="C4662" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4663" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4663" t="s">
+        <v>9409</v>
+      </c>
+      <c r="B4663" t="s">
+        <v>9410</v>
+      </c>
+      <c r="C4663" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4664" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4664" t="s">
+        <v>9411</v>
+      </c>
+      <c r="B4664" t="s">
+        <v>9412</v>
+      </c>
+      <c r="C4664" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4665" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4665" t="s">
+        <v>9413</v>
+      </c>
+      <c r="B4665" t="s">
+        <v>9414</v>
+      </c>
+      <c r="C4665" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4666" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4666" t="s">
+        <v>9415</v>
+      </c>
+      <c r="B4666" t="s">
+        <v>9416</v>
+      </c>
+      <c r="C4666" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4667" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4667" t="s">
+        <v>9417</v>
+      </c>
+      <c r="B4667" t="s">
+        <v>9418</v>
+      </c>
+      <c r="C4667" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4668" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4668" t="s">
+        <v>9419</v>
+      </c>
+      <c r="B4668" t="s">
+        <v>9420</v>
+      </c>
+      <c r="C4668" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4669" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4669" t="s">
+        <v>9421</v>
+      </c>
+      <c r="B4669" t="s">
+        <v>9422</v>
+      </c>
+      <c r="C4669" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4670" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4670" t="s">
+        <v>9423</v>
+      </c>
+      <c r="B4670" t="s">
+        <v>9424</v>
+      </c>
+      <c r="C4670" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4671" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4671" t="s">
+        <v>9425</v>
+      </c>
+      <c r="B4671" t="s">
+        <v>9426</v>
+      </c>
+      <c r="C4671" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4672" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4672" t="s">
+        <v>9427</v>
+      </c>
+      <c r="B4672" t="s">
+        <v>9428</v>
+      </c>
+      <c r="C4672" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4673" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4673" t="s">
+        <v>9429</v>
+      </c>
+      <c r="B4673" t="s">
+        <v>9430</v>
+      </c>
+      <c r="C4673" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4674" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4674" t="s">
+        <v>9431</v>
+      </c>
+      <c r="B4674" t="s">
+        <v>9432</v>
+      </c>
+      <c r="C4674" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4675" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4675" t="s">
+        <v>9433</v>
+      </c>
+      <c r="B4675" t="s">
+        <v>9434</v>
+      </c>
+      <c r="C4675" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4676" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4676" t="s">
+        <v>9435</v>
+      </c>
+      <c r="B4676" t="s">
+        <v>9436</v>
+      </c>
+      <c r="C4676" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4677" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4677" t="s">
+        <v>9437</v>
+      </c>
+      <c r="B4677" t="s">
+        <v>9438</v>
+      </c>
+      <c r="C4677" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4678" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4678" t="s">
+        <v>9439</v>
+      </c>
+      <c r="B4678" t="s">
+        <v>9440</v>
+      </c>
+      <c r="C4678" t="s">
+        <v>9394</v>
+      </c>
+    </row>
+    <row r="4679" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4679" t="s">
+        <v>9441</v>
+      </c>
+      <c r="B4679" t="s">
+        <v>9442</v>
+      </c>
+      <c r="C4679" t="s">
+        <v>9394</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12531" uniqueCount="9443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12582" uniqueCount="9478">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -28346,6 +28346,111 @@
   </si>
   <si>
     <t>КПБ Постельное бельё жаккард Евро-макси - "Боден" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617228</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 70х70 - "Просперо"</t>
+  </si>
+  <si>
+    <t>26-05-2026</t>
+  </si>
+  <si>
+    <t>4681001617211</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4681001617204</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Асунсьон"</t>
+  </si>
+  <si>
+    <t>4681001617198</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное - "Паллада"</t>
+  </si>
+  <si>
+    <t>4681001617181</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное резинка 180х200х30 - "Природный Абстракт" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617174</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра семейное резинка 180х200х30 - "Альбелла" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617167</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 200х220 - "Димитра"</t>
+  </si>
+  <si>
+    <t>4681001617150</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - "Фиорис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617143</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 140х200х20 - "Бронзит"</t>
+  </si>
+  <si>
+    <t>4681001617136</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 160х200х30 - 125 - Терракота</t>
+  </si>
+  <si>
+    <t>4681001617129</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 90х200х30 - "Алоха"</t>
+  </si>
+  <si>
+    <t>4681001617112</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х40 - "Малика"</t>
+  </si>
+  <si>
+    <t>4681001617105</t>
+  </si>
+  <si>
+    <t>Пододеяльник из бязи 200х200 - 120 - Чёрный мрамор</t>
+  </si>
+  <si>
+    <t>4681001617099</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - "Далиян"</t>
+  </si>
+  <si>
+    <t>4681001617082</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - "Сентори"</t>
+  </si>
+  <si>
+    <t>4681001617075</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - Магма А+В</t>
+  </si>
+  <si>
+    <t>4681001617068</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин семейное - Сливочно-кремовый наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -75677,6 +75782,193 @@
         <v>9394</v>
       </c>
     </row>
+    <row r="4680" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4680" t="s">
+        <v>9443</v>
+      </c>
+      <c r="B4680" t="s">
+        <v>9444</v>
+      </c>
+      <c r="C4680" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4681" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4681" t="s">
+        <v>9446</v>
+      </c>
+      <c r="B4681" t="s">
+        <v>9447</v>
+      </c>
+      <c r="C4681" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4682" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4682" t="s">
+        <v>9448</v>
+      </c>
+      <c r="B4682" t="s">
+        <v>9449</v>
+      </c>
+      <c r="C4682" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4683" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4683" t="s">
+        <v>9450</v>
+      </c>
+      <c r="B4683" t="s">
+        <v>9451</v>
+      </c>
+      <c r="C4683" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4684" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4684" t="s">
+        <v>9452</v>
+      </c>
+      <c r="B4684" t="s">
+        <v>9453</v>
+      </c>
+      <c r="C4684" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4685" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4685" t="s">
+        <v>9454</v>
+      </c>
+      <c r="B4685" t="s">
+        <v>9455</v>
+      </c>
+      <c r="C4685" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4686" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4686" t="s">
+        <v>9456</v>
+      </c>
+      <c r="B4686" t="s">
+        <v>9457</v>
+      </c>
+      <c r="C4686" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4687" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4687" t="s">
+        <v>9458</v>
+      </c>
+      <c r="B4687" t="s">
+        <v>9459</v>
+      </c>
+      <c r="C4687" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4688" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4688" t="s">
+        <v>9460</v>
+      </c>
+      <c r="B4688" t="s">
+        <v>9461</v>
+      </c>
+      <c r="C4688" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4689" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4689" t="s">
+        <v>9462</v>
+      </c>
+      <c r="B4689" t="s">
+        <v>9463</v>
+      </c>
+      <c r="C4689" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4690" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4690" t="s">
+        <v>9464</v>
+      </c>
+      <c r="B4690" t="s">
+        <v>9465</v>
+      </c>
+      <c r="C4690" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4691" t="s">
+        <v>9466</v>
+      </c>
+      <c r="B4691" t="s">
+        <v>9467</v>
+      </c>
+      <c r="C4691" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4692" t="s">
+        <v>9468</v>
+      </c>
+      <c r="B4692" t="s">
+        <v>9469</v>
+      </c>
+      <c r="C4692" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4693" t="s">
+        <v>9470</v>
+      </c>
+      <c r="B4693" t="s">
+        <v>9471</v>
+      </c>
+      <c r="C4693" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4694" t="s">
+        <v>9472</v>
+      </c>
+      <c r="B4694" t="s">
+        <v>9473</v>
+      </c>
+      <c r="C4694" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4695" t="s">
+        <v>9474</v>
+      </c>
+      <c r="B4695" t="s">
+        <v>9475</v>
+      </c>
+      <c r="C4695" t="s">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="4696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4696" t="s">
+        <v>9476</v>
+      </c>
+      <c r="B4696" t="s">
+        <v>9477</v>
+      </c>
+      <c r="C4696" t="s">
+        <v>9445</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12582" uniqueCount="9478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12636" uniqueCount="9515">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -28451,6 +28451,117 @@
   </si>
   <si>
     <t>КПБ Постельное бельё поплин семейное - Сливочно-кремовый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617402</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 2 спальное - "Фиорелла"</t>
+  </si>
+  <si>
+    <t>27-05-2026</t>
+  </si>
+  <si>
+    <t>4681001617396</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 180х200х30 - "Твист" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617389</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 80х200х20 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001617372</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - "Филлис" 1х1</t>
+  </si>
+  <si>
+    <t>4681001617365</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 140 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001617358</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - "Лазурный Мегаполис"</t>
+  </si>
+  <si>
+    <t>4681001617341</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - 142 - Черный</t>
+  </si>
+  <si>
+    <t>4681001617334</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль Евро - 110 - Белоснежный луч</t>
+  </si>
+  <si>
+    <t>4681001617327</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро резинка 160х200х30 - Премиум ТС 320 Белый</t>
+  </si>
+  <si>
+    <t>4681001617310</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 160х200х30 - 140 - Белый Лучик наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617303</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х40 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001617297</t>
+  </si>
+  <si>
+    <t>Простыня полисатин на резинке 140х200х40 - "Малика"</t>
+  </si>
+  <si>
+    <t>4681001617280</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4681001617273</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное резинка 140х200х30 - "Бонетто" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617266</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х40 - 4216 Серебро</t>
+  </si>
+  <si>
+    <t>4681001617259</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс 260х260 - "Фантасмагория"</t>
+  </si>
+  <si>
+    <t>4681001617242</t>
+  </si>
+  <si>
+    <t>Наволочка ранфорс 40х60 - "Фантасмагория"</t>
+  </si>
+  <si>
+    <t>4681001617235</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 135 - Марриотт Белый 3х3</t>
   </si>
 </sst>
 </file>
@@ -75969,6 +76080,204 @@
         <v>9445</v>
       </c>
     </row>
+    <row r="4697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4697" t="s">
+        <v>9478</v>
+      </c>
+      <c r="B4697" t="s">
+        <v>9479</v>
+      </c>
+      <c r="C4697" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4698" t="s">
+        <v>9481</v>
+      </c>
+      <c r="B4698" t="s">
+        <v>9482</v>
+      </c>
+      <c r="C4698" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4699" t="s">
+        <v>9483</v>
+      </c>
+      <c r="B4699" t="s">
+        <v>9484</v>
+      </c>
+      <c r="C4699" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4700" t="s">
+        <v>9485</v>
+      </c>
+      <c r="B4700" t="s">
+        <v>9486</v>
+      </c>
+      <c r="C4700" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4701" t="s">
+        <v>9487</v>
+      </c>
+      <c r="B4701" t="s">
+        <v>9488</v>
+      </c>
+      <c r="C4701" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4702" t="s">
+        <v>9489</v>
+      </c>
+      <c r="B4702" t="s">
+        <v>9490</v>
+      </c>
+      <c r="C4702" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4703" t="s">
+        <v>9491</v>
+      </c>
+      <c r="B4703" t="s">
+        <v>9492</v>
+      </c>
+      <c r="C4703" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4704" t="s">
+        <v>9493</v>
+      </c>
+      <c r="B4704" t="s">
+        <v>9494</v>
+      </c>
+      <c r="C4704" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4705" t="s">
+        <v>9495</v>
+      </c>
+      <c r="B4705" t="s">
+        <v>9496</v>
+      </c>
+      <c r="C4705" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4706" t="s">
+        <v>9497</v>
+      </c>
+      <c r="B4706" t="s">
+        <v>9498</v>
+      </c>
+      <c r="C4706" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4707" t="s">
+        <v>9499</v>
+      </c>
+      <c r="B4707" t="s">
+        <v>9500</v>
+      </c>
+      <c r="C4707" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4708" t="s">
+        <v>9501</v>
+      </c>
+      <c r="B4708" t="s">
+        <v>9502</v>
+      </c>
+      <c r="C4708" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4709" t="s">
+        <v>9503</v>
+      </c>
+      <c r="B4709" t="s">
+        <v>9504</v>
+      </c>
+      <c r="C4709" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4710" t="s">
+        <v>9505</v>
+      </c>
+      <c r="B4710" t="s">
+        <v>9506</v>
+      </c>
+      <c r="C4710" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4711" t="s">
+        <v>9507</v>
+      </c>
+      <c r="B4711" t="s">
+        <v>9508</v>
+      </c>
+      <c r="C4711" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4712" t="s">
+        <v>9509</v>
+      </c>
+      <c r="B4712" t="s">
+        <v>9510</v>
+      </c>
+      <c r="C4712" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4713" t="s">
+        <v>9511</v>
+      </c>
+      <c r="B4713" t="s">
+        <v>9512</v>
+      </c>
+      <c r="C4713" t="s">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="4714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4714" t="s">
+        <v>9513</v>
+      </c>
+      <c r="B4714" t="s">
+        <v>9514</v>
+      </c>
+      <c r="C4714" t="s">
+        <v>9480</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12636" uniqueCount="9515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12702" uniqueCount="9560">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -28562,6 +28562,141 @@
   </si>
   <si>
     <t>Наволочка страйп-сатин 70х70 - 135 - Марриотт Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001617624</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Айвелин"</t>
+  </si>
+  <si>
+    <t>28-05-2026</t>
+  </si>
+  <si>
+    <t>4681001617617</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Латунь"</t>
+  </si>
+  <si>
+    <t>4681001617600</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль 1,5 спальное - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001617594</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - "Бланманже" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617587</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 1,5 спальное резинка 120х200х30 - "Бездна" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617570</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - "Нефритовый" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617563</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Мишка в лесу"</t>
+  </si>
+  <si>
+    <t>4681001617556</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Мишка в лесу"</t>
+  </si>
+  <si>
+    <t>4681001617549</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - "Мирелле"</t>
+  </si>
+  <si>
+    <t>4681001617532</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - Петроль наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617525</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро-макси резинка 180х200х30 - "Песочный Рельеф" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617518</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - "Карибская волна" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617501</t>
+  </si>
+  <si>
+    <t>Простыня жатка 220х240 - "Альфредо"</t>
+  </si>
+  <si>
+    <t>4681001617495</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 220х240 - "Гаспар"</t>
+  </si>
+  <si>
+    <t>4681001617488</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Гаспар"</t>
+  </si>
+  <si>
+    <t>4681001617471</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001617464</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х30 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001617457</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 40х40 - Вечерний песок</t>
+  </si>
+  <si>
+    <t>4681001617440</t>
+  </si>
+  <si>
+    <t>Простыня жатка 220х240 - "Письменный Бриз"</t>
+  </si>
+  <si>
+    <t>4681001617433</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001617426</t>
+  </si>
+  <si>
+    <t>КПБ Постельное белье тенсель Евро на резинке 160х200х30 - М - 60S 4393 Темно-серый с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001617419</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - "Пролив" 1х1 наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -76278,6 +76413,248 @@
         <v>9480</v>
       </c>
     </row>
+    <row r="4715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4715" t="s">
+        <v>9515</v>
+      </c>
+      <c r="B4715" t="s">
+        <v>9516</v>
+      </c>
+      <c r="C4715" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4716" t="s">
+        <v>9518</v>
+      </c>
+      <c r="B4716" t="s">
+        <v>9519</v>
+      </c>
+      <c r="C4716" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4717" t="s">
+        <v>9520</v>
+      </c>
+      <c r="B4717" t="s">
+        <v>9521</v>
+      </c>
+      <c r="C4717" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4718" t="s">
+        <v>9522</v>
+      </c>
+      <c r="B4718" t="s">
+        <v>9523</v>
+      </c>
+      <c r="C4718" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4719" t="s">
+        <v>9524</v>
+      </c>
+      <c r="B4719" t="s">
+        <v>9525</v>
+      </c>
+      <c r="C4719" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4720" t="s">
+        <v>9526</v>
+      </c>
+      <c r="B4720" t="s">
+        <v>9527</v>
+      </c>
+      <c r="C4720" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4721" t="s">
+        <v>9528</v>
+      </c>
+      <c r="B4721" t="s">
+        <v>9529</v>
+      </c>
+      <c r="C4721" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4722" t="s">
+        <v>9530</v>
+      </c>
+      <c r="B4722" t="s">
+        <v>9531</v>
+      </c>
+      <c r="C4722" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4723" t="s">
+        <v>9532</v>
+      </c>
+      <c r="B4723" t="s">
+        <v>9533</v>
+      </c>
+      <c r="C4723" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4724" t="s">
+        <v>9534</v>
+      </c>
+      <c r="B4724" t="s">
+        <v>9535</v>
+      </c>
+      <c r="C4724" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4725" t="s">
+        <v>9536</v>
+      </c>
+      <c r="B4725" t="s">
+        <v>9537</v>
+      </c>
+      <c r="C4725" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4726" t="s">
+        <v>9538</v>
+      </c>
+      <c r="B4726" t="s">
+        <v>9539</v>
+      </c>
+      <c r="C4726" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4727" t="s">
+        <v>9540</v>
+      </c>
+      <c r="B4727" t="s">
+        <v>9541</v>
+      </c>
+      <c r="C4727" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4728" t="s">
+        <v>9542</v>
+      </c>
+      <c r="B4728" t="s">
+        <v>9543</v>
+      </c>
+      <c r="C4728" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4729" t="s">
+        <v>9544</v>
+      </c>
+      <c r="B4729" t="s">
+        <v>9545</v>
+      </c>
+      <c r="C4729" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4730" t="s">
+        <v>9546</v>
+      </c>
+      <c r="B4730" t="s">
+        <v>9547</v>
+      </c>
+      <c r="C4730" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4731" t="s">
+        <v>9548</v>
+      </c>
+      <c r="B4731" t="s">
+        <v>9549</v>
+      </c>
+      <c r="C4731" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4732" t="s">
+        <v>9550</v>
+      </c>
+      <c r="B4732" t="s">
+        <v>9551</v>
+      </c>
+      <c r="C4732" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4733" t="s">
+        <v>9552</v>
+      </c>
+      <c r="B4733" t="s">
+        <v>9553</v>
+      </c>
+      <c r="C4733" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4734" t="s">
+        <v>9554</v>
+      </c>
+      <c r="B4734" t="s">
+        <v>9555</v>
+      </c>
+      <c r="C4734" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4735" t="s">
+        <v>9556</v>
+      </c>
+      <c r="B4735" t="s">
+        <v>9557</v>
+      </c>
+      <c r="C4735" t="s">
+        <v>9517</v>
+      </c>
+    </row>
+    <row r="4736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4736" t="s">
+        <v>9558</v>
+      </c>
+      <c r="B4736" t="s">
+        <v>9559</v>
+      </c>
+      <c r="C4736" t="s">
+        <v>9517</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12702" uniqueCount="9560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12978" uniqueCount="9745">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -28697,6 +28697,561 @@
   </si>
   <si>
     <t>КПБ Постельное бельё страйп-сатин Евро-макси - "Пролив" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618546</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 200х200х20 - "Ледяной Мрамор"</t>
+  </si>
+  <si>
+    <t>31-05-2026</t>
+  </si>
+  <si>
+    <t>4681001618539</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное резинка 160х200х30 - 130 - "Дивуар" 1х1</t>
+  </si>
+  <si>
+    <t>4681001618522</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс 200х220 - "Трюфельный шарм"</t>
+  </si>
+  <si>
+    <t>4681001618515</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - 140 - Росток 1х1</t>
+  </si>
+  <si>
+    <t>4681001618508</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - Светлая орхидея</t>
+  </si>
+  <si>
+    <t>4681001618492</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 145х215 - 140 - Сирень 1х1</t>
+  </si>
+  <si>
+    <t>4681001618485</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 90х200х30 - Сливочно-кремовый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618478</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 50х50 - Треббиано</t>
+  </si>
+  <si>
+    <t>4681001618461</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 220х240 - "Астероид"</t>
+  </si>
+  <si>
+    <t>4681001618454</t>
+  </si>
+  <si>
+    <t>Простыня бязь 220х240 - "Митсу"</t>
+  </si>
+  <si>
+    <t>4681001618447</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - 140 - Тенерифе 1х1</t>
+  </si>
+  <si>
+    <t>4681001618430</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное резинка 180х200х30 - Бертолеция</t>
+  </si>
+  <si>
+    <t>4681001618423</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное - "Бирюзовый Рельеф" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618416</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 220х240 - Премиум ТС 320 "Юсан"</t>
+  </si>
+  <si>
+    <t>4681001618409</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 140х200х30 - Премиум ТС 320 "Лулу"</t>
+  </si>
+  <si>
+    <t>4681001618393</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 140х200х30 - "Аделаида"</t>
+  </si>
+  <si>
+    <t>4681001618386</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 230х230х30 - 140 - Миндаль 1х1</t>
+  </si>
+  <si>
+    <t>4681001618379</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001618362</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное Евро простыня - 140 - Винно-красный 1х1</t>
+  </si>
+  <si>
+    <t>4681001618355</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 145х215 - Зеленый чай</t>
+  </si>
+  <si>
+    <t>4681001618348</t>
+  </si>
+  <si>
+    <t>КПБ Постельное белье микросатин 2 спальное на резинке 140х200х30 - "Легкий роман"</t>
+  </si>
+  <si>
+    <t>4681001618331</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Карибская волна"</t>
+  </si>
+  <si>
+    <t>4681001618324</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 240х260 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4681001618317</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное резинка 140х200х30 - Черный матовый</t>
+  </si>
+  <si>
+    <t>4681001618300</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 140 - Тенерифе 1х1</t>
+  </si>
+  <si>
+    <t>4681001618294</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 150х220 - 135 - Фирюз 1х1</t>
+  </si>
+  <si>
+    <t>4681001618287</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 90х200х10 - 120 - Оттенки Звезд</t>
+  </si>
+  <si>
+    <t>4681001618270</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - "Морозный туман" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618263</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - Альбертус</t>
+  </si>
+  <si>
+    <t>4681001618256</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин-жаккард 2 спальное резинка 160х200х30 - "Рендалис"</t>
+  </si>
+  <si>
+    <t>4681001618249</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 280х280 - "Асуль"</t>
+  </si>
+  <si>
+    <t>4681001618232</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 280х280 - "Голубой топаз"</t>
+  </si>
+  <si>
+    <t>4681001618225</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 120х200х30 - Графит (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618218</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё Жатка 1,5 спальное на резинке 140х200х30 - "Звездный Сон"</t>
+  </si>
+  <si>
+    <t>4681001618201</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Кашемировая роза</t>
+  </si>
+  <si>
+    <t>4681001618195</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - 125 - Фисташка 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618188</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 175х215 - "Милда"</t>
+  </si>
+  <si>
+    <t>4681001618171</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4681001618164</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - "Веселые Корги"</t>
+  </si>
+  <si>
+    <t>4681001618157</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - 115 - Космические игры А+В</t>
+  </si>
+  <si>
+    <t>4681001618140</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - Гранола</t>
+  </si>
+  <si>
+    <t>4681001618133</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 175х215 - "Огнерон"</t>
+  </si>
+  <si>
+    <t>4681001618126</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 40х60 - "Огнерон"</t>
+  </si>
+  <si>
+    <t>4681001618119</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х200х30 - "Огнерон"</t>
+  </si>
+  <si>
+    <t>4681001618102</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное - Фазенда Лиара наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618096</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - "Твист"</t>
+  </si>
+  <si>
+    <t>4681001618089</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 220х240 - "Севим"</t>
+  </si>
+  <si>
+    <t>4681001618072</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х30 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4681001618065</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х30 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4681001618058</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное резинка 160х200х30 - 140 - Черный янтарь 3х3 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618041</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Изумруд Эсмеральды</t>
+  </si>
+  <si>
+    <t>4681001618034</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001618027</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 140х200х30 - Нежно-розовый</t>
+  </si>
+  <si>
+    <t>4681001618010</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 160х200х20 - 142 - Рецепт любви</t>
+  </si>
+  <si>
+    <t>4681001618003</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 240х260 - 130 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001617990</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Альфонсо"</t>
+  </si>
+  <si>
+    <t>4681001617983</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 150х200 - "Розовый Сад"</t>
+  </si>
+  <si>
+    <t>4681001617976</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - 142 - Спящий Мишка на голубом</t>
+  </si>
+  <si>
+    <t>4681001617969</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё бязь 1,5 спальное - 120 - Спящий Мишка на голубом наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617952</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 80х200х20 - 142 - Серый</t>
+  </si>
+  <si>
+    <t>4681001617945</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х240х30 - 130 - "Летний дождь" 1х1</t>
+  </si>
+  <si>
+    <t>4681001617938</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Арника"</t>
+  </si>
+  <si>
+    <t>4681001617921</t>
+  </si>
+  <si>
+    <t>Простыня сатин 300х300 - "Бартош"</t>
+  </si>
+  <si>
+    <t>4681001617914</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 220х240 - "Бартош"</t>
+  </si>
+  <si>
+    <t>4681001617907</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х40 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4681001617891</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 200х200х30 - "Бирюзовый Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001617884</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 180х200х30 - 125 - "Морской туман" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617877</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное резинка 180х200х30 - 140 - Голубой 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001617860</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х40 - 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4681001617853</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Зелёный Страйп"</t>
+  </si>
+  <si>
+    <t>4681001617846</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х10 - 142 - Серый</t>
+  </si>
+  <si>
+    <t>4681001617839</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - 140 - Винно-красный 1х1</t>
+  </si>
+  <si>
+    <t>4681001617822</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х40 - "Бриолен" 1х1</t>
+  </si>
+  <si>
+    <t>4681001617815</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Розариум А+В</t>
+  </si>
+  <si>
+    <t>4681001617808</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 150х200 - Розариум А+В</t>
+  </si>
+  <si>
+    <t>4681001617792</t>
+  </si>
+  <si>
+    <t>Простыня жаккард резинка 160х200х40 - Пинкроуз</t>
+  </si>
+  <si>
+    <t>4681001617785</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 50х70 - Пинкроуз</t>
+  </si>
+  <si>
+    <t>4681001617778</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 150х200 - Пинкроуз</t>
+  </si>
+  <si>
+    <t>4681001617761</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - Индостан</t>
+  </si>
+  <si>
+    <t>4681001617754</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - 142 - Бирюза</t>
+  </si>
+  <si>
+    <t>4681001617747</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х220 - "Песочный Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001617730</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Фиорелла"</t>
+  </si>
+  <si>
+    <t>4681001617723</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - "Холодная элегия"</t>
+  </si>
+  <si>
+    <t>4681001617716</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное на резинке 160х200х30 - "Золотой блеск" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001617709</t>
+  </si>
+  <si>
+    <t>Простыня жатка 180х220 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001617693</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4681001617686</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 120 - Бежевая Латка</t>
+  </si>
+  <si>
+    <t>4681001617679</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра 300х300 - "Криола"</t>
+  </si>
+  <si>
+    <t>4681001617662</t>
+  </si>
+  <si>
+    <t>Простыня сатин 300х300 - 140 - Белый Лучик</t>
+  </si>
+  <si>
+    <t>4681001617655</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 112х147 - 142 - Спящий Мишка на голубом</t>
+  </si>
+  <si>
+    <t>4681001617648</t>
+  </si>
+  <si>
+    <t>Простыня поплин резинка 140х200х30 - Гуава</t>
+  </si>
+  <si>
+    <t>4681001617631</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное Евро простыня - "Бонетто" наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -76655,6 +77210,1018 @@
         <v>9517</v>
       </c>
     </row>
+    <row r="4737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4737" t="s">
+        <v>9560</v>
+      </c>
+      <c r="B4737" t="s">
+        <v>9561</v>
+      </c>
+      <c r="C4737" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4738" t="s">
+        <v>9563</v>
+      </c>
+      <c r="B4738" t="s">
+        <v>9564</v>
+      </c>
+      <c r="C4738" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4739" t="s">
+        <v>9565</v>
+      </c>
+      <c r="B4739" t="s">
+        <v>9566</v>
+      </c>
+      <c r="C4739" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4740" t="s">
+        <v>9567</v>
+      </c>
+      <c r="B4740" t="s">
+        <v>9568</v>
+      </c>
+      <c r="C4740" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4741" t="s">
+        <v>9569</v>
+      </c>
+      <c r="B4741" t="s">
+        <v>9570</v>
+      </c>
+      <c r="C4741" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4742" t="s">
+        <v>9571</v>
+      </c>
+      <c r="B4742" t="s">
+        <v>9572</v>
+      </c>
+      <c r="C4742" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4743" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4743" t="s">
+        <v>9573</v>
+      </c>
+      <c r="B4743" t="s">
+        <v>9574</v>
+      </c>
+      <c r="C4743" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4744" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4744" t="s">
+        <v>9575</v>
+      </c>
+      <c r="B4744" t="s">
+        <v>9576</v>
+      </c>
+      <c r="C4744" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4745" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4745" t="s">
+        <v>9577</v>
+      </c>
+      <c r="B4745" t="s">
+        <v>9578</v>
+      </c>
+      <c r="C4745" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4746" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4746" t="s">
+        <v>9579</v>
+      </c>
+      <c r="B4746" t="s">
+        <v>9580</v>
+      </c>
+      <c r="C4746" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4747" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4747" t="s">
+        <v>9581</v>
+      </c>
+      <c r="B4747" t="s">
+        <v>9582</v>
+      </c>
+      <c r="C4747" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4748" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4748" t="s">
+        <v>9583</v>
+      </c>
+      <c r="B4748" t="s">
+        <v>9584</v>
+      </c>
+      <c r="C4748" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4749" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4749" t="s">
+        <v>9585</v>
+      </c>
+      <c r="B4749" t="s">
+        <v>9586</v>
+      </c>
+      <c r="C4749" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4750" t="s">
+        <v>9587</v>
+      </c>
+      <c r="B4750" t="s">
+        <v>9588</v>
+      </c>
+      <c r="C4750" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4751" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4751" t="s">
+        <v>9589</v>
+      </c>
+      <c r="B4751" t="s">
+        <v>9590</v>
+      </c>
+      <c r="C4751" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4752" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4752" t="s">
+        <v>9591</v>
+      </c>
+      <c r="B4752" t="s">
+        <v>9592</v>
+      </c>
+      <c r="C4752" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4753" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4753" t="s">
+        <v>9593</v>
+      </c>
+      <c r="B4753" t="s">
+        <v>9594</v>
+      </c>
+      <c r="C4753" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4754" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4754" t="s">
+        <v>9595</v>
+      </c>
+      <c r="B4754" t="s">
+        <v>9596</v>
+      </c>
+      <c r="C4754" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4755" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4755" t="s">
+        <v>9597</v>
+      </c>
+      <c r="B4755" t="s">
+        <v>9598</v>
+      </c>
+      <c r="C4755" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4756" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4756" t="s">
+        <v>9599</v>
+      </c>
+      <c r="B4756" t="s">
+        <v>9600</v>
+      </c>
+      <c r="C4756" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4757" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4757" t="s">
+        <v>9601</v>
+      </c>
+      <c r="B4757" t="s">
+        <v>9602</v>
+      </c>
+      <c r="C4757" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4758" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4758" t="s">
+        <v>9603</v>
+      </c>
+      <c r="B4758" t="s">
+        <v>9604</v>
+      </c>
+      <c r="C4758" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4759" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4759" t="s">
+        <v>9605</v>
+      </c>
+      <c r="B4759" t="s">
+        <v>9606</v>
+      </c>
+      <c r="C4759" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4760" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4760" t="s">
+        <v>9607</v>
+      </c>
+      <c r="B4760" t="s">
+        <v>9608</v>
+      </c>
+      <c r="C4760" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4761" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4761" t="s">
+        <v>9609</v>
+      </c>
+      <c r="B4761" t="s">
+        <v>9610</v>
+      </c>
+      <c r="C4761" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4762" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4762" t="s">
+        <v>9611</v>
+      </c>
+      <c r="B4762" t="s">
+        <v>9612</v>
+      </c>
+      <c r="C4762" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4763" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4763" t="s">
+        <v>9613</v>
+      </c>
+      <c r="B4763" t="s">
+        <v>9614</v>
+      </c>
+      <c r="C4763" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4764" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4764" t="s">
+        <v>9615</v>
+      </c>
+      <c r="B4764" t="s">
+        <v>9616</v>
+      </c>
+      <c r="C4764" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4765" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4765" t="s">
+        <v>9617</v>
+      </c>
+      <c r="B4765" t="s">
+        <v>9618</v>
+      </c>
+      <c r="C4765" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4766" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4766" t="s">
+        <v>9619</v>
+      </c>
+      <c r="B4766" t="s">
+        <v>9620</v>
+      </c>
+      <c r="C4766" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4767" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4767" t="s">
+        <v>9621</v>
+      </c>
+      <c r="B4767" t="s">
+        <v>9622</v>
+      </c>
+      <c r="C4767" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4768" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4768" t="s">
+        <v>9623</v>
+      </c>
+      <c r="B4768" t="s">
+        <v>9624</v>
+      </c>
+      <c r="C4768" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4769" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4769" t="s">
+        <v>9625</v>
+      </c>
+      <c r="B4769" t="s">
+        <v>9626</v>
+      </c>
+      <c r="C4769" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4770" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4770" t="s">
+        <v>9627</v>
+      </c>
+      <c r="B4770" t="s">
+        <v>9628</v>
+      </c>
+      <c r="C4770" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4771" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4771" t="s">
+        <v>9629</v>
+      </c>
+      <c r="B4771" t="s">
+        <v>9630</v>
+      </c>
+      <c r="C4771" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4772" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4772" t="s">
+        <v>9631</v>
+      </c>
+      <c r="B4772" t="s">
+        <v>9632</v>
+      </c>
+      <c r="C4772" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4773" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4773" t="s">
+        <v>9633</v>
+      </c>
+      <c r="B4773" t="s">
+        <v>9634</v>
+      </c>
+      <c r="C4773" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4774" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4774" t="s">
+        <v>9635</v>
+      </c>
+      <c r="B4774" t="s">
+        <v>9636</v>
+      </c>
+      <c r="C4774" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4775" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4775" t="s">
+        <v>9637</v>
+      </c>
+      <c r="B4775" t="s">
+        <v>9638</v>
+      </c>
+      <c r="C4775" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4776" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4776" t="s">
+        <v>9639</v>
+      </c>
+      <c r="B4776" t="s">
+        <v>9640</v>
+      </c>
+      <c r="C4776" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4777" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4777" t="s">
+        <v>9641</v>
+      </c>
+      <c r="B4777" t="s">
+        <v>9642</v>
+      </c>
+      <c r="C4777" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4778" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4778" t="s">
+        <v>9643</v>
+      </c>
+      <c r="B4778" t="s">
+        <v>9644</v>
+      </c>
+      <c r="C4778" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4779" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4779" t="s">
+        <v>9645</v>
+      </c>
+      <c r="B4779" t="s">
+        <v>9646</v>
+      </c>
+      <c r="C4779" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4780" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4780" t="s">
+        <v>9647</v>
+      </c>
+      <c r="B4780" t="s">
+        <v>9648</v>
+      </c>
+      <c r="C4780" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4781" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4781" t="s">
+        <v>9649</v>
+      </c>
+      <c r="B4781" t="s">
+        <v>9650</v>
+      </c>
+      <c r="C4781" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4782" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4782" t="s">
+        <v>9651</v>
+      </c>
+      <c r="B4782" t="s">
+        <v>9652</v>
+      </c>
+      <c r="C4782" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4783" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4783" t="s">
+        <v>9653</v>
+      </c>
+      <c r="B4783" t="s">
+        <v>9654</v>
+      </c>
+      <c r="C4783" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4784" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4784" t="s">
+        <v>9655</v>
+      </c>
+      <c r="B4784" t="s">
+        <v>9656</v>
+      </c>
+      <c r="C4784" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4785" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4785" t="s">
+        <v>9657</v>
+      </c>
+      <c r="B4785" t="s">
+        <v>9658</v>
+      </c>
+      <c r="C4785" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4786" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4786" t="s">
+        <v>9659</v>
+      </c>
+      <c r="B4786" t="s">
+        <v>9660</v>
+      </c>
+      <c r="C4786" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4787" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4787" t="s">
+        <v>9661</v>
+      </c>
+      <c r="B4787" t="s">
+        <v>9662</v>
+      </c>
+      <c r="C4787" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4788" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4788" t="s">
+        <v>9663</v>
+      </c>
+      <c r="B4788" t="s">
+        <v>9664</v>
+      </c>
+      <c r="C4788" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4789" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4789" t="s">
+        <v>9665</v>
+      </c>
+      <c r="B4789" t="s">
+        <v>9666</v>
+      </c>
+      <c r="C4789" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4790" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4790" t="s">
+        <v>9667</v>
+      </c>
+      <c r="B4790" t="s">
+        <v>9668</v>
+      </c>
+      <c r="C4790" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4791" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4791" t="s">
+        <v>9669</v>
+      </c>
+      <c r="B4791" t="s">
+        <v>9670</v>
+      </c>
+      <c r="C4791" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4792" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4792" t="s">
+        <v>9671</v>
+      </c>
+      <c r="B4792" t="s">
+        <v>9672</v>
+      </c>
+      <c r="C4792" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4793" t="s">
+        <v>9673</v>
+      </c>
+      <c r="B4793" t="s">
+        <v>9674</v>
+      </c>
+      <c r="C4793" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4794" t="s">
+        <v>9675</v>
+      </c>
+      <c r="B4794" t="s">
+        <v>9676</v>
+      </c>
+      <c r="C4794" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4795" t="s">
+        <v>9677</v>
+      </c>
+      <c r="B4795" t="s">
+        <v>9678</v>
+      </c>
+      <c r="C4795" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4796" t="s">
+        <v>9679</v>
+      </c>
+      <c r="B4796" t="s">
+        <v>9680</v>
+      </c>
+      <c r="C4796" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4797" t="s">
+        <v>9681</v>
+      </c>
+      <c r="B4797" t="s">
+        <v>9682</v>
+      </c>
+      <c r="C4797" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4798" t="s">
+        <v>9683</v>
+      </c>
+      <c r="B4798" t="s">
+        <v>9684</v>
+      </c>
+      <c r="C4798" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4799" t="s">
+        <v>9685</v>
+      </c>
+      <c r="B4799" t="s">
+        <v>9686</v>
+      </c>
+      <c r="C4799" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4800" t="s">
+        <v>9687</v>
+      </c>
+      <c r="B4800" t="s">
+        <v>9688</v>
+      </c>
+      <c r="C4800" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4801" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4801" t="s">
+        <v>9689</v>
+      </c>
+      <c r="B4801" t="s">
+        <v>9690</v>
+      </c>
+      <c r="C4801" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4802" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4802" t="s">
+        <v>9691</v>
+      </c>
+      <c r="B4802" t="s">
+        <v>9692</v>
+      </c>
+      <c r="C4802" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4803" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4803" t="s">
+        <v>9693</v>
+      </c>
+      <c r="B4803" t="s">
+        <v>9694</v>
+      </c>
+      <c r="C4803" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4804" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4804" t="s">
+        <v>9695</v>
+      </c>
+      <c r="B4804" t="s">
+        <v>9696</v>
+      </c>
+      <c r="C4804" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4805" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4805" t="s">
+        <v>9697</v>
+      </c>
+      <c r="B4805" t="s">
+        <v>9698</v>
+      </c>
+      <c r="C4805" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4806" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4806" t="s">
+        <v>9699</v>
+      </c>
+      <c r="B4806" t="s">
+        <v>9700</v>
+      </c>
+      <c r="C4806" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4807" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4807" t="s">
+        <v>9701</v>
+      </c>
+      <c r="B4807" t="s">
+        <v>9702</v>
+      </c>
+      <c r="C4807" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4808" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4808" t="s">
+        <v>9703</v>
+      </c>
+      <c r="B4808" t="s">
+        <v>9704</v>
+      </c>
+      <c r="C4808" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4809" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4809" t="s">
+        <v>9705</v>
+      </c>
+      <c r="B4809" t="s">
+        <v>9706</v>
+      </c>
+      <c r="C4809" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4810" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4810" t="s">
+        <v>9707</v>
+      </c>
+      <c r="B4810" t="s">
+        <v>9708</v>
+      </c>
+      <c r="C4810" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4811" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4811" t="s">
+        <v>9709</v>
+      </c>
+      <c r="B4811" t="s">
+        <v>9710</v>
+      </c>
+      <c r="C4811" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4812" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4812" t="s">
+        <v>9711</v>
+      </c>
+      <c r="B4812" t="s">
+        <v>9712</v>
+      </c>
+      <c r="C4812" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4813" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4813" t="s">
+        <v>9713</v>
+      </c>
+      <c r="B4813" t="s">
+        <v>9714</v>
+      </c>
+      <c r="C4813" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4814" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4814" t="s">
+        <v>9715</v>
+      </c>
+      <c r="B4814" t="s">
+        <v>9716</v>
+      </c>
+      <c r="C4814" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4815" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4815" t="s">
+        <v>9717</v>
+      </c>
+      <c r="B4815" t="s">
+        <v>9718</v>
+      </c>
+      <c r="C4815" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4816" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4816" t="s">
+        <v>9719</v>
+      </c>
+      <c r="B4816" t="s">
+        <v>9720</v>
+      </c>
+      <c r="C4816" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4817" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4817" t="s">
+        <v>9721</v>
+      </c>
+      <c r="B4817" t="s">
+        <v>9722</v>
+      </c>
+      <c r="C4817" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4818" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4818" t="s">
+        <v>9723</v>
+      </c>
+      <c r="B4818" t="s">
+        <v>9724</v>
+      </c>
+      <c r="C4818" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4819" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4819" t="s">
+        <v>9725</v>
+      </c>
+      <c r="B4819" t="s">
+        <v>9726</v>
+      </c>
+      <c r="C4819" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4820" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4820" t="s">
+        <v>9727</v>
+      </c>
+      <c r="B4820" t="s">
+        <v>9728</v>
+      </c>
+      <c r="C4820" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4821" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4821" t="s">
+        <v>9729</v>
+      </c>
+      <c r="B4821" t="s">
+        <v>9730</v>
+      </c>
+      <c r="C4821" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4822" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4822" t="s">
+        <v>9731</v>
+      </c>
+      <c r="B4822" t="s">
+        <v>9732</v>
+      </c>
+      <c r="C4822" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4823" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4823" t="s">
+        <v>9733</v>
+      </c>
+      <c r="B4823" t="s">
+        <v>9734</v>
+      </c>
+      <c r="C4823" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4824" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4824" t="s">
+        <v>9735</v>
+      </c>
+      <c r="B4824" t="s">
+        <v>9736</v>
+      </c>
+      <c r="C4824" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4825" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4825" t="s">
+        <v>9737</v>
+      </c>
+      <c r="B4825" t="s">
+        <v>9738</v>
+      </c>
+      <c r="C4825" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4826" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4826" t="s">
+        <v>9739</v>
+      </c>
+      <c r="B4826" t="s">
+        <v>9740</v>
+      </c>
+      <c r="C4826" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4827" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4827" t="s">
+        <v>9741</v>
+      </c>
+      <c r="B4827" t="s">
+        <v>9742</v>
+      </c>
+      <c r="C4827" t="s">
+        <v>9562</v>
+      </c>
+    </row>
+    <row r="4828" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4828" t="s">
+        <v>9743</v>
+      </c>
+      <c r="B4828" t="s">
+        <v>9744</v>
+      </c>
+      <c r="C4828" t="s">
+        <v>9562</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12978" uniqueCount="9745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13044" uniqueCount="9790">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -29252,6 +29252,141 @@
   </si>
   <si>
     <t>КПБ Постельное бельё поплин 2 спальное Евро простыня - "Бонетто" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618768</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 120х200х30 - 120 - Воздушность А+В наволочки 50х70</t>
+  </si>
+  <si>
+    <t>01-06-2026</t>
+  </si>
+  <si>
+    <t>4681001618751</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 50х70 - "Эфирида"</t>
+  </si>
+  <si>
+    <t>4681001618744</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин-жаккард 1,5 спальное - Пинкроуз Универсал</t>
+  </si>
+  <si>
+    <t>4681001618737</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 145х215 - "Облачка"</t>
+  </si>
+  <si>
+    <t>4681001618720</t>
+  </si>
+  <si>
+    <t>Простыня твил-сатин резинка 160х200х20 - "Облачка"</t>
+  </si>
+  <si>
+    <t>4681001618713</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 140х200х40 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001618706</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 120х200х30 - 125 - "Фая" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618690</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное Евро простыня - "Звёздный туман" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618683</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 240х260 - 120 - Снежинка</t>
+  </si>
+  <si>
+    <t>4681001618676</t>
+  </si>
+  <si>
+    <t>Простыня Жатка на резинке 180х200х40 - "Звездный Сон"</t>
+  </si>
+  <si>
+    <t>4681001618669</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 150х220 - 110 - Леопарды</t>
+  </si>
+  <si>
+    <t>4681001618652</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - "Ягуар" Универсал</t>
+  </si>
+  <si>
+    <t>4681001618645</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х20 - "Латунь"</t>
+  </si>
+  <si>
+    <t>4681001618638</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 120 - Иолит</t>
+  </si>
+  <si>
+    <t>4681001618621</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Хризоколла"</t>
+  </si>
+  <si>
+    <t>4681001618614</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Айвелин"</t>
+  </si>
+  <si>
+    <t>4681001618607</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - Прохлада ментола</t>
+  </si>
+  <si>
+    <t>4681001618591</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001618584</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Айвелин"</t>
+  </si>
+  <si>
+    <t>4681001618577</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Холодная элегия"</t>
+  </si>
+  <si>
+    <t>4681001618560</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - Мечта</t>
+  </si>
+  <si>
+    <t>4681001618553</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Мечта</t>
   </si>
 </sst>
 </file>
@@ -78222,6 +78357,248 @@
         <v>9562</v>
       </c>
     </row>
+    <row r="4829" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4829" t="s">
+        <v>9745</v>
+      </c>
+      <c r="B4829" t="s">
+        <v>9746</v>
+      </c>
+      <c r="C4829" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4830" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4830" t="s">
+        <v>9748</v>
+      </c>
+      <c r="B4830" t="s">
+        <v>9749</v>
+      </c>
+      <c r="C4830" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4831" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4831" t="s">
+        <v>9750</v>
+      </c>
+      <c r="B4831" t="s">
+        <v>9751</v>
+      </c>
+      <c r="C4831" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4832" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4832" t="s">
+        <v>9752</v>
+      </c>
+      <c r="B4832" t="s">
+        <v>9753</v>
+      </c>
+      <c r="C4832" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4833" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4833" t="s">
+        <v>9754</v>
+      </c>
+      <c r="B4833" t="s">
+        <v>9755</v>
+      </c>
+      <c r="C4833" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4834" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4834" t="s">
+        <v>9756</v>
+      </c>
+      <c r="B4834" t="s">
+        <v>9757</v>
+      </c>
+      <c r="C4834" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4835" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4835" t="s">
+        <v>9758</v>
+      </c>
+      <c r="B4835" t="s">
+        <v>9759</v>
+      </c>
+      <c r="C4835" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4836" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4836" t="s">
+        <v>9760</v>
+      </c>
+      <c r="B4836" t="s">
+        <v>9761</v>
+      </c>
+      <c r="C4836" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4837" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4837" t="s">
+        <v>9762</v>
+      </c>
+      <c r="B4837" t="s">
+        <v>9763</v>
+      </c>
+      <c r="C4837" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4838" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4838" t="s">
+        <v>9764</v>
+      </c>
+      <c r="B4838" t="s">
+        <v>9765</v>
+      </c>
+      <c r="C4838" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4839" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4839" t="s">
+        <v>9766</v>
+      </c>
+      <c r="B4839" t="s">
+        <v>9767</v>
+      </c>
+      <c r="C4839" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4840" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4840" t="s">
+        <v>9768</v>
+      </c>
+      <c r="B4840" t="s">
+        <v>9769</v>
+      </c>
+      <c r="C4840" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4841" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4841" t="s">
+        <v>9770</v>
+      </c>
+      <c r="B4841" t="s">
+        <v>9771</v>
+      </c>
+      <c r="C4841" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4842" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4842" t="s">
+        <v>9772</v>
+      </c>
+      <c r="B4842" t="s">
+        <v>9773</v>
+      </c>
+      <c r="C4842" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4843" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4843" t="s">
+        <v>9774</v>
+      </c>
+      <c r="B4843" t="s">
+        <v>9775</v>
+      </c>
+      <c r="C4843" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4844" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4844" t="s">
+        <v>9776</v>
+      </c>
+      <c r="B4844" t="s">
+        <v>9777</v>
+      </c>
+      <c r="C4844" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4845" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4845" t="s">
+        <v>9778</v>
+      </c>
+      <c r="B4845" t="s">
+        <v>9779</v>
+      </c>
+      <c r="C4845" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4846" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4846" t="s">
+        <v>9780</v>
+      </c>
+      <c r="B4846" t="s">
+        <v>9781</v>
+      </c>
+      <c r="C4846" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4847" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4847" t="s">
+        <v>9782</v>
+      </c>
+      <c r="B4847" t="s">
+        <v>9783</v>
+      </c>
+      <c r="C4847" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4848" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4848" t="s">
+        <v>9784</v>
+      </c>
+      <c r="B4848" t="s">
+        <v>9785</v>
+      </c>
+      <c r="C4848" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4849" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4849" t="s">
+        <v>9786</v>
+      </c>
+      <c r="B4849" t="s">
+        <v>9787</v>
+      </c>
+      <c r="C4849" t="s">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="4850" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4850" t="s">
+        <v>9788</v>
+      </c>
+      <c r="B4850" t="s">
+        <v>9789</v>
+      </c>
+      <c r="C4850" t="s">
+        <v>9747</v>
+      </c>
+    </row>
     <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4853" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13044" uniqueCount="9790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13083" uniqueCount="9817">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -29387,6 +29387,87 @@
   </si>
   <si>
     <t>Наволочка тенсель 70х70 - Мечта</t>
+  </si>
+  <si>
+    <t>4681001618898</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 120х200х30 - "Теодор" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>02-06-2026</t>
+  </si>
+  <si>
+    <t>4681001618881</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 120х200х30 - "Айсу" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618874</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 220х240 - Премиум ТС 320 Вишенка</t>
+  </si>
+  <si>
+    <t>4681001618867</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - 80 - Теплые Пожелания</t>
+  </si>
+  <si>
+    <t>4681001618850</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Зелёный Страйп" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618843</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 200х220 - Пинклайт</t>
+  </si>
+  <si>
+    <t>4681001618836</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Белава"</t>
+  </si>
+  <si>
+    <t>4681001618829</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4681001618812</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь семейное - 142 - Сиреневые маки</t>
+  </si>
+  <si>
+    <t>4681001618805</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001618799</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное - 130 - "Дивуар" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001618782</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 130 - "Дивуар" 1х1</t>
+  </si>
+  <si>
+    <t>4681001618775</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль семейное - 110 - Изысканность</t>
   </si>
 </sst>
 </file>
@@ -78599,8 +78680,148 @@
         <v>9747</v>
       </c>
     </row>
-    <row r="4853" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4853" s="7"/>
+    <row r="4851" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4851" t="s">
+        <v>9790</v>
+      </c>
+      <c r="B4851" t="s">
+        <v>9791</v>
+      </c>
+      <c r="C4851" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4852" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4852" t="s">
+        <v>9793</v>
+      </c>
+      <c r="B4852" t="s">
+        <v>9794</v>
+      </c>
+      <c r="C4852" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4853" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4853" s="7" t="s">
+        <v>9795</v>
+      </c>
+      <c r="B4853" t="s">
+        <v>9796</v>
+      </c>
+      <c r="C4853" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4854" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4854" t="s">
+        <v>9797</v>
+      </c>
+      <c r="B4854" t="s">
+        <v>9798</v>
+      </c>
+      <c r="C4854" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4855" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4855" t="s">
+        <v>9799</v>
+      </c>
+      <c r="B4855" t="s">
+        <v>9800</v>
+      </c>
+      <c r="C4855" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4856" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4856" t="s">
+        <v>9801</v>
+      </c>
+      <c r="B4856" t="s">
+        <v>9802</v>
+      </c>
+      <c r="C4856" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4857" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4857" t="s">
+        <v>9803</v>
+      </c>
+      <c r="B4857" t="s">
+        <v>9804</v>
+      </c>
+      <c r="C4857" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4858" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4858" t="s">
+        <v>9805</v>
+      </c>
+      <c r="B4858" t="s">
+        <v>9806</v>
+      </c>
+      <c r="C4858" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4859" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4859" t="s">
+        <v>9807</v>
+      </c>
+      <c r="B4859" t="s">
+        <v>9808</v>
+      </c>
+      <c r="C4859" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4860" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4860" t="s">
+        <v>9809</v>
+      </c>
+      <c r="B4860" t="s">
+        <v>9810</v>
+      </c>
+      <c r="C4860" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4861" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4861" t="s">
+        <v>9811</v>
+      </c>
+      <c r="B4861" t="s">
+        <v>9812</v>
+      </c>
+      <c r="C4861" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4862" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4862" t="s">
+        <v>9813</v>
+      </c>
+      <c r="B4862" t="s">
+        <v>9814</v>
+      </c>
+      <c r="C4862" t="s">
+        <v>9792</v>
+      </c>
+    </row>
+    <row r="4863" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4863" t="s">
+        <v>9815</v>
+      </c>
+      <c r="B4863" t="s">
+        <v>9816</v>
+      </c>
+      <c r="C4863" t="s">
+        <v>9792</v>
+      </c>
     </row>
     <row r="4890" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G4890" s="7"/>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13083" uniqueCount="9817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13167" uniqueCount="9874">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -29468,6 +29468,177 @@
   </si>
   <si>
     <t>КПБ Постельное бельё перкаль семейное - 110 - Изысканность</t>
+  </si>
+  <si>
+    <t>4681001619178</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>03-06-2026</t>
+  </si>
+  <si>
+    <t>4681001619161</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 140х200х40 - "Криола"</t>
+  </si>
+  <si>
+    <t>4681001619154</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 145х215 - 130 - "Лавандула" 1х1</t>
+  </si>
+  <si>
+    <t>4681001619147</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х45 - 130 - "Лавандула" 1х1</t>
+  </si>
+  <si>
+    <t>4681001619130</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х30 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001619123</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 175х215 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001619116</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001619109</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 160х200х30 - 110 - Полнолуние</t>
+  </si>
+  <si>
+    <t>4681001619093</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 140х200х30 - "Графитовый Зигзаг" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619086</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное резинка 160х200х20 - "Графитовый Зигзаг"</t>
+  </si>
+  <si>
+    <t>4681001619079</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 135 - Мокрый асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4681001619062</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - "Лунь" 1х1</t>
+  </si>
+  <si>
+    <t>4681001619055</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - "Лунь" 1х1</t>
+  </si>
+  <si>
+    <t>4681001619048</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 160х200х30 - 120 - Трюфель наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619031</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 80х200х40 - "Анхела"</t>
+  </si>
+  <si>
+    <t>4681001619024</t>
+  </si>
+  <si>
+    <t>Простыня поплин 220х240 - Белоснежное</t>
+  </si>
+  <si>
+    <t>4681001619017</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 70х70 - 120 - Отбеленная</t>
+  </si>
+  <si>
+    <t>4681001619000</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 60х60 - Зеленый чай</t>
+  </si>
+  <si>
+    <t>4681001618997</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 145х215 - Голубая сталь</t>
+  </si>
+  <si>
+    <t>4681001618980</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Голубая сталь</t>
+  </si>
+  <si>
+    <t>4681001618973</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 2 спальное Евро простыня - "Коррадо"</t>
+  </si>
+  <si>
+    <t>4681001618966</t>
+  </si>
+  <si>
+    <t>Пододеяльник микрофибра 200х220 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4681001618959</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин семейное резинка 180х200х30 - "Лигурия"</t>
+  </si>
+  <si>
+    <t>4681001618942</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 50х70 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001618935</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 200х220 - "Лиловый тауп"</t>
+  </si>
+  <si>
+    <t>4681001618928</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 140х200х30 - Пастельно-розовый</t>
+  </si>
+  <si>
+    <t>4681001618911</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4681001618904</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 200х200 - "Белый Этюд"</t>
   </si>
 </sst>
 </file>
@@ -78823,8 +78994,314 @@
         <v>9792</v>
       </c>
     </row>
-    <row r="4890" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="4864" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4864" t="s">
+        <v>9817</v>
+      </c>
+      <c r="B4864" t="s">
+        <v>9818</v>
+      </c>
+      <c r="C4864" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4865" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4865" t="s">
+        <v>9820</v>
+      </c>
+      <c r="B4865" t="s">
+        <v>9821</v>
+      </c>
+      <c r="C4865" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4866" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4866" t="s">
+        <v>9822</v>
+      </c>
+      <c r="B4866" t="s">
+        <v>9823</v>
+      </c>
+      <c r="C4866" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4867" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4867" t="s">
+        <v>9824</v>
+      </c>
+      <c r="B4867" t="s">
+        <v>9825</v>
+      </c>
+      <c r="C4867" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4868" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4868" t="s">
+        <v>9826</v>
+      </c>
+      <c r="B4868" t="s">
+        <v>9827</v>
+      </c>
+      <c r="C4868" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4869" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4869" t="s">
+        <v>9828</v>
+      </c>
+      <c r="B4869" t="s">
+        <v>9829</v>
+      </c>
+      <c r="C4869" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4870" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4870" t="s">
+        <v>9830</v>
+      </c>
+      <c r="B4870" t="s">
+        <v>9831</v>
+      </c>
+      <c r="C4870" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4871" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4871" t="s">
+        <v>9832</v>
+      </c>
+      <c r="B4871" t="s">
+        <v>9833</v>
+      </c>
+      <c r="C4871" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4872" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4872" t="s">
+        <v>9834</v>
+      </c>
+      <c r="B4872" t="s">
+        <v>9835</v>
+      </c>
+      <c r="C4872" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4873" t="s">
+        <v>9836</v>
+      </c>
+      <c r="B4873" t="s">
+        <v>9837</v>
+      </c>
+      <c r="C4873" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4874" t="s">
+        <v>9838</v>
+      </c>
+      <c r="B4874" t="s">
+        <v>9839</v>
+      </c>
+      <c r="C4874" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4875" t="s">
+        <v>9840</v>
+      </c>
+      <c r="B4875" t="s">
+        <v>9841</v>
+      </c>
+      <c r="C4875" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4876" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4876" t="s">
+        <v>9842</v>
+      </c>
+      <c r="B4876" t="s">
+        <v>9843</v>
+      </c>
+      <c r="C4876" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4877" t="s">
+        <v>9844</v>
+      </c>
+      <c r="B4877" t="s">
+        <v>9845</v>
+      </c>
+      <c r="C4877" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4878" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4878" t="s">
+        <v>9846</v>
+      </c>
+      <c r="B4878" t="s">
+        <v>9847</v>
+      </c>
+      <c r="C4878" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4879" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4879" t="s">
+        <v>9848</v>
+      </c>
+      <c r="B4879" t="s">
+        <v>9849</v>
+      </c>
+      <c r="C4879" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4880" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4880" t="s">
+        <v>9850</v>
+      </c>
+      <c r="B4880" t="s">
+        <v>9851</v>
+      </c>
+      <c r="C4880" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4881" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4881" t="s">
+        <v>9852</v>
+      </c>
+      <c r="B4881" t="s">
+        <v>9853</v>
+      </c>
+      <c r="C4881" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4882" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4882" t="s">
+        <v>9854</v>
+      </c>
+      <c r="B4882" t="s">
+        <v>9855</v>
+      </c>
+      <c r="C4882" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4883" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4883" t="s">
+        <v>9856</v>
+      </c>
+      <c r="B4883" t="s">
+        <v>9857</v>
+      </c>
+      <c r="C4883" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4884" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4884" t="s">
+        <v>9858</v>
+      </c>
+      <c r="B4884" t="s">
+        <v>9859</v>
+      </c>
+      <c r="C4884" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4885" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4885" t="s">
+        <v>9860</v>
+      </c>
+      <c r="B4885" t="s">
+        <v>9861</v>
+      </c>
+      <c r="C4885" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4886" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4886" t="s">
+        <v>9862</v>
+      </c>
+      <c r="B4886" t="s">
+        <v>9863</v>
+      </c>
+      <c r="C4886" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4887" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4887" t="s">
+        <v>9864</v>
+      </c>
+      <c r="B4887" t="s">
+        <v>9865</v>
+      </c>
+      <c r="C4887" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4888" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4888" t="s">
+        <v>9866</v>
+      </c>
+      <c r="B4888" t="s">
+        <v>9867</v>
+      </c>
+      <c r="C4888" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4889" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4889" t="s">
+        <v>9868</v>
+      </c>
+      <c r="B4889" t="s">
+        <v>9869</v>
+      </c>
+      <c r="C4889" t="s">
+        <v>9819</v>
+      </c>
+    </row>
+    <row r="4890" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4890" t="s">
+        <v>9870</v>
+      </c>
+      <c r="B4890" t="s">
+        <v>9871</v>
+      </c>
+      <c r="C4890" t="s">
+        <v>9819</v>
+      </c>
       <c r="G4890" s="7"/>
+    </row>
+    <row r="4891" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4891" t="s">
+        <v>9872</v>
+      </c>
+      <c r="B4891" t="s">
+        <v>9873</v>
+      </c>
+      <c r="C4891" t="s">
+        <v>9819</v>
+      </c>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13167" uniqueCount="9874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13263" uniqueCount="9939">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -29639,6 +29639,201 @@
   </si>
   <si>
     <t>Пододеяльник жатка 200х200 - "Белый Этюд"</t>
+  </si>
+  <si>
+    <t>4681001619499</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 145х215 - "Севим"</t>
+  </si>
+  <si>
+    <t>04-06-2026</t>
+  </si>
+  <si>
+    <t>4681001619482</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х220х40 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001619475</t>
+  </si>
+  <si>
+    <t>Простыня жатка 260х260 - "Природный Абстракт"</t>
+  </si>
+  <si>
+    <t>4681001619468</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 120х200х30 - "Нева" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619451</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное - "Аперто" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619444</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Туманная Аура"</t>
+  </si>
+  <si>
+    <t>4681001619437</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Туманная Аура"</t>
+  </si>
+  <si>
+    <t>4681001619420</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 145х215 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001619413</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Эрос" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619406</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - 4294 Перламутровый</t>
+  </si>
+  <si>
+    <t>4681001619390</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - 4373 Пудровый</t>
+  </si>
+  <si>
+    <t>4681001619383</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - Нежно-розовый</t>
+  </si>
+  <si>
+    <t>4681001619376</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 260х260 - "Лемпи"</t>
+  </si>
+  <si>
+    <t>4681001619369</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 200х200 - Зеленый чай</t>
+  </si>
+  <si>
+    <t>4681001619352</t>
+  </si>
+  <si>
+    <t>Наволочка микросатин 70х70 - "Легкий роман"</t>
+  </si>
+  <si>
+    <t>4681001619345</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 180х200х30 - "Сиренево-розовый"</t>
+  </si>
+  <si>
+    <t>4681001619338</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 220х240 - "Далиян"</t>
+  </si>
+  <si>
+    <t>4681001619321</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 60х60 - "Айсберг"</t>
+  </si>
+  <si>
+    <t>4681001619314</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Ларион"</t>
+  </si>
+  <si>
+    <t>4681001619307</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - Меропа</t>
+  </si>
+  <si>
+    <t>4681001619291</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 300х300 - Чёрная гавань</t>
+  </si>
+  <si>
+    <t>4681001619284</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 120х200х30 - 135 - Принцесс Эн 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619277</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 112х147 - "Стильные девчонки"</t>
+  </si>
+  <si>
+    <t>4681001619260</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 40х60 - "Стильные девчонки"</t>
+  </si>
+  <si>
+    <t>4681001619253</t>
+  </si>
+  <si>
+    <t>Простыня поплин 100х150 - "Стильные девчонки"</t>
+  </si>
+  <si>
+    <t>4681001619246</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4681001619239</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 140х200х30 - "Эдже" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619222</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х30 - "Флорес" 1х1</t>
+  </si>
+  <si>
+    <t>4681001619215</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Парижский Шарм"</t>
+  </si>
+  <si>
+    <t>4681001619208</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 200х220 - "Тирас"</t>
+  </si>
+  <si>
+    <t>4681001619192</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 70х70 - Солнечное кружево</t>
+  </si>
+  <si>
+    <t>4681001619185</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 125 - "Шампань" 1х1</t>
   </si>
 </sst>
 </file>
@@ -79303,6 +79498,358 @@
         <v>9819</v>
       </c>
     </row>
+    <row r="4892" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4892" t="s">
+        <v>9874</v>
+      </c>
+      <c r="B4892" t="s">
+        <v>9875</v>
+      </c>
+      <c r="C4892" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4893" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4893" t="s">
+        <v>9877</v>
+      </c>
+      <c r="B4893" t="s">
+        <v>9878</v>
+      </c>
+      <c r="C4893" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4894" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4894" t="s">
+        <v>9879</v>
+      </c>
+      <c r="B4894" t="s">
+        <v>9880</v>
+      </c>
+      <c r="C4894" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4895" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4895" t="s">
+        <v>9881</v>
+      </c>
+      <c r="B4895" t="s">
+        <v>9882</v>
+      </c>
+      <c r="C4895" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4896" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4896" t="s">
+        <v>9883</v>
+      </c>
+      <c r="B4896" t="s">
+        <v>9884</v>
+      </c>
+      <c r="C4896" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4897" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4897" t="s">
+        <v>9885</v>
+      </c>
+      <c r="B4897" t="s">
+        <v>9886</v>
+      </c>
+      <c r="C4897" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4898" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4898" t="s">
+        <v>9887</v>
+      </c>
+      <c r="B4898" t="s">
+        <v>9888</v>
+      </c>
+      <c r="C4898" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4899" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4899" t="s">
+        <v>9889</v>
+      </c>
+      <c r="B4899" t="s">
+        <v>9890</v>
+      </c>
+      <c r="C4899" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4900" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4900" t="s">
+        <v>9891</v>
+      </c>
+      <c r="B4900" t="s">
+        <v>9892</v>
+      </c>
+      <c r="C4900" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4901" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4901" t="s">
+        <v>9893</v>
+      </c>
+      <c r="B4901" t="s">
+        <v>9894</v>
+      </c>
+      <c r="C4901" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4902" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4902" t="s">
+        <v>9895</v>
+      </c>
+      <c r="B4902" t="s">
+        <v>9896</v>
+      </c>
+      <c r="C4902" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4903" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4903" t="s">
+        <v>9897</v>
+      </c>
+      <c r="B4903" t="s">
+        <v>9898</v>
+      </c>
+      <c r="C4903" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4904" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4904" t="s">
+        <v>9899</v>
+      </c>
+      <c r="B4904" t="s">
+        <v>9900</v>
+      </c>
+      <c r="C4904" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4905" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4905" t="s">
+        <v>9901</v>
+      </c>
+      <c r="B4905" t="s">
+        <v>9902</v>
+      </c>
+      <c r="C4905" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4906" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4906" t="s">
+        <v>9903</v>
+      </c>
+      <c r="B4906" t="s">
+        <v>9904</v>
+      </c>
+      <c r="C4906" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4907" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4907" t="s">
+        <v>9905</v>
+      </c>
+      <c r="B4907" t="s">
+        <v>9906</v>
+      </c>
+      <c r="C4907" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4908" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4908" t="s">
+        <v>9907</v>
+      </c>
+      <c r="B4908" t="s">
+        <v>9908</v>
+      </c>
+      <c r="C4908" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4909" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4909" t="s">
+        <v>9909</v>
+      </c>
+      <c r="B4909" t="s">
+        <v>9910</v>
+      </c>
+      <c r="C4909" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4910" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4910" t="s">
+        <v>9911</v>
+      </c>
+      <c r="B4910" t="s">
+        <v>9912</v>
+      </c>
+      <c r="C4910" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4911" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4911" t="s">
+        <v>9913</v>
+      </c>
+      <c r="B4911" t="s">
+        <v>9914</v>
+      </c>
+      <c r="C4911" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4912" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4912" t="s">
+        <v>9915</v>
+      </c>
+      <c r="B4912" t="s">
+        <v>9916</v>
+      </c>
+      <c r="C4912" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4913" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4913" t="s">
+        <v>9917</v>
+      </c>
+      <c r="B4913" t="s">
+        <v>9918</v>
+      </c>
+      <c r="C4913" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4914" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4914" t="s">
+        <v>9919</v>
+      </c>
+      <c r="B4914" t="s">
+        <v>9920</v>
+      </c>
+      <c r="C4914" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4915" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4915" t="s">
+        <v>9921</v>
+      </c>
+      <c r="B4915" t="s">
+        <v>9922</v>
+      </c>
+      <c r="C4915" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4916" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4916" t="s">
+        <v>9923</v>
+      </c>
+      <c r="B4916" t="s">
+        <v>9924</v>
+      </c>
+      <c r="C4916" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4917" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4917" t="s">
+        <v>9925</v>
+      </c>
+      <c r="B4917" t="s">
+        <v>9926</v>
+      </c>
+      <c r="C4917" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4918" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4918" t="s">
+        <v>9927</v>
+      </c>
+      <c r="B4918" t="s">
+        <v>9928</v>
+      </c>
+      <c r="C4918" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4919" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4919" t="s">
+        <v>9929</v>
+      </c>
+      <c r="B4919" t="s">
+        <v>9930</v>
+      </c>
+      <c r="C4919" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4920" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4920" t="s">
+        <v>9931</v>
+      </c>
+      <c r="B4920" t="s">
+        <v>9932</v>
+      </c>
+      <c r="C4920" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4921" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4921" t="s">
+        <v>9933</v>
+      </c>
+      <c r="B4921" t="s">
+        <v>9934</v>
+      </c>
+      <c r="C4921" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4922" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4922" t="s">
+        <v>9935</v>
+      </c>
+      <c r="B4922" t="s">
+        <v>9936</v>
+      </c>
+      <c r="C4922" t="s">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="4923" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4923" t="s">
+        <v>9937</v>
+      </c>
+      <c r="B4923" t="s">
+        <v>9938</v>
+      </c>
+      <c r="C4923" t="s">
+        <v>9876</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13263" uniqueCount="9939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13323" uniqueCount="9980">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -29834,6 +29834,129 @@
   </si>
   <si>
     <t>Наволочка страйп-сатин 70х70 - 125 - "Шампань" 1х1</t>
+  </si>
+  <si>
+    <t>4681001619697</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - "Фиорис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>05-06-2026</t>
+  </si>
+  <si>
+    <t>4681001619680</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Дечимо"</t>
+  </si>
+  <si>
+    <t>4681001619673</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 280х280 - "Холодная элегия"</t>
+  </si>
+  <si>
+    <t>4681001619666</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 120х200х10 - "Милда"</t>
+  </si>
+  <si>
+    <t>4681001619659</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 120х200х10 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001619642</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра семейное резинка 160х200х30 - "Альбелла" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619635</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное - "Ледяной Мрамор" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619628</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное Евро простыня - "Бриллиантовые кружева" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619611</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - "Жеманти" 1х1</t>
+  </si>
+  <si>
+    <t>4681001619604</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра резинка 140х200х40 - "Петкана"</t>
+  </si>
+  <si>
+    <t>4681001619598</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 180х200х30 - "Трувиль"</t>
+  </si>
+  <si>
+    <t>4681001619581</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - 80 - Витражи наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619574</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - 4377 Синий</t>
+  </si>
+  <si>
+    <t>4681001619567</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001619550</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - "Джуман"</t>
+  </si>
+  <si>
+    <t>4681001619543</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 300х300 - "Сахарная роза"</t>
+  </si>
+  <si>
+    <t>4681001619536</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 160х200х30 - "Бежевый Коралл"</t>
+  </si>
+  <si>
+    <t>4681001619529</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 125 - Аквамарин 1х1</t>
+  </si>
+  <si>
+    <t>4681001619512</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 125 - Аквамарин 1х1</t>
+  </si>
+  <si>
+    <t>4681001619505</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х30 - 125 - Аквамарин 1х1</t>
   </si>
 </sst>
 </file>
@@ -79850,6 +79973,226 @@
         <v>9876</v>
       </c>
     </row>
+    <row r="4924" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4924" t="s">
+        <v>9939</v>
+      </c>
+      <c r="B4924" t="s">
+        <v>9940</v>
+      </c>
+      <c r="C4924" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4925" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4925" t="s">
+        <v>9942</v>
+      </c>
+      <c r="B4925" t="s">
+        <v>9943</v>
+      </c>
+      <c r="C4925" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4926" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4926" t="s">
+        <v>9944</v>
+      </c>
+      <c r="B4926" t="s">
+        <v>9945</v>
+      </c>
+      <c r="C4926" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4927" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4927" t="s">
+        <v>9946</v>
+      </c>
+      <c r="B4927" t="s">
+        <v>9947</v>
+      </c>
+      <c r="C4927" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4928" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4928" t="s">
+        <v>9948</v>
+      </c>
+      <c r="B4928" t="s">
+        <v>9949</v>
+      </c>
+      <c r="C4928" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4929" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4929" t="s">
+        <v>9950</v>
+      </c>
+      <c r="B4929" t="s">
+        <v>9951</v>
+      </c>
+      <c r="C4929" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4930" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4930" t="s">
+        <v>9952</v>
+      </c>
+      <c r="B4930" t="s">
+        <v>9953</v>
+      </c>
+      <c r="C4930" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4931" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4931" t="s">
+        <v>9954</v>
+      </c>
+      <c r="B4931" t="s">
+        <v>9955</v>
+      </c>
+      <c r="C4931" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4932" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4932" t="s">
+        <v>9956</v>
+      </c>
+      <c r="B4932" t="s">
+        <v>9957</v>
+      </c>
+      <c r="C4932" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4933" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4933" t="s">
+        <v>9958</v>
+      </c>
+      <c r="B4933" t="s">
+        <v>9959</v>
+      </c>
+      <c r="C4933" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4934" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4934" t="s">
+        <v>9960</v>
+      </c>
+      <c r="B4934" t="s">
+        <v>9961</v>
+      </c>
+      <c r="C4934" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4935" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4935" t="s">
+        <v>9962</v>
+      </c>
+      <c r="B4935" t="s">
+        <v>9963</v>
+      </c>
+      <c r="C4935" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4936" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4936" t="s">
+        <v>9964</v>
+      </c>
+      <c r="B4936" t="s">
+        <v>9965</v>
+      </c>
+      <c r="C4936" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4937" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4937" t="s">
+        <v>9966</v>
+      </c>
+      <c r="B4937" t="s">
+        <v>9967</v>
+      </c>
+      <c r="C4937" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4938" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4938" t="s">
+        <v>9968</v>
+      </c>
+      <c r="B4938" t="s">
+        <v>9969</v>
+      </c>
+      <c r="C4938" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4939" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4939" t="s">
+        <v>9970</v>
+      </c>
+      <c r="B4939" t="s">
+        <v>9971</v>
+      </c>
+      <c r="C4939" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4940" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4940" t="s">
+        <v>9972</v>
+      </c>
+      <c r="B4940" t="s">
+        <v>9973</v>
+      </c>
+      <c r="C4940" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4941" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4941" t="s">
+        <v>9974</v>
+      </c>
+      <c r="B4941" t="s">
+        <v>9975</v>
+      </c>
+      <c r="C4941" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4942" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4942" t="s">
+        <v>9976</v>
+      </c>
+      <c r="B4942" t="s">
+        <v>9977</v>
+      </c>
+      <c r="C4942" t="s">
+        <v>9941</v>
+      </c>
+    </row>
+    <row r="4943" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4943" t="s">
+        <v>9978</v>
+      </c>
+      <c r="B4943" t="s">
+        <v>9979</v>
+      </c>
+      <c r="C4943" t="s">
+        <v>9941</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26787A6A-B5E0-4759-8F77-087BE17A703A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
+    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13323" uniqueCount="9980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13410" uniqueCount="10039">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -29957,35 +29958,212 @@
   </si>
   <si>
     <t>Простыня страйп-сатин резинка 120х200х30 - 125 - Аквамарин 1х1</t>
+  </si>
+  <si>
+    <t>4681001619970</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Цветочный Шёпот"</t>
+  </si>
+  <si>
+    <t>06-06-2026</t>
+  </si>
+  <si>
+    <t>4681001619963</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 240х260 - 135 - Фирюз 1х1</t>
+  </si>
+  <si>
+    <t>4681001619956</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001619949</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - 4393 Темно-серый</t>
+  </si>
+  <si>
+    <t>4681001619932</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - 125 - Шашки Шампань 0,5х0,5</t>
+  </si>
+  <si>
+    <t>4681001619925</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 200х200 - Графит (меланж)</t>
+  </si>
+  <si>
+    <t>4681001619918</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - 120 - Урубамба наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619901</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное на резинке 180х200х30 - "Золотой блеск" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001619895</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное резинка 180х200х30 - "Стальная тень" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619888</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - Меропа наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619871</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - "Шарли" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619864</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х20 - Сливочно-кремовый</t>
+  </si>
+  <si>
+    <t>4681001619857</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин семейное - 125 - "Шампань" 1х1</t>
+  </si>
+  <si>
+    <t>4681001619840</t>
+  </si>
+  <si>
+    <t>КПБ Постельное белье тенсель 2 спальное на резинке 160х200х30 - М - Нью Шепард с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001619833</t>
+  </si>
+  <si>
+    <t>КПБ Постельное белье тенсель 2 спальное на резинке 160х200х30 - М - 60S 4393 Темно-серый с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001619826</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 140 - Миндаль 1х1</t>
+  </si>
+  <si>
+    <t>4681001619819</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х70 - Белый</t>
+  </si>
+  <si>
+    <t>4681001619802</t>
+  </si>
+  <si>
+    <t>Простыня бязь 280х280 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001619796</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - 140 - Кремовая пудра 1х1</t>
+  </si>
+  <si>
+    <t>4681001619789</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х40 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001619772</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х40 - 129 Темно-зеленый</t>
+  </si>
+  <si>
+    <t>4681001619765</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х30 - Малахит</t>
+  </si>
+  <si>
+    <t>4681001619758</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 220х240 - 125 - "Фиалка" 1х1</t>
+  </si>
+  <si>
+    <t>4681001619741</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра семейное резинка 160х200х30 - "Эстрелья"</t>
+  </si>
+  <si>
+    <t>4681001619734</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 80х200х30 - 4307 Сливочный Страйп 1х1</t>
+  </si>
+  <si>
+    <t>4681001619727</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Сливочный"</t>
+  </si>
+  <si>
+    <t>4681001619710</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001619703</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - "Мяурель" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001619987</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х20 - 135 - Кувертюр 1х1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -30011,10 +30189,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -30038,7 +30224,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -30315,9 +30501,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
@@ -30325,13 +30511,13 @@
     <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -30360,7 +30546,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -30368,7 +30554,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -30376,7 +30562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -30384,7 +30570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -30392,7 +30578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -30400,7 +30586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -30408,7 +30594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -30416,7 +30602,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -30424,7 +30610,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -30432,7 +30618,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -30440,7 +30626,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -30448,7 +30634,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -42232,7 +42418,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -42240,7 +42426,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -42248,7 +42434,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -42256,7 +42442,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -42264,7 +42450,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -42272,7 +42458,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -42280,7 +42466,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -42288,7 +42474,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -42296,7 +42482,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -42304,7 +42490,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -42312,7 +42498,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -42320,7 +42506,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -42328,7 +42514,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -42336,7 +42522,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -42344,7 +42530,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -79499,7 +79685,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4881" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4881" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4881" t="s">
         <v>9852</v>
       </c>
@@ -79510,7 +79696,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4882" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4882" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4882" t="s">
         <v>9854</v>
       </c>
@@ -79521,7 +79707,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4883" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4883" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4883" t="s">
         <v>9856</v>
       </c>
@@ -79532,7 +79718,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4884" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4884" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4884" t="s">
         <v>9858</v>
       </c>
@@ -79543,7 +79729,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4885" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4885" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4885" t="s">
         <v>9860</v>
       </c>
@@ -79554,7 +79740,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4886" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4886" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4886" t="s">
         <v>9862</v>
       </c>
@@ -79565,7 +79751,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4887" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4887" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4887" t="s">
         <v>9864</v>
       </c>
@@ -79576,7 +79762,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4888" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4888" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4888" t="s">
         <v>9866</v>
       </c>
@@ -79587,7 +79773,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4889" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4889" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4889" t="s">
         <v>9868</v>
       </c>
@@ -79610,7 +79796,7 @@
       </c>
       <c r="G4890" s="7"/>
     </row>
-    <row r="4891" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4891" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4891" t="s">
         <v>9872</v>
       </c>
@@ -79621,7 +79807,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4892" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4892" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4892" t="s">
         <v>9874</v>
       </c>
@@ -79632,7 +79818,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4893" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4893" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4893" t="s">
         <v>9877</v>
       </c>
@@ -79643,7 +79829,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4894" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4894" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4894" t="s">
         <v>9879</v>
       </c>
@@ -79654,7 +79840,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4895" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4895" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4895" t="s">
         <v>9881</v>
       </c>
@@ -79665,7 +79851,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4896" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4896" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4896" t="s">
         <v>9883</v>
       </c>
@@ -80191,6 +80377,325 @@
       </c>
       <c r="C4943" t="s">
         <v>9941</v>
+      </c>
+    </row>
+    <row r="4944" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4944" t="s">
+        <v>9980</v>
+      </c>
+      <c r="B4944" t="s">
+        <v>9981</v>
+      </c>
+      <c r="C4944" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4945" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4945" t="s">
+        <v>9983</v>
+      </c>
+      <c r="B4945" t="s">
+        <v>9984</v>
+      </c>
+      <c r="C4945" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4946" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4946" t="s">
+        <v>9985</v>
+      </c>
+      <c r="B4946" t="s">
+        <v>9986</v>
+      </c>
+      <c r="C4946" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4947" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4947" t="s">
+        <v>9987</v>
+      </c>
+      <c r="B4947" t="s">
+        <v>9988</v>
+      </c>
+      <c r="C4947" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4948" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4948" t="s">
+        <v>9989</v>
+      </c>
+      <c r="B4948" t="s">
+        <v>9990</v>
+      </c>
+      <c r="C4948" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4949" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4949" t="s">
+        <v>9991</v>
+      </c>
+      <c r="B4949" t="s">
+        <v>9992</v>
+      </c>
+      <c r="C4949" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4950" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4950" t="s">
+        <v>9993</v>
+      </c>
+      <c r="B4950" t="s">
+        <v>9994</v>
+      </c>
+      <c r="C4950" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4951" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4951" t="s">
+        <v>9995</v>
+      </c>
+      <c r="B4951" t="s">
+        <v>9996</v>
+      </c>
+      <c r="C4951" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4952" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4952" t="s">
+        <v>9997</v>
+      </c>
+      <c r="B4952" t="s">
+        <v>9998</v>
+      </c>
+      <c r="C4952" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4953" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4953" t="s">
+        <v>9999</v>
+      </c>
+      <c r="B4953" t="s">
+        <v>10000</v>
+      </c>
+      <c r="C4953" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4954" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4954" t="s">
+        <v>10001</v>
+      </c>
+      <c r="B4954" t="s">
+        <v>10002</v>
+      </c>
+      <c r="C4954" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4955" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4955" t="s">
+        <v>10003</v>
+      </c>
+      <c r="B4955" t="s">
+        <v>10004</v>
+      </c>
+      <c r="C4955" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4956" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4956" t="s">
+        <v>10005</v>
+      </c>
+      <c r="B4956" t="s">
+        <v>10006</v>
+      </c>
+      <c r="C4956" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4957" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4957" t="s">
+        <v>10007</v>
+      </c>
+      <c r="B4957" t="s">
+        <v>10008</v>
+      </c>
+      <c r="C4957" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4958" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4958" t="s">
+        <v>10009</v>
+      </c>
+      <c r="B4958" t="s">
+        <v>10010</v>
+      </c>
+      <c r="C4958" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4959" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4959" t="s">
+        <v>10011</v>
+      </c>
+      <c r="B4959" t="s">
+        <v>10012</v>
+      </c>
+      <c r="C4959" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4960" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4960" t="s">
+        <v>10013</v>
+      </c>
+      <c r="B4960" t="s">
+        <v>10014</v>
+      </c>
+      <c r="C4960" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4961" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4961" t="s">
+        <v>10015</v>
+      </c>
+      <c r="B4961" t="s">
+        <v>10016</v>
+      </c>
+      <c r="C4961" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4962" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4962" t="s">
+        <v>10017</v>
+      </c>
+      <c r="B4962" t="s">
+        <v>10018</v>
+      </c>
+      <c r="C4962" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4963" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4963" t="s">
+        <v>10019</v>
+      </c>
+      <c r="B4963" t="s">
+        <v>10020</v>
+      </c>
+      <c r="C4963" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4964" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4964" t="s">
+        <v>10021</v>
+      </c>
+      <c r="B4964" t="s">
+        <v>10022</v>
+      </c>
+      <c r="C4964" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4965" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4965" t="s">
+        <v>10023</v>
+      </c>
+      <c r="B4965" t="s">
+        <v>10024</v>
+      </c>
+      <c r="C4965" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4966" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4966" t="s">
+        <v>10025</v>
+      </c>
+      <c r="B4966" t="s">
+        <v>10026</v>
+      </c>
+      <c r="C4966" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4967" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4967" t="s">
+        <v>10027</v>
+      </c>
+      <c r="B4967" t="s">
+        <v>10028</v>
+      </c>
+      <c r="C4967" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4968" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4968" t="s">
+        <v>10029</v>
+      </c>
+      <c r="B4968" t="s">
+        <v>10030</v>
+      </c>
+      <c r="C4968" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4969" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4969" t="s">
+        <v>10031</v>
+      </c>
+      <c r="B4969" t="s">
+        <v>10032</v>
+      </c>
+      <c r="C4969" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4970" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4970" t="s">
+        <v>10033</v>
+      </c>
+      <c r="B4970" t="s">
+        <v>10034</v>
+      </c>
+      <c r="C4970" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4971" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4971" t="s">
+        <v>10035</v>
+      </c>
+      <c r="B4971" t="s">
+        <v>10036</v>
+      </c>
+      <c r="C4971" t="s">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="4972" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4972" t="s">
+        <v>10037</v>
+      </c>
+      <c r="B4972" t="s">
+        <v>10038</v>
+      </c>
+      <c r="C4972" t="s">
+        <v>9982</v>
       </c>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26787A6A-B5E0-4759-8F77-087BE17A703A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13410" uniqueCount="10039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13557" uniqueCount="10138">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -30135,35 +30134,332 @@
   </si>
   <si>
     <t>Простыня страйп-сатин резинка 120х200х20 - 135 - Кувертюр 1х1</t>
+  </si>
+  <si>
+    <t>4681001620471</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 160х200х30 - 110 - Каори на желтом</t>
+  </si>
+  <si>
+    <t>07-06-2026</t>
+  </si>
+  <si>
+    <t>4681001620464</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 200х220 - 110 - Каори на желтом</t>
+  </si>
+  <si>
+    <t>4681001620457</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 70х70 - 110 - Каори на желтом</t>
+  </si>
+  <si>
+    <t>4681001620440</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - Виридан</t>
+  </si>
+  <si>
+    <t>4681001620433</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Грей блес</t>
+  </si>
+  <si>
+    <t>4681001620426</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 150х220 - Белый</t>
+  </si>
+  <si>
+    <t>4681001620419</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок семейное - Графит (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620402</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - Горький шоколад наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620396</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Горький шоколад</t>
+  </si>
+  <si>
+    <t>4681001620389</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Сумерин"</t>
+  </si>
+  <si>
+    <t>4681001620372</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 220х240 - 135 - Дип Пёрпл 1х1</t>
+  </si>
+  <si>
+    <t>4681001620365</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Лебединое перо"</t>
+  </si>
+  <si>
+    <t>4681001620358</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 135 - Форастеро 1х1</t>
+  </si>
+  <si>
+    <t>4681001620341</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Солнечный Лоск"</t>
+  </si>
+  <si>
+    <t>4681001620334</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 260х260 - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001620327</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Айвелин"</t>
+  </si>
+  <si>
+    <t>4681001620310</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - "Айвелин"</t>
+  </si>
+  <si>
+    <t>4681001620303</t>
+  </si>
+  <si>
+    <t>Простыня из сатина на резинке 140х200х20 - 140 - "Можиана Люкс"</t>
+  </si>
+  <si>
+    <t>4681001620297</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 140 - Асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4681001620280</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001620273</t>
+  </si>
+  <si>
+    <t>Простыня бязь 300х300 - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001620266</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 200х220 - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001620259</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 150х200 - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001620242</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин семейное резинка 160х200х30 - "Триша" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620235</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин семейное резинка 160х200х30 - "Аполлон" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620228</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин семейное резинка 160х200х30 - "Эдже" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620211</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - "Серебряный Лес"</t>
+  </si>
+  <si>
+    <t>4681001620204</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - 129 Темно-зеленый</t>
+  </si>
+  <si>
+    <t>4681001620198</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное - "Пьетро" Универсал</t>
+  </si>
+  <si>
+    <t>4681001620181</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 142 "ВанФан"</t>
+  </si>
+  <si>
+    <t>4681001620174</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - Кружева на голубом</t>
+  </si>
+  <si>
+    <t>4681001620167</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро-макси - 142 - Сиреневые маки</t>
+  </si>
+  <si>
+    <t>4681001620150</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 220х240 - Пурпурный</t>
+  </si>
+  <si>
+    <t>4681001620143</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 120х200х20 - Чёрная гавань</t>
+  </si>
+  <si>
+    <t>4681001620136</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 240х260 - Зеленый чай</t>
+  </si>
+  <si>
+    <t>4681001620129</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая резинка 90х200х40 - Мулетон Полиэстер</t>
+  </si>
+  <si>
+    <t>4681001620112</t>
+  </si>
+  <si>
+    <t>Простыня из страйп-сатина на резинке 140 х 200 х 40 - М - 135 - Кортадерия 1х1</t>
+  </si>
+  <si>
+    <t>4681001620105</t>
+  </si>
+  <si>
+    <t>Пододеяльник ранфорс 150х200 - "Кремневый серый"</t>
+  </si>
+  <si>
+    <t>4681001620099</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка Евро - "Астероид"</t>
+  </si>
+  <si>
+    <t>4681001620082</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 160х200х20 - "Эдже" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620075</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - 80 - Югацу</t>
+  </si>
+  <si>
+    <t>4681001620068</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 70х70 - "Рендалис"</t>
+  </si>
+  <si>
+    <t>4681001620051</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс 180х220 - Милитгрин</t>
+  </si>
+  <si>
+    <t>4681001620044</t>
+  </si>
+  <si>
+    <t>Простыня сатин 150х220 - "Персиль"</t>
+  </si>
+  <si>
+    <t>4681001620037</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х200х20 - "Млада"</t>
+  </si>
+  <si>
+    <t>4681001620020</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х40 - 120 - Диши Корал</t>
+  </si>
+  <si>
+    <t>4681001620013</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001620006</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 140 - Лаванда 1х1</t>
+  </si>
+  <si>
+    <t>4681001619994</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 40х60 - "Морские приключения"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -30189,18 +30485,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -30224,7 +30512,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -30501,9 +30789,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
@@ -30511,13 +30799,13 @@
     <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -30546,7 +30834,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -30554,7 +30842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -30562,7 +30850,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -30570,7 +30858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -30578,7 +30866,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -30586,7 +30874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -30594,7 +30882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -30602,7 +30890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -30610,7 +30898,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -30618,7 +30906,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -30626,7 +30914,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -30634,7 +30922,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -42418,7 +42706,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -42426,7 +42714,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -42434,7 +42722,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -42442,7 +42730,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -42450,7 +42738,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -42458,7 +42746,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -42466,7 +42754,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -42474,7 +42762,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -42482,7 +42770,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -42490,7 +42778,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -42498,7 +42786,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -42506,7 +42794,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -42514,7 +42802,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -42522,7 +42810,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -42530,7 +42818,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -79685,7 +79973,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4881" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4881" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4881" t="s">
         <v>9852</v>
       </c>
@@ -79696,7 +79984,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4882" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4882" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4882" t="s">
         <v>9854</v>
       </c>
@@ -79707,7 +79995,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4883" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4883" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4883" t="s">
         <v>9856</v>
       </c>
@@ -79718,7 +80006,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4884" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4884" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4884" t="s">
         <v>9858</v>
       </c>
@@ -79729,7 +80017,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4885" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4885" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4885" t="s">
         <v>9860</v>
       </c>
@@ -79740,7 +80028,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4886" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4886" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4886" t="s">
         <v>9862</v>
       </c>
@@ -79751,7 +80039,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4887" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4887" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4887" t="s">
         <v>9864</v>
       </c>
@@ -79762,7 +80050,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4888" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4888" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4888" t="s">
         <v>9866</v>
       </c>
@@ -79773,7 +80061,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4889" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4889" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4889" t="s">
         <v>9868</v>
       </c>
@@ -79796,7 +80084,7 @@
       </c>
       <c r="G4890" s="7"/>
     </row>
-    <row r="4891" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4891" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4891" t="s">
         <v>9872</v>
       </c>
@@ -79807,7 +80095,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4892" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4892" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4892" t="s">
         <v>9874</v>
       </c>
@@ -79818,7 +80106,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4893" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4893" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4893" t="s">
         <v>9877</v>
       </c>
@@ -79829,7 +80117,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4894" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4894" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4894" t="s">
         <v>9879</v>
       </c>
@@ -79840,7 +80128,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4895" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4895" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4895" t="s">
         <v>9881</v>
       </c>
@@ -79851,7 +80139,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4896" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4896" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4896" t="s">
         <v>9883</v>
       </c>
@@ -80696,6 +80984,545 @@
       </c>
       <c r="C4972" t="s">
         <v>9982</v>
+      </c>
+    </row>
+    <row r="4973" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4973" t="s">
+        <v>10039</v>
+      </c>
+      <c r="B4973" t="s">
+        <v>10040</v>
+      </c>
+      <c r="C4973" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4974" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4974" t="s">
+        <v>10042</v>
+      </c>
+      <c r="B4974" t="s">
+        <v>10043</v>
+      </c>
+      <c r="C4974" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4975" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4975" t="s">
+        <v>10044</v>
+      </c>
+      <c r="B4975" t="s">
+        <v>10045</v>
+      </c>
+      <c r="C4975" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4976" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4976" t="s">
+        <v>10046</v>
+      </c>
+      <c r="B4976" t="s">
+        <v>10047</v>
+      </c>
+      <c r="C4976" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4977" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4977" t="s">
+        <v>10048</v>
+      </c>
+      <c r="B4977" t="s">
+        <v>10049</v>
+      </c>
+      <c r="C4977" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4978" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4978" t="s">
+        <v>10050</v>
+      </c>
+      <c r="B4978" t="s">
+        <v>10051</v>
+      </c>
+      <c r="C4978" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4979" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4979" t="s">
+        <v>10052</v>
+      </c>
+      <c r="B4979" t="s">
+        <v>10053</v>
+      </c>
+      <c r="C4979" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4980" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4980" t="s">
+        <v>10054</v>
+      </c>
+      <c r="B4980" t="s">
+        <v>10055</v>
+      </c>
+      <c r="C4980" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4981" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4981" t="s">
+        <v>10056</v>
+      </c>
+      <c r="B4981" t="s">
+        <v>10057</v>
+      </c>
+      <c r="C4981" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4982" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4982" t="s">
+        <v>10058</v>
+      </c>
+      <c r="B4982" t="s">
+        <v>10059</v>
+      </c>
+      <c r="C4982" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4983" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4983" t="s">
+        <v>10060</v>
+      </c>
+      <c r="B4983" t="s">
+        <v>10061</v>
+      </c>
+      <c r="C4983" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4984" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4984" t="s">
+        <v>10062</v>
+      </c>
+      <c r="B4984" t="s">
+        <v>10063</v>
+      </c>
+      <c r="C4984" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4985" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4985" t="s">
+        <v>10064</v>
+      </c>
+      <c r="B4985" t="s">
+        <v>10065</v>
+      </c>
+      <c r="C4985" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4986" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4986" t="s">
+        <v>10066</v>
+      </c>
+      <c r="B4986" t="s">
+        <v>10067</v>
+      </c>
+      <c r="C4986" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4987" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4987" t="s">
+        <v>10068</v>
+      </c>
+      <c r="B4987" t="s">
+        <v>10069</v>
+      </c>
+      <c r="C4987" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4988" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4988" t="s">
+        <v>10070</v>
+      </c>
+      <c r="B4988" t="s">
+        <v>10071</v>
+      </c>
+      <c r="C4988" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4989" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4989" t="s">
+        <v>10072</v>
+      </c>
+      <c r="B4989" t="s">
+        <v>10073</v>
+      </c>
+      <c r="C4989" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4990" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4990" t="s">
+        <v>10074</v>
+      </c>
+      <c r="B4990" t="s">
+        <v>10075</v>
+      </c>
+      <c r="C4990" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4991" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4991" t="s">
+        <v>10076</v>
+      </c>
+      <c r="B4991" t="s">
+        <v>10077</v>
+      </c>
+      <c r="C4991" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4992" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4992" t="s">
+        <v>10078</v>
+      </c>
+      <c r="B4992" t="s">
+        <v>10079</v>
+      </c>
+      <c r="C4992" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4993" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4993" t="s">
+        <v>10080</v>
+      </c>
+      <c r="B4993" t="s">
+        <v>10081</v>
+      </c>
+      <c r="C4993" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4994" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4994" t="s">
+        <v>10082</v>
+      </c>
+      <c r="B4994" t="s">
+        <v>10083</v>
+      </c>
+      <c r="C4994" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4995" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4995" t="s">
+        <v>10084</v>
+      </c>
+      <c r="B4995" t="s">
+        <v>10085</v>
+      </c>
+      <c r="C4995" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4996" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4996" t="s">
+        <v>10086</v>
+      </c>
+      <c r="B4996" t="s">
+        <v>10087</v>
+      </c>
+      <c r="C4996" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4997" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4997" t="s">
+        <v>10088</v>
+      </c>
+      <c r="B4997" t="s">
+        <v>10089</v>
+      </c>
+      <c r="C4997" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4998" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4998" t="s">
+        <v>10090</v>
+      </c>
+      <c r="B4998" t="s">
+        <v>10091</v>
+      </c>
+      <c r="C4998" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="4999" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4999" t="s">
+        <v>10092</v>
+      </c>
+      <c r="B4999" t="s">
+        <v>10093</v>
+      </c>
+      <c r="C4999" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5000" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5000" t="s">
+        <v>10094</v>
+      </c>
+      <c r="B5000" t="s">
+        <v>10095</v>
+      </c>
+      <c r="C5000" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5001" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5001" t="s">
+        <v>10096</v>
+      </c>
+      <c r="B5001" t="s">
+        <v>10097</v>
+      </c>
+      <c r="C5001" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5002" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5002" t="s">
+        <v>10098</v>
+      </c>
+      <c r="B5002" t="s">
+        <v>10099</v>
+      </c>
+      <c r="C5002" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5003" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5003" t="s">
+        <v>10100</v>
+      </c>
+      <c r="B5003" t="s">
+        <v>10101</v>
+      </c>
+      <c r="C5003" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5004" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5004" t="s">
+        <v>10102</v>
+      </c>
+      <c r="B5004" t="s">
+        <v>10103</v>
+      </c>
+      <c r="C5004" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5005" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5005" t="s">
+        <v>10104</v>
+      </c>
+      <c r="B5005" t="s">
+        <v>10105</v>
+      </c>
+      <c r="C5005" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5006" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5006" t="s">
+        <v>10106</v>
+      </c>
+      <c r="B5006" t="s">
+        <v>10107</v>
+      </c>
+      <c r="C5006" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5007" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5007" t="s">
+        <v>10108</v>
+      </c>
+      <c r="B5007" t="s">
+        <v>10109</v>
+      </c>
+      <c r="C5007" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5008" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5008" t="s">
+        <v>10110</v>
+      </c>
+      <c r="B5008" t="s">
+        <v>10111</v>
+      </c>
+      <c r="C5008" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5009" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5009" t="s">
+        <v>10112</v>
+      </c>
+      <c r="B5009" t="s">
+        <v>10113</v>
+      </c>
+      <c r="C5009" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5010" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5010" t="s">
+        <v>10114</v>
+      </c>
+      <c r="B5010" t="s">
+        <v>10115</v>
+      </c>
+      <c r="C5010" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5011" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5011" t="s">
+        <v>10116</v>
+      </c>
+      <c r="B5011" t="s">
+        <v>10117</v>
+      </c>
+      <c r="C5011" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5012" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5012" t="s">
+        <v>10118</v>
+      </c>
+      <c r="B5012" t="s">
+        <v>10119</v>
+      </c>
+      <c r="C5012" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5013" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5013" t="s">
+        <v>10120</v>
+      </c>
+      <c r="B5013" t="s">
+        <v>10121</v>
+      </c>
+      <c r="C5013" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5014" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5014" t="s">
+        <v>10122</v>
+      </c>
+      <c r="B5014" t="s">
+        <v>10123</v>
+      </c>
+      <c r="C5014" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5015" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5015" t="s">
+        <v>10124</v>
+      </c>
+      <c r="B5015" t="s">
+        <v>10125</v>
+      </c>
+      <c r="C5015" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5016" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5016" t="s">
+        <v>10126</v>
+      </c>
+      <c r="B5016" t="s">
+        <v>10127</v>
+      </c>
+      <c r="C5016" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5017" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5017" t="s">
+        <v>10128</v>
+      </c>
+      <c r="B5017" t="s">
+        <v>10129</v>
+      </c>
+      <c r="C5017" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5018" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5018" t="s">
+        <v>10130</v>
+      </c>
+      <c r="B5018" t="s">
+        <v>10131</v>
+      </c>
+      <c r="C5018" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5019" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5019" t="s">
+        <v>10132</v>
+      </c>
+      <c r="B5019" t="s">
+        <v>10133</v>
+      </c>
+      <c r="C5019" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5020" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5020" t="s">
+        <v>10134</v>
+      </c>
+      <c r="B5020" t="s">
+        <v>10135</v>
+      </c>
+      <c r="C5020" t="s">
+        <v>10041</v>
+      </c>
+    </row>
+    <row r="5021" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5021" t="s">
+        <v>10136</v>
+      </c>
+      <c r="B5021" t="s">
+        <v>10137</v>
+      </c>
+      <c r="C5021" t="s">
+        <v>10041</v>
       </c>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13557" uniqueCount="10138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13626" uniqueCount="10185">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -30431,6 +30431,147 @@
   </si>
   <si>
     <t>Наволочка перкаль 40х60 - "Морские приключения"</t>
+  </si>
+  <si>
+    <t>4681001620709</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Марриотт Белый 3х3</t>
+  </si>
+  <si>
+    <t>08-06-2026</t>
+  </si>
+  <si>
+    <t>4681001620693</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 200х220 - "Пролив" 1х1</t>
+  </si>
+  <si>
+    <t>4681001620686</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 280х280 - 140 - Голубой 1х1</t>
+  </si>
+  <si>
+    <t>4681001620679</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль семейное резинка 180х200х30 - 125 - Радмила наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620662</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 160х200х30 - 135 - Солнечный, полоска 1х1</t>
+  </si>
+  <si>
+    <t>4681001620655</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Аполлон" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620648</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 140х200х30 - "Аполлон" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620631</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001620624</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин семейное резинка 160х200х30 - "Милда" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620617</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - "Золотой блеск"</t>
+  </si>
+  <si>
+    <t>4681001620600</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х40 - 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4681001620594</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 135 - Бежевый крем 1х1</t>
+  </si>
+  <si>
+    <t>4681001620587</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин браш King Size резинка 200х200х30 - Муравка</t>
+  </si>
+  <si>
+    <t>4681001620570</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Эвергрин"</t>
+  </si>
+  <si>
+    <t>4681001620563</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х240х30 - 130 - Сланцево-серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001620556</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х240х30 - 130 - Мятный фреш 1х1</t>
+  </si>
+  <si>
+    <t>4681001620549</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Цветочный Шарм" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620532</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 90х200х20 - 142 - Магия мяты</t>
+  </si>
+  <si>
+    <t>4681001620525</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - 4217 Бежевый</t>
+  </si>
+  <si>
+    <t>4681001620518</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - АРТ - Рената</t>
+  </si>
+  <si>
+    <t>4681001620501</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 2 спальное - 125 - "Черника" 1х1</t>
+  </si>
+  <si>
+    <t>4681001620495</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 180х200х30 - "Песочный Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001620488</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 200х200 - "Легкий роман"</t>
   </si>
 </sst>
 </file>
@@ -81525,6 +81666,259 @@
         <v>10041</v>
       </c>
     </row>
+    <row r="5022" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5022" t="s">
+        <v>10138</v>
+      </c>
+      <c r="B5022" t="s">
+        <v>10139</v>
+      </c>
+      <c r="C5022" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5023" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5023" t="s">
+        <v>10141</v>
+      </c>
+      <c r="B5023" t="s">
+        <v>10142</v>
+      </c>
+      <c r="C5023" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5024" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5024" t="s">
+        <v>10143</v>
+      </c>
+      <c r="B5024" t="s">
+        <v>10144</v>
+      </c>
+      <c r="C5024" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5025" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5025" t="s">
+        <v>10145</v>
+      </c>
+      <c r="B5025" t="s">
+        <v>10146</v>
+      </c>
+      <c r="C5025" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5026" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5026" t="s">
+        <v>10147</v>
+      </c>
+      <c r="B5026" t="s">
+        <v>10148</v>
+      </c>
+      <c r="C5026" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5027" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5027" t="s">
+        <v>10149</v>
+      </c>
+      <c r="B5027" t="s">
+        <v>10150</v>
+      </c>
+      <c r="C5027" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5028" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5028" t="s">
+        <v>10151</v>
+      </c>
+      <c r="B5028" t="s">
+        <v>10152</v>
+      </c>
+      <c r="C5028" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5029" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5029" t="s">
+        <v>10153</v>
+      </c>
+      <c r="B5029" t="s">
+        <v>10154</v>
+      </c>
+      <c r="C5029" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5030" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5030" t="s">
+        <v>10155</v>
+      </c>
+      <c r="B5030" t="s">
+        <v>10156</v>
+      </c>
+      <c r="C5030" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5031" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5031" t="s">
+        <v>10157</v>
+      </c>
+      <c r="B5031" t="s">
+        <v>10158</v>
+      </c>
+      <c r="C5031" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5032" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5032" t="s">
+        <v>10159</v>
+      </c>
+      <c r="B5032" t="s">
+        <v>10160</v>
+      </c>
+      <c r="C5032" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5033" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5033" t="s">
+        <v>10161</v>
+      </c>
+      <c r="B5033" t="s">
+        <v>10162</v>
+      </c>
+      <c r="C5033" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5034" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5034" t="s">
+        <v>10163</v>
+      </c>
+      <c r="B5034" t="s">
+        <v>10164</v>
+      </c>
+      <c r="C5034" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5035" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5035" t="s">
+        <v>10165</v>
+      </c>
+      <c r="B5035" t="s">
+        <v>10166</v>
+      </c>
+      <c r="C5035" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5036" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5036" t="s">
+        <v>10167</v>
+      </c>
+      <c r="B5036" t="s">
+        <v>10168</v>
+      </c>
+      <c r="C5036" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5037" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5037" t="s">
+        <v>10169</v>
+      </c>
+      <c r="B5037" t="s">
+        <v>10170</v>
+      </c>
+      <c r="C5037" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5038" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5038" t="s">
+        <v>10171</v>
+      </c>
+      <c r="B5038" t="s">
+        <v>10172</v>
+      </c>
+      <c r="C5038" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5039" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5039" t="s">
+        <v>10173</v>
+      </c>
+      <c r="B5039" t="s">
+        <v>10174</v>
+      </c>
+      <c r="C5039" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5040" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5040" t="s">
+        <v>10175</v>
+      </c>
+      <c r="B5040" t="s">
+        <v>10176</v>
+      </c>
+      <c r="C5040" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5041" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5041" t="s">
+        <v>10177</v>
+      </c>
+      <c r="B5041" t="s">
+        <v>10178</v>
+      </c>
+      <c r="C5041" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5042" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5042" t="s">
+        <v>10179</v>
+      </c>
+      <c r="B5042" t="s">
+        <v>10180</v>
+      </c>
+      <c r="C5042" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5043" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5043" t="s">
+        <v>10181</v>
+      </c>
+      <c r="B5043" t="s">
+        <v>10182</v>
+      </c>
+      <c r="C5043" t="s">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="5044" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5044" t="s">
+        <v>10183</v>
+      </c>
+      <c r="B5044" t="s">
+        <v>10184</v>
+      </c>
+      <c r="C5044" t="s">
+        <v>10140</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13626" uniqueCount="10185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13698" uniqueCount="10234">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -30572,6 +30572,153 @@
   </si>
   <si>
     <t>Пододеяльник микросатин 200х200 - "Легкий роман"</t>
+  </si>
+  <si>
+    <t>4681001620945</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное - "Стальная тень" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>09-06-2026</t>
+  </si>
+  <si>
+    <t>4681001620938</t>
+  </si>
+  <si>
+    <t>Простыня поплин 180х220 - Кружева на сером</t>
+  </si>
+  <si>
+    <t>4681001620921</t>
+  </si>
+  <si>
+    <t>Простыня поплин 180х220 - Кружева на розовом</t>
+  </si>
+  <si>
+    <t>4681001620914</t>
+  </si>
+  <si>
+    <t>Простыня поплин 180х220 - Кружева на баклажановом</t>
+  </si>
+  <si>
+    <t>4681001620907</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Милда"</t>
+  </si>
+  <si>
+    <t>4681001620891</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 260х260 - "Аделаида"</t>
+  </si>
+  <si>
+    <t>4681001620884</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро-макси - 120 - Кремовый Бутон наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620877</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро макси - М - 120 - Чёрный мрамор с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001620860</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё бязь для детских кроваток - 125 - Игры Слоника на голубом</t>
+  </si>
+  <si>
+    <t>4681001620853</t>
+  </si>
+  <si>
+    <t>КПБ Детское постельное бельё бязь для детских кроваток - 142 - Зверята на розовом</t>
+  </si>
+  <si>
+    <t>4681001620846</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х200х20 - "Андреза"</t>
+  </si>
+  <si>
+    <t>4681001620839</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - Хрустальный оазис</t>
+  </si>
+  <si>
+    <t>4681001620822</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Хрустальный оазис</t>
+  </si>
+  <si>
+    <t>4681001620815</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микрофибра 2 спальное - "Петкана"</t>
+  </si>
+  <si>
+    <t>4681001620808</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - 4234 Морская нимфа наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620792</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - Королевский пурпур наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620785</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро - Белый</t>
+  </si>
+  <si>
+    <t>4681001620778</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 180х200х30 - "Цветочный Шёпот" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001620761</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - 142 - Сладкий Мёд зелёный</t>
+  </si>
+  <si>
+    <t>4681001620754</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 40х60 - "Песочный Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001620747</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х50 - "Песочный Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001620730</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - 140 - Ежевика 1х1</t>
+  </si>
+  <si>
+    <t>4681001620723</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х40 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001620716</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х220 - 125 - Серый 2</t>
   </si>
 </sst>
 </file>
@@ -81919,6 +82066,270 @@
         <v>10140</v>
       </c>
     </row>
+    <row r="5045" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5045" t="s">
+        <v>10185</v>
+      </c>
+      <c r="B5045" t="s">
+        <v>10186</v>
+      </c>
+      <c r="C5045" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5046" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5046" t="s">
+        <v>10188</v>
+      </c>
+      <c r="B5046" t="s">
+        <v>10189</v>
+      </c>
+      <c r="C5046" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5047" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5047" t="s">
+        <v>10190</v>
+      </c>
+      <c r="B5047" t="s">
+        <v>10191</v>
+      </c>
+      <c r="C5047" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5048" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5048" t="s">
+        <v>10192</v>
+      </c>
+      <c r="B5048" t="s">
+        <v>10193</v>
+      </c>
+      <c r="C5048" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5049" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5049" t="s">
+        <v>10194</v>
+      </c>
+      <c r="B5049" t="s">
+        <v>10195</v>
+      </c>
+      <c r="C5049" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5050" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5050" t="s">
+        <v>10196</v>
+      </c>
+      <c r="B5050" t="s">
+        <v>10197</v>
+      </c>
+      <c r="C5050" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5051" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5051" t="s">
+        <v>10198</v>
+      </c>
+      <c r="B5051" t="s">
+        <v>10199</v>
+      </c>
+      <c r="C5051" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5052" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5052" t="s">
+        <v>10200</v>
+      </c>
+      <c r="B5052" t="s">
+        <v>10201</v>
+      </c>
+      <c r="C5052" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5053" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5053" t="s">
+        <v>10202</v>
+      </c>
+      <c r="B5053" t="s">
+        <v>10203</v>
+      </c>
+      <c r="C5053" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5054" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5054" t="s">
+        <v>10204</v>
+      </c>
+      <c r="B5054" t="s">
+        <v>10205</v>
+      </c>
+      <c r="C5054" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5055" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5055" t="s">
+        <v>10206</v>
+      </c>
+      <c r="B5055" t="s">
+        <v>10207</v>
+      </c>
+      <c r="C5055" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5056" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5056" t="s">
+        <v>10208</v>
+      </c>
+      <c r="B5056" t="s">
+        <v>10209</v>
+      </c>
+      <c r="C5056" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5057" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5057" t="s">
+        <v>10210</v>
+      </c>
+      <c r="B5057" t="s">
+        <v>10211</v>
+      </c>
+      <c r="C5057" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5058" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5058" t="s">
+        <v>10212</v>
+      </c>
+      <c r="B5058" t="s">
+        <v>10213</v>
+      </c>
+      <c r="C5058" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5059" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5059" t="s">
+        <v>10214</v>
+      </c>
+      <c r="B5059" t="s">
+        <v>10215</v>
+      </c>
+      <c r="C5059" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5060" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5060" t="s">
+        <v>10216</v>
+      </c>
+      <c r="B5060" t="s">
+        <v>10217</v>
+      </c>
+      <c r="C5060" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5061" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5061" t="s">
+        <v>10218</v>
+      </c>
+      <c r="B5061" t="s">
+        <v>10219</v>
+      </c>
+      <c r="C5061" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5062" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5062" t="s">
+        <v>10220</v>
+      </c>
+      <c r="B5062" t="s">
+        <v>10221</v>
+      </c>
+      <c r="C5062" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5063" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5063" t="s">
+        <v>10222</v>
+      </c>
+      <c r="B5063" t="s">
+        <v>10223</v>
+      </c>
+      <c r="C5063" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5064" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5064" t="s">
+        <v>10224</v>
+      </c>
+      <c r="B5064" t="s">
+        <v>10225</v>
+      </c>
+      <c r="C5064" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5065" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5065" t="s">
+        <v>10226</v>
+      </c>
+      <c r="B5065" t="s">
+        <v>10227</v>
+      </c>
+      <c r="C5065" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5066" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5066" t="s">
+        <v>10228</v>
+      </c>
+      <c r="B5066" t="s">
+        <v>10229</v>
+      </c>
+      <c r="C5066" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5067" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5067" t="s">
+        <v>10230</v>
+      </c>
+      <c r="B5067" t="s">
+        <v>10231</v>
+      </c>
+      <c r="C5067" t="s">
+        <v>10187</v>
+      </c>
+    </row>
+    <row r="5068" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5068" t="s">
+        <v>10232</v>
+      </c>
+      <c r="B5068" t="s">
+        <v>10233</v>
+      </c>
+      <c r="C5068" t="s">
+        <v>10187</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13698" uniqueCount="10234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13767" uniqueCount="10281">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -30719,6 +30719,147 @@
   </si>
   <si>
     <t>Пододеяльник сатин 200х220 - 125 - Серый 2</t>
+  </si>
+  <si>
+    <t>4681001621164</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 200х220 - "Белый Оникс"</t>
+  </si>
+  <si>
+    <t>10-06-2026</t>
+  </si>
+  <si>
+    <t>4681001621157</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель King Size резинка 200х200х30 - "Песочная роза"</t>
+  </si>
+  <si>
+    <t>4681001621140</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 280х280 - 140 - Асфальт 1х1</t>
+  </si>
+  <si>
+    <t>4681001621133</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 120х200х30 - 125 - "Гармония" 1х1</t>
+  </si>
+  <si>
+    <t>4681001621126</t>
+  </si>
+  <si>
+    <t>Простыня сатин 200х220 - 125 - Марсала</t>
+  </si>
+  <si>
+    <t>4681001621119</t>
+  </si>
+  <si>
+    <t>Простыня непромокаемая резинка 120х200х20 - Мулетон Полиэстер</t>
+  </si>
+  <si>
+    <t>4681001621102</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Аметистовый Шёлк" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621096</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 140х200х20 - "Соколиная охота"</t>
+  </si>
+  <si>
+    <t>4681001621089</t>
+  </si>
+  <si>
+    <t>Простыня из перкаля 300 х 300 - М - 110 - Лунго</t>
+  </si>
+  <si>
+    <t>4681001621072</t>
+  </si>
+  <si>
+    <t>Простыня бязь 180х220 - 142 - Стилизация</t>
+  </si>
+  <si>
+    <t>4681001621065</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 60х60 - "Корги-пати"</t>
+  </si>
+  <si>
+    <t>4681001621058</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 160х200х20 - Сиена</t>
+  </si>
+  <si>
+    <t>4681001621041</t>
+  </si>
+  <si>
+    <t>Простыня из сатина на резинке 160 х 200 х 20 - М - 125 - Абрикос</t>
+  </si>
+  <si>
+    <t>4681001621034</t>
+  </si>
+  <si>
+    <t>Простыня сатин 180х220 - 125 - Амарантово-розовый</t>
+  </si>
+  <si>
+    <t>4681001621027</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 280х280 - 129 Темно-зеленый</t>
+  </si>
+  <si>
+    <t>4681001621010</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х200х40 - "Олуфими"</t>
+  </si>
+  <si>
+    <t>4681001621003</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - Петроль</t>
+  </si>
+  <si>
+    <t>4681001620990</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х220 - "Лилизари"</t>
+  </si>
+  <si>
+    <t>4681001620983</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - 135 - Цитрус 3х3</t>
+  </si>
+  <si>
+    <t>4681001620976</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное на резинке 120х200х30 - М - 80 - Югацу</t>
+  </si>
+  <si>
+    <t>4681001620969</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х30 - "Песочная роза"</t>
+  </si>
+  <si>
+    <t>4681001620952</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Дино-пати"</t>
+  </si>
+  <si>
+    <t>4681001621171</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 145 - Миндаль 1х1</t>
   </si>
 </sst>
 </file>
@@ -82330,6 +82471,259 @@
         <v>10187</v>
       </c>
     </row>
+    <row r="5069" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5069" t="s">
+        <v>10234</v>
+      </c>
+      <c r="B5069" t="s">
+        <v>10235</v>
+      </c>
+      <c r="C5069" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5070" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5070" t="s">
+        <v>10237</v>
+      </c>
+      <c r="B5070" t="s">
+        <v>10238</v>
+      </c>
+      <c r="C5070" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5071" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5071" t="s">
+        <v>10239</v>
+      </c>
+      <c r="B5071" t="s">
+        <v>10240</v>
+      </c>
+      <c r="C5071" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5072" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5072" t="s">
+        <v>10241</v>
+      </c>
+      <c r="B5072" t="s">
+        <v>10242</v>
+      </c>
+      <c r="C5072" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5073" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5073" t="s">
+        <v>10243</v>
+      </c>
+      <c r="B5073" t="s">
+        <v>10244</v>
+      </c>
+      <c r="C5073" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5074" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5074" t="s">
+        <v>10245</v>
+      </c>
+      <c r="B5074" t="s">
+        <v>10246</v>
+      </c>
+      <c r="C5074" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5075" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5075" t="s">
+        <v>10247</v>
+      </c>
+      <c r="B5075" t="s">
+        <v>10248</v>
+      </c>
+      <c r="C5075" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5076" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5076" t="s">
+        <v>10249</v>
+      </c>
+      <c r="B5076" t="s">
+        <v>10250</v>
+      </c>
+      <c r="C5076" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5077" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5077" t="s">
+        <v>10251</v>
+      </c>
+      <c r="B5077" t="s">
+        <v>10252</v>
+      </c>
+      <c r="C5077" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5078" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5078" t="s">
+        <v>10253</v>
+      </c>
+      <c r="B5078" t="s">
+        <v>10254</v>
+      </c>
+      <c r="C5078" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5079" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5079" t="s">
+        <v>10255</v>
+      </c>
+      <c r="B5079" t="s">
+        <v>10256</v>
+      </c>
+      <c r="C5079" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5080" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5080" t="s">
+        <v>10257</v>
+      </c>
+      <c r="B5080" t="s">
+        <v>10258</v>
+      </c>
+      <c r="C5080" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5081" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5081" t="s">
+        <v>10259</v>
+      </c>
+      <c r="B5081" t="s">
+        <v>10260</v>
+      </c>
+      <c r="C5081" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5082" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5082" t="s">
+        <v>10261</v>
+      </c>
+      <c r="B5082" t="s">
+        <v>10262</v>
+      </c>
+      <c r="C5082" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5083" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5083" t="s">
+        <v>10263</v>
+      </c>
+      <c r="B5083" t="s">
+        <v>10264</v>
+      </c>
+      <c r="C5083" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5084" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5084" t="s">
+        <v>10265</v>
+      </c>
+      <c r="B5084" t="s">
+        <v>10266</v>
+      </c>
+      <c r="C5084" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5085" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5085" t="s">
+        <v>10267</v>
+      </c>
+      <c r="B5085" t="s">
+        <v>10268</v>
+      </c>
+      <c r="C5085" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5086" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5086" t="s">
+        <v>10269</v>
+      </c>
+      <c r="B5086" t="s">
+        <v>10270</v>
+      </c>
+      <c r="C5086" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5087" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5087" t="s">
+        <v>10271</v>
+      </c>
+      <c r="B5087" t="s">
+        <v>10272</v>
+      </c>
+      <c r="C5087" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5088" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5088" t="s">
+        <v>10273</v>
+      </c>
+      <c r="B5088" t="s">
+        <v>10274</v>
+      </c>
+      <c r="C5088" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5089" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5089" t="s">
+        <v>10275</v>
+      </c>
+      <c r="B5089" t="s">
+        <v>10276</v>
+      </c>
+      <c r="C5089" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5090" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5090" t="s">
+        <v>10277</v>
+      </c>
+      <c r="B5090" t="s">
+        <v>10278</v>
+      </c>
+      <c r="C5090" t="s">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="5091" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5091" t="s">
+        <v>10279</v>
+      </c>
+      <c r="B5091" t="s">
+        <v>10280</v>
+      </c>
+      <c r="C5091" t="s">
+        <v>10236</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13767" uniqueCount="10281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13839" uniqueCount="10330">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -30860,6 +30860,153 @@
   </si>
   <si>
     <t>Простыня страйп-сатин 180х220 - 145 - Миндаль 1х1</t>
+  </si>
+  <si>
+    <t>4681001621409</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 60х60 - "Дюмар" 1х1</t>
+  </si>
+  <si>
+    <t>11-06-2026</t>
+  </si>
+  <si>
+    <t>4681001621393</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 120х200х40 - "Кетеван"</t>
+  </si>
+  <si>
+    <t>4681001621386</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х70 - "Кетеван"</t>
+  </si>
+  <si>
+    <t>4681001621379</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 175х215 - "Экзотический"</t>
+  </si>
+  <si>
+    <t>4681001621362</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин браш 1,5 спальное резинка 120х200х30 - "Бронзит" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621355</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 200х200х40 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4681001621348</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 40х60 - Чёрная гавань</t>
+  </si>
+  <si>
+    <t>4681001621331</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 280х280 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001621324</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 260х260 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4681001621317</t>
+  </si>
+  <si>
+    <t>Простыня из перкаля 220 х 240 - М - 110 - Лунго</t>
+  </si>
+  <si>
+    <t>4681001621300</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 60х60 - 135 - Грей Нимбус</t>
+  </si>
+  <si>
+    <t>4681001621294</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 50х50 - "Стальная тень" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001621287</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - Фазенда Лиара</t>
+  </si>
+  <si>
+    <t>4681001621270</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - "Сиренево-розовый"</t>
+  </si>
+  <si>
+    <t>4681001621263</t>
+  </si>
+  <si>
+    <t>Простыня круглая полисатин резинка 200х200х20 - "Туманная Аура"</t>
+  </si>
+  <si>
+    <t>4681001621256</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 200х200х20 - 41-020 Серебряный</t>
+  </si>
+  <si>
+    <t>4681001621249</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Трендис" Универсал</t>
+  </si>
+  <si>
+    <t>4681001621232</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 240х260 - "Казимира"</t>
+  </si>
+  <si>
+    <t>4681001621225</t>
+  </si>
+  <si>
+    <t>Простыня круглая тенсель резинка 240х240х30 - 4294 Перламутровый</t>
+  </si>
+  <si>
+    <t>4681001621218</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - Королевский пурпур</t>
+  </si>
+  <si>
+    <t>4681001621201</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 60х60 - "Снежный Лепесток"</t>
+  </si>
+  <si>
+    <t>4681001621195</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 200х200х40 - 4235 Темно-синий</t>
+  </si>
+  <si>
+    <t>4681001621188</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 140х200х30 - Белоснежное</t>
+  </si>
+  <si>
+    <t>4681001621416</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 60х60 - "Ледяной Мрамор"</t>
   </si>
 </sst>
 </file>
@@ -82724,6 +82871,270 @@
         <v>10236</v>
       </c>
     </row>
+    <row r="5092" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5092" t="s">
+        <v>10281</v>
+      </c>
+      <c r="B5092" t="s">
+        <v>10282</v>
+      </c>
+      <c r="C5092" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5093" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5093" t="s">
+        <v>10284</v>
+      </c>
+      <c r="B5093" t="s">
+        <v>10285</v>
+      </c>
+      <c r="C5093" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5094" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5094" t="s">
+        <v>10286</v>
+      </c>
+      <c r="B5094" t="s">
+        <v>10287</v>
+      </c>
+      <c r="C5094" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5095" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5095" t="s">
+        <v>10288</v>
+      </c>
+      <c r="B5095" t="s">
+        <v>10289</v>
+      </c>
+      <c r="C5095" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5096" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5096" t="s">
+        <v>10290</v>
+      </c>
+      <c r="B5096" t="s">
+        <v>10291</v>
+      </c>
+      <c r="C5096" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5097" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5097" t="s">
+        <v>10292</v>
+      </c>
+      <c r="B5097" t="s">
+        <v>10293</v>
+      </c>
+      <c r="C5097" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5098" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5098" t="s">
+        <v>10294</v>
+      </c>
+      <c r="B5098" t="s">
+        <v>10295</v>
+      </c>
+      <c r="C5098" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5099" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5099" t="s">
+        <v>10296</v>
+      </c>
+      <c r="B5099" t="s">
+        <v>10297</v>
+      </c>
+      <c r="C5099" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5100" t="s">
+        <v>10298</v>
+      </c>
+      <c r="B5100" t="s">
+        <v>10299</v>
+      </c>
+      <c r="C5100" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5101" t="s">
+        <v>10300</v>
+      </c>
+      <c r="B5101" t="s">
+        <v>10301</v>
+      </c>
+      <c r="C5101" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5102" t="s">
+        <v>10302</v>
+      </c>
+      <c r="B5102" t="s">
+        <v>10303</v>
+      </c>
+      <c r="C5102" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5103" t="s">
+        <v>10304</v>
+      </c>
+      <c r="B5103" t="s">
+        <v>10305</v>
+      </c>
+      <c r="C5103" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5104" t="s">
+        <v>10306</v>
+      </c>
+      <c r="B5104" t="s">
+        <v>10307</v>
+      </c>
+      <c r="C5104" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5105" t="s">
+        <v>10308</v>
+      </c>
+      <c r="B5105" t="s">
+        <v>10309</v>
+      </c>
+      <c r="C5105" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5106" t="s">
+        <v>10310</v>
+      </c>
+      <c r="B5106" t="s">
+        <v>10311</v>
+      </c>
+      <c r="C5106" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5107" t="s">
+        <v>10312</v>
+      </c>
+      <c r="B5107" t="s">
+        <v>10313</v>
+      </c>
+      <c r="C5107" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5108" t="s">
+        <v>10314</v>
+      </c>
+      <c r="B5108" t="s">
+        <v>10315</v>
+      </c>
+      <c r="C5108" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5109" t="s">
+        <v>10316</v>
+      </c>
+      <c r="B5109" t="s">
+        <v>10317</v>
+      </c>
+      <c r="C5109" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5110" t="s">
+        <v>10318</v>
+      </c>
+      <c r="B5110" t="s">
+        <v>10319</v>
+      </c>
+      <c r="C5110" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5111" t="s">
+        <v>10320</v>
+      </c>
+      <c r="B5111" t="s">
+        <v>10321</v>
+      </c>
+      <c r="C5111" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5112" t="s">
+        <v>10322</v>
+      </c>
+      <c r="B5112" t="s">
+        <v>10323</v>
+      </c>
+      <c r="C5112" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5113" t="s">
+        <v>10324</v>
+      </c>
+      <c r="B5113" t="s">
+        <v>10325</v>
+      </c>
+      <c r="C5113" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5114" t="s">
+        <v>10326</v>
+      </c>
+      <c r="B5114" t="s">
+        <v>10327</v>
+      </c>
+      <c r="C5114" t="s">
+        <v>10283</v>
+      </c>
+    </row>
+    <row r="5115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5115" t="s">
+        <v>10328</v>
+      </c>
+      <c r="B5115" t="s">
+        <v>10329</v>
+      </c>
+      <c r="C5115" t="s">
+        <v>10283</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13839" uniqueCount="10330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14046" uniqueCount="10469">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -31007,6 +31007,423 @@
   </si>
   <si>
     <t>Наволочка жатка 60х60 - "Ледяной Мрамор"</t>
+  </si>
+  <si>
+    <t>4681001622109</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 220х240 - "Котик в космосе"</t>
+  </si>
+  <si>
+    <t>13-06-2026</t>
+  </si>
+  <si>
+    <t>4681001622093</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х50 - "Айсу"</t>
+  </si>
+  <si>
+    <t>4681001622086</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х20 - "Румянец"</t>
+  </si>
+  <si>
+    <t>4681001622079</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - 142 - Спящий Мишка на зеленом</t>
+  </si>
+  <si>
+    <t>4681001622062</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х60 - 142 - Оранжевый</t>
+  </si>
+  <si>
+    <t>4681001622055</t>
+  </si>
+  <si>
+    <t>Простыня бязь 200х220 - 120 - Северные Волки</t>
+  </si>
+  <si>
+    <t>4681001622048</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - "Аргис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622031</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Эбру"</t>
+  </si>
+  <si>
+    <t>4681001622024</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 60х60 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001622017</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро - Гуава</t>
+  </si>
+  <si>
+    <t>4681001622000</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное резинка 140х200х30 - "Бирюзовый Рельеф" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621997</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Лесная Мелодия"</t>
+  </si>
+  <si>
+    <t>4681001621980</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное - "Кетеван" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621973</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 220х240 - Премиум ТС 320 Бесконечность</t>
+  </si>
+  <si>
+    <t>4681001621966</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 140х200х30 - Премиум ТС 320 "Юсан"</t>
+  </si>
+  <si>
+    <t>4681001621959</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 140х200х30 - "Харис"</t>
+  </si>
+  <si>
+    <t>4681001621942</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин семейное резинка 180х200х30 - "Лавандис" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621935</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - "Ягуар" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621928</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро резинка 160х200х30 - "Вилайн" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621911</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Ажур" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621904</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 80х200х20 - "Эдже"</t>
+  </si>
+  <si>
+    <t>4681001621898</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 50х70 - "Просперо"</t>
+  </si>
+  <si>
+    <t>4681001621881</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное - "Экзотический" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621874</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное - "Нефритовый"</t>
+  </si>
+  <si>
+    <t>4681001621867</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное Евро простыня - 142 - Монстера на коричневом</t>
+  </si>
+  <si>
+    <t>4681001621850</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное - "Морозный туман" Универсал</t>
+  </si>
+  <si>
+    <t>4681001621843</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 90х200х30 - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001621836</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 140х200х30 - Графит (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621829</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4681001621812</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 180х200х30 - 140 - Белый Люкс 3х3</t>
+  </si>
+  <si>
+    <t>4681001621805</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - "Розовый Флёр"</t>
+  </si>
+  <si>
+    <t>4681001621799</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное - Премиум ТС 320 Вишенка наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621782</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - 4235 Темно-синий</t>
+  </si>
+  <si>
+    <t>4681001621775</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - Малахит</t>
+  </si>
+  <si>
+    <t>4681001621768</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Эрос"</t>
+  </si>
+  <si>
+    <t>4681001621751</t>
+  </si>
+  <si>
+    <t>Простыня жатка 150х220 - "Ледяной Мрамор"</t>
+  </si>
+  <si>
+    <t>4681001621744</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное - "Цветы в Тумане" Универсал</t>
+  </si>
+  <si>
+    <t>4681001621737</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное на резинке 140х200х30 - М - 120 - Чёрный мрамор</t>
+  </si>
+  <si>
+    <t>4681001621720</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - "Интерстеллар"</t>
+  </si>
+  <si>
+    <t>4681001621713</t>
+  </si>
+  <si>
+    <t>Простыня круглая жатка резинка 210х210х30 - "Фиолетовый Шёпот"</t>
+  </si>
+  <si>
+    <t>4681001621706</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - 4234 Морская нимфа наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621690</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси резинка 180х200х30 - 74 Оливковый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621683</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - Серая умбра</t>
+  </si>
+  <si>
+    <t>4681001621676</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 125 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001621669</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 125 - "Миндаль" 1х1</t>
+  </si>
+  <si>
+    <t>4681001621652</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 125 - Шашки Шампань 0,5х0,5</t>
+  </si>
+  <si>
+    <t>4681001621645</t>
+  </si>
+  <si>
+    <t>Простыня из страйп микрофибры 200 х 220 - М - 85 - Белая 1х1</t>
+  </si>
+  <si>
+    <t>4681001621638</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 2 спальное Евро простыня - "Симоне" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621621</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Стиллит" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621614</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 140х200х30 - "Инспайр"</t>
+  </si>
+  <si>
+    <t>4681001621607</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро-макси - 130 - "Летний дождь" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621591</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - Альбертус</t>
+  </si>
+  <si>
+    <t>4681001621584</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин Евро резинка 160х200х30 - 125 - Черный 1х1</t>
+  </si>
+  <si>
+    <t>4681001621577</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 180х220 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001621560</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х30 - "Сентори"</t>
+  </si>
+  <si>
+    <t>4681001621553</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х20 - "Асунсьон"</t>
+  </si>
+  <si>
+    <t>4681001621546</t>
+  </si>
+  <si>
+    <t>Гобеленовая наволочка 40х40 - М - JF-344</t>
+  </si>
+  <si>
+    <t>4681001621539</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное - "Цветочный Шарм" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621522</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро резинка 160х200х30 - "Ягуар" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621515</t>
+  </si>
+  <si>
+    <t>Простыня бязь резинка 180х200х30 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001621508</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - Малахит</t>
+  </si>
+  <si>
+    <t>4681001621492</t>
+  </si>
+  <si>
+    <t>Простыня круглая микрофибра резинка 200х200х40 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001621485</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Млада"</t>
+  </si>
+  <si>
+    <t>4681001621478</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 200х200 - Гуава</t>
+  </si>
+  <si>
+    <t>4681001621461</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - 142 - Зверята на желтом</t>
+  </si>
+  <si>
+    <t>4681001621454</t>
+  </si>
+  <si>
+    <t>Простыня круглая страйп-сатин резинка 220х220х30 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001621447</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 2 спальное резинка 140х200х30 - "Залив" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001621430</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 140х200х30 - "Камара"</t>
+  </si>
+  <si>
+    <t>4681001621423</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 120х200х30 - "Вишня" (меланж) наволочки 50х70</t>
   </si>
 </sst>
 </file>
@@ -83135,6 +83552,765 @@
         <v>10283</v>
       </c>
     </row>
+    <row r="5116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5116" t="s">
+        <v>10330</v>
+      </c>
+      <c r="B5116" t="s">
+        <v>10331</v>
+      </c>
+      <c r="C5116" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5117" t="s">
+        <v>10333</v>
+      </c>
+      <c r="B5117" t="s">
+        <v>10334</v>
+      </c>
+      <c r="C5117" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5118" t="s">
+        <v>10335</v>
+      </c>
+      <c r="B5118" t="s">
+        <v>10336</v>
+      </c>
+      <c r="C5118" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5119" t="s">
+        <v>10337</v>
+      </c>
+      <c r="B5119" t="s">
+        <v>10338</v>
+      </c>
+      <c r="C5119" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5120" t="s">
+        <v>10339</v>
+      </c>
+      <c r="B5120" t="s">
+        <v>10340</v>
+      </c>
+      <c r="C5120" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5121" t="s">
+        <v>10341</v>
+      </c>
+      <c r="B5121" t="s">
+        <v>10342</v>
+      </c>
+      <c r="C5121" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5122" t="s">
+        <v>10343</v>
+      </c>
+      <c r="B5122" t="s">
+        <v>10344</v>
+      </c>
+      <c r="C5122" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5123" t="s">
+        <v>10345</v>
+      </c>
+      <c r="B5123" t="s">
+        <v>10346</v>
+      </c>
+      <c r="C5123" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5124" t="s">
+        <v>10347</v>
+      </c>
+      <c r="B5124" t="s">
+        <v>10348</v>
+      </c>
+      <c r="C5124" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5125" t="s">
+        <v>10349</v>
+      </c>
+      <c r="B5125" t="s">
+        <v>10350</v>
+      </c>
+      <c r="C5125" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5126" t="s">
+        <v>10351</v>
+      </c>
+      <c r="B5126" t="s">
+        <v>10352</v>
+      </c>
+      <c r="C5126" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5127" t="s">
+        <v>10353</v>
+      </c>
+      <c r="B5127" t="s">
+        <v>10354</v>
+      </c>
+      <c r="C5127" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5128" t="s">
+        <v>10355</v>
+      </c>
+      <c r="B5128" t="s">
+        <v>10356</v>
+      </c>
+      <c r="C5128" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5129" t="s">
+        <v>10357</v>
+      </c>
+      <c r="B5129" t="s">
+        <v>10358</v>
+      </c>
+      <c r="C5129" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5130" t="s">
+        <v>10359</v>
+      </c>
+      <c r="B5130" t="s">
+        <v>10360</v>
+      </c>
+      <c r="C5130" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5131" t="s">
+        <v>10361</v>
+      </c>
+      <c r="B5131" t="s">
+        <v>10362</v>
+      </c>
+      <c r="C5131" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5132" t="s">
+        <v>10363</v>
+      </c>
+      <c r="B5132" t="s">
+        <v>10364</v>
+      </c>
+      <c r="C5132" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5133" t="s">
+        <v>10365</v>
+      </c>
+      <c r="B5133" t="s">
+        <v>10366</v>
+      </c>
+      <c r="C5133" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5134" t="s">
+        <v>10367</v>
+      </c>
+      <c r="B5134" t="s">
+        <v>10368</v>
+      </c>
+      <c r="C5134" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5135" t="s">
+        <v>10369</v>
+      </c>
+      <c r="B5135" t="s">
+        <v>10370</v>
+      </c>
+      <c r="C5135" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5136" t="s">
+        <v>10371</v>
+      </c>
+      <c r="B5136" t="s">
+        <v>10372</v>
+      </c>
+      <c r="C5136" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5137" t="s">
+        <v>10373</v>
+      </c>
+      <c r="B5137" t="s">
+        <v>10374</v>
+      </c>
+      <c r="C5137" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5138" t="s">
+        <v>10375</v>
+      </c>
+      <c r="B5138" t="s">
+        <v>10376</v>
+      </c>
+      <c r="C5138" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5139" t="s">
+        <v>10377</v>
+      </c>
+      <c r="B5139" t="s">
+        <v>10378</v>
+      </c>
+      <c r="C5139" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5140" t="s">
+        <v>10379</v>
+      </c>
+      <c r="B5140" t="s">
+        <v>10380</v>
+      </c>
+      <c r="C5140" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5141" t="s">
+        <v>10381</v>
+      </c>
+      <c r="B5141" t="s">
+        <v>10382</v>
+      </c>
+      <c r="C5141" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5142" t="s">
+        <v>10383</v>
+      </c>
+      <c r="B5142" t="s">
+        <v>10384</v>
+      </c>
+      <c r="C5142" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5143" t="s">
+        <v>10385</v>
+      </c>
+      <c r="B5143" t="s">
+        <v>10386</v>
+      </c>
+      <c r="C5143" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5144" t="s">
+        <v>10387</v>
+      </c>
+      <c r="B5144" t="s">
+        <v>10388</v>
+      </c>
+      <c r="C5144" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5145" t="s">
+        <v>10389</v>
+      </c>
+      <c r="B5145" t="s">
+        <v>10390</v>
+      </c>
+      <c r="C5145" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5146" t="s">
+        <v>10391</v>
+      </c>
+      <c r="B5146" t="s">
+        <v>10392</v>
+      </c>
+      <c r="C5146" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5147" t="s">
+        <v>10393</v>
+      </c>
+      <c r="B5147" t="s">
+        <v>10394</v>
+      </c>
+      <c r="C5147" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5148" t="s">
+        <v>10395</v>
+      </c>
+      <c r="B5148" t="s">
+        <v>10396</v>
+      </c>
+      <c r="C5148" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5149" t="s">
+        <v>10397</v>
+      </c>
+      <c r="B5149" t="s">
+        <v>10398</v>
+      </c>
+      <c r="C5149" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5150" t="s">
+        <v>10399</v>
+      </c>
+      <c r="B5150" t="s">
+        <v>10400</v>
+      </c>
+      <c r="C5150" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5151" t="s">
+        <v>10401</v>
+      </c>
+      <c r="B5151" t="s">
+        <v>10402</v>
+      </c>
+      <c r="C5151" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5152" t="s">
+        <v>10403</v>
+      </c>
+      <c r="B5152" t="s">
+        <v>10404</v>
+      </c>
+      <c r="C5152" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5153" t="s">
+        <v>10405</v>
+      </c>
+      <c r="B5153" t="s">
+        <v>10406</v>
+      </c>
+      <c r="C5153" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5154" t="s">
+        <v>10407</v>
+      </c>
+      <c r="B5154" t="s">
+        <v>10408</v>
+      </c>
+      <c r="C5154" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5155" t="s">
+        <v>10409</v>
+      </c>
+      <c r="B5155" t="s">
+        <v>10410</v>
+      </c>
+      <c r="C5155" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5156" t="s">
+        <v>10411</v>
+      </c>
+      <c r="B5156" t="s">
+        <v>10412</v>
+      </c>
+      <c r="C5156" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5157" t="s">
+        <v>10413</v>
+      </c>
+      <c r="B5157" t="s">
+        <v>10414</v>
+      </c>
+      <c r="C5157" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5158" t="s">
+        <v>10415</v>
+      </c>
+      <c r="B5158" t="s">
+        <v>10416</v>
+      </c>
+      <c r="C5158" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5159" t="s">
+        <v>10417</v>
+      </c>
+      <c r="B5159" t="s">
+        <v>10418</v>
+      </c>
+      <c r="C5159" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5160" t="s">
+        <v>10419</v>
+      </c>
+      <c r="B5160" t="s">
+        <v>10420</v>
+      </c>
+      <c r="C5160" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5161" t="s">
+        <v>10421</v>
+      </c>
+      <c r="B5161" t="s">
+        <v>10422</v>
+      </c>
+      <c r="C5161" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5162" t="s">
+        <v>10423</v>
+      </c>
+      <c r="B5162" t="s">
+        <v>10424</v>
+      </c>
+      <c r="C5162" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5163" t="s">
+        <v>10425</v>
+      </c>
+      <c r="B5163" t="s">
+        <v>10426</v>
+      </c>
+      <c r="C5163" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5164" t="s">
+        <v>10427</v>
+      </c>
+      <c r="B5164" t="s">
+        <v>10428</v>
+      </c>
+      <c r="C5164" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5165" t="s">
+        <v>10429</v>
+      </c>
+      <c r="B5165" t="s">
+        <v>10430</v>
+      </c>
+      <c r="C5165" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5166" t="s">
+        <v>10431</v>
+      </c>
+      <c r="B5166" t="s">
+        <v>10432</v>
+      </c>
+      <c r="C5166" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5167" t="s">
+        <v>10433</v>
+      </c>
+      <c r="B5167" t="s">
+        <v>10434</v>
+      </c>
+      <c r="C5167" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5168" t="s">
+        <v>10435</v>
+      </c>
+      <c r="B5168" t="s">
+        <v>10436</v>
+      </c>
+      <c r="C5168" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5169" t="s">
+        <v>10437</v>
+      </c>
+      <c r="B5169" t="s">
+        <v>10438</v>
+      </c>
+      <c r="C5169" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5170" t="s">
+        <v>10439</v>
+      </c>
+      <c r="B5170" t="s">
+        <v>10440</v>
+      </c>
+      <c r="C5170" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5171" t="s">
+        <v>10441</v>
+      </c>
+      <c r="B5171" t="s">
+        <v>10442</v>
+      </c>
+      <c r="C5171" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5172" t="s">
+        <v>10443</v>
+      </c>
+      <c r="B5172" t="s">
+        <v>10444</v>
+      </c>
+      <c r="C5172" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5173" t="s">
+        <v>10445</v>
+      </c>
+      <c r="B5173" t="s">
+        <v>10446</v>
+      </c>
+      <c r="C5173" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5174" t="s">
+        <v>10447</v>
+      </c>
+      <c r="B5174" t="s">
+        <v>10448</v>
+      </c>
+      <c r="C5174" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5175" t="s">
+        <v>10449</v>
+      </c>
+      <c r="B5175" t="s">
+        <v>10450</v>
+      </c>
+      <c r="C5175" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5176" t="s">
+        <v>10451</v>
+      </c>
+      <c r="B5176" t="s">
+        <v>10452</v>
+      </c>
+      <c r="C5176" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5177" t="s">
+        <v>10453</v>
+      </c>
+      <c r="B5177" t="s">
+        <v>10454</v>
+      </c>
+      <c r="C5177" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5178" t="s">
+        <v>10455</v>
+      </c>
+      <c r="B5178" t="s">
+        <v>10456</v>
+      </c>
+      <c r="C5178" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5179" t="s">
+        <v>10457</v>
+      </c>
+      <c r="B5179" t="s">
+        <v>10458</v>
+      </c>
+      <c r="C5179" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5180" t="s">
+        <v>10459</v>
+      </c>
+      <c r="B5180" t="s">
+        <v>10460</v>
+      </c>
+      <c r="C5180" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5181" t="s">
+        <v>10461</v>
+      </c>
+      <c r="B5181" t="s">
+        <v>10462</v>
+      </c>
+      <c r="C5181" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5182" t="s">
+        <v>10463</v>
+      </c>
+      <c r="B5182" t="s">
+        <v>10464</v>
+      </c>
+      <c r="C5182" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5183" t="s">
+        <v>10465</v>
+      </c>
+      <c r="B5183" t="s">
+        <v>10466</v>
+      </c>
+      <c r="C5183" t="s">
+        <v>10332</v>
+      </c>
+    </row>
+    <row r="5184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5184" t="s">
+        <v>10467</v>
+      </c>
+      <c r="B5184" t="s">
+        <v>10468</v>
+      </c>
+      <c r="C5184" t="s">
+        <v>10332</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14046" uniqueCount="10469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14145" uniqueCount="10536">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -31424,6 +31424,207 @@
   </si>
   <si>
     <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 120х200х30 - "Вишня" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622437</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 300х300 - Серо-зелёный</t>
+  </si>
+  <si>
+    <t>14-06-2026</t>
+  </si>
+  <si>
+    <t>4681001622420</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 60х60 - "Элория"</t>
+  </si>
+  <si>
+    <t>4681001622413</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - Кончерто гроссо</t>
+  </si>
+  <si>
+    <t>4681001622406</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 60х60 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001622390</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 60х60 - 142 - Сиреневый</t>
+  </si>
+  <si>
+    <t>4681001622383</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 60х60 - 4323 Бежево-розовый</t>
+  </si>
+  <si>
+    <t>4681001622376</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 60х60 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4681001622369</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 40х40 - "Джуман"</t>
+  </si>
+  <si>
+    <t>4681001622352</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро-макси - 125 - Паслен А+В наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622345</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - 125 - "Шоколад" 1х1 1</t>
+  </si>
+  <si>
+    <t>4681001622338</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - "Туманная Ветвь" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622321</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Бирюзовый берег</t>
+  </si>
+  <si>
+    <t>4681001622314</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 280х280 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001622307</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 150х220 - "Легкий роман"</t>
+  </si>
+  <si>
+    <t>4681001622291</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 90х200х30 - "Милда" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622284</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - Серая умбра</t>
+  </si>
+  <si>
+    <t>4681001622277</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Бейж"</t>
+  </si>
+  <si>
+    <t>4681001622260</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 120х200х30 - "Ночная Симфония" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622253</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное на резинке 120х200х30 - "Потягуш" с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001622246</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - 120 - Панно</t>
+  </si>
+  <si>
+    <t>4681001622239</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 280х280 - "Аделаида"</t>
+  </si>
+  <si>
+    <t>4681001622222</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 145х215 - "Мирелле"</t>
+  </si>
+  <si>
+    <t>4681001622215</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок King Size семейное резинка 200х200х30 - Графит (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622208</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин King Size резинка 200х200х30 - "Бриолен" 1х1</t>
+  </si>
+  <si>
+    <t>4681001622192</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное - "Сиренево-розовый" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622185</t>
+  </si>
+  <si>
+    <t>Простыня микрофибра 240х260 - "Альбелла" 1х1</t>
+  </si>
+  <si>
+    <t>4681001622178</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х40 - Сарсуэла</t>
+  </si>
+  <si>
+    <t>4681001622161</t>
+  </si>
+  <si>
+    <t>Наволочка ранфорс 40х40 - "Лазурный бриз"</t>
+  </si>
+  <si>
+    <t>4681001622154</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - Горчица</t>
+  </si>
+  <si>
+    <t>4681001622147</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Тонкий Лист"</t>
+  </si>
+  <si>
+    <t>4681001622130</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Туманная Ветвь"</t>
+  </si>
+  <si>
+    <t>4681001622123</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001622116</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 140 - Сирень 1х1</t>
   </si>
 </sst>
 </file>
@@ -84311,6 +84512,369 @@
         <v>10332</v>
       </c>
     </row>
+    <row r="5185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5185" t="s">
+        <v>10469</v>
+      </c>
+      <c r="B5185" t="s">
+        <v>10470</v>
+      </c>
+      <c r="C5185" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5186" t="s">
+        <v>10472</v>
+      </c>
+      <c r="B5186" t="s">
+        <v>10473</v>
+      </c>
+      <c r="C5186" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5187" t="s">
+        <v>10474</v>
+      </c>
+      <c r="B5187" t="s">
+        <v>10475</v>
+      </c>
+      <c r="C5187" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5188" t="s">
+        <v>10476</v>
+      </c>
+      <c r="B5188" t="s">
+        <v>10477</v>
+      </c>
+      <c r="C5188" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5189" t="s">
+        <v>10478</v>
+      </c>
+      <c r="B5189" t="s">
+        <v>10479</v>
+      </c>
+      <c r="C5189" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5190" t="s">
+        <v>10480</v>
+      </c>
+      <c r="B5190" t="s">
+        <v>10481</v>
+      </c>
+      <c r="C5190" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5191" t="s">
+        <v>10482</v>
+      </c>
+      <c r="B5191" t="s">
+        <v>10483</v>
+      </c>
+      <c r="C5191" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5192" t="s">
+        <v>10484</v>
+      </c>
+      <c r="B5192" t="s">
+        <v>10485</v>
+      </c>
+      <c r="C5192" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5193" t="s">
+        <v>10486</v>
+      </c>
+      <c r="B5193" t="s">
+        <v>10487</v>
+      </c>
+      <c r="C5193" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5194" t="s">
+        <v>10488</v>
+      </c>
+      <c r="B5194" t="s">
+        <v>10489</v>
+      </c>
+      <c r="C5194" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5195" t="s">
+        <v>10490</v>
+      </c>
+      <c r="B5195" t="s">
+        <v>10491</v>
+      </c>
+      <c r="C5195" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5196" t="s">
+        <v>10492</v>
+      </c>
+      <c r="B5196" t="s">
+        <v>10493</v>
+      </c>
+      <c r="C5196" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5197" t="s">
+        <v>10494</v>
+      </c>
+      <c r="B5197" t="s">
+        <v>10495</v>
+      </c>
+      <c r="C5197" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5198" t="s">
+        <v>10496</v>
+      </c>
+      <c r="B5198" t="s">
+        <v>10497</v>
+      </c>
+      <c r="C5198" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5199" t="s">
+        <v>10498</v>
+      </c>
+      <c r="B5199" t="s">
+        <v>10499</v>
+      </c>
+      <c r="C5199" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5200" t="s">
+        <v>10500</v>
+      </c>
+      <c r="B5200" t="s">
+        <v>10501</v>
+      </c>
+      <c r="C5200" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5201" t="s">
+        <v>10502</v>
+      </c>
+      <c r="B5201" t="s">
+        <v>10503</v>
+      </c>
+      <c r="C5201" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5202" t="s">
+        <v>10504</v>
+      </c>
+      <c r="B5202" t="s">
+        <v>10505</v>
+      </c>
+      <c r="C5202" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5203" t="s">
+        <v>10506</v>
+      </c>
+      <c r="B5203" t="s">
+        <v>10507</v>
+      </c>
+      <c r="C5203" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5204" t="s">
+        <v>10508</v>
+      </c>
+      <c r="B5204" t="s">
+        <v>10509</v>
+      </c>
+      <c r="C5204" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5205" t="s">
+        <v>10510</v>
+      </c>
+      <c r="B5205" t="s">
+        <v>10511</v>
+      </c>
+      <c r="C5205" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5206" t="s">
+        <v>10512</v>
+      </c>
+      <c r="B5206" t="s">
+        <v>10513</v>
+      </c>
+      <c r="C5206" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5207" t="s">
+        <v>10514</v>
+      </c>
+      <c r="B5207" t="s">
+        <v>10515</v>
+      </c>
+      <c r="C5207" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5208" t="s">
+        <v>10516</v>
+      </c>
+      <c r="B5208" t="s">
+        <v>10517</v>
+      </c>
+      <c r="C5208" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5209" t="s">
+        <v>10518</v>
+      </c>
+      <c r="B5209" t="s">
+        <v>10519</v>
+      </c>
+      <c r="C5209" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5210" t="s">
+        <v>10520</v>
+      </c>
+      <c r="B5210" t="s">
+        <v>10521</v>
+      </c>
+      <c r="C5210" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5211" t="s">
+        <v>10522</v>
+      </c>
+      <c r="B5211" t="s">
+        <v>10523</v>
+      </c>
+      <c r="C5211" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5212" t="s">
+        <v>10524</v>
+      </c>
+      <c r="B5212" t="s">
+        <v>10525</v>
+      </c>
+      <c r="C5212" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5213" t="s">
+        <v>10526</v>
+      </c>
+      <c r="B5213" t="s">
+        <v>10527</v>
+      </c>
+      <c r="C5213" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5214" t="s">
+        <v>10528</v>
+      </c>
+      <c r="B5214" t="s">
+        <v>10529</v>
+      </c>
+      <c r="C5214" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5215" t="s">
+        <v>10530</v>
+      </c>
+      <c r="B5215" t="s">
+        <v>10531</v>
+      </c>
+      <c r="C5215" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5216" t="s">
+        <v>10532</v>
+      </c>
+      <c r="B5216" t="s">
+        <v>10533</v>
+      </c>
+      <c r="C5216" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5217" t="s">
+        <v>10534</v>
+      </c>
+      <c r="B5217" t="s">
+        <v>10535</v>
+      </c>
+      <c r="C5217" t="s">
+        <v>10471</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14145" uniqueCount="10536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14148" uniqueCount="10539">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -31625,6 +31625,15 @@
   </si>
   <si>
     <t>Простыня страйп-сатин 180х220 - 140 - Сирень 1х1</t>
+  </si>
+  <si>
+    <t>4681001622444</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х60 - 125 - "Шоколад" 1х1</t>
+  </si>
+  <si>
+    <t>15-06-2026</t>
   </si>
 </sst>
 </file>
@@ -84875,6 +84884,17 @@
         <v>10471</v>
       </c>
     </row>
+    <row r="5218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5218" t="s">
+        <v>10536</v>
+      </c>
+      <c r="B5218" t="s">
+        <v>10537</v>
+      </c>
+      <c r="C5218" t="s">
+        <v>10538</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C813F082-072E-4261-A382-297D5D3F5FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
+    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14148" uniqueCount="10539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14229" uniqueCount="10593">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -31634,35 +31635,197 @@
   </si>
   <si>
     <t>15-06-2026</t>
+  </si>
+  <si>
+    <t>4681001622710</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 40х60 - "Граса"</t>
+  </si>
+  <si>
+    <t>4681001622703</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 40х60 - "Риннон"</t>
+  </si>
+  <si>
+    <t>4681001622697</t>
+  </si>
+  <si>
+    <t>Простыня из сатина на резинке 160 х 200 х 20 - М - 125 - Дом Периньон</t>
+  </si>
+  <si>
+    <t>4681001622680</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное резинка 90х200х30 - "Серебряный Лес"</t>
+  </si>
+  <si>
+    <t>4681001622673</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 90х200х30 - "Мяурель"</t>
+  </si>
+  <si>
+    <t>4681001622666</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 90х200х30 - Прелат А+В</t>
+  </si>
+  <si>
+    <t>4681001622659</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Илария"</t>
+  </si>
+  <si>
+    <t>4681001622642</t>
+  </si>
+  <si>
+    <t>Простыня бязь 180х220 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001622635</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - "Туманная Ветвь"</t>
+  </si>
+  <si>
+    <t>4681001622628</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Ажур"</t>
+  </si>
+  <si>
+    <t>4681001622611</t>
+  </si>
+  <si>
+    <t>КПБ Постельное белье тенсель семейное - М - 60S 4393 Темно-серый с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001622604</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Млада"</t>
+  </si>
+  <si>
+    <t>4681001622598</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 125 - Аметист 1х1</t>
+  </si>
+  <si>
+    <t>4681001622581</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х30 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001622574</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 120х200х30 - "Лав юселф"</t>
+  </si>
+  <si>
+    <t>4681001622567</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х30 - "Асунсьон"</t>
+  </si>
+  <si>
+    <t>4681001622550</t>
+  </si>
+  <si>
+    <t>Простыня перкаль 150х220 - "Чёрное масло"</t>
+  </si>
+  <si>
+    <t>4681001622543</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 40х40 - 130 - Мятный фреш 1х1</t>
+  </si>
+  <si>
+    <t>4681001622536</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 70х70 - "Юки" 1х1</t>
+  </si>
+  <si>
+    <t>4681001622529</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х70 - "Вилайн" 1х1</t>
+  </si>
+  <si>
+    <t>4681001622512</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - Розовая лаванда</t>
+  </si>
+  <si>
+    <t>4681001622505</t>
+  </si>
+  <si>
+    <t>Пододеяльник бязь 145х215 - 125 - Звездный Мишка на голубом</t>
+  </si>
+  <si>
+    <t>4681001622499</t>
+  </si>
+  <si>
+    <t>Простыня из бязи на резинке 90 х 200 х 20 - М - 125 - Звездный Мишка на голубом</t>
+  </si>
+  <si>
+    <t>4681001622482</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 50х50 - 125 - Звездный Мишка на голубом</t>
+  </si>
+  <si>
+    <t>4681001622475</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш 220х240 - Лайлак</t>
+  </si>
+  <si>
+    <t>4681001622468</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное - Нежно-розовый наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622451</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 160х200х30 - "Эвергрин"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -31688,10 +31851,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -31715,7 +31886,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -31992,9 +32163,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
@@ -32002,13 +32173,13 @@
     <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -32037,7 +32208,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -32045,7 +32216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -32053,7 +32224,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -32061,7 +32232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -32069,7 +32240,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -32077,7 +32248,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -32085,7 +32256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -32093,7 +32264,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -32101,7 +32272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -32109,7 +32280,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -32117,7 +32288,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -32125,7 +32296,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -43909,7 +44080,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -43917,7 +44088,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -43925,7 +44096,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -43933,7 +44104,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -43941,7 +44112,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -43949,7 +44120,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -43957,7 +44128,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -43965,7 +44136,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -43973,7 +44144,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -43981,7 +44152,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -43989,7 +44160,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -43997,7 +44168,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -44005,7 +44176,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -44013,7 +44184,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -44021,7 +44192,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -81176,7 +81347,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4881" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4881" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4881" t="s">
         <v>9852</v>
       </c>
@@ -81187,7 +81358,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4882" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4882" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4882" t="s">
         <v>9854</v>
       </c>
@@ -81198,7 +81369,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4883" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4883" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4883" t="s">
         <v>9856</v>
       </c>
@@ -81209,7 +81380,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4884" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4884" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4884" t="s">
         <v>9858</v>
       </c>
@@ -81220,7 +81391,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4885" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4885" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4885" t="s">
         <v>9860</v>
       </c>
@@ -81231,7 +81402,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4886" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4886" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4886" t="s">
         <v>9862</v>
       </c>
@@ -81242,7 +81413,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4887" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4887" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4887" t="s">
         <v>9864</v>
       </c>
@@ -81253,7 +81424,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4888" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4888" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4888" t="s">
         <v>9866</v>
       </c>
@@ -81264,7 +81435,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4889" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4889" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4889" t="s">
         <v>9868</v>
       </c>
@@ -81287,7 +81458,7 @@
       </c>
       <c r="G4890" s="7"/>
     </row>
-    <row r="4891" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4891" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4891" t="s">
         <v>9872</v>
       </c>
@@ -81298,7 +81469,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4892" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4892" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4892" t="s">
         <v>9874</v>
       </c>
@@ -81309,7 +81480,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4893" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4893" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4893" t="s">
         <v>9877</v>
       </c>
@@ -81320,7 +81491,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4894" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4894" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4894" t="s">
         <v>9879</v>
       </c>
@@ -81331,7 +81502,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4895" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4895" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4895" t="s">
         <v>9881</v>
       </c>
@@ -81342,7 +81513,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4896" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4896" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4896" t="s">
         <v>9883</v>
       </c>
@@ -84892,6 +85063,303 @@
         <v>10537</v>
       </c>
       <c r="C5218" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5219" t="s">
+        <v>10539</v>
+      </c>
+      <c r="B5219" t="s">
+        <v>10540</v>
+      </c>
+      <c r="C5219" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5220" t="s">
+        <v>10541</v>
+      </c>
+      <c r="B5220" t="s">
+        <v>10542</v>
+      </c>
+      <c r="C5220" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5221" t="s">
+        <v>10543</v>
+      </c>
+      <c r="B5221" t="s">
+        <v>10544</v>
+      </c>
+      <c r="C5221" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5222" t="s">
+        <v>10545</v>
+      </c>
+      <c r="B5222" t="s">
+        <v>10546</v>
+      </c>
+      <c r="C5222" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5223" t="s">
+        <v>10547</v>
+      </c>
+      <c r="B5223" t="s">
+        <v>10548</v>
+      </c>
+      <c r="C5223" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5224" t="s">
+        <v>10549</v>
+      </c>
+      <c r="B5224" t="s">
+        <v>10550</v>
+      </c>
+      <c r="C5224" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5225" t="s">
+        <v>10551</v>
+      </c>
+      <c r="B5225" t="s">
+        <v>10552</v>
+      </c>
+      <c r="C5225" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5226" t="s">
+        <v>10553</v>
+      </c>
+      <c r="B5226" t="s">
+        <v>10554</v>
+      </c>
+      <c r="C5226" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5227" t="s">
+        <v>10555</v>
+      </c>
+      <c r="B5227" t="s">
+        <v>10556</v>
+      </c>
+      <c r="C5227" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5228" t="s">
+        <v>10557</v>
+      </c>
+      <c r="B5228" t="s">
+        <v>10558</v>
+      </c>
+      <c r="C5228" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5229" t="s">
+        <v>10559</v>
+      </c>
+      <c r="B5229" t="s">
+        <v>10560</v>
+      </c>
+      <c r="C5229" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5230" t="s">
+        <v>10561</v>
+      </c>
+      <c r="B5230" t="s">
+        <v>10562</v>
+      </c>
+      <c r="C5230" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5231" t="s">
+        <v>10563</v>
+      </c>
+      <c r="B5231" t="s">
+        <v>10564</v>
+      </c>
+      <c r="C5231" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5232" t="s">
+        <v>10565</v>
+      </c>
+      <c r="B5232" t="s">
+        <v>10566</v>
+      </c>
+      <c r="C5232" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5233" t="s">
+        <v>10567</v>
+      </c>
+      <c r="B5233" t="s">
+        <v>10568</v>
+      </c>
+      <c r="C5233" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5234" t="s">
+        <v>10569</v>
+      </c>
+      <c r="B5234" t="s">
+        <v>10570</v>
+      </c>
+      <c r="C5234" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5235" t="s">
+        <v>10571</v>
+      </c>
+      <c r="B5235" t="s">
+        <v>10572</v>
+      </c>
+      <c r="C5235" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5236" t="s">
+        <v>10573</v>
+      </c>
+      <c r="B5236" t="s">
+        <v>10574</v>
+      </c>
+      <c r="C5236" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5237" t="s">
+        <v>10575</v>
+      </c>
+      <c r="B5237" t="s">
+        <v>10576</v>
+      </c>
+      <c r="C5237" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5238" t="s">
+        <v>10577</v>
+      </c>
+      <c r="B5238" t="s">
+        <v>10578</v>
+      </c>
+      <c r="C5238" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5239" t="s">
+        <v>10579</v>
+      </c>
+      <c r="B5239" t="s">
+        <v>10580</v>
+      </c>
+      <c r="C5239" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5240" t="s">
+        <v>10581</v>
+      </c>
+      <c r="B5240" t="s">
+        <v>10582</v>
+      </c>
+      <c r="C5240" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5241" t="s">
+        <v>10583</v>
+      </c>
+      <c r="B5241" t="s">
+        <v>10584</v>
+      </c>
+      <c r="C5241" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5242" t="s">
+        <v>10585</v>
+      </c>
+      <c r="B5242" t="s">
+        <v>10586</v>
+      </c>
+      <c r="C5242" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5243" t="s">
+        <v>10587</v>
+      </c>
+      <c r="B5243" t="s">
+        <v>10588</v>
+      </c>
+      <c r="C5243" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5244" t="s">
+        <v>10589</v>
+      </c>
+      <c r="B5244" t="s">
+        <v>10590</v>
+      </c>
+      <c r="C5244" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="5245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5245" t="s">
+        <v>10591</v>
+      </c>
+      <c r="B5245" t="s">
+        <v>10592</v>
+      </c>
+      <c r="C5245" t="s">
         <v>10538</v>
       </c>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C813F082-072E-4261-A382-297D5D3F5FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Краткий отчет" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Краткий отчет" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Краткий отчет'!$A$4:$C$2979</definedName>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14229" uniqueCount="10593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14301" uniqueCount="10642">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -31797,35 +31796,182 @@
   </si>
   <si>
     <t>Простыня полисатин резинка 160х200х30 - "Эвергрин"</t>
+  </si>
+  <si>
+    <t>4681001622949</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 90х200х30 - Бонди наволочки 50х70</t>
+  </si>
+  <si>
+    <t>16-06-2026</t>
+  </si>
+  <si>
+    <t>4681001622932</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х30 - Мазарин блу</t>
+  </si>
+  <si>
+    <t>4681001622925</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - 125 - Марсала</t>
+  </si>
+  <si>
+    <t>4681001622918</t>
+  </si>
+  <si>
+    <t>Пододеяльник микросатин 175х215 - "Небосвод"</t>
+  </si>
+  <si>
+    <t>4681001622901</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 180х200х20 - "Дюраль"</t>
+  </si>
+  <si>
+    <t>4681001622895</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - "Дюраль"</t>
+  </si>
+  <si>
+    <t>4681001622888</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х60 - "Лигурия"</t>
+  </si>
+  <si>
+    <t>4681001622871</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 40х60 - "Нефритовый"</t>
+  </si>
+  <si>
+    <t>4681001622864</t>
+  </si>
+  <si>
+    <t>Простыня Жатка на резинке 200х200х40 - "Файза"</t>
+  </si>
+  <si>
+    <t>4681001622857</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное резинка 160х200х20 - "Вэспер" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622840</t>
+  </si>
+  <si>
+    <t>Простыня жаккард резинка 120х200х40 - Снежное королевство</t>
+  </si>
+  <si>
+    <t>4681001622833</t>
+  </si>
+  <si>
+    <t>Простыня полисатин на резинке 180х200х30 - "Богумила"</t>
+  </si>
+  <si>
+    <t>4681001622826</t>
+  </si>
+  <si>
+    <t>Пододеяльник перкаль 150х200 - "Асуль"</t>
+  </si>
+  <si>
+    <t>4681001622819</t>
+  </si>
+  <si>
+    <t>Пододеяльник из бязи 200 х 220 - М - 125 - Сансет</t>
+  </si>
+  <si>
+    <t>4681001622802</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 60х60 - "Гаспар"</t>
+  </si>
+  <si>
+    <t>4681001622796</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001622789</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х50 - "Асунсьон"</t>
+  </si>
+  <si>
+    <t>4681001622772</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 220х240 - "Асунсьон"</t>
+  </si>
+  <si>
+    <t>4681001622765</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 240х260 - Черный блеск</t>
+  </si>
+  <si>
+    <t>4681001622758</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - "Осенний Сон"</t>
+  </si>
+  <si>
+    <t>4681001622741</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 2 спальное - "Далиян" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001622734</t>
+  </si>
+  <si>
+    <t>Простыня сатин браш резинка 140х200х40 - "Овсяный"</t>
+  </si>
+  <si>
+    <t>4681001622727</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 50х50 - 135 - Лаймкват 1х1</t>
+  </si>
+  <si>
+    <t>4681001622956</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 140х200х30 - 125 - Обсидиан</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -31851,18 +31997,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -31886,7 +32024,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -32163,9 +32301,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P11478"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="124.5703125" customWidth="1"/>
@@ -32173,13 +32311,13 @@
     <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -32208,7 +32346,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -32216,7 +32354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -32224,7 +32362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -32232,7 +32370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -32240,7 +32378,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -32248,7 +32386,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -32256,7 +32394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -32264,7 +32402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -32272,7 +32410,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -32280,7 +32418,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -32288,7 +32426,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -32296,7 +32434,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -44080,7 +44218,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="1489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
         <v>2973</v>
       </c>
@@ -44088,7 +44226,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="1490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
         <v>2975</v>
       </c>
@@ -44096,7 +44234,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="1491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
         <v>2977</v>
       </c>
@@ -44104,7 +44242,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="1492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
         <v>2979</v>
       </c>
@@ -44112,7 +44250,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="1493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
         <v>2981</v>
       </c>
@@ -44120,7 +44258,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="1494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
         <v>2983</v>
       </c>
@@ -44128,7 +44266,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="1495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
         <v>2985</v>
       </c>
@@ -44136,7 +44274,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="1496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
         <v>2987</v>
       </c>
@@ -44144,7 +44282,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="1497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>2989</v>
       </c>
@@ -44152,7 +44290,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="1498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
         <v>2991</v>
       </c>
@@ -44160,7 +44298,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="1499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>2993</v>
       </c>
@@ -44168,7 +44306,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="1500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
         <v>2995</v>
       </c>
@@ -44176,7 +44314,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>2997</v>
       </c>
@@ -44184,7 +44322,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>2999</v>
       </c>
@@ -44192,7 +44330,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>3001</v>
       </c>
@@ -81347,7 +81485,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4881" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4881" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4881" t="s">
         <v>9852</v>
       </c>
@@ -81358,7 +81496,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4882" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4882" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4882" t="s">
         <v>9854</v>
       </c>
@@ -81369,7 +81507,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4883" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4883" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4883" t="s">
         <v>9856</v>
       </c>
@@ -81380,7 +81518,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4884" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4884" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4884" t="s">
         <v>9858</v>
       </c>
@@ -81391,7 +81529,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4885" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4885" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4885" t="s">
         <v>9860</v>
       </c>
@@ -81402,7 +81540,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4886" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4886" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4886" t="s">
         <v>9862</v>
       </c>
@@ -81413,7 +81551,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4887" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4887" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4887" t="s">
         <v>9864</v>
       </c>
@@ -81424,7 +81562,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4888" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4888" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4888" t="s">
         <v>9866</v>
       </c>
@@ -81435,7 +81573,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4889" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4889" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4889" t="s">
         <v>9868</v>
       </c>
@@ -81458,7 +81596,7 @@
       </c>
       <c r="G4890" s="7"/>
     </row>
-    <row r="4891" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4891" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4891" t="s">
         <v>9872</v>
       </c>
@@ -81469,7 +81607,7 @@
         <v>9819</v>
       </c>
     </row>
-    <row r="4892" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4892" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4892" t="s">
         <v>9874</v>
       </c>
@@ -81480,7 +81618,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4893" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4893" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4893" t="s">
         <v>9877</v>
       </c>
@@ -81491,7 +81629,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4894" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4894" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4894" t="s">
         <v>9879</v>
       </c>
@@ -81502,7 +81640,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4895" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4895" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4895" t="s">
         <v>9881</v>
       </c>
@@ -81513,7 +81651,7 @@
         <v>9876</v>
       </c>
     </row>
-    <row r="4896" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4896" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4896" t="s">
         <v>9883</v>
       </c>
@@ -85361,6 +85499,270 @@
       </c>
       <c r="C5245" t="s">
         <v>10538</v>
+      </c>
+    </row>
+    <row r="5246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5246" t="s">
+        <v>10593</v>
+      </c>
+      <c r="B5246" t="s">
+        <v>10594</v>
+      </c>
+      <c r="C5246" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5247" t="s">
+        <v>10596</v>
+      </c>
+      <c r="B5247" t="s">
+        <v>10597</v>
+      </c>
+      <c r="C5247" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5248" t="s">
+        <v>10598</v>
+      </c>
+      <c r="B5248" t="s">
+        <v>10599</v>
+      </c>
+      <c r="C5248" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5249" t="s">
+        <v>10600</v>
+      </c>
+      <c r="B5249" t="s">
+        <v>10601</v>
+      </c>
+      <c r="C5249" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5250" t="s">
+        <v>10602</v>
+      </c>
+      <c r="B5250" t="s">
+        <v>10603</v>
+      </c>
+      <c r="C5250" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5251" t="s">
+        <v>10604</v>
+      </c>
+      <c r="B5251" t="s">
+        <v>10605</v>
+      </c>
+      <c r="C5251" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5252" t="s">
+        <v>10606</v>
+      </c>
+      <c r="B5252" t="s">
+        <v>10607</v>
+      </c>
+      <c r="C5252" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5253" t="s">
+        <v>10608</v>
+      </c>
+      <c r="B5253" t="s">
+        <v>10609</v>
+      </c>
+      <c r="C5253" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5254" t="s">
+        <v>10610</v>
+      </c>
+      <c r="B5254" t="s">
+        <v>10611</v>
+      </c>
+      <c r="C5254" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5255" t="s">
+        <v>10612</v>
+      </c>
+      <c r="B5255" t="s">
+        <v>10613</v>
+      </c>
+      <c r="C5255" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5256" t="s">
+        <v>10614</v>
+      </c>
+      <c r="B5256" t="s">
+        <v>10615</v>
+      </c>
+      <c r="C5256" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5257" t="s">
+        <v>10616</v>
+      </c>
+      <c r="B5257" t="s">
+        <v>10617</v>
+      </c>
+      <c r="C5257" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5258" t="s">
+        <v>10618</v>
+      </c>
+      <c r="B5258" t="s">
+        <v>10619</v>
+      </c>
+      <c r="C5258" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5259" t="s">
+        <v>10620</v>
+      </c>
+      <c r="B5259" t="s">
+        <v>10621</v>
+      </c>
+      <c r="C5259" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5260" t="s">
+        <v>10622</v>
+      </c>
+      <c r="B5260" t="s">
+        <v>10623</v>
+      </c>
+      <c r="C5260" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5261" t="s">
+        <v>10624</v>
+      </c>
+      <c r="B5261" t="s">
+        <v>10625</v>
+      </c>
+      <c r="C5261" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5262" t="s">
+        <v>10626</v>
+      </c>
+      <c r="B5262" t="s">
+        <v>10627</v>
+      </c>
+      <c r="C5262" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5263" t="s">
+        <v>10628</v>
+      </c>
+      <c r="B5263" t="s">
+        <v>10629</v>
+      </c>
+      <c r="C5263" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5264" t="s">
+        <v>10630</v>
+      </c>
+      <c r="B5264" t="s">
+        <v>10631</v>
+      </c>
+      <c r="C5264" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5265" t="s">
+        <v>10632</v>
+      </c>
+      <c r="B5265" t="s">
+        <v>10633</v>
+      </c>
+      <c r="C5265" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5266" t="s">
+        <v>10634</v>
+      </c>
+      <c r="B5266" t="s">
+        <v>10635</v>
+      </c>
+      <c r="C5266" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5267" t="s">
+        <v>10636</v>
+      </c>
+      <c r="B5267" t="s">
+        <v>10637</v>
+      </c>
+      <c r="C5267" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5268" t="s">
+        <v>10638</v>
+      </c>
+      <c r="B5268" t="s">
+        <v>10639</v>
+      </c>
+      <c r="C5268" t="s">
+        <v>10595</v>
+      </c>
+    </row>
+    <row r="5269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5269" t="s">
+        <v>10640</v>
+      </c>
+      <c r="B5269" t="s">
+        <v>10641</v>
+      </c>
+      <c r="C5269" t="s">
+        <v>10595</v>
       </c>
     </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14301" uniqueCount="10642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14373" uniqueCount="10691">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -31943,6 +31943,153 @@
   </si>
   <si>
     <t>КПБ Постельное бельё сатин 1,5 спальное резинка 140х200х30 - 125 - Обсидиан</t>
+  </si>
+  <si>
+    <t>4681001623199</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 300х300 - "Синтера" 1х1</t>
+  </si>
+  <si>
+    <t>17-06-2026</t>
+  </si>
+  <si>
+    <t>4681001623182</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 1,5 спальное - "Кетеван" Универсал</t>
+  </si>
+  <si>
+    <t>4681001623175</t>
+  </si>
+  <si>
+    <t>Простыня круглая микросатин резинка 230х230х40 - "Небосвод"</t>
+  </si>
+  <si>
+    <t>4681001623168</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 145х215 - "Бенигно"</t>
+  </si>
+  <si>
+    <t>4681001623151</t>
+  </si>
+  <si>
+    <t>Простыня поплин 200х220 - Ясное небо</t>
+  </si>
+  <si>
+    <t>4681001623144</t>
+  </si>
+  <si>
+    <t>Простыня бязь 200х220 - "Теодор"</t>
+  </si>
+  <si>
+    <t>4681001623137</t>
+  </si>
+  <si>
+    <t>Простыня бязь 80х120 - 142 - Черный</t>
+  </si>
+  <si>
+    <t>4681001623120</t>
+  </si>
+  <si>
+    <t>Простыня бязь 80х120 - 142 - Сиреневый</t>
+  </si>
+  <si>
+    <t>4681001623113</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 280х280 - 140 - Белый 1х1</t>
+  </si>
+  <si>
+    <t>4681001623106</t>
+  </si>
+  <si>
+    <t>Наволочка сатин браш 40х60 - "Бежевый Коралл"</t>
+  </si>
+  <si>
+    <t>4681001623090</t>
+  </si>
+  <si>
+    <t>Простыня ранфорс резинка 160х200х30 - "Трюфельный шарм"</t>
+  </si>
+  <si>
+    <t>4681001623083</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 200х220х20 - 140 - Чернила 1х1</t>
+  </si>
+  <si>
+    <t>4681001623076</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок Евро резинка 160х200х30 - Белый</t>
+  </si>
+  <si>
+    <t>4681001623069</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро - Гестхаус Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001623052</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 200х220 - "Дювеля" 1х1</t>
+  </si>
+  <si>
+    <t>4681001623045</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 2 спальное - Голубой</t>
+  </si>
+  <si>
+    <t>4681001623038</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин Евро макси - М - 130 - Блю Маджента с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001623021</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 70х70 - 120 - Спелая малина</t>
+  </si>
+  <si>
+    <t>4681001623014</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 160х200х30 - 120 - Спелая малина</t>
+  </si>
+  <si>
+    <t>4681001623007</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 50х70 - 110 - "Ромбоцвет"</t>
+  </si>
+  <si>
+    <t>4681001622994</t>
+  </si>
+  <si>
+    <t>Наволочка перкаль 40х40 - 110 - "Ромбоцвет"</t>
+  </si>
+  <si>
+    <t>4681001622987</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х220 - Блу Скай</t>
+  </si>
+  <si>
+    <t>4681001622970</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 240х260 - Каштановый</t>
+  </si>
+  <si>
+    <t>4681001622963</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин семейное резинка 180х200х30 - "Хельми"</t>
   </si>
 </sst>
 </file>
@@ -85765,6 +85912,270 @@
         <v>10595</v>
       </c>
     </row>
+    <row r="5270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5270" t="s">
+        <v>10642</v>
+      </c>
+      <c r="B5270" t="s">
+        <v>10643</v>
+      </c>
+      <c r="C5270" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5271" t="s">
+        <v>10645</v>
+      </c>
+      <c r="B5271" t="s">
+        <v>10646</v>
+      </c>
+      <c r="C5271" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5272" t="s">
+        <v>10647</v>
+      </c>
+      <c r="B5272" t="s">
+        <v>10648</v>
+      </c>
+      <c r="C5272" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5273" t="s">
+        <v>10649</v>
+      </c>
+      <c r="B5273" t="s">
+        <v>10650</v>
+      </c>
+      <c r="C5273" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5274" t="s">
+        <v>10651</v>
+      </c>
+      <c r="B5274" t="s">
+        <v>10652</v>
+      </c>
+      <c r="C5274" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5275" t="s">
+        <v>10653</v>
+      </c>
+      <c r="B5275" t="s">
+        <v>10654</v>
+      </c>
+      <c r="C5275" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5276" t="s">
+        <v>10655</v>
+      </c>
+      <c r="B5276" t="s">
+        <v>10656</v>
+      </c>
+      <c r="C5276" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5277" t="s">
+        <v>10657</v>
+      </c>
+      <c r="B5277" t="s">
+        <v>10658</v>
+      </c>
+      <c r="C5277" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5278" t="s">
+        <v>10659</v>
+      </c>
+      <c r="B5278" t="s">
+        <v>10660</v>
+      </c>
+      <c r="C5278" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5279" t="s">
+        <v>10661</v>
+      </c>
+      <c r="B5279" t="s">
+        <v>10662</v>
+      </c>
+      <c r="C5279" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5280" t="s">
+        <v>10663</v>
+      </c>
+      <c r="B5280" t="s">
+        <v>10664</v>
+      </c>
+      <c r="C5280" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5281" t="s">
+        <v>10665</v>
+      </c>
+      <c r="B5281" t="s">
+        <v>10666</v>
+      </c>
+      <c r="C5281" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5282" t="s">
+        <v>10667</v>
+      </c>
+      <c r="B5282" t="s">
+        <v>10668</v>
+      </c>
+      <c r="C5282" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5283" t="s">
+        <v>10669</v>
+      </c>
+      <c r="B5283" t="s">
+        <v>10670</v>
+      </c>
+      <c r="C5283" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5284" t="s">
+        <v>10671</v>
+      </c>
+      <c r="B5284" t="s">
+        <v>10672</v>
+      </c>
+      <c r="C5284" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5285" t="s">
+        <v>10673</v>
+      </c>
+      <c r="B5285" t="s">
+        <v>10674</v>
+      </c>
+      <c r="C5285" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5286" t="s">
+        <v>10675</v>
+      </c>
+      <c r="B5286" t="s">
+        <v>10676</v>
+      </c>
+      <c r="C5286" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5287" t="s">
+        <v>10677</v>
+      </c>
+      <c r="B5287" t="s">
+        <v>10678</v>
+      </c>
+      <c r="C5287" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5288" t="s">
+        <v>10679</v>
+      </c>
+      <c r="B5288" t="s">
+        <v>10680</v>
+      </c>
+      <c r="C5288" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5289" t="s">
+        <v>10681</v>
+      </c>
+      <c r="B5289" t="s">
+        <v>10682</v>
+      </c>
+      <c r="C5289" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5290" t="s">
+        <v>10683</v>
+      </c>
+      <c r="B5290" t="s">
+        <v>10684</v>
+      </c>
+      <c r="C5290" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5291" t="s">
+        <v>10685</v>
+      </c>
+      <c r="B5291" t="s">
+        <v>10686</v>
+      </c>
+      <c r="C5291" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5292" t="s">
+        <v>10687</v>
+      </c>
+      <c r="B5292" t="s">
+        <v>10688</v>
+      </c>
+      <c r="C5292" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="5293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5293" t="s">
+        <v>10689</v>
+      </c>
+      <c r="B5293" t="s">
+        <v>10690</v>
+      </c>
+      <c r="C5293" t="s">
+        <v>10644</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14373" uniqueCount="10691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14427" uniqueCount="10728">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -32090,6 +32090,117 @@
   </si>
   <si>
     <t>КПБ Постельное бельё полисатин семейное резинка 180х200х30 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4681001623373</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин Евро-макси - Черный матовый</t>
+  </si>
+  <si>
+    <t>18-06-2026</t>
+  </si>
+  <si>
+    <t>4681001623366</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х20 - "Мортис"</t>
+  </si>
+  <si>
+    <t>4681001623359</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 160х200х40 - "Ночная Симфония"</t>
+  </si>
+  <si>
+    <t>4681001623342</t>
+  </si>
+  <si>
+    <t>Наволочка сатин 50х70 - 125 - Шоколадный птифур</t>
+  </si>
+  <si>
+    <t>4681001623335</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 240х260 - Льняной</t>
+  </si>
+  <si>
+    <t>4681001623328</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Зелёный Страйп"</t>
+  </si>
+  <si>
+    <t>4681001623311</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное резинка 160х200х30 - "Миндаль Страйп"</t>
+  </si>
+  <si>
+    <t>4681001623304</t>
+  </si>
+  <si>
+    <t>Простыня жаккард резинка 200х200х40 - Снежное королевство</t>
+  </si>
+  <si>
+    <t>4681001623298</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х50 - Розариум А+В</t>
+  </si>
+  <si>
+    <t>4681001623281</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 120х200х30 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4681001623274</t>
+  </si>
+  <si>
+    <t>Наволочка поплин 50х70 - Кружева на голубом</t>
+  </si>
+  <si>
+    <t>4681001623267</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - Морбидецца наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623250</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - "Флафи"</t>
+  </si>
+  <si>
+    <t>4681001623243</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - "Призрачная лагуна"</t>
+  </si>
+  <si>
+    <t>4681001623236</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - 4216 Серебро</t>
+  </si>
+  <si>
+    <t>4681001623229</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 70х70 - "Белава"</t>
+  </si>
+  <si>
+    <t>4681001623212</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Белава"</t>
+  </si>
+  <si>
+    <t>4681001623205</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 120х200х30 - "Белава"</t>
   </si>
 </sst>
 </file>
@@ -86176,6 +86287,204 @@
         <v>10644</v>
       </c>
     </row>
+    <row r="5294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5294" t="s">
+        <v>10691</v>
+      </c>
+      <c r="B5294" t="s">
+        <v>10692</v>
+      </c>
+      <c r="C5294" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5295" t="s">
+        <v>10694</v>
+      </c>
+      <c r="B5295" t="s">
+        <v>10695</v>
+      </c>
+      <c r="C5295" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5296" t="s">
+        <v>10696</v>
+      </c>
+      <c r="B5296" t="s">
+        <v>10697</v>
+      </c>
+      <c r="C5296" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5297" t="s">
+        <v>10698</v>
+      </c>
+      <c r="B5297" t="s">
+        <v>10699</v>
+      </c>
+      <c r="C5297" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5298" t="s">
+        <v>10700</v>
+      </c>
+      <c r="B5298" t="s">
+        <v>10701</v>
+      </c>
+      <c r="C5298" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5299" t="s">
+        <v>10702</v>
+      </c>
+      <c r="B5299" t="s">
+        <v>10703</v>
+      </c>
+      <c r="C5299" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5300" t="s">
+        <v>10704</v>
+      </c>
+      <c r="B5300" t="s">
+        <v>10705</v>
+      </c>
+      <c r="C5300" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5301" t="s">
+        <v>10706</v>
+      </c>
+      <c r="B5301" t="s">
+        <v>10707</v>
+      </c>
+      <c r="C5301" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5302" t="s">
+        <v>10708</v>
+      </c>
+      <c r="B5302" t="s">
+        <v>10709</v>
+      </c>
+      <c r="C5302" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5303" t="s">
+        <v>10710</v>
+      </c>
+      <c r="B5303" t="s">
+        <v>10711</v>
+      </c>
+      <c r="C5303" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5304" t="s">
+        <v>10712</v>
+      </c>
+      <c r="B5304" t="s">
+        <v>10713</v>
+      </c>
+      <c r="C5304" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5305" t="s">
+        <v>10714</v>
+      </c>
+      <c r="B5305" t="s">
+        <v>10715</v>
+      </c>
+      <c r="C5305" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5306" t="s">
+        <v>10716</v>
+      </c>
+      <c r="B5306" t="s">
+        <v>10717</v>
+      </c>
+      <c r="C5306" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5307" t="s">
+        <v>10718</v>
+      </c>
+      <c r="B5307" t="s">
+        <v>10719</v>
+      </c>
+      <c r="C5307" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5308" t="s">
+        <v>10720</v>
+      </c>
+      <c r="B5308" t="s">
+        <v>10721</v>
+      </c>
+      <c r="C5308" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5309" t="s">
+        <v>10722</v>
+      </c>
+      <c r="B5309" t="s">
+        <v>10723</v>
+      </c>
+      <c r="C5309" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5310" t="s">
+        <v>10724</v>
+      </c>
+      <c r="B5310" t="s">
+        <v>10725</v>
+      </c>
+      <c r="C5310" t="s">
+        <v>10693</v>
+      </c>
+    </row>
+    <row r="5311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5311" t="s">
+        <v>10726</v>
+      </c>
+      <c r="B5311" t="s">
+        <v>10727</v>
+      </c>
+      <c r="C5311" t="s">
+        <v>10693</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14427" uniqueCount="10728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14502" uniqueCount="10779">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -32201,6 +32201,159 @@
   </si>
   <si>
     <t>Простыня полисатин резинка 120х200х30 - "Белава"</t>
+  </si>
+  <si>
+    <t>4681001623625</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 300х300 - 4216 Серебро</t>
+  </si>
+  <si>
+    <t>19-06-2026</t>
+  </si>
+  <si>
+    <t>4681001623618</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - Блестящий миндаль</t>
+  </si>
+  <si>
+    <t>4681001623601</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль 1,5 спальное резинка 120х200х30 - "Чёрное масло" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623595</t>
+  </si>
+  <si>
+    <t>Наволочка бязь 60х60 - "Кетеван"</t>
+  </si>
+  <si>
+    <t>4681001623588</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил Евро резинка 160х200х30 - "Хризоколла" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623571</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х30 - "Мелиссит"</t>
+  </si>
+  <si>
+    <t>4681001623564</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 145х215 - "Арналдо"</t>
+  </si>
+  <si>
+    <t>4681001623557</t>
+  </si>
+  <si>
+    <t>Наволочка сатин твил 40х60 - "Арналдо"</t>
+  </si>
+  <si>
+    <t>4681001623540</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Золотой блеск"</t>
+  </si>
+  <si>
+    <t>4681001623533</t>
+  </si>
+  <si>
+    <t>Простыня поплин 220х240 - Санто Стефано</t>
+  </si>
+  <si>
+    <t>4681001623526</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное - Премиум ТС 320 "Лулу" Универсал</t>
+  </si>
+  <si>
+    <t>4681001623519</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - "Темный изумруд"</t>
+  </si>
+  <si>
+    <t>4681001623502</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 50х70 - Морской</t>
+  </si>
+  <si>
+    <t>4681001623496</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное - Тоша с 1 наволочкой 50х70</t>
+  </si>
+  <si>
+    <t>4681001623489</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное - "Лямур" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623472</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 220х240 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001623465</t>
+  </si>
+  <si>
+    <t>Пододеяльник варёный хлопок 220х240 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001623458</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 200х220 - "Глисса"</t>
+  </si>
+  <si>
+    <t>4681001623441</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро-макси - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001623434</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 150х200 - "Димитра"</t>
+  </si>
+  <si>
+    <t>4681001623427</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х30 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001623410</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное - Премиум ТС 320 Вишенка</t>
+  </si>
+  <si>
+    <t>4681001623403</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Осенний Сон"</t>
+  </si>
+  <si>
+    <t>4681001623397</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Осенний Сон"</t>
+  </si>
+  <si>
+    <t>4681001623380</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 220х240 - "Песочная роза"</t>
   </si>
 </sst>
 </file>
@@ -86485,6 +86638,281 @@
         <v>10693</v>
       </c>
     </row>
+    <row r="5312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5312" t="s">
+        <v>10728</v>
+      </c>
+      <c r="B5312" t="s">
+        <v>10729</v>
+      </c>
+      <c r="C5312" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5313" t="s">
+        <v>10731</v>
+      </c>
+      <c r="B5313" t="s">
+        <v>10732</v>
+      </c>
+      <c r="C5313" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5314" t="s">
+        <v>10733</v>
+      </c>
+      <c r="B5314" t="s">
+        <v>10734</v>
+      </c>
+      <c r="C5314" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5315" t="s">
+        <v>10735</v>
+      </c>
+      <c r="B5315" t="s">
+        <v>10736</v>
+      </c>
+      <c r="C5315" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5316" t="s">
+        <v>10737</v>
+      </c>
+      <c r="B5316" t="s">
+        <v>10738</v>
+      </c>
+      <c r="C5316" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5317" t="s">
+        <v>10739</v>
+      </c>
+      <c r="B5317" t="s">
+        <v>10740</v>
+      </c>
+      <c r="C5317" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5318" t="s">
+        <v>10741</v>
+      </c>
+      <c r="B5318" t="s">
+        <v>10742</v>
+      </c>
+      <c r="C5318" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5319" t="s">
+        <v>10743</v>
+      </c>
+      <c r="B5319" t="s">
+        <v>10744</v>
+      </c>
+      <c r="C5319" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5320" t="s">
+        <v>10745</v>
+      </c>
+      <c r="B5320" t="s">
+        <v>10746</v>
+      </c>
+      <c r="C5320" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5321" t="s">
+        <v>10747</v>
+      </c>
+      <c r="B5321" t="s">
+        <v>10748</v>
+      </c>
+      <c r="C5321" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5322" t="s">
+        <v>10749</v>
+      </c>
+      <c r="B5322" t="s">
+        <v>10750</v>
+      </c>
+      <c r="C5322" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5323" t="s">
+        <v>10751</v>
+      </c>
+      <c r="B5323" t="s">
+        <v>10752</v>
+      </c>
+      <c r="C5323" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5324" t="s">
+        <v>10753</v>
+      </c>
+      <c r="B5324" t="s">
+        <v>10754</v>
+      </c>
+      <c r="C5324" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5325" t="s">
+        <v>10755</v>
+      </c>
+      <c r="B5325" t="s">
+        <v>10756</v>
+      </c>
+      <c r="C5325" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5326" t="s">
+        <v>10757</v>
+      </c>
+      <c r="B5326" t="s">
+        <v>10758</v>
+      </c>
+      <c r="C5326" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5327" t="s">
+        <v>10759</v>
+      </c>
+      <c r="B5327" t="s">
+        <v>10760</v>
+      </c>
+      <c r="C5327" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5328" t="s">
+        <v>10761</v>
+      </c>
+      <c r="B5328" t="s">
+        <v>10762</v>
+      </c>
+      <c r="C5328" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5329" t="s">
+        <v>10763</v>
+      </c>
+      <c r="B5329" t="s">
+        <v>10764</v>
+      </c>
+      <c r="C5329" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5330" t="s">
+        <v>10765</v>
+      </c>
+      <c r="B5330" t="s">
+        <v>10766</v>
+      </c>
+      <c r="C5330" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5331" t="s">
+        <v>10767</v>
+      </c>
+      <c r="B5331" t="s">
+        <v>10768</v>
+      </c>
+      <c r="C5331" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5332" t="s">
+        <v>10769</v>
+      </c>
+      <c r="B5332" t="s">
+        <v>10770</v>
+      </c>
+      <c r="C5332" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5333" t="s">
+        <v>10771</v>
+      </c>
+      <c r="B5333" t="s">
+        <v>10772</v>
+      </c>
+      <c r="C5333" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5334" t="s">
+        <v>10773</v>
+      </c>
+      <c r="B5334" t="s">
+        <v>10774</v>
+      </c>
+      <c r="C5334" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5335" t="s">
+        <v>10775</v>
+      </c>
+      <c r="B5335" t="s">
+        <v>10776</v>
+      </c>
+      <c r="C5335" t="s">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="5336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5336" t="s">
+        <v>10777</v>
+      </c>
+      <c r="B5336" t="s">
+        <v>10778</v>
+      </c>
+      <c r="C5336" t="s">
+        <v>10730</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14502" uniqueCount="10779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14616" uniqueCount="10856">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -32354,6 +32354,237 @@
   </si>
   <si>
     <t>Простыня тенсель 220х240 - "Песочная роза"</t>
+  </si>
+  <si>
+    <t>4681001624004</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - Блестящий миндаль</t>
+  </si>
+  <si>
+    <t>20-06-2026</t>
+  </si>
+  <si>
+    <t>4681001623991</t>
+  </si>
+  <si>
+    <t>Простыня перкаль резинка 180х200х30 - 110 - Каори на зеленом</t>
+  </si>
+  <si>
+    <t>4681001623984</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 2 спальное резинка 140х200х30 - 120 - Серебристый металлик наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623977</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё перкаль 1,5 спальное на резинке 140х200х30 - М - 110 - Лунго с наволочками 50х70</t>
+  </si>
+  <si>
+    <t>4681001623960</t>
+  </si>
+  <si>
+    <t>Наволочка страйп-сатин 60х60 - 140 - Белый 3х3</t>
+  </si>
+  <si>
+    <t>4681001623953</t>
+  </si>
+  <si>
+    <t>Простыня сатин твил 200х220 - "Солнечные лучи"</t>
+  </si>
+  <si>
+    <t>4681001623946</t>
+  </si>
+  <si>
+    <t>Простыня бязь 200х220 - "Джуман"</t>
+  </si>
+  <si>
+    <t>4681001623939</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001623922</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - "Белый Страйп"</t>
+  </si>
+  <si>
+    <t>4681001623915</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 70х70 - "Золото короны"</t>
+  </si>
+  <si>
+    <t>4681001623908</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок Евро резинка 160х200х30 - "Стальная тень" (меланж) наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623892</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 260х260 - "Дюраль"</t>
+  </si>
+  <si>
+    <t>4681001623885</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 260х260 - 4216 Серебро</t>
+  </si>
+  <si>
+    <t>4681001623878</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 200х220х30 - Премиум ТС 320 Белый</t>
+  </si>
+  <si>
+    <t>4681001623861</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х220 - "Милда"</t>
+  </si>
+  <si>
+    <t>4681001623854</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 240х260 - "Милда"</t>
+  </si>
+  <si>
+    <t>4681001623847</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное - 130 - "Лавандула" 1х1</t>
+  </si>
+  <si>
+    <t>4681001623830</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное - "Альваро" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623823</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 2 спальное - "Парижский Шарм" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623816</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 2 спальное - "Бездна" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623809</t>
+  </si>
+  <si>
+    <t>Простыня бязь 80х120 - 120 - Спящий Мишка на бежевом</t>
+  </si>
+  <si>
+    <t>4681001623793</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - 140 - Голубой 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623786</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х220 - Архитектор</t>
+  </si>
+  <si>
+    <t>4681001623779</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х220 - "Ламы"</t>
+  </si>
+  <si>
+    <t>4681001623762</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 180х200х20 - "Графитовый Зигзаг"</t>
+  </si>
+  <si>
+    <t>4681001623755</t>
+  </si>
+  <si>
+    <t>Простыня жаккард резинка 160х200х30 - Палладион</t>
+  </si>
+  <si>
+    <t>4681001623748</t>
+  </si>
+  <si>
+    <t>Наволочка жаккард 50х70 - Палладион</t>
+  </si>
+  <si>
+    <t>4681001623731</t>
+  </si>
+  <si>
+    <t>Пододеяльник жаккард 150х200 - Палладион</t>
+  </si>
+  <si>
+    <t>4681001623724</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х20 - Грей блес</t>
+  </si>
+  <si>
+    <t>4681001623717</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 200х200 - Белый</t>
+  </si>
+  <si>
+    <t>4681001623700</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное - "Замороженный Перец" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001623694</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 90х200х20 - Аргентум</t>
+  </si>
+  <si>
+    <t>4681001623687</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 90х200х30 - Аргентум</t>
+  </si>
+  <si>
+    <t>4681001623670</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х30 - "Папоротниковый"</t>
+  </si>
+  <si>
+    <t>4681001623663</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 200х200х30 - "Аркашон"</t>
+  </si>
+  <si>
+    <t>4681001623656</t>
+  </si>
+  <si>
+    <t>Простыня бязь 150х220 - 142 - Белый Бамбук</t>
+  </si>
+  <si>
+    <t>4681001623649</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок резинка 200х220х40 - "Стальная тень" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001623632</t>
+  </si>
+  <si>
+    <t>Наволочка варёный хлопок 40х60 - "Вишня" (меланж)</t>
   </si>
 </sst>
 </file>
@@ -86913,6 +87144,424 @@
         <v>10730</v>
       </c>
     </row>
+    <row r="5337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5337" t="s">
+        <v>10779</v>
+      </c>
+      <c r="B5337" t="s">
+        <v>10780</v>
+      </c>
+      <c r="C5337" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5338" t="s">
+        <v>10782</v>
+      </c>
+      <c r="B5338" t="s">
+        <v>10783</v>
+      </c>
+      <c r="C5338" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5339" t="s">
+        <v>10784</v>
+      </c>
+      <c r="B5339" t="s">
+        <v>10785</v>
+      </c>
+      <c r="C5339" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5340" t="s">
+        <v>10786</v>
+      </c>
+      <c r="B5340" t="s">
+        <v>10787</v>
+      </c>
+      <c r="C5340" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5341" t="s">
+        <v>10788</v>
+      </c>
+      <c r="B5341" t="s">
+        <v>10789</v>
+      </c>
+      <c r="C5341" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5342" t="s">
+        <v>10790</v>
+      </c>
+      <c r="B5342" t="s">
+        <v>10791</v>
+      </c>
+      <c r="C5342" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5343" t="s">
+        <v>10792</v>
+      </c>
+      <c r="B5343" t="s">
+        <v>10793</v>
+      </c>
+      <c r="C5343" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5344" t="s">
+        <v>10794</v>
+      </c>
+      <c r="B5344" t="s">
+        <v>10795</v>
+      </c>
+      <c r="C5344" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5345" t="s">
+        <v>10796</v>
+      </c>
+      <c r="B5345" t="s">
+        <v>10797</v>
+      </c>
+      <c r="C5345" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5346" t="s">
+        <v>10798</v>
+      </c>
+      <c r="B5346" t="s">
+        <v>10799</v>
+      </c>
+      <c r="C5346" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5347" t="s">
+        <v>10800</v>
+      </c>
+      <c r="B5347" t="s">
+        <v>10801</v>
+      </c>
+      <c r="C5347" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5348" t="s">
+        <v>10802</v>
+      </c>
+      <c r="B5348" t="s">
+        <v>10803</v>
+      </c>
+      <c r="C5348" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5349" t="s">
+        <v>10804</v>
+      </c>
+      <c r="B5349" t="s">
+        <v>10805</v>
+      </c>
+      <c r="C5349" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5350" t="s">
+        <v>10806</v>
+      </c>
+      <c r="B5350" t="s">
+        <v>10807</v>
+      </c>
+      <c r="C5350" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5351" t="s">
+        <v>10808</v>
+      </c>
+      <c r="B5351" t="s">
+        <v>10809</v>
+      </c>
+      <c r="C5351" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5352" t="s">
+        <v>10810</v>
+      </c>
+      <c r="B5352" t="s">
+        <v>10811</v>
+      </c>
+      <c r="C5352" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5353" t="s">
+        <v>10812</v>
+      </c>
+      <c r="B5353" t="s">
+        <v>10813</v>
+      </c>
+      <c r="C5353" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5354" t="s">
+        <v>10814</v>
+      </c>
+      <c r="B5354" t="s">
+        <v>10815</v>
+      </c>
+      <c r="C5354" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5355" t="s">
+        <v>10816</v>
+      </c>
+      <c r="B5355" t="s">
+        <v>10817</v>
+      </c>
+      <c r="C5355" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5356" t="s">
+        <v>10818</v>
+      </c>
+      <c r="B5356" t="s">
+        <v>10819</v>
+      </c>
+      <c r="C5356" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5357" t="s">
+        <v>10820</v>
+      </c>
+      <c r="B5357" t="s">
+        <v>10821</v>
+      </c>
+      <c r="C5357" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5358" t="s">
+        <v>10822</v>
+      </c>
+      <c r="B5358" t="s">
+        <v>10823</v>
+      </c>
+      <c r="C5358" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5359" t="s">
+        <v>10824</v>
+      </c>
+      <c r="B5359" t="s">
+        <v>10825</v>
+      </c>
+      <c r="C5359" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5360" t="s">
+        <v>10826</v>
+      </c>
+      <c r="B5360" t="s">
+        <v>10827</v>
+      </c>
+      <c r="C5360" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5361" t="s">
+        <v>10828</v>
+      </c>
+      <c r="B5361" t="s">
+        <v>10829</v>
+      </c>
+      <c r="C5361" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5362" t="s">
+        <v>10830</v>
+      </c>
+      <c r="B5362" t="s">
+        <v>10831</v>
+      </c>
+      <c r="C5362" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5363" t="s">
+        <v>10832</v>
+      </c>
+      <c r="B5363" t="s">
+        <v>10833</v>
+      </c>
+      <c r="C5363" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5364" t="s">
+        <v>10834</v>
+      </c>
+      <c r="B5364" t="s">
+        <v>10835</v>
+      </c>
+      <c r="C5364" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5365" t="s">
+        <v>10836</v>
+      </c>
+      <c r="B5365" t="s">
+        <v>10837</v>
+      </c>
+      <c r="C5365" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5366" t="s">
+        <v>10838</v>
+      </c>
+      <c r="B5366" t="s">
+        <v>10839</v>
+      </c>
+      <c r="C5366" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5367" t="s">
+        <v>10840</v>
+      </c>
+      <c r="B5367" t="s">
+        <v>10841</v>
+      </c>
+      <c r="C5367" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5368" t="s">
+        <v>10842</v>
+      </c>
+      <c r="B5368" t="s">
+        <v>10843</v>
+      </c>
+      <c r="C5368" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5369" t="s">
+        <v>10844</v>
+      </c>
+      <c r="B5369" t="s">
+        <v>10845</v>
+      </c>
+      <c r="C5369" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5370" t="s">
+        <v>10846</v>
+      </c>
+      <c r="B5370" t="s">
+        <v>10847</v>
+      </c>
+      <c r="C5370" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5371" t="s">
+        <v>10848</v>
+      </c>
+      <c r="B5371" t="s">
+        <v>10849</v>
+      </c>
+      <c r="C5371" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5372" t="s">
+        <v>10850</v>
+      </c>
+      <c r="B5372" t="s">
+        <v>10851</v>
+      </c>
+      <c r="C5372" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5373" t="s">
+        <v>10852</v>
+      </c>
+      <c r="B5373" t="s">
+        <v>10853</v>
+      </c>
+      <c r="C5373" t="s">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="5374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5374" t="s">
+        <v>10854</v>
+      </c>
+      <c r="B5374" t="s">
+        <v>10855</v>
+      </c>
+      <c r="C5374" t="s">
+        <v>10781</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14616" uniqueCount="10856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14739" uniqueCount="10939">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -32585,6 +32585,255 @@
   </si>
   <si>
     <t>Наволочка варёный хлопок 40х60 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001624400</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь 2 спальное - "Айсу" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>21-06-2026</t>
+  </si>
+  <si>
+    <t>4681001624394</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 180х200х40 - "Триша"</t>
+  </si>
+  <si>
+    <t>4681001624387</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 145х215 - "Веселые Корги"</t>
+  </si>
+  <si>
+    <t>4681001624370</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 175х215 - "Серебряная Фантазия"</t>
+  </si>
+  <si>
+    <t>4681001624363</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 175х215 - "Ледяной Мрамор"</t>
+  </si>
+  <si>
+    <t>4681001624356</t>
+  </si>
+  <si>
+    <t>Пододеяльник жатка 175х215 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001624349</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 160х200х30 - Изумруд Эсмеральды</t>
+  </si>
+  <si>
+    <t>4681001624332</t>
+  </si>
+  <si>
+    <t>Простыня сатин 180х220 - 125 - Фисташка</t>
+  </si>
+  <si>
+    <t>4681001624325</t>
+  </si>
+  <si>
+    <t>Простыня бязь 300х300 - "Вэспер"</t>
+  </si>
+  <si>
+    <t>4681001624318</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 220х240 - "Кленовая зелень"</t>
+  </si>
+  <si>
+    <t>4681001624301</t>
+  </si>
+  <si>
+    <t>Простыня микросатин 280х280 - "Залив"</t>
+  </si>
+  <si>
+    <t>4681001624295</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - "Бриолен" 1х1</t>
+  </si>
+  <si>
+    <t>4681001624288</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 200х220 - Премиум ТС 320 Вишенка</t>
+  </si>
+  <si>
+    <t>4681001624271</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро резинка 160х200х30 - 80 - Витражи наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624264</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 140х200х30 - 135 - Фирюз 1х1</t>
+  </si>
+  <si>
+    <t>4681001624257</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - 135 - Фирюз 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624240</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё страйп-сатин 1,5 спальное резинка 140х200х30 - 130 - "Лавандула" 1х1 наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624233</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 125 - "Индиго" 1х1</t>
+  </si>
+  <si>
+    <t>4681001624226</t>
+  </si>
+  <si>
+    <t>Простыня варёный хлопок 300х300 - Какао с молоком</t>
+  </si>
+  <si>
+    <t>4681001624219</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 120х200х30 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001624202</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 150х200 - 135 - Углерод 1х1</t>
+  </si>
+  <si>
+    <t>4681001624196</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - Маренго</t>
+  </si>
+  <si>
+    <t>4681001624189</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 2 спальное резинка 160х200х30 - "Небосвод"</t>
+  </si>
+  <si>
+    <t>4681001624172</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 2 спальное резинка 160х200х30 - "Бездна"</t>
+  </si>
+  <si>
+    <t>4681001624165</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное резинка 120х200х30 - Премиум ТС 320 "Лиминал" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624158</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 140х200х30 - 80 - Витражи наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624141</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель семейное резинка 160х200х30 - Петроль</t>
+  </si>
+  <si>
+    <t>4681001624134</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 140х200х30 - "Аполлон" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624127</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё поплин 1,5 спальное резинка 120х200х30 - Городской стиль</t>
+  </si>
+  <si>
+    <t>4681001624110</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Миндаль Страйп"</t>
+  </si>
+  <si>
+    <t>4681001624103</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин резинка 90х200х40 - 130 - Полуночный ультрамарин 1х1</t>
+  </si>
+  <si>
+    <t>4681001624097</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное - "Алоха" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624080</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 1,5 спальное резинка 120х200х30 - Чериньола</t>
+  </si>
+  <si>
+    <t>4681001624073</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 240х260 - 125 - "Капучино" 1х1</t>
+  </si>
+  <si>
+    <t>4681001624066</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 120х200х30 - Кашемировая роза</t>
+  </si>
+  <si>
+    <t>4681001624059</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 120х200х20 - "Песочная роза"</t>
+  </si>
+  <si>
+    <t>4681001624042</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 145х215 - Розовая лаванда</t>
+  </si>
+  <si>
+    <t>4681001624035</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё бязь Евро резинка 160х200х30 - "Вэспер" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624028</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 40х60 - "Потягуш"</t>
+  </si>
+  <si>
+    <t>4681001624011</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 2 спальное резинка 140х200х30 - "Небосвод" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624417</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель 2 спальное - "Эрос"</t>
   </si>
 </sst>
 </file>
@@ -87562,6 +87811,457 @@
         <v>10781</v>
       </c>
     </row>
+    <row r="5375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5375" t="s">
+        <v>10856</v>
+      </c>
+      <c r="B5375" t="s">
+        <v>10857</v>
+      </c>
+      <c r="C5375" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5376" t="s">
+        <v>10859</v>
+      </c>
+      <c r="B5376" t="s">
+        <v>10860</v>
+      </c>
+      <c r="C5376" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5377" t="s">
+        <v>10861</v>
+      </c>
+      <c r="B5377" t="s">
+        <v>10862</v>
+      </c>
+      <c r="C5377" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5378" t="s">
+        <v>10863</v>
+      </c>
+      <c r="B5378" t="s">
+        <v>10864</v>
+      </c>
+      <c r="C5378" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5379" t="s">
+        <v>10865</v>
+      </c>
+      <c r="B5379" t="s">
+        <v>10866</v>
+      </c>
+      <c r="C5379" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5380" t="s">
+        <v>10867</v>
+      </c>
+      <c r="B5380" t="s">
+        <v>10868</v>
+      </c>
+      <c r="C5380" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5381" t="s">
+        <v>10869</v>
+      </c>
+      <c r="B5381" t="s">
+        <v>10870</v>
+      </c>
+      <c r="C5381" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5382" t="s">
+        <v>10871</v>
+      </c>
+      <c r="B5382" t="s">
+        <v>10872</v>
+      </c>
+      <c r="C5382" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5383" t="s">
+        <v>10873</v>
+      </c>
+      <c r="B5383" t="s">
+        <v>10874</v>
+      </c>
+      <c r="C5383" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5384" t="s">
+        <v>10875</v>
+      </c>
+      <c r="B5384" t="s">
+        <v>10876</v>
+      </c>
+      <c r="C5384" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5385" t="s">
+        <v>10877</v>
+      </c>
+      <c r="B5385" t="s">
+        <v>10878</v>
+      </c>
+      <c r="C5385" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5386" t="s">
+        <v>10879</v>
+      </c>
+      <c r="B5386" t="s">
+        <v>10880</v>
+      </c>
+      <c r="C5386" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5387" t="s">
+        <v>10881</v>
+      </c>
+      <c r="B5387" t="s">
+        <v>10882</v>
+      </c>
+      <c r="C5387" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5388" t="s">
+        <v>10883</v>
+      </c>
+      <c r="B5388" t="s">
+        <v>10884</v>
+      </c>
+      <c r="C5388" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5389" t="s">
+        <v>10885</v>
+      </c>
+      <c r="B5389" t="s">
+        <v>10886</v>
+      </c>
+      <c r="C5389" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5390" t="s">
+        <v>10887</v>
+      </c>
+      <c r="B5390" t="s">
+        <v>10888</v>
+      </c>
+      <c r="C5390" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5391" t="s">
+        <v>10889</v>
+      </c>
+      <c r="B5391" t="s">
+        <v>10890</v>
+      </c>
+      <c r="C5391" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5392" t="s">
+        <v>10891</v>
+      </c>
+      <c r="B5392" t="s">
+        <v>10892</v>
+      </c>
+      <c r="C5392" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5393" t="s">
+        <v>10893</v>
+      </c>
+      <c r="B5393" t="s">
+        <v>10894</v>
+      </c>
+      <c r="C5393" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5394" t="s">
+        <v>10895</v>
+      </c>
+      <c r="B5394" t="s">
+        <v>10896</v>
+      </c>
+      <c r="C5394" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5395" t="s">
+        <v>10897</v>
+      </c>
+      <c r="B5395" t="s">
+        <v>10898</v>
+      </c>
+      <c r="C5395" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5396" t="s">
+        <v>10899</v>
+      </c>
+      <c r="B5396" t="s">
+        <v>10900</v>
+      </c>
+      <c r="C5396" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5397" t="s">
+        <v>10901</v>
+      </c>
+      <c r="B5397" t="s">
+        <v>10902</v>
+      </c>
+      <c r="C5397" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5398" t="s">
+        <v>10903</v>
+      </c>
+      <c r="B5398" t="s">
+        <v>10904</v>
+      </c>
+      <c r="C5398" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5399" t="s">
+        <v>10905</v>
+      </c>
+      <c r="B5399" t="s">
+        <v>10906</v>
+      </c>
+      <c r="C5399" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5400" t="s">
+        <v>10907</v>
+      </c>
+      <c r="B5400" t="s">
+        <v>10908</v>
+      </c>
+      <c r="C5400" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5401" t="s">
+        <v>10909</v>
+      </c>
+      <c r="B5401" t="s">
+        <v>10910</v>
+      </c>
+      <c r="C5401" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5402" t="s">
+        <v>10911</v>
+      </c>
+      <c r="B5402" t="s">
+        <v>10912</v>
+      </c>
+      <c r="C5402" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5403" t="s">
+        <v>10913</v>
+      </c>
+      <c r="B5403" t="s">
+        <v>10914</v>
+      </c>
+      <c r="C5403" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5404" t="s">
+        <v>10915</v>
+      </c>
+      <c r="B5404" t="s">
+        <v>10916</v>
+      </c>
+      <c r="C5404" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5405" t="s">
+        <v>10917</v>
+      </c>
+      <c r="B5405" t="s">
+        <v>10918</v>
+      </c>
+      <c r="C5405" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5406" t="s">
+        <v>10919</v>
+      </c>
+      <c r="B5406" t="s">
+        <v>10920</v>
+      </c>
+      <c r="C5406" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5407" t="s">
+        <v>10921</v>
+      </c>
+      <c r="B5407" t="s">
+        <v>10922</v>
+      </c>
+      <c r="C5407" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5408" t="s">
+        <v>10923</v>
+      </c>
+      <c r="B5408" t="s">
+        <v>10924</v>
+      </c>
+      <c r="C5408" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5409" t="s">
+        <v>10925</v>
+      </c>
+      <c r="B5409" t="s">
+        <v>10926</v>
+      </c>
+      <c r="C5409" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5410" t="s">
+        <v>10927</v>
+      </c>
+      <c r="B5410" t="s">
+        <v>10928</v>
+      </c>
+      <c r="C5410" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5411" t="s">
+        <v>10929</v>
+      </c>
+      <c r="B5411" t="s">
+        <v>10930</v>
+      </c>
+      <c r="C5411" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5412" t="s">
+        <v>10931</v>
+      </c>
+      <c r="B5412" t="s">
+        <v>10932</v>
+      </c>
+      <c r="C5412" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5413" t="s">
+        <v>10933</v>
+      </c>
+      <c r="B5413" t="s">
+        <v>10934</v>
+      </c>
+      <c r="C5413" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5414" t="s">
+        <v>10935</v>
+      </c>
+      <c r="B5414" t="s">
+        <v>10936</v>
+      </c>
+      <c r="C5414" t="s">
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="5415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5415" t="s">
+        <v>10937</v>
+      </c>
+      <c r="B5415" t="s">
+        <v>10938</v>
+      </c>
+      <c r="C5415" t="s">
+        <v>10858</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14739" uniqueCount="10939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14829" uniqueCount="11000">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -32834,6 +32834,189 @@
   </si>
   <si>
     <t>КПБ Постельное бельё тенсель 2 спальное - "Эрос"</t>
+  </si>
+  <si>
+    <t>4681001624714</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё микросатин 1,5 спальное - "Страстный гранат" Универсал</t>
+  </si>
+  <si>
+    <t>23-06-2026</t>
+  </si>
+  <si>
+    <t>4681001624707</t>
+  </si>
+  <si>
+    <t>Простыня полисатин 300х300 - "Богумила"</t>
+  </si>
+  <si>
+    <t>4681001624691</t>
+  </si>
+  <si>
+    <t>Простыня страйп-сатин 180х220 - 140 - Агатовый серый 1х1</t>
+  </si>
+  <si>
+    <t>4681001624684</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 150х200 - "Лаззаро"</t>
+  </si>
+  <si>
+    <t>4681001624677</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё ранфорс 2 спальное резинка 140х200х30 - "Лазурный бриз"</t>
+  </si>
+  <si>
+    <t>4681001624660</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель Евро резинка 160х200х30 - "Песочная роза" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624653</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 120х200х30 - "Граус"</t>
+  </si>
+  <si>
+    <t>4681001624646</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 120х200х30 - "Вишня" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001624639</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё варёный хлопок 1,5 спальное резинка 120х200х30 - "Стальная тень" (меланж)</t>
+  </si>
+  <si>
+    <t>4681001624622</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 150х200 - "Русалки"</t>
+  </si>
+  <si>
+    <t>4681001624615</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка семейное резинка 180х200х30 - "Звёздный Вальс"</t>
+  </si>
+  <si>
+    <t>4681001624608</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 140х200х30 - 4247 Сирень</t>
+  </si>
+  <si>
+    <t>4681001624592</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин 1,5 спальное - "Русалки" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624585</t>
+  </si>
+  <si>
+    <t>Простыня жатка 300х300 - "Песочный Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001624578</t>
+  </si>
+  <si>
+    <t>Наволочка жатка 50х70 - "Песочный Рельеф"</t>
+  </si>
+  <si>
+    <t>4681001624561</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 40х60 - "Ледяная Мята"</t>
+  </si>
+  <si>
+    <t>4681001624554</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 175х215 - "Холодная элегия"</t>
+  </si>
+  <si>
+    <t>4681001624547</t>
+  </si>
+  <si>
+    <t>Наволочка тенсель 70х70 - "Туманная Ветвь"</t>
+  </si>
+  <si>
+    <t>4681001624530</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Серый Райнар"</t>
+  </si>
+  <si>
+    <t>4681001624523</t>
+  </si>
+  <si>
+    <t>Пододеяльник поплин 145х215 - "Дизанта"</t>
+  </si>
+  <si>
+    <t>4681001624516</t>
+  </si>
+  <si>
+    <t>Пододеяльник тенсель 150х200 - "Бархатный Букет"</t>
+  </si>
+  <si>
+    <t>4681001624509</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 50х70 - "Млада"</t>
+  </si>
+  <si>
+    <t>4681001624493</t>
+  </si>
+  <si>
+    <t>Наволочка полисатин 70х70 - "Млада"</t>
+  </si>
+  <si>
+    <t>4681001624486</t>
+  </si>
+  <si>
+    <t>Пододеяльник из перкаля 150 х 200 - М - 110 - Лунго</t>
+  </si>
+  <si>
+    <t>4681001624479</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 140х200х30 - "Хельми"</t>
+  </si>
+  <si>
+    <t>4681001624462</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 2 спальное резинка 140х200х30 - "Линнея"</t>
+  </si>
+  <si>
+    <t>4681001624455</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 2 спальное - "Поэзис"</t>
+  </si>
+  <si>
+    <t>4681001624448</t>
+  </si>
+  <si>
+    <t>Простыня тенсель 180х220 - Белый</t>
+  </si>
+  <si>
+    <t>4681001624431</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин 150х200 - Альбертус</t>
+  </si>
+  <si>
+    <t>4681001624424</t>
+  </si>
+  <si>
+    <t>Простыня полисатин резинка 140х200х20 - "Севим"</t>
   </si>
 </sst>
 </file>
@@ -88262,6 +88445,336 @@
         <v>10858</v>
       </c>
     </row>
+    <row r="5416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5416" t="s">
+        <v>10939</v>
+      </c>
+      <c r="B5416" t="s">
+        <v>10940</v>
+      </c>
+      <c r="C5416" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5417" t="s">
+        <v>10942</v>
+      </c>
+      <c r="B5417" t="s">
+        <v>10943</v>
+      </c>
+      <c r="C5417" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5418" t="s">
+        <v>10944</v>
+      </c>
+      <c r="B5418" t="s">
+        <v>10945</v>
+      </c>
+      <c r="C5418" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5419" t="s">
+        <v>10946</v>
+      </c>
+      <c r="B5419" t="s">
+        <v>10947</v>
+      </c>
+      <c r="C5419" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5420" t="s">
+        <v>10948</v>
+      </c>
+      <c r="B5420" t="s">
+        <v>10949</v>
+      </c>
+      <c r="C5420" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5421" t="s">
+        <v>10950</v>
+      </c>
+      <c r="B5421" t="s">
+        <v>10951</v>
+      </c>
+      <c r="C5421" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5422" t="s">
+        <v>10952</v>
+      </c>
+      <c r="B5422" t="s">
+        <v>10953</v>
+      </c>
+      <c r="C5422" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5423" t="s">
+        <v>10954</v>
+      </c>
+      <c r="B5423" t="s">
+        <v>10955</v>
+      </c>
+      <c r="C5423" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5424" t="s">
+        <v>10956</v>
+      </c>
+      <c r="B5424" t="s">
+        <v>10957</v>
+      </c>
+      <c r="C5424" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5425" t="s">
+        <v>10958</v>
+      </c>
+      <c r="B5425" t="s">
+        <v>10959</v>
+      </c>
+      <c r="C5425" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5426" t="s">
+        <v>10960</v>
+      </c>
+      <c r="B5426" t="s">
+        <v>10961</v>
+      </c>
+      <c r="C5426" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5427" t="s">
+        <v>10962</v>
+      </c>
+      <c r="B5427" t="s">
+        <v>10963</v>
+      </c>
+      <c r="C5427" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5428" t="s">
+        <v>10964</v>
+      </c>
+      <c r="B5428" t="s">
+        <v>10965</v>
+      </c>
+      <c r="C5428" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5429" t="s">
+        <v>10966</v>
+      </c>
+      <c r="B5429" t="s">
+        <v>10967</v>
+      </c>
+      <c r="C5429" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5430" t="s">
+        <v>10968</v>
+      </c>
+      <c r="B5430" t="s">
+        <v>10969</v>
+      </c>
+      <c r="C5430" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5431" t="s">
+        <v>10970</v>
+      </c>
+      <c r="B5431" t="s">
+        <v>10971</v>
+      </c>
+      <c r="C5431" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5432" t="s">
+        <v>10972</v>
+      </c>
+      <c r="B5432" t="s">
+        <v>10973</v>
+      </c>
+      <c r="C5432" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5433" t="s">
+        <v>10974</v>
+      </c>
+      <c r="B5433" t="s">
+        <v>10975</v>
+      </c>
+      <c r="C5433" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5434" t="s">
+        <v>10976</v>
+      </c>
+      <c r="B5434" t="s">
+        <v>10977</v>
+      </c>
+      <c r="C5434" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5435" t="s">
+        <v>10978</v>
+      </c>
+      <c r="B5435" t="s">
+        <v>10979</v>
+      </c>
+      <c r="C5435" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5436" t="s">
+        <v>10980</v>
+      </c>
+      <c r="B5436" t="s">
+        <v>10981</v>
+      </c>
+      <c r="C5436" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5437" t="s">
+        <v>10982</v>
+      </c>
+      <c r="B5437" t="s">
+        <v>10983</v>
+      </c>
+      <c r="C5437" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5438" t="s">
+        <v>10984</v>
+      </c>
+      <c r="B5438" t="s">
+        <v>10985</v>
+      </c>
+      <c r="C5438" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5439" t="s">
+        <v>10986</v>
+      </c>
+      <c r="B5439" t="s">
+        <v>10987</v>
+      </c>
+      <c r="C5439" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5440" t="s">
+        <v>10988</v>
+      </c>
+      <c r="B5440" t="s">
+        <v>10989</v>
+      </c>
+      <c r="C5440" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5441" t="s">
+        <v>10990</v>
+      </c>
+      <c r="B5441" t="s">
+        <v>10991</v>
+      </c>
+      <c r="C5441" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5442" t="s">
+        <v>10992</v>
+      </c>
+      <c r="B5442" t="s">
+        <v>10993</v>
+      </c>
+      <c r="C5442" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5443" t="s">
+        <v>10994</v>
+      </c>
+      <c r="B5443" t="s">
+        <v>10995</v>
+      </c>
+      <c r="C5443" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5444" t="s">
+        <v>10996</v>
+      </c>
+      <c r="B5444" t="s">
+        <v>10997</v>
+      </c>
+      <c r="C5444" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5445" t="s">
+        <v>10998</v>
+      </c>
+      <c r="B5445" t="s">
+        <v>10999</v>
+      </c>
+      <c r="C5445" t="s">
+        <v>10941</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14829" uniqueCount="11000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14847" uniqueCount="11012">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -33017,6 +33017,42 @@
   </si>
   <si>
     <t>Простыня полисатин резинка 140х200х20 - "Севим"</t>
+  </si>
+  <si>
+    <t>4681001624776</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё жатка 1,5 спальное резинка 90х200х30 - "Бирюзовый Рельеф" наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624769</t>
+  </si>
+  <si>
+    <t>Простыня сатин резинка 160х200х20 - 140 - Сияющая бирюза</t>
+  </si>
+  <si>
+    <t>4681001624752</t>
+  </si>
+  <si>
+    <t>Простыня жатка резинка 200х200х40 - "Звёздный туман"</t>
+  </si>
+  <si>
+    <t>4681001624745</t>
+  </si>
+  <si>
+    <t>Пододеяльник полисатин 200х200 - "Золти"</t>
+  </si>
+  <si>
+    <t>4681001624738</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин Евро-макси резинка 180х200х30 - "Зайга"</t>
+  </si>
+  <si>
+    <t>4681001624721</t>
+  </si>
+  <si>
+    <t>Пододеяльник страйп-сатин 200х220 - 135 - Платина 1х1</t>
   </si>
 </sst>
 </file>
@@ -88775,6 +88811,72 @@
         <v>10941</v>
       </c>
     </row>
+    <row r="5446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5446" t="s">
+        <v>11000</v>
+      </c>
+      <c r="B5446" t="s">
+        <v>11001</v>
+      </c>
+      <c r="C5446" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5447" t="s">
+        <v>11002</v>
+      </c>
+      <c r="B5447" t="s">
+        <v>11003</v>
+      </c>
+      <c r="C5447" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5448" t="s">
+        <v>11004</v>
+      </c>
+      <c r="B5448" t="s">
+        <v>11005</v>
+      </c>
+      <c r="C5448" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5449" t="s">
+        <v>11006</v>
+      </c>
+      <c r="B5449" t="s">
+        <v>11007</v>
+      </c>
+      <c r="C5449" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5450" t="s">
+        <v>11008</v>
+      </c>
+      <c r="B5450" t="s">
+        <v>11009</v>
+      </c>
+      <c r="C5450" t="s">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="5451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5451" t="s">
+        <v>11010</v>
+      </c>
+      <c r="B5451" t="s">
+        <v>11011</v>
+      </c>
+      <c r="C5451" t="s">
+        <v>10941</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>

--- a/public/Краткий отчет.xlsx
+++ b/public/Краткий отчет.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14847" uniqueCount="11012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14865" uniqueCount="11025">
   <si>
     <t>Краткий отчет по товарам</t>
   </si>
@@ -33053,6 +33053,45 @@
   </si>
   <si>
     <t>Пододеяльник страйп-сатин 200х220 - 135 - Платина 1х1</t>
+  </si>
+  <si>
+    <t>4681001624837</t>
+  </si>
+  <si>
+    <t>Пододеяльник сатин твил 200х200 - "Нева"</t>
+  </si>
+  <si>
+    <t>24-06-2026</t>
+  </si>
+  <si>
+    <t>4681001624820</t>
+  </si>
+  <si>
+    <t>Простыня жатка 280х280 - "Звёздный Вальс"</t>
+  </si>
+  <si>
+    <t>4681001624813</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё полисатин 1,5 спальное резинка 120х200х30 - "Аполлон"</t>
+  </si>
+  <si>
+    <t>4681001624806</t>
+  </si>
+  <si>
+    <t>Простыня тенсель резинка 80х200х20 - "Осенний Сон"</t>
+  </si>
+  <si>
+    <t>4681001624790</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё тенсель King Size резинка 200х200х30 - 4216 Серебро наволочки 50х70</t>
+  </si>
+  <si>
+    <t>4681001624783</t>
+  </si>
+  <si>
+    <t>КПБ Постельное бельё сатин твил 1,5 спальное резинка 120х200х30 - "Тянь-Шань"</t>
   </si>
 </sst>
 </file>
@@ -88877,6 +88916,72 @@
         <v>10941</v>
       </c>
     </row>
+    <row r="5452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5452" t="s">
+        <v>11012</v>
+      </c>
+      <c r="B5452" t="s">
+        <v>11013</v>
+      </c>
+      <c r="C5452" t="s">
+        <v>11014</v>
+      </c>
+    </row>
+    <row r="5453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5453" t="s">
+        <v>11015</v>
+      </c>
+      <c r="B5453" t="s">
+        <v>11016</v>
+      </c>
+      <c r="C5453" t="s">
+        <v>11014</v>
+      </c>
+    </row>
+    <row r="5454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5454" t="s">
+        <v>11017</v>
+      </c>
+      <c r="B5454" t="s">
+        <v>11018</v>
+      </c>
+      <c r="C5454" t="s">
+        <v>11014</v>
+      </c>
+    </row>
+    <row r="5455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5455" t="s">
+        <v>11019</v>
+      </c>
+      <c r="B5455" t="s">
+        <v>11020</v>
+      </c>
+      <c r="C5455" t="s">
+        <v>11014</v>
+      </c>
+    </row>
+    <row r="5456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5456" t="s">
+        <v>11021</v>
+      </c>
+      <c r="B5456" t="s">
+        <v>11022</v>
+      </c>
+      <c r="C5456" t="s">
+        <v>11014</v>
+      </c>
+    </row>
+    <row r="5457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5457" t="s">
+        <v>11023</v>
+      </c>
+      <c r="B5457" t="s">
+        <v>11024</v>
+      </c>
+      <c r="C5457" t="s">
+        <v>11014</v>
+      </c>
+    </row>
     <row r="7716" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7716" s="7"/>
     </row>
